--- a/salf/丙種職業安全衛生業務主管題庫.xlsx
+++ b/salf/丙種職業安全衛生業務主管題庫.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\drher\OneDrive\文件\GitHub\drher.github.io\salf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C736808-DCD8-472A-901B-3F3CBB27C9D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7B380F6-53FE-4917-9F13-31D0D4555A21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="15397" windowHeight="8751" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9764" uniqueCount="6959">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9764" uniqueCount="6960">
   <si>
     <t>題號</t>
   </si>
@@ -18399,9 +18399,6 @@
     <t>正確答案為第4項：「瓦特」。本題重點在於理解題幹所涉及的職業安全衛生管理、危害預防或法規要求。</t>
   </si>
   <si>
-    <t>(4 1227, 下列何種微垃可進入到人體肺泡區 ?</t>
-  </si>
-  <si>
     <t>落塵</t>
   </si>
   <si>
@@ -18409,9 +18406,6 @@
   </si>
   <si>
     <t>胸腔性微粒</t>
-  </si>
-  <si>
-    <t>可呼吸</t>
   </si>
   <si>
     <t>正確答案為第4項：「可呼吸」。本題重點在於理解題幹所涉及的職業安全衛生管理、危害預防或法規要求。</t>
@@ -20921,6 +20915,18 @@
   </si>
   <si>
     <t>水</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>下列何種微粒可進入到人體肺泡區 ?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>胸腔性微粒</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>可呼吸性微粒</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -23332,13 +23338,13 @@
         <v>70</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>6954</v>
+        <v>6952</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>387</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>6953</v>
+        <v>6951</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>388</v>
@@ -27270,13 +27276,13 @@
         <v>1079</v>
       </c>
       <c r="D207" s="2" t="s">
+        <v>6937</v>
+      </c>
+      <c r="E207" s="2" t="s">
+        <v>6938</v>
+      </c>
+      <c r="F207" s="2" t="s">
         <v>6939</v>
-      </c>
-      <c r="E207" s="2" t="s">
-        <v>6940</v>
-      </c>
-      <c r="F207" s="2" t="s">
-        <v>6941</v>
       </c>
       <c r="G207" s="3">
         <v>2</v>
@@ -37378,13 +37384,13 @@
         <v>556</v>
       </c>
       <c r="B557" s="2" t="s">
+        <v>6943</v>
+      </c>
+      <c r="C557" s="2" t="s">
+        <v>6944</v>
+      </c>
+      <c r="D557" s="2" t="s">
         <v>6945</v>
-      </c>
-      <c r="C557" s="2" t="s">
-        <v>6946</v>
-      </c>
-      <c r="D557" s="2" t="s">
-        <v>6947</v>
       </c>
       <c r="E557" s="2" t="s">
         <v>2916</v>
@@ -39753,7 +39759,7 @@
         <v>3333</v>
       </c>
       <c r="F640" s="2" t="s">
-        <v>6952</v>
+        <v>6950</v>
       </c>
       <c r="G640" s="3">
         <v>2</v>
@@ -42688,13 +42694,13 @@
         <v>3811</v>
       </c>
       <c r="C742" s="2" t="s">
-        <v>6942</v>
+        <v>6940</v>
       </c>
       <c r="D742" s="2" t="s">
         <v>3812</v>
       </c>
       <c r="E742" s="2" t="s">
-        <v>6943</v>
+        <v>6941</v>
       </c>
       <c r="F742" s="2" t="s">
         <v>51</v>
@@ -46707,7 +46713,7 @@
         <v>4493</v>
       </c>
       <c r="C881" s="2" t="s">
-        <v>6950</v>
+        <v>6948</v>
       </c>
       <c r="D881" s="2" t="s">
         <v>3124</v>
@@ -46716,7 +46722,7 @@
         <v>4494</v>
       </c>
       <c r="F881" s="2" t="s">
-        <v>6951</v>
+        <v>6949</v>
       </c>
       <c r="G881" s="3">
         <v>1</v>
@@ -47168,16 +47174,16 @@
         <v>896</v>
       </c>
       <c r="B897" s="2" t="s">
-        <v>6956</v>
+        <v>6954</v>
       </c>
       <c r="C897" s="2" t="s">
         <v>4271</v>
       </c>
       <c r="D897" s="2" t="s">
-        <v>6957</v>
+        <v>6955</v>
       </c>
       <c r="E897" s="2" t="s">
-        <v>6958</v>
+        <v>6956</v>
       </c>
       <c r="F897" s="2" t="s">
         <v>4360</v>
@@ -47941,7 +47947,7 @@
         <v>923</v>
       </c>
       <c r="B924" s="2" t="s">
-        <v>6955</v>
+        <v>6953</v>
       </c>
       <c r="C924" s="2" t="s">
         <v>3168</v>
@@ -48788,7 +48794,7 @@
         <v>4861</v>
       </c>
       <c r="F953" s="2" t="s">
-        <v>6944</v>
+        <v>6942</v>
       </c>
       <c r="G953" s="3">
         <v>3</v>
@@ -53542,10 +53548,10 @@
         <v>5662</v>
       </c>
       <c r="E1118" s="2" t="s">
-        <v>6949</v>
+        <v>6947</v>
       </c>
       <c r="F1118" s="2" t="s">
-        <v>6948</v>
+        <v>6946</v>
       </c>
       <c r="G1118" s="3">
         <v>4</v>
@@ -56685,25 +56691,25 @@
         <v>1227</v>
       </c>
       <c r="B1228" s="2" t="s">
+        <v>6957</v>
+      </c>
+      <c r="C1228" s="2" t="s">
         <v>6124</v>
       </c>
-      <c r="C1228" s="2" t="s">
+      <c r="D1228" s="2" t="s">
         <v>6125</v>
       </c>
-      <c r="D1228" s="2" t="s">
-        <v>6126</v>
-      </c>
       <c r="E1228" s="2" t="s">
-        <v>6127</v>
+        <v>6958</v>
       </c>
       <c r="F1228" s="2" t="s">
-        <v>6128</v>
+        <v>6959</v>
       </c>
       <c r="G1228" s="3">
         <v>4</v>
       </c>
       <c r="H1228" s="2" t="s">
-        <v>6129</v>
+        <v>6127</v>
       </c>
       <c r="I1228" s="2" t="s">
         <v>15</v>
@@ -56714,7 +56720,7 @@
         <v>1228</v>
       </c>
       <c r="B1229" s="2" t="s">
-        <v>6130</v>
+        <v>6128</v>
       </c>
       <c r="C1229" s="2" t="s">
         <v>5374</v>
@@ -56726,13 +56732,13 @@
         <v>5376</v>
       </c>
       <c r="F1229" s="2" t="s">
-        <v>6131</v>
+        <v>6129</v>
       </c>
       <c r="G1229" s="3">
         <v>3</v>
       </c>
       <c r="H1229" s="2" t="s">
-        <v>6132</v>
+        <v>6130</v>
       </c>
       <c r="I1229" s="2" t="s">
         <v>160</v>
@@ -56743,7 +56749,7 @@
         <v>1229</v>
       </c>
       <c r="B1230" s="2" t="s">
-        <v>6133</v>
+        <v>6131</v>
       </c>
       <c r="C1230" s="2" t="s">
         <v>5374</v>
@@ -56761,7 +56767,7 @@
         <v>4</v>
       </c>
       <c r="H1230" s="2" t="s">
-        <v>6134</v>
+        <v>6132</v>
       </c>
       <c r="I1230" s="2" t="s">
         <v>15</v>
@@ -56772,10 +56778,10 @@
         <v>1230</v>
       </c>
       <c r="B1231" s="2" t="s">
-        <v>6135</v>
+        <v>6133</v>
       </c>
       <c r="C1231" s="2" t="s">
-        <v>6136</v>
+        <v>6134</v>
       </c>
       <c r="D1231" s="2" t="s">
         <v>4918</v>
@@ -56788,7 +56794,7 @@
         <v>3</v>
       </c>
       <c r="H1231" s="2" t="s">
-        <v>6137</v>
+        <v>6135</v>
       </c>
       <c r="I1231" s="2" t="s">
         <v>15</v>
@@ -56799,25 +56805,25 @@
         <v>1231</v>
       </c>
       <c r="B1232" s="2" t="s">
+        <v>6136</v>
+      </c>
+      <c r="C1232" s="2" t="s">
+        <v>6137</v>
+      </c>
+      <c r="D1232" s="2" t="s">
         <v>6138</v>
       </c>
-      <c r="C1232" s="2" t="s">
+      <c r="E1232" s="2" t="s">
         <v>6139</v>
       </c>
-      <c r="D1232" s="2" t="s">
+      <c r="F1232" s="2" t="s">
         <v>6140</v>
-      </c>
-      <c r="E1232" s="2" t="s">
-        <v>6141</v>
-      </c>
-      <c r="F1232" s="2" t="s">
-        <v>6142</v>
       </c>
       <c r="G1232" s="3">
         <v>3</v>
       </c>
       <c r="H1232" s="2" t="s">
-        <v>6143</v>
+        <v>6141</v>
       </c>
       <c r="I1232" s="2" t="s">
         <v>15</v>
@@ -56828,25 +56834,25 @@
         <v>1232</v>
       </c>
       <c r="B1233" s="2" t="s">
+        <v>6142</v>
+      </c>
+      <c r="C1233" s="2" t="s">
+        <v>6143</v>
+      </c>
+      <c r="D1233" s="2" t="s">
         <v>6144</v>
-      </c>
-      <c r="C1233" s="2" t="s">
-        <v>6145</v>
-      </c>
-      <c r="D1233" s="2" t="s">
-        <v>6146</v>
       </c>
       <c r="E1233" s="2" t="s">
         <v>4023</v>
       </c>
       <c r="F1233" s="2" t="s">
-        <v>6147</v>
+        <v>6145</v>
       </c>
       <c r="G1233" s="3">
         <v>2</v>
       </c>
       <c r="H1233" s="2" t="s">
-        <v>6148</v>
+        <v>6146</v>
       </c>
       <c r="I1233" s="2" t="s">
         <v>15</v>
@@ -56857,25 +56863,25 @@
         <v>1233</v>
       </c>
       <c r="B1234" s="2" t="s">
-        <v>6149</v>
+        <v>6147</v>
       </c>
       <c r="C1234" s="2" t="s">
         <v>5338</v>
       </c>
       <c r="D1234" s="2" t="s">
-        <v>6150</v>
+        <v>6148</v>
       </c>
       <c r="E1234" s="2" t="s">
         <v>1588</v>
       </c>
       <c r="F1234" s="2" t="s">
-        <v>6151</v>
+        <v>6149</v>
       </c>
       <c r="G1234" s="3">
         <v>4</v>
       </c>
       <c r="H1234" s="2" t="s">
-        <v>6152</v>
+        <v>6150</v>
       </c>
       <c r="I1234" s="2" t="s">
         <v>160</v>
@@ -56886,25 +56892,25 @@
         <v>1234</v>
       </c>
       <c r="B1235" s="2" t="s">
+        <v>6151</v>
+      </c>
+      <c r="C1235" s="2" t="s">
+        <v>6152</v>
+      </c>
+      <c r="D1235" s="2" t="s">
         <v>6153</v>
-      </c>
-      <c r="C1235" s="2" t="s">
-        <v>6154</v>
-      </c>
-      <c r="D1235" s="2" t="s">
-        <v>6155</v>
       </c>
       <c r="E1235" s="2" t="s">
         <v>5932</v>
       </c>
       <c r="F1235" s="2" t="s">
-        <v>6156</v>
+        <v>6154</v>
       </c>
       <c r="G1235" s="3">
         <v>1</v>
       </c>
       <c r="H1235" s="2" t="s">
-        <v>6157</v>
+        <v>6155</v>
       </c>
       <c r="I1235" s="2" t="s">
         <v>15</v>
@@ -56915,25 +56921,25 @@
         <v>1235</v>
       </c>
       <c r="B1236" s="2" t="s">
+        <v>6156</v>
+      </c>
+      <c r="C1236" s="2" t="s">
+        <v>6157</v>
+      </c>
+      <c r="D1236" s="2" t="s">
         <v>6158</v>
-      </c>
-      <c r="C1236" s="2" t="s">
-        <v>6159</v>
-      </c>
-      <c r="D1236" s="2" t="s">
-        <v>6160</v>
       </c>
       <c r="E1236" s="2" t="s">
         <v>5567</v>
       </c>
       <c r="F1236" s="2" t="s">
-        <v>6161</v>
+        <v>6159</v>
       </c>
       <c r="G1236" s="3">
         <v>1</v>
       </c>
       <c r="H1236" s="2" t="s">
-        <v>6162</v>
+        <v>6160</v>
       </c>
       <c r="I1236" s="2" t="s">
         <v>15</v>
@@ -56944,25 +56950,25 @@
         <v>1236</v>
       </c>
       <c r="B1237" s="2" t="s">
+        <v>6161</v>
+      </c>
+      <c r="C1237" s="2" t="s">
+        <v>6162</v>
+      </c>
+      <c r="D1237" s="2" t="s">
         <v>6163</v>
       </c>
-      <c r="C1237" s="2" t="s">
+      <c r="E1237" s="2" t="s">
         <v>6164</v>
       </c>
-      <c r="D1237" s="2" t="s">
+      <c r="F1237" s="2" t="s">
         <v>6165</v>
-      </c>
-      <c r="E1237" s="2" t="s">
-        <v>6166</v>
-      </c>
-      <c r="F1237" s="2" t="s">
-        <v>6167</v>
       </c>
       <c r="G1237" s="3">
         <v>3</v>
       </c>
       <c r="H1237" s="2" t="s">
-        <v>6168</v>
+        <v>6166</v>
       </c>
       <c r="I1237" s="2" t="s">
         <v>160</v>
@@ -56973,25 +56979,25 @@
         <v>1237</v>
       </c>
       <c r="B1238" s="2" t="s">
-        <v>6169</v>
+        <v>6167</v>
       </c>
       <c r="C1238" s="2" t="s">
-        <v>6170</v>
+        <v>6168</v>
       </c>
       <c r="D1238" s="2" t="s">
         <v>5460</v>
       </c>
       <c r="E1238" s="2" t="s">
-        <v>6127</v>
+        <v>6126</v>
       </c>
       <c r="F1238" s="2" t="s">
-        <v>6171</v>
+        <v>6169</v>
       </c>
       <c r="G1238" s="3">
         <v>3</v>
       </c>
       <c r="H1238" s="2" t="s">
-        <v>6172</v>
+        <v>6170</v>
       </c>
       <c r="I1238" s="2" t="s">
         <v>15</v>
@@ -57002,16 +57008,16 @@
         <v>1238</v>
       </c>
       <c r="B1239" s="2" t="s">
-        <v>6173</v>
+        <v>6171</v>
       </c>
       <c r="C1239" s="2" t="s">
+        <v>6124</v>
+      </c>
+      <c r="D1239" s="2" t="s">
         <v>6125</v>
       </c>
-      <c r="D1239" s="2" t="s">
+      <c r="E1239" s="2" t="s">
         <v>6126</v>
-      </c>
-      <c r="E1239" s="2" t="s">
-        <v>6127</v>
       </c>
       <c r="F1239" s="2"/>
       <c r="G1239" s="3">
@@ -57029,25 +57035,25 @@
         <v>1239</v>
       </c>
       <c r="B1240" s="2" t="s">
+        <v>6172</v>
+      </c>
+      <c r="C1240" s="2" t="s">
+        <v>6173</v>
+      </c>
+      <c r="D1240" s="2" t="s">
         <v>6174</v>
       </c>
-      <c r="C1240" s="2" t="s">
+      <c r="E1240" s="2" t="s">
         <v>6175</v>
       </c>
-      <c r="D1240" s="2" t="s">
+      <c r="F1240" s="2" t="s">
         <v>6176</v>
-      </c>
-      <c r="E1240" s="2" t="s">
-        <v>6177</v>
-      </c>
-      <c r="F1240" s="2" t="s">
-        <v>6178</v>
       </c>
       <c r="G1240" s="3">
         <v>1</v>
       </c>
       <c r="H1240" s="2" t="s">
-        <v>6179</v>
+        <v>6177</v>
       </c>
       <c r="I1240" s="2" t="s">
         <v>15</v>
@@ -57058,25 +57064,25 @@
         <v>1240</v>
       </c>
       <c r="B1241" s="2" t="s">
+        <v>6178</v>
+      </c>
+      <c r="C1241" s="2" t="s">
+        <v>6179</v>
+      </c>
+      <c r="D1241" s="2" t="s">
         <v>6180</v>
-      </c>
-      <c r="C1241" s="2" t="s">
-        <v>6181</v>
-      </c>
-      <c r="D1241" s="2" t="s">
-        <v>6182</v>
       </c>
       <c r="E1241" s="2" t="s">
         <v>6104</v>
       </c>
       <c r="F1241" s="2" t="s">
-        <v>6183</v>
+        <v>6181</v>
       </c>
       <c r="G1241" s="3">
         <v>2</v>
       </c>
       <c r="H1241" s="2" t="s">
-        <v>6184</v>
+        <v>6182</v>
       </c>
       <c r="I1241" s="2" t="s">
         <v>15</v>
@@ -57087,7 +57093,7 @@
         <v>1241</v>
       </c>
       <c r="B1242" s="2" t="s">
-        <v>6185</v>
+        <v>6183</v>
       </c>
       <c r="C1242" s="2" t="s">
         <v>5376</v>
@@ -57099,13 +57105,13 @@
         <v>5375</v>
       </c>
       <c r="F1242" s="2" t="s">
-        <v>6131</v>
+        <v>6129</v>
       </c>
       <c r="G1242" s="3">
         <v>1</v>
       </c>
       <c r="H1242" s="2" t="s">
-        <v>6186</v>
+        <v>6184</v>
       </c>
       <c r="I1242" s="2" t="s">
         <v>15</v>
@@ -57116,25 +57122,25 @@
         <v>1242</v>
       </c>
       <c r="B1243" s="2" t="s">
+        <v>6185</v>
+      </c>
+      <c r="C1243" s="2" t="s">
+        <v>6186</v>
+      </c>
+      <c r="D1243" s="2" t="s">
         <v>6187</v>
       </c>
-      <c r="C1243" s="2" t="s">
+      <c r="E1243" s="2" t="s">
         <v>6188</v>
       </c>
-      <c r="D1243" s="2" t="s">
+      <c r="F1243" s="2" t="s">
         <v>6189</v>
-      </c>
-      <c r="E1243" s="2" t="s">
-        <v>6190</v>
-      </c>
-      <c r="F1243" s="2" t="s">
-        <v>6191</v>
       </c>
       <c r="G1243" s="3">
         <v>4</v>
       </c>
       <c r="H1243" s="2" t="s">
-        <v>6192</v>
+        <v>6190</v>
       </c>
       <c r="I1243" s="2" t="s">
         <v>15</v>
@@ -57145,25 +57151,25 @@
         <v>1243</v>
       </c>
       <c r="B1244" s="2" t="s">
+        <v>6191</v>
+      </c>
+      <c r="C1244" s="2" t="s">
+        <v>6192</v>
+      </c>
+      <c r="D1244" s="2" t="s">
         <v>6193</v>
-      </c>
-      <c r="C1244" s="2" t="s">
-        <v>6194</v>
-      </c>
-      <c r="D1244" s="2" t="s">
-        <v>6195</v>
       </c>
       <c r="E1244" s="2" t="s">
         <v>4417</v>
       </c>
       <c r="F1244" s="2" t="s">
-        <v>6196</v>
+        <v>6194</v>
       </c>
       <c r="G1244" s="3">
         <v>4</v>
       </c>
       <c r="H1244" s="2" t="s">
-        <v>6197</v>
+        <v>6195</v>
       </c>
       <c r="I1244" s="2" t="s">
         <v>15</v>
@@ -57174,25 +57180,25 @@
         <v>1244</v>
       </c>
       <c r="B1245" s="2" t="s">
+        <v>6196</v>
+      </c>
+      <c r="C1245" s="2" t="s">
+        <v>6197</v>
+      </c>
+      <c r="D1245" s="2" t="s">
         <v>6198</v>
       </c>
-      <c r="C1245" s="2" t="s">
+      <c r="E1245" s="2" t="s">
         <v>6199</v>
       </c>
-      <c r="D1245" s="2" t="s">
+      <c r="F1245" s="2" t="s">
         <v>6200</v>
-      </c>
-      <c r="E1245" s="2" t="s">
-        <v>6201</v>
-      </c>
-      <c r="F1245" s="2" t="s">
-        <v>6202</v>
       </c>
       <c r="G1245" s="3">
         <v>2</v>
       </c>
       <c r="H1245" s="2" t="s">
-        <v>6203</v>
+        <v>6201</v>
       </c>
       <c r="I1245" s="2" t="s">
         <v>160</v>
@@ -57203,10 +57209,10 @@
         <v>1245</v>
       </c>
       <c r="B1246" s="2" t="s">
-        <v>6204</v>
+        <v>6202</v>
       </c>
       <c r="C1246" s="2" t="s">
-        <v>6205</v>
+        <v>6203</v>
       </c>
       <c r="D1246" s="2" t="s">
         <v>5761</v>
@@ -57215,13 +57221,13 @@
         <v>1158</v>
       </c>
       <c r="F1246" s="2" t="s">
-        <v>6206</v>
+        <v>6204</v>
       </c>
       <c r="G1246" s="3">
         <v>4</v>
       </c>
       <c r="H1246" s="2" t="s">
-        <v>6207</v>
+        <v>6205</v>
       </c>
       <c r="I1246" s="2" t="s">
         <v>15</v>
@@ -57232,25 +57238,25 @@
         <v>1246</v>
       </c>
       <c r="B1247" s="2" t="s">
+        <v>6206</v>
+      </c>
+      <c r="C1247" s="2" t="s">
+        <v>6207</v>
+      </c>
+      <c r="D1247" s="2" t="s">
         <v>6208</v>
       </c>
-      <c r="C1247" s="2" t="s">
+      <c r="E1247" s="2" t="s">
         <v>6209</v>
       </c>
-      <c r="D1247" s="2" t="s">
+      <c r="F1247" s="2" t="s">
         <v>6210</v>
-      </c>
-      <c r="E1247" s="2" t="s">
-        <v>6211</v>
-      </c>
-      <c r="F1247" s="2" t="s">
-        <v>6212</v>
       </c>
       <c r="G1247" s="3">
         <v>4</v>
       </c>
       <c r="H1247" s="2" t="s">
-        <v>6213</v>
+        <v>6211</v>
       </c>
       <c r="I1247" s="2" t="s">
         <v>15</v>
@@ -57261,7 +57267,7 @@
         <v>1247</v>
       </c>
       <c r="B1248" s="2" t="s">
-        <v>6214</v>
+        <v>6212</v>
       </c>
       <c r="C1248" s="2" t="s">
         <v>4270</v>
@@ -57270,7 +57276,7 @@
         <v>6116</v>
       </c>
       <c r="E1248" s="2" t="s">
-        <v>6215</v>
+        <v>6213</v>
       </c>
       <c r="F1248" s="2" t="s">
         <v>6117</v>
@@ -57290,25 +57296,25 @@
         <v>1248</v>
       </c>
       <c r="B1249" s="2" t="s">
+        <v>6214</v>
+      </c>
+      <c r="C1249" s="2" t="s">
+        <v>6215</v>
+      </c>
+      <c r="D1249" s="2" t="s">
         <v>6216</v>
       </c>
-      <c r="C1249" s="2" t="s">
+      <c r="E1249" s="2" t="s">
         <v>6217</v>
       </c>
-      <c r="D1249" s="2" t="s">
+      <c r="F1249" s="2" t="s">
         <v>6218</v>
-      </c>
-      <c r="E1249" s="2" t="s">
-        <v>6219</v>
-      </c>
-      <c r="F1249" s="2" t="s">
-        <v>6220</v>
       </c>
       <c r="G1249" s="3">
         <v>3</v>
       </c>
       <c r="H1249" s="2" t="s">
-        <v>6221</v>
+        <v>6219</v>
       </c>
       <c r="I1249" s="2" t="s">
         <v>15</v>
@@ -57319,25 +57325,25 @@
         <v>1249</v>
       </c>
       <c r="B1250" s="2" t="s">
+        <v>6220</v>
+      </c>
+      <c r="C1250" s="2" t="s">
+        <v>6221</v>
+      </c>
+      <c r="D1250" s="2" t="s">
         <v>6222</v>
       </c>
-      <c r="C1250" s="2" t="s">
+      <c r="E1250" s="2" t="s">
         <v>6223</v>
       </c>
-      <c r="D1250" s="2" t="s">
+      <c r="F1250" s="2" t="s">
         <v>6224</v>
-      </c>
-      <c r="E1250" s="2" t="s">
-        <v>6225</v>
-      </c>
-      <c r="F1250" s="2" t="s">
-        <v>6226</v>
       </c>
       <c r="G1250" s="3">
         <v>2</v>
       </c>
       <c r="H1250" s="2" t="s">
-        <v>6227</v>
+        <v>6225</v>
       </c>
       <c r="I1250" s="2" t="s">
         <v>15</v>
@@ -57348,25 +57354,25 @@
         <v>1250</v>
       </c>
       <c r="B1251" s="2" t="s">
+        <v>6226</v>
+      </c>
+      <c r="C1251" s="2" t="s">
+        <v>6227</v>
+      </c>
+      <c r="D1251" s="2" t="s">
         <v>6228</v>
       </c>
-      <c r="C1251" s="2" t="s">
+      <c r="E1251" s="2" t="s">
         <v>6229</v>
       </c>
-      <c r="D1251" s="2" t="s">
+      <c r="F1251" s="2" t="s">
         <v>6230</v>
-      </c>
-      <c r="E1251" s="2" t="s">
-        <v>6231</v>
-      </c>
-      <c r="F1251" s="2" t="s">
-        <v>6232</v>
       </c>
       <c r="G1251" s="3">
         <v>4</v>
       </c>
       <c r="H1251" s="2" t="s">
-        <v>6233</v>
+        <v>6231</v>
       </c>
       <c r="I1251" s="2" t="s">
         <v>15</v>
@@ -57377,25 +57383,25 @@
         <v>1251</v>
       </c>
       <c r="B1252" s="2" t="s">
+        <v>6232</v>
+      </c>
+      <c r="C1252" s="2" t="s">
+        <v>6233</v>
+      </c>
+      <c r="D1252" s="2" t="s">
         <v>6234</v>
       </c>
-      <c r="C1252" s="2" t="s">
+      <c r="E1252" s="2" t="s">
         <v>6235</v>
       </c>
-      <c r="D1252" s="2" t="s">
+      <c r="F1252" s="2" t="s">
         <v>6236</v>
-      </c>
-      <c r="E1252" s="2" t="s">
-        <v>6237</v>
-      </c>
-      <c r="F1252" s="2" t="s">
-        <v>6238</v>
       </c>
       <c r="G1252" s="3">
         <v>1</v>
       </c>
       <c r="H1252" s="2" t="s">
-        <v>6239</v>
+        <v>6237</v>
       </c>
       <c r="I1252" s="2" t="s">
         <v>15</v>
@@ -57406,25 +57412,25 @@
         <v>1252</v>
       </c>
       <c r="B1253" s="2" t="s">
+        <v>6238</v>
+      </c>
+      <c r="C1253" s="2" t="s">
+        <v>6239</v>
+      </c>
+      <c r="D1253" s="2" t="s">
         <v>6240</v>
       </c>
-      <c r="C1253" s="2" t="s">
+      <c r="E1253" s="2" t="s">
         <v>6241</v>
       </c>
-      <c r="D1253" s="2" t="s">
+      <c r="F1253" s="2" t="s">
         <v>6242</v>
-      </c>
-      <c r="E1253" s="2" t="s">
-        <v>6243</v>
-      </c>
-      <c r="F1253" s="2" t="s">
-        <v>6244</v>
       </c>
       <c r="G1253" s="3">
         <v>2</v>
       </c>
       <c r="H1253" s="2" t="s">
-        <v>6245</v>
+        <v>6243</v>
       </c>
       <c r="I1253" s="2" t="s">
         <v>15</v>
@@ -57435,25 +57441,25 @@
         <v>1253</v>
       </c>
       <c r="B1254" s="2" t="s">
-        <v>6246</v>
+        <v>6244</v>
       </c>
       <c r="C1254" s="2" t="s">
         <v>4491</v>
       </c>
       <c r="D1254" s="2" t="s">
+        <v>6245</v>
+      </c>
+      <c r="E1254" s="2" t="s">
+        <v>6246</v>
+      </c>
+      <c r="F1254" s="2" t="s">
         <v>6247</v>
-      </c>
-      <c r="E1254" s="2" t="s">
-        <v>6248</v>
-      </c>
-      <c r="F1254" s="2" t="s">
-        <v>6249</v>
       </c>
       <c r="G1254" s="3">
         <v>2</v>
       </c>
       <c r="H1254" s="2" t="s">
-        <v>6250</v>
+        <v>6248</v>
       </c>
       <c r="I1254" s="2" t="s">
         <v>167</v>
@@ -57464,25 +57470,25 @@
         <v>1254</v>
       </c>
       <c r="B1255" s="2" t="s">
+        <v>6249</v>
+      </c>
+      <c r="C1255" s="2" t="s">
+        <v>6250</v>
+      </c>
+      <c r="D1255" s="2" t="s">
         <v>6251</v>
       </c>
-      <c r="C1255" s="2" t="s">
+      <c r="E1255" s="2" t="s">
         <v>6252</v>
       </c>
-      <c r="D1255" s="2" t="s">
+      <c r="F1255" s="2" t="s">
         <v>6253</v>
-      </c>
-      <c r="E1255" s="2" t="s">
-        <v>6254</v>
-      </c>
-      <c r="F1255" s="2" t="s">
-        <v>6255</v>
       </c>
       <c r="G1255" s="3">
         <v>2</v>
       </c>
       <c r="H1255" s="2" t="s">
-        <v>6256</v>
+        <v>6254</v>
       </c>
       <c r="I1255" s="2" t="s">
         <v>167</v>
@@ -57493,7 +57499,7 @@
         <v>1255</v>
       </c>
       <c r="B1256" s="2" t="s">
-        <v>6257</v>
+        <v>6255</v>
       </c>
       <c r="C1256" s="2" t="s">
         <v>523</v>
@@ -57511,7 +57517,7 @@
         <v>3</v>
       </c>
       <c r="H1256" s="2" t="s">
-        <v>6258</v>
+        <v>6256</v>
       </c>
       <c r="I1256" s="2" t="s">
         <v>167</v>
@@ -57522,25 +57528,25 @@
         <v>1256</v>
       </c>
       <c r="B1257" s="2" t="s">
+        <v>6257</v>
+      </c>
+      <c r="C1257" s="2" t="s">
+        <v>6258</v>
+      </c>
+      <c r="D1257" s="2" t="s">
         <v>6259</v>
       </c>
-      <c r="C1257" s="2" t="s">
+      <c r="E1257" s="2" t="s">
         <v>6260</v>
       </c>
-      <c r="D1257" s="2" t="s">
+      <c r="F1257" s="2" t="s">
         <v>6261</v>
-      </c>
-      <c r="E1257" s="2" t="s">
-        <v>6262</v>
-      </c>
-      <c r="F1257" s="2" t="s">
-        <v>6263</v>
       </c>
       <c r="G1257" s="3">
         <v>3</v>
       </c>
       <c r="H1257" s="2" t="s">
-        <v>6264</v>
+        <v>6262</v>
       </c>
       <c r="I1257" s="2" t="s">
         <v>167</v>
@@ -57551,25 +57557,25 @@
         <v>1257</v>
       </c>
       <c r="B1258" s="2" t="s">
+        <v>6263</v>
+      </c>
+      <c r="C1258" s="2" t="s">
+        <v>6264</v>
+      </c>
+      <c r="D1258" s="2" t="s">
         <v>6265</v>
       </c>
-      <c r="C1258" s="2" t="s">
+      <c r="E1258" s="2" t="s">
         <v>6266</v>
       </c>
-      <c r="D1258" s="2" t="s">
+      <c r="F1258" s="2" t="s">
         <v>6267</v>
-      </c>
-      <c r="E1258" s="2" t="s">
-        <v>6268</v>
-      </c>
-      <c r="F1258" s="2" t="s">
-        <v>6269</v>
       </c>
       <c r="G1258" s="3">
         <v>4</v>
       </c>
       <c r="H1258" s="2" t="s">
-        <v>6270</v>
+        <v>6268</v>
       </c>
       <c r="I1258" s="2" t="s">
         <v>167</v>
@@ -57580,7 +57586,7 @@
         <v>1258</v>
       </c>
       <c r="B1259" s="2" t="s">
-        <v>6271</v>
+        <v>6269</v>
       </c>
       <c r="C1259" s="2" t="s">
         <v>255</v>
@@ -57592,13 +57598,13 @@
         <v>257</v>
       </c>
       <c r="F1259" s="2" t="s">
-        <v>6272</v>
+        <v>6270</v>
       </c>
       <c r="G1259" s="3">
         <v>3</v>
       </c>
       <c r="H1259" s="2" t="s">
-        <v>6273</v>
+        <v>6271</v>
       </c>
       <c r="I1259" s="2" t="s">
         <v>167</v>
@@ -57609,7 +57615,7 @@
         <v>1259</v>
       </c>
       <c r="B1260" s="2" t="s">
-        <v>6274</v>
+        <v>6272</v>
       </c>
       <c r="C1260" s="2" t="s">
         <v>257</v>
@@ -57618,7 +57624,7 @@
         <v>255</v>
       </c>
       <c r="E1260" s="2" t="s">
-        <v>6272</v>
+        <v>6270</v>
       </c>
       <c r="F1260" s="2" t="s">
         <v>256</v>
@@ -57627,7 +57633,7 @@
         <v>3</v>
       </c>
       <c r="H1260" s="2" t="s">
-        <v>6275</v>
+        <v>6273</v>
       </c>
       <c r="I1260" s="2" t="s">
         <v>167</v>
@@ -57638,7 +57644,7 @@
         <v>1260</v>
       </c>
       <c r="B1261" s="2" t="s">
-        <v>6276</v>
+        <v>6274</v>
       </c>
       <c r="C1261" s="2" t="s">
         <v>524</v>
@@ -57656,7 +57662,7 @@
         <v>4</v>
       </c>
       <c r="H1261" s="2" t="s">
-        <v>6277</v>
+        <v>6275</v>
       </c>
       <c r="I1261" s="2" t="s">
         <v>167</v>
@@ -57667,25 +57673,25 @@
         <v>1261</v>
       </c>
       <c r="B1262" s="2" t="s">
+        <v>6276</v>
+      </c>
+      <c r="C1262" s="2" t="s">
+        <v>6277</v>
+      </c>
+      <c r="D1262" s="2" t="s">
         <v>6278</v>
       </c>
-      <c r="C1262" s="2" t="s">
+      <c r="E1262" s="2" t="s">
         <v>6279</v>
       </c>
-      <c r="D1262" s="2" t="s">
+      <c r="F1262" s="2" t="s">
         <v>6280</v>
-      </c>
-      <c r="E1262" s="2" t="s">
-        <v>6281</v>
-      </c>
-      <c r="F1262" s="2" t="s">
-        <v>6282</v>
       </c>
       <c r="G1262" s="3">
         <v>3</v>
       </c>
       <c r="H1262" s="2" t="s">
-        <v>6283</v>
+        <v>6281</v>
       </c>
       <c r="I1262" s="2" t="s">
         <v>15</v>
@@ -57696,25 +57702,25 @@
         <v>1262</v>
       </c>
       <c r="B1263" s="2" t="s">
+        <v>6282</v>
+      </c>
+      <c r="C1263" s="2" t="s">
+        <v>6283</v>
+      </c>
+      <c r="D1263" s="2" t="s">
         <v>6284</v>
       </c>
-      <c r="C1263" s="2" t="s">
+      <c r="E1263" s="2" t="s">
         <v>6285</v>
       </c>
-      <c r="D1263" s="2" t="s">
+      <c r="F1263" s="2" t="s">
         <v>6286</v>
-      </c>
-      <c r="E1263" s="2" t="s">
-        <v>6287</v>
-      </c>
-      <c r="F1263" s="2" t="s">
-        <v>6288</v>
       </c>
       <c r="G1263" s="3">
         <v>3</v>
       </c>
       <c r="H1263" s="2" t="s">
-        <v>6289</v>
+        <v>6287</v>
       </c>
       <c r="I1263" s="2" t="s">
         <v>15</v>
@@ -57725,25 +57731,25 @@
         <v>1263</v>
       </c>
       <c r="B1264" s="2" t="s">
+        <v>6288</v>
+      </c>
+      <c r="C1264" s="2" t="s">
+        <v>6289</v>
+      </c>
+      <c r="D1264" s="2" t="s">
         <v>6290</v>
       </c>
-      <c r="C1264" s="2" t="s">
+      <c r="E1264" s="2" t="s">
         <v>6291</v>
       </c>
-      <c r="D1264" s="2" t="s">
+      <c r="F1264" s="2" t="s">
         <v>6292</v>
-      </c>
-      <c r="E1264" s="2" t="s">
-        <v>6293</v>
-      </c>
-      <c r="F1264" s="2" t="s">
-        <v>6294</v>
       </c>
       <c r="G1264" s="3">
         <v>4</v>
       </c>
       <c r="H1264" s="2" t="s">
-        <v>6295</v>
+        <v>6293</v>
       </c>
       <c r="I1264" s="2" t="s">
         <v>15</v>
@@ -57754,23 +57760,23 @@
         <v>1264</v>
       </c>
       <c r="B1265" s="2" t="s">
+        <v>6294</v>
+      </c>
+      <c r="C1265" s="2" t="s">
+        <v>6295</v>
+      </c>
+      <c r="D1265" s="2" t="s">
         <v>6296</v>
       </c>
-      <c r="C1265" s="2" t="s">
+      <c r="E1265" s="2" t="s">
         <v>6297</v>
-      </c>
-      <c r="D1265" s="2" t="s">
-        <v>6298</v>
-      </c>
-      <c r="E1265" s="2" t="s">
-        <v>6299</v>
       </c>
       <c r="F1265" s="2"/>
       <c r="G1265" s="3">
         <v>3</v>
       </c>
       <c r="H1265" s="2" t="s">
-        <v>6300</v>
+        <v>6298</v>
       </c>
       <c r="I1265" s="2" t="s">
         <v>15</v>
@@ -57781,25 +57787,25 @@
         <v>1265</v>
       </c>
       <c r="B1266" s="2" t="s">
-        <v>6301</v>
+        <v>6299</v>
       </c>
       <c r="C1266" s="2" t="s">
-        <v>6302</v>
+        <v>6300</v>
       </c>
       <c r="D1266" s="2" t="s">
         <v>6069</v>
       </c>
       <c r="E1266" s="2" t="s">
-        <v>6303</v>
+        <v>6301</v>
       </c>
       <c r="F1266" s="2" t="s">
-        <v>6304</v>
+        <v>6302</v>
       </c>
       <c r="G1266" s="3">
         <v>4</v>
       </c>
       <c r="H1266" s="2" t="s">
-        <v>6305</v>
+        <v>6303</v>
       </c>
       <c r="I1266" s="2" t="s">
         <v>15</v>
@@ -57810,25 +57816,25 @@
         <v>1266</v>
       </c>
       <c r="B1267" s="2" t="s">
+        <v>6304</v>
+      </c>
+      <c r="C1267" s="2" t="s">
+        <v>6305</v>
+      </c>
+      <c r="D1267" s="2" t="s">
         <v>6306</v>
       </c>
-      <c r="C1267" s="2" t="s">
+      <c r="E1267" s="2" t="s">
         <v>6307</v>
       </c>
-      <c r="D1267" s="2" t="s">
+      <c r="F1267" s="2" t="s">
         <v>6308</v>
-      </c>
-      <c r="E1267" s="2" t="s">
-        <v>6309</v>
-      </c>
-      <c r="F1267" s="2" t="s">
-        <v>6310</v>
       </c>
       <c r="G1267" s="3">
         <v>4</v>
       </c>
       <c r="H1267" s="2" t="s">
-        <v>6311</v>
+        <v>6309</v>
       </c>
       <c r="I1267" s="2" t="s">
         <v>15</v>
@@ -57839,25 +57845,25 @@
         <v>1267</v>
       </c>
       <c r="B1268" s="2" t="s">
+        <v>6310</v>
+      </c>
+      <c r="C1268" s="2" t="s">
+        <v>6311</v>
+      </c>
+      <c r="D1268" s="2" t="s">
         <v>6312</v>
       </c>
-      <c r="C1268" s="2" t="s">
+      <c r="E1268" s="2" t="s">
         <v>6313</v>
       </c>
-      <c r="D1268" s="2" t="s">
+      <c r="F1268" s="2" t="s">
         <v>6314</v>
-      </c>
-      <c r="E1268" s="2" t="s">
-        <v>6315</v>
-      </c>
-      <c r="F1268" s="2" t="s">
-        <v>6316</v>
       </c>
       <c r="G1268" s="3">
         <v>4</v>
       </c>
       <c r="H1268" s="2" t="s">
-        <v>6317</v>
+        <v>6315</v>
       </c>
       <c r="I1268" s="2" t="s">
         <v>167</v>
@@ -57868,25 +57874,25 @@
         <v>1268</v>
       </c>
       <c r="B1269" s="2" t="s">
+        <v>6316</v>
+      </c>
+      <c r="C1269" s="2" t="s">
+        <v>6317</v>
+      </c>
+      <c r="D1269" s="2" t="s">
         <v>6318</v>
       </c>
-      <c r="C1269" s="2" t="s">
+      <c r="E1269" s="2" t="s">
         <v>6319</v>
       </c>
-      <c r="D1269" s="2" t="s">
+      <c r="F1269" s="2" t="s">
         <v>6320</v>
-      </c>
-      <c r="E1269" s="2" t="s">
-        <v>6321</v>
-      </c>
-      <c r="F1269" s="2" t="s">
-        <v>6322</v>
       </c>
       <c r="G1269" s="3">
         <v>4</v>
       </c>
       <c r="H1269" s="2" t="s">
-        <v>6323</v>
+        <v>6321</v>
       </c>
       <c r="I1269" s="2" t="s">
         <v>15</v>
@@ -57897,25 +57903,25 @@
         <v>1269</v>
       </c>
       <c r="B1270" s="2" t="s">
-        <v>6324</v>
+        <v>6322</v>
       </c>
       <c r="C1270" s="2" t="s">
-        <v>6325</v>
+        <v>6323</v>
       </c>
       <c r="D1270" s="2" t="s">
         <v>2737</v>
       </c>
       <c r="E1270" s="2" t="s">
-        <v>6326</v>
+        <v>6324</v>
       </c>
       <c r="F1270" s="2" t="s">
-        <v>6327</v>
+        <v>6325</v>
       </c>
       <c r="G1270" s="3">
         <v>3</v>
       </c>
       <c r="H1270" s="2" t="s">
-        <v>6328</v>
+        <v>6326</v>
       </c>
       <c r="I1270" s="2" t="s">
         <v>15</v>
@@ -57926,25 +57932,25 @@
         <v>1270</v>
       </c>
       <c r="B1271" s="2" t="s">
+        <v>6327</v>
+      </c>
+      <c r="C1271" s="2" t="s">
+        <v>6328</v>
+      </c>
+      <c r="D1271" s="2" t="s">
         <v>6329</v>
       </c>
-      <c r="C1271" s="2" t="s">
+      <c r="E1271" s="2" t="s">
         <v>6330</v>
       </c>
-      <c r="D1271" s="2" t="s">
+      <c r="F1271" s="2" t="s">
         <v>6331</v>
-      </c>
-      <c r="E1271" s="2" t="s">
-        <v>6332</v>
-      </c>
-      <c r="F1271" s="2" t="s">
-        <v>6333</v>
       </c>
       <c r="G1271" s="3">
         <v>1</v>
       </c>
       <c r="H1271" s="2" t="s">
-        <v>6334</v>
+        <v>6332</v>
       </c>
       <c r="I1271" s="2" t="s">
         <v>15</v>
@@ -57955,25 +57961,25 @@
         <v>1271</v>
       </c>
       <c r="B1272" s="2" t="s">
+        <v>6333</v>
+      </c>
+      <c r="C1272" s="2" t="s">
+        <v>6334</v>
+      </c>
+      <c r="D1272" s="2" t="s">
         <v>6335</v>
       </c>
-      <c r="C1272" s="2" t="s">
+      <c r="E1272" s="2" t="s">
         <v>6336</v>
       </c>
-      <c r="D1272" s="2" t="s">
+      <c r="F1272" s="2" t="s">
         <v>6337</v>
-      </c>
-      <c r="E1272" s="2" t="s">
-        <v>6338</v>
-      </c>
-      <c r="F1272" s="2" t="s">
-        <v>6339</v>
       </c>
       <c r="G1272" s="3">
         <v>1</v>
       </c>
       <c r="H1272" s="2" t="s">
-        <v>6340</v>
+        <v>6338</v>
       </c>
       <c r="I1272" s="2" t="s">
         <v>15</v>
@@ -57984,7 +57990,7 @@
         <v>1272</v>
       </c>
       <c r="B1273" s="2" t="s">
-        <v>6341</v>
+        <v>6339</v>
       </c>
       <c r="C1273" s="2" t="s">
         <v>522</v>
@@ -57996,13 +58002,13 @@
         <v>3940</v>
       </c>
       <c r="F1273" s="2" t="s">
-        <v>6342</v>
+        <v>6340</v>
       </c>
       <c r="G1273" s="3">
         <v>4</v>
       </c>
       <c r="H1273" s="2" t="s">
-        <v>6343</v>
+        <v>6341</v>
       </c>
       <c r="I1273" s="2" t="s">
         <v>167</v>
@@ -58013,10 +58019,10 @@
         <v>1273</v>
       </c>
       <c r="B1274" s="2" t="s">
-        <v>6344</v>
+        <v>6342</v>
       </c>
       <c r="C1274" s="2" t="s">
-        <v>6345</v>
+        <v>6343</v>
       </c>
       <c r="D1274" s="2" t="s">
         <v>5545</v>
@@ -58025,13 +58031,13 @@
         <v>3126</v>
       </c>
       <c r="F1274" s="2" t="s">
-        <v>6346</v>
+        <v>6344</v>
       </c>
       <c r="G1274" s="3">
         <v>3</v>
       </c>
       <c r="H1274" s="2" t="s">
-        <v>6347</v>
+        <v>6345</v>
       </c>
       <c r="I1274" s="2" t="s">
         <v>15</v>
@@ -58042,25 +58048,25 @@
         <v>1274</v>
       </c>
       <c r="B1275" s="2" t="s">
+        <v>6346</v>
+      </c>
+      <c r="C1275" s="2" t="s">
+        <v>6347</v>
+      </c>
+      <c r="D1275" s="2" t="s">
         <v>6348</v>
       </c>
-      <c r="C1275" s="2" t="s">
+      <c r="E1275" s="2" t="s">
         <v>6349</v>
       </c>
-      <c r="D1275" s="2" t="s">
+      <c r="F1275" s="2" t="s">
         <v>6350</v>
-      </c>
-      <c r="E1275" s="2" t="s">
-        <v>6351</v>
-      </c>
-      <c r="F1275" s="2" t="s">
-        <v>6352</v>
       </c>
       <c r="G1275" s="3">
         <v>2</v>
       </c>
       <c r="H1275" s="2" t="s">
-        <v>6353</v>
+        <v>6351</v>
       </c>
       <c r="I1275" s="2" t="s">
         <v>167</v>
@@ -58071,25 +58077,25 @@
         <v>1275</v>
       </c>
       <c r="B1276" s="2" t="s">
+        <v>6352</v>
+      </c>
+      <c r="C1276" s="2" t="s">
+        <v>6353</v>
+      </c>
+      <c r="D1276" s="2" t="s">
         <v>6354</v>
       </c>
-      <c r="C1276" s="2" t="s">
+      <c r="E1276" s="2" t="s">
         <v>6355</v>
       </c>
-      <c r="D1276" s="2" t="s">
+      <c r="F1276" s="2" t="s">
         <v>6356</v>
-      </c>
-      <c r="E1276" s="2" t="s">
-        <v>6357</v>
-      </c>
-      <c r="F1276" s="2" t="s">
-        <v>6358</v>
       </c>
       <c r="G1276" s="3">
         <v>2</v>
       </c>
       <c r="H1276" s="2" t="s">
-        <v>6359</v>
+        <v>6357</v>
       </c>
       <c r="I1276" s="2" t="s">
         <v>15</v>
@@ -58100,7 +58106,7 @@
         <v>1276</v>
       </c>
       <c r="B1277" s="2" t="s">
-        <v>6360</v>
+        <v>6358</v>
       </c>
       <c r="C1277" s="2" t="s">
         <v>1410</v>
@@ -58109,16 +58115,16 @@
         <v>1412</v>
       </c>
       <c r="E1277" s="2" t="s">
-        <v>6361</v>
+        <v>6359</v>
       </c>
       <c r="F1277" s="2" t="s">
-        <v>6362</v>
+        <v>6360</v>
       </c>
       <c r="G1277" s="3">
         <v>4</v>
       </c>
       <c r="H1277" s="2" t="s">
-        <v>6363</v>
+        <v>6361</v>
       </c>
       <c r="I1277" s="2" t="s">
         <v>15</v>
@@ -58129,25 +58135,25 @@
         <v>1277</v>
       </c>
       <c r="B1278" s="2" t="s">
+        <v>6362</v>
+      </c>
+      <c r="C1278" s="2" t="s">
+        <v>6363</v>
+      </c>
+      <c r="D1278" s="2" t="s">
         <v>6364</v>
-      </c>
-      <c r="C1278" s="2" t="s">
-        <v>6365</v>
-      </c>
-      <c r="D1278" s="2" t="s">
-        <v>6366</v>
       </c>
       <c r="E1278" s="2" t="s">
         <v>119</v>
       </c>
       <c r="F1278" s="2" t="s">
-        <v>6367</v>
+        <v>6365</v>
       </c>
       <c r="G1278" s="3">
         <v>4</v>
       </c>
       <c r="H1278" s="2" t="s">
-        <v>6368</v>
+        <v>6366</v>
       </c>
       <c r="I1278" s="2" t="s">
         <v>167</v>
@@ -58158,25 +58164,25 @@
         <v>1278</v>
       </c>
       <c r="B1279" s="2" t="s">
+        <v>6367</v>
+      </c>
+      <c r="C1279" s="2" t="s">
+        <v>6368</v>
+      </c>
+      <c r="D1279" s="2" t="s">
         <v>6369</v>
       </c>
-      <c r="C1279" s="2" t="s">
+      <c r="E1279" s="2" t="s">
         <v>6370</v>
       </c>
-      <c r="D1279" s="2" t="s">
+      <c r="F1279" s="2" t="s">
         <v>6371</v>
-      </c>
-      <c r="E1279" s="2" t="s">
-        <v>6372</v>
-      </c>
-      <c r="F1279" s="2" t="s">
-        <v>6373</v>
       </c>
       <c r="G1279" s="3">
         <v>1</v>
       </c>
       <c r="H1279" s="2" t="s">
-        <v>6374</v>
+        <v>6372</v>
       </c>
       <c r="I1279" s="2" t="s">
         <v>15</v>
@@ -58187,25 +58193,25 @@
         <v>1279</v>
       </c>
       <c r="B1280" s="2" t="s">
+        <v>6373</v>
+      </c>
+      <c r="C1280" s="2" t="s">
+        <v>6374</v>
+      </c>
+      <c r="D1280" s="2" t="s">
         <v>6375</v>
       </c>
-      <c r="C1280" s="2" t="s">
+      <c r="E1280" s="2" t="s">
         <v>6376</v>
       </c>
-      <c r="D1280" s="2" t="s">
+      <c r="F1280" s="2" t="s">
         <v>6377</v>
-      </c>
-      <c r="E1280" s="2" t="s">
-        <v>6378</v>
-      </c>
-      <c r="F1280" s="2" t="s">
-        <v>6379</v>
       </c>
       <c r="G1280" s="3">
         <v>4</v>
       </c>
       <c r="H1280" s="2" t="s">
-        <v>6380</v>
+        <v>6378</v>
       </c>
       <c r="I1280" s="2" t="s">
         <v>15</v>
@@ -58216,10 +58222,10 @@
         <v>1280</v>
       </c>
       <c r="B1281" s="2" t="s">
-        <v>6381</v>
+        <v>6379</v>
       </c>
       <c r="C1281" s="2" t="s">
-        <v>6382</v>
+        <v>6380</v>
       </c>
       <c r="D1281" s="2" t="s">
         <v>179</v>
@@ -58228,13 +58234,13 @@
         <v>181</v>
       </c>
       <c r="F1281" s="2" t="s">
-        <v>6383</v>
+        <v>6381</v>
       </c>
       <c r="G1281" s="3">
         <v>1</v>
       </c>
       <c r="H1281" s="2" t="s">
-        <v>6384</v>
+        <v>6382</v>
       </c>
       <c r="I1281" s="2" t="s">
         <v>15</v>
@@ -58245,25 +58251,25 @@
         <v>1281</v>
       </c>
       <c r="B1282" s="2" t="s">
+        <v>6383</v>
+      </c>
+      <c r="C1282" s="2" t="s">
+        <v>6384</v>
+      </c>
+      <c r="D1282" s="2" t="s">
         <v>6385</v>
-      </c>
-      <c r="C1282" s="2" t="s">
-        <v>6386</v>
-      </c>
-      <c r="D1282" s="2" t="s">
-        <v>6387</v>
       </c>
       <c r="E1282" s="2" t="s">
         <v>5768</v>
       </c>
       <c r="F1282" s="2" t="s">
-        <v>6388</v>
+        <v>6386</v>
       </c>
       <c r="G1282" s="3">
         <v>4</v>
       </c>
       <c r="H1282" s="2" t="s">
-        <v>6389</v>
+        <v>6387</v>
       </c>
       <c r="I1282" s="2" t="s">
         <v>15</v>
@@ -58274,25 +58280,25 @@
         <v>1282</v>
       </c>
       <c r="B1283" s="2" t="s">
+        <v>6388</v>
+      </c>
+      <c r="C1283" s="2" t="s">
+        <v>6389</v>
+      </c>
+      <c r="D1283" s="2" t="s">
         <v>6390</v>
-      </c>
-      <c r="C1283" s="2" t="s">
-        <v>6391</v>
-      </c>
-      <c r="D1283" s="2" t="s">
-        <v>6392</v>
       </c>
       <c r="E1283" s="2" t="s">
         <v>5540</v>
       </c>
       <c r="F1283" s="2" t="s">
-        <v>6393</v>
+        <v>6391</v>
       </c>
       <c r="G1283" s="3">
         <v>2</v>
       </c>
       <c r="H1283" s="2" t="s">
-        <v>6394</v>
+        <v>6392</v>
       </c>
       <c r="I1283" s="2" t="s">
         <v>15</v>
@@ -58303,7 +58309,7 @@
         <v>1283</v>
       </c>
       <c r="B1284" s="2" t="s">
-        <v>6395</v>
+        <v>6393</v>
       </c>
       <c r="C1284" s="2" t="s">
         <v>1864</v>
@@ -58312,16 +58318,16 @@
         <v>1865</v>
       </c>
       <c r="E1284" s="2" t="s">
-        <v>6396</v>
+        <v>6394</v>
       </c>
       <c r="F1284" s="2" t="s">
-        <v>6397</v>
+        <v>6395</v>
       </c>
       <c r="G1284" s="3">
         <v>3</v>
       </c>
       <c r="H1284" s="2" t="s">
-        <v>6398</v>
+        <v>6396</v>
       </c>
       <c r="I1284" s="2" t="s">
         <v>15</v>
@@ -58332,25 +58338,25 @@
         <v>1284</v>
       </c>
       <c r="B1285" s="2" t="s">
-        <v>6399</v>
+        <v>6397</v>
       </c>
       <c r="C1285" s="2" t="s">
-        <v>6400</v>
+        <v>6398</v>
       </c>
       <c r="D1285" s="2" t="s">
         <v>3368</v>
       </c>
       <c r="E1285" s="2" t="s">
-        <v>6401</v>
+        <v>6399</v>
       </c>
       <c r="F1285" s="2" t="s">
-        <v>6402</v>
+        <v>6400</v>
       </c>
       <c r="G1285" s="3">
         <v>2</v>
       </c>
       <c r="H1285" s="2" t="s">
-        <v>6403</v>
+        <v>6401</v>
       </c>
       <c r="I1285" s="2" t="s">
         <v>15</v>
@@ -58361,25 +58367,25 @@
         <v>1285</v>
       </c>
       <c r="B1286" s="2" t="s">
+        <v>6402</v>
+      </c>
+      <c r="C1286" s="2" t="s">
+        <v>6403</v>
+      </c>
+      <c r="D1286" s="2" t="s">
         <v>6404</v>
       </c>
-      <c r="C1286" s="2" t="s">
+      <c r="E1286" s="2" t="s">
         <v>6405</v>
       </c>
-      <c r="D1286" s="2" t="s">
+      <c r="F1286" s="2" t="s">
         <v>6406</v>
-      </c>
-      <c r="E1286" s="2" t="s">
-        <v>6407</v>
-      </c>
-      <c r="F1286" s="2" t="s">
-        <v>6408</v>
       </c>
       <c r="G1286" s="3">
         <v>1</v>
       </c>
       <c r="H1286" s="2" t="s">
-        <v>6409</v>
+        <v>6407</v>
       </c>
       <c r="I1286" s="2" t="s">
         <v>15</v>
@@ -58390,7 +58396,7 @@
         <v>1286</v>
       </c>
       <c r="B1287" s="2" t="s">
-        <v>6410</v>
+        <v>6408</v>
       </c>
       <c r="C1287" s="2" t="s">
         <v>928</v>
@@ -58402,13 +58408,13 @@
         <v>4118</v>
       </c>
       <c r="F1287" s="2" t="s">
-        <v>6411</v>
+        <v>6409</v>
       </c>
       <c r="G1287" s="3">
         <v>3</v>
       </c>
       <c r="H1287" s="2" t="s">
-        <v>6412</v>
+        <v>6410</v>
       </c>
       <c r="I1287" s="2" t="s">
         <v>167</v>
@@ -58419,25 +58425,25 @@
         <v>1287</v>
       </c>
       <c r="B1288" s="2" t="s">
-        <v>6413</v>
+        <v>6411</v>
       </c>
       <c r="C1288" s="2" t="s">
-        <v>6414</v>
+        <v>6412</v>
       </c>
       <c r="D1288" s="2" t="s">
         <v>5368</v>
       </c>
       <c r="E1288" s="2" t="s">
-        <v>6415</v>
+        <v>6413</v>
       </c>
       <c r="F1288" s="2" t="s">
-        <v>6416</v>
+        <v>6414</v>
       </c>
       <c r="G1288" s="3">
         <v>1</v>
       </c>
       <c r="H1288" s="2" t="s">
-        <v>6417</v>
+        <v>6415</v>
       </c>
       <c r="I1288" s="2" t="s">
         <v>160</v>
@@ -58448,25 +58454,25 @@
         <v>1288</v>
       </c>
       <c r="B1289" s="2" t="s">
+        <v>6416</v>
+      </c>
+      <c r="C1289" s="2" t="s">
+        <v>6417</v>
+      </c>
+      <c r="D1289" s="2" t="s">
         <v>6418</v>
       </c>
-      <c r="C1289" s="2" t="s">
+      <c r="E1289" s="2" t="s">
         <v>6419</v>
       </c>
-      <c r="D1289" s="2" t="s">
+      <c r="F1289" s="2" t="s">
         <v>6420</v>
-      </c>
-      <c r="E1289" s="2" t="s">
-        <v>6421</v>
-      </c>
-      <c r="F1289" s="2" t="s">
-        <v>6422</v>
       </c>
       <c r="G1289" s="3">
         <v>4</v>
       </c>
       <c r="H1289" s="2" t="s">
-        <v>6423</v>
+        <v>6421</v>
       </c>
       <c r="I1289" s="2" t="s">
         <v>15</v>
@@ -58477,25 +58483,25 @@
         <v>1289</v>
       </c>
       <c r="B1290" s="2" t="s">
+        <v>6422</v>
+      </c>
+      <c r="C1290" s="2" t="s">
+        <v>6423</v>
+      </c>
+      <c r="D1290" s="2" t="s">
         <v>6424</v>
       </c>
-      <c r="C1290" s="2" t="s">
+      <c r="E1290" s="2" t="s">
         <v>6425</v>
       </c>
-      <c r="D1290" s="2" t="s">
+      <c r="F1290" s="2" t="s">
         <v>6426</v>
-      </c>
-      <c r="E1290" s="2" t="s">
-        <v>6427</v>
-      </c>
-      <c r="F1290" s="2" t="s">
-        <v>6428</v>
       </c>
       <c r="G1290" s="3">
         <v>3</v>
       </c>
       <c r="H1290" s="2" t="s">
-        <v>6429</v>
+        <v>6427</v>
       </c>
       <c r="I1290" s="2" t="s">
         <v>15</v>
@@ -58506,25 +58512,25 @@
         <v>1290</v>
       </c>
       <c r="B1291" s="2" t="s">
-        <v>6430</v>
+        <v>6428</v>
       </c>
       <c r="C1291" s="2" t="s">
-        <v>6431</v>
+        <v>6429</v>
       </c>
       <c r="D1291" s="2" t="s">
         <v>4578</v>
       </c>
       <c r="E1291" s="2" t="s">
-        <v>6432</v>
+        <v>6430</v>
       </c>
       <c r="F1291" s="2" t="s">
-        <v>6433</v>
+        <v>6431</v>
       </c>
       <c r="G1291" s="3">
         <v>1</v>
       </c>
       <c r="H1291" s="2" t="s">
-        <v>6434</v>
+        <v>6432</v>
       </c>
       <c r="I1291" s="2" t="s">
         <v>15</v>
@@ -58535,7 +58541,7 @@
         <v>1291</v>
       </c>
       <c r="B1292" s="2" t="s">
-        <v>6435</v>
+        <v>6433</v>
       </c>
       <c r="C1292" s="2" t="s">
         <v>523</v>
@@ -58547,7 +58553,7 @@
         <v>525</v>
       </c>
       <c r="F1292" s="2" t="s">
-        <v>6436</v>
+        <v>6434</v>
       </c>
       <c r="G1292" s="3">
         <v>2</v>
@@ -58564,25 +58570,25 @@
         <v>1292</v>
       </c>
       <c r="B1293" s="2" t="s">
+        <v>6435</v>
+      </c>
+      <c r="C1293" s="2" t="s">
+        <v>6436</v>
+      </c>
+      <c r="D1293" s="2" t="s">
         <v>6437</v>
       </c>
-      <c r="C1293" s="2" t="s">
+      <c r="E1293" s="2" t="s">
         <v>6438</v>
       </c>
-      <c r="D1293" s="2" t="s">
+      <c r="F1293" s="2" t="s">
         <v>6439</v>
-      </c>
-      <c r="E1293" s="2" t="s">
-        <v>6440</v>
-      </c>
-      <c r="F1293" s="2" t="s">
-        <v>6441</v>
       </c>
       <c r="G1293" s="3">
         <v>4</v>
       </c>
       <c r="H1293" s="2" t="s">
-        <v>6442</v>
+        <v>6440</v>
       </c>
       <c r="I1293" s="2" t="s">
         <v>15</v>
@@ -58593,25 +58599,25 @@
         <v>1293</v>
       </c>
       <c r="B1294" s="2" t="s">
+        <v>6441</v>
+      </c>
+      <c r="C1294" s="2" t="s">
+        <v>6442</v>
+      </c>
+      <c r="D1294" s="2" t="s">
         <v>6443</v>
       </c>
-      <c r="C1294" s="2" t="s">
+      <c r="E1294" s="2" t="s">
         <v>6444</v>
       </c>
-      <c r="D1294" s="2" t="s">
+      <c r="F1294" s="2" t="s">
         <v>6445</v>
-      </c>
-      <c r="E1294" s="2" t="s">
-        <v>6446</v>
-      </c>
-      <c r="F1294" s="2" t="s">
-        <v>6447</v>
       </c>
       <c r="G1294" s="3">
         <v>1</v>
       </c>
       <c r="H1294" s="2" t="s">
-        <v>6448</v>
+        <v>6446</v>
       </c>
       <c r="I1294" s="2" t="s">
         <v>15</v>
@@ -58622,25 +58628,25 @@
         <v>1294</v>
       </c>
       <c r="B1295" s="2" t="s">
-        <v>6449</v>
+        <v>6447</v>
       </c>
       <c r="C1295" s="2" t="s">
         <v>857</v>
       </c>
       <c r="D1295" s="2" t="s">
+        <v>6448</v>
+      </c>
+      <c r="E1295" s="2" t="s">
+        <v>6449</v>
+      </c>
+      <c r="F1295" s="2" t="s">
         <v>6450</v>
-      </c>
-      <c r="E1295" s="2" t="s">
-        <v>6451</v>
-      </c>
-      <c r="F1295" s="2" t="s">
-        <v>6452</v>
       </c>
       <c r="G1295" s="3">
         <v>3</v>
       </c>
       <c r="H1295" s="2" t="s">
-        <v>6453</v>
+        <v>6451</v>
       </c>
       <c r="I1295" s="2" t="s">
         <v>167</v>
@@ -58651,25 +58657,25 @@
         <v>1295</v>
       </c>
       <c r="B1296" s="2" t="s">
+        <v>6452</v>
+      </c>
+      <c r="C1296" s="2" t="s">
+        <v>6453</v>
+      </c>
+      <c r="D1296" s="2" t="s">
         <v>6454</v>
       </c>
-      <c r="C1296" s="2" t="s">
+      <c r="E1296" s="2" t="s">
         <v>6455</v>
       </c>
-      <c r="D1296" s="2" t="s">
+      <c r="F1296" s="2" t="s">
         <v>6456</v>
-      </c>
-      <c r="E1296" s="2" t="s">
-        <v>6457</v>
-      </c>
-      <c r="F1296" s="2" t="s">
-        <v>6458</v>
       </c>
       <c r="G1296" s="3">
         <v>3</v>
       </c>
       <c r="H1296" s="2" t="s">
-        <v>6459</v>
+        <v>6457</v>
       </c>
       <c r="I1296" s="2" t="s">
         <v>15</v>
@@ -58680,7 +58686,7 @@
         <v>1296</v>
       </c>
       <c r="B1297" s="2" t="s">
-        <v>6460</v>
+        <v>6458</v>
       </c>
       <c r="C1297" s="2" t="s">
         <v>622</v>
@@ -58692,13 +58698,13 @@
         <v>633</v>
       </c>
       <c r="F1297" s="2" t="s">
-        <v>6461</v>
+        <v>6459</v>
       </c>
       <c r="G1297" s="3">
         <v>1</v>
       </c>
       <c r="H1297" s="2" t="s">
-        <v>6462</v>
+        <v>6460</v>
       </c>
       <c r="I1297" s="2" t="s">
         <v>15</v>
@@ -58709,7 +58715,7 @@
         <v>1297</v>
       </c>
       <c r="B1298" s="2" t="s">
-        <v>6463</v>
+        <v>6461</v>
       </c>
       <c r="C1298" s="2" t="s">
         <v>594</v>
@@ -58727,7 +58733,7 @@
         <v>1</v>
       </c>
       <c r="H1298" s="2" t="s">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="I1298" s="2" t="s">
         <v>15</v>
@@ -58738,7 +58744,7 @@
         <v>1298</v>
       </c>
       <c r="B1299" s="2" t="s">
-        <v>6465</v>
+        <v>6463</v>
       </c>
       <c r="C1299" s="2" t="s">
         <v>233</v>
@@ -58756,7 +58762,7 @@
         <v>2</v>
       </c>
       <c r="H1299" s="2" t="s">
-        <v>6466</v>
+        <v>6464</v>
       </c>
       <c r="I1299" s="2" t="s">
         <v>22</v>
@@ -58767,25 +58773,25 @@
         <v>1299</v>
       </c>
       <c r="B1300" s="2" t="s">
+        <v>6465</v>
+      </c>
+      <c r="C1300" s="2" t="s">
+        <v>6466</v>
+      </c>
+      <c r="D1300" s="2" t="s">
         <v>6467</v>
       </c>
-      <c r="C1300" s="2" t="s">
+      <c r="E1300" s="2" t="s">
         <v>6468</v>
       </c>
-      <c r="D1300" s="2" t="s">
+      <c r="F1300" s="2" t="s">
         <v>6469</v>
-      </c>
-      <c r="E1300" s="2" t="s">
-        <v>6470</v>
-      </c>
-      <c r="F1300" s="2" t="s">
-        <v>6471</v>
       </c>
       <c r="G1300" s="3">
         <v>1</v>
       </c>
       <c r="H1300" s="2" t="s">
-        <v>6472</v>
+        <v>6470</v>
       </c>
       <c r="I1300" s="2" t="s">
         <v>15</v>
@@ -58796,25 +58802,25 @@
         <v>1300</v>
       </c>
       <c r="B1301" s="2" t="s">
+        <v>6471</v>
+      </c>
+      <c r="C1301" s="2" t="s">
+        <v>6472</v>
+      </c>
+      <c r="D1301" s="2" t="s">
         <v>6473</v>
-      </c>
-      <c r="C1301" s="2" t="s">
-        <v>6474</v>
-      </c>
-      <c r="D1301" s="2" t="s">
-        <v>6475</v>
       </c>
       <c r="E1301" s="2" t="s">
         <v>119</v>
       </c>
       <c r="F1301" s="2" t="s">
-        <v>6476</v>
+        <v>6474</v>
       </c>
       <c r="G1301" s="3">
         <v>1</v>
       </c>
       <c r="H1301" s="2" t="s">
-        <v>6477</v>
+        <v>6475</v>
       </c>
       <c r="I1301" s="2" t="s">
         <v>15</v>
@@ -58825,25 +58831,25 @@
         <v>1301</v>
       </c>
       <c r="B1302" s="2" t="s">
+        <v>6476</v>
+      </c>
+      <c r="C1302" s="2" t="s">
+        <v>6477</v>
+      </c>
+      <c r="D1302" s="2" t="s">
         <v>6478</v>
       </c>
-      <c r="C1302" s="2" t="s">
+      <c r="E1302" s="2" t="s">
         <v>6479</v>
       </c>
-      <c r="D1302" s="2" t="s">
+      <c r="F1302" s="2" t="s">
         <v>6480</v>
-      </c>
-      <c r="E1302" s="2" t="s">
-        <v>6481</v>
-      </c>
-      <c r="F1302" s="2" t="s">
-        <v>6482</v>
       </c>
       <c r="G1302" s="3">
         <v>1</v>
       </c>
       <c r="H1302" s="2" t="s">
-        <v>6483</v>
+        <v>6481</v>
       </c>
       <c r="I1302" s="2" t="s">
         <v>15</v>
@@ -58854,25 +58860,25 @@
         <v>1302</v>
       </c>
       <c r="B1303" s="2" t="s">
+        <v>6482</v>
+      </c>
+      <c r="C1303" s="2" t="s">
+        <v>6483</v>
+      </c>
+      <c r="D1303" s="2" t="s">
         <v>6484</v>
       </c>
-      <c r="C1303" s="2" t="s">
+      <c r="E1303" s="2" t="s">
         <v>6485</v>
       </c>
-      <c r="D1303" s="2" t="s">
+      <c r="F1303" s="2" t="s">
         <v>6486</v>
-      </c>
-      <c r="E1303" s="2" t="s">
-        <v>6487</v>
-      </c>
-      <c r="F1303" s="2" t="s">
-        <v>6488</v>
       </c>
       <c r="G1303" s="3">
         <v>2</v>
       </c>
       <c r="H1303" s="2" t="s">
-        <v>6489</v>
+        <v>6487</v>
       </c>
       <c r="I1303" s="2" t="s">
         <v>15</v>
@@ -58883,25 +58889,25 @@
         <v>1303</v>
       </c>
       <c r="B1304" s="2" t="s">
+        <v>6488</v>
+      </c>
+      <c r="C1304" s="2" t="s">
+        <v>6489</v>
+      </c>
+      <c r="D1304" s="2" t="s">
         <v>6490</v>
       </c>
-      <c r="C1304" s="2" t="s">
+      <c r="E1304" s="2" t="s">
         <v>6491</v>
       </c>
-      <c r="D1304" s="2" t="s">
+      <c r="F1304" s="2" t="s">
         <v>6492</v>
-      </c>
-      <c r="E1304" s="2" t="s">
-        <v>6493</v>
-      </c>
-      <c r="F1304" s="2" t="s">
-        <v>6494</v>
       </c>
       <c r="G1304" s="3">
         <v>3</v>
       </c>
       <c r="H1304" s="2" t="s">
-        <v>6495</v>
+        <v>6493</v>
       </c>
       <c r="I1304" s="2" t="s">
         <v>167</v>
@@ -58912,25 +58918,25 @@
         <v>1304</v>
       </c>
       <c r="B1305" s="2" t="s">
+        <v>6494</v>
+      </c>
+      <c r="C1305" s="2" t="s">
+        <v>6495</v>
+      </c>
+      <c r="D1305" s="2" t="s">
         <v>6496</v>
       </c>
-      <c r="C1305" s="2" t="s">
+      <c r="E1305" s="2" t="s">
         <v>6497</v>
       </c>
-      <c r="D1305" s="2" t="s">
+      <c r="F1305" s="2" t="s">
         <v>6498</v>
-      </c>
-      <c r="E1305" s="2" t="s">
-        <v>6499</v>
-      </c>
-      <c r="F1305" s="2" t="s">
-        <v>6500</v>
       </c>
       <c r="G1305" s="3">
         <v>1</v>
       </c>
       <c r="H1305" s="2" t="s">
-        <v>6501</v>
+        <v>6499</v>
       </c>
       <c r="I1305" s="2" t="s">
         <v>15</v>
@@ -58941,25 +58947,25 @@
         <v>1305</v>
       </c>
       <c r="B1306" s="2" t="s">
+        <v>6500</v>
+      </c>
+      <c r="C1306" s="2" t="s">
+        <v>6501</v>
+      </c>
+      <c r="D1306" s="2" t="s">
         <v>6502</v>
       </c>
-      <c r="C1306" s="2" t="s">
+      <c r="E1306" s="2" t="s">
         <v>6503</v>
       </c>
-      <c r="D1306" s="2" t="s">
+      <c r="F1306" s="2" t="s">
         <v>6504</v>
-      </c>
-      <c r="E1306" s="2" t="s">
-        <v>6505</v>
-      </c>
-      <c r="F1306" s="2" t="s">
-        <v>6506</v>
       </c>
       <c r="G1306" s="3">
         <v>2</v>
       </c>
       <c r="H1306" s="2" t="s">
-        <v>6507</v>
+        <v>6505</v>
       </c>
       <c r="I1306" s="2" t="s">
         <v>15</v>
@@ -58970,25 +58976,25 @@
         <v>1306</v>
       </c>
       <c r="B1307" s="2" t="s">
+        <v>6506</v>
+      </c>
+      <c r="C1307" s="2" t="s">
+        <v>6507</v>
+      </c>
+      <c r="D1307" s="2" t="s">
         <v>6508</v>
-      </c>
-      <c r="C1307" s="2" t="s">
-        <v>6509</v>
-      </c>
-      <c r="D1307" s="2" t="s">
-        <v>6510</v>
       </c>
       <c r="E1307" s="2" t="s">
         <v>5946</v>
       </c>
       <c r="F1307" s="2" t="s">
-        <v>6511</v>
+        <v>6509</v>
       </c>
       <c r="G1307" s="3">
         <v>4</v>
       </c>
       <c r="H1307" s="2" t="s">
-        <v>6512</v>
+        <v>6510</v>
       </c>
       <c r="I1307" s="2" t="s">
         <v>15</v>
@@ -58999,7 +59005,7 @@
         <v>1307</v>
       </c>
       <c r="B1308" s="2" t="s">
-        <v>6513</v>
+        <v>6511</v>
       </c>
       <c r="C1308" s="2" t="s">
         <v>928</v>
@@ -59017,7 +59023,7 @@
         <v>3</v>
       </c>
       <c r="H1308" s="2" t="s">
-        <v>6514</v>
+        <v>6512</v>
       </c>
       <c r="I1308" s="2" t="s">
         <v>15</v>
@@ -59028,7 +59034,7 @@
         <v>1308</v>
       </c>
       <c r="B1309" s="2" t="s">
-        <v>6515</v>
+        <v>6513</v>
       </c>
       <c r="C1309" s="2" t="s">
         <v>4446</v>
@@ -59057,7 +59063,7 @@
         <v>1309</v>
       </c>
       <c r="B1310" s="2" t="s">
-        <v>6516</v>
+        <v>6514</v>
       </c>
       <c r="C1310" s="2" t="s">
         <v>4446</v>
@@ -59075,7 +59081,7 @@
         <v>1</v>
       </c>
       <c r="H1310" s="2" t="s">
-        <v>6517</v>
+        <v>6515</v>
       </c>
       <c r="I1310" s="2" t="s">
         <v>15</v>
@@ -59086,7 +59092,7 @@
         <v>1310</v>
       </c>
       <c r="B1311" s="2" t="s">
-        <v>6518</v>
+        <v>6516</v>
       </c>
       <c r="C1311" s="2" t="s">
         <v>3398</v>
@@ -59115,7 +59121,7 @@
         <v>1311</v>
       </c>
       <c r="B1312" s="2" t="s">
-        <v>6519</v>
+        <v>6517</v>
       </c>
       <c r="C1312" s="2" t="s">
         <v>72</v>
@@ -59124,10 +59130,10 @@
         <v>77</v>
       </c>
       <c r="E1312" s="2" t="s">
-        <v>6520</v>
+        <v>6518</v>
       </c>
       <c r="F1312" s="2" t="s">
-        <v>6521</v>
+        <v>6519</v>
       </c>
       <c r="G1312" s="3">
         <v>2</v>
@@ -59144,25 +59150,25 @@
         <v>1312</v>
       </c>
       <c r="B1313" s="2" t="s">
-        <v>6522</v>
+        <v>6520</v>
       </c>
       <c r="C1313" s="2" t="s">
         <v>5552</v>
       </c>
       <c r="D1313" s="2" t="s">
+        <v>6521</v>
+      </c>
+      <c r="E1313" s="2" t="s">
+        <v>6522</v>
+      </c>
+      <c r="F1313" s="2" t="s">
         <v>6523</v>
-      </c>
-      <c r="E1313" s="2" t="s">
-        <v>6524</v>
-      </c>
-      <c r="F1313" s="2" t="s">
-        <v>6525</v>
       </c>
       <c r="G1313" s="3">
         <v>1</v>
       </c>
       <c r="H1313" s="2" t="s">
-        <v>6526</v>
+        <v>6524</v>
       </c>
       <c r="I1313" s="2" t="s">
         <v>15</v>
@@ -59173,23 +59179,23 @@
         <v>1313</v>
       </c>
       <c r="B1314" s="2" t="s">
-        <v>6527</v>
+        <v>6525</v>
       </c>
       <c r="C1314" s="2" t="s">
-        <v>6320</v>
+        <v>6318</v>
       </c>
       <c r="D1314" s="2" t="s">
-        <v>6528</v>
+        <v>6526</v>
       </c>
       <c r="E1314" s="2"/>
       <c r="F1314" s="2" t="s">
-        <v>6529</v>
+        <v>6527</v>
       </c>
       <c r="G1314" s="3">
         <v>3</v>
       </c>
       <c r="H1314" s="2" t="s">
-        <v>6530</v>
+        <v>6528</v>
       </c>
       <c r="I1314" s="2" t="s">
         <v>15</v>
@@ -59200,13 +59206,13 @@
         <v>1314</v>
       </c>
       <c r="B1315" s="2" t="s">
+        <v>6529</v>
+      </c>
+      <c r="C1315" s="2" t="s">
+        <v>6530</v>
+      </c>
+      <c r="D1315" s="2" t="s">
         <v>6531</v>
-      </c>
-      <c r="C1315" s="2" t="s">
-        <v>6532</v>
-      </c>
-      <c r="D1315" s="2" t="s">
-        <v>6533</v>
       </c>
       <c r="E1315" s="2"/>
       <c r="F1315" s="2"/>
@@ -59225,25 +59231,25 @@
         <v>1315</v>
       </c>
       <c r="B1316" s="2" t="s">
+        <v>6532</v>
+      </c>
+      <c r="C1316" s="2" t="s">
+        <v>6533</v>
+      </c>
+      <c r="D1316" s="2" t="s">
         <v>6534</v>
-      </c>
-      <c r="C1316" s="2" t="s">
-        <v>6535</v>
-      </c>
-      <c r="D1316" s="2" t="s">
-        <v>6536</v>
       </c>
       <c r="E1316" s="2" t="s">
         <v>5362</v>
       </c>
       <c r="F1316" s="2" t="s">
-        <v>6537</v>
+        <v>6535</v>
       </c>
       <c r="G1316" s="3">
         <v>2</v>
       </c>
       <c r="H1316" s="2" t="s">
-        <v>6538</v>
+        <v>6536</v>
       </c>
       <c r="I1316" s="2" t="s">
         <v>15</v>
@@ -59254,23 +59260,23 @@
         <v>1316</v>
       </c>
       <c r="B1317" s="2" t="s">
+        <v>6537</v>
+      </c>
+      <c r="C1317" s="2" t="s">
+        <v>6538</v>
+      </c>
+      <c r="D1317" s="2" t="s">
         <v>6539</v>
       </c>
-      <c r="C1317" s="2" t="s">
+      <c r="E1317" s="2" t="s">
         <v>6540</v>
-      </c>
-      <c r="D1317" s="2" t="s">
-        <v>6541</v>
-      </c>
-      <c r="E1317" s="2" t="s">
-        <v>6542</v>
       </c>
       <c r="F1317" s="2"/>
       <c r="G1317" s="3">
         <v>2</v>
       </c>
       <c r="H1317" s="2" t="s">
-        <v>6543</v>
+        <v>6541</v>
       </c>
       <c r="I1317" s="2" t="s">
         <v>845</v>
@@ -59281,25 +59287,25 @@
         <v>1317</v>
       </c>
       <c r="B1318" s="2" t="s">
+        <v>6542</v>
+      </c>
+      <c r="C1318" s="2" t="s">
+        <v>6543</v>
+      </c>
+      <c r="D1318" s="2" t="s">
         <v>6544</v>
       </c>
-      <c r="C1318" s="2" t="s">
+      <c r="E1318" s="2" t="s">
         <v>6545</v>
       </c>
-      <c r="D1318" s="2" t="s">
+      <c r="F1318" s="2" t="s">
         <v>6546</v>
-      </c>
-      <c r="E1318" s="2" t="s">
-        <v>6547</v>
-      </c>
-      <c r="F1318" s="2" t="s">
-        <v>6548</v>
       </c>
       <c r="G1318" s="3">
         <v>1</v>
       </c>
       <c r="H1318" s="2" t="s">
-        <v>6549</v>
+        <v>6547</v>
       </c>
       <c r="I1318" s="2" t="s">
         <v>15</v>
@@ -59310,10 +59316,10 @@
         <v>1318</v>
       </c>
       <c r="B1319" s="2" t="s">
-        <v>6550</v>
+        <v>6548</v>
       </c>
       <c r="C1319" s="2" t="s">
-        <v>6551</v>
+        <v>6549</v>
       </c>
       <c r="D1319" s="2" t="s">
         <v>337</v>
@@ -59322,13 +59328,13 @@
         <v>338</v>
       </c>
       <c r="F1319" s="2" t="s">
-        <v>6552</v>
+        <v>6550</v>
       </c>
       <c r="G1319" s="3">
         <v>1</v>
       </c>
       <c r="H1319" s="2" t="s">
-        <v>6553</v>
+        <v>6551</v>
       </c>
       <c r="I1319" s="2" t="s">
         <v>160</v>
@@ -59339,7 +59345,7 @@
         <v>1319</v>
       </c>
       <c r="B1320" s="2" t="s">
-        <v>6554</v>
+        <v>6552</v>
       </c>
       <c r="C1320" s="2" t="s">
         <v>244</v>
@@ -59348,16 +59354,16 @@
         <v>750</v>
       </c>
       <c r="E1320" s="2" t="s">
-        <v>6555</v>
+        <v>6553</v>
       </c>
       <c r="F1320" s="2" t="s">
-        <v>6556</v>
+        <v>6554</v>
       </c>
       <c r="G1320" s="3">
         <v>2</v>
       </c>
       <c r="H1320" s="2" t="s">
-        <v>6557</v>
+        <v>6555</v>
       </c>
       <c r="I1320" s="2" t="s">
         <v>15</v>
@@ -59368,7 +59374,7 @@
         <v>1320</v>
       </c>
       <c r="B1321" s="2" t="s">
-        <v>6558</v>
+        <v>6556</v>
       </c>
       <c r="C1321" s="2" t="s">
         <v>1422</v>
@@ -59397,25 +59403,25 @@
         <v>1321</v>
       </c>
       <c r="B1322" s="2" t="s">
+        <v>6557</v>
+      </c>
+      <c r="C1322" s="2" t="s">
+        <v>6558</v>
+      </c>
+      <c r="D1322" s="2" t="s">
         <v>6559</v>
       </c>
-      <c r="C1322" s="2" t="s">
+      <c r="E1322" s="2" t="s">
         <v>6560</v>
       </c>
-      <c r="D1322" s="2" t="s">
+      <c r="F1322" s="2" t="s">
         <v>6561</v>
-      </c>
-      <c r="E1322" s="2" t="s">
-        <v>6562</v>
-      </c>
-      <c r="F1322" s="2" t="s">
-        <v>6563</v>
       </c>
       <c r="G1322" s="3">
         <v>4</v>
       </c>
       <c r="H1322" s="2" t="s">
-        <v>6564</v>
+        <v>6562</v>
       </c>
       <c r="I1322" s="2" t="s">
         <v>845</v>
@@ -59426,7 +59432,7 @@
         <v>1322</v>
       </c>
       <c r="B1323" s="2" t="s">
-        <v>6565</v>
+        <v>6563</v>
       </c>
       <c r="C1323" s="2" t="s">
         <v>1424</v>
@@ -59435,16 +59441,16 @@
         <v>1422</v>
       </c>
       <c r="E1323" s="2" t="s">
-        <v>6566</v>
+        <v>6564</v>
       </c>
       <c r="F1323" s="2" t="s">
-        <v>6567</v>
+        <v>6565</v>
       </c>
       <c r="G1323" s="3">
         <v>3</v>
       </c>
       <c r="H1323" s="2" t="s">
-        <v>6568</v>
+        <v>6566</v>
       </c>
       <c r="I1323" s="2" t="s">
         <v>845</v>
@@ -59455,16 +59461,16 @@
         <v>1323</v>
       </c>
       <c r="B1324" s="2" t="s">
+        <v>6567</v>
+      </c>
+      <c r="C1324" s="2" t="s">
+        <v>6568</v>
+      </c>
+      <c r="D1324" s="2" t="s">
         <v>6569</v>
       </c>
-      <c r="C1324" s="2" t="s">
+      <c r="E1324" s="2" t="s">
         <v>6570</v>
-      </c>
-      <c r="D1324" s="2" t="s">
-        <v>6571</v>
-      </c>
-      <c r="E1324" s="2" t="s">
-        <v>6572</v>
       </c>
       <c r="F1324" s="2" t="s">
         <v>51</v>
@@ -59484,7 +59490,7 @@
         <v>1324</v>
       </c>
       <c r="B1325" s="2" t="s">
-        <v>6573</v>
+        <v>6571</v>
       </c>
       <c r="C1325" s="2" t="s">
         <v>1422</v>
@@ -59513,7 +59519,7 @@
         <v>1325</v>
       </c>
       <c r="B1326" s="2" t="s">
-        <v>6574</v>
+        <v>6572</v>
       </c>
       <c r="C1326" s="2" t="s">
         <v>1422</v>
@@ -59522,14 +59528,14 @@
         <v>1423</v>
       </c>
       <c r="E1326" s="2" t="s">
-        <v>6575</v>
+        <v>6573</v>
       </c>
       <c r="F1326" s="2"/>
       <c r="G1326" s="3">
         <v>1</v>
       </c>
       <c r="H1326" s="2" t="s">
-        <v>6576</v>
+        <v>6574</v>
       </c>
       <c r="I1326" s="2" t="s">
         <v>845</v>
@@ -59540,25 +59546,25 @@
         <v>1326</v>
       </c>
       <c r="B1327" s="2" t="s">
-        <v>6577</v>
+        <v>6575</v>
       </c>
       <c r="C1327" s="2" t="s">
-        <v>6578</v>
+        <v>6576</v>
       </c>
       <c r="D1327" s="2" t="s">
-        <v>6566</v>
+        <v>6564</v>
       </c>
       <c r="E1327" s="2" t="s">
         <v>1422</v>
       </c>
       <c r="F1327" s="2" t="s">
-        <v>6579</v>
+        <v>6577</v>
       </c>
       <c r="G1327" s="3">
         <v>3</v>
       </c>
       <c r="H1327" s="2" t="s">
-        <v>6580</v>
+        <v>6578</v>
       </c>
       <c r="I1327" s="2" t="s">
         <v>15</v>
@@ -59569,13 +59575,13 @@
         <v>1327</v>
       </c>
       <c r="B1328" s="2" t="s">
-        <v>6581</v>
+        <v>6579</v>
       </c>
       <c r="C1328" s="2" t="s">
         <v>1422</v>
       </c>
       <c r="D1328" s="2" t="s">
-        <v>6582</v>
+        <v>6580</v>
       </c>
       <c r="E1328" s="2" t="s">
         <v>1424</v>
@@ -59587,7 +59593,7 @@
         <v>2</v>
       </c>
       <c r="H1328" s="2" t="s">
-        <v>6583</v>
+        <v>6581</v>
       </c>
       <c r="I1328" s="2" t="s">
         <v>816</v>
@@ -59598,13 +59604,13 @@
         <v>1328</v>
       </c>
       <c r="B1329" s="2" t="s">
-        <v>6584</v>
+        <v>6582</v>
       </c>
       <c r="C1329" s="2" t="s">
         <v>1422</v>
       </c>
       <c r="D1329" s="2" t="s">
-        <v>6566</v>
+        <v>6564</v>
       </c>
       <c r="E1329" s="2" t="s">
         <v>1424</v>
@@ -59627,13 +59633,13 @@
         <v>1329</v>
       </c>
       <c r="B1330" s="2" t="s">
-        <v>6585</v>
+        <v>6583</v>
       </c>
       <c r="C1330" s="2" t="s">
         <v>1422</v>
       </c>
       <c r="D1330" s="2" t="s">
-        <v>6566</v>
+        <v>6564</v>
       </c>
       <c r="E1330" s="2" t="s">
         <v>1424</v>
@@ -59656,13 +59662,13 @@
         <v>1330</v>
       </c>
       <c r="B1331" s="2" t="s">
-        <v>6586</v>
+        <v>6584</v>
       </c>
       <c r="C1331" s="2" t="s">
         <v>1422</v>
       </c>
       <c r="D1331" s="2" t="s">
-        <v>6566</v>
+        <v>6564</v>
       </c>
       <c r="E1331" s="2" t="s">
         <v>1424</v>
@@ -59674,7 +59680,7 @@
         <v>2</v>
       </c>
       <c r="H1331" s="2" t="s">
-        <v>6587</v>
+        <v>6585</v>
       </c>
       <c r="I1331" s="2" t="s">
         <v>15</v>
@@ -59685,25 +59691,25 @@
         <v>1331</v>
       </c>
       <c r="B1332" s="2" t="s">
+        <v>6586</v>
+      </c>
+      <c r="C1332" s="2" t="s">
+        <v>6587</v>
+      </c>
+      <c r="D1332" s="2" t="s">
         <v>6588</v>
       </c>
-      <c r="C1332" s="2" t="s">
+      <c r="E1332" s="2" t="s">
         <v>6589</v>
       </c>
-      <c r="D1332" s="2" t="s">
+      <c r="F1332" s="2" t="s">
         <v>6590</v>
-      </c>
-      <c r="E1332" s="2" t="s">
-        <v>6591</v>
-      </c>
-      <c r="F1332" s="2" t="s">
-        <v>6592</v>
       </c>
       <c r="G1332" s="3">
         <v>4</v>
       </c>
       <c r="H1332" s="2" t="s">
-        <v>6593</v>
+        <v>6591</v>
       </c>
       <c r="I1332" s="2" t="s">
         <v>22</v>
@@ -59714,16 +59720,16 @@
         <v>1332</v>
       </c>
       <c r="B1333" s="2" t="s">
-        <v>6594</v>
+        <v>6592</v>
       </c>
       <c r="C1333" s="2" t="s">
         <v>77</v>
       </c>
       <c r="D1333" s="2" t="s">
-        <v>6595</v>
+        <v>6593</v>
       </c>
       <c r="E1333" s="2" t="s">
-        <v>6596</v>
+        <v>6594</v>
       </c>
       <c r="F1333" s="2" t="s">
         <v>2358</v>
@@ -59743,7 +59749,7 @@
         <v>1333</v>
       </c>
       <c r="B1334" s="2" t="s">
-        <v>6597</v>
+        <v>6595</v>
       </c>
       <c r="C1334" s="2" t="s">
         <v>12</v>
@@ -59755,13 +59761,13 @@
         <v>458</v>
       </c>
       <c r="F1334" s="2" t="s">
-        <v>6598</v>
+        <v>6596</v>
       </c>
       <c r="G1334" s="3">
         <v>1</v>
       </c>
       <c r="H1334" s="2" t="s">
-        <v>6599</v>
+        <v>6597</v>
       </c>
       <c r="I1334" s="2" t="s">
         <v>845</v>
@@ -59772,16 +59778,16 @@
         <v>1334</v>
       </c>
       <c r="B1335" s="2" t="s">
+        <v>6598</v>
+      </c>
+      <c r="C1335" s="2" t="s">
+        <v>6599</v>
+      </c>
+      <c r="D1335" s="2" t="s">
         <v>6600</v>
       </c>
-      <c r="C1335" s="2" t="s">
+      <c r="E1335" s="2" t="s">
         <v>6601</v>
-      </c>
-      <c r="D1335" s="2" t="s">
-        <v>6602</v>
-      </c>
-      <c r="E1335" s="2" t="s">
-        <v>6603</v>
       </c>
       <c r="F1335" s="2" t="s">
         <v>199</v>
@@ -59801,7 +59807,7 @@
         <v>1335</v>
       </c>
       <c r="B1336" s="2" t="s">
-        <v>6604</v>
+        <v>6602</v>
       </c>
       <c r="C1336" s="2" t="s">
         <v>5185</v>
@@ -59810,16 +59816,16 @@
         <v>5090</v>
       </c>
       <c r="E1336" s="2" t="s">
-        <v>6605</v>
+        <v>6603</v>
       </c>
       <c r="F1336" s="2" t="s">
-        <v>6606</v>
+        <v>6604</v>
       </c>
       <c r="G1336" s="3">
         <v>3</v>
       </c>
       <c r="H1336" s="2" t="s">
-        <v>6607</v>
+        <v>6605</v>
       </c>
       <c r="I1336" s="2" t="s">
         <v>15</v>
@@ -59830,25 +59836,25 @@
         <v>1336</v>
       </c>
       <c r="B1337" s="2" t="s">
+        <v>6606</v>
+      </c>
+      <c r="C1337" s="2" t="s">
+        <v>6607</v>
+      </c>
+      <c r="D1337" s="2" t="s">
         <v>6608</v>
       </c>
-      <c r="C1337" s="2" t="s">
+      <c r="E1337" s="2" t="s">
         <v>6609</v>
       </c>
-      <c r="D1337" s="2" t="s">
+      <c r="F1337" s="2" t="s">
         <v>6610</v>
-      </c>
-      <c r="E1337" s="2" t="s">
-        <v>6611</v>
-      </c>
-      <c r="F1337" s="2" t="s">
-        <v>6612</v>
       </c>
       <c r="G1337" s="3">
         <v>3</v>
       </c>
       <c r="H1337" s="2" t="s">
-        <v>6613</v>
+        <v>6611</v>
       </c>
       <c r="I1337" s="2" t="s">
         <v>845</v>
@@ -59859,7 +59865,7 @@
         <v>1337</v>
       </c>
       <c r="B1338" s="2" t="s">
-        <v>6614</v>
+        <v>6612</v>
       </c>
       <c r="C1338" s="2" t="s">
         <v>525</v>
@@ -59871,13 +59877,13 @@
         <v>5090</v>
       </c>
       <c r="F1338" s="2" t="s">
-        <v>6615</v>
+        <v>6613</v>
       </c>
       <c r="G1338" s="3">
         <v>4</v>
       </c>
       <c r="H1338" s="2" t="s">
-        <v>6616</v>
+        <v>6614</v>
       </c>
       <c r="I1338" s="2" t="s">
         <v>22</v>
@@ -59888,7 +59894,7 @@
         <v>1338</v>
       </c>
       <c r="B1339" s="2" t="s">
-        <v>6617</v>
+        <v>6615</v>
       </c>
       <c r="C1339" s="2" t="s">
         <v>77</v>
@@ -59897,16 +59903,16 @@
         <v>583</v>
       </c>
       <c r="E1339" s="2" t="s">
-        <v>6618</v>
+        <v>6616</v>
       </c>
       <c r="F1339" s="2" t="s">
-        <v>6619</v>
+        <v>6617</v>
       </c>
       <c r="G1339" s="3">
         <v>2</v>
       </c>
       <c r="H1339" s="2" t="s">
-        <v>6620</v>
+        <v>6618</v>
       </c>
       <c r="I1339" s="2" t="s">
         <v>845</v>
@@ -59917,7 +59923,7 @@
         <v>1339</v>
       </c>
       <c r="B1340" s="2" t="s">
-        <v>6621</v>
+        <v>6619</v>
       </c>
       <c r="C1340" s="2" t="s">
         <v>326</v>
@@ -59929,13 +59935,13 @@
         <v>332</v>
       </c>
       <c r="F1340" s="2" t="s">
-        <v>6622</v>
+        <v>6620</v>
       </c>
       <c r="G1340" s="3">
         <v>2</v>
       </c>
       <c r="H1340" s="2" t="s">
-        <v>6623</v>
+        <v>6621</v>
       </c>
       <c r="I1340" s="2" t="s">
         <v>845</v>
@@ -59946,25 +59952,25 @@
         <v>1340</v>
       </c>
       <c r="B1341" s="2" t="s">
+        <v>6622</v>
+      </c>
+      <c r="C1341" s="2" t="s">
+        <v>6623</v>
+      </c>
+      <c r="D1341" s="2" t="s">
         <v>6624</v>
       </c>
-      <c r="C1341" s="2" t="s">
+      <c r="E1341" s="2" t="s">
+        <v>6607</v>
+      </c>
+      <c r="F1341" s="2" t="s">
         <v>6625</v>
-      </c>
-      <c r="D1341" s="2" t="s">
-        <v>6626</v>
-      </c>
-      <c r="E1341" s="2" t="s">
-        <v>6609</v>
-      </c>
-      <c r="F1341" s="2" t="s">
-        <v>6627</v>
       </c>
       <c r="G1341" s="3">
         <v>4</v>
       </c>
       <c r="H1341" s="2" t="s">
-        <v>6628</v>
+        <v>6626</v>
       </c>
       <c r="I1341" s="2" t="s">
         <v>845</v>
@@ -59975,16 +59981,16 @@
         <v>1341</v>
       </c>
       <c r="B1342" s="2" t="s">
+        <v>6627</v>
+      </c>
+      <c r="C1342" s="2" t="s">
+        <v>6628</v>
+      </c>
+      <c r="D1342" s="2" t="s">
         <v>6629</v>
       </c>
-      <c r="C1342" s="2" t="s">
+      <c r="E1342" s="2" t="s">
         <v>6630</v>
-      </c>
-      <c r="D1342" s="2" t="s">
-        <v>6631</v>
-      </c>
-      <c r="E1342" s="2" t="s">
-        <v>6632</v>
       </c>
       <c r="F1342" s="2" t="s">
         <v>199</v>
@@ -60004,25 +60010,25 @@
         <v>1342</v>
       </c>
       <c r="B1343" s="2" t="s">
+        <v>6631</v>
+      </c>
+      <c r="C1343" s="2" t="s">
+        <v>6632</v>
+      </c>
+      <c r="D1343" s="2" t="s">
         <v>6633</v>
       </c>
-      <c r="C1343" s="2" t="s">
+      <c r="E1343" s="2" t="s">
         <v>6634</v>
       </c>
-      <c r="D1343" s="2" t="s">
+      <c r="F1343" s="2" t="s">
         <v>6635</v>
-      </c>
-      <c r="E1343" s="2" t="s">
-        <v>6636</v>
-      </c>
-      <c r="F1343" s="2" t="s">
-        <v>6637</v>
       </c>
       <c r="G1343" s="3">
         <v>3</v>
       </c>
       <c r="H1343" s="2" t="s">
-        <v>6638</v>
+        <v>6636</v>
       </c>
       <c r="I1343" s="2" t="s">
         <v>845</v>
@@ -60033,25 +60039,25 @@
         <v>1343</v>
       </c>
       <c r="B1344" s="2" t="s">
+        <v>6637</v>
+      </c>
+      <c r="C1344" s="2" t="s">
+        <v>6638</v>
+      </c>
+      <c r="D1344" s="2" t="s">
         <v>6639</v>
       </c>
-      <c r="C1344" s="2" t="s">
+      <c r="E1344" s="2" t="s">
         <v>6640</v>
       </c>
-      <c r="D1344" s="2" t="s">
+      <c r="F1344" s="2" t="s">
         <v>6641</v>
-      </c>
-      <c r="E1344" s="2" t="s">
-        <v>6642</v>
-      </c>
-      <c r="F1344" s="2" t="s">
-        <v>6643</v>
       </c>
       <c r="G1344" s="3">
         <v>4</v>
       </c>
       <c r="H1344" s="2" t="s">
-        <v>6644</v>
+        <v>6642</v>
       </c>
       <c r="I1344" s="2" t="s">
         <v>845</v>
@@ -60062,7 +60068,7 @@
         <v>1344</v>
       </c>
       <c r="B1345" s="2" t="s">
-        <v>6645</v>
+        <v>6643</v>
       </c>
       <c r="C1345" s="2" t="s">
         <v>523</v>
@@ -60071,7 +60077,7 @@
         <v>522</v>
       </c>
       <c r="E1345" s="2" t="s">
-        <v>6646</v>
+        <v>6644</v>
       </c>
       <c r="F1345" s="2"/>
       <c r="G1345" s="3">
@@ -60089,25 +60095,25 @@
         <v>1345</v>
       </c>
       <c r="B1346" s="2" t="s">
+        <v>6645</v>
+      </c>
+      <c r="C1346" s="2" t="s">
+        <v>6646</v>
+      </c>
+      <c r="D1346" s="2" t="s">
         <v>6647</v>
       </c>
-      <c r="C1346" s="2" t="s">
+      <c r="E1346" s="2" t="s">
         <v>6648</v>
       </c>
-      <c r="D1346" s="2" t="s">
+      <c r="F1346" s="2" t="s">
         <v>6649</v>
-      </c>
-      <c r="E1346" s="2" t="s">
-        <v>6650</v>
-      </c>
-      <c r="F1346" s="2" t="s">
-        <v>6651</v>
       </c>
       <c r="G1346" s="3">
         <v>4</v>
       </c>
       <c r="H1346" s="2" t="s">
-        <v>6652</v>
+        <v>6650</v>
       </c>
       <c r="I1346" s="2" t="s">
         <v>15</v>
@@ -60118,25 +60124,25 @@
         <v>1346</v>
       </c>
       <c r="B1347" s="2" t="s">
-        <v>6653</v>
+        <v>6651</v>
       </c>
       <c r="C1347" s="2" t="s">
         <v>1485</v>
       </c>
       <c r="D1347" s="2" t="s">
-        <v>6654</v>
+        <v>6652</v>
       </c>
       <c r="E1347" s="2" t="s">
         <v>1158</v>
       </c>
       <c r="F1347" s="2" t="s">
-        <v>6655</v>
+        <v>6653</v>
       </c>
       <c r="G1347" s="3">
         <v>2</v>
       </c>
       <c r="H1347" s="2" t="s">
-        <v>6656</v>
+        <v>6654</v>
       </c>
       <c r="I1347" s="2" t="s">
         <v>845</v>
@@ -60147,25 +60153,25 @@
         <v>1347</v>
       </c>
       <c r="B1348" s="2" t="s">
+        <v>6655</v>
+      </c>
+      <c r="C1348" s="2" t="s">
+        <v>6656</v>
+      </c>
+      <c r="D1348" s="2" t="s">
         <v>6657</v>
       </c>
-      <c r="C1348" s="2" t="s">
+      <c r="E1348" s="2" t="s">
         <v>6658</v>
       </c>
-      <c r="D1348" s="2" t="s">
+      <c r="F1348" s="2" t="s">
         <v>6659</v>
-      </c>
-      <c r="E1348" s="2" t="s">
-        <v>6660</v>
-      </c>
-      <c r="F1348" s="2" t="s">
-        <v>6661</v>
       </c>
       <c r="G1348" s="3">
         <v>4</v>
       </c>
       <c r="H1348" s="2" t="s">
-        <v>6662</v>
+        <v>6660</v>
       </c>
       <c r="I1348" s="2" t="s">
         <v>845</v>
@@ -60176,13 +60182,13 @@
         <v>1348</v>
       </c>
       <c r="B1349" s="2" t="s">
-        <v>6663</v>
+        <v>6661</v>
       </c>
       <c r="C1349" s="2" t="s">
         <v>119</v>
       </c>
       <c r="D1349" s="2" t="s">
-        <v>6664</v>
+        <v>6662</v>
       </c>
       <c r="E1349" s="2" t="s">
         <v>26</v>
@@ -60194,7 +60200,7 @@
         <v>4</v>
       </c>
       <c r="H1349" s="2" t="s">
-        <v>6665</v>
+        <v>6663</v>
       </c>
       <c r="I1349" s="2" t="s">
         <v>845</v>
@@ -60205,25 +60211,25 @@
         <v>1349</v>
       </c>
       <c r="B1350" s="2" t="s">
+        <v>6664</v>
+      </c>
+      <c r="C1350" s="2" t="s">
+        <v>6665</v>
+      </c>
+      <c r="D1350" s="2" t="s">
         <v>6666</v>
       </c>
-      <c r="C1350" s="2" t="s">
+      <c r="E1350" s="2" t="s">
         <v>6667</v>
       </c>
-      <c r="D1350" s="2" t="s">
+      <c r="F1350" s="2" t="s">
         <v>6668</v>
-      </c>
-      <c r="E1350" s="2" t="s">
-        <v>6669</v>
-      </c>
-      <c r="F1350" s="2" t="s">
-        <v>6670</v>
       </c>
       <c r="G1350" s="3">
         <v>4</v>
       </c>
       <c r="H1350" s="2" t="s">
-        <v>6671</v>
+        <v>6669</v>
       </c>
       <c r="I1350" s="2" t="s">
         <v>22</v>
@@ -60234,7 +60240,7 @@
         <v>1350</v>
       </c>
       <c r="B1351" s="2" t="s">
-        <v>6672</v>
+        <v>6670</v>
       </c>
       <c r="C1351" s="2" t="s">
         <v>791</v>
@@ -60243,7 +60249,7 @@
         <v>410</v>
       </c>
       <c r="E1351" s="2" t="s">
-        <v>6673</v>
+        <v>6671</v>
       </c>
       <c r="F1351" s="2" t="s">
         <v>809</v>
@@ -60252,7 +60258,7 @@
         <v>1</v>
       </c>
       <c r="H1351" s="2" t="s">
-        <v>6674</v>
+        <v>6672</v>
       </c>
       <c r="I1351" s="2" t="s">
         <v>22</v>
@@ -60263,25 +60269,25 @@
         <v>1351</v>
       </c>
       <c r="B1352" s="2" t="s">
+        <v>6673</v>
+      </c>
+      <c r="C1352" s="2" t="s">
+        <v>6674</v>
+      </c>
+      <c r="D1352" s="2" t="s">
         <v>6675</v>
       </c>
-      <c r="C1352" s="2" t="s">
+      <c r="E1352" s="2" t="s">
         <v>6676</v>
       </c>
-      <c r="D1352" s="2" t="s">
+      <c r="F1352" s="2" t="s">
         <v>6677</v>
-      </c>
-      <c r="E1352" s="2" t="s">
-        <v>6678</v>
-      </c>
-      <c r="F1352" s="2" t="s">
-        <v>6679</v>
       </c>
       <c r="G1352" s="3">
         <v>1</v>
       </c>
       <c r="H1352" s="2" t="s">
-        <v>6680</v>
+        <v>6678</v>
       </c>
       <c r="I1352" s="2" t="s">
         <v>22</v>
@@ -60292,7 +60298,7 @@
         <v>1352</v>
       </c>
       <c r="B1353" s="2" t="s">
-        <v>6681</v>
+        <v>6679</v>
       </c>
       <c r="C1353" s="2" t="s">
         <v>162</v>
@@ -60310,7 +60316,7 @@
         <v>1</v>
       </c>
       <c r="H1353" s="2" t="s">
-        <v>6682</v>
+        <v>6680</v>
       </c>
       <c r="I1353" s="2" t="s">
         <v>15</v>
@@ -60321,23 +60327,23 @@
         <v>1353</v>
       </c>
       <c r="B1354" s="2" t="s">
+        <v>6681</v>
+      </c>
+      <c r="C1354" s="2" t="s">
+        <v>6682</v>
+      </c>
+      <c r="D1354" s="2" t="s">
         <v>6683</v>
       </c>
-      <c r="C1354" s="2" t="s">
+      <c r="E1354" s="2" t="s">
         <v>6684</v>
-      </c>
-      <c r="D1354" s="2" t="s">
-        <v>6685</v>
-      </c>
-      <c r="E1354" s="2" t="s">
-        <v>6686</v>
       </c>
       <c r="F1354" s="2"/>
       <c r="G1354" s="3">
         <v>1</v>
       </c>
       <c r="H1354" s="2" t="s">
-        <v>6687</v>
+        <v>6685</v>
       </c>
       <c r="I1354" s="2" t="s">
         <v>845</v>
@@ -60348,7 +60354,7 @@
         <v>1354</v>
       </c>
       <c r="B1355" s="2" t="s">
-        <v>6688</v>
+        <v>6686</v>
       </c>
       <c r="C1355" s="2" t="s">
         <v>861</v>
@@ -60364,7 +60370,7 @@
         <v>4</v>
       </c>
       <c r="H1355" s="2" t="s">
-        <v>6689</v>
+        <v>6687</v>
       </c>
       <c r="I1355" s="2" t="s">
         <v>845</v>
@@ -60375,25 +60381,25 @@
         <v>1355</v>
       </c>
       <c r="B1356" s="2" t="s">
+        <v>6688</v>
+      </c>
+      <c r="C1356" s="2" t="s">
+        <v>6689</v>
+      </c>
+      <c r="D1356" s="2" t="s">
         <v>6690</v>
       </c>
-      <c r="C1356" s="2" t="s">
+      <c r="E1356" s="2" t="s">
         <v>6691</v>
       </c>
-      <c r="D1356" s="2" t="s">
+      <c r="F1356" s="2" t="s">
         <v>6692</v>
-      </c>
-      <c r="E1356" s="2" t="s">
-        <v>6693</v>
-      </c>
-      <c r="F1356" s="2" t="s">
-        <v>6694</v>
       </c>
       <c r="G1356" s="3">
         <v>2</v>
       </c>
       <c r="H1356" s="2" t="s">
-        <v>6695</v>
+        <v>6693</v>
       </c>
       <c r="I1356" s="2" t="s">
         <v>845</v>
@@ -60404,25 +60410,25 @@
         <v>1356</v>
       </c>
       <c r="B1357" s="2" t="s">
+        <v>6694</v>
+      </c>
+      <c r="C1357" s="2" t="s">
+        <v>6695</v>
+      </c>
+      <c r="D1357" s="2" t="s">
         <v>6696</v>
       </c>
-      <c r="C1357" s="2" t="s">
+      <c r="E1357" s="2" t="s">
         <v>6697</v>
       </c>
-      <c r="D1357" s="2" t="s">
+      <c r="F1357" s="2" t="s">
         <v>6698</v>
-      </c>
-      <c r="E1357" s="2" t="s">
-        <v>6699</v>
-      </c>
-      <c r="F1357" s="2" t="s">
-        <v>6700</v>
       </c>
       <c r="G1357" s="3">
         <v>2</v>
       </c>
       <c r="H1357" s="2" t="s">
-        <v>6701</v>
+        <v>6699</v>
       </c>
       <c r="I1357" s="2" t="s">
         <v>845</v>
@@ -60433,25 +60439,25 @@
         <v>1357</v>
       </c>
       <c r="B1358" s="2" t="s">
+        <v>6700</v>
+      </c>
+      <c r="C1358" s="2" t="s">
+        <v>6701</v>
+      </c>
+      <c r="D1358" s="2" t="s">
         <v>6702</v>
       </c>
-      <c r="C1358" s="2" t="s">
+      <c r="E1358" s="2" t="s">
         <v>6703</v>
       </c>
-      <c r="D1358" s="2" t="s">
+      <c r="F1358" s="2" t="s">
         <v>6704</v>
-      </c>
-      <c r="E1358" s="2" t="s">
-        <v>6705</v>
-      </c>
-      <c r="F1358" s="2" t="s">
-        <v>6706</v>
       </c>
       <c r="G1358" s="3">
         <v>4</v>
       </c>
       <c r="H1358" s="2" t="s">
-        <v>6707</v>
+        <v>6705</v>
       </c>
       <c r="I1358" s="2" t="s">
         <v>845</v>
@@ -60462,25 +60468,25 @@
         <v>1358</v>
       </c>
       <c r="B1359" s="2" t="s">
+        <v>6706</v>
+      </c>
+      <c r="C1359" s="2" t="s">
+        <v>6707</v>
+      </c>
+      <c r="D1359" s="2" t="s">
         <v>6708</v>
       </c>
-      <c r="C1359" s="2" t="s">
+      <c r="E1359" s="2" t="s">
         <v>6709</v>
       </c>
-      <c r="D1359" s="2" t="s">
+      <c r="F1359" s="2" t="s">
         <v>6710</v>
-      </c>
-      <c r="E1359" s="2" t="s">
-        <v>6711</v>
-      </c>
-      <c r="F1359" s="2" t="s">
-        <v>6712</v>
       </c>
       <c r="G1359" s="3">
         <v>4</v>
       </c>
       <c r="H1359" s="2" t="s">
-        <v>6713</v>
+        <v>6711</v>
       </c>
       <c r="I1359" s="2" t="s">
         <v>845</v>
@@ -60491,23 +60497,23 @@
         <v>1359</v>
       </c>
       <c r="B1360" s="2" t="s">
-        <v>6714</v>
+        <v>6712</v>
       </c>
       <c r="C1360" s="2" t="s">
-        <v>6715</v>
+        <v>6713</v>
       </c>
       <c r="D1360" s="2"/>
       <c r="E1360" s="2" t="s">
-        <v>6716</v>
+        <v>6714</v>
       </c>
       <c r="F1360" s="2" t="s">
-        <v>6717</v>
+        <v>6715</v>
       </c>
       <c r="G1360" s="3">
         <v>1</v>
       </c>
       <c r="H1360" s="2" t="s">
-        <v>6718</v>
+        <v>6716</v>
       </c>
       <c r="I1360" s="2" t="s">
         <v>845</v>
@@ -60518,25 +60524,25 @@
         <v>1360</v>
       </c>
       <c r="B1361" s="2" t="s">
+        <v>6717</v>
+      </c>
+      <c r="C1361" s="2" t="s">
+        <v>6718</v>
+      </c>
+      <c r="D1361" s="2" t="s">
         <v>6719</v>
       </c>
-      <c r="C1361" s="2" t="s">
+      <c r="E1361" s="2" t="s">
         <v>6720</v>
       </c>
-      <c r="D1361" s="2" t="s">
+      <c r="F1361" s="2" t="s">
         <v>6721</v>
-      </c>
-      <c r="E1361" s="2" t="s">
-        <v>6722</v>
-      </c>
-      <c r="F1361" s="2" t="s">
-        <v>6723</v>
       </c>
       <c r="G1361" s="3">
         <v>3</v>
       </c>
       <c r="H1361" s="2" t="s">
-        <v>6724</v>
+        <v>6722</v>
       </c>
       <c r="I1361" s="2" t="s">
         <v>15</v>
@@ -60547,7 +60553,7 @@
         <v>1361</v>
       </c>
       <c r="B1362" s="2" t="s">
-        <v>6725</v>
+        <v>6723</v>
       </c>
       <c r="C1362" s="2" t="s">
         <v>1351</v>
@@ -60556,10 +60562,10 @@
         <v>1352</v>
       </c>
       <c r="E1362" s="2" t="s">
-        <v>6726</v>
+        <v>6724</v>
       </c>
       <c r="F1362" s="2" t="s">
-        <v>6727</v>
+        <v>6725</v>
       </c>
       <c r="G1362" s="3">
         <v>1</v>
@@ -60576,25 +60582,25 @@
         <v>1362</v>
       </c>
       <c r="B1363" s="2" t="s">
+        <v>6726</v>
+      </c>
+      <c r="C1363" s="2" t="s">
+        <v>6727</v>
+      </c>
+      <c r="D1363" s="2" t="s">
         <v>6728</v>
       </c>
-      <c r="C1363" s="2" t="s">
+      <c r="E1363" s="2" t="s">
         <v>6729</v>
       </c>
-      <c r="D1363" s="2" t="s">
+      <c r="F1363" s="2" t="s">
         <v>6730</v>
-      </c>
-      <c r="E1363" s="2" t="s">
-        <v>6731</v>
-      </c>
-      <c r="F1363" s="2" t="s">
-        <v>6732</v>
       </c>
       <c r="G1363" s="3">
         <v>2</v>
       </c>
       <c r="H1363" s="2" t="s">
-        <v>6733</v>
+        <v>6731</v>
       </c>
       <c r="I1363" s="2" t="s">
         <v>15</v>
@@ -60605,25 +60611,25 @@
         <v>1363</v>
       </c>
       <c r="B1364" s="2" t="s">
+        <v>6732</v>
+      </c>
+      <c r="C1364" s="2" t="s">
+        <v>6733</v>
+      </c>
+      <c r="D1364" s="2" t="s">
         <v>6734</v>
       </c>
-      <c r="C1364" s="2" t="s">
+      <c r="E1364" s="2" t="s">
         <v>6735</v>
       </c>
-      <c r="D1364" s="2" t="s">
+      <c r="F1364" s="2" t="s">
         <v>6736</v>
-      </c>
-      <c r="E1364" s="2" t="s">
-        <v>6737</v>
-      </c>
-      <c r="F1364" s="2" t="s">
-        <v>6738</v>
       </c>
       <c r="G1364" s="3">
         <v>1</v>
       </c>
       <c r="H1364" s="2" t="s">
-        <v>6739</v>
+        <v>6737</v>
       </c>
       <c r="I1364" s="2" t="s">
         <v>15</v>
@@ -60663,7 +60669,7 @@
         <v>1365</v>
       </c>
       <c r="B1366" s="2" t="s">
-        <v>6740</v>
+        <v>6738</v>
       </c>
       <c r="C1366" s="2" t="s">
         <v>1417</v>
@@ -60681,7 +60687,7 @@
         <v>3</v>
       </c>
       <c r="H1366" s="2" t="s">
-        <v>6741</v>
+        <v>6739</v>
       </c>
       <c r="I1366" s="2" t="s">
         <v>15</v>
@@ -60692,25 +60698,25 @@
         <v>1366</v>
       </c>
       <c r="B1367" s="2" t="s">
+        <v>6740</v>
+      </c>
+      <c r="C1367" s="2" t="s">
+        <v>6741</v>
+      </c>
+      <c r="D1367" s="2" t="s">
         <v>6742</v>
       </c>
-      <c r="C1367" s="2" t="s">
+      <c r="E1367" s="2" t="s">
         <v>6743</v>
       </c>
-      <c r="D1367" s="2" t="s">
+      <c r="F1367" s="2" t="s">
         <v>6744</v>
-      </c>
-      <c r="E1367" s="2" t="s">
-        <v>6745</v>
-      </c>
-      <c r="F1367" s="2" t="s">
-        <v>6746</v>
       </c>
       <c r="G1367" s="3">
         <v>3</v>
       </c>
       <c r="H1367" s="2" t="s">
-        <v>6747</v>
+        <v>6745</v>
       </c>
       <c r="I1367" s="2" t="s">
         <v>845</v>
@@ -60721,16 +60727,16 @@
         <v>1367</v>
       </c>
       <c r="B1368" s="2" t="s">
+        <v>6746</v>
+      </c>
+      <c r="C1368" s="2" t="s">
+        <v>6747</v>
+      </c>
+      <c r="D1368" s="2" t="s">
         <v>6748</v>
       </c>
-      <c r="C1368" s="2" t="s">
+      <c r="E1368" s="2" t="s">
         <v>6749</v>
-      </c>
-      <c r="D1368" s="2" t="s">
-        <v>6750</v>
-      </c>
-      <c r="E1368" s="2" t="s">
-        <v>6751</v>
       </c>
       <c r="F1368" s="2" t="s">
         <v>51</v>
@@ -60750,25 +60756,25 @@
         <v>1368</v>
       </c>
       <c r="B1369" s="2" t="s">
+        <v>6750</v>
+      </c>
+      <c r="C1369" s="2" t="s">
+        <v>6751</v>
+      </c>
+      <c r="D1369" s="2" t="s">
         <v>6752</v>
       </c>
-      <c r="C1369" s="2" t="s">
+      <c r="E1369" s="2" t="s">
         <v>6753</v>
       </c>
-      <c r="D1369" s="2" t="s">
+      <c r="F1369" s="2" t="s">
         <v>6754</v>
-      </c>
-      <c r="E1369" s="2" t="s">
-        <v>6755</v>
-      </c>
-      <c r="F1369" s="2" t="s">
-        <v>6756</v>
       </c>
       <c r="G1369" s="3">
         <v>3</v>
       </c>
       <c r="H1369" s="2" t="s">
-        <v>6757</v>
+        <v>6755</v>
       </c>
       <c r="I1369" s="2" t="s">
         <v>816</v>
@@ -60779,25 +60785,25 @@
         <v>1369</v>
       </c>
       <c r="B1370" s="2" t="s">
-        <v>6758</v>
+        <v>6756</v>
       </c>
       <c r="C1370" s="2" t="s">
         <v>1711</v>
       </c>
       <c r="D1370" s="2" t="s">
+        <v>6757</v>
+      </c>
+      <c r="E1370" s="2" t="s">
+        <v>6758</v>
+      </c>
+      <c r="F1370" s="2" t="s">
         <v>6759</v>
-      </c>
-      <c r="E1370" s="2" t="s">
-        <v>6760</v>
-      </c>
-      <c r="F1370" s="2" t="s">
-        <v>6761</v>
       </c>
       <c r="G1370" s="3">
         <v>3</v>
       </c>
       <c r="H1370" s="2" t="s">
-        <v>6762</v>
+        <v>6760</v>
       </c>
       <c r="I1370" s="2" t="s">
         <v>15</v>
@@ -60808,25 +60814,25 @@
         <v>1370</v>
       </c>
       <c r="B1371" s="2" t="s">
+        <v>6761</v>
+      </c>
+      <c r="C1371" s="2" t="s">
+        <v>6762</v>
+      </c>
+      <c r="D1371" s="2" t="s">
         <v>6763</v>
       </c>
-      <c r="C1371" s="2" t="s">
+      <c r="E1371" s="2" t="s">
         <v>6764</v>
       </c>
-      <c r="D1371" s="2" t="s">
+      <c r="F1371" s="2" t="s">
         <v>6765</v>
-      </c>
-      <c r="E1371" s="2" t="s">
-        <v>6766</v>
-      </c>
-      <c r="F1371" s="2" t="s">
-        <v>6767</v>
       </c>
       <c r="G1371" s="3">
         <v>2</v>
       </c>
       <c r="H1371" s="2" t="s">
-        <v>6768</v>
+        <v>6766</v>
       </c>
       <c r="I1371" s="2" t="s">
         <v>15</v>
@@ -60837,13 +60843,13 @@
         <v>1371</v>
       </c>
       <c r="B1372" s="2" t="s">
-        <v>6769</v>
+        <v>6767</v>
       </c>
       <c r="C1372" s="2" t="s">
         <v>2451</v>
       </c>
       <c r="D1372" s="2" t="s">
-        <v>6770</v>
+        <v>6768</v>
       </c>
       <c r="E1372" s="2" t="s">
         <v>2452</v>
@@ -60855,7 +60861,7 @@
         <v>2</v>
       </c>
       <c r="H1372" s="2" t="s">
-        <v>6771</v>
+        <v>6769</v>
       </c>
       <c r="I1372" s="2" t="s">
         <v>15</v>
@@ -60866,25 +60872,25 @@
         <v>1372</v>
       </c>
       <c r="B1373" s="2" t="s">
-        <v>6772</v>
+        <v>6770</v>
       </c>
       <c r="C1373" s="2" t="s">
         <v>2389</v>
       </c>
       <c r="D1373" s="2" t="s">
+        <v>6771</v>
+      </c>
+      <c r="E1373" s="2" t="s">
+        <v>6772</v>
+      </c>
+      <c r="F1373" s="2" t="s">
         <v>6773</v>
-      </c>
-      <c r="E1373" s="2" t="s">
-        <v>6774</v>
-      </c>
-      <c r="F1373" s="2" t="s">
-        <v>6775</v>
       </c>
       <c r="G1373" s="3">
         <v>2</v>
       </c>
       <c r="H1373" s="2" t="s">
-        <v>6776</v>
+        <v>6774</v>
       </c>
       <c r="I1373" s="2" t="s">
         <v>15</v>
@@ -60895,25 +60901,25 @@
         <v>1373</v>
       </c>
       <c r="B1374" s="2" t="s">
+        <v>6775</v>
+      </c>
+      <c r="C1374" s="2" t="s">
+        <v>6776</v>
+      </c>
+      <c r="D1374" s="2" t="s">
         <v>6777</v>
       </c>
-      <c r="C1374" s="2" t="s">
+      <c r="E1374" s="2" t="s">
         <v>6778</v>
       </c>
-      <c r="D1374" s="2" t="s">
+      <c r="F1374" s="2" t="s">
         <v>6779</v>
-      </c>
-      <c r="E1374" s="2" t="s">
-        <v>6780</v>
-      </c>
-      <c r="F1374" s="2" t="s">
-        <v>6781</v>
       </c>
       <c r="G1374" s="3">
         <v>4</v>
       </c>
       <c r="H1374" s="2" t="s">
-        <v>6782</v>
+        <v>6780</v>
       </c>
       <c r="I1374" s="2" t="s">
         <v>15</v>
@@ -60924,25 +60930,25 @@
         <v>1374</v>
       </c>
       <c r="B1375" s="2" t="s">
+        <v>6781</v>
+      </c>
+      <c r="C1375" s="2" t="s">
+        <v>6782</v>
+      </c>
+      <c r="D1375" s="2" t="s">
         <v>6783</v>
       </c>
-      <c r="C1375" s="2" t="s">
+      <c r="E1375" s="2" t="s">
         <v>6784</v>
       </c>
-      <c r="D1375" s="2" t="s">
+      <c r="F1375" s="2" t="s">
         <v>6785</v>
-      </c>
-      <c r="E1375" s="2" t="s">
-        <v>6786</v>
-      </c>
-      <c r="F1375" s="2" t="s">
-        <v>6787</v>
       </c>
       <c r="G1375" s="3">
         <v>1</v>
       </c>
       <c r="H1375" s="2" t="s">
-        <v>6788</v>
+        <v>6786</v>
       </c>
       <c r="I1375" s="2" t="s">
         <v>845</v>
@@ -60953,25 +60959,25 @@
         <v>1375</v>
       </c>
       <c r="B1376" s="2" t="s">
+        <v>6787</v>
+      </c>
+      <c r="C1376" s="2" t="s">
+        <v>6788</v>
+      </c>
+      <c r="D1376" s="2" t="s">
         <v>6789</v>
       </c>
-      <c r="C1376" s="2" t="s">
+      <c r="E1376" s="2" t="s">
         <v>6790</v>
       </c>
-      <c r="D1376" s="2" t="s">
+      <c r="F1376" s="2" t="s">
         <v>6791</v>
-      </c>
-      <c r="E1376" s="2" t="s">
-        <v>6792</v>
-      </c>
-      <c r="F1376" s="2" t="s">
-        <v>6793</v>
       </c>
       <c r="G1376" s="3">
         <v>2</v>
       </c>
       <c r="H1376" s="2" t="s">
-        <v>6794</v>
+        <v>6792</v>
       </c>
       <c r="I1376" s="2" t="s">
         <v>845</v>
@@ -60982,25 +60988,25 @@
         <v>1376</v>
       </c>
       <c r="B1377" s="2" t="s">
+        <v>6793</v>
+      </c>
+      <c r="C1377" s="2" t="s">
+        <v>6794</v>
+      </c>
+      <c r="D1377" s="2" t="s">
         <v>6795</v>
       </c>
-      <c r="C1377" s="2" t="s">
+      <c r="E1377" s="2" t="s">
         <v>6796</v>
       </c>
-      <c r="D1377" s="2" t="s">
+      <c r="F1377" s="2" t="s">
         <v>6797</v>
-      </c>
-      <c r="E1377" s="2" t="s">
-        <v>6798</v>
-      </c>
-      <c r="F1377" s="2" t="s">
-        <v>6799</v>
       </c>
       <c r="G1377" s="3">
         <v>3</v>
       </c>
       <c r="H1377" s="2" t="s">
-        <v>6800</v>
+        <v>6798</v>
       </c>
       <c r="I1377" s="2" t="s">
         <v>15</v>
@@ -61011,7 +61017,7 @@
         <v>1377</v>
       </c>
       <c r="B1378" s="2" t="s">
-        <v>6801</v>
+        <v>6799</v>
       </c>
       <c r="C1378" s="2" t="s">
         <v>77</v>
@@ -61040,25 +61046,25 @@
         <v>1378</v>
       </c>
       <c r="B1379" s="2" t="s">
+        <v>6800</v>
+      </c>
+      <c r="C1379" s="2" t="s">
+        <v>6801</v>
+      </c>
+      <c r="D1379" s="2" t="s">
         <v>6802</v>
       </c>
-      <c r="C1379" s="2" t="s">
+      <c r="E1379" s="2" t="s">
         <v>6803</v>
       </c>
-      <c r="D1379" s="2" t="s">
+      <c r="F1379" s="2" t="s">
         <v>6804</v>
-      </c>
-      <c r="E1379" s="2" t="s">
-        <v>6805</v>
-      </c>
-      <c r="F1379" s="2" t="s">
-        <v>6806</v>
       </c>
       <c r="G1379" s="3">
         <v>1</v>
       </c>
       <c r="H1379" s="2" t="s">
-        <v>6807</v>
+        <v>6805</v>
       </c>
       <c r="I1379" s="2" t="s">
         <v>845</v>
@@ -61069,7 +61075,7 @@
         <v>1379</v>
       </c>
       <c r="B1380" s="2" t="s">
-        <v>6808</v>
+        <v>6806</v>
       </c>
       <c r="C1380" s="2" t="s">
         <v>383</v>
@@ -61087,7 +61093,7 @@
         <v>1</v>
       </c>
       <c r="H1380" s="2" t="s">
-        <v>6809</v>
+        <v>6807</v>
       </c>
       <c r="I1380" s="2" t="s">
         <v>845</v>
@@ -61098,10 +61104,10 @@
         <v>1380</v>
       </c>
       <c r="B1381" s="2" t="s">
-        <v>6810</v>
+        <v>6808</v>
       </c>
       <c r="C1381" s="2" t="s">
-        <v>6811</v>
+        <v>6809</v>
       </c>
       <c r="D1381" s="2" t="s">
         <v>12</v>
@@ -61110,13 +61116,13 @@
         <v>910</v>
       </c>
       <c r="F1381" s="2" t="s">
-        <v>6812</v>
+        <v>6810</v>
       </c>
       <c r="G1381" s="3">
         <v>1</v>
       </c>
       <c r="H1381" s="2" t="s">
-        <v>6813</v>
+        <v>6811</v>
       </c>
       <c r="I1381" s="2" t="s">
         <v>845</v>
@@ -61127,25 +61133,25 @@
         <v>1381</v>
       </c>
       <c r="B1382" s="2" t="s">
+        <v>6812</v>
+      </c>
+      <c r="C1382" s="2" t="s">
+        <v>6813</v>
+      </c>
+      <c r="D1382" s="2" t="s">
         <v>6814</v>
       </c>
-      <c r="C1382" s="2" t="s">
+      <c r="E1382" s="2" t="s">
         <v>6815</v>
       </c>
-      <c r="D1382" s="2" t="s">
+      <c r="F1382" s="2" t="s">
         <v>6816</v>
-      </c>
-      <c r="E1382" s="2" t="s">
-        <v>6817</v>
-      </c>
-      <c r="F1382" s="2" t="s">
-        <v>6818</v>
       </c>
       <c r="G1382" s="3">
         <v>2</v>
       </c>
       <c r="H1382" s="2" t="s">
-        <v>6819</v>
+        <v>6817</v>
       </c>
       <c r="I1382" s="2" t="s">
         <v>15</v>
@@ -61156,25 +61162,25 @@
         <v>1382</v>
       </c>
       <c r="B1383" s="2" t="s">
-        <v>6820</v>
+        <v>6818</v>
       </c>
       <c r="C1383" s="2" t="s">
         <v>1495</v>
       </c>
       <c r="D1383" s="2" t="s">
+        <v>6819</v>
+      </c>
+      <c r="E1383" s="2" t="s">
+        <v>6820</v>
+      </c>
+      <c r="F1383" s="2" t="s">
         <v>6821</v>
-      </c>
-      <c r="E1383" s="2" t="s">
-        <v>6822</v>
-      </c>
-      <c r="F1383" s="2" t="s">
-        <v>6823</v>
       </c>
       <c r="G1383" s="3">
         <v>4</v>
       </c>
       <c r="H1383" s="2" t="s">
-        <v>6824</v>
+        <v>6822</v>
       </c>
       <c r="I1383" s="2" t="s">
         <v>15</v>
@@ -61185,25 +61191,25 @@
         <v>1383</v>
       </c>
       <c r="B1384" s="2" t="s">
+        <v>6823</v>
+      </c>
+      <c r="C1384" s="2" t="s">
+        <v>6607</v>
+      </c>
+      <c r="D1384" s="2" t="s">
+        <v>6824</v>
+      </c>
+      <c r="E1384" s="2" t="s">
         <v>6825</v>
       </c>
-      <c r="C1384" s="2" t="s">
-        <v>6609</v>
-      </c>
-      <c r="D1384" s="2" t="s">
+      <c r="F1384" s="2" t="s">
         <v>6826</v>
-      </c>
-      <c r="E1384" s="2" t="s">
-        <v>6827</v>
-      </c>
-      <c r="F1384" s="2" t="s">
-        <v>6828</v>
       </c>
       <c r="G1384" s="3">
         <v>4</v>
       </c>
       <c r="H1384" s="2" t="s">
-        <v>6829</v>
+        <v>6827</v>
       </c>
       <c r="I1384" s="2" t="s">
         <v>845</v>
@@ -61214,25 +61220,25 @@
         <v>1384</v>
       </c>
       <c r="B1385" s="2" t="s">
+        <v>6828</v>
+      </c>
+      <c r="C1385" s="2" t="s">
+        <v>6829</v>
+      </c>
+      <c r="D1385" s="2" t="s">
         <v>6830</v>
       </c>
-      <c r="C1385" s="2" t="s">
+      <c r="E1385" s="2" t="s">
         <v>6831</v>
       </c>
-      <c r="D1385" s="2" t="s">
+      <c r="F1385" s="2" t="s">
         <v>6832</v>
-      </c>
-      <c r="E1385" s="2" t="s">
-        <v>6833</v>
-      </c>
-      <c r="F1385" s="2" t="s">
-        <v>6834</v>
       </c>
       <c r="G1385" s="3">
         <v>3</v>
       </c>
       <c r="H1385" s="2" t="s">
-        <v>6835</v>
+        <v>6833</v>
       </c>
       <c r="I1385" s="2" t="s">
         <v>845</v>
@@ -61243,25 +61249,25 @@
         <v>1385</v>
       </c>
       <c r="B1386" s="2" t="s">
+        <v>6834</v>
+      </c>
+      <c r="C1386" s="2" t="s">
+        <v>6835</v>
+      </c>
+      <c r="D1386" s="2" t="s">
         <v>6836</v>
       </c>
-      <c r="C1386" s="2" t="s">
+      <c r="E1386" s="2" t="s">
         <v>6837</v>
       </c>
-      <c r="D1386" s="2" t="s">
+      <c r="F1386" s="2" t="s">
         <v>6838</v>
-      </c>
-      <c r="E1386" s="2" t="s">
-        <v>6839</v>
-      </c>
-      <c r="F1386" s="2" t="s">
-        <v>6840</v>
       </c>
       <c r="G1386" s="3">
         <v>3</v>
       </c>
       <c r="H1386" s="2" t="s">
-        <v>6841</v>
+        <v>6839</v>
       </c>
       <c r="I1386" s="2" t="s">
         <v>15</v>
@@ -61272,21 +61278,21 @@
         <v>1386</v>
       </c>
       <c r="B1387" s="2" t="s">
-        <v>6842</v>
+        <v>6840</v>
       </c>
       <c r="C1387" s="2" t="s">
-        <v>6843</v>
+        <v>6841</v>
       </c>
       <c r="D1387" s="2"/>
       <c r="E1387" s="2"/>
       <c r="F1387" s="2" t="s">
-        <v>6844</v>
+        <v>6842</v>
       </c>
       <c r="G1387" s="3">
         <v>1</v>
       </c>
       <c r="H1387" s="2" t="s">
-        <v>6845</v>
+        <v>6843</v>
       </c>
       <c r="I1387" s="2" t="s">
         <v>15</v>
@@ -61297,25 +61303,25 @@
         <v>1387</v>
       </c>
       <c r="B1388" s="2" t="s">
-        <v>6846</v>
+        <v>6844</v>
       </c>
       <c r="C1388" s="2" t="s">
-        <v>6847</v>
+        <v>6845</v>
       </c>
       <c r="D1388" s="2" t="s">
         <v>44</v>
       </c>
       <c r="E1388" s="2" t="s">
-        <v>6848</v>
+        <v>6846</v>
       </c>
       <c r="F1388" s="2" t="s">
-        <v>6849</v>
+        <v>6847</v>
       </c>
       <c r="G1388" s="3">
         <v>1</v>
       </c>
       <c r="H1388" s="2" t="s">
-        <v>6850</v>
+        <v>6848</v>
       </c>
       <c r="I1388" s="2" t="s">
         <v>845</v>
@@ -61326,25 +61332,25 @@
         <v>1388</v>
       </c>
       <c r="B1389" s="2" t="s">
+        <v>6849</v>
+      </c>
+      <c r="C1389" s="2" t="s">
+        <v>6850</v>
+      </c>
+      <c r="D1389" s="2" t="s">
         <v>6851</v>
       </c>
-      <c r="C1389" s="2" t="s">
+      <c r="E1389" s="2" t="s">
         <v>6852</v>
       </c>
-      <c r="D1389" s="2" t="s">
+      <c r="F1389" s="2" t="s">
         <v>6853</v>
-      </c>
-      <c r="E1389" s="2" t="s">
-        <v>6854</v>
-      </c>
-      <c r="F1389" s="2" t="s">
-        <v>6855</v>
       </c>
       <c r="G1389" s="3">
         <v>1</v>
       </c>
       <c r="H1389" s="2" t="s">
-        <v>6856</v>
+        <v>6854</v>
       </c>
       <c r="I1389" s="2" t="s">
         <v>15</v>
@@ -61355,25 +61361,25 @@
         <v>1389</v>
       </c>
       <c r="B1390" s="2" t="s">
+        <v>6855</v>
+      </c>
+      <c r="C1390" s="2" t="s">
+        <v>6856</v>
+      </c>
+      <c r="D1390" s="2" t="s">
         <v>6857</v>
       </c>
-      <c r="C1390" s="2" t="s">
+      <c r="E1390" s="2" t="s">
         <v>6858</v>
       </c>
-      <c r="D1390" s="2" t="s">
+      <c r="F1390" s="2" t="s">
         <v>6859</v>
-      </c>
-      <c r="E1390" s="2" t="s">
-        <v>6860</v>
-      </c>
-      <c r="F1390" s="2" t="s">
-        <v>6861</v>
       </c>
       <c r="G1390" s="3">
         <v>4</v>
       </c>
       <c r="H1390" s="2" t="s">
-        <v>6862</v>
+        <v>6860</v>
       </c>
       <c r="I1390" s="2" t="s">
         <v>15</v>
@@ -61384,25 +61390,25 @@
         <v>1390</v>
       </c>
       <c r="B1391" s="2" t="s">
+        <v>6861</v>
+      </c>
+      <c r="C1391" s="2" t="s">
+        <v>6862</v>
+      </c>
+      <c r="D1391" s="2" t="s">
         <v>6863</v>
       </c>
-      <c r="C1391" s="2" t="s">
+      <c r="E1391" s="2" t="s">
         <v>6864</v>
       </c>
-      <c r="D1391" s="2" t="s">
+      <c r="F1391" s="2" t="s">
         <v>6865</v>
-      </c>
-      <c r="E1391" s="2" t="s">
-        <v>6866</v>
-      </c>
-      <c r="F1391" s="2" t="s">
-        <v>6867</v>
       </c>
       <c r="G1391" s="3">
         <v>1</v>
       </c>
       <c r="H1391" s="2" t="s">
-        <v>6868</v>
+        <v>6866</v>
       </c>
       <c r="I1391" s="2" t="s">
         <v>15</v>
@@ -61413,25 +61419,25 @@
         <v>1391</v>
       </c>
       <c r="B1392" s="2" t="s">
+        <v>6867</v>
+      </c>
+      <c r="C1392" s="2" t="s">
+        <v>6868</v>
+      </c>
+      <c r="D1392" s="2" t="s">
         <v>6869</v>
       </c>
-      <c r="C1392" s="2" t="s">
+      <c r="E1392" s="2" t="s">
         <v>6870</v>
       </c>
-      <c r="D1392" s="2" t="s">
+      <c r="F1392" s="2" t="s">
         <v>6871</v>
-      </c>
-      <c r="E1392" s="2" t="s">
-        <v>6872</v>
-      </c>
-      <c r="F1392" s="2" t="s">
-        <v>6873</v>
       </c>
       <c r="G1392" s="3">
         <v>2</v>
       </c>
       <c r="H1392" s="2" t="s">
-        <v>6874</v>
+        <v>6872</v>
       </c>
       <c r="I1392" s="2" t="s">
         <v>15</v>
@@ -61442,25 +61448,25 @@
         <v>1392</v>
       </c>
       <c r="B1393" s="2" t="s">
+        <v>6873</v>
+      </c>
+      <c r="C1393" s="2" t="s">
+        <v>6874</v>
+      </c>
+      <c r="D1393" s="2" t="s">
         <v>6875</v>
       </c>
-      <c r="C1393" s="2" t="s">
+      <c r="E1393" s="2" t="s">
         <v>6876</v>
       </c>
-      <c r="D1393" s="2" t="s">
+      <c r="F1393" s="2" t="s">
         <v>6877</v>
-      </c>
-      <c r="E1393" s="2" t="s">
-        <v>6878</v>
-      </c>
-      <c r="F1393" s="2" t="s">
-        <v>6879</v>
       </c>
       <c r="G1393" s="3">
         <v>4</v>
       </c>
       <c r="H1393" s="2" t="s">
-        <v>6880</v>
+        <v>6878</v>
       </c>
       <c r="I1393" s="2" t="s">
         <v>845</v>
@@ -61471,25 +61477,25 @@
         <v>1393</v>
       </c>
       <c r="B1394" s="2" t="s">
+        <v>6879</v>
+      </c>
+      <c r="C1394" s="2" t="s">
+        <v>6874</v>
+      </c>
+      <c r="D1394" s="2" t="s">
+        <v>6880</v>
+      </c>
+      <c r="E1394" s="2" t="s">
         <v>6881</v>
       </c>
-      <c r="C1394" s="2" t="s">
-        <v>6876</v>
-      </c>
-      <c r="D1394" s="2" t="s">
+      <c r="F1394" s="2" t="s">
         <v>6882</v>
-      </c>
-      <c r="E1394" s="2" t="s">
-        <v>6883</v>
-      </c>
-      <c r="F1394" s="2" t="s">
-        <v>6884</v>
       </c>
       <c r="G1394" s="3">
         <v>3</v>
       </c>
       <c r="H1394" s="2" t="s">
-        <v>6885</v>
+        <v>6883</v>
       </c>
       <c r="I1394" s="2" t="s">
         <v>845</v>
@@ -61500,7 +61506,7 @@
         <v>1394</v>
       </c>
       <c r="B1395" s="2" t="s">
-        <v>6886</v>
+        <v>6884</v>
       </c>
       <c r="C1395" s="2" t="s">
         <v>523</v>
@@ -61518,7 +61524,7 @@
         <v>4</v>
       </c>
       <c r="H1395" s="2" t="s">
-        <v>6887</v>
+        <v>6885</v>
       </c>
       <c r="I1395" s="2" t="s">
         <v>845</v>
@@ -61529,10 +61535,10 @@
         <v>1395</v>
       </c>
       <c r="B1396" s="2" t="s">
-        <v>6888</v>
+        <v>6886</v>
       </c>
       <c r="C1396" s="2" t="s">
-        <v>6889</v>
+        <v>6887</v>
       </c>
       <c r="D1396" s="2" t="s">
         <v>523</v>
@@ -61541,13 +61547,13 @@
         <v>522</v>
       </c>
       <c r="F1396" s="2" t="s">
-        <v>6890</v>
+        <v>6888</v>
       </c>
       <c r="G1396" s="3">
         <v>2</v>
       </c>
       <c r="H1396" s="2" t="s">
-        <v>6891</v>
+        <v>6889</v>
       </c>
       <c r="I1396" s="2" t="s">
         <v>845</v>
@@ -61558,25 +61564,25 @@
         <v>1396</v>
       </c>
       <c r="B1397" s="2" t="s">
-        <v>6892</v>
+        <v>6890</v>
       </c>
       <c r="C1397" s="2" t="s">
+        <v>6874</v>
+      </c>
+      <c r="D1397" s="2" t="s">
+        <v>6880</v>
+      </c>
+      <c r="E1397" s="2" t="s">
         <v>6876</v>
       </c>
-      <c r="D1397" s="2" t="s">
-        <v>6882</v>
-      </c>
-      <c r="E1397" s="2" t="s">
-        <v>6878</v>
-      </c>
       <c r="F1397" s="2" t="s">
-        <v>6879</v>
+        <v>6877</v>
       </c>
       <c r="G1397" s="3">
         <v>1</v>
       </c>
       <c r="H1397" s="2" t="s">
-        <v>6893</v>
+        <v>6891</v>
       </c>
       <c r="I1397" s="2" t="s">
         <v>845</v>
@@ -61587,25 +61593,25 @@
         <v>1397</v>
       </c>
       <c r="B1398" s="2" t="s">
-        <v>6894</v>
+        <v>6892</v>
       </c>
       <c r="C1398" s="2" t="s">
+        <v>6874</v>
+      </c>
+      <c r="D1398" s="2" t="s">
+        <v>6880</v>
+      </c>
+      <c r="E1398" s="2" t="s">
         <v>6876</v>
       </c>
-      <c r="D1398" s="2" t="s">
-        <v>6882</v>
-      </c>
-      <c r="E1398" s="2" t="s">
-        <v>6878</v>
-      </c>
       <c r="F1398" s="2" t="s">
-        <v>6879</v>
+        <v>6877</v>
       </c>
       <c r="G1398" s="3">
         <v>3</v>
       </c>
       <c r="H1398" s="2" t="s">
-        <v>6895</v>
+        <v>6893</v>
       </c>
       <c r="I1398" s="2" t="s">
         <v>845</v>
@@ -61616,7 +61622,7 @@
         <v>1398</v>
       </c>
       <c r="B1399" s="2" t="s">
-        <v>6896</v>
+        <v>6894</v>
       </c>
       <c r="C1399" s="2" t="s">
         <v>524</v>
@@ -61628,13 +61634,13 @@
         <v>522</v>
       </c>
       <c r="F1399" s="2" t="s">
-        <v>6897</v>
+        <v>6895</v>
       </c>
       <c r="G1399" s="3">
         <v>4</v>
       </c>
       <c r="H1399" s="2" t="s">
-        <v>6898</v>
+        <v>6896</v>
       </c>
       <c r="I1399" s="2" t="s">
         <v>845</v>
@@ -61645,25 +61651,25 @@
         <v>1399</v>
       </c>
       <c r="B1400" s="2" t="s">
+        <v>6897</v>
+      </c>
+      <c r="C1400" s="2" t="s">
+        <v>6898</v>
+      </c>
+      <c r="D1400" s="2" t="s">
         <v>6899</v>
       </c>
-      <c r="C1400" s="2" t="s">
+      <c r="E1400" s="2" t="s">
         <v>6900</v>
       </c>
-      <c r="D1400" s="2" t="s">
+      <c r="F1400" s="2" t="s">
         <v>6901</v>
-      </c>
-      <c r="E1400" s="2" t="s">
-        <v>6902</v>
-      </c>
-      <c r="F1400" s="2" t="s">
-        <v>6903</v>
       </c>
       <c r="G1400" s="3">
         <v>2</v>
       </c>
       <c r="H1400" s="2" t="s">
-        <v>6904</v>
+        <v>6902</v>
       </c>
       <c r="I1400" s="2" t="s">
         <v>845</v>
@@ -61674,25 +61680,25 @@
         <v>1400</v>
       </c>
       <c r="B1401" s="2" t="s">
+        <v>6903</v>
+      </c>
+      <c r="C1401" s="2" t="s">
+        <v>6904</v>
+      </c>
+      <c r="D1401" s="2" t="s">
         <v>6905</v>
       </c>
-      <c r="C1401" s="2" t="s">
+      <c r="E1401" s="2" t="s">
         <v>6906</v>
       </c>
-      <c r="D1401" s="2" t="s">
+      <c r="F1401" s="2" t="s">
         <v>6907</v>
-      </c>
-      <c r="E1401" s="2" t="s">
-        <v>6908</v>
-      </c>
-      <c r="F1401" s="2" t="s">
-        <v>6909</v>
       </c>
       <c r="G1401" s="3">
         <v>2</v>
       </c>
       <c r="H1401" s="2" t="s">
-        <v>6910</v>
+        <v>6908</v>
       </c>
       <c r="I1401" s="2" t="s">
         <v>845</v>
@@ -61703,25 +61709,25 @@
         <v>1401</v>
       </c>
       <c r="B1402" s="2" t="s">
+        <v>6909</v>
+      </c>
+      <c r="C1402" s="2" t="s">
+        <v>6910</v>
+      </c>
+      <c r="D1402" s="2" t="s">
         <v>6911</v>
       </c>
-      <c r="C1402" s="2" t="s">
+      <c r="E1402" s="2" t="s">
         <v>6912</v>
       </c>
-      <c r="D1402" s="2" t="s">
+      <c r="F1402" s="2" t="s">
         <v>6913</v>
-      </c>
-      <c r="E1402" s="2" t="s">
-        <v>6914</v>
-      </c>
-      <c r="F1402" s="2" t="s">
-        <v>6915</v>
       </c>
       <c r="G1402" s="3">
         <v>2</v>
       </c>
       <c r="H1402" s="2" t="s">
-        <v>6916</v>
+        <v>6914</v>
       </c>
       <c r="I1402" s="2" t="s">
         <v>15</v>
@@ -61732,25 +61738,25 @@
         <v>1402</v>
       </c>
       <c r="B1403" s="2" t="s">
+        <v>6915</v>
+      </c>
+      <c r="C1403" s="2" t="s">
+        <v>6916</v>
+      </c>
+      <c r="D1403" s="2" t="s">
         <v>6917</v>
       </c>
-      <c r="C1403" s="2" t="s">
+      <c r="E1403" s="2" t="s">
         <v>6918</v>
       </c>
-      <c r="D1403" s="2" t="s">
+      <c r="F1403" s="2" t="s">
         <v>6919</v>
-      </c>
-      <c r="E1403" s="2" t="s">
-        <v>6920</v>
-      </c>
-      <c r="F1403" s="2" t="s">
-        <v>6921</v>
       </c>
       <c r="G1403" s="3">
         <v>3</v>
       </c>
       <c r="H1403" s="2" t="s">
-        <v>6922</v>
+        <v>6920</v>
       </c>
       <c r="I1403" s="2" t="s">
         <v>15</v>
@@ -61761,25 +61767,25 @@
         <v>1403</v>
       </c>
       <c r="B1404" s="2" t="s">
+        <v>6921</v>
+      </c>
+      <c r="C1404" s="2" t="s">
+        <v>6922</v>
+      </c>
+      <c r="D1404" s="2" t="s">
         <v>6923</v>
       </c>
-      <c r="C1404" s="2" t="s">
+      <c r="E1404" s="2" t="s">
         <v>6924</v>
       </c>
-      <c r="D1404" s="2" t="s">
+      <c r="F1404" s="2" t="s">
         <v>6925</v>
-      </c>
-      <c r="E1404" s="2" t="s">
-        <v>6926</v>
-      </c>
-      <c r="F1404" s="2" t="s">
-        <v>6927</v>
       </c>
       <c r="G1404" s="3">
         <v>2</v>
       </c>
       <c r="H1404" s="2" t="s">
-        <v>6928</v>
+        <v>6926</v>
       </c>
       <c r="I1404" s="2" t="s">
         <v>15</v>
@@ -61807,10 +61813,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>6929</v>
+        <v>6927</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>6930</v>
+        <v>6928</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.45">
@@ -61818,10 +61824,10 @@
         <v>241</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>6931</v>
+        <v>6929</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>6932</v>
+        <v>6930</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.45">
@@ -61829,10 +61835,10 @@
         <v>491</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>6931</v>
+        <v>6929</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>6932</v>
+        <v>6930</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.45">
@@ -61840,10 +61846,10 @@
         <v>567</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>6931</v>
+        <v>6929</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>6932</v>
+        <v>6930</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.45">
@@ -61851,10 +61857,10 @@
         <v>703</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>6931</v>
+        <v>6929</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>6932</v>
+        <v>6930</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.45">
@@ -61862,10 +61868,10 @@
         <v>937</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>6931</v>
+        <v>6929</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>6932</v>
+        <v>6930</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.45">
@@ -61873,10 +61879,10 @@
         <v>1134</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>6931</v>
+        <v>6929</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>6932</v>
+        <v>6930</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.45">
@@ -61884,10 +61890,10 @@
         <v>1188</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>6931</v>
+        <v>6929</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>6932</v>
+        <v>6930</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.45">
@@ -61895,10 +61901,10 @@
         <v>1189</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>6931</v>
+        <v>6929</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>6932</v>
+        <v>6930</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.45">
@@ -61906,10 +61912,10 @@
         <v>1190</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>6931</v>
+        <v>6929</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>6932</v>
+        <v>6930</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.45">
@@ -61917,10 +61923,10 @@
         <v>1192</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>6931</v>
+        <v>6929</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>6932</v>
+        <v>6930</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.45">
@@ -61928,10 +61934,10 @@
         <v>1193</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>6931</v>
+        <v>6929</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>6932</v>
+        <v>6930</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.45">
@@ -61939,10 +61945,10 @@
         <v>1194</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>6931</v>
+        <v>6929</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>6932</v>
+        <v>6930</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.45">
@@ -61950,10 +61956,10 @@
         <v>1195</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>6931</v>
+        <v>6929</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>6932</v>
+        <v>6930</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.45">
@@ -61961,10 +61967,10 @@
         <v>1250</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>6931</v>
+        <v>6929</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>6932</v>
+        <v>6930</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.45">
@@ -61972,10 +61978,10 @@
         <v>320</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>6933</v>
+        <v>6931</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>6934</v>
+        <v>6932</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.45">
@@ -61983,10 +61989,10 @@
         <v>826</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>6933</v>
+        <v>6931</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>6934</v>
+        <v>6932</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.45">
@@ -61994,10 +62000,10 @@
         <v>861</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>6933</v>
+        <v>6931</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>6934</v>
+        <v>6932</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.45">
@@ -62005,10 +62011,10 @@
         <v>876</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>6933</v>
+        <v>6931</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>6934</v>
+        <v>6932</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.45">
@@ -62016,10 +62022,10 @@
         <v>878</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>6933</v>
+        <v>6931</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>6934</v>
+        <v>6932</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.45">
@@ -62027,10 +62033,10 @@
         <v>955</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>6933</v>
+        <v>6931</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>6934</v>
+        <v>6932</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.45">
@@ -62038,10 +62044,10 @@
         <v>1064</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>6933</v>
+        <v>6931</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>6934</v>
+        <v>6932</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.45">
@@ -62049,10 +62055,10 @@
         <v>1069</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>6933</v>
+        <v>6931</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>6934</v>
+        <v>6932</v>
       </c>
     </row>
   </sheetData>
@@ -62071,22 +62077,22 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
-        <v>6935</v>
+        <v>6933</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="30.9" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
-        <v>6936</v>
+        <v>6934</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="30.9" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
-        <v>6937</v>
+        <v>6935</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
-        <v>6938</v>
+        <v>6936</v>
       </c>
     </row>
   </sheetData>

--- a/salf/丙種職業安全衛生業務主管題庫.xlsx
+++ b/salf/丙種職業安全衛生業務主管題庫.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25f5a1833553ad9e/文件/GitHub/drher.github.io/salf/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{60500821-8D89-4C6B-AF3B-12226DB870A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{04625EC0-5A00-45A8-B4C7-4529C97A95F7}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="13_ncr:1_{60500821-8D89-4C6B-AF3B-12226DB870A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC7193BA-E77D-42B8-95D0-56893380919D}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9463" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19499" uniqueCount="6973">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9779" uniqueCount="6976">
   <si>
     <t>題號</t>
   </si>
@@ -19386,24 +19386,12 @@
     <t>關節活動度與下列何種健康體能檢測項目較相關 ?</t>
   </si>
   <si>
-    <t>身體組成 3) 柔軟度</t>
-  </si>
-  <si>
-    <t>1314. 下列何者為容易接觸到虎頭蜂之戶外工作者 ?</t>
-  </si>
-  <si>
     <t>容易接觸到虎頭蜂之戶外工作者包括 : 景觀維護業、園藝業、農業、林業、土木建築與修繕業、空調裝修業業工作者、田野調查。</t>
   </si>
   <si>
-    <t>. 下列何者為容易接觸到虎頭蜂之戶外工作者 ?</t>
-  </si>
-  <si>
     <t>園藝業工作者</t>
   </si>
   <si>
-    <t>空調裝修業工作者 ss 09 * 維護業、園鞭業、農業、林業、土水建築與修位業、全 J 央 +</t>
-  </si>
-  <si>
     <t>鳥腳病是什麼中毒 ?</t>
   </si>
   <si>
@@ -19417,9 +19405,6 @@
   </si>
   <si>
     <t>正確答案為第2項：「砷」。本題重點在於理解題幹所涉及的職業安全衛生管理、危害預防或法規要求。</t>
-  </si>
-  <si>
-    <t>(站) 職業災害調查處理</t>
   </si>
   <si>
     <t>工安部門</t>
@@ -21113,15 +21098,47 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">分析潛在的風險及危害 (41) </t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>決定安全的工作方法。</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>分析潛在的風險及危害</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>下列何者為容易接觸到虎頭蜂之戶外工作者 ?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>空調裝修業工作者</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>田野調查人員</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>以上皆是</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>柔軟度</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>身體組成</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>心肺適能</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>員工發生傷害事故應由何部門負責填寫災害事故調查表</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>政風部門</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -22224,10 +22241,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>6948</v>
+        <v>6943</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>6949</v>
+        <v>6944</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>136</v>
@@ -23554,13 +23571,13 @@
         <v>70</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>6875</v>
+        <v>6870</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>385</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>6874</v>
+        <v>6869</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>386</v>
@@ -23583,7 +23600,7 @@
         <v>71</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>6964</v>
+        <v>6959</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>389</v>
@@ -23592,10 +23609,10 @@
         <v>390</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>6966</v>
+        <v>6961</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>6965</v>
+        <v>6960</v>
       </c>
       <c r="G72" s="3">
         <v>4</v>
@@ -24163,7 +24180,7 @@
         <v>91</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>6924</v>
+        <v>6919</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>493</v>
@@ -24175,7 +24192,7 @@
         <v>495</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>6925</v>
+        <v>6920</v>
       </c>
       <c r="G92" s="3">
         <v>4</v>
@@ -24449,7 +24466,7 @@
         <v>101</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>6901</v>
+        <v>6896</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>547</v>
@@ -24458,10 +24475,10 @@
         <v>548</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>6902</v>
+        <v>6897</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>6903</v>
+        <v>6898</v>
       </c>
       <c r="G102" s="3">
         <v>1</v>
@@ -25346,7 +25363,7 @@
         <v>132</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>6931</v>
+        <v>6926</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>354</v>
@@ -25355,10 +25372,10 @@
         <v>693</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>6932</v>
+        <v>6927</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>6933</v>
+        <v>6928</v>
       </c>
       <c r="G133" s="3">
         <v>3</v>
@@ -26112,7 +26129,7 @@
         <v>819</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>6942</v>
+        <v>6937</v>
       </c>
       <c r="G159" s="3">
         <v>3</v>
@@ -27492,13 +27509,13 @@
         <v>1065</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>6860</v>
+        <v>6855</v>
       </c>
       <c r="E207" s="2" t="s">
-        <v>6861</v>
+        <v>6856</v>
       </c>
       <c r="F207" s="2" t="s">
-        <v>6862</v>
+        <v>6857</v>
       </c>
       <c r="G207" s="3">
         <v>2</v>
@@ -29313,7 +29330,7 @@
         <v>269</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>6883</v>
+        <v>6878</v>
       </c>
       <c r="C270" s="2" t="s">
         <v>1401</v>
@@ -30618,7 +30635,7 @@
         <v>314</v>
       </c>
       <c r="B315" s="2" t="s">
-        <v>6934</v>
+        <v>6929</v>
       </c>
       <c r="C315" s="2" t="s">
         <v>1646</v>
@@ -31256,19 +31273,19 @@
         <v>336</v>
       </c>
       <c r="B337" s="2" t="s">
-        <v>6921</v>
+        <v>6916</v>
       </c>
       <c r="C337" s="2" t="s">
         <v>1769</v>
       </c>
       <c r="D337" s="2" t="s">
-        <v>6922</v>
+        <v>6917</v>
       </c>
       <c r="E337" s="2" t="s">
         <v>733</v>
       </c>
       <c r="F337" s="2" t="s">
-        <v>6923</v>
+        <v>6918</v>
       </c>
       <c r="G337" s="3">
         <v>4</v>
@@ -31460,7 +31477,7 @@
         <v>1804</v>
       </c>
       <c r="C344" s="2" t="s">
-        <v>6929</v>
+        <v>6924</v>
       </c>
       <c r="D344" s="2" t="s">
         <v>1799</v>
@@ -31469,7 +31486,7 @@
         <v>1800</v>
       </c>
       <c r="F344" s="2" t="s">
-        <v>6930</v>
+        <v>6925</v>
       </c>
       <c r="G344" s="3">
         <v>1</v>
@@ -33284,16 +33301,16 @@
         <v>406</v>
       </c>
       <c r="B407" s="2" t="s">
-        <v>6945</v>
+        <v>6940</v>
       </c>
       <c r="C407" s="2" t="s">
-        <v>6947</v>
+        <v>6942</v>
       </c>
       <c r="D407" s="2" t="s">
         <v>2159</v>
       </c>
       <c r="E407" s="2" t="s">
-        <v>6946</v>
+        <v>6941</v>
       </c>
       <c r="F407" s="2" t="s">
         <v>2160</v>
@@ -34092,7 +34109,7 @@
         <v>434</v>
       </c>
       <c r="B435" s="2" t="s">
-        <v>6956</v>
+        <v>6951</v>
       </c>
       <c r="C435" s="2" t="s">
         <v>2298</v>
@@ -34104,7 +34121,7 @@
         <v>2300</v>
       </c>
       <c r="F435" s="2" t="s">
-        <v>6957</v>
+        <v>6952</v>
       </c>
       <c r="G435" s="3">
         <v>1</v>
@@ -34621,10 +34638,10 @@
         <v>2379</v>
       </c>
       <c r="E453" s="2" t="s">
-        <v>6972</v>
+        <v>6966</v>
       </c>
       <c r="F453" s="2" t="s">
-        <v>6971</v>
+        <v>6965</v>
       </c>
       <c r="G453" s="3">
         <v>1</v>
@@ -34641,7 +34658,7 @@
         <v>453</v>
       </c>
       <c r="B454" s="2" t="s">
-        <v>6967</v>
+        <v>6962</v>
       </c>
       <c r="C454" s="2" t="s">
         <v>1443</v>
@@ -34650,10 +34667,10 @@
         <v>1425</v>
       </c>
       <c r="E454" s="2" t="s">
-        <v>6969</v>
+        <v>6964</v>
       </c>
       <c r="F454" s="2" t="s">
-        <v>6968</v>
+        <v>6963</v>
       </c>
       <c r="G454" s="3">
         <v>4</v>
@@ -37606,13 +37623,13 @@
         <v>556</v>
       </c>
       <c r="B557" s="2" t="s">
-        <v>6866</v>
+        <v>6861</v>
       </c>
       <c r="C557" s="2" t="s">
-        <v>6867</v>
+        <v>6862</v>
       </c>
       <c r="D557" s="2" t="s">
-        <v>6868</v>
+        <v>6863</v>
       </c>
       <c r="E557" s="2" t="s">
         <v>2888</v>
@@ -39281,7 +39298,7 @@
         <v>615</v>
       </c>
       <c r="B616" s="2" t="s">
-        <v>6895</v>
+        <v>6890</v>
       </c>
       <c r="C616" s="2" t="s">
         <v>3174</v>
@@ -39397,7 +39414,7 @@
         <v>619</v>
       </c>
       <c r="B620" s="2" t="s">
-        <v>6958</v>
+        <v>6953</v>
       </c>
       <c r="C620" s="2" t="s">
         <v>3195</v>
@@ -39409,7 +39426,7 @@
         <v>3197</v>
       </c>
       <c r="F620" s="2" t="s">
-        <v>6959</v>
+        <v>6954</v>
       </c>
       <c r="G620" s="3">
         <v>4</v>
@@ -39981,7 +39998,7 @@
         <v>3302</v>
       </c>
       <c r="F640" s="2" t="s">
-        <v>6873</v>
+        <v>6868</v>
       </c>
       <c r="G640" s="3">
         <v>2</v>
@@ -40288,7 +40305,7 @@
         <v>650</v>
       </c>
       <c r="B651" s="2" t="s">
-        <v>6906</v>
+        <v>6901</v>
       </c>
       <c r="C651" s="2" t="s">
         <v>3355</v>
@@ -40297,10 +40314,10 @@
         <v>3356</v>
       </c>
       <c r="E651" s="2" t="s">
-        <v>6907</v>
+        <v>6902</v>
       </c>
       <c r="F651" s="2" t="s">
-        <v>6908</v>
+        <v>6903</v>
       </c>
       <c r="G651" s="3">
         <v>2</v>
@@ -40346,7 +40363,7 @@
         <v>652</v>
       </c>
       <c r="B653" s="2" t="s">
-        <v>6954</v>
+        <v>6949</v>
       </c>
       <c r="C653" s="2" t="s">
         <v>1545</v>
@@ -40358,7 +40375,7 @@
         <v>3365</v>
       </c>
       <c r="F653" s="2" t="s">
-        <v>6955</v>
+        <v>6950</v>
       </c>
       <c r="G653" s="3">
         <v>1</v>
@@ -42918,13 +42935,13 @@
         <v>3777</v>
       </c>
       <c r="C742" s="2" t="s">
-        <v>6863</v>
+        <v>6858</v>
       </c>
       <c r="D742" s="2" t="s">
         <v>3778</v>
       </c>
       <c r="E742" s="2" t="s">
-        <v>6864</v>
+        <v>6859</v>
       </c>
       <c r="F742" s="2" t="s">
         <v>51</v>
@@ -43319,25 +43336,25 @@
         <v>755</v>
       </c>
       <c r="B756" s="2" t="s">
-        <v>6884</v>
+        <v>6879</v>
       </c>
       <c r="C756" s="2" t="s">
-        <v>6885</v>
+        <v>6880</v>
       </c>
       <c r="D756" s="2" t="s">
-        <v>6886</v>
+        <v>6881</v>
       </c>
       <c r="E756" s="2" t="s">
-        <v>6887</v>
+        <v>6882</v>
       </c>
       <c r="F756" s="2" t="s">
-        <v>6888</v>
+        <v>6883</v>
       </c>
       <c r="G756" s="3">
         <v>2</v>
       </c>
       <c r="H756" s="2" t="s">
-        <v>6889</v>
+        <v>6884</v>
       </c>
       <c r="I756" s="2" t="s">
         <v>803</v>
@@ -44970,13 +44987,13 @@
         <v>812</v>
       </c>
       <c r="B813" s="2" t="s">
-        <v>6952</v>
+        <v>6947</v>
       </c>
       <c r="C813" s="2" t="s">
         <v>4099</v>
       </c>
       <c r="D813" s="2" t="s">
-        <v>6953</v>
+        <v>6948</v>
       </c>
       <c r="E813" s="2" t="s">
         <v>4100</v>
@@ -45028,7 +45045,7 @@
         <v>814</v>
       </c>
       <c r="B815" s="2" t="s">
-        <v>6950</v>
+        <v>6945</v>
       </c>
       <c r="C815" s="2" t="s">
         <v>4109</v>
@@ -45040,7 +45057,7 @@
         <v>4111</v>
       </c>
       <c r="F815" s="2" t="s">
-        <v>6951</v>
+        <v>6946</v>
       </c>
       <c r="G815" s="3">
         <v>1</v>
@@ -46474,7 +46491,7 @@
         <v>864</v>
       </c>
       <c r="B865" s="2" t="s">
-        <v>6911</v>
+        <v>6906</v>
       </c>
       <c r="C865" s="2" t="s">
         <v>4363</v>
@@ -46483,10 +46500,10 @@
         <v>3096</v>
       </c>
       <c r="E865" s="2" t="s">
-        <v>6909</v>
+        <v>6904</v>
       </c>
       <c r="F865" s="2" t="s">
-        <v>6910</v>
+        <v>6905</v>
       </c>
       <c r="G865" s="3">
         <v>4</v>
@@ -46503,19 +46520,19 @@
         <v>865</v>
       </c>
       <c r="B866" s="2" t="s">
-        <v>6916</v>
+        <v>6911</v>
       </c>
       <c r="C866" s="2" t="s">
-        <v>6917</v>
+        <v>6912</v>
       </c>
       <c r="D866" s="5" t="s">
-        <v>6918</v>
+        <v>6913</v>
       </c>
       <c r="E866" s="2" t="s">
-        <v>6919</v>
+        <v>6914</v>
       </c>
       <c r="F866" s="2" t="s">
-        <v>6920</v>
+        <v>6915</v>
       </c>
       <c r="G866" s="3">
         <v>3</v>
@@ -46939,7 +46956,7 @@
         <v>4442</v>
       </c>
       <c r="C881" s="2" t="s">
-        <v>6871</v>
+        <v>6866</v>
       </c>
       <c r="D881" s="2" t="s">
         <v>3096</v>
@@ -46948,7 +46965,7 @@
         <v>4443</v>
       </c>
       <c r="F881" s="2" t="s">
-        <v>6872</v>
+        <v>6867</v>
       </c>
       <c r="G881" s="3">
         <v>1</v>
@@ -47400,16 +47417,16 @@
         <v>896</v>
       </c>
       <c r="B897" s="2" t="s">
-        <v>6877</v>
+        <v>6872</v>
       </c>
       <c r="C897" s="2" t="s">
         <v>4227</v>
       </c>
       <c r="D897" s="2" t="s">
-        <v>6878</v>
+        <v>6873</v>
       </c>
       <c r="E897" s="2" t="s">
-        <v>6879</v>
+        <v>6874</v>
       </c>
       <c r="F897" s="2" t="s">
         <v>4316</v>
@@ -48173,7 +48190,7 @@
         <v>923</v>
       </c>
       <c r="B924" s="2" t="s">
-        <v>6876</v>
+        <v>6871</v>
       </c>
       <c r="C924" s="2" t="s">
         <v>3140</v>
@@ -49020,7 +49037,7 @@
         <v>4810</v>
       </c>
       <c r="F953" s="2" t="s">
-        <v>6865</v>
+        <v>6860</v>
       </c>
       <c r="G953" s="3">
         <v>3</v>
@@ -49812,19 +49829,19 @@
         <v>980</v>
       </c>
       <c r="B981" s="2" t="s">
-        <v>6935</v>
+        <v>6930</v>
       </c>
       <c r="C981" s="2" t="s">
-        <v>6937</v>
+        <v>6932</v>
       </c>
       <c r="D981" s="2" t="s">
-        <v>6938</v>
+        <v>6933</v>
       </c>
       <c r="E981" s="2" t="s">
         <v>4954</v>
       </c>
       <c r="F981" s="2" t="s">
-        <v>6936</v>
+        <v>6931</v>
       </c>
       <c r="G981" s="3">
         <v>2</v>
@@ -50044,19 +50061,19 @@
         <v>988</v>
       </c>
       <c r="B989" s="2" t="s">
-        <v>6896</v>
+        <v>6891</v>
       </c>
       <c r="C989" s="2" t="s">
-        <v>6897</v>
+        <v>6892</v>
       </c>
       <c r="D989" s="2" t="s">
-        <v>6898</v>
+        <v>6893</v>
       </c>
       <c r="E989" s="2" t="s">
-        <v>6899</v>
+        <v>6894</v>
       </c>
       <c r="F989" s="2" t="s">
-        <v>6900</v>
+        <v>6895</v>
       </c>
       <c r="G989" s="3">
         <v>3</v>
@@ -51113,7 +51130,7 @@
         <v>1025</v>
       </c>
       <c r="B1026" s="2" t="s">
-        <v>6939</v>
+        <v>6934</v>
       </c>
       <c r="C1026" s="2" t="s">
         <v>5146</v>
@@ -51122,10 +51139,10 @@
         <v>1001</v>
       </c>
       <c r="E1026" s="2" t="s">
-        <v>6940</v>
+        <v>6935</v>
       </c>
       <c r="F1026" s="2" t="s">
-        <v>6941</v>
+        <v>6936</v>
       </c>
       <c r="G1026" s="3">
         <v>1</v>
@@ -51519,19 +51536,19 @@
         <v>1039</v>
       </c>
       <c r="B1040" s="2" t="s">
-        <v>6890</v>
+        <v>6885</v>
       </c>
       <c r="C1040" s="2" t="s">
-        <v>6891</v>
+        <v>6886</v>
       </c>
       <c r="D1040" s="2" t="s">
-        <v>6892</v>
+        <v>6887</v>
       </c>
       <c r="E1040" s="2" t="s">
-        <v>6893</v>
+        <v>6888</v>
       </c>
       <c r="F1040" s="2" t="s">
-        <v>6894</v>
+        <v>6889</v>
       </c>
       <c r="G1040" s="3">
         <v>4</v>
@@ -53782,10 +53799,10 @@
         <v>5598</v>
       </c>
       <c r="E1118" s="2" t="s">
-        <v>6870</v>
+        <v>6865</v>
       </c>
       <c r="F1118" s="2" t="s">
-        <v>6869</v>
+        <v>6864</v>
       </c>
       <c r="G1118" s="3">
         <v>4</v>
@@ -56925,7 +56942,7 @@
         <v>1227</v>
       </c>
       <c r="B1228" s="2" t="s">
-        <v>6880</v>
+        <v>6875</v>
       </c>
       <c r="C1228" s="2" t="s">
         <v>6060</v>
@@ -56934,10 +56951,10 @@
         <v>6061</v>
       </c>
       <c r="E1228" s="2" t="s">
-        <v>6881</v>
+        <v>6876</v>
       </c>
       <c r="F1228" s="2" t="s">
-        <v>6882</v>
+        <v>6877</v>
       </c>
       <c r="G1228" s="3">
         <v>4</v>
@@ -57301,10 +57318,10 @@
         <v>6114</v>
       </c>
       <c r="C1241" s="2" t="s">
-        <v>6943</v>
+        <v>6938</v>
       </c>
       <c r="D1241" s="2" t="s">
-        <v>6944</v>
+        <v>6939</v>
       </c>
       <c r="E1241" s="2" t="s">
         <v>6040</v>
@@ -58572,10 +58589,10 @@
         <v>1284</v>
       </c>
       <c r="B1285" s="2" t="s">
-        <v>6926</v>
+        <v>6921</v>
       </c>
       <c r="C1285" s="2" t="s">
-        <v>6927</v>
+        <v>6922</v>
       </c>
       <c r="D1285" s="2" t="s">
         <v>3337</v>
@@ -58584,7 +58601,7 @@
         <v>6331</v>
       </c>
       <c r="F1285" s="2" t="s">
-        <v>6928</v>
+        <v>6923</v>
       </c>
       <c r="G1285" s="3">
         <v>2</v>
@@ -58717,19 +58734,19 @@
         <v>1289</v>
       </c>
       <c r="B1290" s="2" t="s">
-        <v>6912</v>
+        <v>6907</v>
       </c>
       <c r="C1290" s="2" t="s">
-        <v>6913</v>
+        <v>6908</v>
       </c>
       <c r="D1290" s="2" t="s">
-        <v>6914</v>
+        <v>6909</v>
       </c>
       <c r="E1290" s="2" t="s">
         <v>6353</v>
       </c>
       <c r="F1290" s="2" t="s">
-        <v>6915</v>
+        <v>6910</v>
       </c>
       <c r="G1290" s="3">
         <v>3</v>
@@ -59419,37 +59436,43 @@
         <v>6252</v>
       </c>
       <c r="D1314" s="2" t="s">
-        <v>6453</v>
-      </c>
-      <c r="E1314" s="2"/>
+        <v>6972</v>
+      </c>
+      <c r="E1314" s="2" t="s">
+        <v>6971</v>
+      </c>
       <c r="F1314" s="2" t="s">
-        <v>6454</v>
+        <v>6973</v>
       </c>
       <c r="G1314" s="3">
         <v>3</v>
       </c>
       <c r="H1314" s="2" t="s">
-        <v>6455</v>
+        <v>6453</v>
       </c>
       <c r="I1314" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="1315" spans="1:9" ht="46.3">
+    <row r="1315" spans="1:9">
       <c r="A1315" s="2">
         <v>1314</v>
       </c>
       <c r="B1315" s="2" t="s">
-        <v>6456</v>
+        <v>6967</v>
       </c>
       <c r="C1315" s="2" t="s">
-        <v>6457</v>
+        <v>6454</v>
       </c>
       <c r="D1315" s="2" t="s">
-        <v>6458</v>
-      </c>
-      <c r="E1315" s="2"/>
-      <c r="F1315" s="2"/>
+        <v>6968</v>
+      </c>
+      <c r="E1315" s="2" t="s">
+        <v>6969</v>
+      </c>
+      <c r="F1315" s="2" t="s">
+        <v>6970</v>
+      </c>
       <c r="G1315" s="3">
         <v>4</v>
       </c>
@@ -59465,25 +59488,25 @@
         <v>1315</v>
       </c>
       <c r="B1316" s="2" t="s">
-        <v>6459</v>
+        <v>6455</v>
       </c>
       <c r="C1316" s="2" t="s">
-        <v>6460</v>
+        <v>6456</v>
       </c>
       <c r="D1316" s="2" t="s">
-        <v>6461</v>
+        <v>6457</v>
       </c>
       <c r="E1316" s="2" t="s">
         <v>5298</v>
       </c>
       <c r="F1316" s="2" t="s">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="G1316" s="3">
         <v>2</v>
       </c>
       <c r="H1316" s="2" t="s">
-        <v>6463</v>
+        <v>6459</v>
       </c>
       <c r="I1316" s="2" t="s">
         <v>15</v>
@@ -59494,23 +59517,25 @@
         <v>1316</v>
       </c>
       <c r="B1317" s="2" t="s">
-        <v>6464</v>
+        <v>6974</v>
       </c>
       <c r="C1317" s="2" t="s">
-        <v>6465</v>
+        <v>6460</v>
       </c>
       <c r="D1317" s="2" t="s">
-        <v>6466</v>
+        <v>6461</v>
       </c>
       <c r="E1317" s="2" t="s">
-        <v>6467</v>
-      </c>
-      <c r="F1317" s="2"/>
+        <v>6462</v>
+      </c>
+      <c r="F1317" s="2" t="s">
+        <v>6975</v>
+      </c>
       <c r="G1317" s="3">
         <v>2</v>
       </c>
       <c r="H1317" s="2" t="s">
-        <v>6468</v>
+        <v>6463</v>
       </c>
       <c r="I1317" s="2" t="s">
         <v>831</v>
@@ -59521,25 +59546,25 @@
         <v>1317</v>
       </c>
       <c r="B1318" s="2" t="s">
-        <v>6469</v>
+        <v>6464</v>
       </c>
       <c r="C1318" s="2" t="s">
-        <v>6470</v>
+        <v>6465</v>
       </c>
       <c r="D1318" s="2" t="s">
-        <v>6471</v>
+        <v>6466</v>
       </c>
       <c r="E1318" s="2" t="s">
-        <v>6472</v>
+        <v>6467</v>
       </c>
       <c r="F1318" s="2" t="s">
-        <v>6473</v>
+        <v>6468</v>
       </c>
       <c r="G1318" s="3">
         <v>1</v>
       </c>
       <c r="H1318" s="2" t="s">
-        <v>6474</v>
+        <v>6469</v>
       </c>
       <c r="I1318" s="2" t="s">
         <v>15</v>
@@ -59550,10 +59575,10 @@
         <v>1318</v>
       </c>
       <c r="B1319" s="2" t="s">
-        <v>6475</v>
+        <v>6470</v>
       </c>
       <c r="C1319" s="2" t="s">
-        <v>6476</v>
+        <v>6471</v>
       </c>
       <c r="D1319" s="2" t="s">
         <v>335</v>
@@ -59562,13 +59587,13 @@
         <v>336</v>
       </c>
       <c r="F1319" s="2" t="s">
-        <v>6477</v>
+        <v>6472</v>
       </c>
       <c r="G1319" s="3">
         <v>1</v>
       </c>
       <c r="H1319" s="2" t="s">
-        <v>6478</v>
+        <v>6473</v>
       </c>
       <c r="I1319" s="2" t="s">
         <v>158</v>
@@ -59579,7 +59604,7 @@
         <v>1319</v>
       </c>
       <c r="B1320" s="2" t="s">
-        <v>6479</v>
+        <v>6474</v>
       </c>
       <c r="C1320" s="2" t="s">
         <v>242</v>
@@ -59588,16 +59613,16 @@
         <v>737</v>
       </c>
       <c r="E1320" s="2" t="s">
-        <v>6480</v>
+        <v>6475</v>
       </c>
       <c r="F1320" s="2" t="s">
-        <v>6481</v>
+        <v>6476</v>
       </c>
       <c r="G1320" s="3">
         <v>2</v>
       </c>
       <c r="H1320" s="2" t="s">
-        <v>6482</v>
+        <v>6477</v>
       </c>
       <c r="I1320" s="2" t="s">
         <v>15</v>
@@ -59608,7 +59633,7 @@
         <v>1320</v>
       </c>
       <c r="B1321" s="2" t="s">
-        <v>6483</v>
+        <v>6478</v>
       </c>
       <c r="C1321" s="2" t="s">
         <v>1407</v>
@@ -59637,25 +59662,25 @@
         <v>1321</v>
       </c>
       <c r="B1322" s="2" t="s">
-        <v>6484</v>
+        <v>6479</v>
       </c>
       <c r="C1322" s="2" t="s">
-        <v>6904</v>
+        <v>6899</v>
       </c>
       <c r="D1322" s="2" t="s">
-        <v>6485</v>
+        <v>6480</v>
       </c>
       <c r="E1322" s="2" t="s">
-        <v>6486</v>
+        <v>6481</v>
       </c>
       <c r="F1322" s="2" t="s">
-        <v>6905</v>
+        <v>6900</v>
       </c>
       <c r="G1322" s="3">
         <v>4</v>
       </c>
       <c r="H1322" s="2" t="s">
-        <v>6487</v>
+        <v>6482</v>
       </c>
       <c r="I1322" s="2" t="s">
         <v>831</v>
@@ -59666,7 +59691,7 @@
         <v>1322</v>
       </c>
       <c r="B1323" s="2" t="s">
-        <v>6488</v>
+        <v>6483</v>
       </c>
       <c r="C1323" s="2" t="s">
         <v>1409</v>
@@ -59675,16 +59700,16 @@
         <v>1407</v>
       </c>
       <c r="E1323" s="2" t="s">
-        <v>6489</v>
+        <v>6484</v>
       </c>
       <c r="F1323" s="2" t="s">
-        <v>6490</v>
+        <v>6485</v>
       </c>
       <c r="G1323" s="3">
         <v>3</v>
       </c>
       <c r="H1323" s="2" t="s">
-        <v>6491</v>
+        <v>6486</v>
       </c>
       <c r="I1323" s="2" t="s">
         <v>831</v>
@@ -59695,16 +59720,16 @@
         <v>1323</v>
       </c>
       <c r="B1324" s="2" t="s">
-        <v>6492</v>
+        <v>6487</v>
       </c>
       <c r="C1324" s="2" t="s">
-        <v>6493</v>
+        <v>6488</v>
       </c>
       <c r="D1324" s="2" t="s">
-        <v>6494</v>
+        <v>6489</v>
       </c>
       <c r="E1324" s="2" t="s">
-        <v>6495</v>
+        <v>6490</v>
       </c>
       <c r="F1324" s="2" t="s">
         <v>51</v>
@@ -59724,7 +59749,7 @@
         <v>1324</v>
       </c>
       <c r="B1325" s="2" t="s">
-        <v>6496</v>
+        <v>6491</v>
       </c>
       <c r="C1325" s="2" t="s">
         <v>1407</v>
@@ -59753,7 +59778,7 @@
         <v>1325</v>
       </c>
       <c r="B1326" s="2" t="s">
-        <v>6497</v>
+        <v>6492</v>
       </c>
       <c r="C1326" s="2" t="s">
         <v>1407</v>
@@ -59762,14 +59787,14 @@
         <v>1408</v>
       </c>
       <c r="E1326" s="2" t="s">
-        <v>6498</v>
+        <v>6493</v>
       </c>
       <c r="F1326" s="2"/>
       <c r="G1326" s="3">
         <v>1</v>
       </c>
       <c r="H1326" s="2" t="s">
-        <v>6499</v>
+        <v>6494</v>
       </c>
       <c r="I1326" s="2" t="s">
         <v>831</v>
@@ -59780,25 +59805,25 @@
         <v>1326</v>
       </c>
       <c r="B1327" s="2" t="s">
-        <v>6500</v>
+        <v>6495</v>
       </c>
       <c r="C1327" s="2" t="s">
-        <v>6501</v>
+        <v>6496</v>
       </c>
       <c r="D1327" s="2" t="s">
-        <v>6489</v>
+        <v>6484</v>
       </c>
       <c r="E1327" s="2" t="s">
         <v>1407</v>
       </c>
       <c r="F1327" s="2" t="s">
-        <v>6502</v>
+        <v>6497</v>
       </c>
       <c r="G1327" s="3">
         <v>3</v>
       </c>
       <c r="H1327" s="2" t="s">
-        <v>6503</v>
+        <v>6498</v>
       </c>
       <c r="I1327" s="2" t="s">
         <v>15</v>
@@ -59809,13 +59834,13 @@
         <v>1327</v>
       </c>
       <c r="B1328" s="2" t="s">
-        <v>6504</v>
+        <v>6499</v>
       </c>
       <c r="C1328" s="2" t="s">
         <v>1407</v>
       </c>
       <c r="D1328" s="2" t="s">
-        <v>6505</v>
+        <v>6500</v>
       </c>
       <c r="E1328" s="2" t="s">
         <v>1409</v>
@@ -59827,7 +59852,7 @@
         <v>2</v>
       </c>
       <c r="H1328" s="2" t="s">
-        <v>6506</v>
+        <v>6501</v>
       </c>
       <c r="I1328" s="2" t="s">
         <v>803</v>
@@ -59838,13 +59863,13 @@
         <v>1328</v>
       </c>
       <c r="B1329" s="2" t="s">
-        <v>6507</v>
+        <v>6502</v>
       </c>
       <c r="C1329" s="2" t="s">
         <v>1407</v>
       </c>
       <c r="D1329" s="2" t="s">
-        <v>6489</v>
+        <v>6484</v>
       </c>
       <c r="E1329" s="2" t="s">
         <v>1409</v>
@@ -59867,13 +59892,13 @@
         <v>1329</v>
       </c>
       <c r="B1330" s="2" t="s">
-        <v>6508</v>
+        <v>6503</v>
       </c>
       <c r="C1330" s="2" t="s">
         <v>1407</v>
       </c>
       <c r="D1330" s="2" t="s">
-        <v>6489</v>
+        <v>6484</v>
       </c>
       <c r="E1330" s="2" t="s">
         <v>1409</v>
@@ -59896,13 +59921,13 @@
         <v>1330</v>
       </c>
       <c r="B1331" s="2" t="s">
-        <v>6509</v>
+        <v>6504</v>
       </c>
       <c r="C1331" s="2" t="s">
         <v>1407</v>
       </c>
       <c r="D1331" s="2" t="s">
-        <v>6489</v>
+        <v>6484</v>
       </c>
       <c r="E1331" s="2" t="s">
         <v>1409</v>
@@ -59914,7 +59939,7 @@
         <v>2</v>
       </c>
       <c r="H1331" s="2" t="s">
-        <v>6510</v>
+        <v>6505</v>
       </c>
       <c r="I1331" s="2" t="s">
         <v>15</v>
@@ -59925,25 +59950,25 @@
         <v>1331</v>
       </c>
       <c r="B1332" s="2" t="s">
-        <v>6511</v>
+        <v>6506</v>
       </c>
       <c r="C1332" s="2" t="s">
-        <v>6512</v>
+        <v>6507</v>
       </c>
       <c r="D1332" s="2" t="s">
-        <v>6513</v>
+        <v>6508</v>
       </c>
       <c r="E1332" s="2" t="s">
-        <v>6514</v>
+        <v>6509</v>
       </c>
       <c r="F1332" s="2" t="s">
-        <v>6515</v>
+        <v>6510</v>
       </c>
       <c r="G1332" s="3">
         <v>4</v>
       </c>
       <c r="H1332" s="2" t="s">
-        <v>6516</v>
+        <v>6511</v>
       </c>
       <c r="I1332" s="2" t="s">
         <v>22</v>
@@ -59954,16 +59979,16 @@
         <v>1332</v>
       </c>
       <c r="B1333" s="2" t="s">
-        <v>6517</v>
+        <v>6512</v>
       </c>
       <c r="C1333" s="2" t="s">
         <v>77</v>
       </c>
       <c r="D1333" s="2" t="s">
-        <v>6518</v>
+        <v>6513</v>
       </c>
       <c r="E1333" s="2" t="s">
-        <v>6519</v>
+        <v>6514</v>
       </c>
       <c r="F1333" s="2" t="s">
         <v>2333</v>
@@ -59983,7 +60008,7 @@
         <v>1333</v>
       </c>
       <c r="B1334" s="2" t="s">
-        <v>6520</v>
+        <v>6515</v>
       </c>
       <c r="C1334" s="2" t="s">
         <v>12</v>
@@ -59995,13 +60020,13 @@
         <v>453</v>
       </c>
       <c r="F1334" s="2" t="s">
-        <v>6521</v>
+        <v>6516</v>
       </c>
       <c r="G1334" s="3">
         <v>1</v>
       </c>
       <c r="H1334" s="2" t="s">
-        <v>6522</v>
+        <v>6517</v>
       </c>
       <c r="I1334" s="2" t="s">
         <v>831</v>
@@ -60012,16 +60037,16 @@
         <v>1334</v>
       </c>
       <c r="B1335" s="2" t="s">
-        <v>6523</v>
+        <v>6518</v>
       </c>
       <c r="C1335" s="2" t="s">
-        <v>6524</v>
+        <v>6519</v>
       </c>
       <c r="D1335" s="2" t="s">
-        <v>6525</v>
+        <v>6520</v>
       </c>
       <c r="E1335" s="2" t="s">
-        <v>6526</v>
+        <v>6521</v>
       </c>
       <c r="F1335" s="2" t="s">
         <v>197</v>
@@ -60041,7 +60066,7 @@
         <v>1335</v>
       </c>
       <c r="B1336" s="2" t="s">
-        <v>6527</v>
+        <v>6522</v>
       </c>
       <c r="C1336" s="2" t="s">
         <v>5125</v>
@@ -60050,16 +60075,16 @@
         <v>5030</v>
       </c>
       <c r="E1336" s="2" t="s">
-        <v>6528</v>
+        <v>6523</v>
       </c>
       <c r="F1336" s="2" t="s">
-        <v>6529</v>
+        <v>6524</v>
       </c>
       <c r="G1336" s="3">
         <v>3</v>
       </c>
       <c r="H1336" s="2" t="s">
-        <v>6530</v>
+        <v>6525</v>
       </c>
       <c r="I1336" s="2" t="s">
         <v>15</v>
@@ -60070,25 +60095,25 @@
         <v>1336</v>
       </c>
       <c r="B1337" s="2" t="s">
-        <v>6531</v>
+        <v>6526</v>
       </c>
       <c r="C1337" s="2" t="s">
-        <v>6532</v>
+        <v>6527</v>
       </c>
       <c r="D1337" s="2" t="s">
-        <v>6533</v>
+        <v>6528</v>
       </c>
       <c r="E1337" s="2" t="s">
-        <v>6534</v>
+        <v>6529</v>
       </c>
       <c r="F1337" s="2" t="s">
-        <v>6535</v>
+        <v>6530</v>
       </c>
       <c r="G1337" s="3">
         <v>3</v>
       </c>
       <c r="H1337" s="2" t="s">
-        <v>6536</v>
+        <v>6531</v>
       </c>
       <c r="I1337" s="2" t="s">
         <v>831</v>
@@ -60099,7 +60124,7 @@
         <v>1337</v>
       </c>
       <c r="B1338" s="2" t="s">
-        <v>6537</v>
+        <v>6532</v>
       </c>
       <c r="C1338" s="2" t="s">
         <v>518</v>
@@ -60111,13 +60136,13 @@
         <v>5030</v>
       </c>
       <c r="F1338" s="2" t="s">
-        <v>6538</v>
+        <v>6533</v>
       </c>
       <c r="G1338" s="3">
         <v>4</v>
       </c>
       <c r="H1338" s="2" t="s">
-        <v>6539</v>
+        <v>6534</v>
       </c>
       <c r="I1338" s="2" t="s">
         <v>22</v>
@@ -60128,7 +60153,7 @@
         <v>1338</v>
       </c>
       <c r="B1339" s="2" t="s">
-        <v>6540</v>
+        <v>6535</v>
       </c>
       <c r="C1339" s="2" t="s">
         <v>77</v>
@@ -60137,16 +60162,16 @@
         <v>573</v>
       </c>
       <c r="E1339" s="2" t="s">
-        <v>6541</v>
+        <v>6536</v>
       </c>
       <c r="F1339" s="2" t="s">
-        <v>6542</v>
+        <v>6537</v>
       </c>
       <c r="G1339" s="3">
         <v>2</v>
       </c>
       <c r="H1339" s="2" t="s">
-        <v>6543</v>
+        <v>6538</v>
       </c>
       <c r="I1339" s="2" t="s">
         <v>831</v>
@@ -60157,7 +60182,7 @@
         <v>1339</v>
       </c>
       <c r="B1340" s="2" t="s">
-        <v>6544</v>
+        <v>6539</v>
       </c>
       <c r="C1340" s="2" t="s">
         <v>324</v>
@@ -60169,13 +60194,13 @@
         <v>330</v>
       </c>
       <c r="F1340" s="2" t="s">
-        <v>6545</v>
+        <v>6540</v>
       </c>
       <c r="G1340" s="3">
         <v>2</v>
       </c>
       <c r="H1340" s="2" t="s">
-        <v>6546</v>
+        <v>6541</v>
       </c>
       <c r="I1340" s="2" t="s">
         <v>831</v>
@@ -60186,25 +60211,25 @@
         <v>1340</v>
       </c>
       <c r="B1341" s="2" t="s">
-        <v>6547</v>
+        <v>6542</v>
       </c>
       <c r="C1341" s="2" t="s">
-        <v>6548</v>
+        <v>6543</v>
       </c>
       <c r="D1341" s="2" t="s">
-        <v>6549</v>
+        <v>6544</v>
       </c>
       <c r="E1341" s="2" t="s">
-        <v>6532</v>
+        <v>6527</v>
       </c>
       <c r="F1341" s="2" t="s">
-        <v>6550</v>
+        <v>6545</v>
       </c>
       <c r="G1341" s="3">
         <v>4</v>
       </c>
       <c r="H1341" s="2" t="s">
-        <v>6551</v>
+        <v>6546</v>
       </c>
       <c r="I1341" s="2" t="s">
         <v>831</v>
@@ -60215,16 +60240,16 @@
         <v>1341</v>
       </c>
       <c r="B1342" s="2" t="s">
-        <v>6552</v>
+        <v>6547</v>
       </c>
       <c r="C1342" s="2" t="s">
-        <v>6553</v>
+        <v>6548</v>
       </c>
       <c r="D1342" s="2" t="s">
-        <v>6554</v>
+        <v>6549</v>
       </c>
       <c r="E1342" s="2" t="s">
-        <v>6555</v>
+        <v>6550</v>
       </c>
       <c r="F1342" s="2" t="s">
         <v>197</v>
@@ -60244,25 +60269,25 @@
         <v>1342</v>
       </c>
       <c r="B1343" s="2" t="s">
-        <v>6556</v>
+        <v>6551</v>
       </c>
       <c r="C1343" s="2" t="s">
-        <v>6557</v>
+        <v>6552</v>
       </c>
       <c r="D1343" s="2" t="s">
-        <v>6558</v>
+        <v>6553</v>
       </c>
       <c r="E1343" s="2" t="s">
-        <v>6559</v>
+        <v>6554</v>
       </c>
       <c r="F1343" s="2" t="s">
-        <v>6560</v>
+        <v>6555</v>
       </c>
       <c r="G1343" s="3">
         <v>3</v>
       </c>
       <c r="H1343" s="2" t="s">
-        <v>6561</v>
+        <v>6556</v>
       </c>
       <c r="I1343" s="2" t="s">
         <v>831</v>
@@ -60273,25 +60298,25 @@
         <v>1343</v>
       </c>
       <c r="B1344" s="2" t="s">
-        <v>6562</v>
+        <v>6557</v>
       </c>
       <c r="C1344" s="2" t="s">
-        <v>6563</v>
+        <v>6558</v>
       </c>
       <c r="D1344" s="2" t="s">
-        <v>6564</v>
+        <v>6559</v>
       </c>
       <c r="E1344" s="2" t="s">
-        <v>6565</v>
+        <v>6560</v>
       </c>
       <c r="F1344" s="2" t="s">
-        <v>6566</v>
+        <v>6561</v>
       </c>
       <c r="G1344" s="3">
         <v>4</v>
       </c>
       <c r="H1344" s="2" t="s">
-        <v>6567</v>
+        <v>6562</v>
       </c>
       <c r="I1344" s="2" t="s">
         <v>831</v>
@@ -60302,7 +60327,7 @@
         <v>1344</v>
       </c>
       <c r="B1345" s="2" t="s">
-        <v>6568</v>
+        <v>6563</v>
       </c>
       <c r="C1345" s="2" t="s">
         <v>516</v>
@@ -60311,7 +60336,7 @@
         <v>515</v>
       </c>
       <c r="E1345" s="2" t="s">
-        <v>6569</v>
+        <v>6564</v>
       </c>
       <c r="F1345" s="2"/>
       <c r="G1345" s="3">
@@ -60329,25 +60354,25 @@
         <v>1345</v>
       </c>
       <c r="B1346" s="2" t="s">
-        <v>6570</v>
+        <v>6565</v>
       </c>
       <c r="C1346" s="2" t="s">
-        <v>6571</v>
+        <v>6566</v>
       </c>
       <c r="D1346" s="2" t="s">
-        <v>6572</v>
+        <v>6567</v>
       </c>
       <c r="E1346" s="2" t="s">
-        <v>6573</v>
+        <v>6568</v>
       </c>
       <c r="F1346" s="2" t="s">
-        <v>6574</v>
+        <v>6569</v>
       </c>
       <c r="G1346" s="3">
         <v>4</v>
       </c>
       <c r="H1346" s="2" t="s">
-        <v>6575</v>
+        <v>6570</v>
       </c>
       <c r="I1346" s="2" t="s">
         <v>15</v>
@@ -60358,25 +60383,25 @@
         <v>1346</v>
       </c>
       <c r="B1347" s="2" t="s">
-        <v>6576</v>
+        <v>6571</v>
       </c>
       <c r="C1347" s="2" t="s">
         <v>1470</v>
       </c>
       <c r="D1347" s="2" t="s">
-        <v>6577</v>
+        <v>6572</v>
       </c>
       <c r="E1347" s="2" t="s">
         <v>1144</v>
       </c>
       <c r="F1347" s="2" t="s">
-        <v>6578</v>
+        <v>6573</v>
       </c>
       <c r="G1347" s="3">
         <v>2</v>
       </c>
       <c r="H1347" s="2" t="s">
-        <v>6579</v>
+        <v>6574</v>
       </c>
       <c r="I1347" s="2" t="s">
         <v>831</v>
@@ -60387,25 +60412,25 @@
         <v>1347</v>
       </c>
       <c r="B1348" s="2" t="s">
-        <v>6580</v>
+        <v>6575</v>
       </c>
       <c r="C1348" s="2" t="s">
-        <v>6581</v>
+        <v>6576</v>
       </c>
       <c r="D1348" s="2" t="s">
-        <v>6582</v>
+        <v>6577</v>
       </c>
       <c r="E1348" s="2" t="s">
-        <v>6583</v>
+        <v>6578</v>
       </c>
       <c r="F1348" s="2" t="s">
-        <v>6584</v>
+        <v>6579</v>
       </c>
       <c r="G1348" s="3">
         <v>4</v>
       </c>
       <c r="H1348" s="2" t="s">
-        <v>6585</v>
+        <v>6580</v>
       </c>
       <c r="I1348" s="2" t="s">
         <v>831</v>
@@ -60416,13 +60441,13 @@
         <v>1348</v>
       </c>
       <c r="B1349" s="2" t="s">
-        <v>6586</v>
+        <v>6581</v>
       </c>
       <c r="C1349" s="2" t="s">
         <v>119</v>
       </c>
       <c r="D1349" s="2" t="s">
-        <v>6587</v>
+        <v>6582</v>
       </c>
       <c r="E1349" s="2" t="s">
         <v>26</v>
@@ -60434,7 +60459,7 @@
         <v>4</v>
       </c>
       <c r="H1349" s="2" t="s">
-        <v>6588</v>
+        <v>6583</v>
       </c>
       <c r="I1349" s="2" t="s">
         <v>831</v>
@@ -60445,25 +60470,25 @@
         <v>1349</v>
       </c>
       <c r="B1350" s="2" t="s">
-        <v>6589</v>
+        <v>6584</v>
       </c>
       <c r="C1350" s="2" t="s">
-        <v>6590</v>
+        <v>6585</v>
       </c>
       <c r="D1350" s="2" t="s">
-        <v>6591</v>
+        <v>6586</v>
       </c>
       <c r="E1350" s="2" t="s">
-        <v>6592</v>
+        <v>6587</v>
       </c>
       <c r="F1350" s="2" t="s">
-        <v>6593</v>
+        <v>6588</v>
       </c>
       <c r="G1350" s="3">
         <v>4</v>
       </c>
       <c r="H1350" s="2" t="s">
-        <v>6594</v>
+        <v>6589</v>
       </c>
       <c r="I1350" s="2" t="s">
         <v>22</v>
@@ -60474,7 +60499,7 @@
         <v>1350</v>
       </c>
       <c r="B1351" s="2" t="s">
-        <v>6595</v>
+        <v>6590</v>
       </c>
       <c r="C1351" s="2" t="s">
         <v>778</v>
@@ -60483,7 +60508,7 @@
         <v>405</v>
       </c>
       <c r="E1351" s="2" t="s">
-        <v>6596</v>
+        <v>6591</v>
       </c>
       <c r="F1351" s="2" t="s">
         <v>796</v>
@@ -60492,7 +60517,7 @@
         <v>1</v>
       </c>
       <c r="H1351" s="2" t="s">
-        <v>6597</v>
+        <v>6592</v>
       </c>
       <c r="I1351" s="2" t="s">
         <v>22</v>
@@ -60503,25 +60528,25 @@
         <v>1351</v>
       </c>
       <c r="B1352" s="2" t="s">
-        <v>6598</v>
+        <v>6593</v>
       </c>
       <c r="C1352" s="2" t="s">
-        <v>6599</v>
+        <v>6594</v>
       </c>
       <c r="D1352" s="2" t="s">
-        <v>6600</v>
+        <v>6595</v>
       </c>
       <c r="E1352" s="2" t="s">
-        <v>6601</v>
+        <v>6596</v>
       </c>
       <c r="F1352" s="2" t="s">
-        <v>6602</v>
+        <v>6597</v>
       </c>
       <c r="G1352" s="3">
         <v>1</v>
       </c>
       <c r="H1352" s="2" t="s">
-        <v>6603</v>
+        <v>6598</v>
       </c>
       <c r="I1352" s="2" t="s">
         <v>22</v>
@@ -60532,7 +60557,7 @@
         <v>1352</v>
       </c>
       <c r="B1353" s="2" t="s">
-        <v>6604</v>
+        <v>6599</v>
       </c>
       <c r="C1353" s="2" t="s">
         <v>160</v>
@@ -60550,7 +60575,7 @@
         <v>1</v>
       </c>
       <c r="H1353" s="2" t="s">
-        <v>6605</v>
+        <v>6600</v>
       </c>
       <c r="I1353" s="2" t="s">
         <v>15</v>
@@ -60561,23 +60586,23 @@
         <v>1353</v>
       </c>
       <c r="B1354" s="2" t="s">
-        <v>6606</v>
+        <v>6601</v>
       </c>
       <c r="C1354" s="2" t="s">
-        <v>6607</v>
+        <v>6602</v>
       </c>
       <c r="D1354" s="2" t="s">
-        <v>6608</v>
+        <v>6603</v>
       </c>
       <c r="E1354" s="2" t="s">
-        <v>6609</v>
+        <v>6604</v>
       </c>
       <c r="F1354" s="2"/>
       <c r="G1354" s="3">
         <v>1</v>
       </c>
       <c r="H1354" s="2" t="s">
-        <v>6610</v>
+        <v>6605</v>
       </c>
       <c r="I1354" s="2" t="s">
         <v>831</v>
@@ -60588,7 +60613,7 @@
         <v>1354</v>
       </c>
       <c r="B1355" s="2" t="s">
-        <v>6611</v>
+        <v>6606</v>
       </c>
       <c r="C1355" s="2" t="s">
         <v>847</v>
@@ -60604,7 +60629,7 @@
         <v>4</v>
       </c>
       <c r="H1355" s="2" t="s">
-        <v>6612</v>
+        <v>6607</v>
       </c>
       <c r="I1355" s="2" t="s">
         <v>831</v>
@@ -60615,25 +60640,25 @@
         <v>1355</v>
       </c>
       <c r="B1356" s="2" t="s">
-        <v>6613</v>
+        <v>6608</v>
       </c>
       <c r="C1356" s="2" t="s">
-        <v>6614</v>
+        <v>6609</v>
       </c>
       <c r="D1356" s="2" t="s">
-        <v>6615</v>
+        <v>6610</v>
       </c>
       <c r="E1356" s="2" t="s">
-        <v>6616</v>
+        <v>6611</v>
       </c>
       <c r="F1356" s="2" t="s">
-        <v>6617</v>
+        <v>6612</v>
       </c>
       <c r="G1356" s="3">
         <v>2</v>
       </c>
       <c r="H1356" s="2" t="s">
-        <v>6618</v>
+        <v>6613</v>
       </c>
       <c r="I1356" s="2" t="s">
         <v>831</v>
@@ -60644,25 +60669,25 @@
         <v>1356</v>
       </c>
       <c r="B1357" s="2" t="s">
-        <v>6619</v>
+        <v>6614</v>
       </c>
       <c r="C1357" s="2" t="s">
-        <v>6620</v>
+        <v>6615</v>
       </c>
       <c r="D1357" s="2" t="s">
-        <v>6621</v>
+        <v>6616</v>
       </c>
       <c r="E1357" s="2" t="s">
-        <v>6622</v>
+        <v>6617</v>
       </c>
       <c r="F1357" s="2" t="s">
-        <v>6623</v>
+        <v>6618</v>
       </c>
       <c r="G1357" s="3">
         <v>2</v>
       </c>
       <c r="H1357" s="2" t="s">
-        <v>6624</v>
+        <v>6619</v>
       </c>
       <c r="I1357" s="2" t="s">
         <v>831</v>
@@ -60673,25 +60698,25 @@
         <v>1357</v>
       </c>
       <c r="B1358" s="2" t="s">
-        <v>6625</v>
+        <v>6620</v>
       </c>
       <c r="C1358" s="2" t="s">
-        <v>6626</v>
+        <v>6621</v>
       </c>
       <c r="D1358" s="2" t="s">
-        <v>6627</v>
+        <v>6622</v>
       </c>
       <c r="E1358" s="2" t="s">
-        <v>6628</v>
+        <v>6623</v>
       </c>
       <c r="F1358" s="2" t="s">
-        <v>6629</v>
+        <v>6624</v>
       </c>
       <c r="G1358" s="3">
         <v>4</v>
       </c>
       <c r="H1358" s="2" t="s">
-        <v>6630</v>
+        <v>6625</v>
       </c>
       <c r="I1358" s="2" t="s">
         <v>831</v>
@@ -60702,25 +60727,25 @@
         <v>1358</v>
       </c>
       <c r="B1359" s="2" t="s">
-        <v>6631</v>
+        <v>6626</v>
       </c>
       <c r="C1359" s="2" t="s">
-        <v>6632</v>
+        <v>6627</v>
       </c>
       <c r="D1359" s="2" t="s">
-        <v>6633</v>
+        <v>6628</v>
       </c>
       <c r="E1359" s="2" t="s">
-        <v>6634</v>
+        <v>6629</v>
       </c>
       <c r="F1359" s="2" t="s">
-        <v>6635</v>
+        <v>6630</v>
       </c>
       <c r="G1359" s="3">
         <v>4</v>
       </c>
       <c r="H1359" s="2" t="s">
-        <v>6636</v>
+        <v>6631</v>
       </c>
       <c r="I1359" s="2" t="s">
         <v>831</v>
@@ -60731,23 +60756,23 @@
         <v>1359</v>
       </c>
       <c r="B1360" s="2" t="s">
-        <v>6637</v>
+        <v>6632</v>
       </c>
       <c r="C1360" s="2" t="s">
-        <v>6638</v>
+        <v>6633</v>
       </c>
       <c r="D1360" s="2"/>
       <c r="E1360" s="2" t="s">
-        <v>6639</v>
+        <v>6634</v>
       </c>
       <c r="F1360" s="2" t="s">
-        <v>6640</v>
+        <v>6635</v>
       </c>
       <c r="G1360" s="3">
         <v>1</v>
       </c>
       <c r="H1360" s="2" t="s">
-        <v>6641</v>
+        <v>6636</v>
       </c>
       <c r="I1360" s="2" t="s">
         <v>831</v>
@@ -60758,25 +60783,25 @@
         <v>1360</v>
       </c>
       <c r="B1361" s="2" t="s">
-        <v>6642</v>
+        <v>6637</v>
       </c>
       <c r="C1361" s="2" t="s">
-        <v>6643</v>
+        <v>6638</v>
       </c>
       <c r="D1361" s="2" t="s">
-        <v>6644</v>
+        <v>6639</v>
       </c>
       <c r="E1361" s="2" t="s">
-        <v>6645</v>
+        <v>6640</v>
       </c>
       <c r="F1361" s="2" t="s">
-        <v>6646</v>
+        <v>6641</v>
       </c>
       <c r="G1361" s="3">
         <v>3</v>
       </c>
       <c r="H1361" s="2" t="s">
-        <v>6647</v>
+        <v>6642</v>
       </c>
       <c r="I1361" s="2" t="s">
         <v>15</v>
@@ -60787,7 +60812,7 @@
         <v>1361</v>
       </c>
       <c r="B1362" s="2" t="s">
-        <v>6648</v>
+        <v>6643</v>
       </c>
       <c r="C1362" s="2" t="s">
         <v>1337</v>
@@ -60796,10 +60821,10 @@
         <v>1338</v>
       </c>
       <c r="E1362" s="2" t="s">
-        <v>6649</v>
+        <v>6644</v>
       </c>
       <c r="F1362" s="2" t="s">
-        <v>6650</v>
+        <v>6645</v>
       </c>
       <c r="G1362" s="3">
         <v>1</v>
@@ -60816,25 +60841,25 @@
         <v>1362</v>
       </c>
       <c r="B1363" s="2" t="s">
-        <v>6651</v>
+        <v>6646</v>
       </c>
       <c r="C1363" s="2" t="s">
-        <v>6652</v>
+        <v>6647</v>
       </c>
       <c r="D1363" s="2" t="s">
-        <v>6653</v>
+        <v>6648</v>
       </c>
       <c r="E1363" s="2" t="s">
-        <v>6654</v>
+        <v>6649</v>
       </c>
       <c r="F1363" s="2" t="s">
-        <v>6655</v>
+        <v>6650</v>
       </c>
       <c r="G1363" s="3">
         <v>2</v>
       </c>
       <c r="H1363" s="2" t="s">
-        <v>6656</v>
+        <v>6651</v>
       </c>
       <c r="I1363" s="2" t="s">
         <v>15</v>
@@ -60845,25 +60870,25 @@
         <v>1363</v>
       </c>
       <c r="B1364" s="2" t="s">
-        <v>6657</v>
+        <v>6652</v>
       </c>
       <c r="C1364" s="2" t="s">
-        <v>6658</v>
+        <v>6653</v>
       </c>
       <c r="D1364" s="2" t="s">
-        <v>6659</v>
+        <v>6654</v>
       </c>
       <c r="E1364" s="2" t="s">
-        <v>6660</v>
+        <v>6655</v>
       </c>
       <c r="F1364" s="2" t="s">
-        <v>6661</v>
+        <v>6656</v>
       </c>
       <c r="G1364" s="3">
         <v>1</v>
       </c>
       <c r="H1364" s="2" t="s">
-        <v>6662</v>
+        <v>6657</v>
       </c>
       <c r="I1364" s="2" t="s">
         <v>15</v>
@@ -60903,7 +60928,7 @@
         <v>1365</v>
       </c>
       <c r="B1366" s="2" t="s">
-        <v>6663</v>
+        <v>6658</v>
       </c>
       <c r="C1366" s="2" t="s">
         <v>1402</v>
@@ -60921,7 +60946,7 @@
         <v>3</v>
       </c>
       <c r="H1366" s="2" t="s">
-        <v>6664</v>
+        <v>6659</v>
       </c>
       <c r="I1366" s="2" t="s">
         <v>15</v>
@@ -60932,25 +60957,25 @@
         <v>1366</v>
       </c>
       <c r="B1367" s="2" t="s">
-        <v>6665</v>
+        <v>6660</v>
       </c>
       <c r="C1367" s="2" t="s">
-        <v>6666</v>
+        <v>6661</v>
       </c>
       <c r="D1367" s="2" t="s">
-        <v>6667</v>
+        <v>6662</v>
       </c>
       <c r="E1367" s="2" t="s">
-        <v>6668</v>
+        <v>6663</v>
       </c>
       <c r="F1367" s="2" t="s">
-        <v>6669</v>
+        <v>6664</v>
       </c>
       <c r="G1367" s="3">
         <v>3</v>
       </c>
       <c r="H1367" s="2" t="s">
-        <v>6670</v>
+        <v>6665</v>
       </c>
       <c r="I1367" s="2" t="s">
         <v>831</v>
@@ -60961,16 +60986,16 @@
         <v>1367</v>
       </c>
       <c r="B1368" s="2" t="s">
-        <v>6671</v>
+        <v>6666</v>
       </c>
       <c r="C1368" s="2" t="s">
-        <v>6672</v>
+        <v>6667</v>
       </c>
       <c r="D1368" s="2" t="s">
-        <v>6673</v>
+        <v>6668</v>
       </c>
       <c r="E1368" s="2" t="s">
-        <v>6674</v>
+        <v>6669</v>
       </c>
       <c r="F1368" s="2" t="s">
         <v>51</v>
@@ -60990,25 +61015,25 @@
         <v>1368</v>
       </c>
       <c r="B1369" s="2" t="s">
-        <v>6675</v>
+        <v>6670</v>
       </c>
       <c r="C1369" s="2" t="s">
-        <v>6676</v>
+        <v>6671</v>
       </c>
       <c r="D1369" s="2" t="s">
-        <v>6677</v>
+        <v>6672</v>
       </c>
       <c r="E1369" s="2" t="s">
-        <v>6678</v>
+        <v>6673</v>
       </c>
       <c r="F1369" s="2" t="s">
-        <v>6679</v>
+        <v>6674</v>
       </c>
       <c r="G1369" s="3">
         <v>3</v>
       </c>
       <c r="H1369" s="2" t="s">
-        <v>6680</v>
+        <v>6675</v>
       </c>
       <c r="I1369" s="2" t="s">
         <v>803</v>
@@ -61019,25 +61044,25 @@
         <v>1369</v>
       </c>
       <c r="B1370" s="2" t="s">
-        <v>6681</v>
+        <v>6676</v>
       </c>
       <c r="C1370" s="2" t="s">
         <v>1695</v>
       </c>
       <c r="D1370" s="2" t="s">
-        <v>6682</v>
+        <v>6677</v>
       </c>
       <c r="E1370" s="2" t="s">
-        <v>6683</v>
+        <v>6678</v>
       </c>
       <c r="F1370" s="2" t="s">
-        <v>6684</v>
+        <v>6679</v>
       </c>
       <c r="G1370" s="3">
         <v>3</v>
       </c>
       <c r="H1370" s="2" t="s">
-        <v>6685</v>
+        <v>6680</v>
       </c>
       <c r="I1370" s="2" t="s">
         <v>15</v>
@@ -61048,25 +61073,25 @@
         <v>1370</v>
       </c>
       <c r="B1371" s="2" t="s">
-        <v>6686</v>
+        <v>6681</v>
       </c>
       <c r="C1371" s="2" t="s">
-        <v>6687</v>
+        <v>6682</v>
       </c>
       <c r="D1371" s="2" t="s">
-        <v>6688</v>
+        <v>6683</v>
       </c>
       <c r="E1371" s="2" t="s">
-        <v>6689</v>
+        <v>6684</v>
       </c>
       <c r="F1371" s="2" t="s">
-        <v>6690</v>
+        <v>6685</v>
       </c>
       <c r="G1371" s="3">
         <v>2</v>
       </c>
       <c r="H1371" s="2" t="s">
-        <v>6691</v>
+        <v>6686</v>
       </c>
       <c r="I1371" s="2" t="s">
         <v>15</v>
@@ -61077,13 +61102,13 @@
         <v>1371</v>
       </c>
       <c r="B1372" s="2" t="s">
-        <v>6692</v>
+        <v>6687</v>
       </c>
       <c r="C1372" s="2" t="s">
         <v>2423</v>
       </c>
       <c r="D1372" s="2" t="s">
-        <v>6693</v>
+        <v>6688</v>
       </c>
       <c r="E1372" s="2" t="s">
         <v>2424</v>
@@ -61095,7 +61120,7 @@
         <v>2</v>
       </c>
       <c r="H1372" s="2" t="s">
-        <v>6694</v>
+        <v>6689</v>
       </c>
       <c r="I1372" s="2" t="s">
         <v>15</v>
@@ -61106,25 +61131,25 @@
         <v>1372</v>
       </c>
       <c r="B1373" s="2" t="s">
-        <v>6695</v>
+        <v>6690</v>
       </c>
       <c r="C1373" s="2" t="s">
         <v>2364</v>
       </c>
       <c r="D1373" s="2" t="s">
-        <v>6696</v>
+        <v>6691</v>
       </c>
       <c r="E1373" s="2" t="s">
-        <v>6697</v>
+        <v>6692</v>
       </c>
       <c r="F1373" s="2" t="s">
-        <v>6698</v>
+        <v>6693</v>
       </c>
       <c r="G1373" s="3">
         <v>2</v>
       </c>
       <c r="H1373" s="2" t="s">
-        <v>6699</v>
+        <v>6694</v>
       </c>
       <c r="I1373" s="2" t="s">
         <v>15</v>
@@ -61135,25 +61160,25 @@
         <v>1373</v>
       </c>
       <c r="B1374" s="2" t="s">
-        <v>6700</v>
+        <v>6695</v>
       </c>
       <c r="C1374" s="2" t="s">
-        <v>6701</v>
+        <v>6696</v>
       </c>
       <c r="D1374" s="2" t="s">
-        <v>6702</v>
+        <v>6697</v>
       </c>
       <c r="E1374" s="2" t="s">
-        <v>6703</v>
+        <v>6698</v>
       </c>
       <c r="F1374" s="2" t="s">
-        <v>6704</v>
+        <v>6699</v>
       </c>
       <c r="G1374" s="3">
         <v>4</v>
       </c>
       <c r="H1374" s="2" t="s">
-        <v>6705</v>
+        <v>6700</v>
       </c>
       <c r="I1374" s="2" t="s">
         <v>15</v>
@@ -61164,25 +61189,25 @@
         <v>1374</v>
       </c>
       <c r="B1375" s="2" t="s">
-        <v>6706</v>
+        <v>6701</v>
       </c>
       <c r="C1375" s="2" t="s">
-        <v>6707</v>
+        <v>6702</v>
       </c>
       <c r="D1375" s="2" t="s">
-        <v>6708</v>
+        <v>6703</v>
       </c>
       <c r="E1375" s="2" t="s">
-        <v>6709</v>
+        <v>6704</v>
       </c>
       <c r="F1375" s="2" t="s">
-        <v>6710</v>
+        <v>6705</v>
       </c>
       <c r="G1375" s="3">
         <v>1</v>
       </c>
       <c r="H1375" s="2" t="s">
-        <v>6711</v>
+        <v>6706</v>
       </c>
       <c r="I1375" s="2" t="s">
         <v>831</v>
@@ -61193,25 +61218,25 @@
         <v>1375</v>
       </c>
       <c r="B1376" s="2" t="s">
-        <v>6712</v>
+        <v>6707</v>
       </c>
       <c r="C1376" s="2" t="s">
-        <v>6713</v>
+        <v>6708</v>
       </c>
       <c r="D1376" s="2" t="s">
-        <v>6714</v>
+        <v>6709</v>
       </c>
       <c r="E1376" s="2" t="s">
-        <v>6715</v>
+        <v>6710</v>
       </c>
       <c r="F1376" s="2" t="s">
-        <v>6716</v>
+        <v>6711</v>
       </c>
       <c r="G1376" s="3">
         <v>2</v>
       </c>
       <c r="H1376" s="2" t="s">
-        <v>6717</v>
+        <v>6712</v>
       </c>
       <c r="I1376" s="2" t="s">
         <v>831</v>
@@ -61222,25 +61247,25 @@
         <v>1376</v>
       </c>
       <c r="B1377" s="2" t="s">
-        <v>6718</v>
+        <v>6713</v>
       </c>
       <c r="C1377" s="2" t="s">
-        <v>6719</v>
+        <v>6714</v>
       </c>
       <c r="D1377" s="2" t="s">
-        <v>6720</v>
+        <v>6715</v>
       </c>
       <c r="E1377" s="2" t="s">
-        <v>6721</v>
+        <v>6716</v>
       </c>
       <c r="F1377" s="2" t="s">
-        <v>6722</v>
+        <v>6717</v>
       </c>
       <c r="G1377" s="3">
         <v>3</v>
       </c>
       <c r="H1377" s="2" t="s">
-        <v>6723</v>
+        <v>6718</v>
       </c>
       <c r="I1377" s="2" t="s">
         <v>15</v>
@@ -61251,7 +61276,7 @@
         <v>1377</v>
       </c>
       <c r="B1378" s="2" t="s">
-        <v>6724</v>
+        <v>6719</v>
       </c>
       <c r="C1378" s="2" t="s">
         <v>77</v>
@@ -61280,25 +61305,25 @@
         <v>1378</v>
       </c>
       <c r="B1379" s="2" t="s">
-        <v>6725</v>
+        <v>6720</v>
       </c>
       <c r="C1379" s="2" t="s">
-        <v>6726</v>
+        <v>6721</v>
       </c>
       <c r="D1379" s="2" t="s">
-        <v>6727</v>
+        <v>6722</v>
       </c>
       <c r="E1379" s="2" t="s">
-        <v>6728</v>
+        <v>6723</v>
       </c>
       <c r="F1379" s="2" t="s">
-        <v>6729</v>
+        <v>6724</v>
       </c>
       <c r="G1379" s="3">
         <v>1</v>
       </c>
       <c r="H1379" s="2" t="s">
-        <v>6730</v>
+        <v>6725</v>
       </c>
       <c r="I1379" s="2" t="s">
         <v>831</v>
@@ -61309,7 +61334,7 @@
         <v>1379</v>
       </c>
       <c r="B1380" s="2" t="s">
-        <v>6731</v>
+        <v>6726</v>
       </c>
       <c r="C1380" s="2" t="s">
         <v>381</v>
@@ -61327,7 +61352,7 @@
         <v>1</v>
       </c>
       <c r="H1380" s="2" t="s">
-        <v>6732</v>
+        <v>6727</v>
       </c>
       <c r="I1380" s="2" t="s">
         <v>831</v>
@@ -61338,10 +61363,10 @@
         <v>1380</v>
       </c>
       <c r="B1381" s="2" t="s">
-        <v>6733</v>
+        <v>6728</v>
       </c>
       <c r="C1381" s="2" t="s">
-        <v>6734</v>
+        <v>6729</v>
       </c>
       <c r="D1381" s="2" t="s">
         <v>12</v>
@@ -61350,13 +61375,13 @@
         <v>896</v>
       </c>
       <c r="F1381" s="2" t="s">
-        <v>6735</v>
+        <v>6730</v>
       </c>
       <c r="G1381" s="3">
         <v>1</v>
       </c>
       <c r="H1381" s="2" t="s">
-        <v>6736</v>
+        <v>6731</v>
       </c>
       <c r="I1381" s="2" t="s">
         <v>831</v>
@@ -61367,25 +61392,25 @@
         <v>1381</v>
       </c>
       <c r="B1382" s="2" t="s">
-        <v>6737</v>
+        <v>6732</v>
       </c>
       <c r="C1382" s="2" t="s">
-        <v>6738</v>
+        <v>6733</v>
       </c>
       <c r="D1382" s="2" t="s">
-        <v>6739</v>
+        <v>6734</v>
       </c>
       <c r="E1382" s="2" t="s">
-        <v>6740</v>
+        <v>6735</v>
       </c>
       <c r="F1382" s="2" t="s">
-        <v>6741</v>
+        <v>6736</v>
       </c>
       <c r="G1382" s="3">
         <v>2</v>
       </c>
       <c r="H1382" s="2" t="s">
-        <v>6742</v>
+        <v>6737</v>
       </c>
       <c r="I1382" s="2" t="s">
         <v>15</v>
@@ -61396,25 +61421,25 @@
         <v>1382</v>
       </c>
       <c r="B1383" s="2" t="s">
-        <v>6743</v>
+        <v>6738</v>
       </c>
       <c r="C1383" s="2" t="s">
         <v>1480</v>
       </c>
       <c r="D1383" s="2" t="s">
-        <v>6744</v>
+        <v>6739</v>
       </c>
       <c r="E1383" s="2" t="s">
-        <v>6745</v>
+        <v>6740</v>
       </c>
       <c r="F1383" s="2" t="s">
-        <v>6746</v>
+        <v>6741</v>
       </c>
       <c r="G1383" s="3">
         <v>4</v>
       </c>
       <c r="H1383" s="2" t="s">
-        <v>6747</v>
+        <v>6742</v>
       </c>
       <c r="I1383" s="2" t="s">
         <v>15</v>
@@ -61425,25 +61450,25 @@
         <v>1383</v>
       </c>
       <c r="B1384" s="2" t="s">
-        <v>6748</v>
+        <v>6743</v>
       </c>
       <c r="C1384" s="2" t="s">
-        <v>6532</v>
+        <v>6527</v>
       </c>
       <c r="D1384" s="2" t="s">
-        <v>6749</v>
+        <v>6744</v>
       </c>
       <c r="E1384" s="2" t="s">
-        <v>6750</v>
+        <v>6745</v>
       </c>
       <c r="F1384" s="2" t="s">
-        <v>6751</v>
+        <v>6746</v>
       </c>
       <c r="G1384" s="3">
         <v>4</v>
       </c>
       <c r="H1384" s="2" t="s">
-        <v>6752</v>
+        <v>6747</v>
       </c>
       <c r="I1384" s="2" t="s">
         <v>831</v>
@@ -61454,25 +61479,25 @@
         <v>1384</v>
       </c>
       <c r="B1385" s="2" t="s">
-        <v>6753</v>
+        <v>6748</v>
       </c>
       <c r="C1385" s="2" t="s">
-        <v>6754</v>
+        <v>6749</v>
       </c>
       <c r="D1385" s="2" t="s">
-        <v>6755</v>
+        <v>6750</v>
       </c>
       <c r="E1385" s="2" t="s">
-        <v>6756</v>
+        <v>6751</v>
       </c>
       <c r="F1385" s="2" t="s">
-        <v>6757</v>
+        <v>6752</v>
       </c>
       <c r="G1385" s="3">
         <v>3</v>
       </c>
       <c r="H1385" s="2" t="s">
-        <v>6758</v>
+        <v>6753</v>
       </c>
       <c r="I1385" s="2" t="s">
         <v>831</v>
@@ -61483,25 +61508,25 @@
         <v>1385</v>
       </c>
       <c r="B1386" s="2" t="s">
-        <v>6759</v>
+        <v>6754</v>
       </c>
       <c r="C1386" s="2" t="s">
-        <v>6760</v>
+        <v>6755</v>
       </c>
       <c r="D1386" s="2" t="s">
-        <v>6761</v>
+        <v>6756</v>
       </c>
       <c r="E1386" s="2" t="s">
-        <v>6762</v>
+        <v>6757</v>
       </c>
       <c r="F1386" s="2" t="s">
-        <v>6763</v>
+        <v>6758</v>
       </c>
       <c r="G1386" s="3">
         <v>3</v>
       </c>
       <c r="H1386" s="2" t="s">
-        <v>6764</v>
+        <v>6759</v>
       </c>
       <c r="I1386" s="2" t="s">
         <v>15</v>
@@ -61512,25 +61537,25 @@
         <v>1386</v>
       </c>
       <c r="B1387" s="2" t="s">
-        <v>6765</v>
+        <v>6760</v>
       </c>
       <c r="C1387" s="2" t="s">
-        <v>6960</v>
+        <v>6955</v>
       </c>
       <c r="D1387" s="2" t="s">
-        <v>6961</v>
+        <v>6956</v>
       </c>
       <c r="E1387" s="2" t="s">
-        <v>6962</v>
+        <v>6957</v>
       </c>
       <c r="F1387" s="2" t="s">
-        <v>6963</v>
+        <v>6958</v>
       </c>
       <c r="G1387" s="3">
         <v>1</v>
       </c>
       <c r="H1387" s="2" t="s">
-        <v>6766</v>
+        <v>6761</v>
       </c>
       <c r="I1387" s="2" t="s">
         <v>15</v>
@@ -61541,25 +61566,25 @@
         <v>1387</v>
       </c>
       <c r="B1388" s="2" t="s">
-        <v>6767</v>
+        <v>6762</v>
       </c>
       <c r="C1388" s="2" t="s">
-        <v>6768</v>
+        <v>6763</v>
       </c>
       <c r="D1388" s="2" t="s">
         <v>44</v>
       </c>
       <c r="E1388" s="2" t="s">
-        <v>6769</v>
+        <v>6764</v>
       </c>
       <c r="F1388" s="2" t="s">
-        <v>6770</v>
+        <v>6765</v>
       </c>
       <c r="G1388" s="3">
         <v>1</v>
       </c>
       <c r="H1388" s="2" t="s">
-        <v>6771</v>
+        <v>6766</v>
       </c>
       <c r="I1388" s="2" t="s">
         <v>831</v>
@@ -61570,25 +61595,25 @@
         <v>1388</v>
       </c>
       <c r="B1389" s="2" t="s">
-        <v>6772</v>
+        <v>6767</v>
       </c>
       <c r="C1389" s="2" t="s">
-        <v>6773</v>
+        <v>6768</v>
       </c>
       <c r="D1389" s="2" t="s">
-        <v>6774</v>
+        <v>6769</v>
       </c>
       <c r="E1389" s="2" t="s">
-        <v>6775</v>
+        <v>6770</v>
       </c>
       <c r="F1389" s="2" t="s">
-        <v>6776</v>
+        <v>6771</v>
       </c>
       <c r="G1389" s="3">
         <v>1</v>
       </c>
       <c r="H1389" s="2" t="s">
-        <v>6777</v>
+        <v>6772</v>
       </c>
       <c r="I1389" s="2" t="s">
         <v>15</v>
@@ -61599,25 +61624,25 @@
         <v>1389</v>
       </c>
       <c r="B1390" s="2" t="s">
-        <v>6778</v>
+        <v>6773</v>
       </c>
       <c r="C1390" s="2" t="s">
-        <v>6779</v>
+        <v>6774</v>
       </c>
       <c r="D1390" s="2" t="s">
-        <v>6780</v>
+        <v>6775</v>
       </c>
       <c r="E1390" s="2" t="s">
-        <v>6781</v>
+        <v>6776</v>
       </c>
       <c r="F1390" s="2" t="s">
-        <v>6782</v>
+        <v>6777</v>
       </c>
       <c r="G1390" s="3">
         <v>4</v>
       </c>
       <c r="H1390" s="2" t="s">
-        <v>6783</v>
+        <v>6778</v>
       </c>
       <c r="I1390" s="2" t="s">
         <v>15</v>
@@ -61628,25 +61653,25 @@
         <v>1390</v>
       </c>
       <c r="B1391" s="2" t="s">
-        <v>6784</v>
+        <v>6779</v>
       </c>
       <c r="C1391" s="2" t="s">
-        <v>6785</v>
+        <v>6780</v>
       </c>
       <c r="D1391" s="2" t="s">
-        <v>6786</v>
+        <v>6781</v>
       </c>
       <c r="E1391" s="2" t="s">
-        <v>6787</v>
+        <v>6782</v>
       </c>
       <c r="F1391" s="2" t="s">
-        <v>6788</v>
+        <v>6783</v>
       </c>
       <c r="G1391" s="3">
         <v>1</v>
       </c>
       <c r="H1391" s="2" t="s">
-        <v>6789</v>
+        <v>6784</v>
       </c>
       <c r="I1391" s="2" t="s">
         <v>15</v>
@@ -61657,25 +61682,25 @@
         <v>1391</v>
       </c>
       <c r="B1392" s="2" t="s">
-        <v>6790</v>
+        <v>6785</v>
       </c>
       <c r="C1392" s="2" t="s">
-        <v>6791</v>
+        <v>6786</v>
       </c>
       <c r="D1392" s="2" t="s">
-        <v>6792</v>
+        <v>6787</v>
       </c>
       <c r="E1392" s="2" t="s">
-        <v>6793</v>
+        <v>6788</v>
       </c>
       <c r="F1392" s="2" t="s">
-        <v>6794</v>
+        <v>6789</v>
       </c>
       <c r="G1392" s="3">
         <v>2</v>
       </c>
       <c r="H1392" s="2" t="s">
-        <v>6795</v>
+        <v>6790</v>
       </c>
       <c r="I1392" s="2" t="s">
         <v>15</v>
@@ -61686,25 +61711,25 @@
         <v>1392</v>
       </c>
       <c r="B1393" s="2" t="s">
-        <v>6796</v>
+        <v>6791</v>
       </c>
       <c r="C1393" s="2" t="s">
-        <v>6797</v>
+        <v>6792</v>
       </c>
       <c r="D1393" s="2" t="s">
-        <v>6798</v>
+        <v>6793</v>
       </c>
       <c r="E1393" s="2" t="s">
-        <v>6799</v>
+        <v>6794</v>
       </c>
       <c r="F1393" s="2" t="s">
-        <v>6800</v>
+        <v>6795</v>
       </c>
       <c r="G1393" s="3">
         <v>4</v>
       </c>
       <c r="H1393" s="2" t="s">
-        <v>6801</v>
+        <v>6796</v>
       </c>
       <c r="I1393" s="2" t="s">
         <v>831</v>
@@ -61715,25 +61740,25 @@
         <v>1393</v>
       </c>
       <c r="B1394" s="2" t="s">
-        <v>6802</v>
+        <v>6797</v>
       </c>
       <c r="C1394" s="2" t="s">
-        <v>6797</v>
+        <v>6792</v>
       </c>
       <c r="D1394" s="2" t="s">
-        <v>6803</v>
+        <v>6798</v>
       </c>
       <c r="E1394" s="2" t="s">
-        <v>6804</v>
+        <v>6799</v>
       </c>
       <c r="F1394" s="2" t="s">
-        <v>6805</v>
+        <v>6800</v>
       </c>
       <c r="G1394" s="3">
         <v>3</v>
       </c>
       <c r="H1394" s="2" t="s">
-        <v>6806</v>
+        <v>6801</v>
       </c>
       <c r="I1394" s="2" t="s">
         <v>831</v>
@@ -61744,7 +61769,7 @@
         <v>1394</v>
       </c>
       <c r="B1395" s="2" t="s">
-        <v>6807</v>
+        <v>6802</v>
       </c>
       <c r="C1395" s="2" t="s">
         <v>516</v>
@@ -61762,7 +61787,7 @@
         <v>4</v>
       </c>
       <c r="H1395" s="2" t="s">
-        <v>6808</v>
+        <v>6803</v>
       </c>
       <c r="I1395" s="2" t="s">
         <v>831</v>
@@ -61773,10 +61798,10 @@
         <v>1395</v>
       </c>
       <c r="B1396" s="2" t="s">
-        <v>6809</v>
+        <v>6804</v>
       </c>
       <c r="C1396" s="2" t="s">
-        <v>6810</v>
+        <v>6805</v>
       </c>
       <c r="D1396" s="2" t="s">
         <v>516</v>
@@ -61785,13 +61810,13 @@
         <v>515</v>
       </c>
       <c r="F1396" s="2" t="s">
-        <v>6811</v>
+        <v>6806</v>
       </c>
       <c r="G1396" s="3">
         <v>2</v>
       </c>
       <c r="H1396" s="2" t="s">
-        <v>6812</v>
+        <v>6807</v>
       </c>
       <c r="I1396" s="2" t="s">
         <v>831</v>
@@ -61802,25 +61827,25 @@
         <v>1396</v>
       </c>
       <c r="B1397" s="2" t="s">
-        <v>6813</v>
+        <v>6808</v>
       </c>
       <c r="C1397" s="2" t="s">
-        <v>6797</v>
+        <v>6792</v>
       </c>
       <c r="D1397" s="2" t="s">
-        <v>6803</v>
+        <v>6798</v>
       </c>
       <c r="E1397" s="2" t="s">
-        <v>6799</v>
+        <v>6794</v>
       </c>
       <c r="F1397" s="2" t="s">
-        <v>6800</v>
+        <v>6795</v>
       </c>
       <c r="G1397" s="3">
         <v>1</v>
       </c>
       <c r="H1397" s="2" t="s">
-        <v>6814</v>
+        <v>6809</v>
       </c>
       <c r="I1397" s="2" t="s">
         <v>831</v>
@@ -61831,25 +61856,25 @@
         <v>1397</v>
       </c>
       <c r="B1398" s="2" t="s">
-        <v>6815</v>
+        <v>6810</v>
       </c>
       <c r="C1398" s="2" t="s">
-        <v>6797</v>
+        <v>6792</v>
       </c>
       <c r="D1398" s="2" t="s">
-        <v>6803</v>
+        <v>6798</v>
       </c>
       <c r="E1398" s="2" t="s">
-        <v>6799</v>
+        <v>6794</v>
       </c>
       <c r="F1398" s="2" t="s">
-        <v>6800</v>
+        <v>6795</v>
       </c>
       <c r="G1398" s="3">
         <v>3</v>
       </c>
       <c r="H1398" s="2" t="s">
-        <v>6816</v>
+        <v>6811</v>
       </c>
       <c r="I1398" s="2" t="s">
         <v>831</v>
@@ -61860,7 +61885,7 @@
         <v>1398</v>
       </c>
       <c r="B1399" s="2" t="s">
-        <v>6817</v>
+        <v>6812</v>
       </c>
       <c r="C1399" s="2" t="s">
         <v>517</v>
@@ -61872,13 +61897,13 @@
         <v>515</v>
       </c>
       <c r="F1399" s="2" t="s">
-        <v>6818</v>
+        <v>6813</v>
       </c>
       <c r="G1399" s="3">
         <v>4</v>
       </c>
       <c r="H1399" s="2" t="s">
-        <v>6819</v>
+        <v>6814</v>
       </c>
       <c r="I1399" s="2" t="s">
         <v>831</v>
@@ -61889,25 +61914,25 @@
         <v>1399</v>
       </c>
       <c r="B1400" s="2" t="s">
-        <v>6820</v>
+        <v>6815</v>
       </c>
       <c r="C1400" s="2" t="s">
-        <v>6821</v>
+        <v>6816</v>
       </c>
       <c r="D1400" s="2" t="s">
-        <v>6822</v>
+        <v>6817</v>
       </c>
       <c r="E1400" s="2" t="s">
-        <v>6823</v>
+        <v>6818</v>
       </c>
       <c r="F1400" s="2" t="s">
-        <v>6824</v>
+        <v>6819</v>
       </c>
       <c r="G1400" s="3">
         <v>2</v>
       </c>
       <c r="H1400" s="2" t="s">
-        <v>6825</v>
+        <v>6820</v>
       </c>
       <c r="I1400" s="2" t="s">
         <v>831</v>
@@ -61918,25 +61943,25 @@
         <v>1400</v>
       </c>
       <c r="B1401" s="2" t="s">
-        <v>6826</v>
+        <v>6821</v>
       </c>
       <c r="C1401" s="2" t="s">
-        <v>6827</v>
+        <v>6822</v>
       </c>
       <c r="D1401" s="2" t="s">
-        <v>6828</v>
+        <v>6823</v>
       </c>
       <c r="E1401" s="2" t="s">
-        <v>6829</v>
+        <v>6824</v>
       </c>
       <c r="F1401" s="2" t="s">
-        <v>6830</v>
+        <v>6825</v>
       </c>
       <c r="G1401" s="3">
         <v>2</v>
       </c>
       <c r="H1401" s="2" t="s">
-        <v>6831</v>
+        <v>6826</v>
       </c>
       <c r="I1401" s="2" t="s">
         <v>831</v>
@@ -61947,25 +61972,25 @@
         <v>1401</v>
       </c>
       <c r="B1402" s="2" t="s">
-        <v>6832</v>
+        <v>6827</v>
       </c>
       <c r="C1402" s="2" t="s">
-        <v>6833</v>
+        <v>6828</v>
       </c>
       <c r="D1402" s="2" t="s">
-        <v>6834</v>
+        <v>6829</v>
       </c>
       <c r="E1402" s="2" t="s">
-        <v>6835</v>
+        <v>6830</v>
       </c>
       <c r="F1402" s="2" t="s">
-        <v>6836</v>
+        <v>6831</v>
       </c>
       <c r="G1402" s="3">
         <v>2</v>
       </c>
       <c r="H1402" s="2" t="s">
-        <v>6837</v>
+        <v>6832</v>
       </c>
       <c r="I1402" s="2" t="s">
         <v>15</v>
@@ -61976,25 +62001,25 @@
         <v>1402</v>
       </c>
       <c r="B1403" s="2" t="s">
-        <v>6838</v>
+        <v>6833</v>
       </c>
       <c r="C1403" s="2" t="s">
-        <v>6839</v>
+        <v>6834</v>
       </c>
       <c r="D1403" s="2" t="s">
-        <v>6840</v>
+        <v>6835</v>
       </c>
       <c r="E1403" s="2" t="s">
-        <v>6841</v>
+        <v>6836</v>
       </c>
       <c r="F1403" s="2" t="s">
-        <v>6842</v>
+        <v>6837</v>
       </c>
       <c r="G1403" s="3">
         <v>3</v>
       </c>
       <c r="H1403" s="2" t="s">
-        <v>6843</v>
+        <v>6838</v>
       </c>
       <c r="I1403" s="2" t="s">
         <v>15</v>
@@ -62005,25 +62030,25 @@
         <v>1403</v>
       </c>
       <c r="B1404" s="2" t="s">
-        <v>6844</v>
+        <v>6839</v>
       </c>
       <c r="C1404" s="2" t="s">
-        <v>6845</v>
+        <v>6840</v>
       </c>
       <c r="D1404" s="2" t="s">
-        <v>6846</v>
+        <v>6841</v>
       </c>
       <c r="E1404" s="2" t="s">
-        <v>6847</v>
+        <v>6842</v>
       </c>
       <c r="F1404" s="2" t="s">
-        <v>6848</v>
+        <v>6843</v>
       </c>
       <c r="G1404" s="3">
         <v>2</v>
       </c>
       <c r="H1404" s="2" t="s">
-        <v>6849</v>
+        <v>6844</v>
       </c>
       <c r="I1404" s="2" t="s">
         <v>15</v>
@@ -62051,10 +62076,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>6850</v>
+        <v>6845</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>6851</v>
+        <v>6846</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -62062,10 +62087,10 @@
         <v>241</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>6852</v>
+        <v>6847</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>6853</v>
+        <v>6848</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -62073,10 +62098,10 @@
         <v>491</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>6852</v>
+        <v>6847</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>6853</v>
+        <v>6848</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -62084,10 +62109,10 @@
         <v>567</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>6852</v>
+        <v>6847</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>6853</v>
+        <v>6848</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -62095,10 +62120,10 @@
         <v>703</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>6852</v>
+        <v>6847</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>6853</v>
+        <v>6848</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -62106,10 +62131,10 @@
         <v>937</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>6852</v>
+        <v>6847</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>6853</v>
+        <v>6848</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -62117,10 +62142,10 @@
         <v>1134</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>6852</v>
+        <v>6847</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>6853</v>
+        <v>6848</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -62128,10 +62153,10 @@
         <v>1188</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>6852</v>
+        <v>6847</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>6853</v>
+        <v>6848</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -62139,10 +62164,10 @@
         <v>1189</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>6852</v>
+        <v>6847</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>6853</v>
+        <v>6848</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -62150,10 +62175,10 @@
         <v>1190</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>6852</v>
+        <v>6847</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>6853</v>
+        <v>6848</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -62161,10 +62186,10 @@
         <v>1192</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>6852</v>
+        <v>6847</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>6853</v>
+        <v>6848</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -62172,10 +62197,10 @@
         <v>1193</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>6852</v>
+        <v>6847</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>6853</v>
+        <v>6848</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -62183,10 +62208,10 @@
         <v>1194</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>6852</v>
+        <v>6847</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>6853</v>
+        <v>6848</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -62194,10 +62219,10 @@
         <v>1195</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>6852</v>
+        <v>6847</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>6853</v>
+        <v>6848</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -62205,10 +62230,10 @@
         <v>1250</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>6852</v>
+        <v>6847</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>6853</v>
+        <v>6848</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -62216,10 +62241,10 @@
         <v>320</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>6854</v>
+        <v>6849</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>6855</v>
+        <v>6850</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -62227,10 +62252,10 @@
         <v>826</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>6854</v>
+        <v>6849</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>6855</v>
+        <v>6850</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -62238,10 +62263,10 @@
         <v>861</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>6854</v>
+        <v>6849</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>6855</v>
+        <v>6850</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -62249,10 +62274,10 @@
         <v>876</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>6854</v>
+        <v>6849</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>6855</v>
+        <v>6850</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -62260,10 +62285,10 @@
         <v>878</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>6854</v>
+        <v>6849</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>6855</v>
+        <v>6850</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -62271,10 +62296,10 @@
         <v>955</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>6854</v>
+        <v>6849</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>6855</v>
+        <v>6850</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -62282,10 +62307,10 @@
         <v>1064</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>6854</v>
+        <v>6849</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>6855</v>
+        <v>6850</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -62293,10 +62318,10 @@
         <v>1069</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>6854</v>
+        <v>6849</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>6855</v>
+        <v>6850</v>
       </c>
     </row>
   </sheetData>
@@ -62315,22 +62340,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="2" t="s">
-        <v>6856</v>
+        <v>6851</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="30.9">
       <c r="A2" s="2" t="s">
-        <v>6857</v>
+        <v>6852</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="30.9">
       <c r="A3" s="2" t="s">
-        <v>6858</v>
+        <v>6853</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="2" t="s">
-        <v>6859</v>
+        <v>6854</v>
       </c>
     </row>
   </sheetData>

--- a/salf/丙種職業安全衛生業務主管題庫.xlsx
+++ b/salf/丙種職業安全衛生業務主管題庫.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25f5a1833553ad9e/文件/GitHub/drher.github.io/salf/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\drher\OneDrive\文件\GitHub\drher.github.io\salf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="116" documentId="13_ncr:1_{60500821-8D89-4C6B-AF3B-12226DB870A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7BEB9631-A12D-4473-9A16-E38F78801B71}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E545FC3-85A4-41E9-8FD9-63F8EFFB672E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9463" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="15397" windowHeight="8751" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="乾淨題庫" sheetId="1" r:id="rId1"/>
@@ -17862,9 +17862,6 @@
     <t>正確答案為第4項：「叨音。」。本題重點在於理解題幹所涉及的職業安全衛生管理、危害預防或法規要求。</t>
   </si>
   <si>
-    <t>. 下列何者屬於噪音危害預防之工程改善項目 ?</t>
-  </si>
-  <si>
     <t>減少暴露時間</t>
   </si>
   <si>
@@ -20050,21 +20047,6 @@
   </si>
   <si>
     <t>勞工發生職業災害, 雇主應負無過失責任之職業災害補償, 另依職業災害勞工保護法之規定, 如涉及損害賠償時, 過失之舉證責任為下列何者 ?</t>
-  </si>
-  <si>
-    <t>. 依職業災害勞工保資料向下列何單位機構</t>
-  </si>
-  <si>
-    <t>代行檢查機構。法之規定, 勞工或雇主對於職業疾病診斷有異議時, 得檢附相關定 ?</t>
-  </si>
-  <si>
-    <t>直轄市、縣 (市) 主勞機關</t>
-  </si>
-  <si>
-    <t>中岩主菅機關</t>
-  </si>
-  <si>
-    <t>勞動檢查</t>
   </si>
   <si>
     <t>正確答案為第1項：「代行檢查機構。法之規定, 勞工或雇主對於職業疾病診斷有異議時, 得檢附相關定 ?」。本題重點在於理解題幹所涉及的職業安全衛生管理、危害預防或法規要求。</t>
@@ -21238,6 +21220,31 @@
   </si>
   <si>
     <t>吵雜的環境。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>下列何者屬於噪音危害預防之工程改善項目 ?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>依職業災害勞工保護法之規定，勞工或雇主對於職業疾病診斷有異議時，得檢附相關資料向下列何單位申請認定？</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">直轄市、縣(市)主管機關
+</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>中央主管機關</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>勞動檢查機構</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>代行檢查機構。</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -21342,10 +21349,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -22343,10 +22346,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>6898</v>
+        <v>6892</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>6899</v>
+        <v>6893</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>136</v>
@@ -23499,7 +23502,7 @@
         <v>64</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>6964</v>
+        <v>6958</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>352</v>
@@ -23534,7 +23537,7 @@
         <v>358</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>6965</v>
+        <v>6959</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>353</v>
@@ -23673,13 +23676,13 @@
         <v>70</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>6825</v>
+        <v>6819</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>383</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>6824</v>
+        <v>6818</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>384</v>
@@ -23702,7 +23705,7 @@
         <v>71</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>6914</v>
+        <v>6908</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>387</v>
@@ -23711,10 +23714,10 @@
         <v>388</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>6916</v>
+        <v>6910</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>6915</v>
+        <v>6909</v>
       </c>
       <c r="G72" s="3">
         <v>4</v>
@@ -24282,7 +24285,7 @@
         <v>91</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>6874</v>
+        <v>6868</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>491</v>
@@ -24294,7 +24297,7 @@
         <v>493</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>6875</v>
+        <v>6869</v>
       </c>
       <c r="G92" s="3">
         <v>4</v>
@@ -24568,7 +24571,7 @@
         <v>101</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>6851</v>
+        <v>6845</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>545</v>
@@ -24577,10 +24580,10 @@
         <v>546</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>6852</v>
+        <v>6846</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>6853</v>
+        <v>6847</v>
       </c>
       <c r="G102" s="3">
         <v>1</v>
@@ -25465,7 +25468,7 @@
         <v>132</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>6881</v>
+        <v>6875</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>353</v>
@@ -25474,10 +25477,10 @@
         <v>691</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>6882</v>
+        <v>6876</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>6883</v>
+        <v>6877</v>
       </c>
       <c r="G133" s="3">
         <v>3</v>
@@ -26231,7 +26234,7 @@
         <v>817</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>6892</v>
+        <v>6886</v>
       </c>
       <c r="G159" s="3">
         <v>3</v>
@@ -26703,7 +26706,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="176" spans="1:9" ht="61.75">
+    <row r="176" spans="1:9" ht="46.3">
       <c r="A176" s="2">
         <v>175</v>
       </c>
@@ -26795,7 +26798,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>6931</v>
+        <v>6925</v>
       </c>
       <c r="C179" s="2" t="s">
         <v>898</v>
@@ -27611,13 +27614,13 @@
         <v>1062</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>6810</v>
+        <v>6804</v>
       </c>
       <c r="E207" s="2" t="s">
-        <v>6811</v>
+        <v>6805</v>
       </c>
       <c r="F207" s="2" t="s">
-        <v>6812</v>
+        <v>6806</v>
       </c>
       <c r="G207" s="3">
         <v>2</v>
@@ -29432,7 +29435,7 @@
         <v>269</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>6833</v>
+        <v>6827</v>
       </c>
       <c r="C270" s="2" t="s">
         <v>1398</v>
@@ -30737,7 +30740,7 @@
         <v>314</v>
       </c>
       <c r="B315" s="2" t="s">
-        <v>6884</v>
+        <v>6878</v>
       </c>
       <c r="C315" s="2" t="s">
         <v>1643</v>
@@ -31120,13 +31123,13 @@
         <v>1716</v>
       </c>
       <c r="D328" s="2" t="s">
-        <v>6966</v>
+        <v>6960</v>
       </c>
       <c r="E328" s="2" t="s">
         <v>1718</v>
       </c>
       <c r="F328" s="2" t="s">
-        <v>6967</v>
+        <v>6961</v>
       </c>
       <c r="G328" s="3">
         <v>4</v>
@@ -31254,7 +31257,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="333" spans="1:9" ht="46.3">
+    <row r="333" spans="1:9" ht="30.9">
       <c r="A333" s="2">
         <v>332</v>
       </c>
@@ -31375,19 +31378,19 @@
         <v>336</v>
       </c>
       <c r="B337" s="2" t="s">
-        <v>6871</v>
+        <v>6865</v>
       </c>
       <c r="C337" s="2" t="s">
         <v>1765</v>
       </c>
       <c r="D337" s="2" t="s">
-        <v>6872</v>
+        <v>6866</v>
       </c>
       <c r="E337" s="2" t="s">
         <v>731</v>
       </c>
       <c r="F337" s="2" t="s">
-        <v>6873</v>
+        <v>6867</v>
       </c>
       <c r="G337" s="3">
         <v>4</v>
@@ -31579,7 +31582,7 @@
         <v>1800</v>
       </c>
       <c r="C344" s="2" t="s">
-        <v>6879</v>
+        <v>6873</v>
       </c>
       <c r="D344" s="2" t="s">
         <v>1795</v>
@@ -31588,7 +31591,7 @@
         <v>1796</v>
       </c>
       <c r="F344" s="2" t="s">
-        <v>6880</v>
+        <v>6874</v>
       </c>
       <c r="G344" s="3">
         <v>1</v>
@@ -33403,16 +33406,16 @@
         <v>406</v>
       </c>
       <c r="B407" s="2" t="s">
-        <v>6895</v>
+        <v>6889</v>
       </c>
       <c r="C407" s="2" t="s">
-        <v>6897</v>
+        <v>6891</v>
       </c>
       <c r="D407" s="2" t="s">
         <v>2155</v>
       </c>
       <c r="E407" s="2" t="s">
-        <v>6896</v>
+        <v>6890</v>
       </c>
       <c r="F407" s="2" t="s">
         <v>2156</v>
@@ -34211,7 +34214,7 @@
         <v>434</v>
       </c>
       <c r="B435" s="2" t="s">
-        <v>6906</v>
+        <v>6900</v>
       </c>
       <c r="C435" s="2" t="s">
         <v>2294</v>
@@ -34223,7 +34226,7 @@
         <v>2296</v>
       </c>
       <c r="F435" s="2" t="s">
-        <v>6907</v>
+        <v>6901</v>
       </c>
       <c r="G435" s="3">
         <v>1</v>
@@ -34740,10 +34743,10 @@
         <v>2375</v>
       </c>
       <c r="E453" s="2" t="s">
-        <v>6921</v>
+        <v>6915</v>
       </c>
       <c r="F453" s="2" t="s">
-        <v>6920</v>
+        <v>6914</v>
       </c>
       <c r="G453" s="3">
         <v>1</v>
@@ -34760,7 +34763,7 @@
         <v>453</v>
       </c>
       <c r="B454" s="2" t="s">
-        <v>6917</v>
+        <v>6911</v>
       </c>
       <c r="C454" s="2" t="s">
         <v>1440</v>
@@ -34769,10 +34772,10 @@
         <v>1422</v>
       </c>
       <c r="E454" s="2" t="s">
-        <v>6919</v>
+        <v>6913</v>
       </c>
       <c r="F454" s="2" t="s">
-        <v>6918</v>
+        <v>6912</v>
       </c>
       <c r="G454" s="3">
         <v>4</v>
@@ -35766,7 +35769,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="489" spans="1:9" ht="46.3">
+    <row r="489" spans="1:9" ht="30.9">
       <c r="A489" s="2">
         <v>488</v>
       </c>
@@ -36206,19 +36209,19 @@
         <v>503</v>
       </c>
       <c r="B504" s="2" t="s">
-        <v>6968</v>
+        <v>6962</v>
       </c>
       <c r="C504" s="2" t="s">
-        <v>6969</v>
+        <v>6963</v>
       </c>
       <c r="D504" s="2" t="s">
         <v>2624</v>
       </c>
       <c r="E504" s="2" t="s">
-        <v>6970</v>
+        <v>6964</v>
       </c>
       <c r="F504" s="2" t="s">
-        <v>6971</v>
+        <v>6965</v>
       </c>
       <c r="G504" s="3">
         <v>4</v>
@@ -37177,7 +37180,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="538" spans="1:9" ht="46.3">
+    <row r="538" spans="1:9" ht="30.9">
       <c r="A538" s="2">
         <v>537</v>
       </c>
@@ -37691,7 +37694,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="556" spans="1:9" ht="46.3">
+    <row r="556" spans="1:9" ht="30.9">
       <c r="A556" s="2">
         <v>555</v>
       </c>
@@ -37725,13 +37728,13 @@
         <v>556</v>
       </c>
       <c r="B557" s="2" t="s">
-        <v>6816</v>
+        <v>6810</v>
       </c>
       <c r="C557" s="2" t="s">
-        <v>6817</v>
+        <v>6811</v>
       </c>
       <c r="D557" s="2" t="s">
-        <v>6818</v>
+        <v>6812</v>
       </c>
       <c r="E557" s="2" t="s">
         <v>2880</v>
@@ -38158,19 +38161,19 @@
         <v>571</v>
       </c>
       <c r="B572" s="2" t="s">
-        <v>6940</v>
+        <v>6934</v>
       </c>
       <c r="C572" s="2" t="s">
-        <v>6941</v>
+        <v>6935</v>
       </c>
       <c r="D572" s="2" t="s">
-        <v>6942</v>
+        <v>6936</v>
       </c>
       <c r="E572" s="2" t="s">
-        <v>6944</v>
+        <v>6938</v>
       </c>
       <c r="F572" s="2" t="s">
-        <v>6943</v>
+        <v>6937</v>
       </c>
       <c r="G572" s="3">
         <v>4</v>
@@ -38187,19 +38190,19 @@
         <v>572</v>
       </c>
       <c r="B573" s="2" t="s">
-        <v>6945</v>
+        <v>6939</v>
       </c>
       <c r="C573" s="2" t="s">
-        <v>6944</v>
+        <v>6938</v>
       </c>
       <c r="D573" s="2" t="s">
-        <v>6943</v>
+        <v>6937</v>
       </c>
       <c r="E573" s="2" t="s">
-        <v>6941</v>
+        <v>6935</v>
       </c>
       <c r="F573" s="2" t="s">
-        <v>6942</v>
+        <v>6936</v>
       </c>
       <c r="G573" s="3">
         <v>4</v>
@@ -38216,19 +38219,19 @@
         <v>573</v>
       </c>
       <c r="B574" s="2" t="s">
-        <v>6946</v>
+        <v>6940</v>
       </c>
       <c r="C574" s="2" t="s">
-        <v>6943</v>
+        <v>6937</v>
       </c>
       <c r="D574" s="2" t="s">
-        <v>6947</v>
+        <v>6941</v>
       </c>
       <c r="E574" s="2" t="s">
-        <v>6948</v>
+        <v>6942</v>
       </c>
       <c r="F574" s="2" t="s">
-        <v>6944</v>
+        <v>6938</v>
       </c>
       <c r="G574" s="3">
         <v>2</v>
@@ -38251,7 +38254,7 @@
         <v>2962</v>
       </c>
       <c r="D575" s="2" t="s">
-        <v>6949</v>
+        <v>6943</v>
       </c>
       <c r="E575" s="2" t="s">
         <v>2963</v>
@@ -38303,19 +38306,19 @@
         <v>576</v>
       </c>
       <c r="B577" s="2" t="s">
-        <v>6955</v>
+        <v>6949</v>
       </c>
       <c r="C577" s="2" t="s">
-        <v>6959</v>
+        <v>6953</v>
       </c>
       <c r="D577" s="2" t="s">
-        <v>6956</v>
+        <v>6950</v>
       </c>
       <c r="E577" s="2" t="s">
-        <v>6957</v>
+        <v>6951</v>
       </c>
       <c r="F577" s="2" t="s">
-        <v>6958</v>
+        <v>6952</v>
       </c>
       <c r="G577" s="3">
         <v>3</v>
@@ -38332,19 +38335,19 @@
         <v>577</v>
       </c>
       <c r="B578" s="6" t="s">
-        <v>6950</v>
+        <v>6944</v>
       </c>
       <c r="C578" s="2" t="s">
-        <v>6951</v>
+        <v>6945</v>
       </c>
       <c r="D578" s="2" t="s">
-        <v>6952</v>
+        <v>6946</v>
       </c>
       <c r="E578" s="2" t="s">
-        <v>6954</v>
+        <v>6948</v>
       </c>
       <c r="F578" s="2" t="s">
-        <v>6953</v>
+        <v>6947</v>
       </c>
       <c r="G578" s="3">
         <v>1</v>
@@ -38361,16 +38364,16 @@
         <v>578</v>
       </c>
       <c r="B579" s="2" t="s">
-        <v>6960</v>
+        <v>6954</v>
       </c>
       <c r="C579" s="2" t="s">
-        <v>6961</v>
+        <v>6955</v>
       </c>
       <c r="D579" s="2" t="s">
-        <v>6962</v>
+        <v>6956</v>
       </c>
       <c r="E579" s="2" t="s">
-        <v>6963</v>
+        <v>6957</v>
       </c>
       <c r="F579" s="2" t="s">
         <v>2972</v>
@@ -39426,7 +39429,7 @@
         <v>615</v>
       </c>
       <c r="B616" s="2" t="s">
-        <v>6845</v>
+        <v>6839</v>
       </c>
       <c r="C616" s="2" t="s">
         <v>3154</v>
@@ -39542,7 +39545,7 @@
         <v>619</v>
       </c>
       <c r="B620" s="2" t="s">
-        <v>6908</v>
+        <v>6902</v>
       </c>
       <c r="C620" s="2" t="s">
         <v>3175</v>
@@ -39554,7 +39557,7 @@
         <v>3177</v>
       </c>
       <c r="F620" s="2" t="s">
-        <v>6909</v>
+        <v>6903</v>
       </c>
       <c r="G620" s="3">
         <v>4</v>
@@ -40126,7 +40129,7 @@
         <v>3282</v>
       </c>
       <c r="F640" s="2" t="s">
-        <v>6823</v>
+        <v>6817</v>
       </c>
       <c r="G640" s="3">
         <v>2</v>
@@ -40433,7 +40436,7 @@
         <v>650</v>
       </c>
       <c r="B651" s="2" t="s">
-        <v>6856</v>
+        <v>6850</v>
       </c>
       <c r="C651" s="2" t="s">
         <v>3335</v>
@@ -40442,10 +40445,10 @@
         <v>3336</v>
       </c>
       <c r="E651" s="2" t="s">
-        <v>6857</v>
+        <v>6851</v>
       </c>
       <c r="F651" s="2" t="s">
-        <v>6858</v>
+        <v>6852</v>
       </c>
       <c r="G651" s="3">
         <v>2</v>
@@ -40491,7 +40494,7 @@
         <v>652</v>
       </c>
       <c r="B653" s="2" t="s">
-        <v>6904</v>
+        <v>6898</v>
       </c>
       <c r="C653" s="2" t="s">
         <v>1542</v>
@@ -40503,7 +40506,7 @@
         <v>3345</v>
       </c>
       <c r="F653" s="2" t="s">
-        <v>6905</v>
+        <v>6899</v>
       </c>
       <c r="G653" s="3">
         <v>1</v>
@@ -41646,7 +41649,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="693" spans="1:9" ht="123.45">
+    <row r="693" spans="1:9" ht="108">
       <c r="A693" s="2">
         <v>692</v>
       </c>
@@ -42401,7 +42404,7 @@
         <v>718</v>
       </c>
       <c r="B719" s="2" t="s">
-        <v>6932</v>
+        <v>6926</v>
       </c>
       <c r="C719" s="2" t="s">
         <v>712</v>
@@ -43063,13 +43066,13 @@
         <v>3756</v>
       </c>
       <c r="C742" s="2" t="s">
-        <v>6813</v>
+        <v>6807</v>
       </c>
       <c r="D742" s="2" t="s">
         <v>3757</v>
       </c>
       <c r="E742" s="2" t="s">
-        <v>6814</v>
+        <v>6808</v>
       </c>
       <c r="F742" s="2" t="s">
         <v>51</v>
@@ -43464,25 +43467,25 @@
         <v>755</v>
       </c>
       <c r="B756" s="2" t="s">
-        <v>6834</v>
+        <v>6828</v>
       </c>
       <c r="C756" s="2" t="s">
-        <v>6835</v>
+        <v>6829</v>
       </c>
       <c r="D756" s="2" t="s">
-        <v>6836</v>
+        <v>6830</v>
       </c>
       <c r="E756" s="2" t="s">
-        <v>6837</v>
+        <v>6831</v>
       </c>
       <c r="F756" s="2" t="s">
-        <v>6838</v>
+        <v>6832</v>
       </c>
       <c r="G756" s="3">
         <v>2</v>
       </c>
       <c r="H756" s="2" t="s">
-        <v>6839</v>
+        <v>6833</v>
       </c>
       <c r="I756" s="2" t="s">
         <v>801</v>
@@ -44037,7 +44040,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="776" spans="1:9" ht="46.3">
+    <row r="776" spans="1:9" ht="30.9">
       <c r="A776" s="2">
         <v>775</v>
       </c>
@@ -44883,7 +44886,7 @@
         <v>804</v>
       </c>
       <c r="B805" s="2" t="s">
-        <v>6973</v>
+        <v>6967</v>
       </c>
       <c r="C805" s="2" t="s">
         <v>4035</v>
@@ -45115,13 +45118,13 @@
         <v>812</v>
       </c>
       <c r="B813" s="2" t="s">
-        <v>6902</v>
+        <v>6896</v>
       </c>
       <c r="C813" s="2" t="s">
         <v>4077</v>
       </c>
       <c r="D813" s="2" t="s">
-        <v>6903</v>
+        <v>6897</v>
       </c>
       <c r="E813" s="2" t="s">
         <v>4078</v>
@@ -45173,7 +45176,7 @@
         <v>814</v>
       </c>
       <c r="B815" s="2" t="s">
-        <v>6900</v>
+        <v>6894</v>
       </c>
       <c r="C815" s="2" t="s">
         <v>4087</v>
@@ -45185,7 +45188,7 @@
         <v>4089</v>
       </c>
       <c r="F815" s="2" t="s">
-        <v>6901</v>
+        <v>6895</v>
       </c>
       <c r="G815" s="3">
         <v>1</v>
@@ -45579,7 +45582,7 @@
         <v>828</v>
       </c>
       <c r="B829" s="2" t="s">
-        <v>6972</v>
+        <v>6966</v>
       </c>
       <c r="C829" s="2" t="s">
         <v>4156</v>
@@ -45667,16 +45670,16 @@
         <v>4172</v>
       </c>
       <c r="C832" s="2" t="s">
-        <v>6936</v>
+        <v>6930</v>
       </c>
       <c r="D832" s="2" t="s">
-        <v>6937</v>
+        <v>6931</v>
       </c>
       <c r="E832" s="2" t="s">
-        <v>6938</v>
+        <v>6932</v>
       </c>
       <c r="F832" s="2" t="s">
-        <v>6939</v>
+        <v>6933</v>
       </c>
       <c r="G832" s="3">
         <v>4</v>
@@ -46619,7 +46622,7 @@
         <v>864</v>
       </c>
       <c r="B865" s="2" t="s">
-        <v>6861</v>
+        <v>6855</v>
       </c>
       <c r="C865" s="2" t="s">
         <v>4336</v>
@@ -46628,10 +46631,10 @@
         <v>3076</v>
       </c>
       <c r="E865" s="2" t="s">
-        <v>6859</v>
+        <v>6853</v>
       </c>
       <c r="F865" s="2" t="s">
-        <v>6860</v>
+        <v>6854</v>
       </c>
       <c r="G865" s="3">
         <v>4</v>
@@ -46648,19 +46651,19 @@
         <v>865</v>
       </c>
       <c r="B866" s="2" t="s">
-        <v>6866</v>
+        <v>6860</v>
       </c>
       <c r="C866" s="2" t="s">
-        <v>6867</v>
+        <v>6861</v>
       </c>
       <c r="D866" s="5" t="s">
-        <v>6868</v>
+        <v>6862</v>
       </c>
       <c r="E866" s="2" t="s">
-        <v>6869</v>
+        <v>6863</v>
       </c>
       <c r="F866" s="2" t="s">
-        <v>6870</v>
+        <v>6864</v>
       </c>
       <c r="G866" s="3">
         <v>3</v>
@@ -47084,7 +47087,7 @@
         <v>4415</v>
       </c>
       <c r="C881" s="2" t="s">
-        <v>6821</v>
+        <v>6815</v>
       </c>
       <c r="D881" s="2" t="s">
         <v>3076</v>
@@ -47093,7 +47096,7 @@
         <v>4416</v>
       </c>
       <c r="F881" s="2" t="s">
-        <v>6822</v>
+        <v>6816</v>
       </c>
       <c r="G881" s="3">
         <v>1</v>
@@ -47545,16 +47548,16 @@
         <v>896</v>
       </c>
       <c r="B897" s="2" t="s">
-        <v>6827</v>
+        <v>6821</v>
       </c>
       <c r="C897" s="2" t="s">
         <v>4200</v>
       </c>
       <c r="D897" s="2" t="s">
-        <v>6828</v>
+        <v>6822</v>
       </c>
       <c r="E897" s="2" t="s">
-        <v>6829</v>
+        <v>6823</v>
       </c>
       <c r="F897" s="2" t="s">
         <v>4289</v>
@@ -48034,19 +48037,19 @@
         <v>913</v>
       </c>
       <c r="B914" s="2" t="s">
-        <v>6974</v>
+        <v>6968</v>
       </c>
       <c r="C914" s="2" t="s">
-        <v>6975</v>
+        <v>6969</v>
       </c>
       <c r="D914" s="2" t="s">
         <v>4585</v>
       </c>
       <c r="E914" s="2" t="s">
-        <v>6976</v>
+        <v>6970</v>
       </c>
       <c r="F914" s="2" t="s">
-        <v>6977</v>
+        <v>6971</v>
       </c>
       <c r="G914" s="3">
         <v>3</v>
@@ -48318,7 +48321,7 @@
         <v>923</v>
       </c>
       <c r="B924" s="2" t="s">
-        <v>6826</v>
+        <v>6820</v>
       </c>
       <c r="C924" s="2" t="s">
         <v>3120</v>
@@ -49165,7 +49168,7 @@
         <v>4779</v>
       </c>
       <c r="F953" s="2" t="s">
-        <v>6815</v>
+        <v>6809</v>
       </c>
       <c r="G953" s="3">
         <v>3</v>
@@ -49957,19 +49960,19 @@
         <v>980</v>
       </c>
       <c r="B981" s="2" t="s">
-        <v>6885</v>
+        <v>6879</v>
       </c>
       <c r="C981" s="2" t="s">
-        <v>6887</v>
+        <v>6881</v>
       </c>
       <c r="D981" s="2" t="s">
-        <v>6888</v>
+        <v>6882</v>
       </c>
       <c r="E981" s="2" t="s">
         <v>4923</v>
       </c>
       <c r="F981" s="2" t="s">
-        <v>6886</v>
+        <v>6880</v>
       </c>
       <c r="G981" s="3">
         <v>2</v>
@@ -50189,19 +50192,19 @@
         <v>988</v>
       </c>
       <c r="B989" s="2" t="s">
-        <v>6846</v>
+        <v>6840</v>
       </c>
       <c r="C989" s="2" t="s">
-        <v>6847</v>
+        <v>6841</v>
       </c>
       <c r="D989" s="2" t="s">
-        <v>6848</v>
+        <v>6842</v>
       </c>
       <c r="E989" s="2" t="s">
-        <v>6849</v>
+        <v>6843</v>
       </c>
       <c r="F989" s="2" t="s">
-        <v>6850</v>
+        <v>6844</v>
       </c>
       <c r="G989" s="3">
         <v>3</v>
@@ -50971,16 +50974,16 @@
         <v>5066</v>
       </c>
       <c r="C1016" s="2" t="s">
-        <v>6978</v>
+        <v>6972</v>
       </c>
       <c r="D1016" s="2" t="s">
-        <v>6979</v>
+        <v>6973</v>
       </c>
       <c r="E1016" s="2" t="s">
         <v>5067</v>
       </c>
       <c r="F1016" s="2" t="s">
-        <v>6980</v>
+        <v>6974</v>
       </c>
       <c r="G1016" s="3">
         <v>1</v>
@@ -50997,7 +51000,7 @@
         <v>1016</v>
       </c>
       <c r="B1017" s="2" t="s">
-        <v>6981</v>
+        <v>6975</v>
       </c>
       <c r="C1017" s="2" t="s">
         <v>5069</v>
@@ -51258,7 +51261,7 @@
         <v>1025</v>
       </c>
       <c r="B1026" s="2" t="s">
-        <v>6889</v>
+        <v>6883</v>
       </c>
       <c r="C1026" s="2" t="s">
         <v>5111</v>
@@ -51267,10 +51270,10 @@
         <v>998</v>
       </c>
       <c r="E1026" s="2" t="s">
-        <v>6890</v>
+        <v>6884</v>
       </c>
       <c r="F1026" s="2" t="s">
-        <v>6891</v>
+        <v>6885</v>
       </c>
       <c r="G1026" s="3">
         <v>1</v>
@@ -51635,7 +51638,7 @@
         <v>1038</v>
       </c>
       <c r="B1039" s="2" t="s">
-        <v>6984</v>
+        <v>6978</v>
       </c>
       <c r="C1039" s="2" t="s">
         <v>5178</v>
@@ -51644,10 +51647,10 @@
         <v>5179</v>
       </c>
       <c r="E1039" s="2" t="s">
-        <v>6982</v>
+        <v>6976</v>
       </c>
       <c r="F1039" s="2" t="s">
-        <v>6983</v>
+        <v>6977</v>
       </c>
       <c r="G1039" s="3">
         <v>2</v>
@@ -51664,19 +51667,19 @@
         <v>1039</v>
       </c>
       <c r="B1040" s="2" t="s">
-        <v>6840</v>
+        <v>6834</v>
       </c>
       <c r="C1040" s="2" t="s">
-        <v>6841</v>
+        <v>6835</v>
       </c>
       <c r="D1040" s="2" t="s">
-        <v>6842</v>
+        <v>6836</v>
       </c>
       <c r="E1040" s="2" t="s">
-        <v>6843</v>
+        <v>6837</v>
       </c>
       <c r="F1040" s="2" t="s">
-        <v>6844</v>
+        <v>6838</v>
       </c>
       <c r="G1040" s="3">
         <v>4</v>
@@ -52903,7 +52906,7 @@
         <v>1082</v>
       </c>
       <c r="B1083" s="2" t="s">
-        <v>6985</v>
+        <v>6979</v>
       </c>
       <c r="C1083" s="2" t="s">
         <v>5393</v>
@@ -53927,10 +53930,10 @@
         <v>5559</v>
       </c>
       <c r="E1118" s="2" t="s">
-        <v>6820</v>
+        <v>6814</v>
       </c>
       <c r="F1118" s="2" t="s">
-        <v>6819</v>
+        <v>6813</v>
       </c>
       <c r="G1118" s="3">
         <v>4</v>
@@ -55736,10 +55739,10 @@
         <v>1181</v>
       </c>
       <c r="B1182" s="2" t="s">
-        <v>6933</v>
+        <v>6927</v>
       </c>
       <c r="C1182" s="2" t="s">
-        <v>6934</v>
+        <v>6928</v>
       </c>
       <c r="D1182" s="2" t="s">
         <v>5852</v>
@@ -55748,7 +55751,7 @@
         <v>1823</v>
       </c>
       <c r="F1182" s="2" t="s">
-        <v>6935</v>
+        <v>6929</v>
       </c>
       <c r="G1182" s="3">
         <v>4</v>
@@ -55794,7 +55797,7 @@
         <v>1183</v>
       </c>
       <c r="B1184" s="2" t="s">
-        <v>6986</v>
+        <v>6980</v>
       </c>
       <c r="C1184" s="2" t="s">
         <v>4367</v>
@@ -56572,7 +56575,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="1211" spans="1:9" ht="46.3">
+    <row r="1211" spans="1:9" ht="30.9">
       <c r="A1211" s="2">
         <v>1210</v>
       </c>
@@ -56635,25 +56638,25 @@
         <v>1212</v>
       </c>
       <c r="B1213" s="2" t="s">
+        <v>6983</v>
+      </c>
+      <c r="C1213" s="2" t="s">
         <v>5945</v>
       </c>
-      <c r="C1213" s="2" t="s">
+      <c r="D1213" s="2" t="s">
         <v>5946</v>
       </c>
-      <c r="D1213" s="2" t="s">
+      <c r="E1213" s="2" t="s">
         <v>5947</v>
       </c>
-      <c r="E1213" s="2" t="s">
+      <c r="F1213" s="2" t="s">
         <v>5948</v>
-      </c>
-      <c r="F1213" s="2" t="s">
-        <v>5949</v>
       </c>
       <c r="G1213" s="3">
         <v>4</v>
       </c>
       <c r="H1213" s="2" t="s">
-        <v>5950</v>
+        <v>5949</v>
       </c>
       <c r="I1213" s="2" t="s">
         <v>158</v>
@@ -56664,10 +56667,10 @@
         <v>1213</v>
       </c>
       <c r="B1214" s="2" t="s">
+        <v>5950</v>
+      </c>
+      <c r="C1214" s="2" t="s">
         <v>5951</v>
-      </c>
-      <c r="C1214" s="2" t="s">
-        <v>5952</v>
       </c>
       <c r="D1214" s="2" t="s">
         <v>5219</v>
@@ -56676,13 +56679,13 @@
         <v>3078</v>
       </c>
       <c r="F1214" s="2" t="s">
-        <v>5953</v>
+        <v>5952</v>
       </c>
       <c r="G1214" s="3">
         <v>1</v>
       </c>
       <c r="H1214" s="2" t="s">
-        <v>5954</v>
+        <v>5953</v>
       </c>
       <c r="I1214" s="2" t="s">
         <v>15</v>
@@ -56693,25 +56696,25 @@
         <v>1214</v>
       </c>
       <c r="B1215" s="2" t="s">
+        <v>5954</v>
+      </c>
+      <c r="C1215" s="2" t="s">
         <v>5955</v>
       </c>
-      <c r="C1215" s="2" t="s">
+      <c r="D1215" s="2" t="s">
+        <v>6981</v>
+      </c>
+      <c r="E1215" s="2" t="s">
         <v>5956</v>
       </c>
-      <c r="D1215" s="2" t="s">
-        <v>6987</v>
-      </c>
-      <c r="E1215" s="2" t="s">
-        <v>5957</v>
-      </c>
       <c r="F1215" s="2" t="s">
-        <v>6988</v>
+        <v>6982</v>
       </c>
       <c r="G1215" s="3">
         <v>4</v>
       </c>
       <c r="H1215" s="2" t="s">
-        <v>5958</v>
+        <v>5957</v>
       </c>
       <c r="I1215" s="2" t="s">
         <v>15</v>
@@ -56722,25 +56725,25 @@
         <v>1215</v>
       </c>
       <c r="B1216" s="2" t="s">
-        <v>5959</v>
+        <v>5958</v>
       </c>
       <c r="C1216" s="2" t="s">
         <v>3344</v>
       </c>
       <c r="D1216" s="2" t="s">
-        <v>5960</v>
+        <v>5959</v>
       </c>
       <c r="E1216" s="2" t="s">
         <v>1542</v>
       </c>
       <c r="F1216" s="2" t="s">
-        <v>5961</v>
+        <v>5960</v>
       </c>
       <c r="G1216" s="3">
         <v>2</v>
       </c>
       <c r="H1216" s="2" t="s">
-        <v>5962</v>
+        <v>5961</v>
       </c>
       <c r="I1216" s="2" t="s">
         <v>15</v>
@@ -56751,7 +56754,7 @@
         <v>1216</v>
       </c>
       <c r="B1217" s="2" t="s">
-        <v>5963</v>
+        <v>5962</v>
       </c>
       <c r="C1217" s="2" t="s">
         <v>3344</v>
@@ -56769,7 +56772,7 @@
         <v>4</v>
       </c>
       <c r="H1217" s="2" t="s">
-        <v>5964</v>
+        <v>5963</v>
       </c>
       <c r="I1217" s="2" t="s">
         <v>15</v>
@@ -56780,25 +56783,25 @@
         <v>1217</v>
       </c>
       <c r="B1218" s="2" t="s">
+        <v>5964</v>
+      </c>
+      <c r="C1218" s="2" t="s">
         <v>5965</v>
       </c>
-      <c r="C1218" s="2" t="s">
+      <c r="D1218" s="2" t="s">
         <v>5966</v>
       </c>
-      <c r="D1218" s="2" t="s">
+      <c r="E1218" s="2" t="s">
         <v>5967</v>
       </c>
-      <c r="E1218" s="2" t="s">
+      <c r="F1218" s="2" t="s">
         <v>5968</v>
-      </c>
-      <c r="F1218" s="2" t="s">
-        <v>5969</v>
       </c>
       <c r="G1218" s="3">
         <v>2</v>
       </c>
       <c r="H1218" s="2" t="s">
-        <v>5970</v>
+        <v>5969</v>
       </c>
       <c r="I1218" s="2" t="s">
         <v>15</v>
@@ -56809,25 +56812,25 @@
         <v>1218</v>
       </c>
       <c r="B1219" s="2" t="s">
+        <v>5970</v>
+      </c>
+      <c r="C1219" s="2" t="s">
         <v>5971</v>
       </c>
-      <c r="C1219" s="2" t="s">
+      <c r="D1219" s="2" t="s">
         <v>5972</v>
       </c>
-      <c r="D1219" s="2" t="s">
+      <c r="E1219" s="2" t="s">
         <v>5973</v>
       </c>
-      <c r="E1219" s="2" t="s">
+      <c r="F1219" s="2" t="s">
         <v>5974</v>
-      </c>
-      <c r="F1219" s="2" t="s">
-        <v>5975</v>
       </c>
       <c r="G1219" s="3">
         <v>2</v>
       </c>
       <c r="H1219" s="2" t="s">
-        <v>5976</v>
+        <v>5975</v>
       </c>
       <c r="I1219" s="2" t="s">
         <v>15</v>
@@ -56838,10 +56841,10 @@
         <v>1219</v>
       </c>
       <c r="B1220" s="2" t="s">
+        <v>5976</v>
+      </c>
+      <c r="C1220" s="2" t="s">
         <v>5977</v>
-      </c>
-      <c r="C1220" s="2" t="s">
-        <v>5978</v>
       </c>
       <c r="D1220" s="2" t="s">
         <v>5460</v>
@@ -56850,13 +56853,13 @@
         <v>5441</v>
       </c>
       <c r="F1220" s="2" t="s">
-        <v>5979</v>
+        <v>5978</v>
       </c>
       <c r="G1220" s="3">
         <v>3</v>
       </c>
       <c r="H1220" s="2" t="s">
-        <v>5980</v>
+        <v>5979</v>
       </c>
       <c r="I1220" s="2" t="s">
         <v>15</v>
@@ -56867,25 +56870,25 @@
         <v>1220</v>
       </c>
       <c r="B1221" s="2" t="s">
+        <v>5980</v>
+      </c>
+      <c r="C1221" s="2" t="s">
         <v>5981</v>
       </c>
-      <c r="C1221" s="2" t="s">
+      <c r="D1221" s="2" t="s">
         <v>5982</v>
       </c>
-      <c r="D1221" s="2" t="s">
+      <c r="E1221" s="2" t="s">
         <v>5983</v>
       </c>
-      <c r="E1221" s="2" t="s">
+      <c r="F1221" s="2" t="s">
         <v>5984</v>
-      </c>
-      <c r="F1221" s="2" t="s">
-        <v>5985</v>
       </c>
       <c r="G1221" s="3">
         <v>1</v>
       </c>
       <c r="H1221" s="2" t="s">
-        <v>5986</v>
+        <v>5985</v>
       </c>
       <c r="I1221" s="2" t="s">
         <v>15</v>
@@ -56896,25 +56899,25 @@
         <v>1221</v>
       </c>
       <c r="B1222" s="2" t="s">
+        <v>5986</v>
+      </c>
+      <c r="C1222" s="2" t="s">
         <v>5987</v>
-      </c>
-      <c r="C1222" s="2" t="s">
-        <v>5988</v>
       </c>
       <c r="D1222" s="2" t="s">
         <v>4395</v>
       </c>
       <c r="E1222" s="2" t="s">
+        <v>5988</v>
+      </c>
+      <c r="F1222" s="2" t="s">
         <v>5989</v>
-      </c>
-      <c r="F1222" s="2" t="s">
-        <v>5990</v>
       </c>
       <c r="G1222" s="3">
         <v>1</v>
       </c>
       <c r="H1222" s="2" t="s">
-        <v>5991</v>
+        <v>5990</v>
       </c>
       <c r="I1222" s="2" t="s">
         <v>15</v>
@@ -56925,25 +56928,25 @@
         <v>1222</v>
       </c>
       <c r="B1223" s="2" t="s">
+        <v>5991</v>
+      </c>
+      <c r="C1223" s="2" t="s">
         <v>5992</v>
       </c>
-      <c r="C1223" s="2" t="s">
+      <c r="D1223" s="2" t="s">
         <v>5993</v>
       </c>
-      <c r="D1223" s="2" t="s">
+      <c r="E1223" s="2" t="s">
         <v>5994</v>
       </c>
-      <c r="E1223" s="2" t="s">
+      <c r="F1223" s="2" t="s">
         <v>5995</v>
-      </c>
-      <c r="F1223" s="2" t="s">
-        <v>5996</v>
       </c>
       <c r="G1223" s="3">
         <v>4</v>
       </c>
       <c r="H1223" s="2" t="s">
-        <v>5997</v>
+        <v>5996</v>
       </c>
       <c r="I1223" s="2" t="s">
         <v>15</v>
@@ -56954,13 +56957,13 @@
         <v>1223</v>
       </c>
       <c r="B1224" s="2" t="s">
+        <v>5997</v>
+      </c>
+      <c r="C1224" s="2" t="s">
         <v>5998</v>
       </c>
-      <c r="C1224" s="2" t="s">
+      <c r="D1224" s="2" t="s">
         <v>5999</v>
-      </c>
-      <c r="D1224" s="2" t="s">
-        <v>6000</v>
       </c>
       <c r="E1224" s="2" t="s">
         <v>4677</v>
@@ -56972,7 +56975,7 @@
         <v>1</v>
       </c>
       <c r="H1224" s="2" t="s">
-        <v>6001</v>
+        <v>6000</v>
       </c>
       <c r="I1224" s="2" t="s">
         <v>15</v>
@@ -56983,10 +56986,10 @@
         <v>1224</v>
       </c>
       <c r="B1225" s="2" t="s">
+        <v>6001</v>
+      </c>
+      <c r="C1225" s="2" t="s">
         <v>6002</v>
-      </c>
-      <c r="C1225" s="2" t="s">
-        <v>6003</v>
       </c>
       <c r="D1225" s="2" t="s">
         <v>5247</v>
@@ -56995,13 +56998,13 @@
         <v>5500</v>
       </c>
       <c r="F1225" s="2" t="s">
-        <v>6004</v>
+        <v>6003</v>
       </c>
       <c r="G1225" s="3">
         <v>1</v>
       </c>
       <c r="H1225" s="2" t="s">
-        <v>6005</v>
+        <v>6004</v>
       </c>
       <c r="I1225" s="2" t="s">
         <v>15</v>
@@ -57012,19 +57015,19 @@
         <v>1225</v>
       </c>
       <c r="B1226" s="2" t="s">
-        <v>6006</v>
+        <v>6005</v>
       </c>
       <c r="C1226" s="2" t="s">
         <v>4199</v>
       </c>
       <c r="D1226" s="2" t="s">
-        <v>6007</v>
+        <v>6006</v>
       </c>
       <c r="E1226" s="2" t="s">
         <v>4327</v>
       </c>
       <c r="F1226" s="2" t="s">
-        <v>6008</v>
+        <v>6007</v>
       </c>
       <c r="G1226" s="3">
         <v>1</v>
@@ -57041,25 +57044,25 @@
         <v>1226</v>
       </c>
       <c r="B1227" s="2" t="s">
+        <v>6008</v>
+      </c>
+      <c r="C1227" s="2" t="s">
         <v>6009</v>
       </c>
-      <c r="C1227" s="2" t="s">
+      <c r="D1227" s="2" t="s">
         <v>6010</v>
       </c>
-      <c r="D1227" s="2" t="s">
+      <c r="E1227" s="2" t="s">
         <v>6011</v>
       </c>
-      <c r="E1227" s="2" t="s">
+      <c r="F1227" s="2" t="s">
         <v>6012</v>
-      </c>
-      <c r="F1227" s="2" t="s">
-        <v>6013</v>
       </c>
       <c r="G1227" s="3">
         <v>4</v>
       </c>
       <c r="H1227" s="2" t="s">
-        <v>6014</v>
+        <v>6013</v>
       </c>
       <c r="I1227" s="2" t="s">
         <v>15</v>
@@ -57070,25 +57073,25 @@
         <v>1227</v>
       </c>
       <c r="B1228" s="2" t="s">
-        <v>6830</v>
+        <v>6824</v>
       </c>
       <c r="C1228" s="2" t="s">
+        <v>6014</v>
+      </c>
+      <c r="D1228" s="2" t="s">
         <v>6015</v>
       </c>
-      <c r="D1228" s="2" t="s">
-        <v>6016</v>
-      </c>
       <c r="E1228" s="2" t="s">
-        <v>6831</v>
+        <v>6825</v>
       </c>
       <c r="F1228" s="2" t="s">
-        <v>6832</v>
+        <v>6826</v>
       </c>
       <c r="G1228" s="3">
         <v>4</v>
       </c>
       <c r="H1228" s="2" t="s">
-        <v>6018</v>
+        <v>6017</v>
       </c>
       <c r="I1228" s="2" t="s">
         <v>15</v>
@@ -57099,7 +57102,7 @@
         <v>1228</v>
       </c>
       <c r="B1229" s="2" t="s">
-        <v>6019</v>
+        <v>6018</v>
       </c>
       <c r="C1229" s="2" t="s">
         <v>5272</v>
@@ -57111,13 +57114,13 @@
         <v>5274</v>
       </c>
       <c r="F1229" s="2" t="s">
-        <v>6020</v>
+        <v>6019</v>
       </c>
       <c r="G1229" s="3">
         <v>3</v>
       </c>
       <c r="H1229" s="2" t="s">
-        <v>6021</v>
+        <v>6020</v>
       </c>
       <c r="I1229" s="2" t="s">
         <v>158</v>
@@ -57128,7 +57131,7 @@
         <v>1229</v>
       </c>
       <c r="B1230" s="2" t="s">
-        <v>6022</v>
+        <v>6021</v>
       </c>
       <c r="C1230" s="2" t="s">
         <v>5272</v>
@@ -57146,7 +57149,7 @@
         <v>4</v>
       </c>
       <c r="H1230" s="2" t="s">
-        <v>6023</v>
+        <v>6022</v>
       </c>
       <c r="I1230" s="2" t="s">
         <v>15</v>
@@ -57157,10 +57160,10 @@
         <v>1230</v>
       </c>
       <c r="B1231" s="2" t="s">
+        <v>6023</v>
+      </c>
+      <c r="C1231" s="2" t="s">
         <v>6024</v>
-      </c>
-      <c r="C1231" s="2" t="s">
-        <v>6025</v>
       </c>
       <c r="D1231" s="2" t="s">
         <v>4836</v>
@@ -57173,7 +57176,7 @@
         <v>3</v>
       </c>
       <c r="H1231" s="2" t="s">
-        <v>6026</v>
+        <v>6025</v>
       </c>
       <c r="I1231" s="2" t="s">
         <v>15</v>
@@ -57184,25 +57187,25 @@
         <v>1231</v>
       </c>
       <c r="B1232" s="2" t="s">
+        <v>6026</v>
+      </c>
+      <c r="C1232" s="2" t="s">
         <v>6027</v>
       </c>
-      <c r="C1232" s="2" t="s">
+      <c r="D1232" s="2" t="s">
         <v>6028</v>
       </c>
-      <c r="D1232" s="2" t="s">
+      <c r="E1232" s="2" t="s">
         <v>6029</v>
       </c>
-      <c r="E1232" s="2" t="s">
+      <c r="F1232" s="2" t="s">
         <v>6030</v>
-      </c>
-      <c r="F1232" s="2" t="s">
-        <v>6031</v>
       </c>
       <c r="G1232" s="3">
         <v>3</v>
       </c>
       <c r="H1232" s="2" t="s">
-        <v>6032</v>
+        <v>6031</v>
       </c>
       <c r="I1232" s="2" t="s">
         <v>15</v>
@@ -57213,25 +57216,25 @@
         <v>1232</v>
       </c>
       <c r="B1233" s="2" t="s">
+        <v>6032</v>
+      </c>
+      <c r="C1233" s="2" t="s">
         <v>6033</v>
       </c>
-      <c r="C1233" s="2" t="s">
+      <c r="D1233" s="2" t="s">
         <v>6034</v>
-      </c>
-      <c r="D1233" s="2" t="s">
-        <v>6035</v>
       </c>
       <c r="E1233" s="2" t="s">
         <v>3962</v>
       </c>
       <c r="F1233" s="2" t="s">
-        <v>6036</v>
+        <v>6035</v>
       </c>
       <c r="G1233" s="3">
         <v>2</v>
       </c>
       <c r="H1233" s="2" t="s">
-        <v>6037</v>
+        <v>6036</v>
       </c>
       <c r="I1233" s="2" t="s">
         <v>15</v>
@@ -57242,25 +57245,25 @@
         <v>1233</v>
       </c>
       <c r="B1234" s="2" t="s">
-        <v>6038</v>
+        <v>6037</v>
       </c>
       <c r="C1234" s="2" t="s">
         <v>5236</v>
       </c>
       <c r="D1234" s="2" t="s">
-        <v>6039</v>
+        <v>6038</v>
       </c>
       <c r="E1234" s="2" t="s">
         <v>1570</v>
       </c>
       <c r="F1234" s="2" t="s">
-        <v>6040</v>
+        <v>6039</v>
       </c>
       <c r="G1234" s="3">
         <v>4</v>
       </c>
       <c r="H1234" s="2" t="s">
-        <v>6041</v>
+        <v>6040</v>
       </c>
       <c r="I1234" s="2" t="s">
         <v>158</v>
@@ -57271,25 +57274,25 @@
         <v>1234</v>
       </c>
       <c r="B1235" s="2" t="s">
+        <v>6041</v>
+      </c>
+      <c r="C1235" s="2" t="s">
         <v>6042</v>
       </c>
-      <c r="C1235" s="2" t="s">
+      <c r="D1235" s="2" t="s">
         <v>6043</v>
-      </c>
-      <c r="D1235" s="2" t="s">
-        <v>6044</v>
       </c>
       <c r="E1235" s="2" t="s">
         <v>5829</v>
       </c>
       <c r="F1235" s="2" t="s">
-        <v>6045</v>
+        <v>6044</v>
       </c>
       <c r="G1235" s="3">
         <v>1</v>
       </c>
       <c r="H1235" s="2" t="s">
-        <v>6046</v>
+        <v>6045</v>
       </c>
       <c r="I1235" s="2" t="s">
         <v>15</v>
@@ -57300,25 +57303,25 @@
         <v>1235</v>
       </c>
       <c r="B1236" s="2" t="s">
+        <v>6046</v>
+      </c>
+      <c r="C1236" s="2" t="s">
         <v>6047</v>
       </c>
-      <c r="C1236" s="2" t="s">
+      <c r="D1236" s="2" t="s">
         <v>6048</v>
-      </c>
-      <c r="D1236" s="2" t="s">
-        <v>6049</v>
       </c>
       <c r="E1236" s="2" t="s">
         <v>5464</v>
       </c>
       <c r="F1236" s="2" t="s">
-        <v>6050</v>
+        <v>6049</v>
       </c>
       <c r="G1236" s="3">
         <v>1</v>
       </c>
       <c r="H1236" s="2" t="s">
-        <v>6051</v>
+        <v>6050</v>
       </c>
       <c r="I1236" s="2" t="s">
         <v>15</v>
@@ -57329,25 +57332,25 @@
         <v>1236</v>
       </c>
       <c r="B1237" s="2" t="s">
+        <v>6051</v>
+      </c>
+      <c r="C1237" s="2" t="s">
         <v>6052</v>
       </c>
-      <c r="C1237" s="2" t="s">
+      <c r="D1237" s="2" t="s">
         <v>6053</v>
       </c>
-      <c r="D1237" s="2" t="s">
+      <c r="E1237" s="2" t="s">
         <v>6054</v>
       </c>
-      <c r="E1237" s="2" t="s">
+      <c r="F1237" s="2" t="s">
         <v>6055</v>
-      </c>
-      <c r="F1237" s="2" t="s">
-        <v>6056</v>
       </c>
       <c r="G1237" s="3">
         <v>3</v>
       </c>
       <c r="H1237" s="2" t="s">
-        <v>6057</v>
+        <v>6056</v>
       </c>
       <c r="I1237" s="2" t="s">
         <v>158</v>
@@ -57358,25 +57361,25 @@
         <v>1237</v>
       </c>
       <c r="B1238" s="2" t="s">
+        <v>6057</v>
+      </c>
+      <c r="C1238" s="2" t="s">
         <v>6058</v>
-      </c>
-      <c r="C1238" s="2" t="s">
-        <v>6059</v>
       </c>
       <c r="D1238" s="2" t="s">
         <v>5358</v>
       </c>
       <c r="E1238" s="2" t="s">
-        <v>6017</v>
+        <v>6016</v>
       </c>
       <c r="F1238" s="2" t="s">
-        <v>6060</v>
+        <v>6059</v>
       </c>
       <c r="G1238" s="3">
         <v>3</v>
       </c>
       <c r="H1238" s="2" t="s">
-        <v>6061</v>
+        <v>6060</v>
       </c>
       <c r="I1238" s="2" t="s">
         <v>15</v>
@@ -57387,16 +57390,16 @@
         <v>1238</v>
       </c>
       <c r="B1239" s="2" t="s">
-        <v>6062</v>
+        <v>6061</v>
       </c>
       <c r="C1239" s="2" t="s">
+        <v>6014</v>
+      </c>
+      <c r="D1239" s="2" t="s">
         <v>6015</v>
       </c>
-      <c r="D1239" s="2" t="s">
+      <c r="E1239" s="2" t="s">
         <v>6016</v>
-      </c>
-      <c r="E1239" s="2" t="s">
-        <v>6017</v>
       </c>
       <c r="F1239" s="2"/>
       <c r="G1239" s="3">
@@ -57414,25 +57417,25 @@
         <v>1239</v>
       </c>
       <c r="B1240" s="2" t="s">
+        <v>6062</v>
+      </c>
+      <c r="C1240" s="2" t="s">
         <v>6063</v>
       </c>
-      <c r="C1240" s="2" t="s">
+      <c r="D1240" s="2" t="s">
         <v>6064</v>
       </c>
-      <c r="D1240" s="2" t="s">
+      <c r="E1240" s="2" t="s">
         <v>6065</v>
       </c>
-      <c r="E1240" s="2" t="s">
+      <c r="F1240" s="2" t="s">
         <v>6066</v>
-      </c>
-      <c r="F1240" s="2" t="s">
-        <v>6067</v>
       </c>
       <c r="G1240" s="3">
         <v>1</v>
       </c>
       <c r="H1240" s="2" t="s">
-        <v>6068</v>
+        <v>6067</v>
       </c>
       <c r="I1240" s="2" t="s">
         <v>15</v>
@@ -57443,25 +57446,25 @@
         <v>1240</v>
       </c>
       <c r="B1241" s="2" t="s">
+        <v>6068</v>
+      </c>
+      <c r="C1241" s="2" t="s">
+        <v>6887</v>
+      </c>
+      <c r="D1241" s="2" t="s">
+        <v>6888</v>
+      </c>
+      <c r="E1241" s="2" t="s">
+        <v>5994</v>
+      </c>
+      <c r="F1241" s="2" t="s">
         <v>6069</v>
-      </c>
-      <c r="C1241" s="2" t="s">
-        <v>6893</v>
-      </c>
-      <c r="D1241" s="2" t="s">
-        <v>6894</v>
-      </c>
-      <c r="E1241" s="2" t="s">
-        <v>5995</v>
-      </c>
-      <c r="F1241" s="2" t="s">
-        <v>6070</v>
       </c>
       <c r="G1241" s="3">
         <v>2</v>
       </c>
       <c r="H1241" s="2" t="s">
-        <v>6071</v>
+        <v>6070</v>
       </c>
       <c r="I1241" s="2" t="s">
         <v>15</v>
@@ -57472,7 +57475,7 @@
         <v>1241</v>
       </c>
       <c r="B1242" s="2" t="s">
-        <v>6072</v>
+        <v>6071</v>
       </c>
       <c r="C1242" s="2" t="s">
         <v>5274</v>
@@ -57484,13 +57487,13 @@
         <v>5273</v>
       </c>
       <c r="F1242" s="2" t="s">
-        <v>6020</v>
+        <v>6019</v>
       </c>
       <c r="G1242" s="3">
         <v>1</v>
       </c>
       <c r="H1242" s="2" t="s">
-        <v>6073</v>
+        <v>6072</v>
       </c>
       <c r="I1242" s="2" t="s">
         <v>15</v>
@@ -57501,25 +57504,25 @@
         <v>1242</v>
       </c>
       <c r="B1243" s="2" t="s">
+        <v>6073</v>
+      </c>
+      <c r="C1243" s="2" t="s">
         <v>6074</v>
       </c>
-      <c r="C1243" s="2" t="s">
+      <c r="D1243" s="2" t="s">
         <v>6075</v>
       </c>
-      <c r="D1243" s="2" t="s">
+      <c r="E1243" s="2" t="s">
         <v>6076</v>
       </c>
-      <c r="E1243" s="2" t="s">
+      <c r="F1243" s="2" t="s">
         <v>6077</v>
-      </c>
-      <c r="F1243" s="2" t="s">
-        <v>6078</v>
       </c>
       <c r="G1243" s="3">
         <v>4</v>
       </c>
       <c r="H1243" s="2" t="s">
-        <v>6079</v>
+        <v>6078</v>
       </c>
       <c r="I1243" s="2" t="s">
         <v>15</v>
@@ -57530,25 +57533,25 @@
         <v>1243</v>
       </c>
       <c r="B1244" s="2" t="s">
+        <v>6079</v>
+      </c>
+      <c r="C1244" s="2" t="s">
         <v>6080</v>
       </c>
-      <c r="C1244" s="2" t="s">
+      <c r="D1244" s="2" t="s">
         <v>6081</v>
-      </c>
-      <c r="D1244" s="2" t="s">
-        <v>6082</v>
       </c>
       <c r="E1244" s="2" t="s">
         <v>4339</v>
       </c>
       <c r="F1244" s="2" t="s">
-        <v>6083</v>
+        <v>6082</v>
       </c>
       <c r="G1244" s="3">
         <v>4</v>
       </c>
       <c r="H1244" s="2" t="s">
-        <v>6084</v>
+        <v>6083</v>
       </c>
       <c r="I1244" s="2" t="s">
         <v>15</v>
@@ -57559,25 +57562,25 @@
         <v>1244</v>
       </c>
       <c r="B1245" s="2" t="s">
+        <v>6084</v>
+      </c>
+      <c r="C1245" s="2" t="s">
         <v>6085</v>
       </c>
-      <c r="C1245" s="2" t="s">
+      <c r="D1245" s="2" t="s">
         <v>6086</v>
       </c>
-      <c r="D1245" s="2" t="s">
+      <c r="E1245" s="2" t="s">
         <v>6087</v>
       </c>
-      <c r="E1245" s="2" t="s">
+      <c r="F1245" s="2" t="s">
         <v>6088</v>
-      </c>
-      <c r="F1245" s="2" t="s">
-        <v>6089</v>
       </c>
       <c r="G1245" s="3">
         <v>2</v>
       </c>
       <c r="H1245" s="2" t="s">
-        <v>6090</v>
+        <v>6089</v>
       </c>
       <c r="I1245" s="2" t="s">
         <v>158</v>
@@ -57588,10 +57591,10 @@
         <v>1245</v>
       </c>
       <c r="B1246" s="2" t="s">
+        <v>6090</v>
+      </c>
+      <c r="C1246" s="2" t="s">
         <v>6091</v>
-      </c>
-      <c r="C1246" s="2" t="s">
-        <v>6092</v>
       </c>
       <c r="D1246" s="2" t="s">
         <v>5658</v>
@@ -57600,13 +57603,13 @@
         <v>1141</v>
       </c>
       <c r="F1246" s="2" t="s">
-        <v>6093</v>
+        <v>6092</v>
       </c>
       <c r="G1246" s="3">
         <v>4</v>
       </c>
       <c r="H1246" s="2" t="s">
-        <v>6094</v>
+        <v>6093</v>
       </c>
       <c r="I1246" s="2" t="s">
         <v>15</v>
@@ -57617,25 +57620,25 @@
         <v>1246</v>
       </c>
       <c r="B1247" s="2" t="s">
+        <v>6094</v>
+      </c>
+      <c r="C1247" s="2" t="s">
         <v>6095</v>
       </c>
-      <c r="C1247" s="2" t="s">
+      <c r="D1247" s="2" t="s">
         <v>6096</v>
       </c>
-      <c r="D1247" s="2" t="s">
+      <c r="E1247" s="2" t="s">
         <v>6097</v>
       </c>
-      <c r="E1247" s="2" t="s">
+      <c r="F1247" s="2" t="s">
         <v>6098</v>
-      </c>
-      <c r="F1247" s="2" t="s">
-        <v>6099</v>
       </c>
       <c r="G1247" s="3">
         <v>4</v>
       </c>
       <c r="H1247" s="2" t="s">
-        <v>6100</v>
+        <v>6099</v>
       </c>
       <c r="I1247" s="2" t="s">
         <v>15</v>
@@ -57646,19 +57649,19 @@
         <v>1247</v>
       </c>
       <c r="B1248" s="2" t="s">
-        <v>6101</v>
+        <v>6100</v>
       </c>
       <c r="C1248" s="2" t="s">
         <v>4199</v>
       </c>
       <c r="D1248" s="2" t="s">
+        <v>6006</v>
+      </c>
+      <c r="E1248" s="2" t="s">
+        <v>6101</v>
+      </c>
+      <c r="F1248" s="2" t="s">
         <v>6007</v>
-      </c>
-      <c r="E1248" s="2" t="s">
-        <v>6102</v>
-      </c>
-      <c r="F1248" s="2" t="s">
-        <v>6008</v>
       </c>
       <c r="G1248" s="3">
         <v>1</v>
@@ -57675,25 +57678,25 @@
         <v>1248</v>
       </c>
       <c r="B1249" s="2" t="s">
+        <v>6102</v>
+      </c>
+      <c r="C1249" s="2" t="s">
         <v>6103</v>
       </c>
-      <c r="C1249" s="2" t="s">
+      <c r="D1249" s="2" t="s">
         <v>6104</v>
       </c>
-      <c r="D1249" s="2" t="s">
+      <c r="E1249" s="2" t="s">
         <v>6105</v>
       </c>
-      <c r="E1249" s="2" t="s">
+      <c r="F1249" s="2" t="s">
         <v>6106</v>
-      </c>
-      <c r="F1249" s="2" t="s">
-        <v>6107</v>
       </c>
       <c r="G1249" s="3">
         <v>3</v>
       </c>
       <c r="H1249" s="2" t="s">
-        <v>6108</v>
+        <v>6107</v>
       </c>
       <c r="I1249" s="2" t="s">
         <v>15</v>
@@ -57704,25 +57707,25 @@
         <v>1249</v>
       </c>
       <c r="B1250" s="2" t="s">
+        <v>6108</v>
+      </c>
+      <c r="C1250" s="2" t="s">
         <v>6109</v>
       </c>
-      <c r="C1250" s="2" t="s">
+      <c r="D1250" s="2" t="s">
         <v>6110</v>
       </c>
-      <c r="D1250" s="2" t="s">
+      <c r="E1250" s="2" t="s">
         <v>6111</v>
       </c>
-      <c r="E1250" s="2" t="s">
+      <c r="F1250" s="2" t="s">
         <v>6112</v>
-      </c>
-      <c r="F1250" s="2" t="s">
-        <v>6113</v>
       </c>
       <c r="G1250" s="3">
         <v>2</v>
       </c>
       <c r="H1250" s="2" t="s">
-        <v>6114</v>
+        <v>6113</v>
       </c>
       <c r="I1250" s="2" t="s">
         <v>15</v>
@@ -57733,25 +57736,25 @@
         <v>1250</v>
       </c>
       <c r="B1251" s="2" t="s">
+        <v>6114</v>
+      </c>
+      <c r="C1251" s="2" t="s">
         <v>6115</v>
       </c>
-      <c r="C1251" s="2" t="s">
+      <c r="D1251" s="2" t="s">
         <v>6116</v>
       </c>
-      <c r="D1251" s="2" t="s">
+      <c r="E1251" s="2" t="s">
         <v>6117</v>
       </c>
-      <c r="E1251" s="2" t="s">
+      <c r="F1251" s="2" t="s">
         <v>6118</v>
-      </c>
-      <c r="F1251" s="2" t="s">
-        <v>6119</v>
       </c>
       <c r="G1251" s="3">
         <v>4</v>
       </c>
       <c r="H1251" s="2" t="s">
-        <v>6120</v>
+        <v>6119</v>
       </c>
       <c r="I1251" s="2" t="s">
         <v>15</v>
@@ -57762,25 +57765,25 @@
         <v>1251</v>
       </c>
       <c r="B1252" s="2" t="s">
+        <v>6120</v>
+      </c>
+      <c r="C1252" s="2" t="s">
         <v>6121</v>
       </c>
-      <c r="C1252" s="2" t="s">
+      <c r="D1252" s="2" t="s">
         <v>6122</v>
       </c>
-      <c r="D1252" s="2" t="s">
+      <c r="E1252" s="2" t="s">
         <v>6123</v>
       </c>
-      <c r="E1252" s="2" t="s">
+      <c r="F1252" s="2" t="s">
         <v>6124</v>
-      </c>
-      <c r="F1252" s="2" t="s">
-        <v>6125</v>
       </c>
       <c r="G1252" s="3">
         <v>1</v>
       </c>
       <c r="H1252" s="2" t="s">
-        <v>6126</v>
+        <v>6125</v>
       </c>
       <c r="I1252" s="2" t="s">
         <v>15</v>
@@ -57791,25 +57794,25 @@
         <v>1252</v>
       </c>
       <c r="B1253" s="2" t="s">
+        <v>6126</v>
+      </c>
+      <c r="C1253" s="2" t="s">
         <v>6127</v>
       </c>
-      <c r="C1253" s="2" t="s">
+      <c r="D1253" s="2" t="s">
         <v>6128</v>
       </c>
-      <c r="D1253" s="2" t="s">
+      <c r="E1253" s="2" t="s">
         <v>6129</v>
       </c>
-      <c r="E1253" s="2" t="s">
+      <c r="F1253" s="2" t="s">
         <v>6130</v>
-      </c>
-      <c r="F1253" s="2" t="s">
-        <v>6131</v>
       </c>
       <c r="G1253" s="3">
         <v>2</v>
       </c>
       <c r="H1253" s="2" t="s">
-        <v>6132</v>
+        <v>6131</v>
       </c>
       <c r="I1253" s="2" t="s">
         <v>15</v>
@@ -57820,25 +57823,25 @@
         <v>1253</v>
       </c>
       <c r="B1254" s="2" t="s">
-        <v>6133</v>
+        <v>6132</v>
       </c>
       <c r="C1254" s="2" t="s">
         <v>4413</v>
       </c>
       <c r="D1254" s="2" t="s">
+        <v>6133</v>
+      </c>
+      <c r="E1254" s="2" t="s">
         <v>6134</v>
       </c>
-      <c r="E1254" s="2" t="s">
+      <c r="F1254" s="2" t="s">
         <v>6135</v>
-      </c>
-      <c r="F1254" s="2" t="s">
-        <v>6136</v>
       </c>
       <c r="G1254" s="3">
         <v>2</v>
       </c>
       <c r="H1254" s="2" t="s">
-        <v>6137</v>
+        <v>6136</v>
       </c>
       <c r="I1254" s="2" t="s">
         <v>165</v>
@@ -57849,25 +57852,25 @@
         <v>1254</v>
       </c>
       <c r="B1255" s="2" t="s">
+        <v>6137</v>
+      </c>
+      <c r="C1255" s="2" t="s">
         <v>6138</v>
       </c>
-      <c r="C1255" s="2" t="s">
+      <c r="D1255" s="2" t="s">
         <v>6139</v>
       </c>
-      <c r="D1255" s="2" t="s">
+      <c r="E1255" s="2" t="s">
         <v>6140</v>
       </c>
-      <c r="E1255" s="2" t="s">
+      <c r="F1255" s="2" t="s">
         <v>6141</v>
-      </c>
-      <c r="F1255" s="2" t="s">
-        <v>6142</v>
       </c>
       <c r="G1255" s="3">
         <v>2</v>
       </c>
       <c r="H1255" s="2" t="s">
-        <v>6143</v>
+        <v>6142</v>
       </c>
       <c r="I1255" s="2" t="s">
         <v>165</v>
@@ -57878,7 +57881,7 @@
         <v>1255</v>
       </c>
       <c r="B1256" s="2" t="s">
-        <v>6144</v>
+        <v>6143</v>
       </c>
       <c r="C1256" s="2" t="s">
         <v>514</v>
@@ -57896,7 +57899,7 @@
         <v>3</v>
       </c>
       <c r="H1256" s="2" t="s">
-        <v>6145</v>
+        <v>6144</v>
       </c>
       <c r="I1256" s="2" t="s">
         <v>165</v>
@@ -57907,25 +57910,25 @@
         <v>1256</v>
       </c>
       <c r="B1257" s="2" t="s">
+        <v>6145</v>
+      </c>
+      <c r="C1257" s="2" t="s">
         <v>6146</v>
       </c>
-      <c r="C1257" s="2" t="s">
+      <c r="D1257" s="2" t="s">
         <v>6147</v>
       </c>
-      <c r="D1257" s="2" t="s">
+      <c r="E1257" s="2" t="s">
         <v>6148</v>
       </c>
-      <c r="E1257" s="2" t="s">
+      <c r="F1257" s="2" t="s">
         <v>6149</v>
-      </c>
-      <c r="F1257" s="2" t="s">
-        <v>6150</v>
       </c>
       <c r="G1257" s="3">
         <v>3</v>
       </c>
       <c r="H1257" s="2" t="s">
-        <v>6151</v>
+        <v>6150</v>
       </c>
       <c r="I1257" s="2" t="s">
         <v>165</v>
@@ -57936,25 +57939,25 @@
         <v>1257</v>
       </c>
       <c r="B1258" s="2" t="s">
+        <v>6151</v>
+      </c>
+      <c r="C1258" s="2" t="s">
         <v>6152</v>
       </c>
-      <c r="C1258" s="2" t="s">
+      <c r="D1258" s="2" t="s">
         <v>6153</v>
       </c>
-      <c r="D1258" s="2" t="s">
+      <c r="E1258" s="2" t="s">
         <v>6154</v>
       </c>
-      <c r="E1258" s="2" t="s">
+      <c r="F1258" s="2" t="s">
         <v>6155</v>
-      </c>
-      <c r="F1258" s="2" t="s">
-        <v>6156</v>
       </c>
       <c r="G1258" s="3">
         <v>4</v>
       </c>
       <c r="H1258" s="2" t="s">
-        <v>6157</v>
+        <v>6156</v>
       </c>
       <c r="I1258" s="2" t="s">
         <v>165</v>
@@ -57965,7 +57968,7 @@
         <v>1258</v>
       </c>
       <c r="B1259" s="2" t="s">
-        <v>6158</v>
+        <v>6157</v>
       </c>
       <c r="C1259" s="2" t="s">
         <v>253</v>
@@ -57977,13 +57980,13 @@
         <v>255</v>
       </c>
       <c r="F1259" s="2" t="s">
-        <v>6159</v>
+        <v>6158</v>
       </c>
       <c r="G1259" s="3">
         <v>3</v>
       </c>
       <c r="H1259" s="2" t="s">
-        <v>6160</v>
+        <v>6159</v>
       </c>
       <c r="I1259" s="2" t="s">
         <v>165</v>
@@ -57994,7 +57997,7 @@
         <v>1259</v>
       </c>
       <c r="B1260" s="2" t="s">
-        <v>6161</v>
+        <v>6160</v>
       </c>
       <c r="C1260" s="2" t="s">
         <v>255</v>
@@ -58003,7 +58006,7 @@
         <v>253</v>
       </c>
       <c r="E1260" s="2" t="s">
-        <v>6159</v>
+        <v>6158</v>
       </c>
       <c r="F1260" s="2" t="s">
         <v>254</v>
@@ -58012,7 +58015,7 @@
         <v>3</v>
       </c>
       <c r="H1260" s="2" t="s">
-        <v>6162</v>
+        <v>6161</v>
       </c>
       <c r="I1260" s="2" t="s">
         <v>165</v>
@@ -58023,7 +58026,7 @@
         <v>1260</v>
       </c>
       <c r="B1261" s="2" t="s">
-        <v>6163</v>
+        <v>6162</v>
       </c>
       <c r="C1261" s="2" t="s">
         <v>515</v>
@@ -58041,7 +58044,7 @@
         <v>4</v>
       </c>
       <c r="H1261" s="2" t="s">
-        <v>6164</v>
+        <v>6163</v>
       </c>
       <c r="I1261" s="2" t="s">
         <v>165</v>
@@ -58052,25 +58055,25 @@
         <v>1261</v>
       </c>
       <c r="B1262" s="2" t="s">
+        <v>6164</v>
+      </c>
+      <c r="C1262" s="2" t="s">
         <v>6165</v>
       </c>
-      <c r="C1262" s="2" t="s">
+      <c r="D1262" s="2" t="s">
         <v>6166</v>
       </c>
-      <c r="D1262" s="2" t="s">
+      <c r="E1262" s="2" t="s">
         <v>6167</v>
       </c>
-      <c r="E1262" s="2" t="s">
+      <c r="F1262" s="2" t="s">
         <v>6168</v>
-      </c>
-      <c r="F1262" s="2" t="s">
-        <v>6169</v>
       </c>
       <c r="G1262" s="3">
         <v>3</v>
       </c>
       <c r="H1262" s="2" t="s">
-        <v>6170</v>
+        <v>6169</v>
       </c>
       <c r="I1262" s="2" t="s">
         <v>15</v>
@@ -58081,25 +58084,25 @@
         <v>1262</v>
       </c>
       <c r="B1263" s="2" t="s">
+        <v>6170</v>
+      </c>
+      <c r="C1263" s="2" t="s">
         <v>6171</v>
       </c>
-      <c r="C1263" s="2" t="s">
+      <c r="D1263" s="2" t="s">
         <v>6172</v>
       </c>
-      <c r="D1263" s="2" t="s">
+      <c r="E1263" s="2" t="s">
         <v>6173</v>
       </c>
-      <c r="E1263" s="2" t="s">
+      <c r="F1263" s="2" t="s">
         <v>6174</v>
-      </c>
-      <c r="F1263" s="2" t="s">
-        <v>6175</v>
       </c>
       <c r="G1263" s="3">
         <v>3</v>
       </c>
       <c r="H1263" s="2" t="s">
-        <v>6176</v>
+        <v>6175</v>
       </c>
       <c r="I1263" s="2" t="s">
         <v>15</v>
@@ -58110,25 +58113,25 @@
         <v>1263</v>
       </c>
       <c r="B1264" s="2" t="s">
+        <v>6176</v>
+      </c>
+      <c r="C1264" s="2" t="s">
         <v>6177</v>
       </c>
-      <c r="C1264" s="2" t="s">
+      <c r="D1264" s="2" t="s">
         <v>6178</v>
       </c>
-      <c r="D1264" s="2" t="s">
+      <c r="E1264" s="2" t="s">
         <v>6179</v>
       </c>
-      <c r="E1264" s="2" t="s">
+      <c r="F1264" s="2" t="s">
         <v>6180</v>
-      </c>
-      <c r="F1264" s="2" t="s">
-        <v>6181</v>
       </c>
       <c r="G1264" s="3">
         <v>4</v>
       </c>
       <c r="H1264" s="2" t="s">
-        <v>6182</v>
+        <v>6181</v>
       </c>
       <c r="I1264" s="2" t="s">
         <v>15</v>
@@ -58139,23 +58142,23 @@
         <v>1264</v>
       </c>
       <c r="B1265" s="2" t="s">
+        <v>6182</v>
+      </c>
+      <c r="C1265" s="2" t="s">
         <v>6183</v>
       </c>
-      <c r="C1265" s="2" t="s">
+      <c r="D1265" s="2" t="s">
         <v>6184</v>
       </c>
-      <c r="D1265" s="2" t="s">
+      <c r="E1265" s="2" t="s">
         <v>6185</v>
-      </c>
-      <c r="E1265" s="2" t="s">
-        <v>6186</v>
       </c>
       <c r="F1265" s="2"/>
       <c r="G1265" s="3">
         <v>3</v>
       </c>
       <c r="H1265" s="2" t="s">
-        <v>6187</v>
+        <v>6186</v>
       </c>
       <c r="I1265" s="2" t="s">
         <v>15</v>
@@ -58166,25 +58169,25 @@
         <v>1265</v>
       </c>
       <c r="B1266" s="2" t="s">
+        <v>6187</v>
+      </c>
+      <c r="C1266" s="2" t="s">
         <v>6188</v>
       </c>
-      <c r="C1266" s="2" t="s">
+      <c r="D1266" s="2" t="s">
+        <v>5959</v>
+      </c>
+      <c r="E1266" s="2" t="s">
         <v>6189</v>
       </c>
-      <c r="D1266" s="2" t="s">
-        <v>5960</v>
-      </c>
-      <c r="E1266" s="2" t="s">
+      <c r="F1266" s="2" t="s">
         <v>6190</v>
-      </c>
-      <c r="F1266" s="2" t="s">
-        <v>6191</v>
       </c>
       <c r="G1266" s="3">
         <v>4</v>
       </c>
       <c r="H1266" s="2" t="s">
-        <v>6192</v>
+        <v>6191</v>
       </c>
       <c r="I1266" s="2" t="s">
         <v>15</v>
@@ -58195,25 +58198,25 @@
         <v>1266</v>
       </c>
       <c r="B1267" s="2" t="s">
+        <v>6192</v>
+      </c>
+      <c r="C1267" s="2" t="s">
         <v>6193</v>
       </c>
-      <c r="C1267" s="2" t="s">
+      <c r="D1267" s="2" t="s">
         <v>6194</v>
       </c>
-      <c r="D1267" s="2" t="s">
+      <c r="E1267" s="2" t="s">
         <v>6195</v>
       </c>
-      <c r="E1267" s="2" t="s">
+      <c r="F1267" s="2" t="s">
         <v>6196</v>
-      </c>
-      <c r="F1267" s="2" t="s">
-        <v>6197</v>
       </c>
       <c r="G1267" s="3">
         <v>4</v>
       </c>
       <c r="H1267" s="2" t="s">
-        <v>6198</v>
+        <v>6197</v>
       </c>
       <c r="I1267" s="2" t="s">
         <v>15</v>
@@ -58224,25 +58227,25 @@
         <v>1267</v>
       </c>
       <c r="B1268" s="2" t="s">
+        <v>6198</v>
+      </c>
+      <c r="C1268" s="2" t="s">
         <v>6199</v>
       </c>
-      <c r="C1268" s="2" t="s">
+      <c r="D1268" s="2" t="s">
         <v>6200</v>
       </c>
-      <c r="D1268" s="2" t="s">
+      <c r="E1268" s="2" t="s">
         <v>6201</v>
       </c>
-      <c r="E1268" s="2" t="s">
+      <c r="F1268" s="2" t="s">
         <v>6202</v>
-      </c>
-      <c r="F1268" s="2" t="s">
-        <v>6203</v>
       </c>
       <c r="G1268" s="3">
         <v>4</v>
       </c>
       <c r="H1268" s="2" t="s">
-        <v>6204</v>
+        <v>6203</v>
       </c>
       <c r="I1268" s="2" t="s">
         <v>165</v>
@@ -58253,25 +58256,25 @@
         <v>1268</v>
       </c>
       <c r="B1269" s="2" t="s">
+        <v>6204</v>
+      </c>
+      <c r="C1269" s="2" t="s">
         <v>6205</v>
       </c>
-      <c r="C1269" s="2" t="s">
+      <c r="D1269" s="2" t="s">
         <v>6206</v>
       </c>
-      <c r="D1269" s="2" t="s">
+      <c r="E1269" s="2" t="s">
         <v>6207</v>
       </c>
-      <c r="E1269" s="2" t="s">
+      <c r="F1269" s="2" t="s">
         <v>6208</v>
-      </c>
-      <c r="F1269" s="2" t="s">
-        <v>6209</v>
       </c>
       <c r="G1269" s="3">
         <v>4</v>
       </c>
       <c r="H1269" s="2" t="s">
-        <v>6210</v>
+        <v>6209</v>
       </c>
       <c r="I1269" s="2" t="s">
         <v>15</v>
@@ -58282,25 +58285,25 @@
         <v>1269</v>
       </c>
       <c r="B1270" s="2" t="s">
+        <v>6210</v>
+      </c>
+      <c r="C1270" s="2" t="s">
         <v>6211</v>
-      </c>
-      <c r="C1270" s="2" t="s">
-        <v>6212</v>
       </c>
       <c r="D1270" s="2" t="s">
         <v>2701</v>
       </c>
       <c r="E1270" s="2" t="s">
+        <v>6212</v>
+      </c>
+      <c r="F1270" s="2" t="s">
         <v>6213</v>
-      </c>
-      <c r="F1270" s="2" t="s">
-        <v>6214</v>
       </c>
       <c r="G1270" s="3">
         <v>3</v>
       </c>
       <c r="H1270" s="2" t="s">
-        <v>6215</v>
+        <v>6214</v>
       </c>
       <c r="I1270" s="2" t="s">
         <v>15</v>
@@ -58311,25 +58314,25 @@
         <v>1270</v>
       </c>
       <c r="B1271" s="2" t="s">
+        <v>6215</v>
+      </c>
+      <c r="C1271" s="2" t="s">
         <v>6216</v>
       </c>
-      <c r="C1271" s="2" t="s">
+      <c r="D1271" s="2" t="s">
         <v>6217</v>
       </c>
-      <c r="D1271" s="2" t="s">
+      <c r="E1271" s="2" t="s">
         <v>6218</v>
       </c>
-      <c r="E1271" s="2" t="s">
+      <c r="F1271" s="2" t="s">
         <v>6219</v>
-      </c>
-      <c r="F1271" s="2" t="s">
-        <v>6220</v>
       </c>
       <c r="G1271" s="3">
         <v>1</v>
       </c>
       <c r="H1271" s="2" t="s">
-        <v>6221</v>
+        <v>6220</v>
       </c>
       <c r="I1271" s="2" t="s">
         <v>15</v>
@@ -58340,25 +58343,25 @@
         <v>1271</v>
       </c>
       <c r="B1272" s="2" t="s">
+        <v>6221</v>
+      </c>
+      <c r="C1272" s="2" t="s">
         <v>6222</v>
       </c>
-      <c r="C1272" s="2" t="s">
+      <c r="D1272" s="2" t="s">
         <v>6223</v>
       </c>
-      <c r="D1272" s="2" t="s">
+      <c r="E1272" s="2" t="s">
         <v>6224</v>
       </c>
-      <c r="E1272" s="2" t="s">
+      <c r="F1272" s="2" t="s">
         <v>6225</v>
-      </c>
-      <c r="F1272" s="2" t="s">
-        <v>6226</v>
       </c>
       <c r="G1272" s="3">
         <v>1</v>
       </c>
       <c r="H1272" s="2" t="s">
-        <v>6227</v>
+        <v>6226</v>
       </c>
       <c r="I1272" s="2" t="s">
         <v>15</v>
@@ -58369,7 +58372,7 @@
         <v>1272</v>
       </c>
       <c r="B1273" s="2" t="s">
-        <v>6228</v>
+        <v>6227</v>
       </c>
       <c r="C1273" s="2" t="s">
         <v>513</v>
@@ -58381,13 +58384,13 @@
         <v>3879</v>
       </c>
       <c r="F1273" s="2" t="s">
-        <v>6229</v>
+        <v>6228</v>
       </c>
       <c r="G1273" s="3">
         <v>4</v>
       </c>
       <c r="H1273" s="2" t="s">
-        <v>6230</v>
+        <v>6229</v>
       </c>
       <c r="I1273" s="2" t="s">
         <v>165</v>
@@ -58398,10 +58401,10 @@
         <v>1273</v>
       </c>
       <c r="B1274" s="2" t="s">
+        <v>6230</v>
+      </c>
+      <c r="C1274" s="2" t="s">
         <v>6231</v>
-      </c>
-      <c r="C1274" s="2" t="s">
-        <v>6232</v>
       </c>
       <c r="D1274" s="2" t="s">
         <v>5442</v>
@@ -58410,13 +58413,13 @@
         <v>3078</v>
       </c>
       <c r="F1274" s="2" t="s">
-        <v>6233</v>
+        <v>6232</v>
       </c>
       <c r="G1274" s="3">
         <v>3</v>
       </c>
       <c r="H1274" s="2" t="s">
-        <v>6234</v>
+        <v>6233</v>
       </c>
       <c r="I1274" s="2" t="s">
         <v>15</v>
@@ -58427,25 +58430,25 @@
         <v>1274</v>
       </c>
       <c r="B1275" s="2" t="s">
+        <v>6234</v>
+      </c>
+      <c r="C1275" s="2" t="s">
         <v>6235</v>
       </c>
-      <c r="C1275" s="2" t="s">
+      <c r="D1275" s="2" t="s">
         <v>6236</v>
       </c>
-      <c r="D1275" s="2" t="s">
+      <c r="E1275" s="2" t="s">
         <v>6237</v>
       </c>
-      <c r="E1275" s="2" t="s">
+      <c r="F1275" s="2" t="s">
         <v>6238</v>
-      </c>
-      <c r="F1275" s="2" t="s">
-        <v>6239</v>
       </c>
       <c r="G1275" s="3">
         <v>2</v>
       </c>
       <c r="H1275" s="2" t="s">
-        <v>6240</v>
+        <v>6239</v>
       </c>
       <c r="I1275" s="2" t="s">
         <v>165</v>
@@ -58456,25 +58459,25 @@
         <v>1275</v>
       </c>
       <c r="B1276" s="2" t="s">
+        <v>6240</v>
+      </c>
+      <c r="C1276" s="2" t="s">
         <v>6241</v>
       </c>
-      <c r="C1276" s="2" t="s">
+      <c r="D1276" s="2" t="s">
         <v>6242</v>
       </c>
-      <c r="D1276" s="2" t="s">
+      <c r="E1276" s="2" t="s">
         <v>6243</v>
       </c>
-      <c r="E1276" s="2" t="s">
+      <c r="F1276" s="2" t="s">
         <v>6244</v>
-      </c>
-      <c r="F1276" s="2" t="s">
-        <v>6245</v>
       </c>
       <c r="G1276" s="3">
         <v>2</v>
       </c>
       <c r="H1276" s="2" t="s">
-        <v>6246</v>
+        <v>6245</v>
       </c>
       <c r="I1276" s="2" t="s">
         <v>15</v>
@@ -58485,7 +58488,7 @@
         <v>1276</v>
       </c>
       <c r="B1277" s="2" t="s">
-        <v>6247</v>
+        <v>6246</v>
       </c>
       <c r="C1277" s="2" t="s">
         <v>1393</v>
@@ -58494,16 +58497,16 @@
         <v>1395</v>
       </c>
       <c r="E1277" s="2" t="s">
+        <v>6247</v>
+      </c>
+      <c r="F1277" s="2" t="s">
         <v>6248</v>
-      </c>
-      <c r="F1277" s="2" t="s">
-        <v>6249</v>
       </c>
       <c r="G1277" s="3">
         <v>4</v>
       </c>
       <c r="H1277" s="2" t="s">
-        <v>6250</v>
+        <v>6249</v>
       </c>
       <c r="I1277" s="2" t="s">
         <v>15</v>
@@ -58514,25 +58517,25 @@
         <v>1277</v>
       </c>
       <c r="B1278" s="2" t="s">
+        <v>6250</v>
+      </c>
+      <c r="C1278" s="2" t="s">
         <v>6251</v>
       </c>
-      <c r="C1278" s="2" t="s">
+      <c r="D1278" s="2" t="s">
         <v>6252</v>
-      </c>
-      <c r="D1278" s="2" t="s">
-        <v>6253</v>
       </c>
       <c r="E1278" s="2" t="s">
         <v>119</v>
       </c>
       <c r="F1278" s="2" t="s">
-        <v>6254</v>
+        <v>6253</v>
       </c>
       <c r="G1278" s="3">
         <v>4</v>
       </c>
       <c r="H1278" s="2" t="s">
-        <v>6255</v>
+        <v>6254</v>
       </c>
       <c r="I1278" s="2" t="s">
         <v>165</v>
@@ -58543,25 +58546,25 @@
         <v>1278</v>
       </c>
       <c r="B1279" s="2" t="s">
+        <v>6255</v>
+      </c>
+      <c r="C1279" s="2" t="s">
         <v>6256</v>
       </c>
-      <c r="C1279" s="2" t="s">
+      <c r="D1279" s="2" t="s">
         <v>6257</v>
       </c>
-      <c r="D1279" s="2" t="s">
+      <c r="E1279" s="2" t="s">
         <v>6258</v>
       </c>
-      <c r="E1279" s="2" t="s">
+      <c r="F1279" s="2" t="s">
         <v>6259</v>
-      </c>
-      <c r="F1279" s="2" t="s">
-        <v>6260</v>
       </c>
       <c r="G1279" s="3">
         <v>1</v>
       </c>
       <c r="H1279" s="2" t="s">
-        <v>6261</v>
+        <v>6260</v>
       </c>
       <c r="I1279" s="2" t="s">
         <v>15</v>
@@ -58572,25 +58575,25 @@
         <v>1279</v>
       </c>
       <c r="B1280" s="2" t="s">
+        <v>6261</v>
+      </c>
+      <c r="C1280" s="2" t="s">
         <v>6262</v>
       </c>
-      <c r="C1280" s="2" t="s">
+      <c r="D1280" s="2" t="s">
         <v>6263</v>
       </c>
-      <c r="D1280" s="2" t="s">
+      <c r="E1280" s="2" t="s">
         <v>6264</v>
       </c>
-      <c r="E1280" s="2" t="s">
+      <c r="F1280" s="2" t="s">
         <v>6265</v>
-      </c>
-      <c r="F1280" s="2" t="s">
-        <v>6266</v>
       </c>
       <c r="G1280" s="3">
         <v>4</v>
       </c>
       <c r="H1280" s="2" t="s">
-        <v>6267</v>
+        <v>6266</v>
       </c>
       <c r="I1280" s="2" t="s">
         <v>15</v>
@@ -58601,10 +58604,10 @@
         <v>1280</v>
       </c>
       <c r="B1281" s="2" t="s">
+        <v>6267</v>
+      </c>
+      <c r="C1281" s="2" t="s">
         <v>6268</v>
-      </c>
-      <c r="C1281" s="2" t="s">
-        <v>6269</v>
       </c>
       <c r="D1281" s="2" t="s">
         <v>177</v>
@@ -58613,13 +58616,13 @@
         <v>179</v>
       </c>
       <c r="F1281" s="2" t="s">
-        <v>6270</v>
+        <v>6269</v>
       </c>
       <c r="G1281" s="3">
         <v>1</v>
       </c>
       <c r="H1281" s="2" t="s">
-        <v>6271</v>
+        <v>6270</v>
       </c>
       <c r="I1281" s="2" t="s">
         <v>15</v>
@@ -58630,25 +58633,25 @@
         <v>1281</v>
       </c>
       <c r="B1282" s="2" t="s">
+        <v>6271</v>
+      </c>
+      <c r="C1282" s="2" t="s">
         <v>6272</v>
       </c>
-      <c r="C1282" s="2" t="s">
+      <c r="D1282" s="2" t="s">
         <v>6273</v>
-      </c>
-      <c r="D1282" s="2" t="s">
-        <v>6274</v>
       </c>
       <c r="E1282" s="2" t="s">
         <v>5665</v>
       </c>
       <c r="F1282" s="2" t="s">
-        <v>6275</v>
+        <v>6274</v>
       </c>
       <c r="G1282" s="3">
         <v>4</v>
       </c>
       <c r="H1282" s="2" t="s">
-        <v>6276</v>
+        <v>6275</v>
       </c>
       <c r="I1282" s="2" t="s">
         <v>15</v>
@@ -58659,25 +58662,25 @@
         <v>1282</v>
       </c>
       <c r="B1283" s="2" t="s">
+        <v>6276</v>
+      </c>
+      <c r="C1283" s="2" t="s">
         <v>6277</v>
       </c>
-      <c r="C1283" s="2" t="s">
+      <c r="D1283" s="2" t="s">
         <v>6278</v>
-      </c>
-      <c r="D1283" s="2" t="s">
-        <v>6279</v>
       </c>
       <c r="E1283" s="2" t="s">
         <v>5437</v>
       </c>
       <c r="F1283" s="2" t="s">
-        <v>6280</v>
+        <v>6279</v>
       </c>
       <c r="G1283" s="3">
         <v>2</v>
       </c>
       <c r="H1283" s="2" t="s">
-        <v>6281</v>
+        <v>6280</v>
       </c>
       <c r="I1283" s="2" t="s">
         <v>15</v>
@@ -58688,7 +58691,7 @@
         <v>1283</v>
       </c>
       <c r="B1284" s="2" t="s">
-        <v>6282</v>
+        <v>6281</v>
       </c>
       <c r="C1284" s="2" t="s">
         <v>1839</v>
@@ -58697,16 +58700,16 @@
         <v>1840</v>
       </c>
       <c r="E1284" s="2" t="s">
+        <v>6282</v>
+      </c>
+      <c r="F1284" s="2" t="s">
         <v>6283</v>
-      </c>
-      <c r="F1284" s="2" t="s">
-        <v>6284</v>
       </c>
       <c r="G1284" s="3">
         <v>3</v>
       </c>
       <c r="H1284" s="2" t="s">
-        <v>6285</v>
+        <v>6284</v>
       </c>
       <c r="I1284" s="2" t="s">
         <v>15</v>
@@ -58717,25 +58720,25 @@
         <v>1284</v>
       </c>
       <c r="B1285" s="2" t="s">
-        <v>6876</v>
+        <v>6870</v>
       </c>
       <c r="C1285" s="2" t="s">
-        <v>6877</v>
+        <v>6871</v>
       </c>
       <c r="D1285" s="2" t="s">
         <v>3317</v>
       </c>
       <c r="E1285" s="2" t="s">
-        <v>6286</v>
+        <v>6285</v>
       </c>
       <c r="F1285" s="2" t="s">
-        <v>6878</v>
+        <v>6872</v>
       </c>
       <c r="G1285" s="3">
         <v>2</v>
       </c>
       <c r="H1285" s="2" t="s">
-        <v>6287</v>
+        <v>6286</v>
       </c>
       <c r="I1285" s="2" t="s">
         <v>15</v>
@@ -58746,25 +58749,25 @@
         <v>1285</v>
       </c>
       <c r="B1286" s="2" t="s">
+        <v>6287</v>
+      </c>
+      <c r="C1286" s="2" t="s">
         <v>6288</v>
       </c>
-      <c r="C1286" s="2" t="s">
+      <c r="D1286" s="2" t="s">
         <v>6289</v>
       </c>
-      <c r="D1286" s="2" t="s">
+      <c r="E1286" s="2" t="s">
         <v>6290</v>
       </c>
-      <c r="E1286" s="2" t="s">
+      <c r="F1286" s="2" t="s">
         <v>6291</v>
-      </c>
-      <c r="F1286" s="2" t="s">
-        <v>6292</v>
       </c>
       <c r="G1286" s="3">
         <v>1</v>
       </c>
       <c r="H1286" s="2" t="s">
-        <v>6293</v>
+        <v>6292</v>
       </c>
       <c r="I1286" s="2" t="s">
         <v>15</v>
@@ -58775,7 +58778,7 @@
         <v>1286</v>
       </c>
       <c r="B1287" s="2" t="s">
-        <v>6294</v>
+        <v>6293</v>
       </c>
       <c r="C1287" s="2" t="s">
         <v>912</v>
@@ -58787,13 +58790,13 @@
         <v>4056</v>
       </c>
       <c r="F1287" s="2" t="s">
-        <v>6295</v>
+        <v>6294</v>
       </c>
       <c r="G1287" s="3">
         <v>3</v>
       </c>
       <c r="H1287" s="2" t="s">
-        <v>6296</v>
+        <v>6295</v>
       </c>
       <c r="I1287" s="2" t="s">
         <v>165</v>
@@ -58804,25 +58807,25 @@
         <v>1287</v>
       </c>
       <c r="B1288" s="2" t="s">
+        <v>6296</v>
+      </c>
+      <c r="C1288" s="2" t="s">
         <v>6297</v>
-      </c>
-      <c r="C1288" s="2" t="s">
-        <v>6298</v>
       </c>
       <c r="D1288" s="2" t="s">
         <v>5266</v>
       </c>
       <c r="E1288" s="2" t="s">
+        <v>6298</v>
+      </c>
+      <c r="F1288" s="2" t="s">
         <v>6299</v>
-      </c>
-      <c r="F1288" s="2" t="s">
-        <v>6300</v>
       </c>
       <c r="G1288" s="3">
         <v>1</v>
       </c>
       <c r="H1288" s="2" t="s">
-        <v>6301</v>
+        <v>6300</v>
       </c>
       <c r="I1288" s="2" t="s">
         <v>158</v>
@@ -58833,25 +58836,25 @@
         <v>1288</v>
       </c>
       <c r="B1289" s="2" t="s">
+        <v>6301</v>
+      </c>
+      <c r="C1289" s="2" t="s">
         <v>6302</v>
       </c>
-      <c r="C1289" s="2" t="s">
+      <c r="D1289" s="2" t="s">
         <v>6303</v>
       </c>
-      <c r="D1289" s="2" t="s">
+      <c r="E1289" s="2" t="s">
         <v>6304</v>
       </c>
-      <c r="E1289" s="2" t="s">
+      <c r="F1289" s="2" t="s">
         <v>6305</v>
-      </c>
-      <c r="F1289" s="2" t="s">
-        <v>6306</v>
       </c>
       <c r="G1289" s="3">
         <v>4</v>
       </c>
       <c r="H1289" s="2" t="s">
-        <v>6307</v>
+        <v>6306</v>
       </c>
       <c r="I1289" s="2" t="s">
         <v>15</v>
@@ -58862,25 +58865,25 @@
         <v>1289</v>
       </c>
       <c r="B1290" s="2" t="s">
-        <v>6862</v>
+        <v>6856</v>
       </c>
       <c r="C1290" s="2" t="s">
-        <v>6863</v>
+        <v>6857</v>
       </c>
       <c r="D1290" s="2" t="s">
-        <v>6864</v>
+        <v>6858</v>
       </c>
       <c r="E1290" s="2" t="s">
-        <v>6308</v>
+        <v>6307</v>
       </c>
       <c r="F1290" s="2" t="s">
-        <v>6865</v>
+        <v>6859</v>
       </c>
       <c r="G1290" s="3">
         <v>3</v>
       </c>
       <c r="H1290" s="2" t="s">
-        <v>6309</v>
+        <v>6308</v>
       </c>
       <c r="I1290" s="2" t="s">
         <v>15</v>
@@ -58891,25 +58894,25 @@
         <v>1290</v>
       </c>
       <c r="B1291" s="2" t="s">
+        <v>6309</v>
+      </c>
+      <c r="C1291" s="2" t="s">
         <v>6310</v>
-      </c>
-      <c r="C1291" s="2" t="s">
-        <v>6311</v>
       </c>
       <c r="D1291" s="2" t="s">
         <v>4500</v>
       </c>
       <c r="E1291" s="2" t="s">
+        <v>6311</v>
+      </c>
+      <c r="F1291" s="2" t="s">
         <v>6312</v>
-      </c>
-      <c r="F1291" s="2" t="s">
-        <v>6313</v>
       </c>
       <c r="G1291" s="3">
         <v>1</v>
       </c>
       <c r="H1291" s="2" t="s">
-        <v>6314</v>
+        <v>6313</v>
       </c>
       <c r="I1291" s="2" t="s">
         <v>15</v>
@@ -58920,7 +58923,7 @@
         <v>1291</v>
       </c>
       <c r="B1292" s="2" t="s">
-        <v>6315</v>
+        <v>6314</v>
       </c>
       <c r="C1292" s="2" t="s">
         <v>514</v>
@@ -58932,7 +58935,7 @@
         <v>516</v>
       </c>
       <c r="F1292" s="2" t="s">
-        <v>6316</v>
+        <v>6315</v>
       </c>
       <c r="G1292" s="3">
         <v>2</v>
@@ -58949,25 +58952,25 @@
         <v>1292</v>
       </c>
       <c r="B1293" s="2" t="s">
+        <v>6316</v>
+      </c>
+      <c r="C1293" s="2" t="s">
         <v>6317</v>
       </c>
-      <c r="C1293" s="2" t="s">
+      <c r="D1293" s="2" t="s">
         <v>6318</v>
       </c>
-      <c r="D1293" s="2" t="s">
+      <c r="E1293" s="2" t="s">
         <v>6319</v>
       </c>
-      <c r="E1293" s="2" t="s">
+      <c r="F1293" s="2" t="s">
         <v>6320</v>
-      </c>
-      <c r="F1293" s="2" t="s">
-        <v>6321</v>
       </c>
       <c r="G1293" s="3">
         <v>4</v>
       </c>
       <c r="H1293" s="2" t="s">
-        <v>6322</v>
+        <v>6321</v>
       </c>
       <c r="I1293" s="2" t="s">
         <v>15</v>
@@ -58978,25 +58981,25 @@
         <v>1293</v>
       </c>
       <c r="B1294" s="2" t="s">
+        <v>6322</v>
+      </c>
+      <c r="C1294" s="2" t="s">
         <v>6323</v>
       </c>
-      <c r="C1294" s="2" t="s">
+      <c r="D1294" s="2" t="s">
         <v>6324</v>
       </c>
-      <c r="D1294" s="2" t="s">
+      <c r="E1294" s="2" t="s">
         <v>6325</v>
       </c>
-      <c r="E1294" s="2" t="s">
+      <c r="F1294" s="2" t="s">
         <v>6326</v>
-      </c>
-      <c r="F1294" s="2" t="s">
-        <v>6327</v>
       </c>
       <c r="G1294" s="3">
         <v>1</v>
       </c>
       <c r="H1294" s="2" t="s">
-        <v>6328</v>
+        <v>6327</v>
       </c>
       <c r="I1294" s="2" t="s">
         <v>15</v>
@@ -59007,25 +59010,25 @@
         <v>1294</v>
       </c>
       <c r="B1295" s="2" t="s">
-        <v>6329</v>
+        <v>6328</v>
       </c>
       <c r="C1295" s="2" t="s">
         <v>841</v>
       </c>
       <c r="D1295" s="2" t="s">
+        <v>6329</v>
+      </c>
+      <c r="E1295" s="2" t="s">
         <v>6330</v>
       </c>
-      <c r="E1295" s="2" t="s">
+      <c r="F1295" s="2" t="s">
         <v>6331</v>
-      </c>
-      <c r="F1295" s="2" t="s">
-        <v>6332</v>
       </c>
       <c r="G1295" s="3">
         <v>3</v>
       </c>
       <c r="H1295" s="2" t="s">
-        <v>6333</v>
+        <v>6332</v>
       </c>
       <c r="I1295" s="2" t="s">
         <v>165</v>
@@ -59036,25 +59039,25 @@
         <v>1295</v>
       </c>
       <c r="B1296" s="2" t="s">
+        <v>6333</v>
+      </c>
+      <c r="C1296" s="2" t="s">
         <v>6334</v>
       </c>
-      <c r="C1296" s="2" t="s">
+      <c r="D1296" s="2" t="s">
         <v>6335</v>
       </c>
-      <c r="D1296" s="2" t="s">
+      <c r="E1296" s="2" t="s">
         <v>6336</v>
       </c>
-      <c r="E1296" s="2" t="s">
+      <c r="F1296" s="2" t="s">
         <v>6337</v>
-      </c>
-      <c r="F1296" s="2" t="s">
-        <v>6338</v>
       </c>
       <c r="G1296" s="3">
         <v>3</v>
       </c>
       <c r="H1296" s="2" t="s">
-        <v>6339</v>
+        <v>6338</v>
       </c>
       <c r="I1296" s="2" t="s">
         <v>15</v>
@@ -59065,7 +59068,7 @@
         <v>1296</v>
       </c>
       <c r="B1297" s="2" t="s">
-        <v>6340</v>
+        <v>6339</v>
       </c>
       <c r="C1297" s="2" t="s">
         <v>610</v>
@@ -59077,13 +59080,13 @@
         <v>621</v>
       </c>
       <c r="F1297" s="2" t="s">
-        <v>6341</v>
+        <v>6340</v>
       </c>
       <c r="G1297" s="3">
         <v>1</v>
       </c>
       <c r="H1297" s="2" t="s">
-        <v>6342</v>
+        <v>6341</v>
       </c>
       <c r="I1297" s="2" t="s">
         <v>15</v>
@@ -59094,7 +59097,7 @@
         <v>1297</v>
       </c>
       <c r="B1298" s="2" t="s">
-        <v>6343</v>
+        <v>6342</v>
       </c>
       <c r="C1298" s="2" t="s">
         <v>582</v>
@@ -59112,7 +59115,7 @@
         <v>1</v>
       </c>
       <c r="H1298" s="2" t="s">
-        <v>6344</v>
+        <v>6343</v>
       </c>
       <c r="I1298" s="2" t="s">
         <v>15</v>
@@ -59123,7 +59126,7 @@
         <v>1298</v>
       </c>
       <c r="B1299" s="2" t="s">
-        <v>6345</v>
+        <v>6344</v>
       </c>
       <c r="C1299" s="2" t="s">
         <v>231</v>
@@ -59141,7 +59144,7 @@
         <v>2</v>
       </c>
       <c r="H1299" s="2" t="s">
-        <v>6346</v>
+        <v>6345</v>
       </c>
       <c r="I1299" s="2" t="s">
         <v>22</v>
@@ -59152,25 +59155,25 @@
         <v>1299</v>
       </c>
       <c r="B1300" s="2" t="s">
+        <v>6346</v>
+      </c>
+      <c r="C1300" s="2" t="s">
         <v>6347</v>
       </c>
-      <c r="C1300" s="2" t="s">
+      <c r="D1300" s="2" t="s">
         <v>6348</v>
       </c>
-      <c r="D1300" s="2" t="s">
+      <c r="E1300" s="2" t="s">
         <v>6349</v>
       </c>
-      <c r="E1300" s="2" t="s">
+      <c r="F1300" s="2" t="s">
         <v>6350</v>
-      </c>
-      <c r="F1300" s="2" t="s">
-        <v>6351</v>
       </c>
       <c r="G1300" s="3">
         <v>1</v>
       </c>
       <c r="H1300" s="2" t="s">
-        <v>6352</v>
+        <v>6351</v>
       </c>
       <c r="I1300" s="2" t="s">
         <v>15</v>
@@ -59181,25 +59184,25 @@
         <v>1300</v>
       </c>
       <c r="B1301" s="2" t="s">
+        <v>6352</v>
+      </c>
+      <c r="C1301" s="2" t="s">
         <v>6353</v>
       </c>
-      <c r="C1301" s="2" t="s">
+      <c r="D1301" s="2" t="s">
         <v>6354</v>
-      </c>
-      <c r="D1301" s="2" t="s">
-        <v>6355</v>
       </c>
       <c r="E1301" s="2" t="s">
         <v>119</v>
       </c>
       <c r="F1301" s="2" t="s">
-        <v>6356</v>
+        <v>6355</v>
       </c>
       <c r="G1301" s="3">
         <v>1</v>
       </c>
       <c r="H1301" s="2" t="s">
-        <v>6357</v>
+        <v>6356</v>
       </c>
       <c r="I1301" s="2" t="s">
         <v>15</v>
@@ -59210,25 +59213,25 @@
         <v>1301</v>
       </c>
       <c r="B1302" s="2" t="s">
+        <v>6357</v>
+      </c>
+      <c r="C1302" s="2" t="s">
         <v>6358</v>
       </c>
-      <c r="C1302" s="2" t="s">
+      <c r="D1302" s="2" t="s">
         <v>6359</v>
       </c>
-      <c r="D1302" s="2" t="s">
+      <c r="E1302" s="2" t="s">
         <v>6360</v>
       </c>
-      <c r="E1302" s="2" t="s">
+      <c r="F1302" s="2" t="s">
         <v>6361</v>
-      </c>
-      <c r="F1302" s="2" t="s">
-        <v>6362</v>
       </c>
       <c r="G1302" s="3">
         <v>1</v>
       </c>
       <c r="H1302" s="2" t="s">
-        <v>6363</v>
+        <v>6362</v>
       </c>
       <c r="I1302" s="2" t="s">
         <v>15</v>
@@ -59239,25 +59242,25 @@
         <v>1302</v>
       </c>
       <c r="B1303" s="2" t="s">
+        <v>6363</v>
+      </c>
+      <c r="C1303" s="2" t="s">
         <v>6364</v>
       </c>
-      <c r="C1303" s="2" t="s">
+      <c r="D1303" s="2" t="s">
         <v>6365</v>
       </c>
-      <c r="D1303" s="2" t="s">
+      <c r="E1303" s="2" t="s">
         <v>6366</v>
       </c>
-      <c r="E1303" s="2" t="s">
+      <c r="F1303" s="2" t="s">
         <v>6367</v>
-      </c>
-      <c r="F1303" s="2" t="s">
-        <v>6368</v>
       </c>
       <c r="G1303" s="3">
         <v>2</v>
       </c>
       <c r="H1303" s="2" t="s">
-        <v>6369</v>
+        <v>6368</v>
       </c>
       <c r="I1303" s="2" t="s">
         <v>15</v>
@@ -59268,25 +59271,25 @@
         <v>1303</v>
       </c>
       <c r="B1304" s="2" t="s">
+        <v>6369</v>
+      </c>
+      <c r="C1304" s="2" t="s">
         <v>6370</v>
       </c>
-      <c r="C1304" s="2" t="s">
+      <c r="D1304" s="2" t="s">
         <v>6371</v>
       </c>
-      <c r="D1304" s="2" t="s">
+      <c r="E1304" s="2" t="s">
         <v>6372</v>
       </c>
-      <c r="E1304" s="2" t="s">
+      <c r="F1304" s="2" t="s">
         <v>6373</v>
-      </c>
-      <c r="F1304" s="2" t="s">
-        <v>6374</v>
       </c>
       <c r="G1304" s="3">
         <v>3</v>
       </c>
       <c r="H1304" s="2" t="s">
-        <v>6375</v>
+        <v>6374</v>
       </c>
       <c r="I1304" s="2" t="s">
         <v>165</v>
@@ -59297,25 +59300,25 @@
         <v>1304</v>
       </c>
       <c r="B1305" s="2" t="s">
+        <v>6375</v>
+      </c>
+      <c r="C1305" s="2" t="s">
         <v>6376</v>
       </c>
-      <c r="C1305" s="2" t="s">
+      <c r="D1305" s="2" t="s">
         <v>6377</v>
       </c>
-      <c r="D1305" s="2" t="s">
+      <c r="E1305" s="2" t="s">
         <v>6378</v>
       </c>
-      <c r="E1305" s="2" t="s">
+      <c r="F1305" s="2" t="s">
         <v>6379</v>
-      </c>
-      <c r="F1305" s="2" t="s">
-        <v>6380</v>
       </c>
       <c r="G1305" s="3">
         <v>1</v>
       </c>
       <c r="H1305" s="2" t="s">
-        <v>6381</v>
+        <v>6380</v>
       </c>
       <c r="I1305" s="2" t="s">
         <v>15</v>
@@ -59326,25 +59329,25 @@
         <v>1305</v>
       </c>
       <c r="B1306" s="2" t="s">
+        <v>6381</v>
+      </c>
+      <c r="C1306" s="2" t="s">
         <v>6382</v>
       </c>
-      <c r="C1306" s="2" t="s">
+      <c r="D1306" s="2" t="s">
         <v>6383</v>
       </c>
-      <c r="D1306" s="2" t="s">
+      <c r="E1306" s="2" t="s">
         <v>6384</v>
       </c>
-      <c r="E1306" s="2" t="s">
+      <c r="F1306" s="2" t="s">
         <v>6385</v>
-      </c>
-      <c r="F1306" s="2" t="s">
-        <v>6386</v>
       </c>
       <c r="G1306" s="3">
         <v>2</v>
       </c>
       <c r="H1306" s="2" t="s">
-        <v>6387</v>
+        <v>6386</v>
       </c>
       <c r="I1306" s="2" t="s">
         <v>15</v>
@@ -59355,25 +59358,25 @@
         <v>1306</v>
       </c>
       <c r="B1307" s="2" t="s">
+        <v>6387</v>
+      </c>
+      <c r="C1307" s="2" t="s">
         <v>6388</v>
       </c>
-      <c r="C1307" s="2" t="s">
+      <c r="D1307" s="2" t="s">
         <v>6389</v>
-      </c>
-      <c r="D1307" s="2" t="s">
-        <v>6390</v>
       </c>
       <c r="E1307" s="2" t="s">
         <v>5843</v>
       </c>
       <c r="F1307" s="2" t="s">
-        <v>6391</v>
+        <v>6390</v>
       </c>
       <c r="G1307" s="3">
         <v>4</v>
       </c>
       <c r="H1307" s="2" t="s">
-        <v>6392</v>
+        <v>6391</v>
       </c>
       <c r="I1307" s="2" t="s">
         <v>15</v>
@@ -59384,7 +59387,7 @@
         <v>1307</v>
       </c>
       <c r="B1308" s="2" t="s">
-        <v>6393</v>
+        <v>6392</v>
       </c>
       <c r="C1308" s="2" t="s">
         <v>912</v>
@@ -59402,7 +59405,7 @@
         <v>3</v>
       </c>
       <c r="H1308" s="2" t="s">
-        <v>6394</v>
+        <v>6393</v>
       </c>
       <c r="I1308" s="2" t="s">
         <v>15</v>
@@ -59413,7 +59416,7 @@
         <v>1308</v>
       </c>
       <c r="B1309" s="2" t="s">
-        <v>6395</v>
+        <v>6394</v>
       </c>
       <c r="C1309" s="2" t="s">
         <v>4368</v>
@@ -59442,7 +59445,7 @@
         <v>1309</v>
       </c>
       <c r="B1310" s="2" t="s">
-        <v>6396</v>
+        <v>6395</v>
       </c>
       <c r="C1310" s="2" t="s">
         <v>4368</v>
@@ -59460,7 +59463,7 @@
         <v>1</v>
       </c>
       <c r="H1310" s="2" t="s">
-        <v>6397</v>
+        <v>6396</v>
       </c>
       <c r="I1310" s="2" t="s">
         <v>15</v>
@@ -59471,13 +59474,13 @@
         <v>1310</v>
       </c>
       <c r="B1311" s="2" t="s">
-        <v>6398</v>
+        <v>6397</v>
       </c>
       <c r="C1311" s="2" t="s">
         <v>3344</v>
       </c>
       <c r="D1311" s="2" t="s">
-        <v>5960</v>
+        <v>5959</v>
       </c>
       <c r="E1311" s="2" t="s">
         <v>1542</v>
@@ -59489,7 +59492,7 @@
         <v>2</v>
       </c>
       <c r="H1311" s="2" t="s">
-        <v>5962</v>
+        <v>5961</v>
       </c>
       <c r="I1311" s="2" t="s">
         <v>15</v>
@@ -59500,7 +59503,7 @@
         <v>1311</v>
       </c>
       <c r="B1312" s="2" t="s">
-        <v>6399</v>
+        <v>6398</v>
       </c>
       <c r="C1312" s="2" t="s">
         <v>72</v>
@@ -59509,10 +59512,10 @@
         <v>77</v>
       </c>
       <c r="E1312" s="2" t="s">
+        <v>6399</v>
+      </c>
+      <c r="F1312" s="2" t="s">
         <v>6400</v>
-      </c>
-      <c r="F1312" s="2" t="s">
-        <v>6401</v>
       </c>
       <c r="G1312" s="3">
         <v>2</v>
@@ -59529,25 +59532,25 @@
         <v>1312</v>
       </c>
       <c r="B1313" s="2" t="s">
-        <v>6402</v>
+        <v>6401</v>
       </c>
       <c r="C1313" s="2" t="s">
         <v>5449</v>
       </c>
       <c r="D1313" s="2" t="s">
+        <v>6402</v>
+      </c>
+      <c r="E1313" s="2" t="s">
         <v>6403</v>
       </c>
-      <c r="E1313" s="2" t="s">
+      <c r="F1313" s="2" t="s">
         <v>6404</v>
-      </c>
-      <c r="F1313" s="2" t="s">
-        <v>6405</v>
       </c>
       <c r="G1313" s="3">
         <v>1</v>
       </c>
       <c r="H1313" s="2" t="s">
-        <v>6406</v>
+        <v>6405</v>
       </c>
       <c r="I1313" s="2" t="s">
         <v>15</v>
@@ -59558,25 +59561,25 @@
         <v>1313</v>
       </c>
       <c r="B1314" s="2" t="s">
-        <v>6407</v>
+        <v>6406</v>
       </c>
       <c r="C1314" s="2" t="s">
-        <v>6207</v>
+        <v>6206</v>
       </c>
       <c r="D1314" s="2" t="s">
-        <v>6927</v>
+        <v>6921</v>
       </c>
       <c r="E1314" s="2" t="s">
-        <v>6926</v>
+        <v>6920</v>
       </c>
       <c r="F1314" s="2" t="s">
-        <v>6928</v>
+        <v>6922</v>
       </c>
       <c r="G1314" s="3">
         <v>3</v>
       </c>
       <c r="H1314" s="2" t="s">
-        <v>6408</v>
+        <v>6407</v>
       </c>
       <c r="I1314" s="2" t="s">
         <v>15</v>
@@ -59587,19 +59590,19 @@
         <v>1314</v>
       </c>
       <c r="B1315" s="2" t="s">
-        <v>6922</v>
+        <v>6916</v>
       </c>
       <c r="C1315" s="2" t="s">
-        <v>6409</v>
+        <v>6408</v>
       </c>
       <c r="D1315" s="2" t="s">
-        <v>6923</v>
+        <v>6917</v>
       </c>
       <c r="E1315" s="2" t="s">
-        <v>6924</v>
+        <v>6918</v>
       </c>
       <c r="F1315" s="2" t="s">
-        <v>6925</v>
+        <v>6919</v>
       </c>
       <c r="G1315" s="3">
         <v>4</v>
@@ -59616,25 +59619,25 @@
         <v>1315</v>
       </c>
       <c r="B1316" s="2" t="s">
+        <v>6409</v>
+      </c>
+      <c r="C1316" s="2" t="s">
         <v>6410</v>
       </c>
-      <c r="C1316" s="2" t="s">
+      <c r="D1316" s="2" t="s">
         <v>6411</v>
-      </c>
-      <c r="D1316" s="2" t="s">
-        <v>6412</v>
       </c>
       <c r="E1316" s="2" t="s">
         <v>5260</v>
       </c>
       <c r="F1316" s="2" t="s">
-        <v>6413</v>
+        <v>6412</v>
       </c>
       <c r="G1316" s="3">
         <v>2</v>
       </c>
       <c r="H1316" s="2" t="s">
-        <v>6414</v>
+        <v>6413</v>
       </c>
       <c r="I1316" s="2" t="s">
         <v>15</v>
@@ -59645,25 +59648,25 @@
         <v>1316</v>
       </c>
       <c r="B1317" s="2" t="s">
-        <v>6929</v>
+        <v>6923</v>
       </c>
       <c r="C1317" s="2" t="s">
+        <v>6414</v>
+      </c>
+      <c r="D1317" s="2" t="s">
         <v>6415</v>
       </c>
-      <c r="D1317" s="2" t="s">
+      <c r="E1317" s="2" t="s">
         <v>6416</v>
       </c>
-      <c r="E1317" s="2" t="s">
-        <v>6417</v>
-      </c>
       <c r="F1317" s="2" t="s">
-        <v>6930</v>
+        <v>6924</v>
       </c>
       <c r="G1317" s="3">
         <v>2</v>
       </c>
       <c r="H1317" s="2" t="s">
-        <v>6418</v>
+        <v>6417</v>
       </c>
       <c r="I1317" s="2" t="s">
         <v>829</v>
@@ -59674,25 +59677,25 @@
         <v>1317</v>
       </c>
       <c r="B1318" s="2" t="s">
+        <v>6418</v>
+      </c>
+      <c r="C1318" s="2" t="s">
         <v>6419</v>
       </c>
-      <c r="C1318" s="2" t="s">
+      <c r="D1318" s="2" t="s">
         <v>6420</v>
       </c>
-      <c r="D1318" s="2" t="s">
+      <c r="E1318" s="2" t="s">
         <v>6421</v>
       </c>
-      <c r="E1318" s="2" t="s">
+      <c r="F1318" s="2" t="s">
         <v>6422</v>
-      </c>
-      <c r="F1318" s="2" t="s">
-        <v>6423</v>
       </c>
       <c r="G1318" s="3">
         <v>1</v>
       </c>
       <c r="H1318" s="2" t="s">
-        <v>6424</v>
+        <v>6423</v>
       </c>
       <c r="I1318" s="2" t="s">
         <v>15</v>
@@ -59703,10 +59706,10 @@
         <v>1318</v>
       </c>
       <c r="B1319" s="2" t="s">
+        <v>6424</v>
+      </c>
+      <c r="C1319" s="2" t="s">
         <v>6425</v>
-      </c>
-      <c r="C1319" s="2" t="s">
-        <v>6426</v>
       </c>
       <c r="D1319" s="2" t="s">
         <v>335</v>
@@ -59715,13 +59718,13 @@
         <v>336</v>
       </c>
       <c r="F1319" s="2" t="s">
-        <v>6427</v>
+        <v>6426</v>
       </c>
       <c r="G1319" s="3">
         <v>1</v>
       </c>
       <c r="H1319" s="2" t="s">
-        <v>6428</v>
+        <v>6427</v>
       </c>
       <c r="I1319" s="2" t="s">
         <v>158</v>
@@ -59732,7 +59735,7 @@
         <v>1319</v>
       </c>
       <c r="B1320" s="2" t="s">
-        <v>6429</v>
+        <v>6428</v>
       </c>
       <c r="C1320" s="2" t="s">
         <v>242</v>
@@ -59741,16 +59744,16 @@
         <v>735</v>
       </c>
       <c r="E1320" s="2" t="s">
+        <v>6429</v>
+      </c>
+      <c r="F1320" s="2" t="s">
         <v>6430</v>
-      </c>
-      <c r="F1320" s="2" t="s">
-        <v>6431</v>
       </c>
       <c r="G1320" s="3">
         <v>2</v>
       </c>
       <c r="H1320" s="2" t="s">
-        <v>6432</v>
+        <v>6431</v>
       </c>
       <c r="I1320" s="2" t="s">
         <v>15</v>
@@ -59761,7 +59764,7 @@
         <v>1320</v>
       </c>
       <c r="B1321" s="2" t="s">
-        <v>6433</v>
+        <v>6432</v>
       </c>
       <c r="C1321" s="2" t="s">
         <v>1404</v>
@@ -59790,25 +59793,25 @@
         <v>1321</v>
       </c>
       <c r="B1322" s="2" t="s">
+        <v>6433</v>
+      </c>
+      <c r="C1322" s="2" t="s">
+        <v>6848</v>
+      </c>
+      <c r="D1322" s="2" t="s">
         <v>6434</v>
       </c>
-      <c r="C1322" s="2" t="s">
-        <v>6854</v>
-      </c>
-      <c r="D1322" s="2" t="s">
+      <c r="E1322" s="2" t="s">
         <v>6435</v>
       </c>
-      <c r="E1322" s="2" t="s">
-        <v>6436</v>
-      </c>
       <c r="F1322" s="2" t="s">
-        <v>6855</v>
+        <v>6849</v>
       </c>
       <c r="G1322" s="3">
         <v>4</v>
       </c>
       <c r="H1322" s="2" t="s">
-        <v>6437</v>
+        <v>6436</v>
       </c>
       <c r="I1322" s="2" t="s">
         <v>829</v>
@@ -59819,7 +59822,7 @@
         <v>1322</v>
       </c>
       <c r="B1323" s="2" t="s">
-        <v>6438</v>
+        <v>6437</v>
       </c>
       <c r="C1323" s="2" t="s">
         <v>1406</v>
@@ -59828,16 +59831,16 @@
         <v>1404</v>
       </c>
       <c r="E1323" s="2" t="s">
+        <v>6438</v>
+      </c>
+      <c r="F1323" s="2" t="s">
         <v>6439</v>
-      </c>
-      <c r="F1323" s="2" t="s">
-        <v>6440</v>
       </c>
       <c r="G1323" s="3">
         <v>3</v>
       </c>
       <c r="H1323" s="2" t="s">
-        <v>6441</v>
+        <v>6440</v>
       </c>
       <c r="I1323" s="2" t="s">
         <v>829</v>
@@ -59848,16 +59851,16 @@
         <v>1323</v>
       </c>
       <c r="B1324" s="2" t="s">
+        <v>6441</v>
+      </c>
+      <c r="C1324" s="2" t="s">
         <v>6442</v>
       </c>
-      <c r="C1324" s="2" t="s">
+      <c r="D1324" s="2" t="s">
         <v>6443</v>
       </c>
-      <c r="D1324" s="2" t="s">
+      <c r="E1324" s="2" t="s">
         <v>6444</v>
-      </c>
-      <c r="E1324" s="2" t="s">
-        <v>6445</v>
       </c>
       <c r="F1324" s="2" t="s">
         <v>51</v>
@@ -59877,7 +59880,7 @@
         <v>1324</v>
       </c>
       <c r="B1325" s="2" t="s">
-        <v>6446</v>
+        <v>6445</v>
       </c>
       <c r="C1325" s="2" t="s">
         <v>1404</v>
@@ -59906,7 +59909,7 @@
         <v>1325</v>
       </c>
       <c r="B1326" s="2" t="s">
-        <v>6447</v>
+        <v>6446</v>
       </c>
       <c r="C1326" s="2" t="s">
         <v>1404</v>
@@ -59915,14 +59918,14 @@
         <v>1405</v>
       </c>
       <c r="E1326" s="2" t="s">
-        <v>6448</v>
+        <v>6447</v>
       </c>
       <c r="F1326" s="2"/>
       <c r="G1326" s="3">
         <v>1</v>
       </c>
       <c r="H1326" s="2" t="s">
-        <v>6449</v>
+        <v>6448</v>
       </c>
       <c r="I1326" s="2" t="s">
         <v>829</v>
@@ -59933,25 +59936,25 @@
         <v>1326</v>
       </c>
       <c r="B1327" s="2" t="s">
+        <v>6449</v>
+      </c>
+      <c r="C1327" s="2" t="s">
         <v>6450</v>
       </c>
-      <c r="C1327" s="2" t="s">
-        <v>6451</v>
-      </c>
       <c r="D1327" s="2" t="s">
-        <v>6439</v>
+        <v>6438</v>
       </c>
       <c r="E1327" s="2" t="s">
         <v>1404</v>
       </c>
       <c r="F1327" s="2" t="s">
-        <v>6452</v>
+        <v>6451</v>
       </c>
       <c r="G1327" s="3">
         <v>3</v>
       </c>
       <c r="H1327" s="2" t="s">
-        <v>6453</v>
+        <v>6452</v>
       </c>
       <c r="I1327" s="2" t="s">
         <v>15</v>
@@ -59962,13 +59965,13 @@
         <v>1327</v>
       </c>
       <c r="B1328" s="2" t="s">
-        <v>6454</v>
+        <v>6453</v>
       </c>
       <c r="C1328" s="2" t="s">
         <v>1404</v>
       </c>
       <c r="D1328" s="2" t="s">
-        <v>6455</v>
+        <v>6454</v>
       </c>
       <c r="E1328" s="2" t="s">
         <v>1406</v>
@@ -59980,7 +59983,7 @@
         <v>2</v>
       </c>
       <c r="H1328" s="2" t="s">
-        <v>6456</v>
+        <v>6455</v>
       </c>
       <c r="I1328" s="2" t="s">
         <v>801</v>
@@ -59991,13 +59994,13 @@
         <v>1328</v>
       </c>
       <c r="B1329" s="2" t="s">
-        <v>6457</v>
+        <v>6456</v>
       </c>
       <c r="C1329" s="2" t="s">
         <v>1404</v>
       </c>
       <c r="D1329" s="2" t="s">
-        <v>6439</v>
+        <v>6438</v>
       </c>
       <c r="E1329" s="2" t="s">
         <v>1406</v>
@@ -60020,13 +60023,13 @@
         <v>1329</v>
       </c>
       <c r="B1330" s="2" t="s">
-        <v>6458</v>
+        <v>6457</v>
       </c>
       <c r="C1330" s="2" t="s">
         <v>1404</v>
       </c>
       <c r="D1330" s="2" t="s">
-        <v>6439</v>
+        <v>6438</v>
       </c>
       <c r="E1330" s="2" t="s">
         <v>1406</v>
@@ -60049,13 +60052,13 @@
         <v>1330</v>
       </c>
       <c r="B1331" s="2" t="s">
-        <v>6459</v>
+        <v>6458</v>
       </c>
       <c r="C1331" s="2" t="s">
         <v>1404</v>
       </c>
       <c r="D1331" s="2" t="s">
-        <v>6439</v>
+        <v>6438</v>
       </c>
       <c r="E1331" s="2" t="s">
         <v>1406</v>
@@ -60067,7 +60070,7 @@
         <v>2</v>
       </c>
       <c r="H1331" s="2" t="s">
-        <v>6460</v>
+        <v>6459</v>
       </c>
       <c r="I1331" s="2" t="s">
         <v>15</v>
@@ -60078,25 +60081,25 @@
         <v>1331</v>
       </c>
       <c r="B1332" s="2" t="s">
+        <v>6460</v>
+      </c>
+      <c r="C1332" s="2" t="s">
         <v>6461</v>
       </c>
-      <c r="C1332" s="2" t="s">
+      <c r="D1332" s="2" t="s">
         <v>6462</v>
       </c>
-      <c r="D1332" s="2" t="s">
+      <c r="E1332" s="2" t="s">
         <v>6463</v>
       </c>
-      <c r="E1332" s="2" t="s">
+      <c r="F1332" s="2" t="s">
         <v>6464</v>
-      </c>
-      <c r="F1332" s="2" t="s">
-        <v>6465</v>
       </c>
       <c r="G1332" s="3">
         <v>4</v>
       </c>
       <c r="H1332" s="2" t="s">
-        <v>6466</v>
+        <v>6465</v>
       </c>
       <c r="I1332" s="2" t="s">
         <v>22</v>
@@ -60107,16 +60110,16 @@
         <v>1332</v>
       </c>
       <c r="B1333" s="2" t="s">
-        <v>6467</v>
+        <v>6466</v>
       </c>
       <c r="C1333" s="2" t="s">
         <v>77</v>
       </c>
       <c r="D1333" s="2" t="s">
+        <v>6467</v>
+      </c>
+      <c r="E1333" s="2" t="s">
         <v>6468</v>
-      </c>
-      <c r="E1333" s="2" t="s">
-        <v>6469</v>
       </c>
       <c r="F1333" s="2" t="s">
         <v>2329</v>
@@ -60136,7 +60139,7 @@
         <v>1333</v>
       </c>
       <c r="B1334" s="2" t="s">
-        <v>6470</v>
+        <v>6469</v>
       </c>
       <c r="C1334" s="2" t="s">
         <v>12</v>
@@ -60148,13 +60151,13 @@
         <v>451</v>
       </c>
       <c r="F1334" s="2" t="s">
-        <v>6471</v>
+        <v>6470</v>
       </c>
       <c r="G1334" s="3">
         <v>1</v>
       </c>
       <c r="H1334" s="2" t="s">
-        <v>6472</v>
+        <v>6471</v>
       </c>
       <c r="I1334" s="2" t="s">
         <v>829</v>
@@ -60165,16 +60168,16 @@
         <v>1334</v>
       </c>
       <c r="B1335" s="2" t="s">
+        <v>6472</v>
+      </c>
+      <c r="C1335" s="2" t="s">
         <v>6473</v>
       </c>
-      <c r="C1335" s="2" t="s">
+      <c r="D1335" s="2" t="s">
         <v>6474</v>
       </c>
-      <c r="D1335" s="2" t="s">
+      <c r="E1335" s="2" t="s">
         <v>6475</v>
-      </c>
-      <c r="E1335" s="2" t="s">
-        <v>6476</v>
       </c>
       <c r="F1335" s="2" t="s">
         <v>197</v>
@@ -60194,7 +60197,7 @@
         <v>1335</v>
       </c>
       <c r="B1336" s="2" t="s">
-        <v>6477</v>
+        <v>6476</v>
       </c>
       <c r="C1336" s="2" t="s">
         <v>5090</v>
@@ -60203,16 +60206,16 @@
         <v>4999</v>
       </c>
       <c r="E1336" s="2" t="s">
+        <v>6477</v>
+      </c>
+      <c r="F1336" s="2" t="s">
         <v>6478</v>
-      </c>
-      <c r="F1336" s="2" t="s">
-        <v>6479</v>
       </c>
       <c r="G1336" s="3">
         <v>3</v>
       </c>
       <c r="H1336" s="2" t="s">
-        <v>6480</v>
+        <v>6479</v>
       </c>
       <c r="I1336" s="2" t="s">
         <v>15</v>
@@ -60223,25 +60226,25 @@
         <v>1336</v>
       </c>
       <c r="B1337" s="2" t="s">
+        <v>6480</v>
+      </c>
+      <c r="C1337" s="2" t="s">
         <v>6481</v>
       </c>
-      <c r="C1337" s="2" t="s">
+      <c r="D1337" s="2" t="s">
         <v>6482</v>
       </c>
-      <c r="D1337" s="2" t="s">
+      <c r="E1337" s="2" t="s">
         <v>6483</v>
       </c>
-      <c r="E1337" s="2" t="s">
+      <c r="F1337" s="2" t="s">
         <v>6484</v>
-      </c>
-      <c r="F1337" s="2" t="s">
-        <v>6485</v>
       </c>
       <c r="G1337" s="3">
         <v>3</v>
       </c>
       <c r="H1337" s="2" t="s">
-        <v>6486</v>
+        <v>6485</v>
       </c>
       <c r="I1337" s="2" t="s">
         <v>829</v>
@@ -60252,7 +60255,7 @@
         <v>1337</v>
       </c>
       <c r="B1338" s="2" t="s">
-        <v>6487</v>
+        <v>6486</v>
       </c>
       <c r="C1338" s="2" t="s">
         <v>516</v>
@@ -60264,13 +60267,13 @@
         <v>4999</v>
       </c>
       <c r="F1338" s="2" t="s">
-        <v>6488</v>
+        <v>6487</v>
       </c>
       <c r="G1338" s="3">
         <v>4</v>
       </c>
       <c r="H1338" s="2" t="s">
-        <v>6489</v>
+        <v>6488</v>
       </c>
       <c r="I1338" s="2" t="s">
         <v>22</v>
@@ -60281,7 +60284,7 @@
         <v>1338</v>
       </c>
       <c r="B1339" s="2" t="s">
-        <v>6490</v>
+        <v>6489</v>
       </c>
       <c r="C1339" s="2" t="s">
         <v>77</v>
@@ -60290,16 +60293,16 @@
         <v>571</v>
       </c>
       <c r="E1339" s="2" t="s">
+        <v>6490</v>
+      </c>
+      <c r="F1339" s="2" t="s">
         <v>6491</v>
-      </c>
-      <c r="F1339" s="2" t="s">
-        <v>6492</v>
       </c>
       <c r="G1339" s="3">
         <v>2</v>
       </c>
       <c r="H1339" s="2" t="s">
-        <v>6493</v>
+        <v>6492</v>
       </c>
       <c r="I1339" s="2" t="s">
         <v>829</v>
@@ -60310,7 +60313,7 @@
         <v>1339</v>
       </c>
       <c r="B1340" s="2" t="s">
-        <v>6494</v>
+        <v>6493</v>
       </c>
       <c r="C1340" s="2" t="s">
         <v>324</v>
@@ -60322,13 +60325,13 @@
         <v>330</v>
       </c>
       <c r="F1340" s="2" t="s">
-        <v>6495</v>
+        <v>6494</v>
       </c>
       <c r="G1340" s="3">
         <v>2</v>
       </c>
       <c r="H1340" s="2" t="s">
-        <v>6496</v>
+        <v>6495</v>
       </c>
       <c r="I1340" s="2" t="s">
         <v>829</v>
@@ -60339,25 +60342,25 @@
         <v>1340</v>
       </c>
       <c r="B1341" s="2" t="s">
+        <v>6496</v>
+      </c>
+      <c r="C1341" s="2" t="s">
         <v>6497</v>
       </c>
-      <c r="C1341" s="2" t="s">
+      <c r="D1341" s="2" t="s">
         <v>6498</v>
       </c>
-      <c r="D1341" s="2" t="s">
+      <c r="E1341" s="2" t="s">
+        <v>6481</v>
+      </c>
+      <c r="F1341" s="2" t="s">
         <v>6499</v>
-      </c>
-      <c r="E1341" s="2" t="s">
-        <v>6482</v>
-      </c>
-      <c r="F1341" s="2" t="s">
-        <v>6500</v>
       </c>
       <c r="G1341" s="3">
         <v>4</v>
       </c>
       <c r="H1341" s="2" t="s">
-        <v>6501</v>
+        <v>6500</v>
       </c>
       <c r="I1341" s="2" t="s">
         <v>829</v>
@@ -60368,16 +60371,16 @@
         <v>1341</v>
       </c>
       <c r="B1342" s="2" t="s">
+        <v>6501</v>
+      </c>
+      <c r="C1342" s="2" t="s">
         <v>6502</v>
       </c>
-      <c r="C1342" s="2" t="s">
+      <c r="D1342" s="2" t="s">
         <v>6503</v>
       </c>
-      <c r="D1342" s="2" t="s">
+      <c r="E1342" s="2" t="s">
         <v>6504</v>
-      </c>
-      <c r="E1342" s="2" t="s">
-        <v>6505</v>
       </c>
       <c r="F1342" s="2" t="s">
         <v>197</v>
@@ -60397,25 +60400,25 @@
         <v>1342</v>
       </c>
       <c r="B1343" s="2" t="s">
+        <v>6505</v>
+      </c>
+      <c r="C1343" s="2" t="s">
         <v>6506</v>
       </c>
-      <c r="C1343" s="2" t="s">
+      <c r="D1343" s="2" t="s">
         <v>6507</v>
       </c>
-      <c r="D1343" s="2" t="s">
+      <c r="E1343" s="2" t="s">
         <v>6508</v>
       </c>
-      <c r="E1343" s="2" t="s">
+      <c r="F1343" s="2" t="s">
         <v>6509</v>
-      </c>
-      <c r="F1343" s="2" t="s">
-        <v>6510</v>
       </c>
       <c r="G1343" s="3">
         <v>3</v>
       </c>
       <c r="H1343" s="2" t="s">
-        <v>6511</v>
+        <v>6510</v>
       </c>
       <c r="I1343" s="2" t="s">
         <v>829</v>
@@ -60426,25 +60429,25 @@
         <v>1343</v>
       </c>
       <c r="B1344" s="2" t="s">
+        <v>6511</v>
+      </c>
+      <c r="C1344" s="2" t="s">
         <v>6512</v>
       </c>
-      <c r="C1344" s="2" t="s">
+      <c r="D1344" s="2" t="s">
         <v>6513</v>
       </c>
-      <c r="D1344" s="2" t="s">
+      <c r="E1344" s="2" t="s">
         <v>6514</v>
       </c>
-      <c r="E1344" s="2" t="s">
+      <c r="F1344" s="2" t="s">
         <v>6515</v>
-      </c>
-      <c r="F1344" s="2" t="s">
-        <v>6516</v>
       </c>
       <c r="G1344" s="3">
         <v>4</v>
       </c>
       <c r="H1344" s="2" t="s">
-        <v>6517</v>
+        <v>6516</v>
       </c>
       <c r="I1344" s="2" t="s">
         <v>829</v>
@@ -60455,7 +60458,7 @@
         <v>1344</v>
       </c>
       <c r="B1345" s="2" t="s">
-        <v>6518</v>
+        <v>6517</v>
       </c>
       <c r="C1345" s="2" t="s">
         <v>514</v>
@@ -60464,7 +60467,7 @@
         <v>513</v>
       </c>
       <c r="E1345" s="2" t="s">
-        <v>6519</v>
+        <v>6518</v>
       </c>
       <c r="F1345" s="2"/>
       <c r="G1345" s="3">
@@ -60482,25 +60485,25 @@
         <v>1345</v>
       </c>
       <c r="B1346" s="2" t="s">
+        <v>6519</v>
+      </c>
+      <c r="C1346" s="2" t="s">
         <v>6520</v>
       </c>
-      <c r="C1346" s="2" t="s">
+      <c r="D1346" s="2" t="s">
         <v>6521</v>
       </c>
-      <c r="D1346" s="2" t="s">
+      <c r="E1346" s="2" t="s">
         <v>6522</v>
       </c>
-      <c r="E1346" s="2" t="s">
+      <c r="F1346" s="2" t="s">
         <v>6523</v>
-      </c>
-      <c r="F1346" s="2" t="s">
-        <v>6524</v>
       </c>
       <c r="G1346" s="3">
         <v>4</v>
       </c>
       <c r="H1346" s="2" t="s">
-        <v>6525</v>
+        <v>6524</v>
       </c>
       <c r="I1346" s="2" t="s">
         <v>15</v>
@@ -60511,25 +60514,25 @@
         <v>1346</v>
       </c>
       <c r="B1347" s="2" t="s">
-        <v>6526</v>
+        <v>6525</v>
       </c>
       <c r="C1347" s="2" t="s">
         <v>1467</v>
       </c>
       <c r="D1347" s="2" t="s">
-        <v>6527</v>
+        <v>6526</v>
       </c>
       <c r="E1347" s="2" t="s">
         <v>1141</v>
       </c>
       <c r="F1347" s="2" t="s">
-        <v>6528</v>
+        <v>6527</v>
       </c>
       <c r="G1347" s="3">
         <v>2</v>
       </c>
       <c r="H1347" s="2" t="s">
-        <v>6529</v>
+        <v>6528</v>
       </c>
       <c r="I1347" s="2" t="s">
         <v>829</v>
@@ -60540,25 +60543,25 @@
         <v>1347</v>
       </c>
       <c r="B1348" s="2" t="s">
+        <v>6529</v>
+      </c>
+      <c r="C1348" s="2" t="s">
         <v>6530</v>
       </c>
-      <c r="C1348" s="2" t="s">
+      <c r="D1348" s="2" t="s">
         <v>6531</v>
       </c>
-      <c r="D1348" s="2" t="s">
+      <c r="E1348" s="2" t="s">
         <v>6532</v>
       </c>
-      <c r="E1348" s="2" t="s">
+      <c r="F1348" s="2" t="s">
         <v>6533</v>
-      </c>
-      <c r="F1348" s="2" t="s">
-        <v>6534</v>
       </c>
       <c r="G1348" s="3">
         <v>4</v>
       </c>
       <c r="H1348" s="2" t="s">
-        <v>6535</v>
+        <v>6534</v>
       </c>
       <c r="I1348" s="2" t="s">
         <v>829</v>
@@ -60569,13 +60572,13 @@
         <v>1348</v>
       </c>
       <c r="B1349" s="2" t="s">
-        <v>6536</v>
+        <v>6535</v>
       </c>
       <c r="C1349" s="2" t="s">
         <v>119</v>
       </c>
       <c r="D1349" s="2" t="s">
-        <v>6537</v>
+        <v>6536</v>
       </c>
       <c r="E1349" s="2" t="s">
         <v>26</v>
@@ -60587,7 +60590,7 @@
         <v>4</v>
       </c>
       <c r="H1349" s="2" t="s">
-        <v>6538</v>
+        <v>6537</v>
       </c>
       <c r="I1349" s="2" t="s">
         <v>829</v>
@@ -60598,36 +60601,36 @@
         <v>1349</v>
       </c>
       <c r="B1350" s="2" t="s">
+        <v>6538</v>
+      </c>
+      <c r="C1350" s="2" t="s">
         <v>6539</v>
       </c>
-      <c r="C1350" s="2" t="s">
+      <c r="D1350" s="2" t="s">
         <v>6540</v>
       </c>
-      <c r="D1350" s="2" t="s">
+      <c r="E1350" s="2" t="s">
         <v>6541</v>
       </c>
-      <c r="E1350" s="2" t="s">
+      <c r="F1350" s="2" t="s">
         <v>6542</v>
-      </c>
-      <c r="F1350" s="2" t="s">
-        <v>6543</v>
       </c>
       <c r="G1350" s="3">
         <v>4</v>
       </c>
       <c r="H1350" s="2" t="s">
-        <v>6544</v>
+        <v>6543</v>
       </c>
       <c r="I1350" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="1351" spans="1:9" ht="46.3">
+    <row r="1351" spans="1:9" ht="30.9">
       <c r="A1351" s="2">
         <v>1350</v>
       </c>
       <c r="B1351" s="2" t="s">
-        <v>6545</v>
+        <v>6544</v>
       </c>
       <c r="C1351" s="2" t="s">
         <v>776</v>
@@ -60636,7 +60639,7 @@
         <v>403</v>
       </c>
       <c r="E1351" s="2" t="s">
-        <v>6546</v>
+        <v>6545</v>
       </c>
       <c r="F1351" s="2" t="s">
         <v>794</v>
@@ -60645,7 +60648,7 @@
         <v>1</v>
       </c>
       <c r="H1351" s="2" t="s">
-        <v>6547</v>
+        <v>6546</v>
       </c>
       <c r="I1351" s="2" t="s">
         <v>22</v>
@@ -60656,36 +60659,36 @@
         <v>1351</v>
       </c>
       <c r="B1352" s="2" t="s">
+        <v>6547</v>
+      </c>
+      <c r="C1352" s="2" t="s">
         <v>6548</v>
       </c>
-      <c r="C1352" s="2" t="s">
+      <c r="D1352" s="2" t="s">
         <v>6549</v>
       </c>
-      <c r="D1352" s="2" t="s">
+      <c r="E1352" s="2" t="s">
         <v>6550</v>
       </c>
-      <c r="E1352" s="2" t="s">
+      <c r="F1352" s="2" t="s">
         <v>6551</v>
-      </c>
-      <c r="F1352" s="2" t="s">
-        <v>6552</v>
       </c>
       <c r="G1352" s="3">
         <v>1</v>
       </c>
       <c r="H1352" s="2" t="s">
-        <v>6553</v>
+        <v>6552</v>
       </c>
       <c r="I1352" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="1353" spans="1:9" ht="46.3">
+    <row r="1353" spans="1:9" ht="30.9">
       <c r="A1353" s="2">
         <v>1352</v>
       </c>
       <c r="B1353" s="2" t="s">
-        <v>6554</v>
+        <v>6553</v>
       </c>
       <c r="C1353" s="2" t="s">
         <v>160</v>
@@ -60703,7 +60706,7 @@
         <v>1</v>
       </c>
       <c r="H1353" s="2" t="s">
-        <v>6555</v>
+        <v>6554</v>
       </c>
       <c r="I1353" s="2" t="s">
         <v>15</v>
@@ -60714,23 +60717,23 @@
         <v>1353</v>
       </c>
       <c r="B1354" s="2" t="s">
+        <v>6555</v>
+      </c>
+      <c r="C1354" s="2" t="s">
         <v>6556</v>
       </c>
-      <c r="C1354" s="2" t="s">
+      <c r="D1354" s="2" t="s">
         <v>6557</v>
       </c>
-      <c r="D1354" s="2" t="s">
+      <c r="E1354" s="2" t="s">
         <v>6558</v>
-      </c>
-      <c r="E1354" s="2" t="s">
-        <v>6559</v>
       </c>
       <c r="F1354" s="2"/>
       <c r="G1354" s="3">
         <v>1</v>
       </c>
       <c r="H1354" s="2" t="s">
-        <v>6560</v>
+        <v>6559</v>
       </c>
       <c r="I1354" s="2" t="s">
         <v>829</v>
@@ -60741,7 +60744,7 @@
         <v>1354</v>
       </c>
       <c r="B1355" s="2" t="s">
-        <v>6561</v>
+        <v>6560</v>
       </c>
       <c r="C1355" s="2" t="s">
         <v>845</v>
@@ -60757,7 +60760,7 @@
         <v>4</v>
       </c>
       <c r="H1355" s="2" t="s">
-        <v>6562</v>
+        <v>6561</v>
       </c>
       <c r="I1355" s="2" t="s">
         <v>829</v>
@@ -60768,25 +60771,25 @@
         <v>1355</v>
       </c>
       <c r="B1356" s="2" t="s">
+        <v>6562</v>
+      </c>
+      <c r="C1356" s="2" t="s">
         <v>6563</v>
       </c>
-      <c r="C1356" s="2" t="s">
+      <c r="D1356" s="2" t="s">
         <v>6564</v>
       </c>
-      <c r="D1356" s="2" t="s">
+      <c r="E1356" s="2" t="s">
         <v>6565</v>
       </c>
-      <c r="E1356" s="2" t="s">
+      <c r="F1356" s="2" t="s">
         <v>6566</v>
-      </c>
-      <c r="F1356" s="2" t="s">
-        <v>6567</v>
       </c>
       <c r="G1356" s="3">
         <v>2</v>
       </c>
       <c r="H1356" s="2" t="s">
-        <v>6568</v>
+        <v>6567</v>
       </c>
       <c r="I1356" s="2" t="s">
         <v>829</v>
@@ -60797,25 +60800,25 @@
         <v>1356</v>
       </c>
       <c r="B1357" s="2" t="s">
+        <v>6568</v>
+      </c>
+      <c r="C1357" s="2" t="s">
         <v>6569</v>
       </c>
-      <c r="C1357" s="2" t="s">
+      <c r="D1357" s="2" t="s">
         <v>6570</v>
       </c>
-      <c r="D1357" s="2" t="s">
+      <c r="E1357" s="2" t="s">
         <v>6571</v>
       </c>
-      <c r="E1357" s="2" t="s">
+      <c r="F1357" s="2" t="s">
         <v>6572</v>
-      </c>
-      <c r="F1357" s="2" t="s">
-        <v>6573</v>
       </c>
       <c r="G1357" s="3">
         <v>2</v>
       </c>
       <c r="H1357" s="2" t="s">
-        <v>6574</v>
+        <v>6573</v>
       </c>
       <c r="I1357" s="2" t="s">
         <v>829</v>
@@ -60826,25 +60829,25 @@
         <v>1357</v>
       </c>
       <c r="B1358" s="2" t="s">
+        <v>6574</v>
+      </c>
+      <c r="C1358" s="2" t="s">
         <v>6575</v>
       </c>
-      <c r="C1358" s="2" t="s">
+      <c r="D1358" s="2" t="s">
         <v>6576</v>
       </c>
-      <c r="D1358" s="2" t="s">
+      <c r="E1358" s="2" t="s">
         <v>6577</v>
       </c>
-      <c r="E1358" s="2" t="s">
+      <c r="F1358" s="2" t="s">
         <v>6578</v>
-      </c>
-      <c r="F1358" s="2" t="s">
-        <v>6579</v>
       </c>
       <c r="G1358" s="3">
         <v>4</v>
       </c>
       <c r="H1358" s="2" t="s">
-        <v>6580</v>
+        <v>6579</v>
       </c>
       <c r="I1358" s="2" t="s">
         <v>829</v>
@@ -60855,25 +60858,25 @@
         <v>1358</v>
       </c>
       <c r="B1359" s="2" t="s">
+        <v>6580</v>
+      </c>
+      <c r="C1359" s="2" t="s">
         <v>6581</v>
       </c>
-      <c r="C1359" s="2" t="s">
+      <c r="D1359" s="2" t="s">
         <v>6582</v>
       </c>
-      <c r="D1359" s="2" t="s">
+      <c r="E1359" s="2" t="s">
         <v>6583</v>
       </c>
-      <c r="E1359" s="2" t="s">
+      <c r="F1359" s="2" t="s">
         <v>6584</v>
-      </c>
-      <c r="F1359" s="2" t="s">
-        <v>6585</v>
       </c>
       <c r="G1359" s="3">
         <v>4</v>
       </c>
       <c r="H1359" s="2" t="s">
-        <v>6586</v>
+        <v>6585</v>
       </c>
       <c r="I1359" s="2" t="s">
         <v>829</v>
@@ -60884,23 +60887,23 @@
         <v>1359</v>
       </c>
       <c r="B1360" s="2" t="s">
+        <v>6586</v>
+      </c>
+      <c r="C1360" s="2" t="s">
         <v>6587</v>
-      </c>
-      <c r="C1360" s="2" t="s">
-        <v>6588</v>
       </c>
       <c r="D1360" s="2"/>
       <c r="E1360" s="2" t="s">
+        <v>6588</v>
+      </c>
+      <c r="F1360" s="2" t="s">
         <v>6589</v>
-      </c>
-      <c r="F1360" s="2" t="s">
-        <v>6590</v>
       </c>
       <c r="G1360" s="3">
         <v>1</v>
       </c>
       <c r="H1360" s="2" t="s">
-        <v>6591</v>
+        <v>6590</v>
       </c>
       <c r="I1360" s="2" t="s">
         <v>829</v>
@@ -60911,25 +60914,25 @@
         <v>1360</v>
       </c>
       <c r="B1361" s="2" t="s">
+        <v>6591</v>
+      </c>
+      <c r="C1361" s="2" t="s">
         <v>6592</v>
       </c>
-      <c r="C1361" s="2" t="s">
+      <c r="D1361" s="2" t="s">
         <v>6593</v>
       </c>
-      <c r="D1361" s="2" t="s">
+      <c r="E1361" s="2" t="s">
         <v>6594</v>
       </c>
-      <c r="E1361" s="2" t="s">
+      <c r="F1361" s="2" t="s">
         <v>6595</v>
-      </c>
-      <c r="F1361" s="2" t="s">
-        <v>6596</v>
       </c>
       <c r="G1361" s="3">
         <v>3</v>
       </c>
       <c r="H1361" s="2" t="s">
-        <v>6597</v>
+        <v>6596</v>
       </c>
       <c r="I1361" s="2" t="s">
         <v>15</v>
@@ -60940,7 +60943,7 @@
         <v>1361</v>
       </c>
       <c r="B1362" s="2" t="s">
-        <v>6598</v>
+        <v>6597</v>
       </c>
       <c r="C1362" s="2" t="s">
         <v>1334</v>
@@ -60949,10 +60952,10 @@
         <v>1335</v>
       </c>
       <c r="E1362" s="2" t="s">
+        <v>6598</v>
+      </c>
+      <c r="F1362" s="2" t="s">
         <v>6599</v>
-      </c>
-      <c r="F1362" s="2" t="s">
-        <v>6600</v>
       </c>
       <c r="G1362" s="3">
         <v>1</v>
@@ -60969,25 +60972,25 @@
         <v>1362</v>
       </c>
       <c r="B1363" s="2" t="s">
+        <v>6600</v>
+      </c>
+      <c r="C1363" s="2" t="s">
         <v>6601</v>
       </c>
-      <c r="C1363" s="2" t="s">
+      <c r="D1363" s="2" t="s">
         <v>6602</v>
       </c>
-      <c r="D1363" s="2" t="s">
+      <c r="E1363" s="2" t="s">
         <v>6603</v>
       </c>
-      <c r="E1363" s="2" t="s">
+      <c r="F1363" s="2" t="s">
         <v>6604</v>
-      </c>
-      <c r="F1363" s="2" t="s">
-        <v>6605</v>
       </c>
       <c r="G1363" s="3">
         <v>2</v>
       </c>
       <c r="H1363" s="2" t="s">
-        <v>6606</v>
+        <v>6605</v>
       </c>
       <c r="I1363" s="2" t="s">
         <v>15</v>
@@ -60998,25 +61001,25 @@
         <v>1363</v>
       </c>
       <c r="B1364" s="2" t="s">
+        <v>6606</v>
+      </c>
+      <c r="C1364" s="2" t="s">
         <v>6607</v>
       </c>
-      <c r="C1364" s="2" t="s">
+      <c r="D1364" s="2" t="s">
         <v>6608</v>
       </c>
-      <c r="D1364" s="2" t="s">
+      <c r="E1364" s="2" t="s">
         <v>6609</v>
       </c>
-      <c r="E1364" s="2" t="s">
+      <c r="F1364" s="2" t="s">
         <v>6610</v>
-      </c>
-      <c r="F1364" s="2" t="s">
-        <v>6611</v>
       </c>
       <c r="G1364" s="3">
         <v>1</v>
       </c>
       <c r="H1364" s="2" t="s">
-        <v>6612</v>
+        <v>6611</v>
       </c>
       <c r="I1364" s="2" t="s">
         <v>15</v>
@@ -61056,7 +61059,7 @@
         <v>1365</v>
       </c>
       <c r="B1366" s="2" t="s">
-        <v>6613</v>
+        <v>6612</v>
       </c>
       <c r="C1366" s="2" t="s">
         <v>1399</v>
@@ -61074,7 +61077,7 @@
         <v>3</v>
       </c>
       <c r="H1366" s="2" t="s">
-        <v>6614</v>
+        <v>6613</v>
       </c>
       <c r="I1366" s="2" t="s">
         <v>15</v>
@@ -61085,25 +61088,25 @@
         <v>1366</v>
       </c>
       <c r="B1367" s="2" t="s">
+        <v>6614</v>
+      </c>
+      <c r="C1367" s="2" t="s">
         <v>6615</v>
       </c>
-      <c r="C1367" s="2" t="s">
+      <c r="D1367" s="2" t="s">
         <v>6616</v>
       </c>
-      <c r="D1367" s="2" t="s">
+      <c r="E1367" s="2" t="s">
         <v>6617</v>
       </c>
-      <c r="E1367" s="2" t="s">
+      <c r="F1367" s="2" t="s">
         <v>6618</v>
-      </c>
-      <c r="F1367" s="2" t="s">
-        <v>6619</v>
       </c>
       <c r="G1367" s="3">
         <v>3</v>
       </c>
       <c r="H1367" s="2" t="s">
-        <v>6620</v>
+        <v>6619</v>
       </c>
       <c r="I1367" s="2" t="s">
         <v>829</v>
@@ -61114,16 +61117,16 @@
         <v>1367</v>
       </c>
       <c r="B1368" s="2" t="s">
+        <v>6620</v>
+      </c>
+      <c r="C1368" s="2" t="s">
         <v>6621</v>
       </c>
-      <c r="C1368" s="2" t="s">
+      <c r="D1368" s="2" t="s">
         <v>6622</v>
       </c>
-      <c r="D1368" s="2" t="s">
+      <c r="E1368" s="2" t="s">
         <v>6623</v>
-      </c>
-      <c r="E1368" s="2" t="s">
-        <v>6624</v>
       </c>
       <c r="F1368" s="2" t="s">
         <v>51</v>
@@ -61143,25 +61146,25 @@
         <v>1368</v>
       </c>
       <c r="B1369" s="2" t="s">
+        <v>6624</v>
+      </c>
+      <c r="C1369" s="2" t="s">
         <v>6625</v>
       </c>
-      <c r="C1369" s="2" t="s">
+      <c r="D1369" s="2" t="s">
         <v>6626</v>
       </c>
-      <c r="D1369" s="2" t="s">
+      <c r="E1369" s="2" t="s">
         <v>6627</v>
       </c>
-      <c r="E1369" s="2" t="s">
+      <c r="F1369" s="2" t="s">
         <v>6628</v>
-      </c>
-      <c r="F1369" s="2" t="s">
-        <v>6629</v>
       </c>
       <c r="G1369" s="3">
         <v>3</v>
       </c>
       <c r="H1369" s="2" t="s">
-        <v>6630</v>
+        <v>6629</v>
       </c>
       <c r="I1369" s="2" t="s">
         <v>801</v>
@@ -61172,25 +61175,25 @@
         <v>1369</v>
       </c>
       <c r="B1370" s="2" t="s">
-        <v>6631</v>
+        <v>6630</v>
       </c>
       <c r="C1370" s="2" t="s">
         <v>1692</v>
       </c>
       <c r="D1370" s="2" t="s">
+        <v>6631</v>
+      </c>
+      <c r="E1370" s="2" t="s">
         <v>6632</v>
       </c>
-      <c r="E1370" s="2" t="s">
+      <c r="F1370" s="2" t="s">
         <v>6633</v>
-      </c>
-      <c r="F1370" s="2" t="s">
-        <v>6634</v>
       </c>
       <c r="G1370" s="3">
         <v>3</v>
       </c>
       <c r="H1370" s="2" t="s">
-        <v>6635</v>
+        <v>6634</v>
       </c>
       <c r="I1370" s="2" t="s">
         <v>15</v>
@@ -61201,25 +61204,25 @@
         <v>1370</v>
       </c>
       <c r="B1371" s="2" t="s">
+        <v>6635</v>
+      </c>
+      <c r="C1371" s="2" t="s">
         <v>6636</v>
       </c>
-      <c r="C1371" s="2" t="s">
+      <c r="D1371" s="2" t="s">
         <v>6637</v>
       </c>
-      <c r="D1371" s="2" t="s">
+      <c r="E1371" s="2" t="s">
         <v>6638</v>
       </c>
-      <c r="E1371" s="2" t="s">
+      <c r="F1371" s="2" t="s">
         <v>6639</v>
-      </c>
-      <c r="F1371" s="2" t="s">
-        <v>6640</v>
       </c>
       <c r="G1371" s="3">
         <v>2</v>
       </c>
       <c r="H1371" s="2" t="s">
-        <v>6641</v>
+        <v>6640</v>
       </c>
       <c r="I1371" s="2" t="s">
         <v>15</v>
@@ -61230,13 +61233,13 @@
         <v>1371</v>
       </c>
       <c r="B1372" s="2" t="s">
-        <v>6642</v>
+        <v>6641</v>
       </c>
       <c r="C1372" s="2" t="s">
         <v>2419</v>
       </c>
       <c r="D1372" s="2" t="s">
-        <v>6643</v>
+        <v>6642</v>
       </c>
       <c r="E1372" s="2" t="s">
         <v>2420</v>
@@ -61248,7 +61251,7 @@
         <v>2</v>
       </c>
       <c r="H1372" s="2" t="s">
-        <v>6644</v>
+        <v>6643</v>
       </c>
       <c r="I1372" s="2" t="s">
         <v>15</v>
@@ -61259,25 +61262,25 @@
         <v>1372</v>
       </c>
       <c r="B1373" s="2" t="s">
-        <v>6645</v>
+        <v>6644</v>
       </c>
       <c r="C1373" s="2" t="s">
         <v>2360</v>
       </c>
       <c r="D1373" s="2" t="s">
+        <v>6645</v>
+      </c>
+      <c r="E1373" s="2" t="s">
         <v>6646</v>
       </c>
-      <c r="E1373" s="2" t="s">
+      <c r="F1373" s="2" t="s">
         <v>6647</v>
-      </c>
-      <c r="F1373" s="2" t="s">
-        <v>6648</v>
       </c>
       <c r="G1373" s="3">
         <v>2</v>
       </c>
       <c r="H1373" s="2" t="s">
-        <v>6649</v>
+        <v>6648</v>
       </c>
       <c r="I1373" s="2" t="s">
         <v>15</v>
@@ -61288,25 +61291,25 @@
         <v>1373</v>
       </c>
       <c r="B1374" s="2" t="s">
+        <v>6649</v>
+      </c>
+      <c r="C1374" s="2" t="s">
         <v>6650</v>
       </c>
-      <c r="C1374" s="2" t="s">
+      <c r="D1374" s="2" t="s">
         <v>6651</v>
       </c>
-      <c r="D1374" s="2" t="s">
+      <c r="E1374" s="2" t="s">
         <v>6652</v>
       </c>
-      <c r="E1374" s="2" t="s">
+      <c r="F1374" s="2" t="s">
         <v>6653</v>
-      </c>
-      <c r="F1374" s="2" t="s">
-        <v>6654</v>
       </c>
       <c r="G1374" s="3">
         <v>4</v>
       </c>
       <c r="H1374" s="2" t="s">
-        <v>6655</v>
+        <v>6654</v>
       </c>
       <c r="I1374" s="2" t="s">
         <v>15</v>
@@ -61317,25 +61320,25 @@
         <v>1374</v>
       </c>
       <c r="B1375" s="2" t="s">
+        <v>6655</v>
+      </c>
+      <c r="C1375" s="2" t="s">
         <v>6656</v>
       </c>
-      <c r="C1375" s="2" t="s">
+      <c r="D1375" s="2" t="s">
         <v>6657</v>
       </c>
-      <c r="D1375" s="2" t="s">
+      <c r="E1375" s="2" t="s">
         <v>6658</v>
       </c>
-      <c r="E1375" s="2" t="s">
+      <c r="F1375" s="2" t="s">
         <v>6659</v>
-      </c>
-      <c r="F1375" s="2" t="s">
-        <v>6660</v>
       </c>
       <c r="G1375" s="3">
         <v>1</v>
       </c>
       <c r="H1375" s="2" t="s">
-        <v>6661</v>
+        <v>6660</v>
       </c>
       <c r="I1375" s="2" t="s">
         <v>829</v>
@@ -61346,25 +61349,25 @@
         <v>1375</v>
       </c>
       <c r="B1376" s="2" t="s">
+        <v>6661</v>
+      </c>
+      <c r="C1376" s="2" t="s">
         <v>6662</v>
       </c>
-      <c r="C1376" s="2" t="s">
+      <c r="D1376" s="2" t="s">
         <v>6663</v>
       </c>
-      <c r="D1376" s="2" t="s">
+      <c r="E1376" s="2" t="s">
         <v>6664</v>
       </c>
-      <c r="E1376" s="2" t="s">
+      <c r="F1376" s="2" t="s">
         <v>6665</v>
-      </c>
-      <c r="F1376" s="2" t="s">
-        <v>6666</v>
       </c>
       <c r="G1376" s="3">
         <v>2</v>
       </c>
       <c r="H1376" s="2" t="s">
-        <v>6667</v>
+        <v>6666</v>
       </c>
       <c r="I1376" s="2" t="s">
         <v>829</v>
@@ -61375,25 +61378,25 @@
         <v>1376</v>
       </c>
       <c r="B1377" s="2" t="s">
+        <v>6667</v>
+      </c>
+      <c r="C1377" s="2" t="s">
         <v>6668</v>
       </c>
-      <c r="C1377" s="2" t="s">
+      <c r="D1377" s="2" t="s">
         <v>6669</v>
       </c>
-      <c r="D1377" s="2" t="s">
+      <c r="E1377" s="2" t="s">
         <v>6670</v>
       </c>
-      <c r="E1377" s="2" t="s">
+      <c r="F1377" s="2" t="s">
         <v>6671</v>
-      </c>
-      <c r="F1377" s="2" t="s">
-        <v>6672</v>
       </c>
       <c r="G1377" s="3">
         <v>3</v>
       </c>
       <c r="H1377" s="2" t="s">
-        <v>6673</v>
+        <v>6672</v>
       </c>
       <c r="I1377" s="2" t="s">
         <v>15</v>
@@ -61404,7 +61407,7 @@
         <v>1377</v>
       </c>
       <c r="B1378" s="2" t="s">
-        <v>6674</v>
+        <v>6673</v>
       </c>
       <c r="C1378" s="2" t="s">
         <v>77</v>
@@ -61433,25 +61436,25 @@
         <v>1378</v>
       </c>
       <c r="B1379" s="2" t="s">
-        <v>6675</v>
+        <v>6984</v>
       </c>
       <c r="C1379" s="2" t="s">
-        <v>6676</v>
+        <v>6985</v>
       </c>
       <c r="D1379" s="2" t="s">
-        <v>6677</v>
+        <v>6986</v>
       </c>
       <c r="E1379" s="2" t="s">
-        <v>6678</v>
+        <v>6987</v>
       </c>
       <c r="F1379" s="2" t="s">
-        <v>6679</v>
+        <v>6988</v>
       </c>
       <c r="G1379" s="3">
         <v>1</v>
       </c>
       <c r="H1379" s="2" t="s">
-        <v>6680</v>
+        <v>6674</v>
       </c>
       <c r="I1379" s="2" t="s">
         <v>829</v>
@@ -61462,7 +61465,7 @@
         <v>1379</v>
       </c>
       <c r="B1380" s="2" t="s">
-        <v>6681</v>
+        <v>6675</v>
       </c>
       <c r="C1380" s="2" t="s">
         <v>379</v>
@@ -61480,7 +61483,7 @@
         <v>1</v>
       </c>
       <c r="H1380" s="2" t="s">
-        <v>6682</v>
+        <v>6676</v>
       </c>
       <c r="I1380" s="2" t="s">
         <v>829</v>
@@ -61491,10 +61494,10 @@
         <v>1380</v>
       </c>
       <c r="B1381" s="2" t="s">
-        <v>6683</v>
+        <v>6677</v>
       </c>
       <c r="C1381" s="2" t="s">
-        <v>6684</v>
+        <v>6678</v>
       </c>
       <c r="D1381" s="2" t="s">
         <v>12</v>
@@ -61503,13 +61506,13 @@
         <v>894</v>
       </c>
       <c r="F1381" s="2" t="s">
-        <v>6685</v>
+        <v>6679</v>
       </c>
       <c r="G1381" s="3">
         <v>1</v>
       </c>
       <c r="H1381" s="2" t="s">
-        <v>6686</v>
+        <v>6680</v>
       </c>
       <c r="I1381" s="2" t="s">
         <v>829</v>
@@ -61520,25 +61523,25 @@
         <v>1381</v>
       </c>
       <c r="B1382" s="2" t="s">
-        <v>6687</v>
+        <v>6681</v>
       </c>
       <c r="C1382" s="2" t="s">
-        <v>6688</v>
+        <v>6682</v>
       </c>
       <c r="D1382" s="2" t="s">
-        <v>6689</v>
+        <v>6683</v>
       </c>
       <c r="E1382" s="2" t="s">
-        <v>6690</v>
+        <v>6684</v>
       </c>
       <c r="F1382" s="2" t="s">
-        <v>6691</v>
+        <v>6685</v>
       </c>
       <c r="G1382" s="3">
         <v>2</v>
       </c>
       <c r="H1382" s="2" t="s">
-        <v>6692</v>
+        <v>6686</v>
       </c>
       <c r="I1382" s="2" t="s">
         <v>15</v>
@@ -61549,25 +61552,25 @@
         <v>1382</v>
       </c>
       <c r="B1383" s="2" t="s">
-        <v>6693</v>
+        <v>6687</v>
       </c>
       <c r="C1383" s="2" t="s">
         <v>1477</v>
       </c>
       <c r="D1383" s="2" t="s">
-        <v>6694</v>
+        <v>6688</v>
       </c>
       <c r="E1383" s="2" t="s">
-        <v>6695</v>
+        <v>6689</v>
       </c>
       <c r="F1383" s="2" t="s">
-        <v>6696</v>
+        <v>6690</v>
       </c>
       <c r="G1383" s="3">
         <v>4</v>
       </c>
       <c r="H1383" s="2" t="s">
-        <v>6697</v>
+        <v>6691</v>
       </c>
       <c r="I1383" s="2" t="s">
         <v>15</v>
@@ -61578,25 +61581,25 @@
         <v>1383</v>
       </c>
       <c r="B1384" s="2" t="s">
-        <v>6698</v>
+        <v>6692</v>
       </c>
       <c r="C1384" s="2" t="s">
-        <v>6482</v>
+        <v>6481</v>
       </c>
       <c r="D1384" s="2" t="s">
-        <v>6699</v>
+        <v>6693</v>
       </c>
       <c r="E1384" s="2" t="s">
-        <v>6700</v>
+        <v>6694</v>
       </c>
       <c r="F1384" s="2" t="s">
-        <v>6701</v>
+        <v>6695</v>
       </c>
       <c r="G1384" s="3">
         <v>4</v>
       </c>
       <c r="H1384" s="2" t="s">
-        <v>6702</v>
+        <v>6696</v>
       </c>
       <c r="I1384" s="2" t="s">
         <v>829</v>
@@ -61607,54 +61610,54 @@
         <v>1384</v>
       </c>
       <c r="B1385" s="2" t="s">
-        <v>6703</v>
+        <v>6697</v>
       </c>
       <c r="C1385" s="2" t="s">
-        <v>6704</v>
+        <v>6698</v>
       </c>
       <c r="D1385" s="2" t="s">
-        <v>6705</v>
+        <v>6699</v>
       </c>
       <c r="E1385" s="2" t="s">
-        <v>6706</v>
+        <v>6700</v>
       </c>
       <c r="F1385" s="2" t="s">
-        <v>6707</v>
+        <v>6701</v>
       </c>
       <c r="G1385" s="3">
         <v>3</v>
       </c>
       <c r="H1385" s="2" t="s">
-        <v>6708</v>
+        <v>6702</v>
       </c>
       <c r="I1385" s="2" t="s">
         <v>829</v>
       </c>
     </row>
-    <row r="1386" spans="1:9" ht="92.6">
+    <row r="1386" spans="1:9" ht="77.150000000000006">
       <c r="A1386" s="2">
         <v>1385</v>
       </c>
       <c r="B1386" s="2" t="s">
-        <v>6709</v>
+        <v>6703</v>
       </c>
       <c r="C1386" s="2" t="s">
-        <v>6710</v>
+        <v>6704</v>
       </c>
       <c r="D1386" s="2" t="s">
-        <v>6711</v>
+        <v>6705</v>
       </c>
       <c r="E1386" s="2" t="s">
-        <v>6712</v>
+        <v>6706</v>
       </c>
       <c r="F1386" s="2" t="s">
-        <v>6713</v>
+        <v>6707</v>
       </c>
       <c r="G1386" s="3">
         <v>3</v>
       </c>
       <c r="H1386" s="2" t="s">
-        <v>6714</v>
+        <v>6708</v>
       </c>
       <c r="I1386" s="2" t="s">
         <v>15</v>
@@ -61665,25 +61668,25 @@
         <v>1386</v>
       </c>
       <c r="B1387" s="2" t="s">
-        <v>6715</v>
+        <v>6709</v>
       </c>
       <c r="C1387" s="2" t="s">
-        <v>6910</v>
+        <v>6904</v>
       </c>
       <c r="D1387" s="2" t="s">
-        <v>6911</v>
+        <v>6905</v>
       </c>
       <c r="E1387" s="2" t="s">
-        <v>6912</v>
+        <v>6906</v>
       </c>
       <c r="F1387" s="2" t="s">
-        <v>6913</v>
+        <v>6907</v>
       </c>
       <c r="G1387" s="3">
         <v>1</v>
       </c>
       <c r="H1387" s="2" t="s">
-        <v>6716</v>
+        <v>6710</v>
       </c>
       <c r="I1387" s="2" t="s">
         <v>15</v>
@@ -61694,25 +61697,25 @@
         <v>1387</v>
       </c>
       <c r="B1388" s="2" t="s">
-        <v>6717</v>
+        <v>6711</v>
       </c>
       <c r="C1388" s="2" t="s">
-        <v>6718</v>
+        <v>6712</v>
       </c>
       <c r="D1388" s="2" t="s">
         <v>44</v>
       </c>
       <c r="E1388" s="2" t="s">
-        <v>6719</v>
+        <v>6713</v>
       </c>
       <c r="F1388" s="2" t="s">
-        <v>6720</v>
+        <v>6714</v>
       </c>
       <c r="G1388" s="3">
         <v>1</v>
       </c>
       <c r="H1388" s="2" t="s">
-        <v>6721</v>
+        <v>6715</v>
       </c>
       <c r="I1388" s="2" t="s">
         <v>829</v>
@@ -61723,25 +61726,25 @@
         <v>1388</v>
       </c>
       <c r="B1389" s="2" t="s">
-        <v>6722</v>
+        <v>6716</v>
       </c>
       <c r="C1389" s="2" t="s">
-        <v>6723</v>
+        <v>6717</v>
       </c>
       <c r="D1389" s="2" t="s">
-        <v>6724</v>
+        <v>6718</v>
       </c>
       <c r="E1389" s="2" t="s">
-        <v>6725</v>
+        <v>6719</v>
       </c>
       <c r="F1389" s="2" t="s">
-        <v>6726</v>
+        <v>6720</v>
       </c>
       <c r="G1389" s="3">
         <v>1</v>
       </c>
       <c r="H1389" s="2" t="s">
-        <v>6727</v>
+        <v>6721</v>
       </c>
       <c r="I1389" s="2" t="s">
         <v>15</v>
@@ -61752,25 +61755,25 @@
         <v>1389</v>
       </c>
       <c r="B1390" s="2" t="s">
-        <v>6728</v>
+        <v>6722</v>
       </c>
       <c r="C1390" s="2" t="s">
-        <v>6729</v>
+        <v>6723</v>
       </c>
       <c r="D1390" s="2" t="s">
-        <v>6730</v>
+        <v>6724</v>
       </c>
       <c r="E1390" s="2" t="s">
-        <v>6731</v>
+        <v>6725</v>
       </c>
       <c r="F1390" s="2" t="s">
-        <v>6732</v>
+        <v>6726</v>
       </c>
       <c r="G1390" s="3">
         <v>4</v>
       </c>
       <c r="H1390" s="2" t="s">
-        <v>6733</v>
+        <v>6727</v>
       </c>
       <c r="I1390" s="2" t="s">
         <v>15</v>
@@ -61781,25 +61784,25 @@
         <v>1390</v>
       </c>
       <c r="B1391" s="2" t="s">
-        <v>6734</v>
+        <v>6728</v>
       </c>
       <c r="C1391" s="2" t="s">
-        <v>6735</v>
+        <v>6729</v>
       </c>
       <c r="D1391" s="2" t="s">
-        <v>6736</v>
+        <v>6730</v>
       </c>
       <c r="E1391" s="2" t="s">
-        <v>6737</v>
+        <v>6731</v>
       </c>
       <c r="F1391" s="2" t="s">
-        <v>6738</v>
+        <v>6732</v>
       </c>
       <c r="G1391" s="3">
         <v>1</v>
       </c>
       <c r="H1391" s="2" t="s">
-        <v>6739</v>
+        <v>6733</v>
       </c>
       <c r="I1391" s="2" t="s">
         <v>15</v>
@@ -61810,25 +61813,25 @@
         <v>1391</v>
       </c>
       <c r="B1392" s="2" t="s">
-        <v>6740</v>
+        <v>6734</v>
       </c>
       <c r="C1392" s="2" t="s">
-        <v>6741</v>
+        <v>6735</v>
       </c>
       <c r="D1392" s="2" t="s">
-        <v>6742</v>
+        <v>6736</v>
       </c>
       <c r="E1392" s="2" t="s">
-        <v>6743</v>
+        <v>6737</v>
       </c>
       <c r="F1392" s="2" t="s">
-        <v>6744</v>
+        <v>6738</v>
       </c>
       <c r="G1392" s="3">
         <v>2</v>
       </c>
       <c r="H1392" s="2" t="s">
-        <v>6745</v>
+        <v>6739</v>
       </c>
       <c r="I1392" s="2" t="s">
         <v>15</v>
@@ -61839,25 +61842,25 @@
         <v>1392</v>
       </c>
       <c r="B1393" s="2" t="s">
-        <v>6746</v>
+        <v>6740</v>
       </c>
       <c r="C1393" s="2" t="s">
-        <v>6747</v>
+        <v>6741</v>
       </c>
       <c r="D1393" s="2" t="s">
-        <v>6748</v>
+        <v>6742</v>
       </c>
       <c r="E1393" s="2" t="s">
-        <v>6749</v>
+        <v>6743</v>
       </c>
       <c r="F1393" s="2" t="s">
-        <v>6750</v>
+        <v>6744</v>
       </c>
       <c r="G1393" s="3">
         <v>4</v>
       </c>
       <c r="H1393" s="2" t="s">
-        <v>6751</v>
+        <v>6745</v>
       </c>
       <c r="I1393" s="2" t="s">
         <v>829</v>
@@ -61868,25 +61871,25 @@
         <v>1393</v>
       </c>
       <c r="B1394" s="2" t="s">
-        <v>6752</v>
+        <v>6746</v>
       </c>
       <c r="C1394" s="2" t="s">
+        <v>6741</v>
+      </c>
+      <c r="D1394" s="2" t="s">
         <v>6747</v>
       </c>
-      <c r="D1394" s="2" t="s">
-        <v>6753</v>
-      </c>
       <c r="E1394" s="2" t="s">
-        <v>6754</v>
+        <v>6748</v>
       </c>
       <c r="F1394" s="2" t="s">
-        <v>6755</v>
+        <v>6749</v>
       </c>
       <c r="G1394" s="3">
         <v>3</v>
       </c>
       <c r="H1394" s="2" t="s">
-        <v>6756</v>
+        <v>6750</v>
       </c>
       <c r="I1394" s="2" t="s">
         <v>829</v>
@@ -61897,7 +61900,7 @@
         <v>1394</v>
       </c>
       <c r="B1395" s="2" t="s">
-        <v>6757</v>
+        <v>6751</v>
       </c>
       <c r="C1395" s="2" t="s">
         <v>514</v>
@@ -61915,7 +61918,7 @@
         <v>4</v>
       </c>
       <c r="H1395" s="2" t="s">
-        <v>6758</v>
+        <v>6752</v>
       </c>
       <c r="I1395" s="2" t="s">
         <v>829</v>
@@ -61926,10 +61929,10 @@
         <v>1395</v>
       </c>
       <c r="B1396" s="2" t="s">
-        <v>6759</v>
+        <v>6753</v>
       </c>
       <c r="C1396" s="2" t="s">
-        <v>6760</v>
+        <v>6754</v>
       </c>
       <c r="D1396" s="2" t="s">
         <v>514</v>
@@ -61938,13 +61941,13 @@
         <v>513</v>
       </c>
       <c r="F1396" s="2" t="s">
-        <v>6761</v>
+        <v>6755</v>
       </c>
       <c r="G1396" s="3">
         <v>2</v>
       </c>
       <c r="H1396" s="2" t="s">
-        <v>6762</v>
+        <v>6756</v>
       </c>
       <c r="I1396" s="2" t="s">
         <v>829</v>
@@ -61955,25 +61958,25 @@
         <v>1396</v>
       </c>
       <c r="B1397" s="2" t="s">
-        <v>6763</v>
+        <v>6757</v>
       </c>
       <c r="C1397" s="2" t="s">
+        <v>6741</v>
+      </c>
+      <c r="D1397" s="2" t="s">
         <v>6747</v>
       </c>
-      <c r="D1397" s="2" t="s">
-        <v>6753</v>
-      </c>
       <c r="E1397" s="2" t="s">
-        <v>6749</v>
+        <v>6743</v>
       </c>
       <c r="F1397" s="2" t="s">
-        <v>6750</v>
+        <v>6744</v>
       </c>
       <c r="G1397" s="3">
         <v>1</v>
       </c>
       <c r="H1397" s="2" t="s">
-        <v>6764</v>
+        <v>6758</v>
       </c>
       <c r="I1397" s="2" t="s">
         <v>829</v>
@@ -61984,25 +61987,25 @@
         <v>1397</v>
       </c>
       <c r="B1398" s="2" t="s">
-        <v>6765</v>
+        <v>6759</v>
       </c>
       <c r="C1398" s="2" t="s">
+        <v>6741</v>
+      </c>
+      <c r="D1398" s="2" t="s">
         <v>6747</v>
       </c>
-      <c r="D1398" s="2" t="s">
-        <v>6753</v>
-      </c>
       <c r="E1398" s="2" t="s">
-        <v>6749</v>
+        <v>6743</v>
       </c>
       <c r="F1398" s="2" t="s">
-        <v>6750</v>
+        <v>6744</v>
       </c>
       <c r="G1398" s="3">
         <v>3</v>
       </c>
       <c r="H1398" s="2" t="s">
-        <v>6766</v>
+        <v>6760</v>
       </c>
       <c r="I1398" s="2" t="s">
         <v>829</v>
@@ -62013,7 +62016,7 @@
         <v>1398</v>
       </c>
       <c r="B1399" s="2" t="s">
-        <v>6767</v>
+        <v>6761</v>
       </c>
       <c r="C1399" s="2" t="s">
         <v>515</v>
@@ -62025,13 +62028,13 @@
         <v>513</v>
       </c>
       <c r="F1399" s="2" t="s">
-        <v>6768</v>
+        <v>6762</v>
       </c>
       <c r="G1399" s="3">
         <v>4</v>
       </c>
       <c r="H1399" s="2" t="s">
-        <v>6769</v>
+        <v>6763</v>
       </c>
       <c r="I1399" s="2" t="s">
         <v>829</v>
@@ -62042,25 +62045,25 @@
         <v>1399</v>
       </c>
       <c r="B1400" s="2" t="s">
-        <v>6770</v>
+        <v>6764</v>
       </c>
       <c r="C1400" s="2" t="s">
-        <v>6771</v>
+        <v>6765</v>
       </c>
       <c r="D1400" s="2" t="s">
-        <v>6772</v>
+        <v>6766</v>
       </c>
       <c r="E1400" s="2" t="s">
-        <v>6773</v>
+        <v>6767</v>
       </c>
       <c r="F1400" s="2" t="s">
-        <v>6774</v>
+        <v>6768</v>
       </c>
       <c r="G1400" s="3">
         <v>2</v>
       </c>
       <c r="H1400" s="2" t="s">
-        <v>6775</v>
+        <v>6769</v>
       </c>
       <c r="I1400" s="2" t="s">
         <v>829</v>
@@ -62071,25 +62074,25 @@
         <v>1400</v>
       </c>
       <c r="B1401" s="2" t="s">
-        <v>6776</v>
+        <v>6770</v>
       </c>
       <c r="C1401" s="2" t="s">
-        <v>6777</v>
+        <v>6771</v>
       </c>
       <c r="D1401" s="2" t="s">
-        <v>6778</v>
+        <v>6772</v>
       </c>
       <c r="E1401" s="2" t="s">
-        <v>6779</v>
+        <v>6773</v>
       </c>
       <c r="F1401" s="2" t="s">
-        <v>6780</v>
+        <v>6774</v>
       </c>
       <c r="G1401" s="3">
         <v>2</v>
       </c>
       <c r="H1401" s="2" t="s">
-        <v>6781</v>
+        <v>6775</v>
       </c>
       <c r="I1401" s="2" t="s">
         <v>829</v>
@@ -62100,25 +62103,25 @@
         <v>1401</v>
       </c>
       <c r="B1402" s="2" t="s">
-        <v>6782</v>
+        <v>6776</v>
       </c>
       <c r="C1402" s="2" t="s">
-        <v>6783</v>
+        <v>6777</v>
       </c>
       <c r="D1402" s="2" t="s">
-        <v>6784</v>
+        <v>6778</v>
       </c>
       <c r="E1402" s="2" t="s">
-        <v>6785</v>
+        <v>6779</v>
       </c>
       <c r="F1402" s="2" t="s">
-        <v>6786</v>
+        <v>6780</v>
       </c>
       <c r="G1402" s="3">
         <v>2</v>
       </c>
       <c r="H1402" s="2" t="s">
-        <v>6787</v>
+        <v>6781</v>
       </c>
       <c r="I1402" s="2" t="s">
         <v>15</v>
@@ -62129,25 +62132,25 @@
         <v>1402</v>
       </c>
       <c r="B1403" s="2" t="s">
-        <v>6788</v>
+        <v>6782</v>
       </c>
       <c r="C1403" s="2" t="s">
-        <v>6789</v>
+        <v>6783</v>
       </c>
       <c r="D1403" s="2" t="s">
-        <v>6790</v>
+        <v>6784</v>
       </c>
       <c r="E1403" s="2" t="s">
-        <v>6791</v>
+        <v>6785</v>
       </c>
       <c r="F1403" s="2" t="s">
-        <v>6792</v>
+        <v>6786</v>
       </c>
       <c r="G1403" s="3">
         <v>3</v>
       </c>
       <c r="H1403" s="2" t="s">
-        <v>6793</v>
+        <v>6787</v>
       </c>
       <c r="I1403" s="2" t="s">
         <v>15</v>
@@ -62158,25 +62161,25 @@
         <v>1403</v>
       </c>
       <c r="B1404" s="2" t="s">
-        <v>6794</v>
+        <v>6788</v>
       </c>
       <c r="C1404" s="2" t="s">
-        <v>6795</v>
+        <v>6789</v>
       </c>
       <c r="D1404" s="2" t="s">
-        <v>6796</v>
+        <v>6790</v>
       </c>
       <c r="E1404" s="2" t="s">
-        <v>6797</v>
+        <v>6791</v>
       </c>
       <c r="F1404" s="2" t="s">
-        <v>6798</v>
+        <v>6792</v>
       </c>
       <c r="G1404" s="3">
         <v>2</v>
       </c>
       <c r="H1404" s="2" t="s">
-        <v>6799</v>
+        <v>6793</v>
       </c>
       <c r="I1404" s="2" t="s">
         <v>15</v>
@@ -62204,10 +62207,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>6800</v>
+        <v>6794</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>6801</v>
+        <v>6795</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -62215,10 +62218,10 @@
         <v>241</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>6802</v>
+        <v>6796</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>6803</v>
+        <v>6797</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -62226,10 +62229,10 @@
         <v>491</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>6802</v>
+        <v>6796</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>6803</v>
+        <v>6797</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -62237,10 +62240,10 @@
         <v>567</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>6802</v>
+        <v>6796</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>6803</v>
+        <v>6797</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -62248,10 +62251,10 @@
         <v>703</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>6802</v>
+        <v>6796</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>6803</v>
+        <v>6797</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -62259,10 +62262,10 @@
         <v>937</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>6802</v>
+        <v>6796</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>6803</v>
+        <v>6797</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -62270,10 +62273,10 @@
         <v>1134</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>6802</v>
+        <v>6796</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>6803</v>
+        <v>6797</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -62281,10 +62284,10 @@
         <v>1188</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>6802</v>
+        <v>6796</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>6803</v>
+        <v>6797</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -62292,10 +62295,10 @@
         <v>1189</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>6802</v>
+        <v>6796</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>6803</v>
+        <v>6797</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -62303,10 +62306,10 @@
         <v>1190</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>6802</v>
+        <v>6796</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>6803</v>
+        <v>6797</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -62314,10 +62317,10 @@
         <v>1192</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>6802</v>
+        <v>6796</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>6803</v>
+        <v>6797</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -62325,10 +62328,10 @@
         <v>1193</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>6802</v>
+        <v>6796</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>6803</v>
+        <v>6797</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -62336,10 +62339,10 @@
         <v>1194</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>6802</v>
+        <v>6796</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>6803</v>
+        <v>6797</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -62347,10 +62350,10 @@
         <v>1195</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>6802</v>
+        <v>6796</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>6803</v>
+        <v>6797</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -62358,10 +62361,10 @@
         <v>1250</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>6802</v>
+        <v>6796</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>6803</v>
+        <v>6797</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -62369,10 +62372,10 @@
         <v>320</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>6804</v>
+        <v>6798</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>6805</v>
+        <v>6799</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -62380,10 +62383,10 @@
         <v>826</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>6804</v>
+        <v>6798</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>6805</v>
+        <v>6799</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -62391,10 +62394,10 @@
         <v>861</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>6804</v>
+        <v>6798</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>6805</v>
+        <v>6799</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -62402,10 +62405,10 @@
         <v>876</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>6804</v>
+        <v>6798</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>6805</v>
+        <v>6799</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -62413,10 +62416,10 @@
         <v>878</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>6804</v>
+        <v>6798</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>6805</v>
+        <v>6799</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -62424,10 +62427,10 @@
         <v>955</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>6804</v>
+        <v>6798</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>6805</v>
+        <v>6799</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -62435,10 +62438,10 @@
         <v>1064</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>6804</v>
+        <v>6798</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>6805</v>
+        <v>6799</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -62446,10 +62449,10 @@
         <v>1069</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>6804</v>
+        <v>6798</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>6805</v>
+        <v>6799</v>
       </c>
     </row>
   </sheetData>
@@ -62468,22 +62471,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="2" t="s">
-        <v>6806</v>
+        <v>6800</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="30.9">
       <c r="A2" s="2" t="s">
-        <v>6807</v>
+        <v>6801</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="30.9">
       <c r="A3" s="2" t="s">
-        <v>6808</v>
+        <v>6802</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="2" t="s">
-        <v>6809</v>
+        <v>6803</v>
       </c>
     </row>
   </sheetData>

--- a/salf/丙種職業安全衛生業務主管題庫.xlsx
+++ b/salf/丙種職業安全衛生業務主管題庫.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25f5a1833553ad9e/文件/GitHub/drher.github.io/salf/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{0E545FC3-85A4-41E9-8FD9-63F8EFFB672E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9935A1D4-FDF3-440A-9827-C1233B3EC523}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="13_ncr:1_{0E545FC3-85A4-41E9-8FD9-63F8EFFB672E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6F5C5862-D83C-4BED-8F00-562B7FF4C3BE}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9463" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20246,9 +20246,6 @@
   </si>
   <si>
     <t>傷害損失日數</t>
-  </si>
-  <si>
-    <t>總經壓工時</t>
   </si>
   <si>
     <t>失能傷害次數。</t>
@@ -21220,6 +21217,10 @@
   </si>
   <si>
     <t>重力</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>總經歷工時</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -22318,10 +22319,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
+        <v>6874</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>6875</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>6876</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>136</v>
@@ -23474,7 +23475,7 @@
         <v>64</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>6939</v>
+        <v>6938</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>352</v>
@@ -23509,7 +23510,7 @@
         <v>358</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>6940</v>
+        <v>6939</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>353</v>
@@ -23648,13 +23649,13 @@
         <v>70</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>6802</v>
+        <v>6801</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>383</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>6801</v>
+        <v>6800</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>384</v>
@@ -23677,7 +23678,7 @@
         <v>71</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>6891</v>
+        <v>6890</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>387</v>
@@ -23686,10 +23687,10 @@
         <v>388</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>6893</v>
+        <v>6892</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>6892</v>
+        <v>6891</v>
       </c>
       <c r="G72" s="3">
         <v>4</v>
@@ -24257,7 +24258,7 @@
         <v>91</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>6851</v>
+        <v>6850</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>491</v>
@@ -24269,7 +24270,7 @@
         <v>493</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>6852</v>
+        <v>6851</v>
       </c>
       <c r="G92" s="3">
         <v>4</v>
@@ -24543,7 +24544,7 @@
         <v>101</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>6828</v>
+        <v>6827</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>545</v>
@@ -24552,10 +24553,10 @@
         <v>546</v>
       </c>
       <c r="E102" s="2" t="s">
+        <v>6828</v>
+      </c>
+      <c r="F102" s="2" t="s">
         <v>6829</v>
-      </c>
-      <c r="F102" s="2" t="s">
-        <v>6830</v>
       </c>
       <c r="G102" s="3">
         <v>1</v>
@@ -25440,7 +25441,7 @@
         <v>132</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>6858</v>
+        <v>6857</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>353</v>
@@ -25449,10 +25450,10 @@
         <v>691</v>
       </c>
       <c r="E133" s="2" t="s">
+        <v>6858</v>
+      </c>
+      <c r="F133" s="2" t="s">
         <v>6859</v>
-      </c>
-      <c r="F133" s="2" t="s">
-        <v>6860</v>
       </c>
       <c r="G133" s="3">
         <v>3</v>
@@ -26206,7 +26207,7 @@
         <v>817</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>6869</v>
+        <v>6868</v>
       </c>
       <c r="G159" s="3">
         <v>3</v>
@@ -26770,7 +26771,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>6908</v>
+        <v>6907</v>
       </c>
       <c r="C179" s="2" t="s">
         <v>898</v>
@@ -27586,13 +27587,13 @@
         <v>1062</v>
       </c>
       <c r="D207" s="2" t="s">
+        <v>6786</v>
+      </c>
+      <c r="E207" s="2" t="s">
         <v>6787</v>
       </c>
-      <c r="E207" s="2" t="s">
+      <c r="F207" s="2" t="s">
         <v>6788</v>
-      </c>
-      <c r="F207" s="2" t="s">
-        <v>6789</v>
       </c>
       <c r="G207" s="3">
         <v>2</v>
@@ -29407,7 +29408,7 @@
         <v>269</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>6810</v>
+        <v>6809</v>
       </c>
       <c r="C270" s="2" t="s">
         <v>1398</v>
@@ -30712,7 +30713,7 @@
         <v>314</v>
       </c>
       <c r="B315" s="2" t="s">
-        <v>6861</v>
+        <v>6860</v>
       </c>
       <c r="C315" s="2" t="s">
         <v>1643</v>
@@ -31095,13 +31096,13 @@
         <v>1716</v>
       </c>
       <c r="D328" s="2" t="s">
-        <v>6941</v>
+        <v>6940</v>
       </c>
       <c r="E328" s="2" t="s">
         <v>1718</v>
       </c>
       <c r="F328" s="2" t="s">
-        <v>6942</v>
+        <v>6941</v>
       </c>
       <c r="G328" s="3">
         <v>4</v>
@@ -31350,19 +31351,19 @@
         <v>336</v>
       </c>
       <c r="B337" s="2" t="s">
-        <v>6848</v>
+        <v>6847</v>
       </c>
       <c r="C337" s="2" t="s">
         <v>1765</v>
       </c>
       <c r="D337" s="2" t="s">
-        <v>6849</v>
+        <v>6848</v>
       </c>
       <c r="E337" s="2" t="s">
         <v>731</v>
       </c>
       <c r="F337" s="2" t="s">
-        <v>6850</v>
+        <v>6849</v>
       </c>
       <c r="G337" s="3">
         <v>4</v>
@@ -31554,7 +31555,7 @@
         <v>1800</v>
       </c>
       <c r="C344" s="2" t="s">
-        <v>6856</v>
+        <v>6855</v>
       </c>
       <c r="D344" s="2" t="s">
         <v>1795</v>
@@ -31563,7 +31564,7 @@
         <v>1796</v>
       </c>
       <c r="F344" s="2" t="s">
-        <v>6857</v>
+        <v>6856</v>
       </c>
       <c r="G344" s="3">
         <v>1</v>
@@ -33378,16 +33379,16 @@
         <v>406</v>
       </c>
       <c r="B407" s="2" t="s">
-        <v>6872</v>
+        <v>6871</v>
       </c>
       <c r="C407" s="2" t="s">
-        <v>6874</v>
+        <v>6873</v>
       </c>
       <c r="D407" s="2" t="s">
         <v>2155</v>
       </c>
       <c r="E407" s="2" t="s">
-        <v>6873</v>
+        <v>6872</v>
       </c>
       <c r="F407" s="2" t="s">
         <v>2156</v>
@@ -34186,7 +34187,7 @@
         <v>434</v>
       </c>
       <c r="B435" s="2" t="s">
-        <v>6883</v>
+        <v>6882</v>
       </c>
       <c r="C435" s="2" t="s">
         <v>2294</v>
@@ -34198,7 +34199,7 @@
         <v>2296</v>
       </c>
       <c r="F435" s="2" t="s">
-        <v>6884</v>
+        <v>6883</v>
       </c>
       <c r="G435" s="3">
         <v>1</v>
@@ -34715,10 +34716,10 @@
         <v>2375</v>
       </c>
       <c r="E453" s="2" t="s">
-        <v>6898</v>
+        <v>6897</v>
       </c>
       <c r="F453" s="2" t="s">
-        <v>6897</v>
+        <v>6896</v>
       </c>
       <c r="G453" s="3">
         <v>1</v>
@@ -34735,7 +34736,7 @@
         <v>453</v>
       </c>
       <c r="B454" s="2" t="s">
-        <v>6894</v>
+        <v>6893</v>
       </c>
       <c r="C454" s="2" t="s">
         <v>1440</v>
@@ -34744,10 +34745,10 @@
         <v>1422</v>
       </c>
       <c r="E454" s="2" t="s">
-        <v>6896</v>
+        <v>6895</v>
       </c>
       <c r="F454" s="2" t="s">
-        <v>6895</v>
+        <v>6894</v>
       </c>
       <c r="G454" s="3">
         <v>4</v>
@@ -36181,19 +36182,19 @@
         <v>503</v>
       </c>
       <c r="B504" s="2" t="s">
+        <v>6942</v>
+      </c>
+      <c r="C504" s="2" t="s">
         <v>6943</v>
-      </c>
-      <c r="C504" s="2" t="s">
-        <v>6944</v>
       </c>
       <c r="D504" s="2" t="s">
         <v>2624</v>
       </c>
       <c r="E504" s="2" t="s">
+        <v>6944</v>
+      </c>
+      <c r="F504" s="2" t="s">
         <v>6945</v>
-      </c>
-      <c r="F504" s="2" t="s">
-        <v>6946</v>
       </c>
       <c r="G504" s="3">
         <v>4</v>
@@ -37700,13 +37701,13 @@
         <v>556</v>
       </c>
       <c r="B557" s="2" t="s">
+        <v>6792</v>
+      </c>
+      <c r="C557" s="2" t="s">
         <v>6793</v>
       </c>
-      <c r="C557" s="2" t="s">
+      <c r="D557" s="2" t="s">
         <v>6794</v>
-      </c>
-      <c r="D557" s="2" t="s">
-        <v>6795</v>
       </c>
       <c r="E557" s="2" t="s">
         <v>2880</v>
@@ -38133,19 +38134,19 @@
         <v>571</v>
       </c>
       <c r="B572" s="2" t="s">
-        <v>6974</v>
+        <v>6973</v>
       </c>
       <c r="C572" s="2" t="s">
+        <v>6916</v>
+      </c>
+      <c r="D572" s="2" t="s">
         <v>6917</v>
       </c>
-      <c r="D572" s="2" t="s">
+      <c r="E572" s="2" t="s">
+        <v>6919</v>
+      </c>
+      <c r="F572" s="2" t="s">
         <v>6918</v>
-      </c>
-      <c r="E572" s="2" t="s">
-        <v>6920</v>
-      </c>
-      <c r="F572" s="2" t="s">
-        <v>6919</v>
       </c>
       <c r="G572" s="3">
         <v>4</v>
@@ -38162,19 +38163,19 @@
         <v>572</v>
       </c>
       <c r="B573" s="2" t="s">
-        <v>6975</v>
+        <v>6974</v>
       </c>
       <c r="C573" s="2" t="s">
-        <v>6920</v>
+        <v>6919</v>
       </c>
       <c r="D573" s="2" t="s">
-        <v>6919</v>
+        <v>6918</v>
       </c>
       <c r="E573" s="2" t="s">
+        <v>6916</v>
+      </c>
+      <c r="F573" s="2" t="s">
         <v>6917</v>
-      </c>
-      <c r="F573" s="2" t="s">
-        <v>6918</v>
       </c>
       <c r="G573" s="3">
         <v>4</v>
@@ -38191,19 +38192,19 @@
         <v>573</v>
       </c>
       <c r="B574" s="2" t="s">
+        <v>6920</v>
+      </c>
+      <c r="C574" s="2" t="s">
+        <v>6918</v>
+      </c>
+      <c r="D574" s="2" t="s">
         <v>6921</v>
       </c>
-      <c r="C574" s="2" t="s">
+      <c r="E574" s="2" t="s">
+        <v>6922</v>
+      </c>
+      <c r="F574" s="2" t="s">
         <v>6919</v>
-      </c>
-      <c r="D574" s="2" t="s">
-        <v>6922</v>
-      </c>
-      <c r="E574" s="2" t="s">
-        <v>6923</v>
-      </c>
-      <c r="F574" s="2" t="s">
-        <v>6920</v>
       </c>
       <c r="G574" s="3">
         <v>2</v>
@@ -38226,7 +38227,7 @@
         <v>2962</v>
       </c>
       <c r="D575" s="2" t="s">
-        <v>6924</v>
+        <v>6923</v>
       </c>
       <c r="E575" s="2" t="s">
         <v>2963</v>
@@ -38278,19 +38279,19 @@
         <v>576</v>
       </c>
       <c r="B577" s="2" t="s">
+        <v>6929</v>
+      </c>
+      <c r="C577" s="2" t="s">
+        <v>6933</v>
+      </c>
+      <c r="D577" s="2" t="s">
         <v>6930</v>
       </c>
-      <c r="C577" s="2" t="s">
-        <v>6934</v>
-      </c>
-      <c r="D577" s="2" t="s">
+      <c r="E577" s="2" t="s">
         <v>6931</v>
       </c>
-      <c r="E577" s="2" t="s">
+      <c r="F577" s="2" t="s">
         <v>6932</v>
-      </c>
-      <c r="F577" s="2" t="s">
-        <v>6933</v>
       </c>
       <c r="G577" s="3">
         <v>3</v>
@@ -38307,19 +38308,19 @@
         <v>577</v>
       </c>
       <c r="B578" s="5" t="s">
+        <v>6924</v>
+      </c>
+      <c r="C578" s="2" t="s">
         <v>6925</v>
       </c>
-      <c r="C578" s="2" t="s">
+      <c r="D578" s="2" t="s">
         <v>6926</v>
       </c>
-      <c r="D578" s="2" t="s">
+      <c r="E578" s="2" t="s">
+        <v>6928</v>
+      </c>
+      <c r="F578" s="2" t="s">
         <v>6927</v>
-      </c>
-      <c r="E578" s="2" t="s">
-        <v>6929</v>
-      </c>
-      <c r="F578" s="2" t="s">
-        <v>6928</v>
       </c>
       <c r="G578" s="3">
         <v>1</v>
@@ -38336,16 +38337,16 @@
         <v>578</v>
       </c>
       <c r="B579" s="2" t="s">
+        <v>6934</v>
+      </c>
+      <c r="C579" s="2" t="s">
         <v>6935</v>
       </c>
-      <c r="C579" s="2" t="s">
+      <c r="D579" s="2" t="s">
         <v>6936</v>
       </c>
-      <c r="D579" s="2" t="s">
+      <c r="E579" s="2" t="s">
         <v>6937</v>
-      </c>
-      <c r="E579" s="2" t="s">
-        <v>6938</v>
       </c>
       <c r="F579" s="2" t="s">
         <v>2972</v>
@@ -39401,7 +39402,7 @@
         <v>615</v>
       </c>
       <c r="B616" s="2" t="s">
-        <v>6822</v>
+        <v>6821</v>
       </c>
       <c r="C616" s="2" t="s">
         <v>3154</v>
@@ -39517,7 +39518,7 @@
         <v>619</v>
       </c>
       <c r="B620" s="2" t="s">
-        <v>6885</v>
+        <v>6884</v>
       </c>
       <c r="C620" s="2" t="s">
         <v>3175</v>
@@ -39529,7 +39530,7 @@
         <v>3177</v>
       </c>
       <c r="F620" s="2" t="s">
-        <v>6886</v>
+        <v>6885</v>
       </c>
       <c r="G620" s="3">
         <v>4</v>
@@ -40101,7 +40102,7 @@
         <v>3282</v>
       </c>
       <c r="F640" s="2" t="s">
-        <v>6800</v>
+        <v>6799</v>
       </c>
       <c r="G640" s="3">
         <v>2</v>
@@ -40408,7 +40409,7 @@
         <v>650</v>
       </c>
       <c r="B651" s="2" t="s">
-        <v>6833</v>
+        <v>6832</v>
       </c>
       <c r="C651" s="2" t="s">
         <v>3335</v>
@@ -40417,10 +40418,10 @@
         <v>3336</v>
       </c>
       <c r="E651" s="2" t="s">
+        <v>6833</v>
+      </c>
+      <c r="F651" s="2" t="s">
         <v>6834</v>
-      </c>
-      <c r="F651" s="2" t="s">
-        <v>6835</v>
       </c>
       <c r="G651" s="3">
         <v>2</v>
@@ -40466,7 +40467,7 @@
         <v>652</v>
       </c>
       <c r="B653" s="2" t="s">
-        <v>6881</v>
+        <v>6880</v>
       </c>
       <c r="C653" s="2" t="s">
         <v>1542</v>
@@ -40478,7 +40479,7 @@
         <v>3345</v>
       </c>
       <c r="F653" s="2" t="s">
-        <v>6882</v>
+        <v>6881</v>
       </c>
       <c r="G653" s="3">
         <v>1</v>
@@ -42376,7 +42377,7 @@
         <v>718</v>
       </c>
       <c r="B719" s="2" t="s">
-        <v>6909</v>
+        <v>6908</v>
       </c>
       <c r="C719" s="2" t="s">
         <v>712</v>
@@ -42575,7 +42576,7 @@
         <v>725</v>
       </c>
       <c r="B726" s="2" t="s">
-        <v>6976</v>
+        <v>6975</v>
       </c>
       <c r="C726" s="2" t="s">
         <v>3680</v>
@@ -42584,10 +42585,10 @@
         <v>3681</v>
       </c>
       <c r="E726" s="2" t="s">
+        <v>6976</v>
+      </c>
+      <c r="F726" s="2" t="s">
         <v>6977</v>
-      </c>
-      <c r="F726" s="2" t="s">
-        <v>6978</v>
       </c>
       <c r="G726" s="3">
         <v>1</v>
@@ -42890,7 +42891,7 @@
         <v>736</v>
       </c>
       <c r="B737" s="2" t="s">
-        <v>6970</v>
+        <v>6969</v>
       </c>
       <c r="C737" s="2" t="s">
         <v>3728</v>
@@ -42919,13 +42920,13 @@
         <v>737</v>
       </c>
       <c r="B738" s="2" t="s">
+        <v>6970</v>
+      </c>
+      <c r="C738" s="2" t="s">
         <v>6971</v>
       </c>
-      <c r="C738" s="2" t="s">
+      <c r="D738" s="2" t="s">
         <v>6972</v>
-      </c>
-      <c r="D738" s="2" t="s">
-        <v>6973</v>
       </c>
       <c r="E738" s="2" t="s">
         <v>3733</v>
@@ -43038,13 +43039,13 @@
         <v>3749</v>
       </c>
       <c r="C742" s="2" t="s">
-        <v>6790</v>
+        <v>6789</v>
       </c>
       <c r="D742" s="2" t="s">
         <v>3750</v>
       </c>
       <c r="E742" s="2" t="s">
-        <v>6791</v>
+        <v>6790</v>
       </c>
       <c r="F742" s="2" t="s">
         <v>51</v>
@@ -43439,25 +43440,25 @@
         <v>755</v>
       </c>
       <c r="B756" s="2" t="s">
+        <v>6810</v>
+      </c>
+      <c r="C756" s="2" t="s">
         <v>6811</v>
       </c>
-      <c r="C756" s="2" t="s">
+      <c r="D756" s="2" t="s">
         <v>6812</v>
       </c>
-      <c r="D756" s="2" t="s">
+      <c r="E756" s="2" t="s">
         <v>6813</v>
       </c>
-      <c r="E756" s="2" t="s">
+      <c r="F756" s="2" t="s">
         <v>6814</v>
-      </c>
-      <c r="F756" s="2" t="s">
-        <v>6815</v>
       </c>
       <c r="G756" s="3">
         <v>2</v>
       </c>
       <c r="H756" s="2" t="s">
-        <v>6816</v>
+        <v>6815</v>
       </c>
       <c r="I756" s="2" t="s">
         <v>801</v>
@@ -44858,7 +44859,7 @@
         <v>804</v>
       </c>
       <c r="B805" s="2" t="s">
-        <v>6948</v>
+        <v>6947</v>
       </c>
       <c r="C805" s="2" t="s">
         <v>4028</v>
@@ -45090,13 +45091,13 @@
         <v>812</v>
       </c>
       <c r="B813" s="2" t="s">
-        <v>6879</v>
+        <v>6878</v>
       </c>
       <c r="C813" s="2" t="s">
         <v>4070</v>
       </c>
       <c r="D813" s="2" t="s">
-        <v>6880</v>
+        <v>6879</v>
       </c>
       <c r="E813" s="2" t="s">
         <v>4071</v>
@@ -45148,7 +45149,7 @@
         <v>814</v>
       </c>
       <c r="B815" s="2" t="s">
-        <v>6877</v>
+        <v>6876</v>
       </c>
       <c r="C815" s="2" t="s">
         <v>4080</v>
@@ -45160,7 +45161,7 @@
         <v>4082</v>
       </c>
       <c r="F815" s="2" t="s">
-        <v>6878</v>
+        <v>6877</v>
       </c>
       <c r="G815" s="3">
         <v>1</v>
@@ -45554,7 +45555,7 @@
         <v>828</v>
       </c>
       <c r="B829" s="2" t="s">
-        <v>6947</v>
+        <v>6946</v>
       </c>
       <c r="C829" s="2" t="s">
         <v>4149</v>
@@ -45642,16 +45643,16 @@
         <v>4165</v>
       </c>
       <c r="C832" s="2" t="s">
+        <v>6912</v>
+      </c>
+      <c r="D832" s="2" t="s">
         <v>6913</v>
       </c>
-      <c r="D832" s="2" t="s">
+      <c r="E832" s="2" t="s">
         <v>6914</v>
       </c>
-      <c r="E832" s="2" t="s">
+      <c r="F832" s="2" t="s">
         <v>6915</v>
-      </c>
-      <c r="F832" s="2" t="s">
-        <v>6916</v>
       </c>
       <c r="G832" s="3">
         <v>4</v>
@@ -46594,7 +46595,7 @@
         <v>864</v>
       </c>
       <c r="B865" s="2" t="s">
-        <v>6838</v>
+        <v>6837</v>
       </c>
       <c r="C865" s="2" t="s">
         <v>4329</v>
@@ -46603,10 +46604,10 @@
         <v>3076</v>
       </c>
       <c r="E865" s="2" t="s">
+        <v>6835</v>
+      </c>
+      <c r="F865" s="2" t="s">
         <v>6836</v>
-      </c>
-      <c r="F865" s="2" t="s">
-        <v>6837</v>
       </c>
       <c r="G865" s="3">
         <v>4</v>
@@ -46623,19 +46624,19 @@
         <v>865</v>
       </c>
       <c r="B866" s="2" t="s">
+        <v>6842</v>
+      </c>
+      <c r="C866" s="2" t="s">
         <v>6843</v>
       </c>
-      <c r="C866" s="2" t="s">
+      <c r="D866" s="4" t="s">
         <v>6844</v>
       </c>
-      <c r="D866" s="4" t="s">
+      <c r="E866" s="2" t="s">
         <v>6845</v>
       </c>
-      <c r="E866" s="2" t="s">
+      <c r="F866" s="2" t="s">
         <v>6846</v>
-      </c>
-      <c r="F866" s="2" t="s">
-        <v>6847</v>
       </c>
       <c r="G866" s="3">
         <v>3</v>
@@ -47059,7 +47060,7 @@
         <v>4408</v>
       </c>
       <c r="C881" s="2" t="s">
-        <v>6798</v>
+        <v>6797</v>
       </c>
       <c r="D881" s="2" t="s">
         <v>3076</v>
@@ -47068,7 +47069,7 @@
         <v>4409</v>
       </c>
       <c r="F881" s="2" t="s">
-        <v>6799</v>
+        <v>6798</v>
       </c>
       <c r="G881" s="3">
         <v>1</v>
@@ -47520,16 +47521,16 @@
         <v>896</v>
       </c>
       <c r="B897" s="2" t="s">
-        <v>6804</v>
+        <v>6803</v>
       </c>
       <c r="C897" s="2" t="s">
         <v>4193</v>
       </c>
       <c r="D897" s="2" t="s">
+        <v>6804</v>
+      </c>
+      <c r="E897" s="2" t="s">
         <v>6805</v>
-      </c>
-      <c r="E897" s="2" t="s">
-        <v>6806</v>
       </c>
       <c r="F897" s="2" t="s">
         <v>4282</v>
@@ -48009,19 +48010,19 @@
         <v>913</v>
       </c>
       <c r="B914" s="2" t="s">
+        <v>6948</v>
+      </c>
+      <c r="C914" s="2" t="s">
         <v>6949</v>
-      </c>
-      <c r="C914" s="2" t="s">
-        <v>6950</v>
       </c>
       <c r="D914" s="2" t="s">
         <v>4578</v>
       </c>
       <c r="E914" s="2" t="s">
+        <v>6950</v>
+      </c>
+      <c r="F914" s="2" t="s">
         <v>6951</v>
-      </c>
-      <c r="F914" s="2" t="s">
-        <v>6952</v>
       </c>
       <c r="G914" s="3">
         <v>3</v>
@@ -48293,7 +48294,7 @@
         <v>923</v>
       </c>
       <c r="B924" s="2" t="s">
-        <v>6803</v>
+        <v>6802</v>
       </c>
       <c r="C924" s="2" t="s">
         <v>3120</v>
@@ -49140,7 +49141,7 @@
         <v>4772</v>
       </c>
       <c r="F953" s="2" t="s">
-        <v>6792</v>
+        <v>6791</v>
       </c>
       <c r="G953" s="3">
         <v>3</v>
@@ -49932,19 +49933,19 @@
         <v>980</v>
       </c>
       <c r="B981" s="2" t="s">
-        <v>6862</v>
+        <v>6861</v>
       </c>
       <c r="C981" s="2" t="s">
+        <v>6863</v>
+      </c>
+      <c r="D981" s="2" t="s">
         <v>6864</v>
-      </c>
-      <c r="D981" s="2" t="s">
-        <v>6865</v>
       </c>
       <c r="E981" s="2" t="s">
         <v>4916</v>
       </c>
       <c r="F981" s="2" t="s">
-        <v>6863</v>
+        <v>6862</v>
       </c>
       <c r="G981" s="3">
         <v>2</v>
@@ -50164,19 +50165,19 @@
         <v>988</v>
       </c>
       <c r="B989" s="2" t="s">
+        <v>6822</v>
+      </c>
+      <c r="C989" s="2" t="s">
         <v>6823</v>
       </c>
-      <c r="C989" s="2" t="s">
+      <c r="D989" s="2" t="s">
         <v>6824</v>
       </c>
-      <c r="D989" s="2" t="s">
+      <c r="E989" s="2" t="s">
         <v>6825</v>
       </c>
-      <c r="E989" s="2" t="s">
+      <c r="F989" s="2" t="s">
         <v>6826</v>
-      </c>
-      <c r="F989" s="2" t="s">
-        <v>6827</v>
       </c>
       <c r="G989" s="3">
         <v>3</v>
@@ -50946,16 +50947,16 @@
         <v>5059</v>
       </c>
       <c r="C1016" s="2" t="s">
+        <v>6952</v>
+      </c>
+      <c r="D1016" s="2" t="s">
         <v>6953</v>
-      </c>
-      <c r="D1016" s="2" t="s">
-        <v>6954</v>
       </c>
       <c r="E1016" s="2" t="s">
         <v>5060</v>
       </c>
       <c r="F1016" s="2" t="s">
-        <v>6955</v>
+        <v>6954</v>
       </c>
       <c r="G1016" s="3">
         <v>1</v>
@@ -50972,7 +50973,7 @@
         <v>1016</v>
       </c>
       <c r="B1017" s="2" t="s">
-        <v>6956</v>
+        <v>6955</v>
       </c>
       <c r="C1017" s="2" t="s">
         <v>5062</v>
@@ -51233,7 +51234,7 @@
         <v>1025</v>
       </c>
       <c r="B1026" s="2" t="s">
-        <v>6866</v>
+        <v>6865</v>
       </c>
       <c r="C1026" s="2" t="s">
         <v>5104</v>
@@ -51242,10 +51243,10 @@
         <v>998</v>
       </c>
       <c r="E1026" s="2" t="s">
+        <v>6866</v>
+      </c>
+      <c r="F1026" s="2" t="s">
         <v>6867</v>
-      </c>
-      <c r="F1026" s="2" t="s">
-        <v>6868</v>
       </c>
       <c r="G1026" s="3">
         <v>1</v>
@@ -51610,7 +51611,7 @@
         <v>1038</v>
       </c>
       <c r="B1039" s="2" t="s">
-        <v>6959</v>
+        <v>6958</v>
       </c>
       <c r="C1039" s="2" t="s">
         <v>5171</v>
@@ -51619,10 +51620,10 @@
         <v>5172</v>
       </c>
       <c r="E1039" s="2" t="s">
+        <v>6956</v>
+      </c>
+      <c r="F1039" s="2" t="s">
         <v>6957</v>
-      </c>
-      <c r="F1039" s="2" t="s">
-        <v>6958</v>
       </c>
       <c r="G1039" s="3">
         <v>2</v>
@@ -51639,19 +51640,19 @@
         <v>1039</v>
       </c>
       <c r="B1040" s="2" t="s">
+        <v>6816</v>
+      </c>
+      <c r="C1040" s="2" t="s">
         <v>6817</v>
       </c>
-      <c r="C1040" s="2" t="s">
+      <c r="D1040" s="2" t="s">
         <v>6818</v>
       </c>
-      <c r="D1040" s="2" t="s">
+      <c r="E1040" s="2" t="s">
         <v>6819</v>
       </c>
-      <c r="E1040" s="2" t="s">
+      <c r="F1040" s="2" t="s">
         <v>6820</v>
-      </c>
-      <c r="F1040" s="2" t="s">
-        <v>6821</v>
       </c>
       <c r="G1040" s="3">
         <v>4</v>
@@ -52878,7 +52879,7 @@
         <v>1082</v>
       </c>
       <c r="B1083" s="2" t="s">
-        <v>6960</v>
+        <v>6959</v>
       </c>
       <c r="C1083" s="2" t="s">
         <v>5386</v>
@@ -53902,10 +53903,10 @@
         <v>5552</v>
       </c>
       <c r="E1118" s="2" t="s">
-        <v>6797</v>
+        <v>6796</v>
       </c>
       <c r="F1118" s="2" t="s">
-        <v>6796</v>
+        <v>6795</v>
       </c>
       <c r="G1118" s="3">
         <v>4</v>
@@ -55711,10 +55712,10 @@
         <v>1181</v>
       </c>
       <c r="B1182" s="2" t="s">
+        <v>6909</v>
+      </c>
+      <c r="C1182" s="2" t="s">
         <v>6910</v>
-      </c>
-      <c r="C1182" s="2" t="s">
-        <v>6911</v>
       </c>
       <c r="D1182" s="2" t="s">
         <v>5845</v>
@@ -55723,7 +55724,7 @@
         <v>1823</v>
       </c>
       <c r="F1182" s="2" t="s">
-        <v>6912</v>
+        <v>6911</v>
       </c>
       <c r="G1182" s="3">
         <v>4</v>
@@ -55769,7 +55770,7 @@
         <v>1183</v>
       </c>
       <c r="B1184" s="2" t="s">
-        <v>6961</v>
+        <v>6960</v>
       </c>
       <c r="C1184" s="2" t="s">
         <v>4360</v>
@@ -56610,7 +56611,7 @@
         <v>1212</v>
       </c>
       <c r="B1213" s="2" t="s">
-        <v>6964</v>
+        <v>6963</v>
       </c>
       <c r="C1213" s="2" t="s">
         <v>5938</v>
@@ -56674,13 +56675,13 @@
         <v>5948</v>
       </c>
       <c r="D1215" s="2" t="s">
-        <v>6962</v>
+        <v>6961</v>
       </c>
       <c r="E1215" s="2" t="s">
         <v>5949</v>
       </c>
       <c r="F1215" s="2" t="s">
-        <v>6963</v>
+        <v>6962</v>
       </c>
       <c r="G1215" s="3">
         <v>4</v>
@@ -57045,7 +57046,7 @@
         <v>1227</v>
       </c>
       <c r="B1228" s="2" t="s">
-        <v>6807</v>
+        <v>6806</v>
       </c>
       <c r="C1228" s="2" t="s">
         <v>6007</v>
@@ -57054,10 +57055,10 @@
         <v>6008</v>
       </c>
       <c r="E1228" s="2" t="s">
+        <v>6807</v>
+      </c>
+      <c r="F1228" s="2" t="s">
         <v>6808</v>
-      </c>
-      <c r="F1228" s="2" t="s">
-        <v>6809</v>
       </c>
       <c r="G1228" s="3">
         <v>4</v>
@@ -57421,10 +57422,10 @@
         <v>6061</v>
       </c>
       <c r="C1241" s="2" t="s">
+        <v>6869</v>
+      </c>
+      <c r="D1241" s="2" t="s">
         <v>6870</v>
-      </c>
-      <c r="D1241" s="2" t="s">
-        <v>6871</v>
       </c>
       <c r="E1241" s="2" t="s">
         <v>5987</v>
@@ -58692,10 +58693,10 @@
         <v>1284</v>
       </c>
       <c r="B1285" s="2" t="s">
+        <v>6852</v>
+      </c>
+      <c r="C1285" s="2" t="s">
         <v>6853</v>
-      </c>
-      <c r="C1285" s="2" t="s">
-        <v>6854</v>
       </c>
       <c r="D1285" s="2" t="s">
         <v>3317</v>
@@ -58704,7 +58705,7 @@
         <v>6278</v>
       </c>
       <c r="F1285" s="2" t="s">
-        <v>6855</v>
+        <v>6854</v>
       </c>
       <c r="G1285" s="3">
         <v>2</v>
@@ -58837,19 +58838,19 @@
         <v>1289</v>
       </c>
       <c r="B1290" s="2" t="s">
+        <v>6838</v>
+      </c>
+      <c r="C1290" s="2" t="s">
         <v>6839</v>
       </c>
-      <c r="C1290" s="2" t="s">
+      <c r="D1290" s="2" t="s">
         <v>6840</v>
-      </c>
-      <c r="D1290" s="2" t="s">
-        <v>6841</v>
       </c>
       <c r="E1290" s="2" t="s">
         <v>6300</v>
       </c>
       <c r="F1290" s="2" t="s">
-        <v>6842</v>
+        <v>6841</v>
       </c>
       <c r="G1290" s="3">
         <v>3</v>
@@ -59539,13 +59540,13 @@
         <v>6199</v>
       </c>
       <c r="D1314" s="2" t="s">
+        <v>6903</v>
+      </c>
+      <c r="E1314" s="2" t="s">
+        <v>6902</v>
+      </c>
+      <c r="F1314" s="2" t="s">
         <v>6904</v>
-      </c>
-      <c r="E1314" s="2" t="s">
-        <v>6903</v>
-      </c>
-      <c r="F1314" s="2" t="s">
-        <v>6905</v>
       </c>
       <c r="G1314" s="3">
         <v>3</v>
@@ -59562,19 +59563,19 @@
         <v>1314</v>
       </c>
       <c r="B1315" s="2" t="s">
-        <v>6899</v>
+        <v>6898</v>
       </c>
       <c r="C1315" s="2" t="s">
         <v>6401</v>
       </c>
       <c r="D1315" s="2" t="s">
+        <v>6899</v>
+      </c>
+      <c r="E1315" s="2" t="s">
         <v>6900</v>
       </c>
-      <c r="E1315" s="2" t="s">
+      <c r="F1315" s="2" t="s">
         <v>6901</v>
-      </c>
-      <c r="F1315" s="2" t="s">
-        <v>6902</v>
       </c>
       <c r="G1315" s="3">
         <v>4</v>
@@ -59620,7 +59621,7 @@
         <v>1316</v>
       </c>
       <c r="B1317" s="2" t="s">
-        <v>6906</v>
+        <v>6905</v>
       </c>
       <c r="C1317" s="2" t="s">
         <v>6407</v>
@@ -59632,7 +59633,7 @@
         <v>6409</v>
       </c>
       <c r="F1317" s="2" t="s">
-        <v>6907</v>
+        <v>6906</v>
       </c>
       <c r="G1317" s="3">
         <v>2</v>
@@ -59768,7 +59769,7 @@
         <v>6426</v>
       </c>
       <c r="C1322" s="2" t="s">
-        <v>6831</v>
+        <v>6830</v>
       </c>
       <c r="D1322" s="2" t="s">
         <v>6427</v>
@@ -59777,7 +59778,7 @@
         <v>6428</v>
       </c>
       <c r="F1322" s="2" t="s">
-        <v>6832</v>
+        <v>6831</v>
       </c>
       <c r="G1322" s="3">
         <v>4</v>
@@ -61408,19 +61409,19 @@
         <v>1378</v>
       </c>
       <c r="B1379" s="2" t="s">
+        <v>6964</v>
+      </c>
+      <c r="C1379" s="2" t="s">
         <v>6965</v>
       </c>
-      <c r="C1379" s="2" t="s">
+      <c r="D1379" s="2" t="s">
         <v>6966</v>
       </c>
-      <c r="D1379" s="2" t="s">
+      <c r="E1379" s="2" t="s">
         <v>6967</v>
       </c>
-      <c r="E1379" s="2" t="s">
+      <c r="F1379" s="2" t="s">
         <v>6968</v>
-      </c>
-      <c r="F1379" s="2" t="s">
-        <v>6969</v>
       </c>
       <c r="G1379" s="3">
         <v>1</v>
@@ -61643,16 +61644,16 @@
         <v>6702</v>
       </c>
       <c r="C1387" s="2" t="s">
+        <v>6886</v>
+      </c>
+      <c r="D1387" s="2" t="s">
         <v>6887</v>
       </c>
-      <c r="D1387" s="2" t="s">
+      <c r="E1387" s="2" t="s">
         <v>6888</v>
       </c>
-      <c r="E1387" s="2" t="s">
+      <c r="F1387" s="2" t="s">
         <v>6889</v>
-      </c>
-      <c r="F1387" s="2" t="s">
-        <v>6890</v>
       </c>
       <c r="G1387" s="3">
         <v>1</v>
@@ -61852,16 +61853,16 @@
         <v>6740</v>
       </c>
       <c r="E1394" s="2" t="s">
+        <v>6978</v>
+      </c>
+      <c r="F1394" s="2" t="s">
         <v>6741</v>
-      </c>
-      <c r="F1394" s="2" t="s">
-        <v>6742</v>
       </c>
       <c r="G1394" s="3">
         <v>3</v>
       </c>
       <c r="H1394" s="2" t="s">
-        <v>6743</v>
+        <v>6742</v>
       </c>
       <c r="I1394" s="2" t="s">
         <v>829</v>
@@ -61872,7 +61873,7 @@
         <v>1394</v>
       </c>
       <c r="B1395" s="2" t="s">
-        <v>6744</v>
+        <v>6743</v>
       </c>
       <c r="C1395" s="2" t="s">
         <v>514</v>
@@ -61890,7 +61891,7 @@
         <v>4</v>
       </c>
       <c r="H1395" s="2" t="s">
-        <v>6745</v>
+        <v>6744</v>
       </c>
       <c r="I1395" s="2" t="s">
         <v>829</v>
@@ -61901,10 +61902,10 @@
         <v>1395</v>
       </c>
       <c r="B1396" s="2" t="s">
+        <v>6745</v>
+      </c>
+      <c r="C1396" s="2" t="s">
         <v>6746</v>
-      </c>
-      <c r="C1396" s="2" t="s">
-        <v>6747</v>
       </c>
       <c r="D1396" s="2" t="s">
         <v>514</v>
@@ -61913,13 +61914,13 @@
         <v>513</v>
       </c>
       <c r="F1396" s="2" t="s">
-        <v>6748</v>
+        <v>6747</v>
       </c>
       <c r="G1396" s="3">
         <v>2</v>
       </c>
       <c r="H1396" s="2" t="s">
-        <v>6749</v>
+        <v>6748</v>
       </c>
       <c r="I1396" s="2" t="s">
         <v>829</v>
@@ -61930,7 +61931,7 @@
         <v>1396</v>
       </c>
       <c r="B1397" s="2" t="s">
-        <v>6750</v>
+        <v>6749</v>
       </c>
       <c r="C1397" s="2" t="s">
         <v>6734</v>
@@ -61948,7 +61949,7 @@
         <v>1</v>
       </c>
       <c r="H1397" s="2" t="s">
-        <v>6751</v>
+        <v>6750</v>
       </c>
       <c r="I1397" s="2" t="s">
         <v>829</v>
@@ -61959,7 +61960,7 @@
         <v>1397</v>
       </c>
       <c r="B1398" s="2" t="s">
-        <v>6752</v>
+        <v>6751</v>
       </c>
       <c r="C1398" s="2" t="s">
         <v>6734</v>
@@ -61977,7 +61978,7 @@
         <v>3</v>
       </c>
       <c r="H1398" s="2" t="s">
-        <v>6753</v>
+        <v>6752</v>
       </c>
       <c r="I1398" s="2" t="s">
         <v>829</v>
@@ -61988,7 +61989,7 @@
         <v>1398</v>
       </c>
       <c r="B1399" s="2" t="s">
-        <v>6754</v>
+        <v>6753</v>
       </c>
       <c r="C1399" s="2" t="s">
         <v>515</v>
@@ -62000,13 +62001,13 @@
         <v>513</v>
       </c>
       <c r="F1399" s="2" t="s">
-        <v>6755</v>
+        <v>6754</v>
       </c>
       <c r="G1399" s="3">
         <v>4</v>
       </c>
       <c r="H1399" s="2" t="s">
-        <v>6756</v>
+        <v>6755</v>
       </c>
       <c r="I1399" s="2" t="s">
         <v>829</v>
@@ -62017,25 +62018,25 @@
         <v>1399</v>
       </c>
       <c r="B1400" s="2" t="s">
+        <v>6756</v>
+      </c>
+      <c r="C1400" s="2" t="s">
         <v>6757</v>
       </c>
-      <c r="C1400" s="2" t="s">
+      <c r="D1400" s="2" t="s">
         <v>6758</v>
       </c>
-      <c r="D1400" s="2" t="s">
+      <c r="E1400" s="2" t="s">
         <v>6759</v>
       </c>
-      <c r="E1400" s="2" t="s">
+      <c r="F1400" s="2" t="s">
         <v>6760</v>
-      </c>
-      <c r="F1400" s="2" t="s">
-        <v>6761</v>
       </c>
       <c r="G1400" s="3">
         <v>2</v>
       </c>
       <c r="H1400" s="2" t="s">
-        <v>6762</v>
+        <v>6761</v>
       </c>
       <c r="I1400" s="2" t="s">
         <v>829</v>
@@ -62046,25 +62047,25 @@
         <v>1400</v>
       </c>
       <c r="B1401" s="2" t="s">
+        <v>6762</v>
+      </c>
+      <c r="C1401" s="2" t="s">
         <v>6763</v>
       </c>
-      <c r="C1401" s="2" t="s">
+      <c r="D1401" s="2" t="s">
         <v>6764</v>
       </c>
-      <c r="D1401" s="2" t="s">
+      <c r="E1401" s="2" t="s">
         <v>6765</v>
       </c>
-      <c r="E1401" s="2" t="s">
+      <c r="F1401" s="2" t="s">
         <v>6766</v>
-      </c>
-      <c r="F1401" s="2" t="s">
-        <v>6767</v>
       </c>
       <c r="G1401" s="3">
         <v>2</v>
       </c>
       <c r="H1401" s="2" t="s">
-        <v>6768</v>
+        <v>6767</v>
       </c>
       <c r="I1401" s="2" t="s">
         <v>829</v>
@@ -62075,25 +62076,25 @@
         <v>1401</v>
       </c>
       <c r="B1402" s="2" t="s">
+        <v>6768</v>
+      </c>
+      <c r="C1402" s="2" t="s">
         <v>6769</v>
       </c>
-      <c r="C1402" s="2" t="s">
+      <c r="D1402" s="2" t="s">
         <v>6770</v>
       </c>
-      <c r="D1402" s="2" t="s">
+      <c r="E1402" s="2" t="s">
         <v>6771</v>
       </c>
-      <c r="E1402" s="2" t="s">
+      <c r="F1402" s="2" t="s">
         <v>6772</v>
-      </c>
-      <c r="F1402" s="2" t="s">
-        <v>6773</v>
       </c>
       <c r="G1402" s="3">
         <v>2</v>
       </c>
       <c r="H1402" s="2" t="s">
-        <v>6774</v>
+        <v>6773</v>
       </c>
       <c r="I1402" s="2" t="s">
         <v>15</v>
@@ -62104,25 +62105,25 @@
         <v>1402</v>
       </c>
       <c r="B1403" s="2" t="s">
+        <v>6774</v>
+      </c>
+      <c r="C1403" s="2" t="s">
         <v>6775</v>
       </c>
-      <c r="C1403" s="2" t="s">
+      <c r="D1403" s="2" t="s">
         <v>6776</v>
       </c>
-      <c r="D1403" s="2" t="s">
+      <c r="E1403" s="2" t="s">
         <v>6777</v>
       </c>
-      <c r="E1403" s="2" t="s">
+      <c r="F1403" s="2" t="s">
         <v>6778</v>
-      </c>
-      <c r="F1403" s="2" t="s">
-        <v>6779</v>
       </c>
       <c r="G1403" s="3">
         <v>3</v>
       </c>
       <c r="H1403" s="2" t="s">
-        <v>6780</v>
+        <v>6779</v>
       </c>
       <c r="I1403" s="2" t="s">
         <v>15</v>
@@ -62133,25 +62134,25 @@
         <v>1403</v>
       </c>
       <c r="B1404" s="2" t="s">
+        <v>6780</v>
+      </c>
+      <c r="C1404" s="2" t="s">
         <v>6781</v>
       </c>
-      <c r="C1404" s="2" t="s">
+      <c r="D1404" s="2" t="s">
         <v>6782</v>
       </c>
-      <c r="D1404" s="2" t="s">
+      <c r="E1404" s="2" t="s">
         <v>6783</v>
       </c>
-      <c r="E1404" s="2" t="s">
+      <c r="F1404" s="2" t="s">
         <v>6784</v>
-      </c>
-      <c r="F1404" s="2" t="s">
-        <v>6785</v>
       </c>
       <c r="G1404" s="3">
         <v>2</v>
       </c>
       <c r="H1404" s="2" t="s">
-        <v>6786</v>
+        <v>6785</v>
       </c>
       <c r="I1404" s="2" t="s">
         <v>15</v>

--- a/salf/丙種職業安全衛生業務主管題庫.xlsx
+++ b/salf/丙種職業安全衛生業務主管題庫.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25f5a1833553ad9e/文件/GitHub/drher.github.io/salf/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\drher\OneDrive\文件\GitHub\drher.github.io\salf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="30" documentId="13_ncr:1_{0E545FC3-85A4-41E9-8FD9-63F8EFFB672E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F573FEF3-00B8-486A-9A52-171B2CE53066}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F242CAFF-C335-4BE1-901E-2F3454C058ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9463" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="15397" windowHeight="8751" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="乾淨題庫" sheetId="1" r:id="rId1"/>
@@ -18758,21 +18758,6 @@
   </si>
   <si>
     <t>正確答案為第1項：「高麗菜」。本題重點在於理解題幹所涉及的職業安全衛生管理、危害預防或法規要求。</t>
-  </si>
-  <si>
-    <t>防塵口單選用原則, 下列敘述何者錯誤 ?</t>
-  </si>
-  <si>
-    <t>捕集效率愈高合好</t>
-  </si>
-  <si>
-    <t>吸氣抵抗愈低愈好</t>
-  </si>
-  <si>
-    <t>重量合輕全好</t>
-  </si>
-  <si>
-    <t>視野合小全好。</t>
   </si>
   <si>
     <t>正確答案為第4項：「視野合小全好。」。本題重點在於理解題幹所涉及的職業安全衛生管理、危害預防或法規要求。</t>
@@ -21234,6 +21219,26 @@
   </si>
   <si>
     <t>依職業安全衛生設施規則之規定。工作場所噪音超過多少分貝時, 即應採取工程控制、減少勞工噪音暴露時間, 以符合容許暴露標準 ?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>防塵口罩選用原則, 下列敘述何者錯誤 ?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>捕集效率愈高愈好</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>重量愈輕愈好</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>視野愈小愈好。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>吸氣阻抗愈低愈好</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -22332,10 +22337,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>6865</v>
+        <v>6860</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>6866</v>
+        <v>6861</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>136</v>
@@ -22852,19 +22857,19 @@
         <v>42</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>6973</v>
+        <v>6968</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>6974</v>
+        <v>6969</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>6975</v>
+        <v>6970</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>234</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>6976</v>
+        <v>6971</v>
       </c>
       <c r="G43" s="3">
         <v>3</v>
@@ -23490,7 +23495,7 @@
         <v>64</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>6929</v>
+        <v>6924</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>349</v>
@@ -23525,7 +23530,7 @@
         <v>355</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>6930</v>
+        <v>6925</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>350</v>
@@ -23664,13 +23669,13 @@
         <v>70</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>6792</v>
+        <v>6787</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>380</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>6791</v>
+        <v>6786</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>381</v>
@@ -23693,7 +23698,7 @@
         <v>71</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>6881</v>
+        <v>6876</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>384</v>
@@ -23702,10 +23707,10 @@
         <v>385</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>6883</v>
+        <v>6878</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>6882</v>
+        <v>6877</v>
       </c>
       <c r="G72" s="3">
         <v>4</v>
@@ -24273,7 +24278,7 @@
         <v>91</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>6841</v>
+        <v>6836</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>488</v>
@@ -24285,7 +24290,7 @@
         <v>490</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>6842</v>
+        <v>6837</v>
       </c>
       <c r="G92" s="3">
         <v>4</v>
@@ -24559,7 +24564,7 @@
         <v>101</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>6818</v>
+        <v>6813</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>542</v>
@@ -24568,10 +24573,10 @@
         <v>543</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>6819</v>
+        <v>6814</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>6820</v>
+        <v>6815</v>
       </c>
       <c r="G102" s="3">
         <v>1</v>
@@ -25456,7 +25461,7 @@
         <v>132</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>6848</v>
+        <v>6843</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>350</v>
@@ -25465,10 +25470,10 @@
         <v>688</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>6849</v>
+        <v>6844</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>6850</v>
+        <v>6845</v>
       </c>
       <c r="G133" s="3">
         <v>3</v>
@@ -26222,7 +26227,7 @@
         <v>814</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>6859</v>
+        <v>6854</v>
       </c>
       <c r="G159" s="3">
         <v>3</v>
@@ -26694,7 +26699,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="176" spans="1:9" ht="61.75">
+    <row r="176" spans="1:9" ht="46.3">
       <c r="A176" s="2">
         <v>175</v>
       </c>
@@ -26786,7 +26791,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>6898</v>
+        <v>6893</v>
       </c>
       <c r="C179" s="2" t="s">
         <v>895</v>
@@ -27074,7 +27079,7 @@
         <v>188</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>6972</v>
+        <v>6967</v>
       </c>
       <c r="C189" s="2" t="s">
         <v>956</v>
@@ -27602,13 +27607,13 @@
         <v>1058</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>6777</v>
+        <v>6772</v>
       </c>
       <c r="E207" s="2" t="s">
-        <v>6778</v>
+        <v>6773</v>
       </c>
       <c r="F207" s="2" t="s">
-        <v>6779</v>
+        <v>6774</v>
       </c>
       <c r="G207" s="3">
         <v>2</v>
@@ -29423,7 +29428,7 @@
         <v>269</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>6800</v>
+        <v>6795</v>
       </c>
       <c r="C270" s="2" t="s">
         <v>1394</v>
@@ -30728,7 +30733,7 @@
         <v>314</v>
       </c>
       <c r="B315" s="2" t="s">
-        <v>6851</v>
+        <v>6846</v>
       </c>
       <c r="C315" s="2" t="s">
         <v>1639</v>
@@ -31111,13 +31116,13 @@
         <v>1712</v>
       </c>
       <c r="D328" s="2" t="s">
-        <v>6931</v>
+        <v>6926</v>
       </c>
       <c r="E328" s="2" t="s">
         <v>1714</v>
       </c>
       <c r="F328" s="2" t="s">
-        <v>6932</v>
+        <v>6927</v>
       </c>
       <c r="G328" s="3">
         <v>4</v>
@@ -31245,7 +31250,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="333" spans="1:9" ht="46.3">
+    <row r="333" spans="1:9" ht="30.9">
       <c r="A333" s="2">
         <v>332</v>
       </c>
@@ -31366,19 +31371,19 @@
         <v>336</v>
       </c>
       <c r="B337" s="2" t="s">
-        <v>6838</v>
+        <v>6833</v>
       </c>
       <c r="C337" s="2" t="s">
         <v>1761</v>
       </c>
       <c r="D337" s="2" t="s">
-        <v>6839</v>
+        <v>6834</v>
       </c>
       <c r="E337" s="2" t="s">
         <v>728</v>
       </c>
       <c r="F337" s="2" t="s">
-        <v>6840</v>
+        <v>6835</v>
       </c>
       <c r="G337" s="3">
         <v>4</v>
@@ -31570,7 +31575,7 @@
         <v>1796</v>
       </c>
       <c r="C344" s="2" t="s">
-        <v>6846</v>
+        <v>6841</v>
       </c>
       <c r="D344" s="2" t="s">
         <v>1791</v>
@@ -31579,7 +31584,7 @@
         <v>1792</v>
       </c>
       <c r="F344" s="2" t="s">
-        <v>6847</v>
+        <v>6842</v>
       </c>
       <c r="G344" s="3">
         <v>1</v>
@@ -33394,16 +33399,16 @@
         <v>406</v>
       </c>
       <c r="B407" s="2" t="s">
-        <v>6862</v>
+        <v>6857</v>
       </c>
       <c r="C407" s="2" t="s">
-        <v>6864</v>
+        <v>6859</v>
       </c>
       <c r="D407" s="2" t="s">
         <v>2151</v>
       </c>
       <c r="E407" s="2" t="s">
-        <v>6863</v>
+        <v>6858</v>
       </c>
       <c r="F407" s="2" t="s">
         <v>2152</v>
@@ -34202,7 +34207,7 @@
         <v>434</v>
       </c>
       <c r="B435" s="2" t="s">
-        <v>6873</v>
+        <v>6868</v>
       </c>
       <c r="C435" s="2" t="s">
         <v>2290</v>
@@ -34214,7 +34219,7 @@
         <v>2292</v>
       </c>
       <c r="F435" s="2" t="s">
-        <v>6874</v>
+        <v>6869</v>
       </c>
       <c r="G435" s="3">
         <v>1</v>
@@ -34731,10 +34736,10 @@
         <v>2371</v>
       </c>
       <c r="E453" s="2" t="s">
-        <v>6888</v>
+        <v>6883</v>
       </c>
       <c r="F453" s="2" t="s">
-        <v>6887</v>
+        <v>6882</v>
       </c>
       <c r="G453" s="3">
         <v>1</v>
@@ -34751,7 +34756,7 @@
         <v>453</v>
       </c>
       <c r="B454" s="2" t="s">
-        <v>6884</v>
+        <v>6879</v>
       </c>
       <c r="C454" s="2" t="s">
         <v>1436</v>
@@ -34760,10 +34765,10 @@
         <v>1418</v>
       </c>
       <c r="E454" s="2" t="s">
-        <v>6886</v>
+        <v>6881</v>
       </c>
       <c r="F454" s="2" t="s">
-        <v>6885</v>
+        <v>6880</v>
       </c>
       <c r="G454" s="3">
         <v>4</v>
@@ -35757,7 +35762,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="489" spans="1:9" ht="46.3">
+    <row r="489" spans="1:9" ht="30.9">
       <c r="A489" s="2">
         <v>488</v>
       </c>
@@ -36197,19 +36202,19 @@
         <v>503</v>
       </c>
       <c r="B504" s="2" t="s">
-        <v>6933</v>
+        <v>6928</v>
       </c>
       <c r="C504" s="2" t="s">
-        <v>6934</v>
+        <v>6929</v>
       </c>
       <c r="D504" s="2" t="s">
         <v>2620</v>
       </c>
       <c r="E504" s="2" t="s">
-        <v>6935</v>
+        <v>6930</v>
       </c>
       <c r="F504" s="2" t="s">
-        <v>6936</v>
+        <v>6931</v>
       </c>
       <c r="G504" s="3">
         <v>4</v>
@@ -37168,7 +37173,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="538" spans="1:9" ht="46.3">
+    <row r="538" spans="1:9" ht="30.9">
       <c r="A538" s="2">
         <v>537</v>
       </c>
@@ -37682,7 +37687,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="556" spans="1:9" ht="46.3">
+    <row r="556" spans="1:9" ht="30.9">
       <c r="A556" s="2">
         <v>555</v>
       </c>
@@ -37716,13 +37721,13 @@
         <v>556</v>
       </c>
       <c r="B557" s="2" t="s">
-        <v>6783</v>
+        <v>6778</v>
       </c>
       <c r="C557" s="2" t="s">
-        <v>6784</v>
+        <v>6779</v>
       </c>
       <c r="D557" s="2" t="s">
-        <v>6785</v>
+        <v>6780</v>
       </c>
       <c r="E557" s="2" t="s">
         <v>2876</v>
@@ -38149,19 +38154,19 @@
         <v>571</v>
       </c>
       <c r="B572" s="2" t="s">
-        <v>6964</v>
+        <v>6959</v>
       </c>
       <c r="C572" s="2" t="s">
-        <v>6907</v>
+        <v>6902</v>
       </c>
       <c r="D572" s="2" t="s">
-        <v>6908</v>
+        <v>6903</v>
       </c>
       <c r="E572" s="2" t="s">
-        <v>6910</v>
+        <v>6905</v>
       </c>
       <c r="F572" s="2" t="s">
-        <v>6909</v>
+        <v>6904</v>
       </c>
       <c r="G572" s="3">
         <v>4</v>
@@ -38178,19 +38183,19 @@
         <v>572</v>
       </c>
       <c r="B573" s="2" t="s">
-        <v>6965</v>
+        <v>6960</v>
       </c>
       <c r="C573" s="2" t="s">
-        <v>6910</v>
+        <v>6905</v>
       </c>
       <c r="D573" s="2" t="s">
-        <v>6909</v>
+        <v>6904</v>
       </c>
       <c r="E573" s="2" t="s">
-        <v>6907</v>
+        <v>6902</v>
       </c>
       <c r="F573" s="2" t="s">
-        <v>6908</v>
+        <v>6903</v>
       </c>
       <c r="G573" s="3">
         <v>4</v>
@@ -38207,19 +38212,19 @@
         <v>573</v>
       </c>
       <c r="B574" s="2" t="s">
-        <v>6911</v>
+        <v>6906</v>
       </c>
       <c r="C574" s="2" t="s">
-        <v>6909</v>
+        <v>6904</v>
       </c>
       <c r="D574" s="2" t="s">
-        <v>6912</v>
+        <v>6907</v>
       </c>
       <c r="E574" s="2" t="s">
-        <v>6913</v>
+        <v>6908</v>
       </c>
       <c r="F574" s="2" t="s">
-        <v>6910</v>
+        <v>6905</v>
       </c>
       <c r="G574" s="3">
         <v>2</v>
@@ -38242,7 +38247,7 @@
         <v>2958</v>
       </c>
       <c r="D575" s="2" t="s">
-        <v>6914</v>
+        <v>6909</v>
       </c>
       <c r="E575" s="2" t="s">
         <v>2959</v>
@@ -38294,19 +38299,19 @@
         <v>576</v>
       </c>
       <c r="B577" s="2" t="s">
-        <v>6920</v>
+        <v>6915</v>
       </c>
       <c r="C577" s="2" t="s">
-        <v>6924</v>
+        <v>6919</v>
       </c>
       <c r="D577" s="2" t="s">
-        <v>6921</v>
+        <v>6916</v>
       </c>
       <c r="E577" s="2" t="s">
-        <v>6922</v>
+        <v>6917</v>
       </c>
       <c r="F577" s="2" t="s">
-        <v>6923</v>
+        <v>6918</v>
       </c>
       <c r="G577" s="3">
         <v>3</v>
@@ -38323,19 +38328,19 @@
         <v>577</v>
       </c>
       <c r="B578" s="5" t="s">
-        <v>6915</v>
+        <v>6910</v>
       </c>
       <c r="C578" s="2" t="s">
-        <v>6916</v>
+        <v>6911</v>
       </c>
       <c r="D578" s="2" t="s">
-        <v>6917</v>
+        <v>6912</v>
       </c>
       <c r="E578" s="2" t="s">
-        <v>6919</v>
+        <v>6914</v>
       </c>
       <c r="F578" s="2" t="s">
-        <v>6918</v>
+        <v>6913</v>
       </c>
       <c r="G578" s="3">
         <v>1</v>
@@ -38352,16 +38357,16 @@
         <v>578</v>
       </c>
       <c r="B579" s="2" t="s">
-        <v>6925</v>
+        <v>6920</v>
       </c>
       <c r="C579" s="2" t="s">
-        <v>6926</v>
+        <v>6921</v>
       </c>
       <c r="D579" s="2" t="s">
-        <v>6927</v>
+        <v>6922</v>
       </c>
       <c r="E579" s="2" t="s">
-        <v>6928</v>
+        <v>6923</v>
       </c>
       <c r="F579" s="2" t="s">
         <v>2968</v>
@@ -39417,7 +39422,7 @@
         <v>615</v>
       </c>
       <c r="B616" s="2" t="s">
-        <v>6812</v>
+        <v>6807</v>
       </c>
       <c r="C616" s="2" t="s">
         <v>3150</v>
@@ -39533,7 +39538,7 @@
         <v>619</v>
       </c>
       <c r="B620" s="2" t="s">
-        <v>6875</v>
+        <v>6870</v>
       </c>
       <c r="C620" s="2" t="s">
         <v>3171</v>
@@ -39545,7 +39550,7 @@
         <v>3173</v>
       </c>
       <c r="F620" s="2" t="s">
-        <v>6876</v>
+        <v>6871</v>
       </c>
       <c r="G620" s="3">
         <v>4</v>
@@ -40117,7 +40122,7 @@
         <v>3278</v>
       </c>
       <c r="F640" s="2" t="s">
-        <v>6790</v>
+        <v>6785</v>
       </c>
       <c r="G640" s="3">
         <v>2</v>
@@ -40424,7 +40429,7 @@
         <v>650</v>
       </c>
       <c r="B651" s="2" t="s">
-        <v>6823</v>
+        <v>6818</v>
       </c>
       <c r="C651" s="2" t="s">
         <v>3331</v>
@@ -40433,10 +40438,10 @@
         <v>3332</v>
       </c>
       <c r="E651" s="2" t="s">
-        <v>6824</v>
+        <v>6819</v>
       </c>
       <c r="F651" s="2" t="s">
-        <v>6825</v>
+        <v>6820</v>
       </c>
       <c r="G651" s="3">
         <v>2</v>
@@ -40482,7 +40487,7 @@
         <v>652</v>
       </c>
       <c r="B653" s="2" t="s">
-        <v>6871</v>
+        <v>6866</v>
       </c>
       <c r="C653" s="2" t="s">
         <v>1538</v>
@@ -40494,7 +40499,7 @@
         <v>3341</v>
       </c>
       <c r="F653" s="2" t="s">
-        <v>6872</v>
+        <v>6867</v>
       </c>
       <c r="G653" s="3">
         <v>1</v>
@@ -41637,7 +41642,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="693" spans="1:9" ht="123.45">
+    <row r="693" spans="1:9" ht="108">
       <c r="A693" s="2">
         <v>692</v>
       </c>
@@ -42392,7 +42397,7 @@
         <v>718</v>
       </c>
       <c r="B719" s="2" t="s">
-        <v>6899</v>
+        <v>6894</v>
       </c>
       <c r="C719" s="2" t="s">
         <v>709</v>
@@ -42591,7 +42596,7 @@
         <v>725</v>
       </c>
       <c r="B726" s="2" t="s">
-        <v>6966</v>
+        <v>6961</v>
       </c>
       <c r="C726" s="2" t="s">
         <v>3676</v>
@@ -42600,10 +42605,10 @@
         <v>3677</v>
       </c>
       <c r="E726" s="2" t="s">
-        <v>6967</v>
+        <v>6962</v>
       </c>
       <c r="F726" s="2" t="s">
-        <v>6968</v>
+        <v>6963</v>
       </c>
       <c r="G726" s="3">
         <v>1</v>
@@ -42906,7 +42911,7 @@
         <v>736</v>
       </c>
       <c r="B737" s="2" t="s">
-        <v>6960</v>
+        <v>6955</v>
       </c>
       <c r="C737" s="2" t="s">
         <v>3724</v>
@@ -42935,13 +42940,13 @@
         <v>737</v>
       </c>
       <c r="B738" s="2" t="s">
-        <v>6961</v>
+        <v>6956</v>
       </c>
       <c r="C738" s="2" t="s">
-        <v>6962</v>
+        <v>6957</v>
       </c>
       <c r="D738" s="2" t="s">
-        <v>6963</v>
+        <v>6958</v>
       </c>
       <c r="E738" s="2" t="s">
         <v>3729</v>
@@ -43054,13 +43059,13 @@
         <v>3745</v>
       </c>
       <c r="C742" s="2" t="s">
-        <v>6780</v>
+        <v>6775</v>
       </c>
       <c r="D742" s="2" t="s">
         <v>3746</v>
       </c>
       <c r="E742" s="2" t="s">
-        <v>6781</v>
+        <v>6776</v>
       </c>
       <c r="F742" s="2" t="s">
         <v>51</v>
@@ -43455,25 +43460,25 @@
         <v>755</v>
       </c>
       <c r="B756" s="2" t="s">
-        <v>6801</v>
+        <v>6796</v>
       </c>
       <c r="C756" s="2" t="s">
-        <v>6802</v>
+        <v>6797</v>
       </c>
       <c r="D756" s="2" t="s">
-        <v>6803</v>
+        <v>6798</v>
       </c>
       <c r="E756" s="2" t="s">
-        <v>6804</v>
+        <v>6799</v>
       </c>
       <c r="F756" s="2" t="s">
-        <v>6805</v>
+        <v>6800</v>
       </c>
       <c r="G756" s="3">
         <v>2</v>
       </c>
       <c r="H756" s="2" t="s">
-        <v>6806</v>
+        <v>6801</v>
       </c>
       <c r="I756" s="2" t="s">
         <v>798</v>
@@ -44028,7 +44033,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="776" spans="1:9" ht="46.3">
+    <row r="776" spans="1:9" ht="30.9">
       <c r="A776" s="2">
         <v>775</v>
       </c>
@@ -44874,7 +44879,7 @@
         <v>804</v>
       </c>
       <c r="B805" s="2" t="s">
-        <v>6938</v>
+        <v>6933</v>
       </c>
       <c r="C805" s="2" t="s">
         <v>4024</v>
@@ -45106,13 +45111,13 @@
         <v>812</v>
       </c>
       <c r="B813" s="2" t="s">
-        <v>6869</v>
+        <v>6864</v>
       </c>
       <c r="C813" s="2" t="s">
         <v>4066</v>
       </c>
       <c r="D813" s="2" t="s">
-        <v>6870</v>
+        <v>6865</v>
       </c>
       <c r="E813" s="2" t="s">
         <v>4067</v>
@@ -45164,7 +45169,7 @@
         <v>814</v>
       </c>
       <c r="B815" s="2" t="s">
-        <v>6867</v>
+        <v>6862</v>
       </c>
       <c r="C815" s="2" t="s">
         <v>4076</v>
@@ -45176,7 +45181,7 @@
         <v>4078</v>
       </c>
       <c r="F815" s="2" t="s">
-        <v>6868</v>
+        <v>6863</v>
       </c>
       <c r="G815" s="3">
         <v>1</v>
@@ -45315,13 +45320,13 @@
         <v>4098</v>
       </c>
       <c r="D820" s="2" t="s">
-        <v>6977</v>
+        <v>6972</v>
       </c>
       <c r="E820" s="2" t="s">
         <v>4099</v>
       </c>
       <c r="F820" s="2" t="s">
-        <v>6978</v>
+        <v>6973</v>
       </c>
       <c r="G820" s="3">
         <v>4</v>
@@ -45570,7 +45575,7 @@
         <v>828</v>
       </c>
       <c r="B829" s="2" t="s">
-        <v>6937</v>
+        <v>6932</v>
       </c>
       <c r="C829" s="2" t="s">
         <v>4143</v>
@@ -45658,16 +45663,16 @@
         <v>4159</v>
       </c>
       <c r="C832" s="2" t="s">
-        <v>6903</v>
+        <v>6898</v>
       </c>
       <c r="D832" s="2" t="s">
-        <v>6904</v>
+        <v>6899</v>
       </c>
       <c r="E832" s="2" t="s">
-        <v>6905</v>
+        <v>6900</v>
       </c>
       <c r="F832" s="2" t="s">
-        <v>6906</v>
+        <v>6901</v>
       </c>
       <c r="G832" s="3">
         <v>4</v>
@@ -46610,7 +46615,7 @@
         <v>864</v>
       </c>
       <c r="B865" s="2" t="s">
-        <v>6828</v>
+        <v>6823</v>
       </c>
       <c r="C865" s="2" t="s">
         <v>4323</v>
@@ -46619,10 +46624,10 @@
         <v>3072</v>
       </c>
       <c r="E865" s="2" t="s">
-        <v>6826</v>
+        <v>6821</v>
       </c>
       <c r="F865" s="2" t="s">
-        <v>6827</v>
+        <v>6822</v>
       </c>
       <c r="G865" s="3">
         <v>4</v>
@@ -46639,19 +46644,19 @@
         <v>865</v>
       </c>
       <c r="B866" s="2" t="s">
-        <v>6833</v>
+        <v>6828</v>
       </c>
       <c r="C866" s="2" t="s">
-        <v>6834</v>
+        <v>6829</v>
       </c>
       <c r="D866" s="4" t="s">
-        <v>6835</v>
+        <v>6830</v>
       </c>
       <c r="E866" s="2" t="s">
-        <v>6836</v>
+        <v>6831</v>
       </c>
       <c r="F866" s="2" t="s">
-        <v>6837</v>
+        <v>6832</v>
       </c>
       <c r="G866" s="3">
         <v>3</v>
@@ -47075,7 +47080,7 @@
         <v>4402</v>
       </c>
       <c r="C881" s="2" t="s">
-        <v>6788</v>
+        <v>6783</v>
       </c>
       <c r="D881" s="2" t="s">
         <v>3072</v>
@@ -47084,7 +47089,7 @@
         <v>4403</v>
       </c>
       <c r="F881" s="2" t="s">
-        <v>6789</v>
+        <v>6784</v>
       </c>
       <c r="G881" s="3">
         <v>1</v>
@@ -47536,16 +47541,16 @@
         <v>896</v>
       </c>
       <c r="B897" s="2" t="s">
-        <v>6794</v>
+        <v>6789</v>
       </c>
       <c r="C897" s="2" t="s">
         <v>4187</v>
       </c>
       <c r="D897" s="2" t="s">
-        <v>6795</v>
+        <v>6790</v>
       </c>
       <c r="E897" s="2" t="s">
-        <v>6796</v>
+        <v>6791</v>
       </c>
       <c r="F897" s="2" t="s">
         <v>4276</v>
@@ -48025,19 +48030,19 @@
         <v>913</v>
       </c>
       <c r="B914" s="2" t="s">
-        <v>6939</v>
+        <v>6934</v>
       </c>
       <c r="C914" s="2" t="s">
-        <v>6940</v>
+        <v>6935</v>
       </c>
       <c r="D914" s="2" t="s">
         <v>4572</v>
       </c>
       <c r="E914" s="2" t="s">
-        <v>6941</v>
+        <v>6936</v>
       </c>
       <c r="F914" s="2" t="s">
-        <v>6942</v>
+        <v>6937</v>
       </c>
       <c r="G914" s="3">
         <v>3</v>
@@ -48309,7 +48314,7 @@
         <v>923</v>
       </c>
       <c r="B924" s="2" t="s">
-        <v>6793</v>
+        <v>6788</v>
       </c>
       <c r="C924" s="2" t="s">
         <v>3116</v>
@@ -49156,7 +49161,7 @@
         <v>4766</v>
       </c>
       <c r="F953" s="2" t="s">
-        <v>6782</v>
+        <v>6777</v>
       </c>
       <c r="G953" s="3">
         <v>3</v>
@@ -49948,19 +49953,19 @@
         <v>980</v>
       </c>
       <c r="B981" s="2" t="s">
-        <v>6852</v>
+        <v>6847</v>
       </c>
       <c r="C981" s="2" t="s">
-        <v>6854</v>
+        <v>6849</v>
       </c>
       <c r="D981" s="2" t="s">
-        <v>6855</v>
+        <v>6850</v>
       </c>
       <c r="E981" s="2" t="s">
         <v>4910</v>
       </c>
       <c r="F981" s="2" t="s">
-        <v>6853</v>
+        <v>6848</v>
       </c>
       <c r="G981" s="3">
         <v>2</v>
@@ -50180,19 +50185,19 @@
         <v>988</v>
       </c>
       <c r="B989" s="2" t="s">
-        <v>6813</v>
+        <v>6808</v>
       </c>
       <c r="C989" s="2" t="s">
-        <v>6814</v>
+        <v>6809</v>
       </c>
       <c r="D989" s="2" t="s">
-        <v>6815</v>
+        <v>6810</v>
       </c>
       <c r="E989" s="2" t="s">
-        <v>6816</v>
+        <v>6811</v>
       </c>
       <c r="F989" s="2" t="s">
-        <v>6817</v>
+        <v>6812</v>
       </c>
       <c r="G989" s="3">
         <v>3</v>
@@ -50962,16 +50967,16 @@
         <v>5053</v>
       </c>
       <c r="C1016" s="2" t="s">
-        <v>6943</v>
+        <v>6938</v>
       </c>
       <c r="D1016" s="2" t="s">
-        <v>6944</v>
+        <v>6939</v>
       </c>
       <c r="E1016" s="2" t="s">
         <v>5054</v>
       </c>
       <c r="F1016" s="2" t="s">
-        <v>6945</v>
+        <v>6940</v>
       </c>
       <c r="G1016" s="3">
         <v>1</v>
@@ -50988,7 +50993,7 @@
         <v>1016</v>
       </c>
       <c r="B1017" s="2" t="s">
-        <v>6946</v>
+        <v>6941</v>
       </c>
       <c r="C1017" s="2" t="s">
         <v>5056</v>
@@ -51249,7 +51254,7 @@
         <v>1025</v>
       </c>
       <c r="B1026" s="2" t="s">
-        <v>6856</v>
+        <v>6851</v>
       </c>
       <c r="C1026" s="2" t="s">
         <v>5098</v>
@@ -51258,10 +51263,10 @@
         <v>994</v>
       </c>
       <c r="E1026" s="2" t="s">
-        <v>6857</v>
+        <v>6852</v>
       </c>
       <c r="F1026" s="2" t="s">
-        <v>6858</v>
+        <v>6853</v>
       </c>
       <c r="G1026" s="3">
         <v>1</v>
@@ -51626,7 +51631,7 @@
         <v>1038</v>
       </c>
       <c r="B1039" s="2" t="s">
-        <v>6949</v>
+        <v>6944</v>
       </c>
       <c r="C1039" s="2" t="s">
         <v>5165</v>
@@ -51635,10 +51640,10 @@
         <v>5166</v>
       </c>
       <c r="E1039" s="2" t="s">
-        <v>6947</v>
+        <v>6942</v>
       </c>
       <c r="F1039" s="2" t="s">
-        <v>6948</v>
+        <v>6943</v>
       </c>
       <c r="G1039" s="3">
         <v>2</v>
@@ -51655,19 +51660,19 @@
         <v>1039</v>
       </c>
       <c r="B1040" s="2" t="s">
-        <v>6807</v>
+        <v>6802</v>
       </c>
       <c r="C1040" s="2" t="s">
-        <v>6808</v>
+        <v>6803</v>
       </c>
       <c r="D1040" s="2" t="s">
-        <v>6809</v>
+        <v>6804</v>
       </c>
       <c r="E1040" s="2" t="s">
-        <v>6810</v>
+        <v>6805</v>
       </c>
       <c r="F1040" s="2" t="s">
-        <v>6811</v>
+        <v>6806</v>
       </c>
       <c r="G1040" s="3">
         <v>4</v>
@@ -52894,7 +52899,7 @@
         <v>1082</v>
       </c>
       <c r="B1083" s="2" t="s">
-        <v>6950</v>
+        <v>6945</v>
       </c>
       <c r="C1083" s="2" t="s">
         <v>5380</v>
@@ -53918,10 +53923,10 @@
         <v>5546</v>
       </c>
       <c r="E1118" s="2" t="s">
-        <v>6787</v>
+        <v>6782</v>
       </c>
       <c r="F1118" s="2" t="s">
-        <v>6786</v>
+        <v>6781</v>
       </c>
       <c r="G1118" s="3">
         <v>4</v>
@@ -55727,10 +55732,10 @@
         <v>1181</v>
       </c>
       <c r="B1182" s="2" t="s">
-        <v>6900</v>
+        <v>6895</v>
       </c>
       <c r="C1182" s="2" t="s">
-        <v>6901</v>
+        <v>6896</v>
       </c>
       <c r="D1182" s="2" t="s">
         <v>5839</v>
@@ -55739,7 +55744,7 @@
         <v>1819</v>
       </c>
       <c r="F1182" s="2" t="s">
-        <v>6902</v>
+        <v>6897</v>
       </c>
       <c r="G1182" s="3">
         <v>4</v>
@@ -55785,7 +55790,7 @@
         <v>1183</v>
       </c>
       <c r="B1184" s="2" t="s">
-        <v>6951</v>
+        <v>6946</v>
       </c>
       <c r="C1184" s="2" t="s">
         <v>4354</v>
@@ -55843,7 +55848,7 @@
         <v>1185</v>
       </c>
       <c r="B1186" s="2" t="s">
-        <v>6979</v>
+        <v>6974</v>
       </c>
       <c r="C1186" s="2" t="s">
         <v>4355</v>
@@ -56563,7 +56568,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="1211" spans="1:9" ht="46.3">
+    <row r="1211" spans="1:9" ht="30.9">
       <c r="A1211" s="2">
         <v>1210</v>
       </c>
@@ -56626,7 +56631,7 @@
         <v>1212</v>
       </c>
       <c r="B1213" s="2" t="s">
-        <v>6954</v>
+        <v>6949</v>
       </c>
       <c r="C1213" s="2" t="s">
         <v>5931</v>
@@ -56690,13 +56695,13 @@
         <v>5941</v>
       </c>
       <c r="D1215" s="2" t="s">
-        <v>6952</v>
+        <v>6947</v>
       </c>
       <c r="E1215" s="2" t="s">
         <v>5942</v>
       </c>
       <c r="F1215" s="2" t="s">
-        <v>6953</v>
+        <v>6948</v>
       </c>
       <c r="G1215" s="3">
         <v>4</v>
@@ -57061,7 +57066,7 @@
         <v>1227</v>
       </c>
       <c r="B1228" s="2" t="s">
-        <v>6797</v>
+        <v>6792</v>
       </c>
       <c r="C1228" s="2" t="s">
         <v>6000</v>
@@ -57070,10 +57075,10 @@
         <v>6001</v>
       </c>
       <c r="E1228" s="2" t="s">
-        <v>6798</v>
+        <v>6793</v>
       </c>
       <c r="F1228" s="2" t="s">
-        <v>6799</v>
+        <v>6794</v>
       </c>
       <c r="G1228" s="3">
         <v>4</v>
@@ -57204,13 +57209,13 @@
         <v>1232</v>
       </c>
       <c r="B1233" s="2" t="s">
-        <v>6970</v>
+        <v>6965</v>
       </c>
       <c r="C1233" s="2" t="s">
         <v>6018</v>
       </c>
       <c r="D1233" s="2" t="s">
-        <v>6971</v>
+        <v>6966</v>
       </c>
       <c r="E1233" s="2" t="s">
         <v>3951</v>
@@ -57437,10 +57442,10 @@
         <v>6052</v>
       </c>
       <c r="C1241" s="2" t="s">
-        <v>6860</v>
+        <v>6855</v>
       </c>
       <c r="D1241" s="2" t="s">
-        <v>6861</v>
+        <v>6856</v>
       </c>
       <c r="E1241" s="2" t="s">
         <v>5980</v>
@@ -58563,25 +58568,25 @@
         <v>1279</v>
       </c>
       <c r="B1280" s="2" t="s">
-        <v>6245</v>
+        <v>6975</v>
       </c>
       <c r="C1280" s="2" t="s">
-        <v>6246</v>
+        <v>6976</v>
       </c>
       <c r="D1280" s="2" t="s">
-        <v>6247</v>
+        <v>6979</v>
       </c>
       <c r="E1280" s="2" t="s">
-        <v>6248</v>
+        <v>6977</v>
       </c>
       <c r="F1280" s="2" t="s">
-        <v>6249</v>
+        <v>6978</v>
       </c>
       <c r="G1280" s="3">
         <v>4</v>
       </c>
       <c r="H1280" s="2" t="s">
-        <v>6250</v>
+        <v>6245</v>
       </c>
       <c r="I1280" s="2" t="s">
         <v>15</v>
@@ -58592,10 +58597,10 @@
         <v>1280</v>
       </c>
       <c r="B1281" s="2" t="s">
-        <v>6251</v>
+        <v>6246</v>
       </c>
       <c r="C1281" s="2" t="s">
-        <v>6252</v>
+        <v>6247</v>
       </c>
       <c r="D1281" s="2" t="s">
         <v>177</v>
@@ -58604,13 +58609,13 @@
         <v>179</v>
       </c>
       <c r="F1281" s="2" t="s">
-        <v>6253</v>
+        <v>6248</v>
       </c>
       <c r="G1281" s="3">
         <v>1</v>
       </c>
       <c r="H1281" s="2" t="s">
-        <v>6254</v>
+        <v>6249</v>
       </c>
       <c r="I1281" s="2" t="s">
         <v>15</v>
@@ -58621,25 +58626,25 @@
         <v>1281</v>
       </c>
       <c r="B1282" s="2" t="s">
-        <v>6255</v>
+        <v>6250</v>
       </c>
       <c r="C1282" s="2" t="s">
-        <v>6256</v>
+        <v>6251</v>
       </c>
       <c r="D1282" s="2" t="s">
-        <v>6257</v>
+        <v>6252</v>
       </c>
       <c r="E1282" s="2" t="s">
         <v>5652</v>
       </c>
       <c r="F1282" s="2" t="s">
-        <v>6258</v>
+        <v>6253</v>
       </c>
       <c r="G1282" s="3">
         <v>4</v>
       </c>
       <c r="H1282" s="2" t="s">
-        <v>6259</v>
+        <v>6254</v>
       </c>
       <c r="I1282" s="2" t="s">
         <v>15</v>
@@ -58650,25 +58655,25 @@
         <v>1282</v>
       </c>
       <c r="B1283" s="2" t="s">
-        <v>6260</v>
+        <v>6255</v>
       </c>
       <c r="C1283" s="2" t="s">
-        <v>6261</v>
+        <v>6256</v>
       </c>
       <c r="D1283" s="2" t="s">
-        <v>6262</v>
+        <v>6257</v>
       </c>
       <c r="E1283" s="2" t="s">
         <v>5424</v>
       </c>
       <c r="F1283" s="2" t="s">
-        <v>6263</v>
+        <v>6258</v>
       </c>
       <c r="G1283" s="3">
         <v>2</v>
       </c>
       <c r="H1283" s="2" t="s">
-        <v>6264</v>
+        <v>6259</v>
       </c>
       <c r="I1283" s="2" t="s">
         <v>15</v>
@@ -58679,7 +58684,7 @@
         <v>1283</v>
       </c>
       <c r="B1284" s="2" t="s">
-        <v>6265</v>
+        <v>6260</v>
       </c>
       <c r="C1284" s="2" t="s">
         <v>1835</v>
@@ -58688,16 +58693,16 @@
         <v>1836</v>
       </c>
       <c r="E1284" s="2" t="s">
-        <v>6266</v>
+        <v>6261</v>
       </c>
       <c r="F1284" s="2" t="s">
-        <v>6267</v>
+        <v>6262</v>
       </c>
       <c r="G1284" s="3">
         <v>3</v>
       </c>
       <c r="H1284" s="2" t="s">
-        <v>6268</v>
+        <v>6263</v>
       </c>
       <c r="I1284" s="2" t="s">
         <v>15</v>
@@ -58708,25 +58713,25 @@
         <v>1284</v>
       </c>
       <c r="B1285" s="2" t="s">
-        <v>6843</v>
+        <v>6838</v>
       </c>
       <c r="C1285" s="2" t="s">
-        <v>6844</v>
+        <v>6839</v>
       </c>
       <c r="D1285" s="2" t="s">
         <v>3313</v>
       </c>
       <c r="E1285" s="2" t="s">
-        <v>6269</v>
+        <v>6264</v>
       </c>
       <c r="F1285" s="2" t="s">
-        <v>6845</v>
+        <v>6840</v>
       </c>
       <c r="G1285" s="3">
         <v>2</v>
       </c>
       <c r="H1285" s="2" t="s">
-        <v>6270</v>
+        <v>6265</v>
       </c>
       <c r="I1285" s="2" t="s">
         <v>15</v>
@@ -58737,25 +58742,25 @@
         <v>1285</v>
       </c>
       <c r="B1286" s="2" t="s">
-        <v>6271</v>
+        <v>6266</v>
       </c>
       <c r="C1286" s="2" t="s">
-        <v>6272</v>
+        <v>6267</v>
       </c>
       <c r="D1286" s="2" t="s">
-        <v>6273</v>
+        <v>6268</v>
       </c>
       <c r="E1286" s="2" t="s">
-        <v>6274</v>
+        <v>6269</v>
       </c>
       <c r="F1286" s="2" t="s">
-        <v>6275</v>
+        <v>6270</v>
       </c>
       <c r="G1286" s="3">
         <v>1</v>
       </c>
       <c r="H1286" s="2" t="s">
-        <v>6276</v>
+        <v>6271</v>
       </c>
       <c r="I1286" s="2" t="s">
         <v>15</v>
@@ -58766,7 +58771,7 @@
         <v>1286</v>
       </c>
       <c r="B1287" s="2" t="s">
-        <v>6277</v>
+        <v>6272</v>
       </c>
       <c r="C1287" s="2" t="s">
         <v>909</v>
@@ -58778,13 +58783,13 @@
         <v>4045</v>
       </c>
       <c r="F1287" s="2" t="s">
-        <v>6278</v>
+        <v>6273</v>
       </c>
       <c r="G1287" s="3">
         <v>3</v>
       </c>
       <c r="H1287" s="2" t="s">
-        <v>6279</v>
+        <v>6274</v>
       </c>
       <c r="I1287" s="2" t="s">
         <v>165</v>
@@ -58795,25 +58800,25 @@
         <v>1287</v>
       </c>
       <c r="B1288" s="2" t="s">
-        <v>6280</v>
+        <v>6275</v>
       </c>
       <c r="C1288" s="2" t="s">
-        <v>6281</v>
+        <v>6276</v>
       </c>
       <c r="D1288" s="2" t="s">
         <v>5253</v>
       </c>
       <c r="E1288" s="2" t="s">
-        <v>6282</v>
+        <v>6277</v>
       </c>
       <c r="F1288" s="2" t="s">
-        <v>6283</v>
+        <v>6278</v>
       </c>
       <c r="G1288" s="3">
         <v>1</v>
       </c>
       <c r="H1288" s="2" t="s">
-        <v>6284</v>
+        <v>6279</v>
       </c>
       <c r="I1288" s="2" t="s">
         <v>158</v>
@@ -58824,25 +58829,25 @@
         <v>1288</v>
       </c>
       <c r="B1289" s="2" t="s">
-        <v>6285</v>
+        <v>6280</v>
       </c>
       <c r="C1289" s="2" t="s">
-        <v>6286</v>
+        <v>6281</v>
       </c>
       <c r="D1289" s="2" t="s">
-        <v>6287</v>
+        <v>6282</v>
       </c>
       <c r="E1289" s="2" t="s">
-        <v>6288</v>
+        <v>6283</v>
       </c>
       <c r="F1289" s="2" t="s">
-        <v>6289</v>
+        <v>6284</v>
       </c>
       <c r="G1289" s="3">
         <v>4</v>
       </c>
       <c r="H1289" s="2" t="s">
-        <v>6290</v>
+        <v>6285</v>
       </c>
       <c r="I1289" s="2" t="s">
         <v>15</v>
@@ -58853,25 +58858,25 @@
         <v>1289</v>
       </c>
       <c r="B1290" s="2" t="s">
-        <v>6829</v>
+        <v>6824</v>
       </c>
       <c r="C1290" s="2" t="s">
-        <v>6830</v>
+        <v>6825</v>
       </c>
       <c r="D1290" s="2" t="s">
-        <v>6831</v>
+        <v>6826</v>
       </c>
       <c r="E1290" s="2" t="s">
-        <v>6291</v>
+        <v>6286</v>
       </c>
       <c r="F1290" s="2" t="s">
-        <v>6832</v>
+        <v>6827</v>
       </c>
       <c r="G1290" s="3">
         <v>3</v>
       </c>
       <c r="H1290" s="2" t="s">
-        <v>6292</v>
+        <v>6287</v>
       </c>
       <c r="I1290" s="2" t="s">
         <v>15</v>
@@ -58882,25 +58887,25 @@
         <v>1290</v>
       </c>
       <c r="B1291" s="2" t="s">
-        <v>6293</v>
+        <v>6288</v>
       </c>
       <c r="C1291" s="2" t="s">
-        <v>6294</v>
+        <v>6289</v>
       </c>
       <c r="D1291" s="2" t="s">
         <v>4487</v>
       </c>
       <c r="E1291" s="2" t="s">
-        <v>6295</v>
+        <v>6290</v>
       </c>
       <c r="F1291" s="2" t="s">
-        <v>6296</v>
+        <v>6291</v>
       </c>
       <c r="G1291" s="3">
         <v>1</v>
       </c>
       <c r="H1291" s="2" t="s">
-        <v>6297</v>
+        <v>6292</v>
       </c>
       <c r="I1291" s="2" t="s">
         <v>15</v>
@@ -58911,7 +58916,7 @@
         <v>1291</v>
       </c>
       <c r="B1292" s="2" t="s">
-        <v>6298</v>
+        <v>6293</v>
       </c>
       <c r="C1292" s="2" t="s">
         <v>511</v>
@@ -58923,7 +58928,7 @@
         <v>513</v>
       </c>
       <c r="F1292" s="2" t="s">
-        <v>6299</v>
+        <v>6294</v>
       </c>
       <c r="G1292" s="3">
         <v>2</v>
@@ -58940,25 +58945,25 @@
         <v>1292</v>
       </c>
       <c r="B1293" s="2" t="s">
-        <v>6300</v>
+        <v>6295</v>
       </c>
       <c r="C1293" s="2" t="s">
-        <v>6301</v>
+        <v>6296</v>
       </c>
       <c r="D1293" s="2" t="s">
-        <v>6302</v>
+        <v>6297</v>
       </c>
       <c r="E1293" s="2" t="s">
-        <v>6303</v>
+        <v>6298</v>
       </c>
       <c r="F1293" s="2" t="s">
-        <v>6304</v>
+        <v>6299</v>
       </c>
       <c r="G1293" s="3">
         <v>4</v>
       </c>
       <c r="H1293" s="2" t="s">
-        <v>6305</v>
+        <v>6300</v>
       </c>
       <c r="I1293" s="2" t="s">
         <v>15</v>
@@ -58969,25 +58974,25 @@
         <v>1293</v>
       </c>
       <c r="B1294" s="2" t="s">
-        <v>6306</v>
+        <v>6301</v>
       </c>
       <c r="C1294" s="2" t="s">
-        <v>6307</v>
+        <v>6302</v>
       </c>
       <c r="D1294" s="2" t="s">
-        <v>6308</v>
+        <v>6303</v>
       </c>
       <c r="E1294" s="2" t="s">
-        <v>6309</v>
+        <v>6304</v>
       </c>
       <c r="F1294" s="2" t="s">
-        <v>6310</v>
+        <v>6305</v>
       </c>
       <c r="G1294" s="3">
         <v>1</v>
       </c>
       <c r="H1294" s="2" t="s">
-        <v>6311</v>
+        <v>6306</v>
       </c>
       <c r="I1294" s="2" t="s">
         <v>15</v>
@@ -58998,25 +59003,25 @@
         <v>1294</v>
       </c>
       <c r="B1295" s="2" t="s">
-        <v>6312</v>
+        <v>6307</v>
       </c>
       <c r="C1295" s="2" t="s">
         <v>838</v>
       </c>
       <c r="D1295" s="2" t="s">
-        <v>6313</v>
+        <v>6308</v>
       </c>
       <c r="E1295" s="2" t="s">
-        <v>6314</v>
+        <v>6309</v>
       </c>
       <c r="F1295" s="2" t="s">
-        <v>6315</v>
+        <v>6310</v>
       </c>
       <c r="G1295" s="3">
         <v>3</v>
       </c>
       <c r="H1295" s="2" t="s">
-        <v>6316</v>
+        <v>6311</v>
       </c>
       <c r="I1295" s="2" t="s">
         <v>165</v>
@@ -59027,25 +59032,25 @@
         <v>1295</v>
       </c>
       <c r="B1296" s="2" t="s">
-        <v>6317</v>
+        <v>6312</v>
       </c>
       <c r="C1296" s="2" t="s">
-        <v>6318</v>
+        <v>6313</v>
       </c>
       <c r="D1296" s="2" t="s">
-        <v>6319</v>
+        <v>6314</v>
       </c>
       <c r="E1296" s="2" t="s">
-        <v>6320</v>
+        <v>6315</v>
       </c>
       <c r="F1296" s="2" t="s">
-        <v>6321</v>
+        <v>6316</v>
       </c>
       <c r="G1296" s="3">
         <v>3</v>
       </c>
       <c r="H1296" s="2" t="s">
-        <v>6322</v>
+        <v>6317</v>
       </c>
       <c r="I1296" s="2" t="s">
         <v>15</v>
@@ -59056,7 +59061,7 @@
         <v>1296</v>
       </c>
       <c r="B1297" s="2" t="s">
-        <v>6323</v>
+        <v>6318</v>
       </c>
       <c r="C1297" s="2" t="s">
         <v>607</v>
@@ -59068,13 +59073,13 @@
         <v>618</v>
       </c>
       <c r="F1297" s="2" t="s">
-        <v>6324</v>
+        <v>6319</v>
       </c>
       <c r="G1297" s="3">
         <v>1</v>
       </c>
       <c r="H1297" s="2" t="s">
-        <v>6325</v>
+        <v>6320</v>
       </c>
       <c r="I1297" s="2" t="s">
         <v>15</v>
@@ -59085,7 +59090,7 @@
         <v>1297</v>
       </c>
       <c r="B1298" s="2" t="s">
-        <v>6326</v>
+        <v>6321</v>
       </c>
       <c r="C1298" s="2" t="s">
         <v>579</v>
@@ -59103,7 +59108,7 @@
         <v>1</v>
       </c>
       <c r="H1298" s="2" t="s">
-        <v>6327</v>
+        <v>6322</v>
       </c>
       <c r="I1298" s="2" t="s">
         <v>15</v>
@@ -59114,7 +59119,7 @@
         <v>1298</v>
       </c>
       <c r="B1299" s="2" t="s">
-        <v>6328</v>
+        <v>6323</v>
       </c>
       <c r="C1299" s="2" t="s">
         <v>231</v>
@@ -59132,7 +59137,7 @@
         <v>2</v>
       </c>
       <c r="H1299" s="2" t="s">
-        <v>6329</v>
+        <v>6324</v>
       </c>
       <c r="I1299" s="2" t="s">
         <v>22</v>
@@ -59143,25 +59148,25 @@
         <v>1299</v>
       </c>
       <c r="B1300" s="2" t="s">
-        <v>6330</v>
+        <v>6325</v>
       </c>
       <c r="C1300" s="2" t="s">
-        <v>6331</v>
+        <v>6326</v>
       </c>
       <c r="D1300" s="2" t="s">
-        <v>6332</v>
+        <v>6327</v>
       </c>
       <c r="E1300" s="2" t="s">
-        <v>6333</v>
+        <v>6328</v>
       </c>
       <c r="F1300" s="2" t="s">
-        <v>6334</v>
+        <v>6329</v>
       </c>
       <c r="G1300" s="3">
         <v>1</v>
       </c>
       <c r="H1300" s="2" t="s">
-        <v>6335</v>
+        <v>6330</v>
       </c>
       <c r="I1300" s="2" t="s">
         <v>15</v>
@@ -59172,25 +59177,25 @@
         <v>1300</v>
       </c>
       <c r="B1301" s="2" t="s">
-        <v>6336</v>
+        <v>6331</v>
       </c>
       <c r="C1301" s="2" t="s">
-        <v>6337</v>
+        <v>6332</v>
       </c>
       <c r="D1301" s="2" t="s">
-        <v>6338</v>
+        <v>6333</v>
       </c>
       <c r="E1301" s="2" t="s">
         <v>119</v>
       </c>
       <c r="F1301" s="2" t="s">
-        <v>6339</v>
+        <v>6334</v>
       </c>
       <c r="G1301" s="3">
         <v>1</v>
       </c>
       <c r="H1301" s="2" t="s">
-        <v>6340</v>
+        <v>6335</v>
       </c>
       <c r="I1301" s="2" t="s">
         <v>15</v>
@@ -59201,25 +59206,25 @@
         <v>1301</v>
       </c>
       <c r="B1302" s="2" t="s">
-        <v>6341</v>
+        <v>6336</v>
       </c>
       <c r="C1302" s="2" t="s">
-        <v>6342</v>
+        <v>6337</v>
       </c>
       <c r="D1302" s="2" t="s">
-        <v>6343</v>
+        <v>6338</v>
       </c>
       <c r="E1302" s="2" t="s">
-        <v>6344</v>
+        <v>6339</v>
       </c>
       <c r="F1302" s="2" t="s">
-        <v>6345</v>
+        <v>6340</v>
       </c>
       <c r="G1302" s="3">
         <v>1</v>
       </c>
       <c r="H1302" s="2" t="s">
-        <v>6346</v>
+        <v>6341</v>
       </c>
       <c r="I1302" s="2" t="s">
         <v>15</v>
@@ -59230,25 +59235,25 @@
         <v>1302</v>
       </c>
       <c r="B1303" s="2" t="s">
-        <v>6347</v>
+        <v>6342</v>
       </c>
       <c r="C1303" s="2" t="s">
-        <v>6348</v>
+        <v>6343</v>
       </c>
       <c r="D1303" s="2" t="s">
-        <v>6349</v>
+        <v>6344</v>
       </c>
       <c r="E1303" s="2" t="s">
-        <v>6350</v>
+        <v>6345</v>
       </c>
       <c r="F1303" s="2" t="s">
-        <v>6351</v>
+        <v>6346</v>
       </c>
       <c r="G1303" s="3">
         <v>2</v>
       </c>
       <c r="H1303" s="2" t="s">
-        <v>6352</v>
+        <v>6347</v>
       </c>
       <c r="I1303" s="2" t="s">
         <v>15</v>
@@ -59259,25 +59264,25 @@
         <v>1303</v>
       </c>
       <c r="B1304" s="2" t="s">
-        <v>6353</v>
+        <v>6348</v>
       </c>
       <c r="C1304" s="2" t="s">
-        <v>6354</v>
+        <v>6349</v>
       </c>
       <c r="D1304" s="2" t="s">
-        <v>6355</v>
+        <v>6350</v>
       </c>
       <c r="E1304" s="2" t="s">
-        <v>6356</v>
+        <v>6351</v>
       </c>
       <c r="F1304" s="2" t="s">
-        <v>6357</v>
+        <v>6352</v>
       </c>
       <c r="G1304" s="3">
         <v>3</v>
       </c>
       <c r="H1304" s="2" t="s">
-        <v>6358</v>
+        <v>6353</v>
       </c>
       <c r="I1304" s="2" t="s">
         <v>165</v>
@@ -59288,25 +59293,25 @@
         <v>1304</v>
       </c>
       <c r="B1305" s="2" t="s">
-        <v>6359</v>
+        <v>6354</v>
       </c>
       <c r="C1305" s="2" t="s">
-        <v>6360</v>
+        <v>6355</v>
       </c>
       <c r="D1305" s="2" t="s">
-        <v>6361</v>
+        <v>6356</v>
       </c>
       <c r="E1305" s="2" t="s">
-        <v>6362</v>
+        <v>6357</v>
       </c>
       <c r="F1305" s="2" t="s">
-        <v>6363</v>
+        <v>6358</v>
       </c>
       <c r="G1305" s="3">
         <v>1</v>
       </c>
       <c r="H1305" s="2" t="s">
-        <v>6364</v>
+        <v>6359</v>
       </c>
       <c r="I1305" s="2" t="s">
         <v>15</v>
@@ -59317,25 +59322,25 @@
         <v>1305</v>
       </c>
       <c r="B1306" s="2" t="s">
-        <v>6365</v>
+        <v>6360</v>
       </c>
       <c r="C1306" s="2" t="s">
-        <v>6366</v>
+        <v>6361</v>
       </c>
       <c r="D1306" s="2" t="s">
-        <v>6367</v>
+        <v>6362</v>
       </c>
       <c r="E1306" s="2" t="s">
-        <v>6368</v>
+        <v>6363</v>
       </c>
       <c r="F1306" s="2" t="s">
-        <v>6369</v>
+        <v>6364</v>
       </c>
       <c r="G1306" s="3">
         <v>2</v>
       </c>
       <c r="H1306" s="2" t="s">
-        <v>6370</v>
+        <v>6365</v>
       </c>
       <c r="I1306" s="2" t="s">
         <v>15</v>
@@ -59346,25 +59351,25 @@
         <v>1306</v>
       </c>
       <c r="B1307" s="2" t="s">
-        <v>6371</v>
+        <v>6366</v>
       </c>
       <c r="C1307" s="2" t="s">
-        <v>6372</v>
+        <v>6367</v>
       </c>
       <c r="D1307" s="2" t="s">
-        <v>6373</v>
+        <v>6368</v>
       </c>
       <c r="E1307" s="2" t="s">
         <v>5830</v>
       </c>
       <c r="F1307" s="2" t="s">
-        <v>6374</v>
+        <v>6369</v>
       </c>
       <c r="G1307" s="3">
         <v>4</v>
       </c>
       <c r="H1307" s="2" t="s">
-        <v>6375</v>
+        <v>6370</v>
       </c>
       <c r="I1307" s="2" t="s">
         <v>15</v>
@@ -59375,7 +59380,7 @@
         <v>1307</v>
       </c>
       <c r="B1308" s="2" t="s">
-        <v>6376</v>
+        <v>6371</v>
       </c>
       <c r="C1308" s="2" t="s">
         <v>909</v>
@@ -59393,7 +59398,7 @@
         <v>3</v>
       </c>
       <c r="H1308" s="2" t="s">
-        <v>6377</v>
+        <v>6372</v>
       </c>
       <c r="I1308" s="2" t="s">
         <v>15</v>
@@ -59404,7 +59409,7 @@
         <v>1308</v>
       </c>
       <c r="B1309" s="2" t="s">
-        <v>6378</v>
+        <v>6373</v>
       </c>
       <c r="C1309" s="2" t="s">
         <v>4355</v>
@@ -59433,7 +59438,7 @@
         <v>1309</v>
       </c>
       <c r="B1310" s="2" t="s">
-        <v>6379</v>
+        <v>6374</v>
       </c>
       <c r="C1310" s="2" t="s">
         <v>4355</v>
@@ -59451,7 +59456,7 @@
         <v>1</v>
       </c>
       <c r="H1310" s="2" t="s">
-        <v>6380</v>
+        <v>6375</v>
       </c>
       <c r="I1310" s="2" t="s">
         <v>15</v>
@@ -59462,7 +59467,7 @@
         <v>1310</v>
       </c>
       <c r="B1311" s="2" t="s">
-        <v>6381</v>
+        <v>6376</v>
       </c>
       <c r="C1311" s="2" t="s">
         <v>3340</v>
@@ -59491,7 +59496,7 @@
         <v>1311</v>
       </c>
       <c r="B1312" s="2" t="s">
-        <v>6382</v>
+        <v>6377</v>
       </c>
       <c r="C1312" s="2" t="s">
         <v>72</v>
@@ -59500,10 +59505,10 @@
         <v>77</v>
       </c>
       <c r="E1312" s="2" t="s">
-        <v>6383</v>
+        <v>6378</v>
       </c>
       <c r="F1312" s="2" t="s">
-        <v>6384</v>
+        <v>6379</v>
       </c>
       <c r="G1312" s="3">
         <v>2</v>
@@ -59520,25 +59525,25 @@
         <v>1312</v>
       </c>
       <c r="B1313" s="2" t="s">
-        <v>6385</v>
+        <v>6380</v>
       </c>
       <c r="C1313" s="2" t="s">
         <v>5436</v>
       </c>
       <c r="D1313" s="2" t="s">
-        <v>6386</v>
+        <v>6381</v>
       </c>
       <c r="E1313" s="2" t="s">
-        <v>6387</v>
+        <v>6382</v>
       </c>
       <c r="F1313" s="2" t="s">
-        <v>6388</v>
+        <v>6383</v>
       </c>
       <c r="G1313" s="3">
         <v>1</v>
       </c>
       <c r="H1313" s="2" t="s">
-        <v>6389</v>
+        <v>6384</v>
       </c>
       <c r="I1313" s="2" t="s">
         <v>15</v>
@@ -59549,25 +59554,25 @@
         <v>1313</v>
       </c>
       <c r="B1314" s="2" t="s">
-        <v>6390</v>
+        <v>6385</v>
       </c>
       <c r="C1314" s="2" t="s">
         <v>6190</v>
       </c>
       <c r="D1314" s="2" t="s">
-        <v>6894</v>
+        <v>6889</v>
       </c>
       <c r="E1314" s="2" t="s">
-        <v>6893</v>
+        <v>6888</v>
       </c>
       <c r="F1314" s="2" t="s">
-        <v>6895</v>
+        <v>6890</v>
       </c>
       <c r="G1314" s="3">
         <v>3</v>
       </c>
       <c r="H1314" s="2" t="s">
-        <v>6391</v>
+        <v>6386</v>
       </c>
       <c r="I1314" s="2" t="s">
         <v>15</v>
@@ -59578,19 +59583,19 @@
         <v>1314</v>
       </c>
       <c r="B1315" s="2" t="s">
-        <v>6889</v>
+        <v>6884</v>
       </c>
       <c r="C1315" s="2" t="s">
-        <v>6392</v>
+        <v>6387</v>
       </c>
       <c r="D1315" s="2" t="s">
-        <v>6890</v>
+        <v>6885</v>
       </c>
       <c r="E1315" s="2" t="s">
-        <v>6891</v>
+        <v>6886</v>
       </c>
       <c r="F1315" s="2" t="s">
-        <v>6892</v>
+        <v>6887</v>
       </c>
       <c r="G1315" s="3">
         <v>4</v>
@@ -59607,25 +59612,25 @@
         <v>1315</v>
       </c>
       <c r="B1316" s="2" t="s">
-        <v>6393</v>
+        <v>6388</v>
       </c>
       <c r="C1316" s="2" t="s">
-        <v>6394</v>
+        <v>6389</v>
       </c>
       <c r="D1316" s="2" t="s">
-        <v>6395</v>
+        <v>6390</v>
       </c>
       <c r="E1316" s="2" t="s">
         <v>5247</v>
       </c>
       <c r="F1316" s="2" t="s">
-        <v>6396</v>
+        <v>6391</v>
       </c>
       <c r="G1316" s="3">
         <v>2</v>
       </c>
       <c r="H1316" s="2" t="s">
-        <v>6397</v>
+        <v>6392</v>
       </c>
       <c r="I1316" s="2" t="s">
         <v>15</v>
@@ -59636,25 +59641,25 @@
         <v>1316</v>
       </c>
       <c r="B1317" s="2" t="s">
-        <v>6896</v>
+        <v>6891</v>
       </c>
       <c r="C1317" s="2" t="s">
-        <v>6398</v>
+        <v>6393</v>
       </c>
       <c r="D1317" s="2" t="s">
-        <v>6399</v>
+        <v>6394</v>
       </c>
       <c r="E1317" s="2" t="s">
-        <v>6400</v>
+        <v>6395</v>
       </c>
       <c r="F1317" s="2" t="s">
-        <v>6897</v>
+        <v>6892</v>
       </c>
       <c r="G1317" s="3">
         <v>2</v>
       </c>
       <c r="H1317" s="2" t="s">
-        <v>6401</v>
+        <v>6396</v>
       </c>
       <c r="I1317" s="2" t="s">
         <v>826</v>
@@ -59665,25 +59670,25 @@
         <v>1317</v>
       </c>
       <c r="B1318" s="2" t="s">
-        <v>6402</v>
+        <v>6397</v>
       </c>
       <c r="C1318" s="2" t="s">
-        <v>6403</v>
+        <v>6398</v>
       </c>
       <c r="D1318" s="2" t="s">
-        <v>6404</v>
+        <v>6399</v>
       </c>
       <c r="E1318" s="2" t="s">
-        <v>6405</v>
+        <v>6400</v>
       </c>
       <c r="F1318" s="2" t="s">
-        <v>6406</v>
+        <v>6401</v>
       </c>
       <c r="G1318" s="3">
         <v>1</v>
       </c>
       <c r="H1318" s="2" t="s">
-        <v>6407</v>
+        <v>6402</v>
       </c>
       <c r="I1318" s="2" t="s">
         <v>15</v>
@@ -59694,10 +59699,10 @@
         <v>1318</v>
       </c>
       <c r="B1319" s="2" t="s">
-        <v>6408</v>
+        <v>6403</v>
       </c>
       <c r="C1319" s="2" t="s">
-        <v>6409</v>
+        <v>6404</v>
       </c>
       <c r="D1319" s="2" t="s">
         <v>332</v>
@@ -59706,13 +59711,13 @@
         <v>333</v>
       </c>
       <c r="F1319" s="2" t="s">
-        <v>6410</v>
+        <v>6405</v>
       </c>
       <c r="G1319" s="3">
         <v>1</v>
       </c>
       <c r="H1319" s="2" t="s">
-        <v>6411</v>
+        <v>6406</v>
       </c>
       <c r="I1319" s="2" t="s">
         <v>158</v>
@@ -59723,7 +59728,7 @@
         <v>1319</v>
       </c>
       <c r="B1320" s="2" t="s">
-        <v>6412</v>
+        <v>6407</v>
       </c>
       <c r="C1320" s="2" t="s">
         <v>239</v>
@@ -59732,16 +59737,16 @@
         <v>732</v>
       </c>
       <c r="E1320" s="2" t="s">
-        <v>6413</v>
+        <v>6408</v>
       </c>
       <c r="F1320" s="2" t="s">
-        <v>6414</v>
+        <v>6409</v>
       </c>
       <c r="G1320" s="3">
         <v>2</v>
       </c>
       <c r="H1320" s="2" t="s">
-        <v>6415</v>
+        <v>6410</v>
       </c>
       <c r="I1320" s="2" t="s">
         <v>15</v>
@@ -59752,7 +59757,7 @@
         <v>1320</v>
       </c>
       <c r="B1321" s="2" t="s">
-        <v>6416</v>
+        <v>6411</v>
       </c>
       <c r="C1321" s="2" t="s">
         <v>1400</v>
@@ -59781,25 +59786,25 @@
         <v>1321</v>
       </c>
       <c r="B1322" s="2" t="s">
-        <v>6417</v>
+        <v>6412</v>
       </c>
       <c r="C1322" s="2" t="s">
-        <v>6821</v>
+        <v>6816</v>
       </c>
       <c r="D1322" s="2" t="s">
-        <v>6418</v>
+        <v>6413</v>
       </c>
       <c r="E1322" s="2" t="s">
-        <v>6419</v>
+        <v>6414</v>
       </c>
       <c r="F1322" s="2" t="s">
-        <v>6822</v>
+        <v>6817</v>
       </c>
       <c r="G1322" s="3">
         <v>4</v>
       </c>
       <c r="H1322" s="2" t="s">
-        <v>6420</v>
+        <v>6415</v>
       </c>
       <c r="I1322" s="2" t="s">
         <v>826</v>
@@ -59810,7 +59815,7 @@
         <v>1322</v>
       </c>
       <c r="B1323" s="2" t="s">
-        <v>6421</v>
+        <v>6416</v>
       </c>
       <c r="C1323" s="2" t="s">
         <v>1402</v>
@@ -59819,16 +59824,16 @@
         <v>1400</v>
       </c>
       <c r="E1323" s="2" t="s">
-        <v>6422</v>
+        <v>6417</v>
       </c>
       <c r="F1323" s="2" t="s">
-        <v>6423</v>
+        <v>6418</v>
       </c>
       <c r="G1323" s="3">
         <v>3</v>
       </c>
       <c r="H1323" s="2" t="s">
-        <v>6424</v>
+        <v>6419</v>
       </c>
       <c r="I1323" s="2" t="s">
         <v>826</v>
@@ -59839,16 +59844,16 @@
         <v>1323</v>
       </c>
       <c r="B1324" s="2" t="s">
-        <v>6425</v>
+        <v>6420</v>
       </c>
       <c r="C1324" s="2" t="s">
-        <v>6426</v>
+        <v>6421</v>
       </c>
       <c r="D1324" s="2" t="s">
-        <v>6427</v>
+        <v>6422</v>
       </c>
       <c r="E1324" s="2" t="s">
-        <v>6428</v>
+        <v>6423</v>
       </c>
       <c r="F1324" s="2" t="s">
         <v>51</v>
@@ -59868,7 +59873,7 @@
         <v>1324</v>
       </c>
       <c r="B1325" s="2" t="s">
-        <v>6429</v>
+        <v>6424</v>
       </c>
       <c r="C1325" s="2" t="s">
         <v>1400</v>
@@ -59897,7 +59902,7 @@
         <v>1325</v>
       </c>
       <c r="B1326" s="2" t="s">
-        <v>6430</v>
+        <v>6425</v>
       </c>
       <c r="C1326" s="2" t="s">
         <v>1400</v>
@@ -59906,14 +59911,14 @@
         <v>1401</v>
       </c>
       <c r="E1326" s="2" t="s">
-        <v>6431</v>
+        <v>6426</v>
       </c>
       <c r="F1326" s="2"/>
       <c r="G1326" s="3">
         <v>1</v>
       </c>
       <c r="H1326" s="2" t="s">
-        <v>6432</v>
+        <v>6427</v>
       </c>
       <c r="I1326" s="2" t="s">
         <v>826</v>
@@ -59924,25 +59929,25 @@
         <v>1326</v>
       </c>
       <c r="B1327" s="2" t="s">
-        <v>6433</v>
+        <v>6428</v>
       </c>
       <c r="C1327" s="2" t="s">
-        <v>6434</v>
+        <v>6429</v>
       </c>
       <c r="D1327" s="2" t="s">
-        <v>6422</v>
+        <v>6417</v>
       </c>
       <c r="E1327" s="2" t="s">
         <v>1400</v>
       </c>
       <c r="F1327" s="2" t="s">
-        <v>6435</v>
+        <v>6430</v>
       </c>
       <c r="G1327" s="3">
         <v>3</v>
       </c>
       <c r="H1327" s="2" t="s">
-        <v>6436</v>
+        <v>6431</v>
       </c>
       <c r="I1327" s="2" t="s">
         <v>15</v>
@@ -59953,13 +59958,13 @@
         <v>1327</v>
       </c>
       <c r="B1328" s="2" t="s">
-        <v>6437</v>
+        <v>6432</v>
       </c>
       <c r="C1328" s="2" t="s">
         <v>1400</v>
       </c>
       <c r="D1328" s="2" t="s">
-        <v>6438</v>
+        <v>6433</v>
       </c>
       <c r="E1328" s="2" t="s">
         <v>1402</v>
@@ -59971,7 +59976,7 @@
         <v>2</v>
       </c>
       <c r="H1328" s="2" t="s">
-        <v>6439</v>
+        <v>6434</v>
       </c>
       <c r="I1328" s="2" t="s">
         <v>798</v>
@@ -59982,13 +59987,13 @@
         <v>1328</v>
       </c>
       <c r="B1329" s="2" t="s">
-        <v>6440</v>
+        <v>6435</v>
       </c>
       <c r="C1329" s="2" t="s">
         <v>1400</v>
       </c>
       <c r="D1329" s="2" t="s">
-        <v>6422</v>
+        <v>6417</v>
       </c>
       <c r="E1329" s="2" t="s">
         <v>1402</v>
@@ -60011,13 +60016,13 @@
         <v>1329</v>
       </c>
       <c r="B1330" s="2" t="s">
-        <v>6441</v>
+        <v>6436</v>
       </c>
       <c r="C1330" s="2" t="s">
         <v>1400</v>
       </c>
       <c r="D1330" s="2" t="s">
-        <v>6422</v>
+        <v>6417</v>
       </c>
       <c r="E1330" s="2" t="s">
         <v>1402</v>
@@ -60040,13 +60045,13 @@
         <v>1330</v>
       </c>
       <c r="B1331" s="2" t="s">
-        <v>6442</v>
+        <v>6437</v>
       </c>
       <c r="C1331" s="2" t="s">
         <v>1400</v>
       </c>
       <c r="D1331" s="2" t="s">
-        <v>6422</v>
+        <v>6417</v>
       </c>
       <c r="E1331" s="2" t="s">
         <v>1402</v>
@@ -60058,7 +60063,7 @@
         <v>2</v>
       </c>
       <c r="H1331" s="2" t="s">
-        <v>6443</v>
+        <v>6438</v>
       </c>
       <c r="I1331" s="2" t="s">
         <v>15</v>
@@ -60069,25 +60074,25 @@
         <v>1331</v>
       </c>
       <c r="B1332" s="2" t="s">
-        <v>6444</v>
+        <v>6439</v>
       </c>
       <c r="C1332" s="2" t="s">
-        <v>6445</v>
+        <v>6440</v>
       </c>
       <c r="D1332" s="2" t="s">
-        <v>6446</v>
+        <v>6441</v>
       </c>
       <c r="E1332" s="2" t="s">
-        <v>6447</v>
+        <v>6442</v>
       </c>
       <c r="F1332" s="2" t="s">
-        <v>6448</v>
+        <v>6443</v>
       </c>
       <c r="G1332" s="3">
         <v>4</v>
       </c>
       <c r="H1332" s="2" t="s">
-        <v>6449</v>
+        <v>6444</v>
       </c>
       <c r="I1332" s="2" t="s">
         <v>22</v>
@@ -60098,16 +60103,16 @@
         <v>1332</v>
       </c>
       <c r="B1333" s="2" t="s">
-        <v>6450</v>
+        <v>6445</v>
       </c>
       <c r="C1333" s="2" t="s">
         <v>77</v>
       </c>
       <c r="D1333" s="2" t="s">
-        <v>6451</v>
+        <v>6446</v>
       </c>
       <c r="E1333" s="2" t="s">
-        <v>6452</v>
+        <v>6447</v>
       </c>
       <c r="F1333" s="2" t="s">
         <v>2325</v>
@@ -60127,7 +60132,7 @@
         <v>1333</v>
       </c>
       <c r="B1334" s="2" t="s">
-        <v>6453</v>
+        <v>6448</v>
       </c>
       <c r="C1334" s="2" t="s">
         <v>12</v>
@@ -60139,13 +60144,13 @@
         <v>448</v>
       </c>
       <c r="F1334" s="2" t="s">
-        <v>6454</v>
+        <v>6449</v>
       </c>
       <c r="G1334" s="3">
         <v>1</v>
       </c>
       <c r="H1334" s="2" t="s">
-        <v>6455</v>
+        <v>6450</v>
       </c>
       <c r="I1334" s="2" t="s">
         <v>826</v>
@@ -60156,16 +60161,16 @@
         <v>1334</v>
       </c>
       <c r="B1335" s="2" t="s">
-        <v>6456</v>
+        <v>6451</v>
       </c>
       <c r="C1335" s="2" t="s">
-        <v>6457</v>
+        <v>6452</v>
       </c>
       <c r="D1335" s="2" t="s">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="E1335" s="2" t="s">
-        <v>6459</v>
+        <v>6454</v>
       </c>
       <c r="F1335" s="2" t="s">
         <v>197</v>
@@ -60185,7 +60190,7 @@
         <v>1335</v>
       </c>
       <c r="B1336" s="2" t="s">
-        <v>6460</v>
+        <v>6455</v>
       </c>
       <c r="C1336" s="2" t="s">
         <v>5077</v>
@@ -60194,16 +60199,16 @@
         <v>4986</v>
       </c>
       <c r="E1336" s="2" t="s">
-        <v>6461</v>
+        <v>6456</v>
       </c>
       <c r="F1336" s="2" t="s">
-        <v>6462</v>
+        <v>6457</v>
       </c>
       <c r="G1336" s="3">
         <v>3</v>
       </c>
       <c r="H1336" s="2" t="s">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="I1336" s="2" t="s">
         <v>15</v>
@@ -60214,25 +60219,25 @@
         <v>1336</v>
       </c>
       <c r="B1337" s="2" t="s">
-        <v>6464</v>
+        <v>6459</v>
       </c>
       <c r="C1337" s="2" t="s">
-        <v>6465</v>
+        <v>6460</v>
       </c>
       <c r="D1337" s="2" t="s">
-        <v>6466</v>
+        <v>6461</v>
       </c>
       <c r="E1337" s="2" t="s">
-        <v>6467</v>
+        <v>6462</v>
       </c>
       <c r="F1337" s="2" t="s">
-        <v>6468</v>
+        <v>6463</v>
       </c>
       <c r="G1337" s="3">
         <v>3</v>
       </c>
       <c r="H1337" s="2" t="s">
-        <v>6469</v>
+        <v>6464</v>
       </c>
       <c r="I1337" s="2" t="s">
         <v>826</v>
@@ -60243,7 +60248,7 @@
         <v>1337</v>
       </c>
       <c r="B1338" s="2" t="s">
-        <v>6470</v>
+        <v>6465</v>
       </c>
       <c r="C1338" s="2" t="s">
         <v>513</v>
@@ -60255,13 +60260,13 @@
         <v>4986</v>
       </c>
       <c r="F1338" s="2" t="s">
-        <v>6471</v>
+        <v>6466</v>
       </c>
       <c r="G1338" s="3">
         <v>4</v>
       </c>
       <c r="H1338" s="2" t="s">
-        <v>6472</v>
+        <v>6467</v>
       </c>
       <c r="I1338" s="2" t="s">
         <v>22</v>
@@ -60272,7 +60277,7 @@
         <v>1338</v>
       </c>
       <c r="B1339" s="2" t="s">
-        <v>6473</v>
+        <v>6468</v>
       </c>
       <c r="C1339" s="2" t="s">
         <v>77</v>
@@ -60281,16 +60286,16 @@
         <v>568</v>
       </c>
       <c r="E1339" s="2" t="s">
-        <v>6474</v>
+        <v>6469</v>
       </c>
       <c r="F1339" s="2" t="s">
-        <v>6475</v>
+        <v>6470</v>
       </c>
       <c r="G1339" s="3">
         <v>2</v>
       </c>
       <c r="H1339" s="2" t="s">
-        <v>6476</v>
+        <v>6471</v>
       </c>
       <c r="I1339" s="2" t="s">
         <v>826</v>
@@ -60301,7 +60306,7 @@
         <v>1339</v>
       </c>
       <c r="B1340" s="2" t="s">
-        <v>6477</v>
+        <v>6472</v>
       </c>
       <c r="C1340" s="2" t="s">
         <v>321</v>
@@ -60313,13 +60318,13 @@
         <v>327</v>
       </c>
       <c r="F1340" s="2" t="s">
-        <v>6478</v>
+        <v>6473</v>
       </c>
       <c r="G1340" s="3">
         <v>2</v>
       </c>
       <c r="H1340" s="2" t="s">
-        <v>6479</v>
+        <v>6474</v>
       </c>
       <c r="I1340" s="2" t="s">
         <v>826</v>
@@ -60330,25 +60335,25 @@
         <v>1340</v>
       </c>
       <c r="B1341" s="2" t="s">
-        <v>6480</v>
+        <v>6475</v>
       </c>
       <c r="C1341" s="2" t="s">
-        <v>6481</v>
+        <v>6476</v>
       </c>
       <c r="D1341" s="2" t="s">
-        <v>6482</v>
+        <v>6477</v>
       </c>
       <c r="E1341" s="2" t="s">
-        <v>6465</v>
+        <v>6460</v>
       </c>
       <c r="F1341" s="2" t="s">
-        <v>6483</v>
+        <v>6478</v>
       </c>
       <c r="G1341" s="3">
         <v>4</v>
       </c>
       <c r="H1341" s="2" t="s">
-        <v>6484</v>
+        <v>6479</v>
       </c>
       <c r="I1341" s="2" t="s">
         <v>826</v>
@@ -60359,16 +60364,16 @@
         <v>1341</v>
       </c>
       <c r="B1342" s="2" t="s">
-        <v>6485</v>
+        <v>6480</v>
       </c>
       <c r="C1342" s="2" t="s">
-        <v>6486</v>
+        <v>6481</v>
       </c>
       <c r="D1342" s="2" t="s">
-        <v>6487</v>
+        <v>6482</v>
       </c>
       <c r="E1342" s="2" t="s">
-        <v>6488</v>
+        <v>6483</v>
       </c>
       <c r="F1342" s="2" t="s">
         <v>197</v>
@@ -60388,25 +60393,25 @@
         <v>1342</v>
       </c>
       <c r="B1343" s="2" t="s">
-        <v>6489</v>
+        <v>6484</v>
       </c>
       <c r="C1343" s="2" t="s">
-        <v>6490</v>
+        <v>6485</v>
       </c>
       <c r="D1343" s="2" t="s">
-        <v>6491</v>
+        <v>6486</v>
       </c>
       <c r="E1343" s="2" t="s">
-        <v>6492</v>
+        <v>6487</v>
       </c>
       <c r="F1343" s="2" t="s">
-        <v>6493</v>
+        <v>6488</v>
       </c>
       <c r="G1343" s="3">
         <v>3</v>
       </c>
       <c r="H1343" s="2" t="s">
-        <v>6494</v>
+        <v>6489</v>
       </c>
       <c r="I1343" s="2" t="s">
         <v>826</v>
@@ -60417,25 +60422,25 @@
         <v>1343</v>
       </c>
       <c r="B1344" s="2" t="s">
-        <v>6495</v>
+        <v>6490</v>
       </c>
       <c r="C1344" s="2" t="s">
-        <v>6496</v>
+        <v>6491</v>
       </c>
       <c r="D1344" s="2" t="s">
-        <v>6497</v>
+        <v>6492</v>
       </c>
       <c r="E1344" s="2" t="s">
-        <v>6498</v>
+        <v>6493</v>
       </c>
       <c r="F1344" s="2" t="s">
-        <v>6499</v>
+        <v>6494</v>
       </c>
       <c r="G1344" s="3">
         <v>4</v>
       </c>
       <c r="H1344" s="2" t="s">
-        <v>6500</v>
+        <v>6495</v>
       </c>
       <c r="I1344" s="2" t="s">
         <v>826</v>
@@ -60446,7 +60451,7 @@
         <v>1344</v>
       </c>
       <c r="B1345" s="2" t="s">
-        <v>6501</v>
+        <v>6496</v>
       </c>
       <c r="C1345" s="2" t="s">
         <v>511</v>
@@ -60455,7 +60460,7 @@
         <v>510</v>
       </c>
       <c r="E1345" s="2" t="s">
-        <v>6502</v>
+        <v>6497</v>
       </c>
       <c r="F1345" s="2"/>
       <c r="G1345" s="3">
@@ -60473,25 +60478,25 @@
         <v>1345</v>
       </c>
       <c r="B1346" s="2" t="s">
-        <v>6503</v>
+        <v>6498</v>
       </c>
       <c r="C1346" s="2" t="s">
-        <v>6504</v>
+        <v>6499</v>
       </c>
       <c r="D1346" s="2" t="s">
-        <v>6505</v>
+        <v>6500</v>
       </c>
       <c r="E1346" s="2" t="s">
-        <v>6506</v>
+        <v>6501</v>
       </c>
       <c r="F1346" s="2" t="s">
-        <v>6507</v>
+        <v>6502</v>
       </c>
       <c r="G1346" s="3">
         <v>4</v>
       </c>
       <c r="H1346" s="2" t="s">
-        <v>6508</v>
+        <v>6503</v>
       </c>
       <c r="I1346" s="2" t="s">
         <v>15</v>
@@ -60502,25 +60507,25 @@
         <v>1346</v>
       </c>
       <c r="B1347" s="2" t="s">
-        <v>6509</v>
+        <v>6504</v>
       </c>
       <c r="C1347" s="2" t="s">
         <v>1463</v>
       </c>
       <c r="D1347" s="2" t="s">
-        <v>6510</v>
+        <v>6505</v>
       </c>
       <c r="E1347" s="2" t="s">
         <v>1137</v>
       </c>
       <c r="F1347" s="2" t="s">
-        <v>6511</v>
+        <v>6506</v>
       </c>
       <c r="G1347" s="3">
         <v>2</v>
       </c>
       <c r="H1347" s="2" t="s">
-        <v>6512</v>
+        <v>6507</v>
       </c>
       <c r="I1347" s="2" t="s">
         <v>826</v>
@@ -60531,25 +60536,25 @@
         <v>1347</v>
       </c>
       <c r="B1348" s="2" t="s">
-        <v>6513</v>
+        <v>6508</v>
       </c>
       <c r="C1348" s="2" t="s">
-        <v>6514</v>
+        <v>6509</v>
       </c>
       <c r="D1348" s="2" t="s">
-        <v>6515</v>
+        <v>6510</v>
       </c>
       <c r="E1348" s="2" t="s">
-        <v>6516</v>
+        <v>6511</v>
       </c>
       <c r="F1348" s="2" t="s">
-        <v>6517</v>
+        <v>6512</v>
       </c>
       <c r="G1348" s="3">
         <v>4</v>
       </c>
       <c r="H1348" s="2" t="s">
-        <v>6518</v>
+        <v>6513</v>
       </c>
       <c r="I1348" s="2" t="s">
         <v>826</v>
@@ -60560,13 +60565,13 @@
         <v>1348</v>
       </c>
       <c r="B1349" s="2" t="s">
-        <v>6519</v>
+        <v>6514</v>
       </c>
       <c r="C1349" s="2" t="s">
         <v>119</v>
       </c>
       <c r="D1349" s="2" t="s">
-        <v>6520</v>
+        <v>6515</v>
       </c>
       <c r="E1349" s="2" t="s">
         <v>26</v>
@@ -60578,7 +60583,7 @@
         <v>4</v>
       </c>
       <c r="H1349" s="2" t="s">
-        <v>6521</v>
+        <v>6516</v>
       </c>
       <c r="I1349" s="2" t="s">
         <v>826</v>
@@ -60589,36 +60594,36 @@
         <v>1349</v>
       </c>
       <c r="B1350" s="2" t="s">
-        <v>6522</v>
+        <v>6517</v>
       </c>
       <c r="C1350" s="2" t="s">
-        <v>6523</v>
+        <v>6518</v>
       </c>
       <c r="D1350" s="2" t="s">
-        <v>6524</v>
+        <v>6519</v>
       </c>
       <c r="E1350" s="2" t="s">
-        <v>6525</v>
+        <v>6520</v>
       </c>
       <c r="F1350" s="2" t="s">
-        <v>6526</v>
+        <v>6521</v>
       </c>
       <c r="G1350" s="3">
         <v>4</v>
       </c>
       <c r="H1350" s="2" t="s">
-        <v>6527</v>
+        <v>6522</v>
       </c>
       <c r="I1350" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="1351" spans="1:9" ht="46.3">
+    <row r="1351" spans="1:9" ht="30.9">
       <c r="A1351" s="2">
         <v>1350</v>
       </c>
       <c r="B1351" s="2" t="s">
-        <v>6528</v>
+        <v>6523</v>
       </c>
       <c r="C1351" s="2" t="s">
         <v>773</v>
@@ -60627,7 +60632,7 @@
         <v>400</v>
       </c>
       <c r="E1351" s="2" t="s">
-        <v>6529</v>
+        <v>6524</v>
       </c>
       <c r="F1351" s="2" t="s">
         <v>791</v>
@@ -60636,7 +60641,7 @@
         <v>1</v>
       </c>
       <c r="H1351" s="2" t="s">
-        <v>6530</v>
+        <v>6525</v>
       </c>
       <c r="I1351" s="2" t="s">
         <v>22</v>
@@ -60647,36 +60652,36 @@
         <v>1351</v>
       </c>
       <c r="B1352" s="2" t="s">
-        <v>6531</v>
+        <v>6526</v>
       </c>
       <c r="C1352" s="2" t="s">
-        <v>6532</v>
+        <v>6527</v>
       </c>
       <c r="D1352" s="2" t="s">
-        <v>6533</v>
+        <v>6528</v>
       </c>
       <c r="E1352" s="2" t="s">
-        <v>6534</v>
+        <v>6529</v>
       </c>
       <c r="F1352" s="2" t="s">
-        <v>6535</v>
+        <v>6530</v>
       </c>
       <c r="G1352" s="3">
         <v>1</v>
       </c>
       <c r="H1352" s="2" t="s">
-        <v>6536</v>
+        <v>6531</v>
       </c>
       <c r="I1352" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="1353" spans="1:9" ht="46.3">
+    <row r="1353" spans="1:9" ht="30.9">
       <c r="A1353" s="2">
         <v>1352</v>
       </c>
       <c r="B1353" s="2" t="s">
-        <v>6537</v>
+        <v>6532</v>
       </c>
       <c r="C1353" s="2" t="s">
         <v>160</v>
@@ -60694,7 +60699,7 @@
         <v>1</v>
       </c>
       <c r="H1353" s="2" t="s">
-        <v>6538</v>
+        <v>6533</v>
       </c>
       <c r="I1353" s="2" t="s">
         <v>15</v>
@@ -60705,23 +60710,23 @@
         <v>1353</v>
       </c>
       <c r="B1354" s="2" t="s">
-        <v>6539</v>
+        <v>6534</v>
       </c>
       <c r="C1354" s="2" t="s">
-        <v>6540</v>
+        <v>6535</v>
       </c>
       <c r="D1354" s="2" t="s">
-        <v>6541</v>
+        <v>6536</v>
       </c>
       <c r="E1354" s="2" t="s">
-        <v>6542</v>
+        <v>6537</v>
       </c>
       <c r="F1354" s="2"/>
       <c r="G1354" s="3">
         <v>1</v>
       </c>
       <c r="H1354" s="2" t="s">
-        <v>6543</v>
+        <v>6538</v>
       </c>
       <c r="I1354" s="2" t="s">
         <v>826</v>
@@ -60732,7 +60737,7 @@
         <v>1354</v>
       </c>
       <c r="B1355" s="2" t="s">
-        <v>6544</v>
+        <v>6539</v>
       </c>
       <c r="C1355" s="2" t="s">
         <v>842</v>
@@ -60748,7 +60753,7 @@
         <v>4</v>
       </c>
       <c r="H1355" s="2" t="s">
-        <v>6545</v>
+        <v>6540</v>
       </c>
       <c r="I1355" s="2" t="s">
         <v>826</v>
@@ -60759,25 +60764,25 @@
         <v>1355</v>
       </c>
       <c r="B1356" s="2" t="s">
-        <v>6546</v>
+        <v>6541</v>
       </c>
       <c r="C1356" s="2" t="s">
-        <v>6547</v>
+        <v>6542</v>
       </c>
       <c r="D1356" s="2" t="s">
-        <v>6548</v>
+        <v>6543</v>
       </c>
       <c r="E1356" s="2" t="s">
-        <v>6549</v>
+        <v>6544</v>
       </c>
       <c r="F1356" s="2" t="s">
-        <v>6550</v>
+        <v>6545</v>
       </c>
       <c r="G1356" s="3">
         <v>2</v>
       </c>
       <c r="H1356" s="2" t="s">
-        <v>6551</v>
+        <v>6546</v>
       </c>
       <c r="I1356" s="2" t="s">
         <v>826</v>
@@ -60788,25 +60793,25 @@
         <v>1356</v>
       </c>
       <c r="B1357" s="2" t="s">
-        <v>6552</v>
+        <v>6547</v>
       </c>
       <c r="C1357" s="2" t="s">
-        <v>6553</v>
+        <v>6548</v>
       </c>
       <c r="D1357" s="2" t="s">
-        <v>6554</v>
+        <v>6549</v>
       </c>
       <c r="E1357" s="2" t="s">
-        <v>6555</v>
+        <v>6550</v>
       </c>
       <c r="F1357" s="2" t="s">
-        <v>6556</v>
+        <v>6551</v>
       </c>
       <c r="G1357" s="3">
         <v>2</v>
       </c>
       <c r="H1357" s="2" t="s">
-        <v>6557</v>
+        <v>6552</v>
       </c>
       <c r="I1357" s="2" t="s">
         <v>826</v>
@@ -60817,25 +60822,25 @@
         <v>1357</v>
       </c>
       <c r="B1358" s="2" t="s">
-        <v>6558</v>
+        <v>6553</v>
       </c>
       <c r="C1358" s="2" t="s">
-        <v>6559</v>
+        <v>6554</v>
       </c>
       <c r="D1358" s="2" t="s">
-        <v>6560</v>
+        <v>6555</v>
       </c>
       <c r="E1358" s="2" t="s">
-        <v>6561</v>
+        <v>6556</v>
       </c>
       <c r="F1358" s="2" t="s">
-        <v>6562</v>
+        <v>6557</v>
       </c>
       <c r="G1358" s="3">
         <v>4</v>
       </c>
       <c r="H1358" s="2" t="s">
-        <v>6563</v>
+        <v>6558</v>
       </c>
       <c r="I1358" s="2" t="s">
         <v>826</v>
@@ -60846,25 +60851,25 @@
         <v>1358</v>
       </c>
       <c r="B1359" s="2" t="s">
-        <v>6564</v>
+        <v>6559</v>
       </c>
       <c r="C1359" s="2" t="s">
-        <v>6565</v>
+        <v>6560</v>
       </c>
       <c r="D1359" s="2" t="s">
-        <v>6566</v>
+        <v>6561</v>
       </c>
       <c r="E1359" s="2" t="s">
-        <v>6567</v>
+        <v>6562</v>
       </c>
       <c r="F1359" s="2" t="s">
-        <v>6568</v>
+        <v>6563</v>
       </c>
       <c r="G1359" s="3">
         <v>4</v>
       </c>
       <c r="H1359" s="2" t="s">
-        <v>6569</v>
+        <v>6564</v>
       </c>
       <c r="I1359" s="2" t="s">
         <v>826</v>
@@ -60875,23 +60880,23 @@
         <v>1359</v>
       </c>
       <c r="B1360" s="2" t="s">
-        <v>6570</v>
+        <v>6565</v>
       </c>
       <c r="C1360" s="2" t="s">
-        <v>6571</v>
+        <v>6566</v>
       </c>
       <c r="D1360" s="2"/>
       <c r="E1360" s="2" t="s">
-        <v>6572</v>
+        <v>6567</v>
       </c>
       <c r="F1360" s="2" t="s">
-        <v>6573</v>
+        <v>6568</v>
       </c>
       <c r="G1360" s="3">
         <v>1</v>
       </c>
       <c r="H1360" s="2" t="s">
-        <v>6574</v>
+        <v>6569</v>
       </c>
       <c r="I1360" s="2" t="s">
         <v>826</v>
@@ -60902,25 +60907,25 @@
         <v>1360</v>
       </c>
       <c r="B1361" s="2" t="s">
-        <v>6575</v>
+        <v>6570</v>
       </c>
       <c r="C1361" s="2" t="s">
-        <v>6576</v>
+        <v>6571</v>
       </c>
       <c r="D1361" s="2" t="s">
-        <v>6577</v>
+        <v>6572</v>
       </c>
       <c r="E1361" s="2" t="s">
-        <v>6578</v>
+        <v>6573</v>
       </c>
       <c r="F1361" s="2" t="s">
-        <v>6579</v>
+        <v>6574</v>
       </c>
       <c r="G1361" s="3">
         <v>3</v>
       </c>
       <c r="H1361" s="2" t="s">
-        <v>6580</v>
+        <v>6575</v>
       </c>
       <c r="I1361" s="2" t="s">
         <v>15</v>
@@ -60931,7 +60936,7 @@
         <v>1361</v>
       </c>
       <c r="B1362" s="2" t="s">
-        <v>6581</v>
+        <v>6576</v>
       </c>
       <c r="C1362" s="2" t="s">
         <v>1330</v>
@@ -60940,10 +60945,10 @@
         <v>1331</v>
       </c>
       <c r="E1362" s="2" t="s">
-        <v>6582</v>
+        <v>6577</v>
       </c>
       <c r="F1362" s="2" t="s">
-        <v>6583</v>
+        <v>6578</v>
       </c>
       <c r="G1362" s="3">
         <v>1</v>
@@ -60960,25 +60965,25 @@
         <v>1362</v>
       </c>
       <c r="B1363" s="2" t="s">
-        <v>6584</v>
+        <v>6579</v>
       </c>
       <c r="C1363" s="2" t="s">
-        <v>6585</v>
+        <v>6580</v>
       </c>
       <c r="D1363" s="2" t="s">
-        <v>6586</v>
+        <v>6581</v>
       </c>
       <c r="E1363" s="2" t="s">
-        <v>6587</v>
+        <v>6582</v>
       </c>
       <c r="F1363" s="2" t="s">
-        <v>6588</v>
+        <v>6583</v>
       </c>
       <c r="G1363" s="3">
         <v>2</v>
       </c>
       <c r="H1363" s="2" t="s">
-        <v>6589</v>
+        <v>6584</v>
       </c>
       <c r="I1363" s="2" t="s">
         <v>15</v>
@@ -60989,25 +60994,25 @@
         <v>1363</v>
       </c>
       <c r="B1364" s="2" t="s">
-        <v>6590</v>
+        <v>6585</v>
       </c>
       <c r="C1364" s="2" t="s">
-        <v>6591</v>
+        <v>6586</v>
       </c>
       <c r="D1364" s="2" t="s">
-        <v>6592</v>
+        <v>6587</v>
       </c>
       <c r="E1364" s="2" t="s">
-        <v>6593</v>
+        <v>6588</v>
       </c>
       <c r="F1364" s="2" t="s">
-        <v>6594</v>
+        <v>6589</v>
       </c>
       <c r="G1364" s="3">
         <v>1</v>
       </c>
       <c r="H1364" s="2" t="s">
-        <v>6595</v>
+        <v>6590</v>
       </c>
       <c r="I1364" s="2" t="s">
         <v>15</v>
@@ -61047,7 +61052,7 @@
         <v>1365</v>
       </c>
       <c r="B1366" s="2" t="s">
-        <v>6596</v>
+        <v>6591</v>
       </c>
       <c r="C1366" s="2" t="s">
         <v>1395</v>
@@ -61065,7 +61070,7 @@
         <v>3</v>
       </c>
       <c r="H1366" s="2" t="s">
-        <v>6597</v>
+        <v>6592</v>
       </c>
       <c r="I1366" s="2" t="s">
         <v>15</v>
@@ -61076,25 +61081,25 @@
         <v>1366</v>
       </c>
       <c r="B1367" s="2" t="s">
-        <v>6598</v>
+        <v>6593</v>
       </c>
       <c r="C1367" s="2" t="s">
-        <v>6599</v>
+        <v>6594</v>
       </c>
       <c r="D1367" s="2" t="s">
-        <v>6600</v>
+        <v>6595</v>
       </c>
       <c r="E1367" s="2" t="s">
-        <v>6601</v>
+        <v>6596</v>
       </c>
       <c r="F1367" s="2" t="s">
-        <v>6602</v>
+        <v>6597</v>
       </c>
       <c r="G1367" s="3">
         <v>3</v>
       </c>
       <c r="H1367" s="2" t="s">
-        <v>6603</v>
+        <v>6598</v>
       </c>
       <c r="I1367" s="2" t="s">
         <v>826</v>
@@ -61105,16 +61110,16 @@
         <v>1367</v>
       </c>
       <c r="B1368" s="2" t="s">
-        <v>6604</v>
+        <v>6599</v>
       </c>
       <c r="C1368" s="2" t="s">
-        <v>6605</v>
+        <v>6600</v>
       </c>
       <c r="D1368" s="2" t="s">
-        <v>6606</v>
+        <v>6601</v>
       </c>
       <c r="E1368" s="2" t="s">
-        <v>6607</v>
+        <v>6602</v>
       </c>
       <c r="F1368" s="2" t="s">
         <v>51</v>
@@ -61134,25 +61139,25 @@
         <v>1368</v>
       </c>
       <c r="B1369" s="2" t="s">
-        <v>6608</v>
+        <v>6603</v>
       </c>
       <c r="C1369" s="2" t="s">
-        <v>6609</v>
+        <v>6604</v>
       </c>
       <c r="D1369" s="2" t="s">
-        <v>6610</v>
+        <v>6605</v>
       </c>
       <c r="E1369" s="2" t="s">
-        <v>6611</v>
+        <v>6606</v>
       </c>
       <c r="F1369" s="2" t="s">
-        <v>6612</v>
+        <v>6607</v>
       </c>
       <c r="G1369" s="3">
         <v>3</v>
       </c>
       <c r="H1369" s="2" t="s">
-        <v>6613</v>
+        <v>6608</v>
       </c>
       <c r="I1369" s="2" t="s">
         <v>798</v>
@@ -61163,25 +61168,25 @@
         <v>1369</v>
       </c>
       <c r="B1370" s="2" t="s">
-        <v>6614</v>
+        <v>6609</v>
       </c>
       <c r="C1370" s="2" t="s">
         <v>1688</v>
       </c>
       <c r="D1370" s="2" t="s">
-        <v>6615</v>
+        <v>6610</v>
       </c>
       <c r="E1370" s="2" t="s">
-        <v>6616</v>
+        <v>6611</v>
       </c>
       <c r="F1370" s="2" t="s">
-        <v>6617</v>
+        <v>6612</v>
       </c>
       <c r="G1370" s="3">
         <v>3</v>
       </c>
       <c r="H1370" s="2" t="s">
-        <v>6618</v>
+        <v>6613</v>
       </c>
       <c r="I1370" s="2" t="s">
         <v>15</v>
@@ -61192,25 +61197,25 @@
         <v>1370</v>
       </c>
       <c r="B1371" s="2" t="s">
-        <v>6619</v>
+        <v>6614</v>
       </c>
       <c r="C1371" s="2" t="s">
-        <v>6620</v>
+        <v>6615</v>
       </c>
       <c r="D1371" s="2" t="s">
-        <v>6621</v>
+        <v>6616</v>
       </c>
       <c r="E1371" s="2" t="s">
-        <v>6622</v>
+        <v>6617</v>
       </c>
       <c r="F1371" s="2" t="s">
-        <v>6623</v>
+        <v>6618</v>
       </c>
       <c r="G1371" s="3">
         <v>2</v>
       </c>
       <c r="H1371" s="2" t="s">
-        <v>6624</v>
+        <v>6619</v>
       </c>
       <c r="I1371" s="2" t="s">
         <v>15</v>
@@ -61221,13 +61226,13 @@
         <v>1371</v>
       </c>
       <c r="B1372" s="2" t="s">
-        <v>6625</v>
+        <v>6620</v>
       </c>
       <c r="C1372" s="2" t="s">
         <v>2415</v>
       </c>
       <c r="D1372" s="2" t="s">
-        <v>6626</v>
+        <v>6621</v>
       </c>
       <c r="E1372" s="2" t="s">
         <v>2416</v>
@@ -61239,7 +61244,7 @@
         <v>2</v>
       </c>
       <c r="H1372" s="2" t="s">
-        <v>6627</v>
+        <v>6622</v>
       </c>
       <c r="I1372" s="2" t="s">
         <v>15</v>
@@ -61250,25 +61255,25 @@
         <v>1372</v>
       </c>
       <c r="B1373" s="2" t="s">
-        <v>6628</v>
+        <v>6623</v>
       </c>
       <c r="C1373" s="2" t="s">
         <v>2356</v>
       </c>
       <c r="D1373" s="2" t="s">
-        <v>6629</v>
+        <v>6624</v>
       </c>
       <c r="E1373" s="2" t="s">
-        <v>6630</v>
+        <v>6625</v>
       </c>
       <c r="F1373" s="2" t="s">
-        <v>6631</v>
+        <v>6626</v>
       </c>
       <c r="G1373" s="3">
         <v>2</v>
       </c>
       <c r="H1373" s="2" t="s">
-        <v>6632</v>
+        <v>6627</v>
       </c>
       <c r="I1373" s="2" t="s">
         <v>15</v>
@@ -61279,25 +61284,25 @@
         <v>1373</v>
       </c>
       <c r="B1374" s="2" t="s">
-        <v>6633</v>
+        <v>6628</v>
       </c>
       <c r="C1374" s="2" t="s">
-        <v>6634</v>
+        <v>6629</v>
       </c>
       <c r="D1374" s="2" t="s">
-        <v>6635</v>
+        <v>6630</v>
       </c>
       <c r="E1374" s="2" t="s">
-        <v>6636</v>
+        <v>6631</v>
       </c>
       <c r="F1374" s="2" t="s">
-        <v>6637</v>
+        <v>6632</v>
       </c>
       <c r="G1374" s="3">
         <v>4</v>
       </c>
       <c r="H1374" s="2" t="s">
-        <v>6638</v>
+        <v>6633</v>
       </c>
       <c r="I1374" s="2" t="s">
         <v>15</v>
@@ -61308,25 +61313,25 @@
         <v>1374</v>
       </c>
       <c r="B1375" s="2" t="s">
-        <v>6639</v>
+        <v>6634</v>
       </c>
       <c r="C1375" s="2" t="s">
-        <v>6640</v>
+        <v>6635</v>
       </c>
       <c r="D1375" s="2" t="s">
-        <v>6641</v>
+        <v>6636</v>
       </c>
       <c r="E1375" s="2" t="s">
-        <v>6642</v>
+        <v>6637</v>
       </c>
       <c r="F1375" s="2" t="s">
-        <v>6643</v>
+        <v>6638</v>
       </c>
       <c r="G1375" s="3">
         <v>1</v>
       </c>
       <c r="H1375" s="2" t="s">
-        <v>6644</v>
+        <v>6639</v>
       </c>
       <c r="I1375" s="2" t="s">
         <v>826</v>
@@ -61337,25 +61342,25 @@
         <v>1375</v>
       </c>
       <c r="B1376" s="2" t="s">
-        <v>6645</v>
+        <v>6640</v>
       </c>
       <c r="C1376" s="2" t="s">
-        <v>6646</v>
+        <v>6641</v>
       </c>
       <c r="D1376" s="2" t="s">
-        <v>6647</v>
+        <v>6642</v>
       </c>
       <c r="E1376" s="2" t="s">
-        <v>6648</v>
+        <v>6643</v>
       </c>
       <c r="F1376" s="2" t="s">
-        <v>6649</v>
+        <v>6644</v>
       </c>
       <c r="G1376" s="3">
         <v>2</v>
       </c>
       <c r="H1376" s="2" t="s">
-        <v>6650</v>
+        <v>6645</v>
       </c>
       <c r="I1376" s="2" t="s">
         <v>826</v>
@@ -61366,25 +61371,25 @@
         <v>1376</v>
       </c>
       <c r="B1377" s="2" t="s">
-        <v>6651</v>
+        <v>6646</v>
       </c>
       <c r="C1377" s="2" t="s">
-        <v>6652</v>
+        <v>6647</v>
       </c>
       <c r="D1377" s="2" t="s">
-        <v>6653</v>
+        <v>6648</v>
       </c>
       <c r="E1377" s="2" t="s">
-        <v>6654</v>
+        <v>6649</v>
       </c>
       <c r="F1377" s="2" t="s">
-        <v>6655</v>
+        <v>6650</v>
       </c>
       <c r="G1377" s="3">
         <v>3</v>
       </c>
       <c r="H1377" s="2" t="s">
-        <v>6656</v>
+        <v>6651</v>
       </c>
       <c r="I1377" s="2" t="s">
         <v>15</v>
@@ -61395,7 +61400,7 @@
         <v>1377</v>
       </c>
       <c r="B1378" s="2" t="s">
-        <v>6657</v>
+        <v>6652</v>
       </c>
       <c r="C1378" s="2" t="s">
         <v>77</v>
@@ -61424,25 +61429,25 @@
         <v>1378</v>
       </c>
       <c r="B1379" s="2" t="s">
-        <v>6955</v>
+        <v>6950</v>
       </c>
       <c r="C1379" s="2" t="s">
-        <v>6956</v>
+        <v>6951</v>
       </c>
       <c r="D1379" s="2" t="s">
-        <v>6957</v>
+        <v>6952</v>
       </c>
       <c r="E1379" s="2" t="s">
-        <v>6958</v>
+        <v>6953</v>
       </c>
       <c r="F1379" s="2" t="s">
-        <v>6959</v>
+        <v>6954</v>
       </c>
       <c r="G1379" s="3">
         <v>1</v>
       </c>
       <c r="H1379" s="2" t="s">
-        <v>6658</v>
+        <v>6653</v>
       </c>
       <c r="I1379" s="2" t="s">
         <v>826</v>
@@ -61453,7 +61458,7 @@
         <v>1379</v>
       </c>
       <c r="B1380" s="2" t="s">
-        <v>6659</v>
+        <v>6654</v>
       </c>
       <c r="C1380" s="2" t="s">
         <v>376</v>
@@ -61471,7 +61476,7 @@
         <v>1</v>
       </c>
       <c r="H1380" s="2" t="s">
-        <v>6660</v>
+        <v>6655</v>
       </c>
       <c r="I1380" s="2" t="s">
         <v>826</v>
@@ -61482,10 +61487,10 @@
         <v>1380</v>
       </c>
       <c r="B1381" s="2" t="s">
-        <v>6661</v>
+        <v>6656</v>
       </c>
       <c r="C1381" s="2" t="s">
-        <v>6662</v>
+        <v>6657</v>
       </c>
       <c r="D1381" s="2" t="s">
         <v>12</v>
@@ -61494,13 +61499,13 @@
         <v>891</v>
       </c>
       <c r="F1381" s="2" t="s">
-        <v>6663</v>
+        <v>6658</v>
       </c>
       <c r="G1381" s="3">
         <v>1</v>
       </c>
       <c r="H1381" s="2" t="s">
-        <v>6664</v>
+        <v>6659</v>
       </c>
       <c r="I1381" s="2" t="s">
         <v>826</v>
@@ -61511,25 +61516,25 @@
         <v>1381</v>
       </c>
       <c r="B1382" s="2" t="s">
-        <v>6665</v>
+        <v>6660</v>
       </c>
       <c r="C1382" s="2" t="s">
-        <v>6666</v>
+        <v>6661</v>
       </c>
       <c r="D1382" s="2" t="s">
-        <v>6667</v>
+        <v>6662</v>
       </c>
       <c r="E1382" s="2" t="s">
-        <v>6668</v>
+        <v>6663</v>
       </c>
       <c r="F1382" s="2" t="s">
-        <v>6669</v>
+        <v>6664</v>
       </c>
       <c r="G1382" s="3">
         <v>2</v>
       </c>
       <c r="H1382" s="2" t="s">
-        <v>6670</v>
+        <v>6665</v>
       </c>
       <c r="I1382" s="2" t="s">
         <v>15</v>
@@ -61540,25 +61545,25 @@
         <v>1382</v>
       </c>
       <c r="B1383" s="2" t="s">
-        <v>6671</v>
+        <v>6666</v>
       </c>
       <c r="C1383" s="2" t="s">
         <v>1473</v>
       </c>
       <c r="D1383" s="2" t="s">
-        <v>6672</v>
+        <v>6667</v>
       </c>
       <c r="E1383" s="2" t="s">
-        <v>6673</v>
+        <v>6668</v>
       </c>
       <c r="F1383" s="2" t="s">
-        <v>6674</v>
+        <v>6669</v>
       </c>
       <c r="G1383" s="3">
         <v>4</v>
       </c>
       <c r="H1383" s="2" t="s">
-        <v>6675</v>
+        <v>6670</v>
       </c>
       <c r="I1383" s="2" t="s">
         <v>15</v>
@@ -61569,25 +61574,25 @@
         <v>1383</v>
       </c>
       <c r="B1384" s="2" t="s">
-        <v>6676</v>
+        <v>6671</v>
       </c>
       <c r="C1384" s="2" t="s">
-        <v>6465</v>
+        <v>6460</v>
       </c>
       <c r="D1384" s="2" t="s">
-        <v>6677</v>
+        <v>6672</v>
       </c>
       <c r="E1384" s="2" t="s">
-        <v>6678</v>
+        <v>6673</v>
       </c>
       <c r="F1384" s="2" t="s">
-        <v>6679</v>
+        <v>6674</v>
       </c>
       <c r="G1384" s="3">
         <v>4</v>
       </c>
       <c r="H1384" s="2" t="s">
-        <v>6680</v>
+        <v>6675</v>
       </c>
       <c r="I1384" s="2" t="s">
         <v>826</v>
@@ -61598,54 +61603,54 @@
         <v>1384</v>
       </c>
       <c r="B1385" s="2" t="s">
-        <v>6681</v>
+        <v>6676</v>
       </c>
       <c r="C1385" s="2" t="s">
-        <v>6682</v>
+        <v>6677</v>
       </c>
       <c r="D1385" s="2" t="s">
-        <v>6683</v>
+        <v>6678</v>
       </c>
       <c r="E1385" s="2" t="s">
-        <v>6684</v>
+        <v>6679</v>
       </c>
       <c r="F1385" s="2" t="s">
-        <v>6685</v>
+        <v>6680</v>
       </c>
       <c r="G1385" s="3">
         <v>3</v>
       </c>
       <c r="H1385" s="2" t="s">
-        <v>6686</v>
+        <v>6681</v>
       </c>
       <c r="I1385" s="2" t="s">
         <v>826</v>
       </c>
     </row>
-    <row r="1386" spans="1:9" ht="92.6">
+    <row r="1386" spans="1:9" ht="77.150000000000006">
       <c r="A1386" s="2">
         <v>1385</v>
       </c>
       <c r="B1386" s="2" t="s">
-        <v>6687</v>
+        <v>6682</v>
       </c>
       <c r="C1386" s="2" t="s">
-        <v>6688</v>
+        <v>6683</v>
       </c>
       <c r="D1386" s="2" t="s">
-        <v>6689</v>
+        <v>6684</v>
       </c>
       <c r="E1386" s="2" t="s">
-        <v>6690</v>
+        <v>6685</v>
       </c>
       <c r="F1386" s="2" t="s">
-        <v>6691</v>
+        <v>6686</v>
       </c>
       <c r="G1386" s="3">
         <v>3</v>
       </c>
       <c r="H1386" s="2" t="s">
-        <v>6692</v>
+        <v>6687</v>
       </c>
       <c r="I1386" s="2" t="s">
         <v>15</v>
@@ -61656,25 +61661,25 @@
         <v>1386</v>
       </c>
       <c r="B1387" s="2" t="s">
-        <v>6693</v>
+        <v>6688</v>
       </c>
       <c r="C1387" s="2" t="s">
-        <v>6877</v>
+        <v>6872</v>
       </c>
       <c r="D1387" s="2" t="s">
-        <v>6878</v>
+        <v>6873</v>
       </c>
       <c r="E1387" s="2" t="s">
-        <v>6879</v>
+        <v>6874</v>
       </c>
       <c r="F1387" s="2" t="s">
-        <v>6880</v>
+        <v>6875</v>
       </c>
       <c r="G1387" s="3">
         <v>1</v>
       </c>
       <c r="H1387" s="2" t="s">
-        <v>6694</v>
+        <v>6689</v>
       </c>
       <c r="I1387" s="2" t="s">
         <v>15</v>
@@ -61685,25 +61690,25 @@
         <v>1387</v>
       </c>
       <c r="B1388" s="2" t="s">
-        <v>6695</v>
+        <v>6690</v>
       </c>
       <c r="C1388" s="2" t="s">
-        <v>6696</v>
+        <v>6691</v>
       </c>
       <c r="D1388" s="2" t="s">
         <v>44</v>
       </c>
       <c r="E1388" s="2" t="s">
-        <v>6697</v>
+        <v>6692</v>
       </c>
       <c r="F1388" s="2" t="s">
-        <v>6698</v>
+        <v>6693</v>
       </c>
       <c r="G1388" s="3">
         <v>1</v>
       </c>
       <c r="H1388" s="2" t="s">
-        <v>6699</v>
+        <v>6694</v>
       </c>
       <c r="I1388" s="2" t="s">
         <v>826</v>
@@ -61714,25 +61719,25 @@
         <v>1388</v>
       </c>
       <c r="B1389" s="2" t="s">
-        <v>6700</v>
+        <v>6695</v>
       </c>
       <c r="C1389" s="2" t="s">
-        <v>6701</v>
+        <v>6696</v>
       </c>
       <c r="D1389" s="2" t="s">
-        <v>6702</v>
+        <v>6697</v>
       </c>
       <c r="E1389" s="2" t="s">
-        <v>6703</v>
+        <v>6698</v>
       </c>
       <c r="F1389" s="2" t="s">
-        <v>6704</v>
+        <v>6699</v>
       </c>
       <c r="G1389" s="3">
         <v>1</v>
       </c>
       <c r="H1389" s="2" t="s">
-        <v>6705</v>
+        <v>6700</v>
       </c>
       <c r="I1389" s="2" t="s">
         <v>15</v>
@@ -61743,25 +61748,25 @@
         <v>1389</v>
       </c>
       <c r="B1390" s="2" t="s">
-        <v>6706</v>
+        <v>6701</v>
       </c>
       <c r="C1390" s="2" t="s">
-        <v>6707</v>
+        <v>6702</v>
       </c>
       <c r="D1390" s="2" t="s">
-        <v>6708</v>
+        <v>6703</v>
       </c>
       <c r="E1390" s="2" t="s">
-        <v>6709</v>
+        <v>6704</v>
       </c>
       <c r="F1390" s="2" t="s">
-        <v>6710</v>
+        <v>6705</v>
       </c>
       <c r="G1390" s="3">
         <v>4</v>
       </c>
       <c r="H1390" s="2" t="s">
-        <v>6711</v>
+        <v>6706</v>
       </c>
       <c r="I1390" s="2" t="s">
         <v>15</v>
@@ -61772,25 +61777,25 @@
         <v>1390</v>
       </c>
       <c r="B1391" s="2" t="s">
-        <v>6712</v>
+        <v>6707</v>
       </c>
       <c r="C1391" s="2" t="s">
-        <v>6713</v>
+        <v>6708</v>
       </c>
       <c r="D1391" s="2" t="s">
-        <v>6714</v>
+        <v>6709</v>
       </c>
       <c r="E1391" s="2" t="s">
-        <v>6715</v>
+        <v>6710</v>
       </c>
       <c r="F1391" s="2" t="s">
-        <v>6716</v>
+        <v>6711</v>
       </c>
       <c r="G1391" s="3">
         <v>1</v>
       </c>
       <c r="H1391" s="2" t="s">
-        <v>6717</v>
+        <v>6712</v>
       </c>
       <c r="I1391" s="2" t="s">
         <v>15</v>
@@ -61801,25 +61806,25 @@
         <v>1391</v>
       </c>
       <c r="B1392" s="2" t="s">
-        <v>6718</v>
+        <v>6713</v>
       </c>
       <c r="C1392" s="2" t="s">
-        <v>6719</v>
+        <v>6714</v>
       </c>
       <c r="D1392" s="2" t="s">
-        <v>6720</v>
+        <v>6715</v>
       </c>
       <c r="E1392" s="2" t="s">
-        <v>6721</v>
+        <v>6716</v>
       </c>
       <c r="F1392" s="2" t="s">
-        <v>6722</v>
+        <v>6717</v>
       </c>
       <c r="G1392" s="3">
         <v>2</v>
       </c>
       <c r="H1392" s="2" t="s">
-        <v>6723</v>
+        <v>6718</v>
       </c>
       <c r="I1392" s="2" t="s">
         <v>15</v>
@@ -61830,25 +61835,25 @@
         <v>1392</v>
       </c>
       <c r="B1393" s="2" t="s">
-        <v>6724</v>
+        <v>6719</v>
       </c>
       <c r="C1393" s="2" t="s">
-        <v>6725</v>
+        <v>6720</v>
       </c>
       <c r="D1393" s="2" t="s">
-        <v>6726</v>
+        <v>6721</v>
       </c>
       <c r="E1393" s="2" t="s">
-        <v>6727</v>
+        <v>6722</v>
       </c>
       <c r="F1393" s="2" t="s">
-        <v>6728</v>
+        <v>6723</v>
       </c>
       <c r="G1393" s="3">
         <v>4</v>
       </c>
       <c r="H1393" s="2" t="s">
-        <v>6729</v>
+        <v>6724</v>
       </c>
       <c r="I1393" s="2" t="s">
         <v>826</v>
@@ -61859,25 +61864,25 @@
         <v>1393</v>
       </c>
       <c r="B1394" s="2" t="s">
-        <v>6730</v>
+        <v>6725</v>
       </c>
       <c r="C1394" s="2" t="s">
-        <v>6725</v>
+        <v>6720</v>
       </c>
       <c r="D1394" s="2" t="s">
-        <v>6731</v>
+        <v>6726</v>
       </c>
       <c r="E1394" s="2" t="s">
-        <v>6969</v>
+        <v>6964</v>
       </c>
       <c r="F1394" s="2" t="s">
-        <v>6732</v>
+        <v>6727</v>
       </c>
       <c r="G1394" s="3">
         <v>3</v>
       </c>
       <c r="H1394" s="2" t="s">
-        <v>6733</v>
+        <v>6728</v>
       </c>
       <c r="I1394" s="2" t="s">
         <v>826</v>
@@ -61888,7 +61893,7 @@
         <v>1394</v>
       </c>
       <c r="B1395" s="2" t="s">
-        <v>6734</v>
+        <v>6729</v>
       </c>
       <c r="C1395" s="2" t="s">
         <v>511</v>
@@ -61906,7 +61911,7 @@
         <v>4</v>
       </c>
       <c r="H1395" s="2" t="s">
-        <v>6735</v>
+        <v>6730</v>
       </c>
       <c r="I1395" s="2" t="s">
         <v>826</v>
@@ -61917,10 +61922,10 @@
         <v>1395</v>
       </c>
       <c r="B1396" s="2" t="s">
-        <v>6736</v>
+        <v>6731</v>
       </c>
       <c r="C1396" s="2" t="s">
-        <v>6737</v>
+        <v>6732</v>
       </c>
       <c r="D1396" s="2" t="s">
         <v>511</v>
@@ -61929,13 +61934,13 @@
         <v>510</v>
       </c>
       <c r="F1396" s="2" t="s">
-        <v>6738</v>
+        <v>6733</v>
       </c>
       <c r="G1396" s="3">
         <v>2</v>
       </c>
       <c r="H1396" s="2" t="s">
-        <v>6739</v>
+        <v>6734</v>
       </c>
       <c r="I1396" s="2" t="s">
         <v>826</v>
@@ -61946,25 +61951,25 @@
         <v>1396</v>
       </c>
       <c r="B1397" s="2" t="s">
-        <v>6740</v>
+        <v>6735</v>
       </c>
       <c r="C1397" s="2" t="s">
-        <v>6725</v>
+        <v>6720</v>
       </c>
       <c r="D1397" s="2" t="s">
-        <v>6731</v>
+        <v>6726</v>
       </c>
       <c r="E1397" s="2" t="s">
-        <v>6727</v>
+        <v>6722</v>
       </c>
       <c r="F1397" s="2" t="s">
-        <v>6728</v>
+        <v>6723</v>
       </c>
       <c r="G1397" s="3">
         <v>1</v>
       </c>
       <c r="H1397" s="2" t="s">
-        <v>6741</v>
+        <v>6736</v>
       </c>
       <c r="I1397" s="2" t="s">
         <v>826</v>
@@ -61975,25 +61980,25 @@
         <v>1397</v>
       </c>
       <c r="B1398" s="2" t="s">
-        <v>6742</v>
+        <v>6737</v>
       </c>
       <c r="C1398" s="2" t="s">
-        <v>6725</v>
+        <v>6720</v>
       </c>
       <c r="D1398" s="2" t="s">
-        <v>6731</v>
+        <v>6726</v>
       </c>
       <c r="E1398" s="2" t="s">
-        <v>6727</v>
+        <v>6722</v>
       </c>
       <c r="F1398" s="2" t="s">
-        <v>6728</v>
+        <v>6723</v>
       </c>
       <c r="G1398" s="3">
         <v>3</v>
       </c>
       <c r="H1398" s="2" t="s">
-        <v>6743</v>
+        <v>6738</v>
       </c>
       <c r="I1398" s="2" t="s">
         <v>826</v>
@@ -62004,7 +62009,7 @@
         <v>1398</v>
       </c>
       <c r="B1399" s="2" t="s">
-        <v>6744</v>
+        <v>6739</v>
       </c>
       <c r="C1399" s="2" t="s">
         <v>512</v>
@@ -62016,13 +62021,13 @@
         <v>510</v>
       </c>
       <c r="F1399" s="2" t="s">
-        <v>6745</v>
+        <v>6740</v>
       </c>
       <c r="G1399" s="3">
         <v>4</v>
       </c>
       <c r="H1399" s="2" t="s">
-        <v>6746</v>
+        <v>6741</v>
       </c>
       <c r="I1399" s="2" t="s">
         <v>826</v>
@@ -62033,25 +62038,25 @@
         <v>1399</v>
       </c>
       <c r="B1400" s="2" t="s">
-        <v>6747</v>
+        <v>6742</v>
       </c>
       <c r="C1400" s="2" t="s">
-        <v>6748</v>
+        <v>6743</v>
       </c>
       <c r="D1400" s="2" t="s">
-        <v>6749</v>
+        <v>6744</v>
       </c>
       <c r="E1400" s="2" t="s">
-        <v>6750</v>
+        <v>6745</v>
       </c>
       <c r="F1400" s="2" t="s">
-        <v>6751</v>
+        <v>6746</v>
       </c>
       <c r="G1400" s="3">
         <v>2</v>
       </c>
       <c r="H1400" s="2" t="s">
-        <v>6752</v>
+        <v>6747</v>
       </c>
       <c r="I1400" s="2" t="s">
         <v>826</v>
@@ -62062,25 +62067,25 @@
         <v>1400</v>
       </c>
       <c r="B1401" s="2" t="s">
-        <v>6753</v>
+        <v>6748</v>
       </c>
       <c r="C1401" s="2" t="s">
-        <v>6754</v>
+        <v>6749</v>
       </c>
       <c r="D1401" s="2" t="s">
-        <v>6755</v>
+        <v>6750</v>
       </c>
       <c r="E1401" s="2" t="s">
-        <v>6756</v>
+        <v>6751</v>
       </c>
       <c r="F1401" s="2" t="s">
-        <v>6757</v>
+        <v>6752</v>
       </c>
       <c r="G1401" s="3">
         <v>2</v>
       </c>
       <c r="H1401" s="2" t="s">
-        <v>6758</v>
+        <v>6753</v>
       </c>
       <c r="I1401" s="2" t="s">
         <v>826</v>
@@ -62091,25 +62096,25 @@
         <v>1401</v>
       </c>
       <c r="B1402" s="2" t="s">
-        <v>6759</v>
+        <v>6754</v>
       </c>
       <c r="C1402" s="2" t="s">
-        <v>6760</v>
+        <v>6755</v>
       </c>
       <c r="D1402" s="2" t="s">
-        <v>6761</v>
+        <v>6756</v>
       </c>
       <c r="E1402" s="2" t="s">
-        <v>6762</v>
+        <v>6757</v>
       </c>
       <c r="F1402" s="2" t="s">
-        <v>6763</v>
+        <v>6758</v>
       </c>
       <c r="G1402" s="3">
         <v>2</v>
       </c>
       <c r="H1402" s="2" t="s">
-        <v>6764</v>
+        <v>6759</v>
       </c>
       <c r="I1402" s="2" t="s">
         <v>15</v>
@@ -62120,25 +62125,25 @@
         <v>1402</v>
       </c>
       <c r="B1403" s="2" t="s">
-        <v>6765</v>
+        <v>6760</v>
       </c>
       <c r="C1403" s="2" t="s">
-        <v>6766</v>
+        <v>6761</v>
       </c>
       <c r="D1403" s="2" t="s">
-        <v>6767</v>
+        <v>6762</v>
       </c>
       <c r="E1403" s="2" t="s">
-        <v>6768</v>
+        <v>6763</v>
       </c>
       <c r="F1403" s="2" t="s">
-        <v>6769</v>
+        <v>6764</v>
       </c>
       <c r="G1403" s="3">
         <v>3</v>
       </c>
       <c r="H1403" s="2" t="s">
-        <v>6770</v>
+        <v>6765</v>
       </c>
       <c r="I1403" s="2" t="s">
         <v>15</v>
@@ -62149,25 +62154,25 @@
         <v>1403</v>
       </c>
       <c r="B1404" s="2" t="s">
-        <v>6771</v>
+        <v>6766</v>
       </c>
       <c r="C1404" s="2" t="s">
-        <v>6772</v>
+        <v>6767</v>
       </c>
       <c r="D1404" s="2" t="s">
-        <v>6773</v>
+        <v>6768</v>
       </c>
       <c r="E1404" s="2" t="s">
-        <v>6774</v>
+        <v>6769</v>
       </c>
       <c r="F1404" s="2" t="s">
-        <v>6775</v>
+        <v>6770</v>
       </c>
       <c r="G1404" s="3">
         <v>2</v>
       </c>
       <c r="H1404" s="2" t="s">
-        <v>6776</v>
+        <v>6771</v>
       </c>
       <c r="I1404" s="2" t="s">
         <v>15</v>

--- a/salf/丙種職業安全衛生業務主管題庫.xlsx
+++ b/salf/丙種職業安全衛生業務主管題庫.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\drher\OneDrive\文件\GitHub\drher.github.io\salf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F57823F5-0F7A-45EA-A8A0-0CFD2685A665}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF6CE81F-2934-4179-9510-5C4A32173BDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="15397" windowHeight="8751" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17069,9 +17069,6 @@
     <t>固體</t>
   </si>
   <si>
-    <t>真空。人因</t>
-  </si>
-  <si>
     <t>正確答案為第1項：「固體」。本題重點在於理解題幹所涉及的職業安全衛生管理、危害預防或法規要求。</t>
   </si>
   <si>
@@ -21717,6 +21714,10 @@
   </si>
   <si>
     <t>作業環境測定</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>真空</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -22566,7 +22567,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>6985</v>
+        <v>6984</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>87</v>
@@ -22575,10 +22576,10 @@
         <v>88</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>6987</v>
+        <v>6986</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>6986</v>
+        <v>6985</v>
       </c>
       <c r="G16" s="3">
         <v>1</v>
@@ -22767,7 +22768,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>6818</v>
+        <v>6817</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>122</v>
@@ -22779,7 +22780,7 @@
         <v>124</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>6819</v>
+        <v>6818</v>
       </c>
       <c r="G23" s="3">
         <v>4</v>
@@ -22825,10 +22826,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
+        <v>6574</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>6575</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>6576</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>132</v>
@@ -22883,10 +22884,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>7000</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>7001</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>7002</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>142</v>
@@ -22895,7 +22896,7 @@
         <v>143</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>7003</v>
+        <v>7002</v>
       </c>
       <c r="G27" s="3">
         <v>3</v>
@@ -23345,19 +23346,19 @@
         <v>42</v>
       </c>
       <c r="B43" s="2" t="s">
+        <v>6681</v>
+      </c>
+      <c r="C43" s="2" t="s">
         <v>6682</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="D43" s="2" t="s">
         <v>6683</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>6684</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>227</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>6685</v>
+        <v>6684</v>
       </c>
       <c r="G43" s="3">
         <v>3</v>
@@ -23983,7 +23984,7 @@
         <v>64</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>6639</v>
+        <v>6638</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>342</v>
@@ -24018,7 +24019,7 @@
         <v>348</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>6640</v>
+        <v>6639</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>343</v>
@@ -24157,13 +24158,13 @@
         <v>70</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>6502</v>
+        <v>6501</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>373</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>6501</v>
+        <v>6500</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>374</v>
@@ -24186,7 +24187,7 @@
         <v>71</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>6591</v>
+        <v>6590</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>377</v>
@@ -24195,10 +24196,10 @@
         <v>378</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>6593</v>
+        <v>6592</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>6592</v>
+        <v>6591</v>
       </c>
       <c r="G72" s="3">
         <v>4</v>
@@ -24447,10 +24448,10 @@
         <v>80</v>
       </c>
       <c r="B81" s="2" t="s">
+        <v>6767</v>
+      </c>
+      <c r="C81" s="2" t="s">
         <v>6768</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>6769</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>422</v>
@@ -24766,7 +24767,7 @@
         <v>91</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>6551</v>
+        <v>6550</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>479</v>
@@ -24778,7 +24779,7 @@
         <v>481</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>6552</v>
+        <v>6551</v>
       </c>
       <c r="G92" s="3">
         <v>4</v>
@@ -24795,19 +24796,19 @@
         <v>92</v>
       </c>
       <c r="B93" s="2" t="s">
+        <v>6808</v>
+      </c>
+      <c r="C93" s="2" t="s">
         <v>6809</v>
       </c>
-      <c r="C93" s="2" t="s">
+      <c r="D93" s="2" t="s">
         <v>6810</v>
       </c>
-      <c r="D93" s="2" t="s">
+      <c r="E93" s="2" t="s">
         <v>6811</v>
       </c>
-      <c r="E93" s="2" t="s">
+      <c r="F93" s="2" t="s">
         <v>6812</v>
-      </c>
-      <c r="F93" s="2" t="s">
-        <v>6813</v>
       </c>
       <c r="G93" s="3">
         <v>4</v>
@@ -24853,7 +24854,7 @@
         <v>94</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>6954</v>
+        <v>6953</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>489</v>
@@ -25052,7 +25053,7 @@
         <v>101</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>6528</v>
+        <v>6527</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>527</v>
@@ -25061,10 +25062,10 @@
         <v>528</v>
       </c>
       <c r="E102" s="2" t="s">
+        <v>6528</v>
+      </c>
+      <c r="F102" s="2" t="s">
         <v>6529</v>
-      </c>
-      <c r="F102" s="2" t="s">
-        <v>6530</v>
       </c>
       <c r="G102" s="3">
         <v>1</v>
@@ -25110,7 +25111,7 @@
         <v>103</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>6891</v>
+        <v>6890</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>536</v>
@@ -25949,7 +25950,7 @@
         <v>132</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>6558</v>
+        <v>6557</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>343</v>
@@ -25958,10 +25959,10 @@
         <v>672</v>
       </c>
       <c r="E133" s="2" t="s">
+        <v>6558</v>
+      </c>
+      <c r="F133" s="2" t="s">
         <v>6559</v>
-      </c>
-      <c r="F133" s="2" t="s">
-        <v>6560</v>
       </c>
       <c r="G133" s="3">
         <v>3</v>
@@ -26425,7 +26426,7 @@
         <v>752</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>7012</v>
+        <v>7011</v>
       </c>
       <c r="G149" s="3">
         <v>4</v>
@@ -26442,7 +26443,7 @@
         <v>149</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>6936</v>
+        <v>6935</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>754</v>
@@ -26674,13 +26675,13 @@
         <v>157</v>
       </c>
       <c r="B158" s="2" t="s">
+        <v>6938</v>
+      </c>
+      <c r="C158" s="2" t="s">
         <v>6939</v>
       </c>
-      <c r="C158" s="2" t="s">
+      <c r="D158" s="2" t="s">
         <v>6940</v>
-      </c>
-      <c r="D158" s="2" t="s">
-        <v>6941</v>
       </c>
       <c r="E158" s="2" t="s">
         <v>787</v>
@@ -26715,7 +26716,7 @@
         <v>793</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>6569</v>
+        <v>6568</v>
       </c>
       <c r="G159" s="3">
         <v>3</v>
@@ -26851,16 +26852,16 @@
         <v>815</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>6976</v>
+        <v>6975</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>6981</v>
+        <v>6980</v>
       </c>
       <c r="E164" s="2" t="s">
         <v>816</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>6978</v>
+        <v>6977</v>
       </c>
       <c r="G164" s="3">
         <v>3</v>
@@ -26877,19 +26878,19 @@
         <v>164</v>
       </c>
       <c r="B165" s="2" t="s">
+        <v>6974</v>
+      </c>
+      <c r="C165" s="2" t="s">
+        <v>6976</v>
+      </c>
+      <c r="D165" s="2" t="s">
         <v>6975</v>
-      </c>
-      <c r="C165" s="2" t="s">
-        <v>6977</v>
-      </c>
-      <c r="D165" s="2" t="s">
-        <v>6976</v>
       </c>
       <c r="E165" s="2" t="s">
         <v>818</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>6979</v>
+        <v>6978</v>
       </c>
       <c r="G165" s="3">
         <v>3</v>
@@ -26918,7 +26919,7 @@
         <v>821</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>6980</v>
+        <v>6979</v>
       </c>
       <c r="G166" s="3">
         <v>3</v>
@@ -26935,25 +26936,25 @@
         <v>166</v>
       </c>
       <c r="B167" s="2" t="s">
+        <v>6721</v>
+      </c>
+      <c r="C167" s="2" t="s">
         <v>6722</v>
       </c>
-      <c r="C167" s="2" t="s">
+      <c r="D167" s="2" t="s">
         <v>6723</v>
       </c>
-      <c r="D167" s="2" t="s">
+      <c r="E167" s="2" t="s">
         <v>6724</v>
       </c>
-      <c r="E167" s="2" t="s">
+      <c r="F167" s="2" t="s">
         <v>6725</v>
-      </c>
-      <c r="F167" s="2" t="s">
-        <v>6726</v>
       </c>
       <c r="G167" s="3">
         <v>3</v>
       </c>
       <c r="H167" s="2" t="s">
-        <v>6727</v>
+        <v>6726</v>
       </c>
       <c r="I167" s="2" t="s">
         <v>15</v>
@@ -27167,7 +27168,7 @@
         <v>174</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>6738</v>
+        <v>6737</v>
       </c>
       <c r="C175" s="2" t="s">
         <v>439</v>
@@ -27283,7 +27284,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>6608</v>
+        <v>6607</v>
       </c>
       <c r="C179" s="2" t="s">
         <v>861</v>
@@ -27426,19 +27427,19 @@
         <v>183</v>
       </c>
       <c r="B184" s="2" t="s">
+        <v>6994</v>
+      </c>
+      <c r="C184" s="2" t="s">
+        <v>6992</v>
+      </c>
+      <c r="D184" s="2" t="s">
+        <v>6993</v>
+      </c>
+      <c r="E184" s="2" t="s">
         <v>6995</v>
       </c>
-      <c r="C184" s="2" t="s">
-        <v>6993</v>
-      </c>
-      <c r="D184" s="2" t="s">
-        <v>6994</v>
-      </c>
-      <c r="E184" s="2" t="s">
+      <c r="F184" s="2" t="s">
         <v>6996</v>
-      </c>
-      <c r="F184" s="2" t="s">
-        <v>6997</v>
       </c>
       <c r="G184" s="3">
         <v>2</v>
@@ -27571,7 +27572,7 @@
         <v>188</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>6681</v>
+        <v>6680</v>
       </c>
       <c r="C189" s="2" t="s">
         <v>917</v>
@@ -27722,13 +27723,13 @@
         <v>942</v>
       </c>
       <c r="D194" s="2" t="s">
+        <v>6738</v>
+      </c>
+      <c r="E194" s="2" t="s">
         <v>6739</v>
       </c>
-      <c r="E194" s="2" t="s">
+      <c r="F194" s="2" t="s">
         <v>6740</v>
-      </c>
-      <c r="F194" s="2" t="s">
-        <v>6741</v>
       </c>
       <c r="G194" s="3">
         <v>4</v>
@@ -27893,16 +27894,16 @@
         <v>974</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>6961</v>
+        <v>6960</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>6959</v>
+        <v>6958</v>
       </c>
       <c r="E200" s="2" t="s">
         <v>975</v>
       </c>
       <c r="F200" s="2" t="s">
-        <v>6960</v>
+        <v>6959</v>
       </c>
       <c r="G200" s="3">
         <v>1</v>
@@ -28099,13 +28100,13 @@
         <v>1013</v>
       </c>
       <c r="D207" s="2" t="s">
+        <v>6486</v>
+      </c>
+      <c r="E207" s="2" t="s">
         <v>6487</v>
       </c>
-      <c r="E207" s="2" t="s">
+      <c r="F207" s="2" t="s">
         <v>6488</v>
-      </c>
-      <c r="F207" s="2" t="s">
-        <v>6489</v>
       </c>
       <c r="G207" s="3">
         <v>2</v>
@@ -29079,7 +29080,7 @@
         <v>240</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>6923</v>
+        <v>6922</v>
       </c>
       <c r="C241" s="2" t="s">
         <v>1183</v>
@@ -29091,7 +29092,7 @@
         <v>1201</v>
       </c>
       <c r="F241" s="2" t="s">
-        <v>6924</v>
+        <v>6923</v>
       </c>
       <c r="G241" s="3">
         <v>1</v>
@@ -29807,13 +29808,13 @@
         <v>1328</v>
       </c>
       <c r="C266" s="2" t="s">
+        <v>6945</v>
+      </c>
+      <c r="D266" s="2" t="s">
+        <v>6947</v>
+      </c>
+      <c r="E266" s="2" t="s">
         <v>6946</v>
-      </c>
-      <c r="D266" s="2" t="s">
-        <v>6948</v>
-      </c>
-      <c r="E266" s="2" t="s">
-        <v>6947</v>
       </c>
       <c r="F266" s="2" t="s">
         <v>1329</v>
@@ -29920,7 +29921,7 @@
         <v>269</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>6510</v>
+        <v>6509</v>
       </c>
       <c r="C270" s="2" t="s">
         <v>1345</v>
@@ -30181,19 +30182,19 @@
         <v>278</v>
       </c>
       <c r="B279" s="2" t="s">
+        <v>6741</v>
+      </c>
+      <c r="C279" s="2" t="s">
+        <v>6743</v>
+      </c>
+      <c r="D279" s="2" t="s">
+        <v>6744</v>
+      </c>
+      <c r="E279" s="2" t="s">
+        <v>6745</v>
+      </c>
+      <c r="F279" s="2" t="s">
         <v>6742</v>
-      </c>
-      <c r="C279" s="2" t="s">
-        <v>6744</v>
-      </c>
-      <c r="D279" s="2" t="s">
-        <v>6745</v>
-      </c>
-      <c r="E279" s="2" t="s">
-        <v>6746</v>
-      </c>
-      <c r="F279" s="2" t="s">
-        <v>6743</v>
       </c>
       <c r="G279" s="3">
         <v>4</v>
@@ -30210,7 +30211,7 @@
         <v>279</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>6801</v>
+        <v>6800</v>
       </c>
       <c r="C280" s="2" t="s">
         <v>1395</v>
@@ -30219,10 +30220,10 @@
         <v>1396</v>
       </c>
       <c r="E280" s="2" t="s">
+        <v>6801</v>
+      </c>
+      <c r="F280" s="2" t="s">
         <v>6802</v>
-      </c>
-      <c r="F280" s="2" t="s">
-        <v>6803</v>
       </c>
       <c r="G280" s="3">
         <v>3</v>
@@ -30500,19 +30501,19 @@
         <v>289</v>
       </c>
       <c r="B290" s="2" t="s">
+        <v>6796</v>
+      </c>
+      <c r="C290" s="2" t="s">
         <v>6797</v>
       </c>
-      <c r="C290" s="2" t="s">
+      <c r="D290" s="2" t="s">
         <v>6798</v>
-      </c>
-      <c r="D290" s="2" t="s">
-        <v>6799</v>
       </c>
       <c r="E290" s="2" t="s">
         <v>1448</v>
       </c>
       <c r="F290" s="2" t="s">
-        <v>6800</v>
+        <v>6799</v>
       </c>
       <c r="G290" s="3">
         <v>1</v>
@@ -30558,19 +30559,19 @@
         <v>291</v>
       </c>
       <c r="B292" s="2" t="s">
+        <v>6729</v>
+      </c>
+      <c r="C292" s="2" t="s">
         <v>6730</v>
       </c>
-      <c r="C292" s="2" t="s">
+      <c r="D292" s="2" t="s">
         <v>6731</v>
       </c>
-      <c r="D292" s="2" t="s">
+      <c r="E292" s="2" t="s">
         <v>6732</v>
       </c>
-      <c r="E292" s="2" t="s">
+      <c r="F292" s="2" t="s">
         <v>6733</v>
-      </c>
-      <c r="F292" s="2" t="s">
-        <v>6734</v>
       </c>
       <c r="G292" s="3">
         <v>1</v>
@@ -31225,7 +31226,7 @@
         <v>314</v>
       </c>
       <c r="B315" s="2" t="s">
-        <v>6561</v>
+        <v>6560</v>
       </c>
       <c r="C315" s="2" t="s">
         <v>1573</v>
@@ -31254,10 +31255,10 @@
         <v>315</v>
       </c>
       <c r="B316" s="2" t="s">
+        <v>6803</v>
+      </c>
+      <c r="C316" s="2" t="s">
         <v>6804</v>
-      </c>
-      <c r="C316" s="2" t="s">
-        <v>6805</v>
       </c>
       <c r="D316" s="2" t="s">
         <v>1578</v>
@@ -31266,7 +31267,7 @@
         <v>1579</v>
       </c>
       <c r="F316" s="2" t="s">
-        <v>6806</v>
+        <v>6805</v>
       </c>
       <c r="G316" s="3">
         <v>1</v>
@@ -31608,13 +31609,13 @@
         <v>1643</v>
       </c>
       <c r="D328" s="2" t="s">
-        <v>6641</v>
+        <v>6640</v>
       </c>
       <c r="E328" s="2" t="s">
         <v>1645</v>
       </c>
       <c r="F328" s="2" t="s">
-        <v>6642</v>
+        <v>6641</v>
       </c>
       <c r="G328" s="3">
         <v>4</v>
@@ -31863,19 +31864,19 @@
         <v>336</v>
       </c>
       <c r="B337" s="2" t="s">
-        <v>6548</v>
+        <v>6547</v>
       </c>
       <c r="C337" s="2" t="s">
         <v>1692</v>
       </c>
       <c r="D337" s="2" t="s">
-        <v>6549</v>
+        <v>6548</v>
       </c>
       <c r="E337" s="2" t="s">
         <v>712</v>
       </c>
       <c r="F337" s="2" t="s">
-        <v>6550</v>
+        <v>6549</v>
       </c>
       <c r="G337" s="3">
         <v>4</v>
@@ -32008,7 +32009,7 @@
         <v>341</v>
       </c>
       <c r="B342" s="2" t="s">
-        <v>6919</v>
+        <v>6918</v>
       </c>
       <c r="C342" s="2" t="s">
         <v>1716</v>
@@ -32017,10 +32018,10 @@
         <v>1717</v>
       </c>
       <c r="E342" s="2" t="s">
+        <v>6916</v>
+      </c>
+      <c r="F342" s="2" t="s">
         <v>6917</v>
-      </c>
-      <c r="F342" s="2" t="s">
-        <v>6918</v>
       </c>
       <c r="G342" s="3">
         <v>2</v>
@@ -32069,7 +32070,7 @@
         <v>1725</v>
       </c>
       <c r="C344" s="2" t="s">
-        <v>6556</v>
+        <v>6555</v>
       </c>
       <c r="D344" s="2" t="s">
         <v>1720</v>
@@ -32078,7 +32079,7 @@
         <v>1721</v>
       </c>
       <c r="F344" s="2" t="s">
-        <v>6557</v>
+        <v>6556</v>
       </c>
       <c r="G344" s="3">
         <v>1</v>
@@ -32356,19 +32357,19 @@
         <v>353</v>
       </c>
       <c r="B354" s="2" t="s">
+        <v>7014</v>
+      </c>
+      <c r="C354" s="2" t="s">
         <v>7015</v>
       </c>
-      <c r="C354" s="2" t="s">
+      <c r="D354" s="2" t="s">
         <v>7016</v>
-      </c>
-      <c r="D354" s="2" t="s">
-        <v>7017</v>
       </c>
       <c r="E354" s="2" t="s">
         <v>1780</v>
       </c>
       <c r="F354" s="2" t="s">
-        <v>7018</v>
+        <v>7017</v>
       </c>
       <c r="G354" s="3">
         <v>1</v>
@@ -33081,10 +33082,10 @@
         <v>378</v>
       </c>
       <c r="B379" s="2" t="s">
+        <v>6727</v>
+      </c>
+      <c r="C379" s="2" t="s">
         <v>6728</v>
-      </c>
-      <c r="C379" s="2" t="s">
-        <v>6729</v>
       </c>
       <c r="D379" s="2" t="s">
         <v>1918</v>
@@ -33287,7 +33288,7 @@
         <v>1954</v>
       </c>
       <c r="C386" s="2" t="s">
-        <v>6837</v>
+        <v>6836</v>
       </c>
       <c r="D386" s="2" t="s">
         <v>1951</v>
@@ -33296,7 +33297,7 @@
         <v>1955</v>
       </c>
       <c r="F386" s="2" t="s">
-        <v>6838</v>
+        <v>6837</v>
       </c>
       <c r="G386" s="3">
         <v>1</v>
@@ -33493,7 +33494,7 @@
         <v>1993</v>
       </c>
       <c r="D393" s="2" t="s">
-        <v>6896</v>
+        <v>6895</v>
       </c>
       <c r="E393" s="2" t="s">
         <v>1994</v>
@@ -33516,13 +33517,13 @@
         <v>393</v>
       </c>
       <c r="B394" s="2" t="s">
-        <v>6895</v>
+        <v>6894</v>
       </c>
       <c r="C394" s="2" t="s">
         <v>1997</v>
       </c>
       <c r="D394" s="2" t="s">
-        <v>6897</v>
+        <v>6896</v>
       </c>
       <c r="E394" s="2" t="s">
         <v>1998</v>
@@ -33893,16 +33894,16 @@
         <v>406</v>
       </c>
       <c r="B407" s="2" t="s">
-        <v>6572</v>
+        <v>6571</v>
       </c>
       <c r="C407" s="2" t="s">
-        <v>6574</v>
+        <v>6573</v>
       </c>
       <c r="D407" s="2" t="s">
         <v>2070</v>
       </c>
       <c r="E407" s="2" t="s">
-        <v>6573</v>
+        <v>6572</v>
       </c>
       <c r="F407" s="2" t="s">
         <v>2071</v>
@@ -34210,7 +34211,7 @@
         <v>417</v>
       </c>
       <c r="B418" s="2" t="s">
-        <v>6817</v>
+        <v>6816</v>
       </c>
       <c r="C418" s="2" t="s">
         <v>77</v>
@@ -34335,10 +34336,10 @@
         <v>2142</v>
       </c>
       <c r="E422" s="2" t="s">
+        <v>7012</v>
+      </c>
+      <c r="F422" s="2" t="s">
         <v>7013</v>
-      </c>
-      <c r="F422" s="2" t="s">
-        <v>7014</v>
       </c>
       <c r="G422" s="3">
         <v>3</v>
@@ -34701,7 +34702,7 @@
         <v>434</v>
       </c>
       <c r="B435" s="2" t="s">
-        <v>6583</v>
+        <v>6582</v>
       </c>
       <c r="C435" s="2" t="s">
         <v>2206</v>
@@ -34713,7 +34714,7 @@
         <v>2208</v>
       </c>
       <c r="F435" s="2" t="s">
-        <v>6584</v>
+        <v>6583</v>
       </c>
       <c r="G435" s="3">
         <v>1</v>
@@ -34786,7 +34787,7 @@
         <v>437</v>
       </c>
       <c r="B438" s="2" t="s">
-        <v>6930</v>
+        <v>6929</v>
       </c>
       <c r="C438" s="2" t="s">
         <v>2218</v>
@@ -34795,10 +34796,10 @@
         <v>2219</v>
       </c>
       <c r="E438" s="2" t="s">
-        <v>6932</v>
+        <v>6931</v>
       </c>
       <c r="F438" s="2" t="s">
-        <v>6931</v>
+        <v>6930</v>
       </c>
       <c r="G438" s="3">
         <v>1</v>
@@ -34969,7 +34970,7 @@
         <v>1296</v>
       </c>
       <c r="E444" s="2" t="s">
-        <v>6935</v>
+        <v>6934</v>
       </c>
       <c r="F444" s="2" t="s">
         <v>2238</v>
@@ -34989,19 +34990,19 @@
         <v>444</v>
       </c>
       <c r="B445" s="2" t="s">
+        <v>6932</v>
+      </c>
+      <c r="C445" s="2" t="s">
         <v>6933</v>
-      </c>
-      <c r="C445" s="2" t="s">
-        <v>6934</v>
       </c>
       <c r="D445" s="2" t="s">
         <v>2218</v>
       </c>
       <c r="E445" s="2" t="s">
+        <v>6930</v>
+      </c>
+      <c r="F445" s="2" t="s">
         <v>6931</v>
-      </c>
-      <c r="F445" s="2" t="s">
-        <v>6932</v>
       </c>
       <c r="G445" s="3">
         <v>4</v>
@@ -35230,10 +35231,10 @@
         <v>2283</v>
       </c>
       <c r="E453" s="2" t="s">
-        <v>6598</v>
+        <v>6597</v>
       </c>
       <c r="F453" s="2" t="s">
-        <v>6597</v>
+        <v>6596</v>
       </c>
       <c r="G453" s="3">
         <v>1</v>
@@ -35250,7 +35251,7 @@
         <v>453</v>
       </c>
       <c r="B454" s="2" t="s">
-        <v>6594</v>
+        <v>6593</v>
       </c>
       <c r="C454" s="2" t="s">
         <v>1387</v>
@@ -35259,10 +35260,10 @@
         <v>1369</v>
       </c>
       <c r="E454" s="2" t="s">
-        <v>6596</v>
+        <v>6595</v>
       </c>
       <c r="F454" s="2" t="s">
-        <v>6595</v>
+        <v>6594</v>
       </c>
       <c r="G454" s="3">
         <v>4</v>
@@ -35689,13 +35690,13 @@
         <v>2352</v>
       </c>
       <c r="D469" s="2" t="s">
-        <v>6952</v>
+        <v>6951</v>
       </c>
       <c r="E469" s="2" t="s">
         <v>2353</v>
       </c>
       <c r="F469" s="2" t="s">
-        <v>6953</v>
+        <v>6952</v>
       </c>
       <c r="G469" s="3">
         <v>1</v>
@@ -36696,19 +36697,19 @@
         <v>503</v>
       </c>
       <c r="B504" s="2" t="s">
+        <v>6642</v>
+      </c>
+      <c r="C504" s="2" t="s">
         <v>6643</v>
-      </c>
-      <c r="C504" s="2" t="s">
-        <v>6644</v>
       </c>
       <c r="D504" s="2" t="s">
         <v>2530</v>
       </c>
       <c r="E504" s="2" t="s">
+        <v>6644</v>
+      </c>
+      <c r="F504" s="2" t="s">
         <v>6645</v>
-      </c>
-      <c r="F504" s="2" t="s">
-        <v>6646</v>
       </c>
       <c r="G504" s="3">
         <v>4</v>
@@ -36781,7 +36782,7 @@
         <v>506</v>
       </c>
       <c r="B507" s="2" t="s">
-        <v>6859</v>
+        <v>6858</v>
       </c>
       <c r="C507" s="2" t="s">
         <v>2542</v>
@@ -36793,13 +36794,13 @@
         <v>2544</v>
       </c>
       <c r="F507" s="2" t="s">
-        <v>6858</v>
+        <v>6857</v>
       </c>
       <c r="G507" s="3">
         <v>3</v>
       </c>
       <c r="H507" s="2" t="s">
-        <v>6860</v>
+        <v>6859</v>
       </c>
       <c r="I507" s="2" t="s">
         <v>285</v>
@@ -37011,10 +37012,10 @@
         <v>514</v>
       </c>
       <c r="B515" s="2" t="s">
-        <v>6966</v>
+        <v>6965</v>
       </c>
       <c r="C515" s="2" t="s">
-        <v>6964</v>
+        <v>6963</v>
       </c>
       <c r="D515" s="2" t="s">
         <v>2578</v>
@@ -37023,7 +37024,7 @@
         <v>2564</v>
       </c>
       <c r="F515" s="2" t="s">
-        <v>6965</v>
+        <v>6964</v>
       </c>
       <c r="G515" s="3">
         <v>3</v>
@@ -37359,19 +37360,19 @@
         <v>526</v>
       </c>
       <c r="B527" s="2" t="s">
-        <v>7007</v>
+        <v>7006</v>
       </c>
       <c r="C527" s="2" t="s">
         <v>440</v>
       </c>
       <c r="D527" s="2" t="s">
+        <v>7007</v>
+      </c>
+      <c r="E527" s="2" t="s">
         <v>7008</v>
       </c>
-      <c r="E527" s="2" t="s">
+      <c r="F527" s="2" t="s">
         <v>7009</v>
-      </c>
-      <c r="F527" s="2" t="s">
-        <v>7010</v>
       </c>
       <c r="G527" s="3">
         <v>1</v>
@@ -37388,7 +37389,7 @@
         <v>527</v>
       </c>
       <c r="B528" s="2" t="s">
-        <v>7011</v>
+        <v>7010</v>
       </c>
       <c r="C528" s="2" t="s">
         <v>2638</v>
@@ -37475,19 +37476,19 @@
         <v>530</v>
       </c>
       <c r="B531" s="2" t="s">
+        <v>6866</v>
+      </c>
+      <c r="C531" s="2" t="s">
+        <v>6868</v>
+      </c>
+      <c r="D531" s="2" t="s">
         <v>6867</v>
-      </c>
-      <c r="C531" s="2" t="s">
-        <v>6869</v>
-      </c>
-      <c r="D531" s="2" t="s">
-        <v>6868</v>
       </c>
       <c r="E531" s="2" t="s">
         <v>77</v>
       </c>
       <c r="F531" s="2" t="s">
-        <v>6870</v>
+        <v>6869</v>
       </c>
       <c r="G531" s="3">
         <v>4</v>
@@ -37874,7 +37875,7 @@
         <v>2717</v>
       </c>
       <c r="C545" s="2" t="s">
-        <v>6871</v>
+        <v>6870</v>
       </c>
       <c r="D545" s="2" t="s">
         <v>2718</v>
@@ -37883,7 +37884,7 @@
         <v>2719</v>
       </c>
       <c r="F545" s="2" t="s">
-        <v>6872</v>
+        <v>6871</v>
       </c>
       <c r="G545" s="3">
         <v>4</v>
@@ -38159,19 +38160,19 @@
         <v>554</v>
       </c>
       <c r="B555" s="2" t="s">
-        <v>6956</v>
+        <v>6955</v>
       </c>
       <c r="C555" s="2" t="s">
         <v>2762</v>
       </c>
       <c r="D555" s="2" t="s">
-        <v>6957</v>
+        <v>6956</v>
       </c>
       <c r="E555" s="2" t="s">
         <v>2763</v>
       </c>
       <c r="F555" s="2" t="s">
-        <v>6958</v>
+        <v>6957</v>
       </c>
       <c r="G555" s="3">
         <v>4</v>
@@ -38217,13 +38218,13 @@
         <v>556</v>
       </c>
       <c r="B557" s="2" t="s">
+        <v>6492</v>
+      </c>
+      <c r="C557" s="2" t="s">
         <v>6493</v>
       </c>
-      <c r="C557" s="2" t="s">
+      <c r="D557" s="2" t="s">
         <v>6494</v>
-      </c>
-      <c r="D557" s="2" t="s">
-        <v>6495</v>
       </c>
       <c r="E557" s="2" t="s">
         <v>2770</v>
@@ -38455,13 +38456,13 @@
         <v>2810</v>
       </c>
       <c r="D565" s="2" t="s">
-        <v>6787</v>
+        <v>6786</v>
       </c>
       <c r="E565" s="2" t="s">
+        <v>6784</v>
+      </c>
+      <c r="F565" s="2" t="s">
         <v>6785</v>
-      </c>
-      <c r="F565" s="2" t="s">
-        <v>6786</v>
       </c>
       <c r="G565" s="3">
         <v>4</v>
@@ -38478,7 +38479,7 @@
         <v>565</v>
       </c>
       <c r="B566" s="2" t="s">
-        <v>6876</v>
+        <v>6875</v>
       </c>
       <c r="C566" s="2" t="s">
         <v>2812</v>
@@ -38490,7 +38491,7 @@
         <v>2814</v>
       </c>
       <c r="F566" s="2" t="s">
-        <v>6877</v>
+        <v>6876</v>
       </c>
       <c r="G566" s="3">
         <v>3</v>
@@ -38652,19 +38653,19 @@
         <v>571</v>
       </c>
       <c r="B572" s="2" t="s">
-        <v>6673</v>
+        <v>6672</v>
       </c>
       <c r="C572" s="2" t="s">
+        <v>6616</v>
+      </c>
+      <c r="D572" s="2" t="s">
         <v>6617</v>
       </c>
-      <c r="D572" s="2" t="s">
+      <c r="E572" s="2" t="s">
+        <v>6619</v>
+      </c>
+      <c r="F572" s="2" t="s">
         <v>6618</v>
-      </c>
-      <c r="E572" s="2" t="s">
-        <v>6620</v>
-      </c>
-      <c r="F572" s="2" t="s">
-        <v>6619</v>
       </c>
       <c r="G572" s="3">
         <v>4</v>
@@ -38681,19 +38682,19 @@
         <v>572</v>
       </c>
       <c r="B573" s="2" t="s">
-        <v>6674</v>
+        <v>6673</v>
       </c>
       <c r="C573" s="2" t="s">
-        <v>6620</v>
+        <v>6619</v>
       </c>
       <c r="D573" s="2" t="s">
-        <v>6619</v>
+        <v>6618</v>
       </c>
       <c r="E573" s="2" t="s">
+        <v>6616</v>
+      </c>
+      <c r="F573" s="2" t="s">
         <v>6617</v>
-      </c>
-      <c r="F573" s="2" t="s">
-        <v>6618</v>
       </c>
       <c r="G573" s="3">
         <v>4</v>
@@ -38710,19 +38711,19 @@
         <v>573</v>
       </c>
       <c r="B574" s="2" t="s">
+        <v>6620</v>
+      </c>
+      <c r="C574" s="2" t="s">
+        <v>6618</v>
+      </c>
+      <c r="D574" s="2" t="s">
         <v>6621</v>
       </c>
-      <c r="C574" s="2" t="s">
+      <c r="E574" s="2" t="s">
+        <v>6622</v>
+      </c>
+      <c r="F574" s="2" t="s">
         <v>6619</v>
-      </c>
-      <c r="D574" s="2" t="s">
-        <v>6622</v>
-      </c>
-      <c r="E574" s="2" t="s">
-        <v>6623</v>
-      </c>
-      <c r="F574" s="2" t="s">
-        <v>6620</v>
       </c>
       <c r="G574" s="3">
         <v>2</v>
@@ -38745,7 +38746,7 @@
         <v>2848</v>
       </c>
       <c r="D575" s="2" t="s">
-        <v>6624</v>
+        <v>6623</v>
       </c>
       <c r="E575" s="2" t="s">
         <v>2849</v>
@@ -38797,19 +38798,19 @@
         <v>576</v>
       </c>
       <c r="B577" s="2" t="s">
+        <v>6629</v>
+      </c>
+      <c r="C577" s="2" t="s">
+        <v>6633</v>
+      </c>
+      <c r="D577" s="2" t="s">
         <v>6630</v>
       </c>
-      <c r="C577" s="2" t="s">
-        <v>6634</v>
-      </c>
-      <c r="D577" s="2" t="s">
+      <c r="E577" s="2" t="s">
         <v>6631</v>
       </c>
-      <c r="E577" s="2" t="s">
+      <c r="F577" s="2" t="s">
         <v>6632</v>
-      </c>
-      <c r="F577" s="2" t="s">
-        <v>6633</v>
       </c>
       <c r="G577" s="3">
         <v>3</v>
@@ -38826,19 +38827,19 @@
         <v>577</v>
       </c>
       <c r="B578" s="5" t="s">
+        <v>6624</v>
+      </c>
+      <c r="C578" s="2" t="s">
         <v>6625</v>
       </c>
-      <c r="C578" s="2" t="s">
+      <c r="D578" s="2" t="s">
         <v>6626</v>
       </c>
-      <c r="D578" s="2" t="s">
+      <c r="E578" s="2" t="s">
+        <v>6628</v>
+      </c>
+      <c r="F578" s="2" t="s">
         <v>6627</v>
-      </c>
-      <c r="E578" s="2" t="s">
-        <v>6629</v>
-      </c>
-      <c r="F578" s="2" t="s">
-        <v>6628</v>
       </c>
       <c r="G578" s="3">
         <v>1</v>
@@ -38855,16 +38856,16 @@
         <v>578</v>
       </c>
       <c r="B579" s="2" t="s">
+        <v>6634</v>
+      </c>
+      <c r="C579" s="2" t="s">
         <v>6635</v>
       </c>
-      <c r="C579" s="2" t="s">
+      <c r="D579" s="2" t="s">
         <v>6636</v>
       </c>
-      <c r="D579" s="2" t="s">
+      <c r="E579" s="2" t="s">
         <v>6637</v>
-      </c>
-      <c r="E579" s="2" t="s">
-        <v>6638</v>
       </c>
       <c r="F579" s="2" t="s">
         <v>2858</v>
@@ -38893,7 +38894,7 @@
         <v>2862</v>
       </c>
       <c r="E580" s="2" t="s">
-        <v>6969</v>
+        <v>6968</v>
       </c>
       <c r="F580" s="2" t="s">
         <v>2863</v>
@@ -38925,7 +38926,7 @@
         <v>2868</v>
       </c>
       <c r="F581" s="2" t="s">
-        <v>6701</v>
+        <v>6700</v>
       </c>
       <c r="G581" s="3">
         <v>3</v>
@@ -39228,19 +39229,19 @@
         <v>591</v>
       </c>
       <c r="B592" s="2" t="s">
+        <v>6769</v>
+      </c>
+      <c r="C592" s="2" t="s">
+        <v>6783</v>
+      </c>
+      <c r="D592" s="2" t="s">
         <v>6770</v>
       </c>
-      <c r="C592" s="2" t="s">
-        <v>6784</v>
-      </c>
-      <c r="D592" s="2" t="s">
+      <c r="E592" s="2" t="s">
         <v>6771</v>
       </c>
-      <c r="E592" s="2" t="s">
+      <c r="F592" s="2" t="s">
         <v>6772</v>
-      </c>
-      <c r="F592" s="2" t="s">
-        <v>6773</v>
       </c>
       <c r="G592" s="3">
         <v>1</v>
@@ -39286,10 +39287,10 @@
         <v>593</v>
       </c>
       <c r="B594" s="2" t="s">
-        <v>6915</v>
+        <v>6914</v>
       </c>
       <c r="C594" s="2" t="s">
-        <v>6914</v>
+        <v>6913</v>
       </c>
       <c r="D594" s="2" t="s">
         <v>2932</v>
@@ -39298,7 +39299,7 @@
         <v>2933</v>
       </c>
       <c r="F594" s="2" t="s">
-        <v>6916</v>
+        <v>6915</v>
       </c>
       <c r="G594" s="3">
         <v>3</v>
@@ -39924,7 +39925,7 @@
         <v>615</v>
       </c>
       <c r="B616" s="2" t="s">
-        <v>6522</v>
+        <v>6521</v>
       </c>
       <c r="C616" s="2" t="s">
         <v>3032</v>
@@ -40040,7 +40041,7 @@
         <v>619</v>
       </c>
       <c r="B620" s="2" t="s">
-        <v>6585</v>
+        <v>6584</v>
       </c>
       <c r="C620" s="2" t="s">
         <v>3053</v>
@@ -40052,7 +40053,7 @@
         <v>3055</v>
       </c>
       <c r="F620" s="2" t="s">
-        <v>6586</v>
+        <v>6585</v>
       </c>
       <c r="G620" s="3">
         <v>4</v>
@@ -40206,19 +40207,19 @@
         <v>625</v>
       </c>
       <c r="B626" s="2" t="s">
+        <v>6787</v>
+      </c>
+      <c r="C626" s="2" t="s">
         <v>6788</v>
       </c>
-      <c r="C626" s="2" t="s">
+      <c r="D626" s="2" t="s">
         <v>6789</v>
       </c>
-      <c r="D626" s="2" t="s">
+      <c r="E626" s="2" t="s">
         <v>6790</v>
       </c>
-      <c r="E626" s="2" t="s">
+      <c r="F626" s="2" t="s">
         <v>6791</v>
-      </c>
-      <c r="F626" s="2" t="s">
-        <v>6792</v>
       </c>
       <c r="G626" s="3">
         <v>4</v>
@@ -40235,7 +40236,7 @@
         <v>626</v>
       </c>
       <c r="B627" s="2" t="s">
-        <v>6719</v>
+        <v>6718</v>
       </c>
       <c r="C627" s="2" t="s">
         <v>1038</v>
@@ -40331,10 +40332,10 @@
         <v>3097</v>
       </c>
       <c r="E630" s="2" t="s">
+        <v>6873</v>
+      </c>
+      <c r="F630" s="2" t="s">
         <v>6874</v>
-      </c>
-      <c r="F630" s="2" t="s">
-        <v>6875</v>
       </c>
       <c r="G630" s="3">
         <v>1</v>
@@ -40409,7 +40410,7 @@
         <v>632</v>
       </c>
       <c r="B633" s="2" t="s">
-        <v>6886</v>
+        <v>6885</v>
       </c>
       <c r="C633" s="2" t="s">
         <v>3111</v>
@@ -40438,19 +40439,19 @@
         <v>633</v>
       </c>
       <c r="B634" s="2" t="s">
+        <v>6888</v>
+      </c>
+      <c r="C634" s="2" t="s">
+        <v>6884</v>
+      </c>
+      <c r="D634" s="2" t="s">
+        <v>6887</v>
+      </c>
+      <c r="E634" s="2" t="s">
         <v>6889</v>
       </c>
-      <c r="C634" s="2" t="s">
-        <v>6885</v>
-      </c>
-      <c r="D634" s="2" t="s">
-        <v>6888</v>
-      </c>
-      <c r="E634" s="2" t="s">
-        <v>6890</v>
-      </c>
       <c r="F634" s="2" t="s">
-        <v>6887</v>
+        <v>6886</v>
       </c>
       <c r="G634" s="3">
         <v>4</v>
@@ -40624,7 +40625,7 @@
         <v>3146</v>
       </c>
       <c r="F640" s="2" t="s">
-        <v>6500</v>
+        <v>6499</v>
       </c>
       <c r="G640" s="3">
         <v>2</v>
@@ -40844,7 +40845,7 @@
         <v>647</v>
       </c>
       <c r="B648" s="2" t="s">
-        <v>6839</v>
+        <v>6838</v>
       </c>
       <c r="C648" s="2" t="s">
         <v>3180</v>
@@ -40856,7 +40857,7 @@
         <v>3183</v>
       </c>
       <c r="F648" s="2" t="s">
-        <v>6840</v>
+        <v>6839</v>
       </c>
       <c r="G648" s="3">
         <v>1</v>
@@ -40931,7 +40932,7 @@
         <v>650</v>
       </c>
       <c r="B651" s="2" t="s">
-        <v>6533</v>
+        <v>6532</v>
       </c>
       <c r="C651" s="2" t="s">
         <v>3197</v>
@@ -40940,10 +40941,10 @@
         <v>3198</v>
       </c>
       <c r="E651" s="2" t="s">
+        <v>6533</v>
+      </c>
+      <c r="F651" s="2" t="s">
         <v>6534</v>
-      </c>
-      <c r="F651" s="2" t="s">
-        <v>6535</v>
       </c>
       <c r="G651" s="3">
         <v>2</v>
@@ -40989,7 +40990,7 @@
         <v>652</v>
       </c>
       <c r="B653" s="2" t="s">
-        <v>6581</v>
+        <v>6580</v>
       </c>
       <c r="C653" s="2" t="s">
         <v>1472</v>
@@ -41001,7 +41002,7 @@
         <v>3207</v>
       </c>
       <c r="F653" s="2" t="s">
-        <v>6582</v>
+        <v>6581</v>
       </c>
       <c r="G653" s="3">
         <v>1</v>
@@ -41047,10 +41048,10 @@
         <v>654</v>
       </c>
       <c r="B655" s="2" t="s">
+        <v>6948</v>
+      </c>
+      <c r="C655" s="2" t="s">
         <v>6949</v>
-      </c>
-      <c r="C655" s="2" t="s">
-        <v>6950</v>
       </c>
       <c r="D655" s="2" t="s">
         <v>3216</v>
@@ -41059,7 +41060,7 @@
         <v>3217</v>
       </c>
       <c r="F655" s="2" t="s">
-        <v>6951</v>
+        <v>6950</v>
       </c>
       <c r="G655" s="3">
         <v>4</v>
@@ -42290,7 +42291,7 @@
         <v>697</v>
       </c>
       <c r="B698" s="2" t="s">
-        <v>6922</v>
+        <v>6921</v>
       </c>
       <c r="C698" s="2" t="s">
         <v>3414</v>
@@ -42302,7 +42303,7 @@
         <v>3416</v>
       </c>
       <c r="F698" s="2" t="s">
-        <v>6921</v>
+        <v>6920</v>
       </c>
       <c r="G698" s="3">
         <v>4</v>
@@ -42319,7 +42320,7 @@
         <v>698</v>
       </c>
       <c r="B699" s="2" t="s">
-        <v>6920</v>
+        <v>6919</v>
       </c>
       <c r="C699" s="2" t="s">
         <v>3418</v>
@@ -42499,19 +42500,19 @@
         <v>3451</v>
       </c>
       <c r="D705" s="2" t="s">
-        <v>6735</v>
+        <v>6734</v>
       </c>
       <c r="E705" s="2" t="s">
         <v>3452</v>
       </c>
       <c r="F705" s="2" t="s">
-        <v>6736</v>
+        <v>6735</v>
       </c>
       <c r="G705" s="3">
         <v>2</v>
       </c>
       <c r="H705" s="2" t="s">
-        <v>6737</v>
+        <v>6736</v>
       </c>
       <c r="I705" s="2" t="s">
         <v>15</v>
@@ -42899,7 +42900,7 @@
         <v>718</v>
       </c>
       <c r="B719" s="2" t="s">
-        <v>6609</v>
+        <v>6608</v>
       </c>
       <c r="C719" s="2" t="s">
         <v>693</v>
@@ -43098,7 +43099,7 @@
         <v>725</v>
       </c>
       <c r="B726" s="2" t="s">
-        <v>6675</v>
+        <v>6674</v>
       </c>
       <c r="C726" s="2" t="s">
         <v>3533</v>
@@ -43107,10 +43108,10 @@
         <v>3534</v>
       </c>
       <c r="E726" s="2" t="s">
+        <v>6675</v>
+      </c>
+      <c r="F726" s="2" t="s">
         <v>6676</v>
-      </c>
-      <c r="F726" s="2" t="s">
-        <v>6677</v>
       </c>
       <c r="G726" s="3">
         <v>1</v>
@@ -43165,10 +43166,10 @@
         <v>3539</v>
       </c>
       <c r="E728" s="2" t="s">
+        <v>6943</v>
+      </c>
+      <c r="F728" s="2" t="s">
         <v>6944</v>
-      </c>
-      <c r="F728" s="2" t="s">
-        <v>6945</v>
       </c>
       <c r="G728" s="3">
         <v>3</v>
@@ -43243,16 +43244,16 @@
         <v>730</v>
       </c>
       <c r="B731" s="2" t="s">
+        <v>6696</v>
+      </c>
+      <c r="C731" s="2" t="s">
         <v>6697</v>
       </c>
-      <c r="C731" s="2" t="s">
+      <c r="D731" s="2" t="s">
         <v>6698</v>
       </c>
-      <c r="D731" s="2" t="s">
+      <c r="E731" s="2" t="s">
         <v>6699</v>
-      </c>
-      <c r="E731" s="2" t="s">
-        <v>6700</v>
       </c>
       <c r="F731" s="2" t="s">
         <v>51</v>
@@ -43330,7 +43331,7 @@
         <v>733</v>
       </c>
       <c r="B734" s="2" t="s">
-        <v>6762</v>
+        <v>6761</v>
       </c>
       <c r="C734" s="6">
         <v>7.0000000000000007E-2</v>
@@ -43362,16 +43363,16 @@
         <v>3563</v>
       </c>
       <c r="C735" s="2" t="s">
+        <v>6758</v>
+      </c>
+      <c r="D735" s="2" t="s">
+        <v>6757</v>
+      </c>
+      <c r="E735" s="2" t="s">
+        <v>6760</v>
+      </c>
+      <c r="F735" s="2" t="s">
         <v>6759</v>
-      </c>
-      <c r="D735" s="2" t="s">
-        <v>6758</v>
-      </c>
-      <c r="E735" s="2" t="s">
-        <v>6761</v>
-      </c>
-      <c r="F735" s="2" t="s">
-        <v>6760</v>
       </c>
       <c r="G735" s="3">
         <v>4</v>
@@ -43417,7 +43418,7 @@
         <v>736</v>
       </c>
       <c r="B737" s="2" t="s">
-        <v>6669</v>
+        <v>6668</v>
       </c>
       <c r="C737" s="2" t="s">
         <v>3568</v>
@@ -43446,13 +43447,13 @@
         <v>737</v>
       </c>
       <c r="B738" s="2" t="s">
+        <v>6669</v>
+      </c>
+      <c r="C738" s="2" t="s">
         <v>6670</v>
       </c>
-      <c r="C738" s="2" t="s">
+      <c r="D738" s="2" t="s">
         <v>6671</v>
-      </c>
-      <c r="D738" s="2" t="s">
-        <v>6672</v>
       </c>
       <c r="E738" s="2" t="s">
         <v>3573</v>
@@ -43504,7 +43505,7 @@
         <v>739</v>
       </c>
       <c r="B740" s="2" t="s">
-        <v>6892</v>
+        <v>6891</v>
       </c>
       <c r="C740" s="6">
         <v>0.05</v>
@@ -43565,13 +43566,13 @@
         <v>3584</v>
       </c>
       <c r="C742" s="2" t="s">
-        <v>6490</v>
+        <v>6489</v>
       </c>
       <c r="D742" s="2" t="s">
         <v>3585</v>
       </c>
       <c r="E742" s="2" t="s">
-        <v>6491</v>
+        <v>6490</v>
       </c>
       <c r="F742" s="2" t="s">
         <v>51</v>
@@ -43966,25 +43967,25 @@
         <v>755</v>
       </c>
       <c r="B756" s="2" t="s">
+        <v>6510</v>
+      </c>
+      <c r="C756" s="2" t="s">
         <v>6511</v>
       </c>
-      <c r="C756" s="2" t="s">
+      <c r="D756" s="2" t="s">
         <v>6512</v>
       </c>
-      <c r="D756" s="2" t="s">
+      <c r="E756" s="2" t="s">
         <v>6513</v>
       </c>
-      <c r="E756" s="2" t="s">
+      <c r="F756" s="2" t="s">
         <v>6514</v>
-      </c>
-      <c r="F756" s="2" t="s">
-        <v>6515</v>
       </c>
       <c r="G756" s="3">
         <v>2</v>
       </c>
       <c r="H756" s="2" t="s">
-        <v>6516</v>
+        <v>6515</v>
       </c>
       <c r="I756" s="2" t="s">
         <v>780</v>
@@ -44285,19 +44286,19 @@
         <v>766</v>
       </c>
       <c r="B767" s="2" t="s">
-        <v>6841</v>
+        <v>6840</v>
       </c>
       <c r="C767" s="2" t="s">
         <v>97</v>
       </c>
       <c r="D767" s="2" t="s">
-        <v>6842</v>
+        <v>6841</v>
       </c>
       <c r="E767" s="2" t="s">
         <v>3686</v>
       </c>
       <c r="F767" s="2" t="s">
-        <v>6843</v>
+        <v>6842</v>
       </c>
       <c r="G767" s="3">
         <v>3</v>
@@ -44457,7 +44458,7 @@
         <v>772</v>
       </c>
       <c r="B773" s="2" t="s">
-        <v>6991</v>
+        <v>6990</v>
       </c>
       <c r="C773" s="2" t="s">
         <v>495</v>
@@ -44469,7 +44470,7 @@
         <v>497</v>
       </c>
       <c r="F773" s="4" t="s">
-        <v>6992</v>
+        <v>6991</v>
       </c>
       <c r="G773" s="3">
         <v>2</v>
@@ -44979,13 +44980,13 @@
         <v>790</v>
       </c>
       <c r="B791" s="2" t="s">
+        <v>6855</v>
+      </c>
+      <c r="C791" s="2" t="s">
+        <v>6854</v>
+      </c>
+      <c r="D791" s="2" t="s">
         <v>6856</v>
-      </c>
-      <c r="C791" s="2" t="s">
-        <v>6855</v>
-      </c>
-      <c r="D791" s="2" t="s">
-        <v>6857</v>
       </c>
       <c r="E791" s="2" t="s">
         <v>3504</v>
@@ -45327,19 +45328,19 @@
         <v>802</v>
       </c>
       <c r="B803" s="2" t="s">
-        <v>6814</v>
+        <v>6813</v>
       </c>
       <c r="C803" s="2" t="s">
         <v>3845</v>
       </c>
       <c r="D803" s="2" t="s">
-        <v>6815</v>
+        <v>6814</v>
       </c>
       <c r="E803" s="2" t="s">
         <v>3846</v>
       </c>
       <c r="F803" s="2" t="s">
-        <v>6816</v>
+        <v>6815</v>
       </c>
       <c r="G803" s="3">
         <v>3</v>
@@ -45385,7 +45386,7 @@
         <v>804</v>
       </c>
       <c r="B805" s="2" t="s">
-        <v>6648</v>
+        <v>6647</v>
       </c>
       <c r="C805" s="2" t="s">
         <v>3854</v>
@@ -45617,13 +45618,13 @@
         <v>812</v>
       </c>
       <c r="B813" s="2" t="s">
-        <v>6579</v>
+        <v>6578</v>
       </c>
       <c r="C813" s="2" t="s">
         <v>3896</v>
       </c>
       <c r="D813" s="2" t="s">
-        <v>6580</v>
+        <v>6579</v>
       </c>
       <c r="E813" s="2" t="s">
         <v>3897</v>
@@ -45646,7 +45647,7 @@
         <v>813</v>
       </c>
       <c r="B814" s="2" t="s">
-        <v>6906</v>
+        <v>6905</v>
       </c>
       <c r="C814" s="2" t="s">
         <v>3900</v>
@@ -45658,7 +45659,7 @@
         <v>3902</v>
       </c>
       <c r="F814" s="2" t="s">
-        <v>6907</v>
+        <v>6906</v>
       </c>
       <c r="G814" s="3">
         <v>1</v>
@@ -45675,7 +45676,7 @@
         <v>814</v>
       </c>
       <c r="B815" s="2" t="s">
-        <v>6577</v>
+        <v>6576</v>
       </c>
       <c r="C815" s="2" t="s">
         <v>3904</v>
@@ -45687,7 +45688,7 @@
         <v>3906</v>
       </c>
       <c r="F815" s="2" t="s">
-        <v>6578</v>
+        <v>6577</v>
       </c>
       <c r="G815" s="3">
         <v>1</v>
@@ -45826,13 +45827,13 @@
         <v>3926</v>
       </c>
       <c r="D820" s="2" t="s">
-        <v>6686</v>
+        <v>6685</v>
       </c>
       <c r="E820" s="2" t="s">
         <v>3927</v>
       </c>
       <c r="F820" s="2" t="s">
-        <v>6687</v>
+        <v>6686</v>
       </c>
       <c r="G820" s="3">
         <v>4</v>
@@ -45907,7 +45908,7 @@
         <v>822</v>
       </c>
       <c r="B823" s="2" t="s">
-        <v>6911</v>
+        <v>6910</v>
       </c>
       <c r="C823" s="2" t="s">
         <v>3940</v>
@@ -45916,10 +45917,10 @@
         <v>3941</v>
       </c>
       <c r="E823" s="2" t="s">
+        <v>6911</v>
+      </c>
+      <c r="F823" s="2" t="s">
         <v>6912</v>
-      </c>
-      <c r="F823" s="2" t="s">
-        <v>6913</v>
       </c>
       <c r="G823" s="3">
         <v>4</v>
@@ -45965,7 +45966,7 @@
         <v>824</v>
       </c>
       <c r="B825" s="2" t="s">
-        <v>7005</v>
+        <v>7004</v>
       </c>
       <c r="C825" s="2" t="s">
         <v>102</v>
@@ -45977,7 +45978,7 @@
         <v>3949</v>
       </c>
       <c r="F825" s="2" t="s">
-        <v>7006</v>
+        <v>7005</v>
       </c>
       <c r="G825" s="3">
         <v>3</v>
@@ -46081,7 +46082,7 @@
         <v>828</v>
       </c>
       <c r="B829" s="2" t="s">
-        <v>6647</v>
+        <v>6646</v>
       </c>
       <c r="C829" s="2" t="s">
         <v>3967</v>
@@ -46113,16 +46114,16 @@
         <v>3972</v>
       </c>
       <c r="C830" s="2" t="s">
+        <v>6793</v>
+      </c>
+      <c r="D830" s="2" t="s">
+        <v>6792</v>
+      </c>
+      <c r="E830" s="2" t="s">
         <v>6794</v>
       </c>
-      <c r="D830" s="2" t="s">
-        <v>6793</v>
-      </c>
-      <c r="E830" s="2" t="s">
+      <c r="F830" s="2" t="s">
         <v>6795</v>
-      </c>
-      <c r="F830" s="2" t="s">
-        <v>6796</v>
       </c>
       <c r="G830" s="3">
         <v>4</v>
@@ -46171,16 +46172,16 @@
         <v>3980</v>
       </c>
       <c r="C832" s="2" t="s">
+        <v>6612</v>
+      </c>
+      <c r="D832" s="2" t="s">
         <v>6613</v>
       </c>
-      <c r="D832" s="2" t="s">
+      <c r="E832" s="2" t="s">
         <v>6614</v>
       </c>
-      <c r="E832" s="2" t="s">
+      <c r="F832" s="2" t="s">
         <v>6615</v>
-      </c>
-      <c r="F832" s="2" t="s">
-        <v>6616</v>
       </c>
       <c r="G832" s="3">
         <v>4</v>
@@ -46981,7 +46982,7 @@
         <v>4116</v>
       </c>
       <c r="C860" s="2" t="s">
-        <v>6967</v>
+        <v>6966</v>
       </c>
       <c r="D860" s="2" t="s">
         <v>4117</v>
@@ -47123,7 +47124,7 @@
         <v>864</v>
       </c>
       <c r="B865" s="2" t="s">
-        <v>6538</v>
+        <v>6537</v>
       </c>
       <c r="C865" s="2" t="s">
         <v>4143</v>
@@ -47132,10 +47133,10 @@
         <v>2954</v>
       </c>
       <c r="E865" s="2" t="s">
+        <v>6535</v>
+      </c>
+      <c r="F865" s="2" t="s">
         <v>6536</v>
-      </c>
-      <c r="F865" s="2" t="s">
-        <v>6537</v>
       </c>
       <c r="G865" s="3">
         <v>4</v>
@@ -47152,19 +47153,19 @@
         <v>865</v>
       </c>
       <c r="B866" s="2" t="s">
+        <v>6542</v>
+      </c>
+      <c r="C866" s="2" t="s">
         <v>6543</v>
       </c>
-      <c r="C866" s="2" t="s">
+      <c r="D866" s="4" t="s">
         <v>6544</v>
       </c>
-      <c r="D866" s="4" t="s">
+      <c r="E866" s="2" t="s">
         <v>6545</v>
       </c>
-      <c r="E866" s="2" t="s">
+      <c r="F866" s="2" t="s">
         <v>6546</v>
-      </c>
-      <c r="F866" s="2" t="s">
-        <v>6547</v>
       </c>
       <c r="G866" s="3">
         <v>3</v>
@@ -47268,7 +47269,7 @@
         <v>869</v>
       </c>
       <c r="B870" s="2" t="s">
-        <v>6749</v>
+        <v>6748</v>
       </c>
       <c r="C870" s="2" t="s">
         <v>4161</v>
@@ -47277,10 +47278,10 @@
         <v>4162</v>
       </c>
       <c r="E870" s="2" t="s">
-        <v>6751</v>
+        <v>6750</v>
       </c>
       <c r="F870" s="2" t="s">
-        <v>6750</v>
+        <v>6749</v>
       </c>
       <c r="G870" s="3">
         <v>4</v>
@@ -47384,7 +47385,7 @@
         <v>873</v>
       </c>
       <c r="B874" s="2" t="s">
-        <v>6909</v>
+        <v>6908</v>
       </c>
       <c r="C874" s="2" t="s">
         <v>938</v>
@@ -47396,7 +47397,7 @@
         <v>4183</v>
       </c>
       <c r="F874" s="2" t="s">
-        <v>6910</v>
+        <v>6909</v>
       </c>
       <c r="G874" s="3">
         <v>1</v>
@@ -47588,7 +47589,7 @@
         <v>4218</v>
       </c>
       <c r="C881" s="2" t="s">
-        <v>6498</v>
+        <v>6497</v>
       </c>
       <c r="D881" s="2" t="s">
         <v>2954</v>
@@ -47597,7 +47598,7 @@
         <v>4219</v>
       </c>
       <c r="F881" s="2" t="s">
-        <v>6499</v>
+        <v>6498</v>
       </c>
       <c r="G881" s="3">
         <v>1</v>
@@ -47614,7 +47615,7 @@
         <v>881</v>
       </c>
       <c r="B882" s="2" t="s">
-        <v>6878</v>
+        <v>6877</v>
       </c>
       <c r="C882" s="2" t="s">
         <v>4008</v>
@@ -47626,7 +47627,7 @@
         <v>4221</v>
       </c>
       <c r="F882" s="2" t="s">
-        <v>6879</v>
+        <v>6878</v>
       </c>
       <c r="G882" s="3">
         <v>3</v>
@@ -47730,7 +47731,7 @@
         <v>885</v>
       </c>
       <c r="B886" s="2" t="s">
-        <v>6854</v>
+        <v>6853</v>
       </c>
       <c r="C886" s="2" t="s">
         <v>4241</v>
@@ -47933,19 +47934,19 @@
         <v>892</v>
       </c>
       <c r="B893" s="2" t="s">
+        <v>6753</v>
+      </c>
+      <c r="C893" s="2" t="s">
         <v>6754</v>
       </c>
-      <c r="C893" s="2" t="s">
+      <c r="D893" s="2" t="s">
         <v>6755</v>
-      </c>
-      <c r="D893" s="2" t="s">
-        <v>6756</v>
       </c>
       <c r="E893" s="2" t="s">
         <v>4273</v>
       </c>
       <c r="F893" s="2" t="s">
-        <v>6757</v>
+        <v>6756</v>
       </c>
       <c r="G893" s="3">
         <v>2</v>
@@ -48026,7 +48027,7 @@
         <v>4288</v>
       </c>
       <c r="D896" s="2" t="s">
-        <v>6967</v>
+        <v>6966</v>
       </c>
       <c r="E896" s="2" t="s">
         <v>4117</v>
@@ -48049,16 +48050,16 @@
         <v>896</v>
       </c>
       <c r="B897" s="2" t="s">
-        <v>6504</v>
+        <v>6503</v>
       </c>
       <c r="C897" s="2" t="s">
         <v>4008</v>
       </c>
       <c r="D897" s="2" t="s">
+        <v>6504</v>
+      </c>
+      <c r="E897" s="2" t="s">
         <v>6505</v>
-      </c>
-      <c r="E897" s="2" t="s">
-        <v>6506</v>
       </c>
       <c r="F897" s="2" t="s">
         <v>4097</v>
@@ -48081,7 +48082,7 @@
         <v>4292</v>
       </c>
       <c r="C898" s="2" t="s">
-        <v>6844</v>
+        <v>6843</v>
       </c>
       <c r="D898" s="2" t="s">
         <v>4293</v>
@@ -48090,7 +48091,7 @@
         <v>4294</v>
       </c>
       <c r="F898" s="2" t="s">
-        <v>6845</v>
+        <v>6844</v>
       </c>
       <c r="G898" s="3">
         <v>1</v>
@@ -48366,19 +48367,19 @@
         <v>907</v>
       </c>
       <c r="B908" s="2" t="s">
-        <v>6861</v>
+        <v>6860</v>
       </c>
       <c r="C908" s="2" t="s">
         <v>4345</v>
       </c>
       <c r="D908" s="2" t="s">
-        <v>6862</v>
+        <v>6861</v>
       </c>
       <c r="E908" s="2" t="s">
         <v>3864</v>
       </c>
       <c r="F908" s="2" t="s">
-        <v>6863</v>
+        <v>6862</v>
       </c>
       <c r="G908" s="3">
         <v>3</v>
@@ -48540,19 +48541,19 @@
         <v>913</v>
       </c>
       <c r="B914" s="2" t="s">
+        <v>6648</v>
+      </c>
+      <c r="C914" s="2" t="s">
         <v>6649</v>
-      </c>
-      <c r="C914" s="2" t="s">
-        <v>6650</v>
       </c>
       <c r="D914" s="2" t="s">
         <v>4377</v>
       </c>
       <c r="E914" s="2" t="s">
+        <v>6650</v>
+      </c>
+      <c r="F914" s="2" t="s">
         <v>6651</v>
-      </c>
-      <c r="F914" s="2" t="s">
-        <v>6652</v>
       </c>
       <c r="G914" s="3">
         <v>3</v>
@@ -48824,7 +48825,7 @@
         <v>923</v>
       </c>
       <c r="B924" s="2" t="s">
-        <v>6503</v>
+        <v>6502</v>
       </c>
       <c r="C924" s="2" t="s">
         <v>2998</v>
@@ -49257,7 +49258,7 @@
         <v>938</v>
       </c>
       <c r="B939" s="2" t="s">
-        <v>6704</v>
+        <v>6703</v>
       </c>
       <c r="C939" s="2" t="s">
         <v>4498</v>
@@ -49521,16 +49522,16 @@
         <v>4550</v>
       </c>
       <c r="C948" s="2" t="s">
-        <v>6998</v>
+        <v>6997</v>
       </c>
       <c r="D948" s="2" t="s">
         <v>4551</v>
       </c>
       <c r="E948" s="2" t="s">
+        <v>6998</v>
+      </c>
+      <c r="F948" s="2" t="s">
         <v>6999</v>
-      </c>
-      <c r="F948" s="2" t="s">
-        <v>7000</v>
       </c>
       <c r="G948" s="3">
         <v>3</v>
@@ -49673,7 +49674,7 @@
         <v>4568</v>
       </c>
       <c r="F953" s="2" t="s">
-        <v>6492</v>
+        <v>6491</v>
       </c>
       <c r="G953" s="3">
         <v>3</v>
@@ -49888,13 +49889,13 @@
         <v>4605</v>
       </c>
       <c r="C961" s="2" t="s">
+        <v>6780</v>
+      </c>
+      <c r="D961" s="2" t="s">
         <v>6781</v>
       </c>
-      <c r="D961" s="2" t="s">
+      <c r="E961" s="2" t="s">
         <v>6782</v>
-      </c>
-      <c r="E961" s="2" t="s">
-        <v>6783</v>
       </c>
       <c r="F961" s="2" t="s">
         <v>4606</v>
@@ -50465,19 +50466,19 @@
         <v>980</v>
       </c>
       <c r="B981" s="2" t="s">
-        <v>6562</v>
+        <v>6561</v>
       </c>
       <c r="C981" s="2" t="s">
+        <v>6563</v>
+      </c>
+      <c r="D981" s="2" t="s">
         <v>6564</v>
-      </c>
-      <c r="D981" s="2" t="s">
-        <v>6565</v>
       </c>
       <c r="E981" s="2" t="s">
         <v>4709</v>
       </c>
       <c r="F981" s="2" t="s">
-        <v>6563</v>
+        <v>6562</v>
       </c>
       <c r="G981" s="3">
         <v>2</v>
@@ -50697,19 +50698,19 @@
         <v>988</v>
       </c>
       <c r="B989" s="2" t="s">
+        <v>6522</v>
+      </c>
+      <c r="C989" s="2" t="s">
         <v>6523</v>
       </c>
-      <c r="C989" s="2" t="s">
+      <c r="D989" s="2" t="s">
         <v>6524</v>
       </c>
-      <c r="D989" s="2" t="s">
+      <c r="E989" s="2" t="s">
         <v>6525</v>
       </c>
-      <c r="E989" s="2" t="s">
+      <c r="F989" s="2" t="s">
         <v>6526</v>
-      </c>
-      <c r="F989" s="2" t="s">
-        <v>6527</v>
       </c>
       <c r="G989" s="3">
         <v>3</v>
@@ -50758,16 +50759,16 @@
         <v>4749</v>
       </c>
       <c r="C991" s="2" t="s">
-        <v>6984</v>
+        <v>6983</v>
       </c>
       <c r="D991" s="2" t="s">
         <v>4750</v>
       </c>
       <c r="E991" s="2" t="s">
+        <v>6981</v>
+      </c>
+      <c r="F991" s="2" t="s">
         <v>6982</v>
-      </c>
-      <c r="F991" s="2" t="s">
-        <v>6983</v>
       </c>
       <c r="G991" s="3">
         <v>2</v>
@@ -50784,10 +50785,10 @@
         <v>991</v>
       </c>
       <c r="B992" s="2" t="s">
-        <v>6852</v>
+        <v>6851</v>
       </c>
       <c r="C992" s="2" t="s">
-        <v>6851</v>
+        <v>6850</v>
       </c>
       <c r="D992" s="2" t="s">
         <v>4752</v>
@@ -50929,19 +50930,19 @@
         <v>996</v>
       </c>
       <c r="B997" s="2" t="s">
-        <v>6694</v>
+        <v>6693</v>
       </c>
       <c r="C997" s="2" t="s">
         <v>3855</v>
       </c>
       <c r="D997" s="2" t="s">
-        <v>6695</v>
+        <v>6694</v>
       </c>
       <c r="E997" s="2" t="s">
         <v>4768</v>
       </c>
       <c r="F997" s="2" t="s">
-        <v>6696</v>
+        <v>6695</v>
       </c>
       <c r="G997" s="3">
         <v>3</v>
@@ -51333,7 +51334,7 @@
         <v>1010</v>
       </c>
       <c r="B1011" s="2" t="s">
-        <v>6988</v>
+        <v>6987</v>
       </c>
       <c r="C1011" s="2" t="s">
         <v>4816</v>
@@ -51394,16 +51395,16 @@
         <v>4827</v>
       </c>
       <c r="C1013" s="2" t="s">
+        <v>6901</v>
+      </c>
+      <c r="D1013" s="2" t="s">
+        <v>6900</v>
+      </c>
+      <c r="E1013" s="2" t="s">
         <v>6902</v>
       </c>
-      <c r="D1013" s="2" t="s">
-        <v>6901</v>
-      </c>
-      <c r="E1013" s="2" t="s">
-        <v>6903</v>
-      </c>
       <c r="F1013" s="2" t="s">
-        <v>6905</v>
+        <v>6904</v>
       </c>
       <c r="G1013" s="3">
         <v>2</v>
@@ -51420,7 +51421,7 @@
         <v>1013</v>
       </c>
       <c r="B1014" s="2" t="s">
-        <v>6904</v>
+        <v>6903</v>
       </c>
       <c r="C1014" s="2" t="s">
         <v>4828</v>
@@ -51481,16 +51482,16 @@
         <v>4840</v>
       </c>
       <c r="C1016" s="2" t="s">
+        <v>6652</v>
+      </c>
+      <c r="D1016" s="2" t="s">
         <v>6653</v>
-      </c>
-      <c r="D1016" s="2" t="s">
-        <v>6654</v>
       </c>
       <c r="E1016" s="2" t="s">
         <v>4841</v>
       </c>
       <c r="F1016" s="2" t="s">
-        <v>6655</v>
+        <v>6654</v>
       </c>
       <c r="G1016" s="3">
         <v>1</v>
@@ -51507,7 +51508,7 @@
         <v>1016</v>
       </c>
       <c r="B1017" s="2" t="s">
-        <v>6656</v>
+        <v>6655</v>
       </c>
       <c r="C1017" s="2" t="s">
         <v>4843</v>
@@ -51536,10 +51537,10 @@
         <v>1017</v>
       </c>
       <c r="B1018" s="2" t="s">
+        <v>6897</v>
+      </c>
+      <c r="C1018" s="2" t="s">
         <v>6898</v>
-      </c>
-      <c r="C1018" s="2" t="s">
-        <v>6899</v>
       </c>
       <c r="D1018" s="2" t="s">
         <v>4848</v>
@@ -51548,7 +51549,7 @@
         <v>4849</v>
       </c>
       <c r="F1018" s="2" t="s">
-        <v>6900</v>
+        <v>6899</v>
       </c>
       <c r="G1018" s="3">
         <v>4</v>
@@ -51768,7 +51769,7 @@
         <v>1025</v>
       </c>
       <c r="B1026" s="2" t="s">
-        <v>6566</v>
+        <v>6565</v>
       </c>
       <c r="C1026" s="2" t="s">
         <v>4882</v>
@@ -51777,10 +51778,10 @@
         <v>952</v>
       </c>
       <c r="E1026" s="2" t="s">
+        <v>6566</v>
+      </c>
+      <c r="F1026" s="2" t="s">
         <v>6567</v>
-      </c>
-      <c r="F1026" s="2" t="s">
-        <v>6568</v>
       </c>
       <c r="G1026" s="3">
         <v>1</v>
@@ -51832,7 +51833,7 @@
         <v>4891</v>
       </c>
       <c r="D1028" s="2" t="s">
-        <v>6968</v>
+        <v>6967</v>
       </c>
       <c r="E1028" s="2" t="s">
         <v>4892</v>
@@ -52116,7 +52117,7 @@
         <v>1037</v>
       </c>
       <c r="B1038" s="2" t="s">
-        <v>6846</v>
+        <v>6845</v>
       </c>
       <c r="C1038" s="2" t="s">
         <v>875</v>
@@ -52145,7 +52146,7 @@
         <v>1038</v>
       </c>
       <c r="B1039" s="2" t="s">
-        <v>6659</v>
+        <v>6658</v>
       </c>
       <c r="C1039" s="2" t="s">
         <v>4946</v>
@@ -52154,10 +52155,10 @@
         <v>4947</v>
       </c>
       <c r="E1039" s="2" t="s">
+        <v>6656</v>
+      </c>
+      <c r="F1039" s="2" t="s">
         <v>6657</v>
-      </c>
-      <c r="F1039" s="2" t="s">
-        <v>6658</v>
       </c>
       <c r="G1039" s="3">
         <v>2</v>
@@ -52174,19 +52175,19 @@
         <v>1039</v>
       </c>
       <c r="B1040" s="2" t="s">
+        <v>6516</v>
+      </c>
+      <c r="C1040" s="2" t="s">
         <v>6517</v>
       </c>
-      <c r="C1040" s="2" t="s">
+      <c r="D1040" s="2" t="s">
         <v>6518</v>
       </c>
-      <c r="D1040" s="2" t="s">
+      <c r="E1040" s="2" t="s">
         <v>6519</v>
       </c>
-      <c r="E1040" s="2" t="s">
+      <c r="F1040" s="2" t="s">
         <v>6520</v>
-      </c>
-      <c r="F1040" s="2" t="s">
-        <v>6521</v>
       </c>
       <c r="G1040" s="3">
         <v>4</v>
@@ -52415,7 +52416,7 @@
         <v>4993</v>
       </c>
       <c r="E1048" s="2" t="s">
-        <v>7004</v>
+        <v>7003</v>
       </c>
       <c r="F1048" s="2" t="s">
         <v>4994</v>
@@ -52464,7 +52465,7 @@
         <v>1049</v>
       </c>
       <c r="B1050" s="2" t="s">
-        <v>6752</v>
+        <v>6751</v>
       </c>
       <c r="C1050" s="2" t="s">
         <v>1502</v>
@@ -52476,7 +52477,7 @@
         <v>5002</v>
       </c>
       <c r="F1050" s="2" t="s">
-        <v>6753</v>
+        <v>6752</v>
       </c>
       <c r="G1050" s="3">
         <v>3</v>
@@ -52493,7 +52494,7 @@
         <v>1050</v>
       </c>
       <c r="B1051" s="2" t="s">
-        <v>6884</v>
+        <v>6883</v>
       </c>
       <c r="C1051" s="2" t="s">
         <v>5004</v>
@@ -52505,7 +52506,7 @@
         <v>5006</v>
       </c>
       <c r="F1051" s="2" t="s">
-        <v>6883</v>
+        <v>6882</v>
       </c>
       <c r="G1051" s="3">
         <v>1</v>
@@ -52754,19 +52755,19 @@
         <v>1059</v>
       </c>
       <c r="B1060" s="2" t="s">
+        <v>6704</v>
+      </c>
+      <c r="C1060" s="2" t="s">
+        <v>6707</v>
+      </c>
+      <c r="D1060" s="2" t="s">
         <v>6705</v>
       </c>
-      <c r="C1060" s="2" t="s">
+      <c r="E1060" s="2" t="s">
+        <v>6706</v>
+      </c>
+      <c r="F1060" s="2" t="s">
         <v>6708</v>
-      </c>
-      <c r="D1060" s="2" t="s">
-        <v>6706</v>
-      </c>
-      <c r="E1060" s="2" t="s">
-        <v>6707</v>
-      </c>
-      <c r="F1060" s="2" t="s">
-        <v>6709</v>
       </c>
       <c r="G1060" s="3">
         <v>4</v>
@@ -52812,19 +52813,19 @@
         <v>1061</v>
       </c>
       <c r="B1062" s="2" t="s">
-        <v>6774</v>
+        <v>6773</v>
       </c>
       <c r="C1062" s="2" t="s">
         <v>5060</v>
       </c>
       <c r="D1062" s="2" t="s">
+        <v>6774</v>
+      </c>
+      <c r="E1062" s="2" t="s">
         <v>6775</v>
       </c>
-      <c r="E1062" s="2" t="s">
+      <c r="F1062" s="2" t="s">
         <v>6776</v>
-      </c>
-      <c r="F1062" s="2" t="s">
-        <v>6777</v>
       </c>
       <c r="G1062" s="3">
         <v>1</v>
@@ -52905,13 +52906,13 @@
         <v>5074</v>
       </c>
       <c r="D1065" s="2" t="s">
-        <v>6807</v>
+        <v>6806</v>
       </c>
       <c r="E1065" s="2" t="s">
         <v>5075</v>
       </c>
       <c r="F1065" s="2" t="s">
-        <v>6808</v>
+        <v>6807</v>
       </c>
       <c r="G1065" s="3">
         <v>2</v>
@@ -53014,16 +53015,16 @@
         <v>5087</v>
       </c>
       <c r="C1069" s="2" t="s">
-        <v>6778</v>
+        <v>6777</v>
       </c>
       <c r="D1069" s="2" t="s">
         <v>5088</v>
       </c>
       <c r="E1069" s="2" t="s">
+        <v>6778</v>
+      </c>
+      <c r="F1069" s="2" t="s">
         <v>6779</v>
-      </c>
-      <c r="F1069" s="2" t="s">
-        <v>6780</v>
       </c>
       <c r="G1069" s="3">
         <v>4</v>
@@ -53040,7 +53041,7 @@
         <v>1069</v>
       </c>
       <c r="B1070" s="2" t="s">
-        <v>6942</v>
+        <v>6941</v>
       </c>
       <c r="C1070" s="2" t="s">
         <v>750</v>
@@ -53052,7 +53053,7 @@
         <v>928</v>
       </c>
       <c r="F1070" s="2" t="s">
-        <v>6943</v>
+        <v>6942</v>
       </c>
       <c r="G1070" s="3">
         <v>4</v>
@@ -53417,7 +53418,7 @@
         <v>1082</v>
       </c>
       <c r="B1083" s="2" t="s">
-        <v>6660</v>
+        <v>6659</v>
       </c>
       <c r="C1083" s="2" t="s">
         <v>5146</v>
@@ -53794,7 +53795,7 @@
         <v>1095</v>
       </c>
       <c r="B1096" s="2" t="s">
-        <v>6973</v>
+        <v>6972</v>
       </c>
       <c r="C1096" s="2" t="s">
         <v>5211</v>
@@ -53806,7 +53807,7 @@
         <v>5212</v>
       </c>
       <c r="F1096" s="2" t="s">
-        <v>6974</v>
+        <v>6973</v>
       </c>
       <c r="G1096" s="3">
         <v>4</v>
@@ -54258,19 +54259,19 @@
         <v>1111</v>
       </c>
       <c r="B1112" s="2" t="s">
+        <v>6762</v>
+      </c>
+      <c r="C1112" s="2" t="s">
         <v>6763</v>
       </c>
-      <c r="C1112" s="2" t="s">
+      <c r="D1112" s="2" t="s">
         <v>6764</v>
       </c>
-      <c r="D1112" s="2" t="s">
+      <c r="E1112" s="2" t="s">
         <v>6765</v>
       </c>
-      <c r="E1112" s="2" t="s">
+      <c r="F1112" s="2" t="s">
         <v>6766</v>
-      </c>
-      <c r="F1112" s="2" t="s">
-        <v>6767</v>
       </c>
       <c r="G1112" s="3">
         <v>4</v>
@@ -54383,10 +54384,10 @@
         <v>5295</v>
       </c>
       <c r="E1116" s="2" t="s">
+        <v>6719</v>
+      </c>
+      <c r="F1116" s="2" t="s">
         <v>6720</v>
-      </c>
-      <c r="F1116" s="2" t="s">
-        <v>6721</v>
       </c>
       <c r="G1116" s="3">
         <v>1</v>
@@ -54441,10 +54442,10 @@
         <v>5305</v>
       </c>
       <c r="E1118" s="2" t="s">
-        <v>6497</v>
+        <v>6496</v>
       </c>
       <c r="F1118" s="2" t="s">
-        <v>6496</v>
+        <v>6495</v>
       </c>
       <c r="G1118" s="3">
         <v>4</v>
@@ -54606,19 +54607,19 @@
         <v>1123</v>
       </c>
       <c r="B1124" s="2" t="s">
+        <v>6846</v>
+      </c>
+      <c r="C1124" s="2" t="s">
         <v>6847</v>
       </c>
-      <c r="C1124" s="2" t="s">
+      <c r="D1124" s="2" t="s">
         <v>6848</v>
       </c>
-      <c r="D1124" s="2" t="s">
+      <c r="E1124" s="2" t="s">
         <v>6849</v>
       </c>
-      <c r="E1124" s="2" t="s">
-        <v>6850</v>
-      </c>
       <c r="F1124" s="2" t="s">
-        <v>6873</v>
+        <v>6872</v>
       </c>
       <c r="G1124" s="3">
         <v>4</v>
@@ -54809,7 +54810,7 @@
         <v>1130</v>
       </c>
       <c r="B1131" s="2" t="s">
-        <v>6821</v>
+        <v>6820</v>
       </c>
       <c r="C1131" s="2" t="s">
         <v>5361</v>
@@ -54818,10 +54819,10 @@
         <v>5362</v>
       </c>
       <c r="E1131" s="2" t="s">
+        <v>6821</v>
+      </c>
+      <c r="F1131" s="2" t="s">
         <v>6822</v>
-      </c>
-      <c r="F1131" s="2" t="s">
-        <v>6823</v>
       </c>
       <c r="G1131" s="3">
         <v>1</v>
@@ -54838,19 +54839,19 @@
         <v>1131</v>
       </c>
       <c r="B1132" s="2" t="s">
+        <v>6824</v>
+      </c>
+      <c r="C1132" s="5" t="s">
         <v>6825</v>
       </c>
-      <c r="C1132" s="5" t="s">
+      <c r="D1132" s="2" t="s">
         <v>6826</v>
       </c>
-      <c r="D1132" s="2" t="s">
+      <c r="E1132" s="2" t="s">
         <v>6827</v>
       </c>
-      <c r="E1132" s="2" t="s">
+      <c r="F1132" s="2" t="s">
         <v>6828</v>
-      </c>
-      <c r="F1132" s="2" t="s">
-        <v>6829</v>
       </c>
       <c r="G1132" s="3">
         <v>3</v>
@@ -54867,19 +54868,19 @@
         <v>1132</v>
       </c>
       <c r="B1133" s="2" t="s">
+        <v>6831</v>
+      </c>
+      <c r="C1133" s="2" t="s">
         <v>6832</v>
       </c>
-      <c r="C1133" s="2" t="s">
+      <c r="D1133" s="2" t="s">
         <v>6833</v>
       </c>
-      <c r="D1133" s="2" t="s">
+      <c r="E1133" s="2" t="s">
         <v>6834</v>
       </c>
-      <c r="E1133" s="2" t="s">
+      <c r="F1133" s="2" t="s">
         <v>6835</v>
-      </c>
-      <c r="F1133" s="2" t="s">
-        <v>6836</v>
       </c>
       <c r="G1133" s="3">
         <v>2</v>
@@ -54896,7 +54897,7 @@
         <v>1133</v>
       </c>
       <c r="B1134" s="2" t="s">
-        <v>6824</v>
+        <v>6823</v>
       </c>
       <c r="C1134" s="2" t="s">
         <v>5364</v>
@@ -54905,10 +54906,10 @@
         <v>5365</v>
       </c>
       <c r="E1134" s="2" t="s">
+        <v>6829</v>
+      </c>
+      <c r="F1134" s="2" t="s">
         <v>6830</v>
-      </c>
-      <c r="F1134" s="2" t="s">
-        <v>6831</v>
       </c>
       <c r="G1134" s="3">
         <v>1</v>
@@ -56268,10 +56269,10 @@
         <v>1181</v>
       </c>
       <c r="B1182" s="2" t="s">
+        <v>6609</v>
+      </c>
+      <c r="C1182" s="2" t="s">
         <v>6610</v>
-      </c>
-      <c r="C1182" s="2" t="s">
-        <v>6611</v>
       </c>
       <c r="D1182" s="2" t="s">
         <v>5586</v>
@@ -56280,7 +56281,7 @@
         <v>1748</v>
       </c>
       <c r="F1182" s="2" t="s">
-        <v>6612</v>
+        <v>6611</v>
       </c>
       <c r="G1182" s="3">
         <v>4</v>
@@ -56326,7 +56327,7 @@
         <v>1183</v>
       </c>
       <c r="B1184" s="2" t="s">
-        <v>6938</v>
+        <v>6937</v>
       </c>
       <c r="C1184" s="2" t="s">
         <v>4172</v>
@@ -56355,7 +56356,7 @@
         <v>1184</v>
       </c>
       <c r="B1185" s="2" t="s">
-        <v>6710</v>
+        <v>6709</v>
       </c>
       <c r="C1185" s="2" t="s">
         <v>5594</v>
@@ -56367,7 +56368,7 @@
         <v>4174</v>
       </c>
       <c r="F1185" s="4" t="s">
-        <v>6711</v>
+        <v>6710</v>
       </c>
       <c r="G1185" s="3">
         <v>1</v>
@@ -56384,7 +56385,7 @@
         <v>1185</v>
       </c>
       <c r="B1186" s="2" t="s">
-        <v>6688</v>
+        <v>6687</v>
       </c>
       <c r="C1186" s="2" t="s">
         <v>4173</v>
@@ -56396,7 +56397,7 @@
         <v>5597</v>
       </c>
       <c r="F1186" s="4" t="s">
-        <v>6712</v>
+        <v>6711</v>
       </c>
       <c r="G1186" s="3">
         <v>2</v>
@@ -56761,7 +56762,7 @@
         <v>1198</v>
       </c>
       <c r="B1199" s="2" t="s">
-        <v>6893</v>
+        <v>6892</v>
       </c>
       <c r="C1199" s="2" t="s">
         <v>5636</v>
@@ -56790,7 +56791,7 @@
         <v>1199</v>
       </c>
       <c r="B1200" s="2" t="s">
-        <v>6894</v>
+        <v>6893</v>
       </c>
       <c r="C1200" s="2" t="s">
         <v>4213</v>
@@ -56802,7 +56803,7 @@
         <v>4215</v>
       </c>
       <c r="F1200" s="2" t="s">
-        <v>6908</v>
+        <v>6907</v>
       </c>
       <c r="G1200" s="3">
         <v>1</v>
@@ -57022,7 +57023,7 @@
         <v>1207</v>
       </c>
       <c r="B1208" s="2" t="s">
-        <v>6702</v>
+        <v>6701</v>
       </c>
       <c r="C1208" s="2" t="s">
         <v>4173</v>
@@ -57051,7 +57052,7 @@
         <v>1208</v>
       </c>
       <c r="B1209" s="2" t="s">
-        <v>6703</v>
+        <v>6702</v>
       </c>
       <c r="C1209" s="2" t="s">
         <v>4173</v>
@@ -57167,7 +57168,7 @@
         <v>1212</v>
       </c>
       <c r="B1213" s="2" t="s">
-        <v>6663</v>
+        <v>6662</v>
       </c>
       <c r="C1213" s="2" t="s">
         <v>5670</v>
@@ -57208,13 +57209,13 @@
         <v>2956</v>
       </c>
       <c r="F1214" s="2" t="s">
-        <v>5677</v>
+        <v>7018</v>
       </c>
       <c r="G1214" s="3">
         <v>1</v>
       </c>
       <c r="H1214" s="2" t="s">
-        <v>5678</v>
+        <v>5677</v>
       </c>
       <c r="I1214" s="2" t="s">
         <v>15</v>
@@ -57225,25 +57226,25 @@
         <v>1214</v>
       </c>
       <c r="B1215" s="2" t="s">
+        <v>5678</v>
+      </c>
+      <c r="C1215" s="2" t="s">
         <v>5679</v>
       </c>
-      <c r="C1215" s="2" t="s">
+      <c r="D1215" s="2" t="s">
+        <v>6660</v>
+      </c>
+      <c r="E1215" s="2" t="s">
         <v>5680</v>
       </c>
-      <c r="D1215" s="2" t="s">
+      <c r="F1215" s="2" t="s">
         <v>6661</v>
-      </c>
-      <c r="E1215" s="2" t="s">
-        <v>5681</v>
-      </c>
-      <c r="F1215" s="2" t="s">
-        <v>6662</v>
       </c>
       <c r="G1215" s="3">
         <v>4</v>
       </c>
       <c r="H1215" s="2" t="s">
-        <v>5682</v>
+        <v>5681</v>
       </c>
       <c r="I1215" s="2" t="s">
         <v>15</v>
@@ -57254,25 +57255,25 @@
         <v>1215</v>
       </c>
       <c r="B1216" s="2" t="s">
-        <v>5683</v>
+        <v>5682</v>
       </c>
       <c r="C1216" s="2" t="s">
         <v>3206</v>
       </c>
       <c r="D1216" s="2" t="s">
-        <v>5684</v>
+        <v>5683</v>
       </c>
       <c r="E1216" s="2" t="s">
         <v>1472</v>
       </c>
       <c r="F1216" s="2" t="s">
-        <v>5685</v>
+        <v>5684</v>
       </c>
       <c r="G1216" s="3">
         <v>2</v>
       </c>
       <c r="H1216" s="2" t="s">
-        <v>5686</v>
+        <v>5685</v>
       </c>
       <c r="I1216" s="2" t="s">
         <v>15</v>
@@ -57283,7 +57284,7 @@
         <v>1216</v>
       </c>
       <c r="B1217" s="2" t="s">
-        <v>5687</v>
+        <v>5686</v>
       </c>
       <c r="C1217" s="2" t="s">
         <v>3206</v>
@@ -57301,7 +57302,7 @@
         <v>4</v>
       </c>
       <c r="H1217" s="2" t="s">
-        <v>5688</v>
+        <v>5687</v>
       </c>
       <c r="I1217" s="2" t="s">
         <v>15</v>
@@ -57312,25 +57313,25 @@
         <v>1217</v>
       </c>
       <c r="B1218" s="2" t="s">
+        <v>5688</v>
+      </c>
+      <c r="C1218" s="2" t="s">
         <v>5689</v>
       </c>
-      <c r="C1218" s="2" t="s">
+      <c r="D1218" s="2" t="s">
         <v>5690</v>
       </c>
-      <c r="D1218" s="2" t="s">
+      <c r="E1218" s="2" t="s">
         <v>5691</v>
       </c>
-      <c r="E1218" s="2" t="s">
+      <c r="F1218" s="2" t="s">
         <v>5692</v>
-      </c>
-      <c r="F1218" s="2" t="s">
-        <v>5693</v>
       </c>
       <c r="G1218" s="3">
         <v>2</v>
       </c>
       <c r="H1218" s="2" t="s">
-        <v>5694</v>
+        <v>5693</v>
       </c>
       <c r="I1218" s="2" t="s">
         <v>15</v>
@@ -57341,25 +57342,25 @@
         <v>1218</v>
       </c>
       <c r="B1219" s="2" t="s">
+        <v>5694</v>
+      </c>
+      <c r="C1219" s="2" t="s">
         <v>5695</v>
       </c>
-      <c r="C1219" s="2" t="s">
+      <c r="D1219" s="2" t="s">
         <v>5696</v>
       </c>
-      <c r="D1219" s="2" t="s">
+      <c r="E1219" s="2" t="s">
         <v>5697</v>
       </c>
-      <c r="E1219" s="2" t="s">
+      <c r="F1219" s="2" t="s">
         <v>5698</v>
-      </c>
-      <c r="F1219" s="2" t="s">
-        <v>5699</v>
       </c>
       <c r="G1219" s="3">
         <v>2</v>
       </c>
       <c r="H1219" s="2" t="s">
-        <v>5700</v>
+        <v>5699</v>
       </c>
       <c r="I1219" s="2" t="s">
         <v>15</v>
@@ -57370,10 +57371,10 @@
         <v>1219</v>
       </c>
       <c r="B1220" s="2" t="s">
+        <v>5700</v>
+      </c>
+      <c r="C1220" s="2" t="s">
         <v>5701</v>
-      </c>
-      <c r="C1220" s="2" t="s">
-        <v>5702</v>
       </c>
       <c r="D1220" s="2" t="s">
         <v>5212</v>
@@ -57382,13 +57383,13 @@
         <v>5194</v>
       </c>
       <c r="F1220" s="2" t="s">
-        <v>5703</v>
+        <v>5702</v>
       </c>
       <c r="G1220" s="3">
         <v>3</v>
       </c>
       <c r="H1220" s="2" t="s">
-        <v>5704</v>
+        <v>5703</v>
       </c>
       <c r="I1220" s="2" t="s">
         <v>15</v>
@@ -57399,25 +57400,25 @@
         <v>1220</v>
       </c>
       <c r="B1221" s="2" t="s">
+        <v>5704</v>
+      </c>
+      <c r="C1221" s="2" t="s">
         <v>5705</v>
       </c>
-      <c r="C1221" s="2" t="s">
+      <c r="D1221" s="2" t="s">
         <v>5706</v>
       </c>
-      <c r="D1221" s="2" t="s">
+      <c r="E1221" s="2" t="s">
         <v>5707</v>
       </c>
-      <c r="E1221" s="2" t="s">
+      <c r="F1221" s="2" t="s">
         <v>5708</v>
-      </c>
-      <c r="F1221" s="2" t="s">
-        <v>5709</v>
       </c>
       <c r="G1221" s="3">
         <v>1</v>
       </c>
       <c r="H1221" s="2" t="s">
-        <v>5710</v>
+        <v>5709</v>
       </c>
       <c r="I1221" s="2" t="s">
         <v>15</v>
@@ -57428,25 +57429,25 @@
         <v>1221</v>
       </c>
       <c r="B1222" s="2" t="s">
+        <v>5710</v>
+      </c>
+      <c r="C1222" s="2" t="s">
         <v>5711</v>
-      </c>
-      <c r="C1222" s="2" t="s">
-        <v>5712</v>
       </c>
       <c r="D1222" s="2" t="s">
         <v>4198</v>
       </c>
       <c r="E1222" s="2" t="s">
+        <v>5712</v>
+      </c>
+      <c r="F1222" s="2" t="s">
         <v>5713</v>
-      </c>
-      <c r="F1222" s="2" t="s">
-        <v>5714</v>
       </c>
       <c r="G1222" s="3">
         <v>1</v>
       </c>
       <c r="H1222" s="2" t="s">
-        <v>5715</v>
+        <v>5714</v>
       </c>
       <c r="I1222" s="2" t="s">
         <v>15</v>
@@ -57457,25 +57458,25 @@
         <v>1222</v>
       </c>
       <c r="B1223" s="2" t="s">
+        <v>5715</v>
+      </c>
+      <c r="C1223" s="2" t="s">
         <v>5716</v>
       </c>
-      <c r="C1223" s="2" t="s">
+      <c r="D1223" s="2" t="s">
         <v>5717</v>
       </c>
-      <c r="D1223" s="2" t="s">
+      <c r="E1223" s="2" t="s">
         <v>5718</v>
       </c>
-      <c r="E1223" s="2" t="s">
+      <c r="F1223" s="2" t="s">
         <v>5719</v>
-      </c>
-      <c r="F1223" s="2" t="s">
-        <v>5720</v>
       </c>
       <c r="G1223" s="3">
         <v>4</v>
       </c>
       <c r="H1223" s="2" t="s">
-        <v>5721</v>
+        <v>5720</v>
       </c>
       <c r="I1223" s="2" t="s">
         <v>15</v>
@@ -57486,13 +57487,13 @@
         <v>1223</v>
       </c>
       <c r="B1224" s="2" t="s">
+        <v>5721</v>
+      </c>
+      <c r="C1224" s="2" t="s">
         <v>5722</v>
       </c>
-      <c r="C1224" s="2" t="s">
+      <c r="D1224" s="2" t="s">
         <v>5723</v>
-      </c>
-      <c r="D1224" s="2" t="s">
-        <v>5724</v>
       </c>
       <c r="E1224" s="2" t="s">
         <v>4469</v>
@@ -57504,7 +57505,7 @@
         <v>1</v>
       </c>
       <c r="H1224" s="2" t="s">
-        <v>5725</v>
+        <v>5724</v>
       </c>
       <c r="I1224" s="2" t="s">
         <v>15</v>
@@ -57515,10 +57516,10 @@
         <v>1224</v>
       </c>
       <c r="B1225" s="2" t="s">
+        <v>5725</v>
+      </c>
+      <c r="C1225" s="2" t="s">
         <v>5726</v>
-      </c>
-      <c r="C1225" s="2" t="s">
-        <v>5727</v>
       </c>
       <c r="D1225" s="2" t="s">
         <v>5010</v>
@@ -57527,13 +57528,13 @@
         <v>5251</v>
       </c>
       <c r="F1225" s="2" t="s">
-        <v>5728</v>
+        <v>5727</v>
       </c>
       <c r="G1225" s="3">
         <v>1</v>
       </c>
       <c r="H1225" s="2" t="s">
-        <v>5729</v>
+        <v>5728</v>
       </c>
       <c r="I1225" s="2" t="s">
         <v>15</v>
@@ -57544,19 +57545,19 @@
         <v>1225</v>
       </c>
       <c r="B1226" s="2" t="s">
-        <v>5730</v>
+        <v>5729</v>
       </c>
       <c r="C1226" s="2" t="s">
         <v>4007</v>
       </c>
       <c r="D1226" s="2" t="s">
-        <v>5731</v>
+        <v>5730</v>
       </c>
       <c r="E1226" s="2" t="s">
         <v>4134</v>
       </c>
       <c r="F1226" s="2" t="s">
-        <v>5732</v>
+        <v>5731</v>
       </c>
       <c r="G1226" s="3">
         <v>1</v>
@@ -57573,25 +57574,25 @@
         <v>1226</v>
       </c>
       <c r="B1227" s="2" t="s">
+        <v>5732</v>
+      </c>
+      <c r="C1227" s="2" t="s">
         <v>5733</v>
       </c>
-      <c r="C1227" s="2" t="s">
+      <c r="D1227" s="2" t="s">
         <v>5734</v>
       </c>
-      <c r="D1227" s="2" t="s">
+      <c r="E1227" s="2" t="s">
         <v>5735</v>
       </c>
-      <c r="E1227" s="2" t="s">
+      <c r="F1227" s="2" t="s">
         <v>5736</v>
-      </c>
-      <c r="F1227" s="2" t="s">
-        <v>5737</v>
       </c>
       <c r="G1227" s="3">
         <v>4</v>
       </c>
       <c r="H1227" s="2" t="s">
-        <v>5738</v>
+        <v>5737</v>
       </c>
       <c r="I1227" s="2" t="s">
         <v>15</v>
@@ -57602,25 +57603,25 @@
         <v>1227</v>
       </c>
       <c r="B1228" s="2" t="s">
+        <v>6506</v>
+      </c>
+      <c r="C1228" s="2" t="s">
+        <v>5738</v>
+      </c>
+      <c r="D1228" s="2" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1228" s="2" t="s">
         <v>6507</v>
       </c>
-      <c r="C1228" s="2" t="s">
-        <v>5739</v>
-      </c>
-      <c r="D1228" s="2" t="s">
-        <v>5740</v>
-      </c>
-      <c r="E1228" s="2" t="s">
+      <c r="F1228" s="2" t="s">
         <v>6508</v>
-      </c>
-      <c r="F1228" s="2" t="s">
-        <v>6509</v>
       </c>
       <c r="G1228" s="3">
         <v>4</v>
       </c>
       <c r="H1228" s="2" t="s">
-        <v>5742</v>
+        <v>5741</v>
       </c>
       <c r="I1228" s="2" t="s">
         <v>15</v>
@@ -57631,7 +57632,7 @@
         <v>1228</v>
       </c>
       <c r="B1229" s="2" t="s">
-        <v>5743</v>
+        <v>5742</v>
       </c>
       <c r="C1229" s="2" t="s">
         <v>5035</v>
@@ -57643,13 +57644,13 @@
         <v>5037</v>
       </c>
       <c r="F1229" s="2" t="s">
-        <v>5744</v>
+        <v>5743</v>
       </c>
       <c r="G1229" s="3">
         <v>3</v>
       </c>
       <c r="H1229" s="2" t="s">
-        <v>5745</v>
+        <v>5744</v>
       </c>
       <c r="I1229" s="2" t="s">
         <v>151</v>
@@ -57660,7 +57661,7 @@
         <v>1229</v>
       </c>
       <c r="B1230" s="2" t="s">
-        <v>5746</v>
+        <v>5745</v>
       </c>
       <c r="C1230" s="2" t="s">
         <v>5035</v>
@@ -57678,7 +57679,7 @@
         <v>4</v>
       </c>
       <c r="H1230" s="2" t="s">
-        <v>5747</v>
+        <v>5746</v>
       </c>
       <c r="I1230" s="2" t="s">
         <v>15</v>
@@ -57689,10 +57690,10 @@
         <v>1230</v>
       </c>
       <c r="B1231" s="2" t="s">
+        <v>5747</v>
+      </c>
+      <c r="C1231" s="2" t="s">
         <v>5748</v>
-      </c>
-      <c r="C1231" s="2" t="s">
-        <v>5749</v>
       </c>
       <c r="D1231" s="2" t="s">
         <v>4622</v>
@@ -57705,7 +57706,7 @@
         <v>3</v>
       </c>
       <c r="H1231" s="2" t="s">
-        <v>5750</v>
+        <v>5749</v>
       </c>
       <c r="I1231" s="2" t="s">
         <v>15</v>
@@ -57716,25 +57717,25 @@
         <v>1231</v>
       </c>
       <c r="B1232" s="2" t="s">
+        <v>5750</v>
+      </c>
+      <c r="C1232" s="2" t="s">
         <v>5751</v>
       </c>
-      <c r="C1232" s="2" t="s">
+      <c r="D1232" s="2" t="s">
         <v>5752</v>
       </c>
-      <c r="D1232" s="2" t="s">
+      <c r="E1232" s="2" t="s">
         <v>5753</v>
       </c>
-      <c r="E1232" s="2" t="s">
+      <c r="F1232" s="2" t="s">
         <v>5754</v>
-      </c>
-      <c r="F1232" s="2" t="s">
-        <v>5755</v>
       </c>
       <c r="G1232" s="3">
         <v>3</v>
       </c>
       <c r="H1232" s="2" t="s">
-        <v>5756</v>
+        <v>5755</v>
       </c>
       <c r="I1232" s="2" t="s">
         <v>15</v>
@@ -57745,25 +57746,25 @@
         <v>1232</v>
       </c>
       <c r="B1233" s="2" t="s">
+        <v>6678</v>
+      </c>
+      <c r="C1233" s="2" t="s">
+        <v>5756</v>
+      </c>
+      <c r="D1233" s="2" t="s">
         <v>6679</v>
-      </c>
-      <c r="C1233" s="2" t="s">
-        <v>5757</v>
-      </c>
-      <c r="D1233" s="2" t="s">
-        <v>6680</v>
       </c>
       <c r="E1233" s="2" t="s">
         <v>3785</v>
       </c>
       <c r="F1233" s="2" t="s">
-        <v>5758</v>
+        <v>5757</v>
       </c>
       <c r="G1233" s="3">
         <v>2</v>
       </c>
       <c r="H1233" s="2" t="s">
-        <v>5759</v>
+        <v>5758</v>
       </c>
       <c r="I1233" s="2" t="s">
         <v>15</v>
@@ -57774,25 +57775,25 @@
         <v>1233</v>
       </c>
       <c r="B1234" s="2" t="s">
-        <v>5760</v>
+        <v>5759</v>
       </c>
       <c r="C1234" s="2" t="s">
         <v>5002</v>
       </c>
       <c r="D1234" s="2" t="s">
-        <v>5761</v>
+        <v>5760</v>
       </c>
       <c r="E1234" s="2" t="s">
         <v>1500</v>
       </c>
       <c r="F1234" s="2" t="s">
-        <v>5762</v>
+        <v>5761</v>
       </c>
       <c r="G1234" s="3">
         <v>4</v>
       </c>
       <c r="H1234" s="2" t="s">
-        <v>5763</v>
+        <v>5762</v>
       </c>
       <c r="I1234" s="2" t="s">
         <v>151</v>
@@ -57803,25 +57804,25 @@
         <v>1234</v>
       </c>
       <c r="B1235" s="2" t="s">
+        <v>5763</v>
+      </c>
+      <c r="C1235" s="2" t="s">
         <v>5764</v>
       </c>
-      <c r="C1235" s="2" t="s">
+      <c r="D1235" s="2" t="s">
         <v>5765</v>
-      </c>
-      <c r="D1235" s="2" t="s">
-        <v>5766</v>
       </c>
       <c r="E1235" s="2" t="s">
         <v>5563</v>
       </c>
       <c r="F1235" s="2" t="s">
-        <v>5767</v>
+        <v>5766</v>
       </c>
       <c r="G1235" s="3">
         <v>1</v>
       </c>
       <c r="H1235" s="2" t="s">
-        <v>5768</v>
+        <v>5767</v>
       </c>
       <c r="I1235" s="2" t="s">
         <v>15</v>
@@ -57832,25 +57833,25 @@
         <v>1235</v>
       </c>
       <c r="B1236" s="2" t="s">
+        <v>5768</v>
+      </c>
+      <c r="C1236" s="2" t="s">
         <v>5769</v>
       </c>
-      <c r="C1236" s="2" t="s">
+      <c r="D1236" s="2" t="s">
         <v>5770</v>
-      </c>
-      <c r="D1236" s="2" t="s">
-        <v>5771</v>
       </c>
       <c r="E1236" s="2" t="s">
         <v>5215</v>
       </c>
       <c r="F1236" s="2" t="s">
-        <v>5772</v>
+        <v>5771</v>
       </c>
       <c r="G1236" s="3">
         <v>1</v>
       </c>
       <c r="H1236" s="2" t="s">
-        <v>5773</v>
+        <v>5772</v>
       </c>
       <c r="I1236" s="2" t="s">
         <v>15</v>
@@ -57861,25 +57862,25 @@
         <v>1236</v>
       </c>
       <c r="B1237" s="2" t="s">
+        <v>6969</v>
+      </c>
+      <c r="C1237" s="2" t="s">
         <v>6970</v>
       </c>
-      <c r="C1237" s="2" t="s">
+      <c r="D1237" s="2" t="s">
+        <v>5773</v>
+      </c>
+      <c r="E1237" s="2" t="s">
         <v>6971</v>
       </c>
-      <c r="D1237" s="2" t="s">
+      <c r="F1237" s="2" t="s">
         <v>5774</v>
-      </c>
-      <c r="E1237" s="2" t="s">
-        <v>6972</v>
-      </c>
-      <c r="F1237" s="2" t="s">
-        <v>5775</v>
       </c>
       <c r="G1237" s="3">
         <v>3</v>
       </c>
       <c r="H1237" s="2" t="s">
-        <v>5776</v>
+        <v>5775</v>
       </c>
       <c r="I1237" s="2" t="s">
         <v>151</v>
@@ -57890,25 +57891,25 @@
         <v>1237</v>
       </c>
       <c r="B1238" s="2" t="s">
+        <v>5776</v>
+      </c>
+      <c r="C1238" s="2" t="s">
         <v>5777</v>
-      </c>
-      <c r="C1238" s="2" t="s">
-        <v>5778</v>
       </c>
       <c r="D1238" s="2" t="s">
         <v>5111</v>
       </c>
       <c r="E1238" s="2" t="s">
-        <v>5741</v>
+        <v>5740</v>
       </c>
       <c r="F1238" s="2" t="s">
-        <v>5779</v>
+        <v>5778</v>
       </c>
       <c r="G1238" s="3">
         <v>3</v>
       </c>
       <c r="H1238" s="2" t="s">
-        <v>5780</v>
+        <v>5779</v>
       </c>
       <c r="I1238" s="2" t="s">
         <v>15</v>
@@ -57919,16 +57920,16 @@
         <v>1238</v>
       </c>
       <c r="B1239" s="2" t="s">
-        <v>5781</v>
+        <v>5780</v>
       </c>
       <c r="C1239" s="2" t="s">
+        <v>5738</v>
+      </c>
+      <c r="D1239" s="2" t="s">
         <v>5739</v>
       </c>
-      <c r="D1239" s="2" t="s">
+      <c r="E1239" s="2" t="s">
         <v>5740</v>
-      </c>
-      <c r="E1239" s="2" t="s">
-        <v>5741</v>
       </c>
       <c r="F1239" s="2"/>
       <c r="G1239" s="3">
@@ -57946,25 +57947,25 @@
         <v>1239</v>
       </c>
       <c r="B1240" s="2" t="s">
+        <v>5781</v>
+      </c>
+      <c r="C1240" s="2" t="s">
         <v>5782</v>
       </c>
-      <c r="C1240" s="2" t="s">
+      <c r="D1240" s="2" t="s">
         <v>5783</v>
       </c>
-      <c r="D1240" s="2" t="s">
+      <c r="E1240" s="2" t="s">
         <v>5784</v>
       </c>
-      <c r="E1240" s="2" t="s">
+      <c r="F1240" s="2" t="s">
         <v>5785</v>
-      </c>
-      <c r="F1240" s="2" t="s">
-        <v>5786</v>
       </c>
       <c r="G1240" s="3">
         <v>1</v>
       </c>
       <c r="H1240" s="2" t="s">
-        <v>5787</v>
+        <v>5786</v>
       </c>
       <c r="I1240" s="2" t="s">
         <v>15</v>
@@ -57975,25 +57976,25 @@
         <v>1240</v>
       </c>
       <c r="B1241" s="2" t="s">
+        <v>5787</v>
+      </c>
+      <c r="C1241" s="2" t="s">
+        <v>6569</v>
+      </c>
+      <c r="D1241" s="2" t="s">
+        <v>6570</v>
+      </c>
+      <c r="E1241" s="2" t="s">
+        <v>5718</v>
+      </c>
+      <c r="F1241" s="2" t="s">
         <v>5788</v>
-      </c>
-      <c r="C1241" s="2" t="s">
-        <v>6570</v>
-      </c>
-      <c r="D1241" s="2" t="s">
-        <v>6571</v>
-      </c>
-      <c r="E1241" s="2" t="s">
-        <v>5719</v>
-      </c>
-      <c r="F1241" s="2" t="s">
-        <v>5789</v>
       </c>
       <c r="G1241" s="3">
         <v>2</v>
       </c>
       <c r="H1241" s="2" t="s">
-        <v>5790</v>
+        <v>5789</v>
       </c>
       <c r="I1241" s="2" t="s">
         <v>15</v>
@@ -58004,7 +58005,7 @@
         <v>1241</v>
       </c>
       <c r="B1242" s="2" t="s">
-        <v>5791</v>
+        <v>5790</v>
       </c>
       <c r="C1242" s="2" t="s">
         <v>5037</v>
@@ -58016,13 +58017,13 @@
         <v>5036</v>
       </c>
       <c r="F1242" s="2" t="s">
-        <v>5744</v>
+        <v>5743</v>
       </c>
       <c r="G1242" s="3">
         <v>1</v>
       </c>
       <c r="H1242" s="2" t="s">
-        <v>5792</v>
+        <v>5791</v>
       </c>
       <c r="I1242" s="2" t="s">
         <v>15</v>
@@ -58033,25 +58034,25 @@
         <v>1242</v>
       </c>
       <c r="B1243" s="2" t="s">
+        <v>5792</v>
+      </c>
+      <c r="C1243" s="2" t="s">
         <v>5793</v>
       </c>
-      <c r="C1243" s="2" t="s">
+      <c r="D1243" s="2" t="s">
         <v>5794</v>
       </c>
-      <c r="D1243" s="2" t="s">
+      <c r="E1243" s="2" t="s">
         <v>5795</v>
       </c>
-      <c r="E1243" s="2" t="s">
+      <c r="F1243" s="2" t="s">
         <v>5796</v>
-      </c>
-      <c r="F1243" s="2" t="s">
-        <v>5797</v>
       </c>
       <c r="G1243" s="3">
         <v>4</v>
       </c>
       <c r="H1243" s="2" t="s">
-        <v>5798</v>
+        <v>5797</v>
       </c>
       <c r="I1243" s="2" t="s">
         <v>15</v>
@@ -58062,25 +58063,25 @@
         <v>1243</v>
       </c>
       <c r="B1244" s="2" t="s">
+        <v>5798</v>
+      </c>
+      <c r="C1244" s="2" t="s">
         <v>5799</v>
       </c>
-      <c r="C1244" s="2" t="s">
+      <c r="D1244" s="2" t="s">
         <v>5800</v>
-      </c>
-      <c r="D1244" s="2" t="s">
-        <v>5801</v>
       </c>
       <c r="E1244" s="2" t="s">
         <v>4146</v>
       </c>
       <c r="F1244" s="2" t="s">
-        <v>5802</v>
+        <v>5801</v>
       </c>
       <c r="G1244" s="3">
         <v>4</v>
       </c>
       <c r="H1244" s="2" t="s">
-        <v>5803</v>
+        <v>5802</v>
       </c>
       <c r="I1244" s="2" t="s">
         <v>15</v>
@@ -58091,25 +58092,25 @@
         <v>1244</v>
       </c>
       <c r="B1245" s="2" t="s">
+        <v>5803</v>
+      </c>
+      <c r="C1245" s="2" t="s">
         <v>5804</v>
       </c>
-      <c r="C1245" s="2" t="s">
+      <c r="D1245" s="2" t="s">
         <v>5805</v>
       </c>
-      <c r="D1245" s="2" t="s">
+      <c r="E1245" s="2" t="s">
         <v>5806</v>
       </c>
-      <c r="E1245" s="2" t="s">
+      <c r="F1245" s="2" t="s">
         <v>5807</v>
-      </c>
-      <c r="F1245" s="2" t="s">
-        <v>5808</v>
       </c>
       <c r="G1245" s="3">
         <v>2</v>
       </c>
       <c r="H1245" s="2" t="s">
-        <v>5809</v>
+        <v>5808</v>
       </c>
       <c r="I1245" s="2" t="s">
         <v>151</v>
@@ -58120,10 +58121,10 @@
         <v>1245</v>
       </c>
       <c r="B1246" s="2" t="s">
-        <v>6955</v>
+        <v>6954</v>
       </c>
       <c r="C1246" s="2" t="s">
-        <v>5810</v>
+        <v>5809</v>
       </c>
       <c r="D1246" s="2" t="s">
         <v>5392</v>
@@ -58132,13 +58133,13 @@
         <v>1092</v>
       </c>
       <c r="F1246" s="2" t="s">
-        <v>5811</v>
+        <v>5810</v>
       </c>
       <c r="G1246" s="3">
         <v>4</v>
       </c>
       <c r="H1246" s="2" t="s">
-        <v>5812</v>
+        <v>5811</v>
       </c>
       <c r="I1246" s="2" t="s">
         <v>15</v>
@@ -58149,25 +58150,25 @@
         <v>1246</v>
       </c>
       <c r="B1247" s="2" t="s">
+        <v>5812</v>
+      </c>
+      <c r="C1247" s="2" t="s">
         <v>5813</v>
       </c>
-      <c r="C1247" s="2" t="s">
+      <c r="D1247" s="2" t="s">
         <v>5814</v>
       </c>
-      <c r="D1247" s="2" t="s">
+      <c r="E1247" s="2" t="s">
         <v>5815</v>
       </c>
-      <c r="E1247" s="2" t="s">
+      <c r="F1247" s="2" t="s">
         <v>5816</v>
-      </c>
-      <c r="F1247" s="2" t="s">
-        <v>5817</v>
       </c>
       <c r="G1247" s="3">
         <v>4</v>
       </c>
       <c r="H1247" s="2" t="s">
-        <v>5818</v>
+        <v>5817</v>
       </c>
       <c r="I1247" s="2" t="s">
         <v>15</v>
@@ -58178,19 +58179,19 @@
         <v>1247</v>
       </c>
       <c r="B1248" s="2" t="s">
-        <v>5819</v>
+        <v>5818</v>
       </c>
       <c r="C1248" s="2" t="s">
         <v>4007</v>
       </c>
       <c r="D1248" s="2" t="s">
+        <v>5730</v>
+      </c>
+      <c r="E1248" s="2" t="s">
+        <v>5819</v>
+      </c>
+      <c r="F1248" s="2" t="s">
         <v>5731</v>
-      </c>
-      <c r="E1248" s="2" t="s">
-        <v>5820</v>
-      </c>
-      <c r="F1248" s="2" t="s">
-        <v>5732</v>
       </c>
       <c r="G1248" s="3">
         <v>1</v>
@@ -58207,25 +58208,25 @@
         <v>1248</v>
       </c>
       <c r="B1249" s="2" t="s">
+        <v>5820</v>
+      </c>
+      <c r="C1249" s="2" t="s">
         <v>5821</v>
       </c>
-      <c r="C1249" s="2" t="s">
+      <c r="D1249" s="2" t="s">
         <v>5822</v>
       </c>
-      <c r="D1249" s="2" t="s">
+      <c r="E1249" s="2" t="s">
         <v>5823</v>
       </c>
-      <c r="E1249" s="2" t="s">
+      <c r="F1249" s="2" t="s">
         <v>5824</v>
-      </c>
-      <c r="F1249" s="2" t="s">
-        <v>5825</v>
       </c>
       <c r="G1249" s="3">
         <v>3</v>
       </c>
       <c r="H1249" s="2" t="s">
-        <v>5826</v>
+        <v>5825</v>
       </c>
       <c r="I1249" s="2" t="s">
         <v>15</v>
@@ -58236,25 +58237,25 @@
         <v>1249</v>
       </c>
       <c r="B1250" s="2" t="s">
+        <v>5826</v>
+      </c>
+      <c r="C1250" s="2" t="s">
         <v>5827</v>
       </c>
-      <c r="C1250" s="2" t="s">
+      <c r="D1250" s="2" t="s">
         <v>5828</v>
       </c>
-      <c r="D1250" s="2" t="s">
+      <c r="E1250" s="2" t="s">
         <v>5829</v>
       </c>
-      <c r="E1250" s="2" t="s">
+      <c r="F1250" s="2" t="s">
         <v>5830</v>
-      </c>
-      <c r="F1250" s="2" t="s">
-        <v>5831</v>
       </c>
       <c r="G1250" s="3">
         <v>2</v>
       </c>
       <c r="H1250" s="2" t="s">
-        <v>5832</v>
+        <v>5831</v>
       </c>
       <c r="I1250" s="2" t="s">
         <v>15</v>
@@ -58265,25 +58266,25 @@
         <v>1250</v>
       </c>
       <c r="B1251" s="2" t="s">
+        <v>5832</v>
+      </c>
+      <c r="C1251" s="2" t="s">
         <v>5833</v>
       </c>
-      <c r="C1251" s="2" t="s">
+      <c r="D1251" s="2" t="s">
         <v>5834</v>
       </c>
-      <c r="D1251" s="2" t="s">
+      <c r="E1251" s="2" t="s">
         <v>5835</v>
       </c>
-      <c r="E1251" s="2" t="s">
+      <c r="F1251" s="2" t="s">
         <v>5836</v>
-      </c>
-      <c r="F1251" s="2" t="s">
-        <v>5837</v>
       </c>
       <c r="G1251" s="3">
         <v>4</v>
       </c>
       <c r="H1251" s="2" t="s">
-        <v>5838</v>
+        <v>5837</v>
       </c>
       <c r="I1251" s="2" t="s">
         <v>15</v>
@@ -58294,25 +58295,25 @@
         <v>1251</v>
       </c>
       <c r="B1252" s="2" t="s">
+        <v>5838</v>
+      </c>
+      <c r="C1252" s="2" t="s">
         <v>5839</v>
       </c>
-      <c r="C1252" s="2" t="s">
+      <c r="D1252" s="2" t="s">
         <v>5840</v>
       </c>
-      <c r="D1252" s="2" t="s">
+      <c r="E1252" s="2" t="s">
         <v>5841</v>
       </c>
-      <c r="E1252" s="2" t="s">
+      <c r="F1252" s="2" t="s">
         <v>5842</v>
-      </c>
-      <c r="F1252" s="2" t="s">
-        <v>5843</v>
       </c>
       <c r="G1252" s="3">
         <v>1</v>
       </c>
       <c r="H1252" s="2" t="s">
-        <v>5844</v>
+        <v>5843</v>
       </c>
       <c r="I1252" s="2" t="s">
         <v>15</v>
@@ -58323,25 +58324,25 @@
         <v>1252</v>
       </c>
       <c r="B1253" s="2" t="s">
+        <v>5844</v>
+      </c>
+      <c r="C1253" s="2" t="s">
         <v>5845</v>
       </c>
-      <c r="C1253" s="2" t="s">
+      <c r="D1253" s="2" t="s">
         <v>5846</v>
       </c>
-      <c r="D1253" s="2" t="s">
+      <c r="E1253" s="2" t="s">
         <v>5847</v>
       </c>
-      <c r="E1253" s="2" t="s">
+      <c r="F1253" s="2" t="s">
         <v>5848</v>
-      </c>
-      <c r="F1253" s="2" t="s">
-        <v>5849</v>
       </c>
       <c r="G1253" s="3">
         <v>2</v>
       </c>
       <c r="H1253" s="2" t="s">
-        <v>5850</v>
+        <v>5849</v>
       </c>
       <c r="I1253" s="2" t="s">
         <v>15</v>
@@ -58352,25 +58353,25 @@
         <v>1253</v>
       </c>
       <c r="B1254" s="2" t="s">
-        <v>5851</v>
+        <v>5850</v>
       </c>
       <c r="C1254" s="2" t="s">
         <v>4216</v>
       </c>
       <c r="D1254" s="2" t="s">
+        <v>5851</v>
+      </c>
+      <c r="E1254" s="2" t="s">
         <v>5852</v>
       </c>
-      <c r="E1254" s="2" t="s">
+      <c r="F1254" s="2" t="s">
         <v>5853</v>
-      </c>
-      <c r="F1254" s="2" t="s">
-        <v>5854</v>
       </c>
       <c r="G1254" s="3">
         <v>2</v>
       </c>
       <c r="H1254" s="2" t="s">
-        <v>5855</v>
+        <v>5854</v>
       </c>
       <c r="I1254" s="2" t="s">
         <v>158</v>
@@ -58381,25 +58382,25 @@
         <v>1254</v>
       </c>
       <c r="B1255" s="2" t="s">
+        <v>5855</v>
+      </c>
+      <c r="C1255" s="2" t="s">
         <v>5856</v>
       </c>
-      <c r="C1255" s="2" t="s">
+      <c r="D1255" s="2" t="s">
         <v>5857</v>
       </c>
-      <c r="D1255" s="2" t="s">
+      <c r="E1255" s="2" t="s">
         <v>5858</v>
       </c>
-      <c r="E1255" s="2" t="s">
+      <c r="F1255" s="2" t="s">
         <v>5859</v>
-      </c>
-      <c r="F1255" s="2" t="s">
-        <v>5860</v>
       </c>
       <c r="G1255" s="3">
         <v>2</v>
       </c>
       <c r="H1255" s="2" t="s">
-        <v>5861</v>
+        <v>5860</v>
       </c>
       <c r="I1255" s="2" t="s">
         <v>158</v>
@@ -58410,7 +58411,7 @@
         <v>1255</v>
       </c>
       <c r="B1256" s="2" t="s">
-        <v>5862</v>
+        <v>5861</v>
       </c>
       <c r="C1256" s="2" t="s">
         <v>496</v>
@@ -58428,7 +58429,7 @@
         <v>3</v>
       </c>
       <c r="H1256" s="2" t="s">
-        <v>5863</v>
+        <v>5862</v>
       </c>
       <c r="I1256" s="2" t="s">
         <v>158</v>
@@ -58439,25 +58440,25 @@
         <v>1256</v>
       </c>
       <c r="B1257" s="2" t="s">
+        <v>5863</v>
+      </c>
+      <c r="C1257" s="2" t="s">
         <v>5864</v>
       </c>
-      <c r="C1257" s="2" t="s">
+      <c r="D1257" s="2" t="s">
         <v>5865</v>
       </c>
-      <c r="D1257" s="2" t="s">
+      <c r="E1257" s="2" t="s">
         <v>5866</v>
       </c>
-      <c r="E1257" s="2" t="s">
+      <c r="F1257" s="2" t="s">
         <v>5867</v>
-      </c>
-      <c r="F1257" s="2" t="s">
-        <v>5868</v>
       </c>
       <c r="G1257" s="3">
         <v>3</v>
       </c>
       <c r="H1257" s="2" t="s">
-        <v>5869</v>
+        <v>5868</v>
       </c>
       <c r="I1257" s="2" t="s">
         <v>158</v>
@@ -58468,25 +58469,25 @@
         <v>1257</v>
       </c>
       <c r="B1258" s="2" t="s">
+        <v>5869</v>
+      </c>
+      <c r="C1258" s="2" t="s">
         <v>5870</v>
       </c>
-      <c r="C1258" s="2" t="s">
+      <c r="D1258" s="2" t="s">
         <v>5871</v>
       </c>
-      <c r="D1258" s="2" t="s">
+      <c r="E1258" s="2" t="s">
         <v>5872</v>
       </c>
-      <c r="E1258" s="2" t="s">
+      <c r="F1258" s="2" t="s">
         <v>5873</v>
-      </c>
-      <c r="F1258" s="2" t="s">
-        <v>5874</v>
       </c>
       <c r="G1258" s="3">
         <v>4</v>
       </c>
       <c r="H1258" s="2" t="s">
-        <v>5875</v>
+        <v>5874</v>
       </c>
       <c r="I1258" s="2" t="s">
         <v>158</v>
@@ -58497,7 +58498,7 @@
         <v>1258</v>
       </c>
       <c r="B1259" s="2" t="s">
-        <v>5876</v>
+        <v>5875</v>
       </c>
       <c r="C1259" s="2" t="s">
         <v>243</v>
@@ -58509,13 +58510,13 @@
         <v>245</v>
       </c>
       <c r="F1259" s="2" t="s">
-        <v>5877</v>
+        <v>5876</v>
       </c>
       <c r="G1259" s="3">
         <v>3</v>
       </c>
       <c r="H1259" s="2" t="s">
-        <v>5878</v>
+        <v>5877</v>
       </c>
       <c r="I1259" s="2" t="s">
         <v>158</v>
@@ -58526,7 +58527,7 @@
         <v>1259</v>
       </c>
       <c r="B1260" s="2" t="s">
-        <v>5879</v>
+        <v>5878</v>
       </c>
       <c r="C1260" s="2" t="s">
         <v>245</v>
@@ -58535,7 +58536,7 @@
         <v>243</v>
       </c>
       <c r="E1260" s="2" t="s">
-        <v>5877</v>
+        <v>5876</v>
       </c>
       <c r="F1260" s="2" t="s">
         <v>244</v>
@@ -58544,7 +58545,7 @@
         <v>3</v>
       </c>
       <c r="H1260" s="2" t="s">
-        <v>5880</v>
+        <v>5879</v>
       </c>
       <c r="I1260" s="2" t="s">
         <v>158</v>
@@ -58555,7 +58556,7 @@
         <v>1260</v>
       </c>
       <c r="B1261" s="2" t="s">
-        <v>5881</v>
+        <v>5880</v>
       </c>
       <c r="C1261" s="2" t="s">
         <v>497</v>
@@ -58573,7 +58574,7 @@
         <v>4</v>
       </c>
       <c r="H1261" s="2" t="s">
-        <v>5882</v>
+        <v>5881</v>
       </c>
       <c r="I1261" s="2" t="s">
         <v>158</v>
@@ -58584,25 +58585,25 @@
         <v>1261</v>
       </c>
       <c r="B1262" s="2" t="s">
+        <v>5882</v>
+      </c>
+      <c r="C1262" s="2" t="s">
         <v>5883</v>
       </c>
-      <c r="C1262" s="2" t="s">
+      <c r="D1262" s="2" t="s">
         <v>5884</v>
       </c>
-      <c r="D1262" s="2" t="s">
+      <c r="E1262" s="2" t="s">
         <v>5885</v>
       </c>
-      <c r="E1262" s="2" t="s">
+      <c r="F1262" s="2" t="s">
         <v>5886</v>
-      </c>
-      <c r="F1262" s="2" t="s">
-        <v>5887</v>
       </c>
       <c r="G1262" s="3">
         <v>3</v>
       </c>
       <c r="H1262" s="2" t="s">
-        <v>5888</v>
+        <v>5887</v>
       </c>
       <c r="I1262" s="2" t="s">
         <v>15</v>
@@ -58613,25 +58614,25 @@
         <v>1262</v>
       </c>
       <c r="B1263" s="2" t="s">
+        <v>5888</v>
+      </c>
+      <c r="C1263" s="2" t="s">
         <v>5889</v>
       </c>
-      <c r="C1263" s="2" t="s">
+      <c r="D1263" s="2" t="s">
         <v>5890</v>
       </c>
-      <c r="D1263" s="2" t="s">
+      <c r="E1263" s="2" t="s">
         <v>5891</v>
       </c>
-      <c r="E1263" s="2" t="s">
+      <c r="F1263" s="2" t="s">
         <v>5892</v>
-      </c>
-      <c r="F1263" s="2" t="s">
-        <v>5893</v>
       </c>
       <c r="G1263" s="3">
         <v>3</v>
       </c>
       <c r="H1263" s="2" t="s">
-        <v>5894</v>
+        <v>5893</v>
       </c>
       <c r="I1263" s="2" t="s">
         <v>15</v>
@@ -58642,25 +58643,25 @@
         <v>1263</v>
       </c>
       <c r="B1264" s="2" t="s">
+        <v>5894</v>
+      </c>
+      <c r="C1264" s="2" t="s">
         <v>5895</v>
       </c>
-      <c r="C1264" s="2" t="s">
+      <c r="D1264" s="2" t="s">
         <v>5896</v>
       </c>
-      <c r="D1264" s="2" t="s">
+      <c r="E1264" s="2" t="s">
         <v>5897</v>
       </c>
-      <c r="E1264" s="2" t="s">
+      <c r="F1264" s="2" t="s">
         <v>5898</v>
-      </c>
-      <c r="F1264" s="2" t="s">
-        <v>5899</v>
       </c>
       <c r="G1264" s="3">
         <v>4</v>
       </c>
       <c r="H1264" s="2" t="s">
-        <v>5900</v>
+        <v>5899</v>
       </c>
       <c r="I1264" s="2" t="s">
         <v>15</v>
@@ -58671,23 +58672,23 @@
         <v>1264</v>
       </c>
       <c r="B1265" s="2" t="s">
+        <v>5900</v>
+      </c>
+      <c r="C1265" s="2" t="s">
         <v>5901</v>
       </c>
-      <c r="C1265" s="2" t="s">
+      <c r="D1265" s="2" t="s">
         <v>5902</v>
       </c>
-      <c r="D1265" s="2" t="s">
+      <c r="E1265" s="2" t="s">
         <v>5903</v>
-      </c>
-      <c r="E1265" s="2" t="s">
-        <v>5904</v>
       </c>
       <c r="F1265" s="2"/>
       <c r="G1265" s="3">
         <v>3</v>
       </c>
       <c r="H1265" s="2" t="s">
-        <v>5905</v>
+        <v>5904</v>
       </c>
       <c r="I1265" s="2" t="s">
         <v>15</v>
@@ -58698,25 +58699,25 @@
         <v>1265</v>
       </c>
       <c r="B1266" s="2" t="s">
+        <v>5905</v>
+      </c>
+      <c r="C1266" s="2" t="s">
         <v>5906</v>
       </c>
-      <c r="C1266" s="2" t="s">
+      <c r="D1266" s="2" t="s">
+        <v>5683</v>
+      </c>
+      <c r="E1266" s="2" t="s">
         <v>5907</v>
       </c>
-      <c r="D1266" s="2" t="s">
-        <v>5684</v>
-      </c>
-      <c r="E1266" s="2" t="s">
+      <c r="F1266" s="2" t="s">
         <v>5908</v>
-      </c>
-      <c r="F1266" s="2" t="s">
-        <v>5909</v>
       </c>
       <c r="G1266" s="3">
         <v>4</v>
       </c>
       <c r="H1266" s="2" t="s">
-        <v>5910</v>
+        <v>5909</v>
       </c>
       <c r="I1266" s="2" t="s">
         <v>15</v>
@@ -58727,25 +58728,25 @@
         <v>1266</v>
       </c>
       <c r="B1267" s="2" t="s">
+        <v>5910</v>
+      </c>
+      <c r="C1267" s="2" t="s">
         <v>5911</v>
       </c>
-      <c r="C1267" s="2" t="s">
+      <c r="D1267" s="2" t="s">
         <v>5912</v>
       </c>
-      <c r="D1267" s="2" t="s">
+      <c r="E1267" s="2" t="s">
         <v>5913</v>
       </c>
-      <c r="E1267" s="2" t="s">
+      <c r="F1267" s="2" t="s">
         <v>5914</v>
-      </c>
-      <c r="F1267" s="2" t="s">
-        <v>5915</v>
       </c>
       <c r="G1267" s="3">
         <v>4</v>
       </c>
       <c r="H1267" s="2" t="s">
-        <v>5916</v>
+        <v>5915</v>
       </c>
       <c r="I1267" s="2" t="s">
         <v>15</v>
@@ -58756,25 +58757,25 @@
         <v>1267</v>
       </c>
       <c r="B1268" s="2" t="s">
+        <v>5916</v>
+      </c>
+      <c r="C1268" s="2" t="s">
         <v>5917</v>
       </c>
-      <c r="C1268" s="2" t="s">
+      <c r="D1268" s="2" t="s">
         <v>5918</v>
       </c>
-      <c r="D1268" s="2" t="s">
+      <c r="E1268" s="2" t="s">
         <v>5919</v>
       </c>
-      <c r="E1268" s="2" t="s">
+      <c r="F1268" s="2" t="s">
         <v>5920</v>
-      </c>
-      <c r="F1268" s="2" t="s">
-        <v>5921</v>
       </c>
       <c r="G1268" s="3">
         <v>4</v>
       </c>
       <c r="H1268" s="2" t="s">
-        <v>5922</v>
+        <v>5921</v>
       </c>
       <c r="I1268" s="2" t="s">
         <v>158</v>
@@ -58785,25 +58786,25 @@
         <v>1268</v>
       </c>
       <c r="B1269" s="2" t="s">
+        <v>5922</v>
+      </c>
+      <c r="C1269" s="2" t="s">
         <v>5923</v>
       </c>
-      <c r="C1269" s="2" t="s">
+      <c r="D1269" s="2" t="s">
         <v>5924</v>
       </c>
-      <c r="D1269" s="2" t="s">
+      <c r="E1269" s="2" t="s">
         <v>5925</v>
       </c>
-      <c r="E1269" s="2" t="s">
+      <c r="F1269" s="2" t="s">
         <v>5926</v>
-      </c>
-      <c r="F1269" s="2" t="s">
-        <v>5927</v>
       </c>
       <c r="G1269" s="3">
         <v>4</v>
       </c>
       <c r="H1269" s="2" t="s">
-        <v>5928</v>
+        <v>5927</v>
       </c>
       <c r="I1269" s="2" t="s">
         <v>15</v>
@@ -58814,25 +58815,25 @@
         <v>1269</v>
       </c>
       <c r="B1270" s="2" t="s">
+        <v>5928</v>
+      </c>
+      <c r="C1270" s="2" t="s">
         <v>5929</v>
-      </c>
-      <c r="C1270" s="2" t="s">
-        <v>5930</v>
       </c>
       <c r="D1270" s="2" t="s">
         <v>2601</v>
       </c>
       <c r="E1270" s="2" t="s">
-        <v>6866</v>
+        <v>6865</v>
       </c>
       <c r="F1270" s="2" t="s">
-        <v>5931</v>
+        <v>5930</v>
       </c>
       <c r="G1270" s="3">
         <v>3</v>
       </c>
       <c r="H1270" s="2" t="s">
-        <v>5932</v>
+        <v>5931</v>
       </c>
       <c r="I1270" s="2" t="s">
         <v>15</v>
@@ -58843,25 +58844,25 @@
         <v>1270</v>
       </c>
       <c r="B1271" s="2" t="s">
+        <v>5932</v>
+      </c>
+      <c r="C1271" s="2" t="s">
         <v>5933</v>
       </c>
-      <c r="C1271" s="2" t="s">
+      <c r="D1271" s="2" t="s">
         <v>5934</v>
       </c>
-      <c r="D1271" s="2" t="s">
+      <c r="E1271" s="2" t="s">
         <v>5935</v>
       </c>
-      <c r="E1271" s="2" t="s">
+      <c r="F1271" s="2" t="s">
         <v>5936</v>
-      </c>
-      <c r="F1271" s="2" t="s">
-        <v>5937</v>
       </c>
       <c r="G1271" s="3">
         <v>1</v>
       </c>
       <c r="H1271" s="2" t="s">
-        <v>5938</v>
+        <v>5937</v>
       </c>
       <c r="I1271" s="2" t="s">
         <v>15</v>
@@ -58872,25 +58873,25 @@
         <v>1271</v>
       </c>
       <c r="B1272" s="2" t="s">
+        <v>5938</v>
+      </c>
+      <c r="C1272" s="2" t="s">
         <v>5939</v>
       </c>
-      <c r="C1272" s="2" t="s">
+      <c r="D1272" s="2" t="s">
         <v>5940</v>
       </c>
-      <c r="D1272" s="2" t="s">
+      <c r="E1272" s="2" t="s">
         <v>5941</v>
       </c>
-      <c r="E1272" s="2" t="s">
+      <c r="F1272" s="2" t="s">
         <v>5942</v>
-      </c>
-      <c r="F1272" s="2" t="s">
-        <v>5943</v>
       </c>
       <c r="G1272" s="3">
         <v>1</v>
       </c>
       <c r="H1272" s="2" t="s">
-        <v>5944</v>
+        <v>5943</v>
       </c>
       <c r="I1272" s="2" t="s">
         <v>15</v>
@@ -58901,7 +58902,7 @@
         <v>1272</v>
       </c>
       <c r="B1273" s="2" t="s">
-        <v>5945</v>
+        <v>5944</v>
       </c>
       <c r="C1273" s="2" t="s">
         <v>495</v>
@@ -58913,13 +58914,13 @@
         <v>3704</v>
       </c>
       <c r="F1273" s="2" t="s">
-        <v>5946</v>
+        <v>5945</v>
       </c>
       <c r="G1273" s="3">
         <v>4</v>
       </c>
       <c r="H1273" s="2" t="s">
-        <v>5947</v>
+        <v>5946</v>
       </c>
       <c r="I1273" s="2" t="s">
         <v>158</v>
@@ -58930,10 +58931,10 @@
         <v>1273</v>
       </c>
       <c r="B1274" s="2" t="s">
+        <v>5947</v>
+      </c>
+      <c r="C1274" s="2" t="s">
         <v>5948</v>
-      </c>
-      <c r="C1274" s="2" t="s">
-        <v>5949</v>
       </c>
       <c r="D1274" s="2" t="s">
         <v>5195</v>
@@ -58942,13 +58943,13 @@
         <v>2956</v>
       </c>
       <c r="F1274" s="2" t="s">
-        <v>5950</v>
+        <v>5949</v>
       </c>
       <c r="G1274" s="3">
         <v>3</v>
       </c>
       <c r="H1274" s="2" t="s">
-        <v>5951</v>
+        <v>5950</v>
       </c>
       <c r="I1274" s="2" t="s">
         <v>15</v>
@@ -58959,25 +58960,25 @@
         <v>1274</v>
       </c>
       <c r="B1275" s="2" t="s">
+        <v>5951</v>
+      </c>
+      <c r="C1275" s="2" t="s">
         <v>5952</v>
       </c>
-      <c r="C1275" s="2" t="s">
+      <c r="D1275" s="2" t="s">
         <v>5953</v>
       </c>
-      <c r="D1275" s="2" t="s">
+      <c r="E1275" s="2" t="s">
         <v>5954</v>
       </c>
-      <c r="E1275" s="2" t="s">
+      <c r="F1275" s="2" t="s">
         <v>5955</v>
-      </c>
-      <c r="F1275" s="2" t="s">
-        <v>5956</v>
       </c>
       <c r="G1275" s="3">
         <v>2</v>
       </c>
       <c r="H1275" s="2" t="s">
-        <v>5957</v>
+        <v>5956</v>
       </c>
       <c r="I1275" s="2" t="s">
         <v>158</v>
@@ -58988,25 +58989,25 @@
         <v>1275</v>
       </c>
       <c r="B1276" s="2" t="s">
+        <v>5957</v>
+      </c>
+      <c r="C1276" s="2" t="s">
         <v>5958</v>
       </c>
-      <c r="C1276" s="2" t="s">
+      <c r="D1276" s="2" t="s">
         <v>5959</v>
       </c>
-      <c r="D1276" s="2" t="s">
+      <c r="E1276" s="2" t="s">
         <v>5960</v>
       </c>
-      <c r="E1276" s="2" t="s">
+      <c r="F1276" s="2" t="s">
         <v>5961</v>
-      </c>
-      <c r="F1276" s="2" t="s">
-        <v>5962</v>
       </c>
       <c r="G1276" s="3">
         <v>2</v>
       </c>
       <c r="H1276" s="2" t="s">
-        <v>5963</v>
+        <v>5962</v>
       </c>
       <c r="I1276" s="2" t="s">
         <v>15</v>
@@ -59017,7 +59018,7 @@
         <v>1276</v>
       </c>
       <c r="B1277" s="2" t="s">
-        <v>5964</v>
+        <v>5963</v>
       </c>
       <c r="C1277" s="2" t="s">
         <v>1340</v>
@@ -59026,16 +59027,16 @@
         <v>1342</v>
       </c>
       <c r="E1277" s="2" t="s">
+        <v>5964</v>
+      </c>
+      <c r="F1277" s="2" t="s">
         <v>5965</v>
-      </c>
-      <c r="F1277" s="2" t="s">
-        <v>5966</v>
       </c>
       <c r="G1277" s="3">
         <v>4</v>
       </c>
       <c r="H1277" s="2" t="s">
-        <v>5967</v>
+        <v>5966</v>
       </c>
       <c r="I1277" s="2" t="s">
         <v>15</v>
@@ -59046,25 +59047,25 @@
         <v>1277</v>
       </c>
       <c r="B1278" s="2" t="s">
-        <v>6747</v>
+        <v>6746</v>
       </c>
       <c r="C1278" s="2" t="s">
+        <v>5967</v>
+      </c>
+      <c r="D1278" s="2" t="s">
         <v>5968</v>
-      </c>
-      <c r="D1278" s="2" t="s">
-        <v>5969</v>
       </c>
       <c r="E1278" s="2" t="s">
         <v>117</v>
       </c>
       <c r="F1278" s="2" t="s">
-        <v>6748</v>
+        <v>6747</v>
       </c>
       <c r="G1278" s="3">
         <v>4</v>
       </c>
       <c r="H1278" s="2" t="s">
-        <v>5970</v>
+        <v>5969</v>
       </c>
       <c r="I1278" s="2" t="s">
         <v>158</v>
@@ -59075,25 +59076,25 @@
         <v>1278</v>
       </c>
       <c r="B1279" s="2" t="s">
+        <v>6879</v>
+      </c>
+      <c r="C1279" s="2" t="s">
+        <v>5970</v>
+      </c>
+      <c r="D1279" s="2" t="s">
+        <v>5971</v>
+      </c>
+      <c r="E1279" s="2" t="s">
         <v>6880</v>
       </c>
-      <c r="C1279" s="2" t="s">
-        <v>5971</v>
-      </c>
-      <c r="D1279" s="2" t="s">
-        <v>5972</v>
-      </c>
-      <c r="E1279" s="2" t="s">
+      <c r="F1279" s="2" t="s">
         <v>6881</v>
-      </c>
-      <c r="F1279" s="2" t="s">
-        <v>6882</v>
       </c>
       <c r="G1279" s="3">
         <v>1</v>
       </c>
       <c r="H1279" s="2" t="s">
-        <v>5973</v>
+        <v>5972</v>
       </c>
       <c r="I1279" s="2" t="s">
         <v>15</v>
@@ -59104,25 +59105,25 @@
         <v>1279</v>
       </c>
       <c r="B1280" s="2" t="s">
+        <v>6688</v>
+      </c>
+      <c r="C1280" s="2" t="s">
         <v>6689</v>
       </c>
-      <c r="C1280" s="2" t="s">
+      <c r="D1280" s="2" t="s">
+        <v>6692</v>
+      </c>
+      <c r="E1280" s="2" t="s">
         <v>6690</v>
       </c>
-      <c r="D1280" s="2" t="s">
-        <v>6693</v>
-      </c>
-      <c r="E1280" s="2" t="s">
+      <c r="F1280" s="2" t="s">
         <v>6691</v>
-      </c>
-      <c r="F1280" s="2" t="s">
-        <v>6692</v>
       </c>
       <c r="G1280" s="3">
         <v>4</v>
       </c>
       <c r="H1280" s="2" t="s">
-        <v>5974</v>
+        <v>5973</v>
       </c>
       <c r="I1280" s="2" t="s">
         <v>15</v>
@@ -59133,10 +59134,10 @@
         <v>1280</v>
       </c>
       <c r="B1281" s="2" t="s">
+        <v>5974</v>
+      </c>
+      <c r="C1281" s="2" t="s">
         <v>5975</v>
-      </c>
-      <c r="C1281" s="2" t="s">
-        <v>5976</v>
       </c>
       <c r="D1281" s="2" t="s">
         <v>170</v>
@@ -59145,13 +59146,13 @@
         <v>172</v>
       </c>
       <c r="F1281" s="2" t="s">
-        <v>5977</v>
+        <v>5976</v>
       </c>
       <c r="G1281" s="3">
         <v>1</v>
       </c>
       <c r="H1281" s="2" t="s">
-        <v>5978</v>
+        <v>5977</v>
       </c>
       <c r="I1281" s="2" t="s">
         <v>15</v>
@@ -59162,25 +59163,25 @@
         <v>1281</v>
       </c>
       <c r="B1282" s="2" t="s">
+        <v>5978</v>
+      </c>
+      <c r="C1282" s="2" t="s">
         <v>5979</v>
       </c>
-      <c r="C1282" s="2" t="s">
+      <c r="D1282" s="2" t="s">
         <v>5980</v>
-      </c>
-      <c r="D1282" s="2" t="s">
-        <v>5981</v>
       </c>
       <c r="E1282" s="2" t="s">
         <v>5399</v>
       </c>
       <c r="F1282" s="2" t="s">
-        <v>5982</v>
+        <v>5981</v>
       </c>
       <c r="G1282" s="3">
         <v>4</v>
       </c>
       <c r="H1282" s="2" t="s">
-        <v>5983</v>
+        <v>5982</v>
       </c>
       <c r="I1282" s="2" t="s">
         <v>15</v>
@@ -59191,25 +59192,25 @@
         <v>1282</v>
       </c>
       <c r="B1283" s="2" t="s">
+        <v>5983</v>
+      </c>
+      <c r="C1283" s="2" t="s">
         <v>5984</v>
       </c>
-      <c r="C1283" s="2" t="s">
+      <c r="D1283" s="2" t="s">
         <v>5985</v>
-      </c>
-      <c r="D1283" s="2" t="s">
-        <v>5986</v>
       </c>
       <c r="E1283" s="2" t="s">
         <v>5190</v>
       </c>
       <c r="F1283" s="2" t="s">
-        <v>5987</v>
+        <v>5986</v>
       </c>
       <c r="G1283" s="3">
         <v>2</v>
       </c>
       <c r="H1283" s="2" t="s">
-        <v>5988</v>
+        <v>5987</v>
       </c>
       <c r="I1283" s="2" t="s">
         <v>15</v>
@@ -59220,7 +59221,7 @@
         <v>1283</v>
       </c>
       <c r="B1284" s="2" t="s">
-        <v>5989</v>
+        <v>5988</v>
       </c>
       <c r="C1284" s="2" t="s">
         <v>1764</v>
@@ -59229,16 +59230,16 @@
         <v>1765</v>
       </c>
       <c r="E1284" s="2" t="s">
+        <v>5989</v>
+      </c>
+      <c r="F1284" s="2" t="s">
         <v>5990</v>
-      </c>
-      <c r="F1284" s="2" t="s">
-        <v>5991</v>
       </c>
       <c r="G1284" s="3">
         <v>3</v>
       </c>
       <c r="H1284" s="2" t="s">
-        <v>5992</v>
+        <v>5991</v>
       </c>
       <c r="I1284" s="2" t="s">
         <v>15</v>
@@ -59249,25 +59250,25 @@
         <v>1284</v>
       </c>
       <c r="B1285" s="2" t="s">
+        <v>6552</v>
+      </c>
+      <c r="C1285" s="2" t="s">
         <v>6553</v>
-      </c>
-      <c r="C1285" s="2" t="s">
-        <v>6554</v>
       </c>
       <c r="D1285" s="2" t="s">
         <v>3181</v>
       </c>
       <c r="E1285" s="2" t="s">
-        <v>5993</v>
+        <v>5992</v>
       </c>
       <c r="F1285" s="2" t="s">
-        <v>6555</v>
+        <v>6554</v>
       </c>
       <c r="G1285" s="3">
         <v>2</v>
       </c>
       <c r="H1285" s="2" t="s">
-        <v>5994</v>
+        <v>5993</v>
       </c>
       <c r="I1285" s="2" t="s">
         <v>15</v>
@@ -59278,25 +59279,25 @@
         <v>1285</v>
       </c>
       <c r="B1286" s="2" t="s">
+        <v>5994</v>
+      </c>
+      <c r="C1286" s="2" t="s">
         <v>5995</v>
       </c>
-      <c r="C1286" s="2" t="s">
+      <c r="D1286" s="2" t="s">
         <v>5996</v>
       </c>
-      <c r="D1286" s="2" t="s">
+      <c r="E1286" s="2" t="s">
         <v>5997</v>
       </c>
-      <c r="E1286" s="2" t="s">
+      <c r="F1286" s="2" t="s">
         <v>5998</v>
-      </c>
-      <c r="F1286" s="2" t="s">
-        <v>5999</v>
       </c>
       <c r="G1286" s="3">
         <v>1</v>
       </c>
       <c r="H1286" s="2" t="s">
-        <v>6000</v>
+        <v>5999</v>
       </c>
       <c r="I1286" s="2" t="s">
         <v>15</v>
@@ -59307,7 +59308,7 @@
         <v>1286</v>
       </c>
       <c r="B1287" s="2" t="s">
-        <v>6001</v>
+        <v>6000</v>
       </c>
       <c r="C1287" s="2" t="s">
         <v>875</v>
@@ -59319,13 +59320,13 @@
         <v>3875</v>
       </c>
       <c r="F1287" s="2" t="s">
-        <v>6002</v>
+        <v>6001</v>
       </c>
       <c r="G1287" s="3">
         <v>3</v>
       </c>
       <c r="H1287" s="2" t="s">
-        <v>6003</v>
+        <v>6002</v>
       </c>
       <c r="I1287" s="2" t="s">
         <v>158</v>
@@ -59336,25 +59337,25 @@
         <v>1287</v>
       </c>
       <c r="B1288" s="2" t="s">
+        <v>6003</v>
+      </c>
+      <c r="C1288" s="2" t="s">
         <v>6004</v>
-      </c>
-      <c r="C1288" s="2" t="s">
-        <v>6005</v>
       </c>
       <c r="D1288" s="2" t="s">
         <v>5029</v>
       </c>
       <c r="E1288" s="2" t="s">
+        <v>6005</v>
+      </c>
+      <c r="F1288" s="2" t="s">
         <v>6006</v>
-      </c>
-      <c r="F1288" s="2" t="s">
-        <v>6007</v>
       </c>
       <c r="G1288" s="3">
         <v>1</v>
       </c>
       <c r="H1288" s="2" t="s">
-        <v>6008</v>
+        <v>6007</v>
       </c>
       <c r="I1288" s="2" t="s">
         <v>151</v>
@@ -59365,25 +59366,25 @@
         <v>1288</v>
       </c>
       <c r="B1289" s="2" t="s">
+        <v>6008</v>
+      </c>
+      <c r="C1289" s="2" t="s">
         <v>6009</v>
       </c>
-      <c r="C1289" s="2" t="s">
+      <c r="D1289" s="2" t="s">
         <v>6010</v>
       </c>
-      <c r="D1289" s="2" t="s">
+      <c r="E1289" s="2" t="s">
         <v>6011</v>
       </c>
-      <c r="E1289" s="2" t="s">
+      <c r="F1289" s="2" t="s">
         <v>6012</v>
-      </c>
-      <c r="F1289" s="2" t="s">
-        <v>6013</v>
       </c>
       <c r="G1289" s="3">
         <v>4</v>
       </c>
       <c r="H1289" s="2" t="s">
-        <v>6014</v>
+        <v>6013</v>
       </c>
       <c r="I1289" s="2" t="s">
         <v>15</v>
@@ -59394,25 +59395,25 @@
         <v>1289</v>
       </c>
       <c r="B1290" s="2" t="s">
+        <v>6538</v>
+      </c>
+      <c r="C1290" s="2" t="s">
         <v>6539</v>
       </c>
-      <c r="C1290" s="2" t="s">
+      <c r="D1290" s="2" t="s">
         <v>6540</v>
       </c>
-      <c r="D1290" s="2" t="s">
+      <c r="E1290" s="2" t="s">
+        <v>6014</v>
+      </c>
+      <c r="F1290" s="2" t="s">
         <v>6541</v>
-      </c>
-      <c r="E1290" s="2" t="s">
-        <v>6015</v>
-      </c>
-      <c r="F1290" s="2" t="s">
-        <v>6542</v>
       </c>
       <c r="G1290" s="3">
         <v>3</v>
       </c>
       <c r="H1290" s="2" t="s">
-        <v>6016</v>
+        <v>6015</v>
       </c>
       <c r="I1290" s="2" t="s">
         <v>15</v>
@@ -59423,25 +59424,25 @@
         <v>1290</v>
       </c>
       <c r="B1291" s="2" t="s">
+        <v>6016</v>
+      </c>
+      <c r="C1291" s="2" t="s">
         <v>6017</v>
-      </c>
-      <c r="C1291" s="2" t="s">
-        <v>6018</v>
       </c>
       <c r="D1291" s="2" t="s">
         <v>4294</v>
       </c>
       <c r="E1291" s="2" t="s">
+        <v>6018</v>
+      </c>
+      <c r="F1291" s="2" t="s">
         <v>6019</v>
-      </c>
-      <c r="F1291" s="2" t="s">
-        <v>6020</v>
       </c>
       <c r="G1291" s="3">
         <v>1</v>
       </c>
       <c r="H1291" s="2" t="s">
-        <v>6021</v>
+        <v>6020</v>
       </c>
       <c r="I1291" s="2" t="s">
         <v>15</v>
@@ -59452,7 +59453,7 @@
         <v>1291</v>
       </c>
       <c r="B1292" s="2" t="s">
-        <v>6864</v>
+        <v>6863</v>
       </c>
       <c r="C1292" s="2" t="s">
         <v>496</v>
@@ -59464,7 +59465,7 @@
         <v>498</v>
       </c>
       <c r="F1292" s="2" t="s">
-        <v>6865</v>
+        <v>6864</v>
       </c>
       <c r="G1292" s="3">
         <v>2</v>
@@ -59481,25 +59482,25 @@
         <v>1292</v>
       </c>
       <c r="B1293" s="2" t="s">
+        <v>6021</v>
+      </c>
+      <c r="C1293" s="2" t="s">
         <v>6022</v>
       </c>
-      <c r="C1293" s="2" t="s">
+      <c r="D1293" s="2" t="s">
         <v>6023</v>
       </c>
-      <c r="D1293" s="2" t="s">
+      <c r="E1293" s="2" t="s">
         <v>6024</v>
       </c>
-      <c r="E1293" s="2" t="s">
+      <c r="F1293" s="2" t="s">
         <v>6025</v>
-      </c>
-      <c r="F1293" s="2" t="s">
-        <v>6026</v>
       </c>
       <c r="G1293" s="3">
         <v>4</v>
       </c>
       <c r="H1293" s="2" t="s">
-        <v>6027</v>
+        <v>6026</v>
       </c>
       <c r="I1293" s="2" t="s">
         <v>15</v>
@@ -59510,25 +59511,25 @@
         <v>1293</v>
       </c>
       <c r="B1294" s="2" t="s">
+        <v>6027</v>
+      </c>
+      <c r="C1294" s="2" t="s">
         <v>6028</v>
       </c>
-      <c r="C1294" s="2" t="s">
+      <c r="D1294" s="2" t="s">
         <v>6029</v>
       </c>
-      <c r="D1294" s="2" t="s">
+      <c r="E1294" s="2" t="s">
         <v>6030</v>
       </c>
-      <c r="E1294" s="2" t="s">
+      <c r="F1294" s="2" t="s">
         <v>6031</v>
-      </c>
-      <c r="F1294" s="2" t="s">
-        <v>6032</v>
       </c>
       <c r="G1294" s="3">
         <v>1</v>
       </c>
       <c r="H1294" s="2" t="s">
-        <v>6033</v>
+        <v>6032</v>
       </c>
       <c r="I1294" s="2" t="s">
         <v>15</v>
@@ -59539,25 +59540,25 @@
         <v>1294</v>
       </c>
       <c r="B1295" s="2" t="s">
-        <v>6034</v>
+        <v>6033</v>
       </c>
       <c r="C1295" s="2" t="s">
         <v>816</v>
       </c>
       <c r="D1295" s="2" t="s">
+        <v>6034</v>
+      </c>
+      <c r="E1295" s="2" t="s">
         <v>6035</v>
       </c>
-      <c r="E1295" s="2" t="s">
+      <c r="F1295" s="2" t="s">
         <v>6036</v>
-      </c>
-      <c r="F1295" s="2" t="s">
-        <v>6037</v>
       </c>
       <c r="G1295" s="3">
         <v>3</v>
       </c>
       <c r="H1295" s="2" t="s">
-        <v>6038</v>
+        <v>6037</v>
       </c>
       <c r="I1295" s="2" t="s">
         <v>158</v>
@@ -59568,25 +59569,25 @@
         <v>1295</v>
       </c>
       <c r="B1296" s="2" t="s">
+        <v>6038</v>
+      </c>
+      <c r="C1296" s="2" t="s">
         <v>6039</v>
       </c>
-      <c r="C1296" s="2" t="s">
+      <c r="D1296" s="2" t="s">
         <v>6040</v>
       </c>
-      <c r="D1296" s="2" t="s">
+      <c r="E1296" s="2" t="s">
         <v>6041</v>
       </c>
-      <c r="E1296" s="2" t="s">
+      <c r="F1296" s="2" t="s">
         <v>6042</v>
-      </c>
-      <c r="F1296" s="2" t="s">
-        <v>6043</v>
       </c>
       <c r="G1296" s="3">
         <v>3</v>
       </c>
       <c r="H1296" s="2" t="s">
-        <v>6044</v>
+        <v>6043</v>
       </c>
       <c r="I1296" s="2" t="s">
         <v>15</v>
@@ -59597,7 +59598,7 @@
         <v>1296</v>
       </c>
       <c r="B1297" s="2" t="s">
-        <v>6045</v>
+        <v>6044</v>
       </c>
       <c r="C1297" s="2" t="s">
         <v>591</v>
@@ -59609,13 +59610,13 @@
         <v>602</v>
       </c>
       <c r="F1297" s="2" t="s">
-        <v>6046</v>
+        <v>6045</v>
       </c>
       <c r="G1297" s="3">
         <v>1</v>
       </c>
       <c r="H1297" s="2" t="s">
-        <v>6047</v>
+        <v>6046</v>
       </c>
       <c r="I1297" s="2" t="s">
         <v>15</v>
@@ -59626,7 +59627,7 @@
         <v>1297</v>
       </c>
       <c r="B1298" s="2" t="s">
-        <v>6048</v>
+        <v>6047</v>
       </c>
       <c r="C1298" s="2" t="s">
         <v>563</v>
@@ -59644,7 +59645,7 @@
         <v>1</v>
       </c>
       <c r="H1298" s="2" t="s">
-        <v>6049</v>
+        <v>6048</v>
       </c>
       <c r="I1298" s="2" t="s">
         <v>15</v>
@@ -59655,7 +59656,7 @@
         <v>1298</v>
       </c>
       <c r="B1299" s="2" t="s">
-        <v>6050</v>
+        <v>6049</v>
       </c>
       <c r="C1299" s="2" t="s">
         <v>224</v>
@@ -59673,7 +59674,7 @@
         <v>2</v>
       </c>
       <c r="H1299" s="2" t="s">
-        <v>6051</v>
+        <v>6050</v>
       </c>
       <c r="I1299" s="2" t="s">
         <v>22</v>
@@ -59684,25 +59685,25 @@
         <v>1299</v>
       </c>
       <c r="B1300" s="2" t="s">
+        <v>6051</v>
+      </c>
+      <c r="C1300" s="2" t="s">
         <v>6052</v>
       </c>
-      <c r="C1300" s="2" t="s">
+      <c r="D1300" s="2" t="s">
         <v>6053</v>
       </c>
-      <c r="D1300" s="2" t="s">
+      <c r="E1300" s="2" t="s">
         <v>6054</v>
       </c>
-      <c r="E1300" s="2" t="s">
+      <c r="F1300" s="2" t="s">
         <v>6055</v>
-      </c>
-      <c r="F1300" s="2" t="s">
-        <v>6056</v>
       </c>
       <c r="G1300" s="3">
         <v>1</v>
       </c>
       <c r="H1300" s="2" t="s">
-        <v>6057</v>
+        <v>6056</v>
       </c>
       <c r="I1300" s="2" t="s">
         <v>15</v>
@@ -59713,25 +59714,25 @@
         <v>1300</v>
       </c>
       <c r="B1301" s="2" t="s">
+        <v>6057</v>
+      </c>
+      <c r="C1301" s="2" t="s">
         <v>6058</v>
       </c>
-      <c r="C1301" s="2" t="s">
+      <c r="D1301" s="2" t="s">
         <v>6059</v>
-      </c>
-      <c r="D1301" s="2" t="s">
-        <v>6060</v>
       </c>
       <c r="E1301" s="2" t="s">
         <v>117</v>
       </c>
       <c r="F1301" s="2" t="s">
-        <v>6061</v>
+        <v>6060</v>
       </c>
       <c r="G1301" s="3">
         <v>1</v>
       </c>
       <c r="H1301" s="2" t="s">
-        <v>6062</v>
+        <v>6061</v>
       </c>
       <c r="I1301" s="2" t="s">
         <v>15</v>
@@ -59742,25 +59743,25 @@
         <v>1301</v>
       </c>
       <c r="B1302" s="2" t="s">
+        <v>6062</v>
+      </c>
+      <c r="C1302" s="2" t="s">
         <v>6063</v>
       </c>
-      <c r="C1302" s="2" t="s">
+      <c r="D1302" s="2" t="s">
         <v>6064</v>
       </c>
-      <c r="D1302" s="2" t="s">
+      <c r="E1302" s="2" t="s">
         <v>6065</v>
       </c>
-      <c r="E1302" s="2" t="s">
+      <c r="F1302" s="2" t="s">
         <v>6066</v>
-      </c>
-      <c r="F1302" s="2" t="s">
-        <v>6067</v>
       </c>
       <c r="G1302" s="3">
         <v>1</v>
       </c>
       <c r="H1302" s="2" t="s">
-        <v>6068</v>
+        <v>6067</v>
       </c>
       <c r="I1302" s="2" t="s">
         <v>15</v>
@@ -59771,25 +59772,25 @@
         <v>1302</v>
       </c>
       <c r="B1303" s="2" t="s">
+        <v>6712</v>
+      </c>
+      <c r="C1303" s="2" t="s">
+        <v>6068</v>
+      </c>
+      <c r="D1303" s="2" t="s">
+        <v>6069</v>
+      </c>
+      <c r="E1303" s="2" t="s">
+        <v>6070</v>
+      </c>
+      <c r="F1303" s="2" t="s">
         <v>6713</v>
-      </c>
-      <c r="C1303" s="2" t="s">
-        <v>6069</v>
-      </c>
-      <c r="D1303" s="2" t="s">
-        <v>6070</v>
-      </c>
-      <c r="E1303" s="2" t="s">
-        <v>6071</v>
-      </c>
-      <c r="F1303" s="2" t="s">
-        <v>6714</v>
       </c>
       <c r="G1303" s="3">
         <v>2</v>
       </c>
       <c r="H1303" s="2" t="s">
-        <v>6072</v>
+        <v>6071</v>
       </c>
       <c r="I1303" s="2" t="s">
         <v>15</v>
@@ -59800,25 +59801,25 @@
         <v>1303</v>
       </c>
       <c r="B1304" s="2" t="s">
+        <v>6072</v>
+      </c>
+      <c r="C1304" s="2" t="s">
         <v>6073</v>
       </c>
-      <c r="C1304" s="2" t="s">
+      <c r="D1304" s="2" t="s">
         <v>6074</v>
       </c>
-      <c r="D1304" s="2" t="s">
+      <c r="E1304" s="2" t="s">
         <v>6075</v>
       </c>
-      <c r="E1304" s="2" t="s">
+      <c r="F1304" s="2" t="s">
         <v>6076</v>
-      </c>
-      <c r="F1304" s="2" t="s">
-        <v>6077</v>
       </c>
       <c r="G1304" s="3">
         <v>3</v>
       </c>
       <c r="H1304" s="2" t="s">
-        <v>6078</v>
+        <v>6077</v>
       </c>
       <c r="I1304" s="2" t="s">
         <v>158</v>
@@ -59829,25 +59830,25 @@
         <v>1304</v>
       </c>
       <c r="B1305" s="2" t="s">
+        <v>6078</v>
+      </c>
+      <c r="C1305" s="2" t="s">
         <v>6079</v>
       </c>
-      <c r="C1305" s="2" t="s">
+      <c r="D1305" s="2" t="s">
         <v>6080</v>
       </c>
-      <c r="D1305" s="2" t="s">
+      <c r="E1305" s="2" t="s">
         <v>6081</v>
       </c>
-      <c r="E1305" s="2" t="s">
+      <c r="F1305" s="2" t="s">
         <v>6082</v>
-      </c>
-      <c r="F1305" s="2" t="s">
-        <v>6083</v>
       </c>
       <c r="G1305" s="3">
         <v>1</v>
       </c>
       <c r="H1305" s="2" t="s">
-        <v>6084</v>
+        <v>6083</v>
       </c>
       <c r="I1305" s="2" t="s">
         <v>15</v>
@@ -59858,25 +59859,25 @@
         <v>1305</v>
       </c>
       <c r="B1306" s="2" t="s">
+        <v>6084</v>
+      </c>
+      <c r="C1306" s="2" t="s">
         <v>6085</v>
       </c>
-      <c r="C1306" s="2" t="s">
+      <c r="D1306" s="2" t="s">
         <v>6086</v>
       </c>
-      <c r="D1306" s="2" t="s">
+      <c r="E1306" s="2" t="s">
         <v>6087</v>
       </c>
-      <c r="E1306" s="2" t="s">
+      <c r="F1306" s="2" t="s">
         <v>6088</v>
-      </c>
-      <c r="F1306" s="2" t="s">
-        <v>6089</v>
       </c>
       <c r="G1306" s="3">
         <v>2</v>
       </c>
       <c r="H1306" s="2" t="s">
-        <v>6090</v>
+        <v>6089</v>
       </c>
       <c r="I1306" s="2" t="s">
         <v>15</v>
@@ -59887,25 +59888,25 @@
         <v>1306</v>
       </c>
       <c r="B1307" s="2" t="s">
+        <v>6090</v>
+      </c>
+      <c r="C1307" s="2" t="s">
         <v>6091</v>
       </c>
-      <c r="C1307" s="2" t="s">
+      <c r="D1307" s="2" t="s">
         <v>6092</v>
-      </c>
-      <c r="D1307" s="2" t="s">
-        <v>6093</v>
       </c>
       <c r="E1307" s="2" t="s">
         <v>5577</v>
       </c>
       <c r="F1307" s="2" t="s">
-        <v>6094</v>
+        <v>6093</v>
       </c>
       <c r="G1307" s="3">
         <v>4</v>
       </c>
       <c r="H1307" s="2" t="s">
-        <v>6095</v>
+        <v>6094</v>
       </c>
       <c r="I1307" s="2" t="s">
         <v>15</v>
@@ -59916,7 +59917,7 @@
         <v>1307</v>
       </c>
       <c r="B1308" s="2" t="s">
-        <v>6096</v>
+        <v>6095</v>
       </c>
       <c r="C1308" s="2" t="s">
         <v>875</v>
@@ -59934,7 +59935,7 @@
         <v>3</v>
       </c>
       <c r="H1308" s="2" t="s">
-        <v>6097</v>
+        <v>6096</v>
       </c>
       <c r="I1308" s="2" t="s">
         <v>15</v>
@@ -59945,7 +59946,7 @@
         <v>1308</v>
       </c>
       <c r="B1309" s="2" t="s">
-        <v>6098</v>
+        <v>6097</v>
       </c>
       <c r="C1309" s="2" t="s">
         <v>4173</v>
@@ -59974,7 +59975,7 @@
         <v>1309</v>
       </c>
       <c r="B1310" s="2" t="s">
-        <v>6099</v>
+        <v>6098</v>
       </c>
       <c r="C1310" s="2" t="s">
         <v>4173</v>
@@ -59992,7 +59993,7 @@
         <v>1</v>
       </c>
       <c r="H1310" s="2" t="s">
-        <v>6100</v>
+        <v>6099</v>
       </c>
       <c r="I1310" s="2" t="s">
         <v>15</v>
@@ -60003,13 +60004,13 @@
         <v>1310</v>
       </c>
       <c r="B1311" s="2" t="s">
-        <v>6101</v>
+        <v>6100</v>
       </c>
       <c r="C1311" s="2" t="s">
         <v>3206</v>
       </c>
       <c r="D1311" s="2" t="s">
-        <v>5684</v>
+        <v>5683</v>
       </c>
       <c r="E1311" s="2" t="s">
         <v>1472</v>
@@ -60021,7 +60022,7 @@
         <v>2</v>
       </c>
       <c r="H1311" s="2" t="s">
-        <v>5686</v>
+        <v>5685</v>
       </c>
       <c r="I1311" s="2" t="s">
         <v>15</v>
@@ -60032,7 +60033,7 @@
         <v>1311</v>
       </c>
       <c r="B1312" s="2" t="s">
-        <v>6102</v>
+        <v>6101</v>
       </c>
       <c r="C1312" s="2" t="s">
         <v>72</v>
@@ -60041,10 +60042,10 @@
         <v>77</v>
       </c>
       <c r="E1312" s="2" t="s">
+        <v>6102</v>
+      </c>
+      <c r="F1312" s="2" t="s">
         <v>6103</v>
-      </c>
-      <c r="F1312" s="2" t="s">
-        <v>6104</v>
       </c>
       <c r="G1312" s="3">
         <v>2</v>
@@ -60061,25 +60062,25 @@
         <v>1312</v>
       </c>
       <c r="B1313" s="2" t="s">
-        <v>6105</v>
+        <v>6104</v>
       </c>
       <c r="C1313" s="2" t="s">
         <v>5202</v>
       </c>
       <c r="D1313" s="2" t="s">
+        <v>6105</v>
+      </c>
+      <c r="E1313" s="2" t="s">
         <v>6106</v>
       </c>
-      <c r="E1313" s="2" t="s">
+      <c r="F1313" s="2" t="s">
         <v>6107</v>
-      </c>
-      <c r="F1313" s="2" t="s">
-        <v>6108</v>
       </c>
       <c r="G1313" s="3">
         <v>1</v>
       </c>
       <c r="H1313" s="2" t="s">
-        <v>6109</v>
+        <v>6108</v>
       </c>
       <c r="I1313" s="2" t="s">
         <v>15</v>
@@ -60090,25 +60091,25 @@
         <v>1313</v>
       </c>
       <c r="B1314" s="2" t="s">
-        <v>6110</v>
+        <v>6109</v>
       </c>
       <c r="C1314" s="2" t="s">
-        <v>5925</v>
+        <v>5924</v>
       </c>
       <c r="D1314" s="2" t="s">
+        <v>6603</v>
+      </c>
+      <c r="E1314" s="2" t="s">
+        <v>6602</v>
+      </c>
+      <c r="F1314" s="2" t="s">
         <v>6604</v>
-      </c>
-      <c r="E1314" s="2" t="s">
-        <v>6603</v>
-      </c>
-      <c r="F1314" s="2" t="s">
-        <v>6605</v>
       </c>
       <c r="G1314" s="3">
         <v>3</v>
       </c>
       <c r="H1314" s="2" t="s">
-        <v>6111</v>
+        <v>6110</v>
       </c>
       <c r="I1314" s="2" t="s">
         <v>15</v>
@@ -60119,19 +60120,19 @@
         <v>1314</v>
       </c>
       <c r="B1315" s="2" t="s">
+        <v>6598</v>
+      </c>
+      <c r="C1315" s="2" t="s">
+        <v>6111</v>
+      </c>
+      <c r="D1315" s="2" t="s">
         <v>6599</v>
       </c>
-      <c r="C1315" s="2" t="s">
-        <v>6112</v>
-      </c>
-      <c r="D1315" s="2" t="s">
+      <c r="E1315" s="2" t="s">
         <v>6600</v>
       </c>
-      <c r="E1315" s="2" t="s">
+      <c r="F1315" s="2" t="s">
         <v>6601</v>
-      </c>
-      <c r="F1315" s="2" t="s">
-        <v>6602</v>
       </c>
       <c r="G1315" s="3">
         <v>4</v>
@@ -60148,25 +60149,25 @@
         <v>1315</v>
       </c>
       <c r="B1316" s="2" t="s">
+        <v>6112</v>
+      </c>
+      <c r="C1316" s="2" t="s">
         <v>6113</v>
       </c>
-      <c r="C1316" s="2" t="s">
+      <c r="D1316" s="2" t="s">
         <v>6114</v>
-      </c>
-      <c r="D1316" s="2" t="s">
-        <v>6115</v>
       </c>
       <c r="E1316" s="2" t="s">
         <v>5023</v>
       </c>
       <c r="F1316" s="2" t="s">
-        <v>6116</v>
+        <v>6115</v>
       </c>
       <c r="G1316" s="3">
         <v>2</v>
       </c>
       <c r="H1316" s="2" t="s">
-        <v>6117</v>
+        <v>6116</v>
       </c>
       <c r="I1316" s="2" t="s">
         <v>15</v>
@@ -60177,25 +60178,25 @@
         <v>1316</v>
       </c>
       <c r="B1317" s="2" t="s">
+        <v>6605</v>
+      </c>
+      <c r="C1317" s="2" t="s">
+        <v>6117</v>
+      </c>
+      <c r="D1317" s="2" t="s">
+        <v>6118</v>
+      </c>
+      <c r="E1317" s="2" t="s">
+        <v>6119</v>
+      </c>
+      <c r="F1317" s="2" t="s">
         <v>6606</v>
-      </c>
-      <c r="C1317" s="2" t="s">
-        <v>6118</v>
-      </c>
-      <c r="D1317" s="2" t="s">
-        <v>6119</v>
-      </c>
-      <c r="E1317" s="2" t="s">
-        <v>6120</v>
-      </c>
-      <c r="F1317" s="2" t="s">
-        <v>6607</v>
       </c>
       <c r="G1317" s="3">
         <v>2</v>
       </c>
       <c r="H1317" s="2" t="s">
-        <v>6121</v>
+        <v>6120</v>
       </c>
       <c r="I1317" s="2" t="s">
         <v>805</v>
@@ -60206,25 +60207,25 @@
         <v>1317</v>
       </c>
       <c r="B1318" s="2" t="s">
+        <v>6121</v>
+      </c>
+      <c r="C1318" s="2" t="s">
         <v>6122</v>
       </c>
-      <c r="C1318" s="2" t="s">
+      <c r="D1318" s="2" t="s">
         <v>6123</v>
       </c>
-      <c r="D1318" s="2" t="s">
+      <c r="E1318" s="2" t="s">
         <v>6124</v>
       </c>
-      <c r="E1318" s="2" t="s">
+      <c r="F1318" s="2" t="s">
         <v>6125</v>
-      </c>
-      <c r="F1318" s="2" t="s">
-        <v>6126</v>
       </c>
       <c r="G1318" s="3">
         <v>1</v>
       </c>
       <c r="H1318" s="2" t="s">
-        <v>6127</v>
+        <v>6126</v>
       </c>
       <c r="I1318" s="2" t="s">
         <v>15</v>
@@ -60235,10 +60236,10 @@
         <v>1318</v>
       </c>
       <c r="B1319" s="2" t="s">
+        <v>6127</v>
+      </c>
+      <c r="C1319" s="2" t="s">
         <v>6128</v>
-      </c>
-      <c r="C1319" s="2" t="s">
-        <v>6129</v>
       </c>
       <c r="D1319" s="2" t="s">
         <v>325</v>
@@ -60247,13 +60248,13 @@
         <v>326</v>
       </c>
       <c r="F1319" s="2" t="s">
-        <v>6130</v>
+        <v>6129</v>
       </c>
       <c r="G1319" s="3">
         <v>1</v>
       </c>
       <c r="H1319" s="2" t="s">
-        <v>6131</v>
+        <v>6130</v>
       </c>
       <c r="I1319" s="2" t="s">
         <v>151</v>
@@ -60264,7 +60265,7 @@
         <v>1319</v>
       </c>
       <c r="B1320" s="2" t="s">
-        <v>6132</v>
+        <v>6131</v>
       </c>
       <c r="C1320" s="2" t="s">
         <v>232</v>
@@ -60273,16 +60274,16 @@
         <v>716</v>
       </c>
       <c r="E1320" s="2" t="s">
+        <v>6132</v>
+      </c>
+      <c r="F1320" s="2" t="s">
         <v>6133</v>
-      </c>
-      <c r="F1320" s="2" t="s">
-        <v>6134</v>
       </c>
       <c r="G1320" s="3">
         <v>2</v>
       </c>
       <c r="H1320" s="2" t="s">
-        <v>6135</v>
+        <v>6134</v>
       </c>
       <c r="I1320" s="2" t="s">
         <v>15</v>
@@ -60293,7 +60294,7 @@
         <v>1320</v>
       </c>
       <c r="B1321" s="2" t="s">
-        <v>6136</v>
+        <v>6135</v>
       </c>
       <c r="C1321" s="2" t="s">
         <v>1351</v>
@@ -60322,25 +60323,25 @@
         <v>1321</v>
       </c>
       <c r="B1322" s="2" t="s">
+        <v>6136</v>
+      </c>
+      <c r="C1322" s="2" t="s">
+        <v>6530</v>
+      </c>
+      <c r="D1322" s="2" t="s">
         <v>6137</v>
       </c>
-      <c r="C1322" s="2" t="s">
+      <c r="E1322" s="2" t="s">
+        <v>6138</v>
+      </c>
+      <c r="F1322" s="2" t="s">
         <v>6531</v>
-      </c>
-      <c r="D1322" s="2" t="s">
-        <v>6138</v>
-      </c>
-      <c r="E1322" s="2" t="s">
-        <v>6139</v>
-      </c>
-      <c r="F1322" s="2" t="s">
-        <v>6532</v>
       </c>
       <c r="G1322" s="3">
         <v>4</v>
       </c>
       <c r="H1322" s="2" t="s">
-        <v>6140</v>
+        <v>6139</v>
       </c>
       <c r="I1322" s="2" t="s">
         <v>805</v>
@@ -60351,7 +60352,7 @@
         <v>1322</v>
       </c>
       <c r="B1323" s="2" t="s">
-        <v>6141</v>
+        <v>6140</v>
       </c>
       <c r="C1323" s="2" t="s">
         <v>1353</v>
@@ -60360,16 +60361,16 @@
         <v>1351</v>
       </c>
       <c r="E1323" s="2" t="s">
+        <v>6141</v>
+      </c>
+      <c r="F1323" s="2" t="s">
         <v>6142</v>
-      </c>
-      <c r="F1323" s="2" t="s">
-        <v>6143</v>
       </c>
       <c r="G1323" s="3">
         <v>3</v>
       </c>
       <c r="H1323" s="2" t="s">
-        <v>6144</v>
+        <v>6143</v>
       </c>
       <c r="I1323" s="2" t="s">
         <v>805</v>
@@ -60380,16 +60381,16 @@
         <v>1323</v>
       </c>
       <c r="B1324" s="2" t="s">
-        <v>6820</v>
+        <v>6819</v>
       </c>
       <c r="C1324" s="2" t="s">
+        <v>6144</v>
+      </c>
+      <c r="D1324" s="2" t="s">
         <v>6145</v>
       </c>
-      <c r="D1324" s="2" t="s">
+      <c r="E1324" s="2" t="s">
         <v>6146</v>
-      </c>
-      <c r="E1324" s="2" t="s">
-        <v>6147</v>
       </c>
       <c r="F1324" s="2" t="s">
         <v>51</v>
@@ -60409,7 +60410,7 @@
         <v>1324</v>
       </c>
       <c r="B1325" s="2" t="s">
-        <v>6148</v>
+        <v>6147</v>
       </c>
       <c r="C1325" s="2" t="s">
         <v>1351</v>
@@ -60438,7 +60439,7 @@
         <v>1325</v>
       </c>
       <c r="B1326" s="2" t="s">
-        <v>6149</v>
+        <v>6148</v>
       </c>
       <c r="C1326" s="2" t="s">
         <v>1351</v>
@@ -60447,14 +60448,14 @@
         <v>1352</v>
       </c>
       <c r="E1326" s="2" t="s">
-        <v>6150</v>
+        <v>6149</v>
       </c>
       <c r="F1326" s="2"/>
       <c r="G1326" s="3">
         <v>1</v>
       </c>
       <c r="H1326" s="2" t="s">
-        <v>6151</v>
+        <v>6150</v>
       </c>
       <c r="I1326" s="2" t="s">
         <v>805</v>
@@ -60465,25 +60466,25 @@
         <v>1326</v>
       </c>
       <c r="B1327" s="2" t="s">
-        <v>6928</v>
+        <v>6927</v>
       </c>
       <c r="C1327" s="2" t="s">
-        <v>6152</v>
+        <v>6151</v>
       </c>
       <c r="D1327" s="2" t="s">
-        <v>6142</v>
+        <v>6141</v>
       </c>
       <c r="E1327" s="2" t="s">
         <v>1351</v>
       </c>
       <c r="F1327" s="2" t="s">
-        <v>6929</v>
+        <v>6928</v>
       </c>
       <c r="G1327" s="3">
         <v>3</v>
       </c>
       <c r="H1327" s="2" t="s">
-        <v>6153</v>
+        <v>6152</v>
       </c>
       <c r="I1327" s="2" t="s">
         <v>15</v>
@@ -60494,13 +60495,13 @@
         <v>1327</v>
       </c>
       <c r="B1328" s="2" t="s">
-        <v>6154</v>
+        <v>6153</v>
       </c>
       <c r="C1328" s="2" t="s">
         <v>1351</v>
       </c>
       <c r="D1328" s="2" t="s">
-        <v>6155</v>
+        <v>6154</v>
       </c>
       <c r="E1328" s="2" t="s">
         <v>1353</v>
@@ -60512,7 +60513,7 @@
         <v>2</v>
       </c>
       <c r="H1328" s="2" t="s">
-        <v>6156</v>
+        <v>6155</v>
       </c>
       <c r="I1328" s="2" t="s">
         <v>780</v>
@@ -60523,13 +60524,13 @@
         <v>1328</v>
       </c>
       <c r="B1329" s="2" t="s">
-        <v>6990</v>
+        <v>6989</v>
       </c>
       <c r="C1329" s="2" t="s">
         <v>1351</v>
       </c>
       <c r="D1329" s="2" t="s">
-        <v>6142</v>
+        <v>6141</v>
       </c>
       <c r="E1329" s="2" t="s">
         <v>1353</v>
@@ -60552,13 +60553,13 @@
         <v>1329</v>
       </c>
       <c r="B1330" s="2" t="s">
-        <v>6157</v>
+        <v>6156</v>
       </c>
       <c r="C1330" s="2" t="s">
         <v>1351</v>
       </c>
       <c r="D1330" s="2" t="s">
-        <v>6142</v>
+        <v>6141</v>
       </c>
       <c r="E1330" s="2" t="s">
         <v>1353</v>
@@ -60581,13 +60582,13 @@
         <v>1330</v>
       </c>
       <c r="B1331" s="2" t="s">
-        <v>6989</v>
+        <v>6988</v>
       </c>
       <c r="C1331" s="2" t="s">
         <v>1351</v>
       </c>
       <c r="D1331" s="2" t="s">
-        <v>6142</v>
+        <v>6141</v>
       </c>
       <c r="E1331" s="2" t="s">
         <v>1353</v>
@@ -60599,7 +60600,7 @@
         <v>2</v>
       </c>
       <c r="H1331" s="2" t="s">
-        <v>6158</v>
+        <v>6157</v>
       </c>
       <c r="I1331" s="2" t="s">
         <v>15</v>
@@ -60610,25 +60611,25 @@
         <v>1331</v>
       </c>
       <c r="B1332" s="2" t="s">
-        <v>6963</v>
+        <v>6962</v>
       </c>
       <c r="C1332" s="2" t="s">
+        <v>6158</v>
+      </c>
+      <c r="D1332" s="2" t="s">
+        <v>6961</v>
+      </c>
+      <c r="E1332" s="2" t="s">
         <v>6159</v>
       </c>
-      <c r="D1332" s="2" t="s">
-        <v>6962</v>
-      </c>
-      <c r="E1332" s="2" t="s">
+      <c r="F1332" s="2" t="s">
         <v>6160</v>
-      </c>
-      <c r="F1332" s="2" t="s">
-        <v>6161</v>
       </c>
       <c r="G1332" s="3">
         <v>4</v>
       </c>
       <c r="H1332" s="2" t="s">
-        <v>6162</v>
+        <v>6161</v>
       </c>
       <c r="I1332" s="2" t="s">
         <v>22</v>
@@ -60639,16 +60640,16 @@
         <v>1332</v>
       </c>
       <c r="B1333" s="2" t="s">
-        <v>6163</v>
+        <v>6162</v>
       </c>
       <c r="C1333" s="2" t="s">
         <v>77</v>
       </c>
       <c r="D1333" s="2" t="s">
+        <v>6163</v>
+      </c>
+      <c r="E1333" s="2" t="s">
         <v>6164</v>
-      </c>
-      <c r="E1333" s="2" t="s">
-        <v>6165</v>
       </c>
       <c r="F1333" s="2" t="s">
         <v>2238</v>
@@ -60668,7 +60669,7 @@
         <v>1333</v>
       </c>
       <c r="B1334" s="2" t="s">
-        <v>6166</v>
+        <v>6165</v>
       </c>
       <c r="C1334" s="2" t="s">
         <v>12</v>
@@ -60680,13 +60681,13 @@
         <v>439</v>
       </c>
       <c r="F1334" s="2" t="s">
-        <v>6167</v>
+        <v>6166</v>
       </c>
       <c r="G1334" s="3">
         <v>1</v>
       </c>
       <c r="H1334" s="2" t="s">
-        <v>6168</v>
+        <v>6167</v>
       </c>
       <c r="I1334" s="2" t="s">
         <v>805</v>
@@ -60697,16 +60698,16 @@
         <v>1334</v>
       </c>
       <c r="B1335" s="2" t="s">
+        <v>6168</v>
+      </c>
+      <c r="C1335" s="2" t="s">
         <v>6169</v>
       </c>
-      <c r="C1335" s="2" t="s">
+      <c r="D1335" s="2" t="s">
         <v>6170</v>
       </c>
-      <c r="D1335" s="2" t="s">
+      <c r="E1335" s="2" t="s">
         <v>6171</v>
-      </c>
-      <c r="E1335" s="2" t="s">
-        <v>6172</v>
       </c>
       <c r="F1335" s="2" t="s">
         <v>190</v>
@@ -60726,7 +60727,7 @@
         <v>1335</v>
       </c>
       <c r="B1336" s="2" t="s">
-        <v>6173</v>
+        <v>6172</v>
       </c>
       <c r="C1336" s="2" t="s">
         <v>4861</v>
@@ -60735,16 +60736,16 @@
         <v>4777</v>
       </c>
       <c r="E1336" s="2" t="s">
+        <v>6173</v>
+      </c>
+      <c r="F1336" s="2" t="s">
         <v>6174</v>
-      </c>
-      <c r="F1336" s="2" t="s">
-        <v>6175</v>
       </c>
       <c r="G1336" s="3">
         <v>3</v>
       </c>
       <c r="H1336" s="2" t="s">
-        <v>6176</v>
+        <v>6175</v>
       </c>
       <c r="I1336" s="2" t="s">
         <v>15</v>
@@ -60755,25 +60756,25 @@
         <v>1336</v>
       </c>
       <c r="B1337" s="2" t="s">
+        <v>6176</v>
+      </c>
+      <c r="C1337" s="2" t="s">
         <v>6177</v>
       </c>
-      <c r="C1337" s="2" t="s">
+      <c r="D1337" s="2" t="s">
         <v>6178</v>
       </c>
-      <c r="D1337" s="2" t="s">
+      <c r="E1337" s="2" t="s">
         <v>6179</v>
       </c>
-      <c r="E1337" s="2" t="s">
+      <c r="F1337" s="2" t="s">
         <v>6180</v>
-      </c>
-      <c r="F1337" s="2" t="s">
-        <v>6181</v>
       </c>
       <c r="G1337" s="3">
         <v>3</v>
       </c>
       <c r="H1337" s="2" t="s">
-        <v>6182</v>
+        <v>6181</v>
       </c>
       <c r="I1337" s="2" t="s">
         <v>805</v>
@@ -60784,7 +60785,7 @@
         <v>1337</v>
       </c>
       <c r="B1338" s="2" t="s">
-        <v>6183</v>
+        <v>6182</v>
       </c>
       <c r="C1338" s="2" t="s">
         <v>498</v>
@@ -60796,13 +60797,13 @@
         <v>4777</v>
       </c>
       <c r="F1338" s="2" t="s">
-        <v>6184</v>
+        <v>6183</v>
       </c>
       <c r="G1338" s="3">
         <v>4</v>
       </c>
       <c r="H1338" s="2" t="s">
-        <v>6185</v>
+        <v>6184</v>
       </c>
       <c r="I1338" s="2" t="s">
         <v>22</v>
@@ -60813,7 +60814,7 @@
         <v>1338</v>
       </c>
       <c r="B1339" s="2" t="s">
-        <v>6186</v>
+        <v>6185</v>
       </c>
       <c r="C1339" s="2" t="s">
         <v>77</v>
@@ -60822,16 +60823,16 @@
         <v>552</v>
       </c>
       <c r="E1339" s="2" t="s">
+        <v>6186</v>
+      </c>
+      <c r="F1339" s="2" t="s">
         <v>6187</v>
-      </c>
-      <c r="F1339" s="2" t="s">
-        <v>6188</v>
       </c>
       <c r="G1339" s="3">
         <v>2</v>
       </c>
       <c r="H1339" s="2" t="s">
-        <v>6189</v>
+        <v>6188</v>
       </c>
       <c r="I1339" s="2" t="s">
         <v>805</v>
@@ -60842,7 +60843,7 @@
         <v>1339</v>
       </c>
       <c r="B1340" s="2" t="s">
-        <v>6190</v>
+        <v>6189</v>
       </c>
       <c r="C1340" s="2" t="s">
         <v>314</v>
@@ -60854,13 +60855,13 @@
         <v>320</v>
       </c>
       <c r="F1340" s="2" t="s">
-        <v>6191</v>
+        <v>6190</v>
       </c>
       <c r="G1340" s="3">
         <v>2</v>
       </c>
       <c r="H1340" s="2" t="s">
-        <v>6192</v>
+        <v>6191</v>
       </c>
       <c r="I1340" s="2" t="s">
         <v>805</v>
@@ -60871,25 +60872,25 @@
         <v>1340</v>
       </c>
       <c r="B1341" s="2" t="s">
+        <v>6192</v>
+      </c>
+      <c r="C1341" s="2" t="s">
         <v>6193</v>
       </c>
-      <c r="C1341" s="2" t="s">
+      <c r="D1341" s="2" t="s">
         <v>6194</v>
       </c>
-      <c r="D1341" s="2" t="s">
+      <c r="E1341" s="2" t="s">
+        <v>6177</v>
+      </c>
+      <c r="F1341" s="2" t="s">
         <v>6195</v>
-      </c>
-      <c r="E1341" s="2" t="s">
-        <v>6178</v>
-      </c>
-      <c r="F1341" s="2" t="s">
-        <v>6196</v>
       </c>
       <c r="G1341" s="3">
         <v>4</v>
       </c>
       <c r="H1341" s="2" t="s">
-        <v>6197</v>
+        <v>6196</v>
       </c>
       <c r="I1341" s="2" t="s">
         <v>805</v>
@@ -60900,16 +60901,16 @@
         <v>1341</v>
       </c>
       <c r="B1342" s="2" t="s">
+        <v>6197</v>
+      </c>
+      <c r="C1342" s="2" t="s">
         <v>6198</v>
       </c>
-      <c r="C1342" s="2" t="s">
+      <c r="D1342" s="2" t="s">
         <v>6199</v>
       </c>
-      <c r="D1342" s="2" t="s">
+      <c r="E1342" s="2" t="s">
         <v>6200</v>
-      </c>
-      <c r="E1342" s="2" t="s">
-        <v>6201</v>
       </c>
       <c r="F1342" s="2" t="s">
         <v>190</v>
@@ -60929,25 +60930,25 @@
         <v>1342</v>
       </c>
       <c r="B1343" s="2" t="s">
+        <v>6201</v>
+      </c>
+      <c r="C1343" s="2" t="s">
         <v>6202</v>
       </c>
-      <c r="C1343" s="2" t="s">
+      <c r="D1343" s="2" t="s">
         <v>6203</v>
       </c>
-      <c r="D1343" s="2" t="s">
+      <c r="E1343" s="2" t="s">
         <v>6204</v>
       </c>
-      <c r="E1343" s="2" t="s">
+      <c r="F1343" s="2" t="s">
         <v>6205</v>
-      </c>
-      <c r="F1343" s="2" t="s">
-        <v>6206</v>
       </c>
       <c r="G1343" s="3">
         <v>3</v>
       </c>
       <c r="H1343" s="2" t="s">
-        <v>6207</v>
+        <v>6206</v>
       </c>
       <c r="I1343" s="2" t="s">
         <v>805</v>
@@ -60958,25 +60959,25 @@
         <v>1343</v>
       </c>
       <c r="B1344" s="2" t="s">
+        <v>6207</v>
+      </c>
+      <c r="C1344" s="2" t="s">
         <v>6208</v>
       </c>
-      <c r="C1344" s="2" t="s">
+      <c r="D1344" s="2" t="s">
         <v>6209</v>
       </c>
-      <c r="D1344" s="2" t="s">
+      <c r="E1344" s="2" t="s">
         <v>6210</v>
       </c>
-      <c r="E1344" s="2" t="s">
+      <c r="F1344" s="2" t="s">
         <v>6211</v>
-      </c>
-      <c r="F1344" s="2" t="s">
-        <v>6212</v>
       </c>
       <c r="G1344" s="3">
         <v>4</v>
       </c>
       <c r="H1344" s="2" t="s">
-        <v>6213</v>
+        <v>6212</v>
       </c>
       <c r="I1344" s="2" t="s">
         <v>805</v>
@@ -60987,7 +60988,7 @@
         <v>1344</v>
       </c>
       <c r="B1345" s="2" t="s">
-        <v>6214</v>
+        <v>6213</v>
       </c>
       <c r="C1345" s="2" t="s">
         <v>496</v>
@@ -60996,7 +60997,7 @@
         <v>495</v>
       </c>
       <c r="E1345" s="2" t="s">
-        <v>6215</v>
+        <v>6214</v>
       </c>
       <c r="F1345" s="2"/>
       <c r="G1345" s="3">
@@ -61014,25 +61015,25 @@
         <v>1345</v>
       </c>
       <c r="B1346" s="2" t="s">
+        <v>6215</v>
+      </c>
+      <c r="C1346" s="2" t="s">
         <v>6216</v>
       </c>
-      <c r="C1346" s="2" t="s">
+      <c r="D1346" s="2" t="s">
         <v>6217</v>
       </c>
-      <c r="D1346" s="2" t="s">
+      <c r="E1346" s="2" t="s">
         <v>6218</v>
       </c>
-      <c r="E1346" s="2" t="s">
+      <c r="F1346" s="2" t="s">
         <v>6219</v>
-      </c>
-      <c r="F1346" s="2" t="s">
-        <v>6220</v>
       </c>
       <c r="G1346" s="3">
         <v>4</v>
       </c>
       <c r="H1346" s="2" t="s">
-        <v>6221</v>
+        <v>6220</v>
       </c>
       <c r="I1346" s="2" t="s">
         <v>15</v>
@@ -61043,25 +61044,25 @@
         <v>1346</v>
       </c>
       <c r="B1347" s="2" t="s">
-        <v>6222</v>
+        <v>6221</v>
       </c>
       <c r="C1347" s="2" t="s">
         <v>1406</v>
       </c>
       <c r="D1347" s="2" t="s">
-        <v>6223</v>
+        <v>6222</v>
       </c>
       <c r="E1347" s="2" t="s">
         <v>1092</v>
       </c>
       <c r="F1347" s="2" t="s">
-        <v>6224</v>
+        <v>6223</v>
       </c>
       <c r="G1347" s="3">
         <v>2</v>
       </c>
       <c r="H1347" s="2" t="s">
-        <v>6225</v>
+        <v>6224</v>
       </c>
       <c r="I1347" s="2" t="s">
         <v>805</v>
@@ -61072,25 +61073,25 @@
         <v>1347</v>
       </c>
       <c r="B1348" s="2" t="s">
+        <v>6225</v>
+      </c>
+      <c r="C1348" s="2" t="s">
         <v>6226</v>
       </c>
-      <c r="C1348" s="2" t="s">
+      <c r="D1348" s="2" t="s">
         <v>6227</v>
       </c>
-      <c r="D1348" s="2" t="s">
+      <c r="E1348" s="2" t="s">
         <v>6228</v>
       </c>
-      <c r="E1348" s="2" t="s">
+      <c r="F1348" s="2" t="s">
         <v>6229</v>
-      </c>
-      <c r="F1348" s="2" t="s">
-        <v>6230</v>
       </c>
       <c r="G1348" s="3">
         <v>4</v>
       </c>
       <c r="H1348" s="2" t="s">
-        <v>6231</v>
+        <v>6230</v>
       </c>
       <c r="I1348" s="2" t="s">
         <v>805</v>
@@ -61101,13 +61102,13 @@
         <v>1348</v>
       </c>
       <c r="B1349" s="2" t="s">
-        <v>6232</v>
+        <v>6231</v>
       </c>
       <c r="C1349" s="2" t="s">
         <v>117</v>
       </c>
       <c r="D1349" s="2" t="s">
-        <v>6233</v>
+        <v>6232</v>
       </c>
       <c r="E1349" s="2" t="s">
         <v>26</v>
@@ -61119,7 +61120,7 @@
         <v>4</v>
       </c>
       <c r="H1349" s="2" t="s">
-        <v>6234</v>
+        <v>6233</v>
       </c>
       <c r="I1349" s="2" t="s">
         <v>805</v>
@@ -61130,25 +61131,25 @@
         <v>1349</v>
       </c>
       <c r="B1350" s="2" t="s">
+        <v>6234</v>
+      </c>
+      <c r="C1350" s="2" t="s">
         <v>6235</v>
       </c>
-      <c r="C1350" s="2" t="s">
+      <c r="D1350" s="2" t="s">
         <v>6236</v>
       </c>
-      <c r="D1350" s="2" t="s">
+      <c r="E1350" s="2" t="s">
         <v>6237</v>
       </c>
-      <c r="E1350" s="2" t="s">
+      <c r="F1350" s="2" t="s">
         <v>6238</v>
-      </c>
-      <c r="F1350" s="2" t="s">
-        <v>6239</v>
       </c>
       <c r="G1350" s="3">
         <v>4</v>
       </c>
       <c r="H1350" s="2" t="s">
-        <v>6240</v>
+        <v>6239</v>
       </c>
       <c r="I1350" s="2" t="s">
         <v>22</v>
@@ -61159,7 +61160,7 @@
         <v>1350</v>
       </c>
       <c r="B1351" s="2" t="s">
-        <v>6241</v>
+        <v>6240</v>
       </c>
       <c r="C1351" s="2" t="s">
         <v>755</v>
@@ -61168,7 +61169,7 @@
         <v>393</v>
       </c>
       <c r="E1351" s="2" t="s">
-        <v>6242</v>
+        <v>6241</v>
       </c>
       <c r="F1351" s="2" t="s">
         <v>773</v>
@@ -61177,7 +61178,7 @@
         <v>1</v>
       </c>
       <c r="H1351" s="2" t="s">
-        <v>6243</v>
+        <v>6242</v>
       </c>
       <c r="I1351" s="2" t="s">
         <v>22</v>
@@ -61188,25 +61189,25 @@
         <v>1351</v>
       </c>
       <c r="B1352" s="2" t="s">
+        <v>6243</v>
+      </c>
+      <c r="C1352" s="2" t="s">
         <v>6244</v>
       </c>
-      <c r="C1352" s="2" t="s">
+      <c r="D1352" s="2" t="s">
         <v>6245</v>
       </c>
-      <c r="D1352" s="2" t="s">
+      <c r="E1352" s="2" t="s">
         <v>6246</v>
       </c>
-      <c r="E1352" s="2" t="s">
+      <c r="F1352" s="2" t="s">
         <v>6247</v>
-      </c>
-      <c r="F1352" s="2" t="s">
-        <v>6248</v>
       </c>
       <c r="G1352" s="3">
         <v>1</v>
       </c>
       <c r="H1352" s="2" t="s">
-        <v>6249</v>
+        <v>6248</v>
       </c>
       <c r="I1352" s="2" t="s">
         <v>22</v>
@@ -61217,7 +61218,7 @@
         <v>1352</v>
       </c>
       <c r="B1353" s="2" t="s">
-        <v>6250</v>
+        <v>6249</v>
       </c>
       <c r="C1353" s="2" t="s">
         <v>153</v>
@@ -61235,7 +61236,7 @@
         <v>1</v>
       </c>
       <c r="H1353" s="2" t="s">
-        <v>6251</v>
+        <v>6250</v>
       </c>
       <c r="I1353" s="2" t="s">
         <v>15</v>
@@ -61246,23 +61247,23 @@
         <v>1353</v>
       </c>
       <c r="B1354" s="2" t="s">
+        <v>6251</v>
+      </c>
+      <c r="C1354" s="2" t="s">
         <v>6252</v>
       </c>
-      <c r="C1354" s="2" t="s">
+      <c r="D1354" s="2" t="s">
         <v>6253</v>
       </c>
-      <c r="D1354" s="2" t="s">
+      <c r="E1354" s="2" t="s">
         <v>6254</v>
-      </c>
-      <c r="E1354" s="2" t="s">
-        <v>6255</v>
       </c>
       <c r="F1354" s="2"/>
       <c r="G1354" s="3">
         <v>1</v>
       </c>
       <c r="H1354" s="2" t="s">
-        <v>6256</v>
+        <v>6255</v>
       </c>
       <c r="I1354" s="2" t="s">
         <v>805</v>
@@ -61273,25 +61274,25 @@
         <v>1354</v>
       </c>
       <c r="B1355" s="2" t="s">
-        <v>6257</v>
+        <v>6256</v>
       </c>
       <c r="C1355" s="2" t="s">
+        <v>6715</v>
+      </c>
+      <c r="D1355" s="2" t="s">
+        <v>6714</v>
+      </c>
+      <c r="E1355" s="2" t="s">
+        <v>6717</v>
+      </c>
+      <c r="F1355" s="2" t="s">
         <v>6716</v>
-      </c>
-      <c r="D1355" s="2" t="s">
-        <v>6715</v>
-      </c>
-      <c r="E1355" s="2" t="s">
-        <v>6718</v>
-      </c>
-      <c r="F1355" s="2" t="s">
-        <v>6717</v>
       </c>
       <c r="G1355" s="3">
         <v>4</v>
       </c>
       <c r="H1355" s="2" t="s">
-        <v>6258</v>
+        <v>6257</v>
       </c>
       <c r="I1355" s="2" t="s">
         <v>805</v>
@@ -61302,25 +61303,25 @@
         <v>1355</v>
       </c>
       <c r="B1356" s="2" t="s">
+        <v>6258</v>
+      </c>
+      <c r="C1356" s="2" t="s">
         <v>6259</v>
       </c>
-      <c r="C1356" s="2" t="s">
+      <c r="D1356" s="2" t="s">
         <v>6260</v>
       </c>
-      <c r="D1356" s="2" t="s">
+      <c r="E1356" s="2" t="s">
         <v>6261</v>
       </c>
-      <c r="E1356" s="2" t="s">
+      <c r="F1356" s="2" t="s">
         <v>6262</v>
-      </c>
-      <c r="F1356" s="2" t="s">
-        <v>6263</v>
       </c>
       <c r="G1356" s="3">
         <v>2</v>
       </c>
       <c r="H1356" s="2" t="s">
-        <v>6264</v>
+        <v>6263</v>
       </c>
       <c r="I1356" s="2" t="s">
         <v>805</v>
@@ -61331,25 +61332,25 @@
         <v>1356</v>
       </c>
       <c r="B1357" s="2" t="s">
+        <v>6264</v>
+      </c>
+      <c r="C1357" s="2" t="s">
         <v>6265</v>
       </c>
-      <c r="C1357" s="2" t="s">
+      <c r="D1357" s="2" t="s">
         <v>6266</v>
       </c>
-      <c r="D1357" s="2" t="s">
+      <c r="E1357" s="2" t="s">
         <v>6267</v>
       </c>
-      <c r="E1357" s="2" t="s">
+      <c r="F1357" s="2" t="s">
         <v>6268</v>
-      </c>
-      <c r="F1357" s="2" t="s">
-        <v>6269</v>
       </c>
       <c r="G1357" s="3">
         <v>2</v>
       </c>
       <c r="H1357" s="2" t="s">
-        <v>6270</v>
+        <v>6269</v>
       </c>
       <c r="I1357" s="2" t="s">
         <v>805</v>
@@ -61360,25 +61361,25 @@
         <v>1357</v>
       </c>
       <c r="B1358" s="2" t="s">
+        <v>6270</v>
+      </c>
+      <c r="C1358" s="2" t="s">
         <v>6271</v>
       </c>
-      <c r="C1358" s="2" t="s">
+      <c r="D1358" s="2" t="s">
         <v>6272</v>
       </c>
-      <c r="D1358" s="2" t="s">
+      <c r="E1358" s="2" t="s">
         <v>6273</v>
       </c>
-      <c r="E1358" s="2" t="s">
+      <c r="F1358" s="2" t="s">
         <v>6274</v>
-      </c>
-      <c r="F1358" s="2" t="s">
-        <v>6275</v>
       </c>
       <c r="G1358" s="3">
         <v>4</v>
       </c>
       <c r="H1358" s="2" t="s">
-        <v>6276</v>
+        <v>6275</v>
       </c>
       <c r="I1358" s="2" t="s">
         <v>805</v>
@@ -61389,25 +61390,25 @@
         <v>1358</v>
       </c>
       <c r="B1359" s="2" t="s">
+        <v>6276</v>
+      </c>
+      <c r="C1359" s="2" t="s">
         <v>6277</v>
       </c>
-      <c r="C1359" s="2" t="s">
+      <c r="D1359" s="2" t="s">
         <v>6278</v>
       </c>
-      <c r="D1359" s="2" t="s">
+      <c r="E1359" s="2" t="s">
         <v>6279</v>
       </c>
-      <c r="E1359" s="2" t="s">
+      <c r="F1359" s="2" t="s">
         <v>6280</v>
-      </c>
-      <c r="F1359" s="2" t="s">
-        <v>6281</v>
       </c>
       <c r="G1359" s="3">
         <v>4</v>
       </c>
       <c r="H1359" s="2" t="s">
-        <v>6282</v>
+        <v>6281</v>
       </c>
       <c r="I1359" s="2" t="s">
         <v>805</v>
@@ -61418,25 +61419,25 @@
         <v>1359</v>
       </c>
       <c r="B1360" s="2" t="s">
+        <v>6282</v>
+      </c>
+      <c r="C1360" s="2" t="s">
+        <v>6924</v>
+      </c>
+      <c r="D1360" s="2" t="s">
+        <v>6925</v>
+      </c>
+      <c r="E1360" s="2" t="s">
         <v>6283</v>
       </c>
-      <c r="C1360" s="2" t="s">
-        <v>6925</v>
-      </c>
-      <c r="D1360" s="2" t="s">
+      <c r="F1360" s="2" t="s">
         <v>6926</v>
-      </c>
-      <c r="E1360" s="2" t="s">
-        <v>6284</v>
-      </c>
-      <c r="F1360" s="2" t="s">
-        <v>6927</v>
       </c>
       <c r="G1360" s="3">
         <v>1</v>
       </c>
       <c r="H1360" s="2" t="s">
-        <v>6285</v>
+        <v>6284</v>
       </c>
       <c r="I1360" s="2" t="s">
         <v>805</v>
@@ -61447,25 +61448,25 @@
         <v>1360</v>
       </c>
       <c r="B1361" s="2" t="s">
+        <v>6285</v>
+      </c>
+      <c r="C1361" s="2" t="s">
         <v>6286</v>
       </c>
-      <c r="C1361" s="2" t="s">
+      <c r="D1361" s="2" t="s">
         <v>6287</v>
       </c>
-      <c r="D1361" s="2" t="s">
+      <c r="E1361" s="2" t="s">
         <v>6288</v>
       </c>
-      <c r="E1361" s="2" t="s">
+      <c r="F1361" s="2" t="s">
         <v>6289</v>
-      </c>
-      <c r="F1361" s="2" t="s">
-        <v>6290</v>
       </c>
       <c r="G1361" s="3">
         <v>3</v>
       </c>
       <c r="H1361" s="2" t="s">
-        <v>6291</v>
+        <v>6290</v>
       </c>
       <c r="I1361" s="2" t="s">
         <v>15</v>
@@ -61476,7 +61477,7 @@
         <v>1361</v>
       </c>
       <c r="B1362" s="2" t="s">
-        <v>6292</v>
+        <v>6291</v>
       </c>
       <c r="C1362" s="2" t="s">
         <v>1284</v>
@@ -61485,10 +61486,10 @@
         <v>1285</v>
       </c>
       <c r="E1362" s="2" t="s">
+        <v>6292</v>
+      </c>
+      <c r="F1362" s="2" t="s">
         <v>6293</v>
-      </c>
-      <c r="F1362" s="2" t="s">
-        <v>6294</v>
       </c>
       <c r="G1362" s="3">
         <v>1</v>
@@ -61505,25 +61506,25 @@
         <v>1362</v>
       </c>
       <c r="B1363" s="2" t="s">
+        <v>6294</v>
+      </c>
+      <c r="C1363" s="2" t="s">
         <v>6295</v>
       </c>
-      <c r="C1363" s="2" t="s">
+      <c r="D1363" s="2" t="s">
         <v>6296</v>
       </c>
-      <c r="D1363" s="2" t="s">
+      <c r="E1363" s="2" t="s">
         <v>6297</v>
       </c>
-      <c r="E1363" s="2" t="s">
+      <c r="F1363" s="2" t="s">
         <v>6298</v>
-      </c>
-      <c r="F1363" s="2" t="s">
-        <v>6299</v>
       </c>
       <c r="G1363" s="3">
         <v>2</v>
       </c>
       <c r="H1363" s="2" t="s">
-        <v>6300</v>
+        <v>6299</v>
       </c>
       <c r="I1363" s="2" t="s">
         <v>15</v>
@@ -61534,25 +61535,25 @@
         <v>1363</v>
       </c>
       <c r="B1364" s="2" t="s">
+        <v>6300</v>
+      </c>
+      <c r="C1364" s="2" t="s">
         <v>6301</v>
       </c>
-      <c r="C1364" s="2" t="s">
+      <c r="D1364" s="2" t="s">
         <v>6302</v>
       </c>
-      <c r="D1364" s="2" t="s">
+      <c r="E1364" s="2" t="s">
         <v>6303</v>
       </c>
-      <c r="E1364" s="2" t="s">
+      <c r="F1364" s="2" t="s">
         <v>6304</v>
-      </c>
-      <c r="F1364" s="2" t="s">
-        <v>6305</v>
       </c>
       <c r="G1364" s="3">
         <v>1</v>
       </c>
       <c r="H1364" s="2" t="s">
-        <v>6306</v>
+        <v>6305</v>
       </c>
       <c r="I1364" s="2" t="s">
         <v>15</v>
@@ -61592,7 +61593,7 @@
         <v>1365</v>
       </c>
       <c r="B1366" s="2" t="s">
-        <v>6307</v>
+        <v>6306</v>
       </c>
       <c r="C1366" s="2" t="s">
         <v>1346</v>
@@ -61610,7 +61611,7 @@
         <v>3</v>
       </c>
       <c r="H1366" s="2" t="s">
-        <v>6308</v>
+        <v>6307</v>
       </c>
       <c r="I1366" s="2" t="s">
         <v>15</v>
@@ -61621,25 +61622,25 @@
         <v>1366</v>
       </c>
       <c r="B1367" s="2" t="s">
+        <v>6308</v>
+      </c>
+      <c r="C1367" s="2" t="s">
         <v>6309</v>
       </c>
-      <c r="C1367" s="2" t="s">
+      <c r="D1367" s="2" t="s">
         <v>6310</v>
       </c>
-      <c r="D1367" s="2" t="s">
+      <c r="E1367" s="2" t="s">
         <v>6311</v>
       </c>
-      <c r="E1367" s="2" t="s">
+      <c r="F1367" s="2" t="s">
         <v>6312</v>
-      </c>
-      <c r="F1367" s="2" t="s">
-        <v>6313</v>
       </c>
       <c r="G1367" s="3">
         <v>3</v>
       </c>
       <c r="H1367" s="2" t="s">
-        <v>6314</v>
+        <v>6313</v>
       </c>
       <c r="I1367" s="2" t="s">
         <v>805</v>
@@ -61650,16 +61651,16 @@
         <v>1367</v>
       </c>
       <c r="B1368" s="2" t="s">
+        <v>6314</v>
+      </c>
+      <c r="C1368" s="2" t="s">
         <v>6315</v>
       </c>
-      <c r="C1368" s="2" t="s">
+      <c r="D1368" s="2" t="s">
         <v>6316</v>
       </c>
-      <c r="D1368" s="2" t="s">
+      <c r="E1368" s="2" t="s">
         <v>6317</v>
-      </c>
-      <c r="E1368" s="2" t="s">
-        <v>6318</v>
       </c>
       <c r="F1368" s="2" t="s">
         <v>51</v>
@@ -61679,25 +61680,25 @@
         <v>1368</v>
       </c>
       <c r="B1369" s="2" t="s">
+        <v>6318</v>
+      </c>
+      <c r="C1369" s="2" t="s">
         <v>6319</v>
       </c>
-      <c r="C1369" s="2" t="s">
+      <c r="D1369" s="2" t="s">
         <v>6320</v>
       </c>
-      <c r="D1369" s="2" t="s">
+      <c r="E1369" s="2" t="s">
         <v>6321</v>
       </c>
-      <c r="E1369" s="2" t="s">
+      <c r="F1369" s="2" t="s">
         <v>6322</v>
-      </c>
-      <c r="F1369" s="2" t="s">
-        <v>6323</v>
       </c>
       <c r="G1369" s="3">
         <v>3</v>
       </c>
       <c r="H1369" s="2" t="s">
-        <v>6324</v>
+        <v>6323</v>
       </c>
       <c r="I1369" s="2" t="s">
         <v>780</v>
@@ -61708,25 +61709,25 @@
         <v>1369</v>
       </c>
       <c r="B1370" s="2" t="s">
-        <v>6325</v>
+        <v>6324</v>
       </c>
       <c r="C1370" s="2" t="s">
         <v>1619</v>
       </c>
       <c r="D1370" s="2" t="s">
+        <v>6325</v>
+      </c>
+      <c r="E1370" s="2" t="s">
         <v>6326</v>
       </c>
-      <c r="E1370" s="2" t="s">
+      <c r="F1370" s="2" t="s">
         <v>6327</v>
-      </c>
-      <c r="F1370" s="2" t="s">
-        <v>6328</v>
       </c>
       <c r="G1370" s="3">
         <v>3</v>
       </c>
       <c r="H1370" s="2" t="s">
-        <v>6329</v>
+        <v>6328</v>
       </c>
       <c r="I1370" s="2" t="s">
         <v>15</v>
@@ -61737,25 +61738,25 @@
         <v>1370</v>
       </c>
       <c r="B1371" s="2" t="s">
+        <v>6329</v>
+      </c>
+      <c r="C1371" s="2" t="s">
         <v>6330</v>
       </c>
-      <c r="C1371" s="2" t="s">
+      <c r="D1371" s="2" t="s">
         <v>6331</v>
       </c>
-      <c r="D1371" s="2" t="s">
+      <c r="E1371" s="2" t="s">
         <v>6332</v>
       </c>
-      <c r="E1371" s="2" t="s">
+      <c r="F1371" s="2" t="s">
         <v>6333</v>
-      </c>
-      <c r="F1371" s="2" t="s">
-        <v>6334</v>
       </c>
       <c r="G1371" s="3">
         <v>2</v>
       </c>
       <c r="H1371" s="2" t="s">
-        <v>6335</v>
+        <v>6334</v>
       </c>
       <c r="I1371" s="2" t="s">
         <v>15</v>
@@ -61766,13 +61767,13 @@
         <v>1371</v>
       </c>
       <c r="B1372" s="2" t="s">
-        <v>6336</v>
+        <v>6335</v>
       </c>
       <c r="C1372" s="2" t="s">
         <v>2327</v>
       </c>
       <c r="D1372" s="2" t="s">
-        <v>6337</v>
+        <v>6336</v>
       </c>
       <c r="E1372" s="2" t="s">
         <v>2328</v>
@@ -61784,7 +61785,7 @@
         <v>2</v>
       </c>
       <c r="H1372" s="2" t="s">
-        <v>6338</v>
+        <v>6337</v>
       </c>
       <c r="I1372" s="2" t="s">
         <v>15</v>
@@ -61795,25 +61796,25 @@
         <v>1372</v>
       </c>
       <c r="B1373" s="2" t="s">
-        <v>6339</v>
+        <v>6338</v>
       </c>
       <c r="C1373" s="2" t="s">
         <v>2268</v>
       </c>
       <c r="D1373" s="2" t="s">
+        <v>6339</v>
+      </c>
+      <c r="E1373" s="2" t="s">
         <v>6340</v>
       </c>
-      <c r="E1373" s="2" t="s">
+      <c r="F1373" s="2" t="s">
         <v>6341</v>
-      </c>
-      <c r="F1373" s="2" t="s">
-        <v>6342</v>
       </c>
       <c r="G1373" s="3">
         <v>2</v>
       </c>
       <c r="H1373" s="2" t="s">
-        <v>6343</v>
+        <v>6342</v>
       </c>
       <c r="I1373" s="2" t="s">
         <v>15</v>
@@ -61824,25 +61825,25 @@
         <v>1373</v>
       </c>
       <c r="B1374" s="2" t="s">
+        <v>6343</v>
+      </c>
+      <c r="C1374" s="2" t="s">
         <v>6344</v>
       </c>
-      <c r="C1374" s="2" t="s">
+      <c r="D1374" s="2" t="s">
         <v>6345</v>
       </c>
-      <c r="D1374" s="2" t="s">
+      <c r="E1374" s="2" t="s">
         <v>6346</v>
       </c>
-      <c r="E1374" s="2" t="s">
+      <c r="F1374" s="2" t="s">
         <v>6347</v>
-      </c>
-      <c r="F1374" s="2" t="s">
-        <v>6348</v>
       </c>
       <c r="G1374" s="3">
         <v>4</v>
       </c>
       <c r="H1374" s="2" t="s">
-        <v>6349</v>
+        <v>6348</v>
       </c>
       <c r="I1374" s="2" t="s">
         <v>15</v>
@@ -61853,25 +61854,25 @@
         <v>1374</v>
       </c>
       <c r="B1375" s="2" t="s">
+        <v>6349</v>
+      </c>
+      <c r="C1375" s="2" t="s">
         <v>6350</v>
       </c>
-      <c r="C1375" s="2" t="s">
+      <c r="D1375" s="2" t="s">
         <v>6351</v>
       </c>
-      <c r="D1375" s="2" t="s">
+      <c r="E1375" s="2" t="s">
         <v>6352</v>
       </c>
-      <c r="E1375" s="2" t="s">
+      <c r="F1375" s="2" t="s">
         <v>6353</v>
-      </c>
-      <c r="F1375" s="2" t="s">
-        <v>6354</v>
       </c>
       <c r="G1375" s="3">
         <v>1</v>
       </c>
       <c r="H1375" s="2" t="s">
-        <v>6355</v>
+        <v>6354</v>
       </c>
       <c r="I1375" s="2" t="s">
         <v>805</v>
@@ -61882,25 +61883,25 @@
         <v>1375</v>
       </c>
       <c r="B1376" s="2" t="s">
-        <v>6853</v>
+        <v>6852</v>
       </c>
       <c r="C1376" s="2" t="s">
+        <v>6355</v>
+      </c>
+      <c r="D1376" s="2" t="s">
         <v>6356</v>
       </c>
-      <c r="D1376" s="2" t="s">
+      <c r="E1376" s="2" t="s">
         <v>6357</v>
       </c>
-      <c r="E1376" s="2" t="s">
+      <c r="F1376" s="2" t="s">
         <v>6358</v>
-      </c>
-      <c r="F1376" s="2" t="s">
-        <v>6359</v>
       </c>
       <c r="G1376" s="3">
         <v>2</v>
       </c>
       <c r="H1376" s="2" t="s">
-        <v>6360</v>
+        <v>6359</v>
       </c>
       <c r="I1376" s="2" t="s">
         <v>805</v>
@@ -61911,25 +61912,25 @@
         <v>1376</v>
       </c>
       <c r="B1377" s="2" t="s">
+        <v>6360</v>
+      </c>
+      <c r="C1377" s="2" t="s">
         <v>6361</v>
       </c>
-      <c r="C1377" s="2" t="s">
+      <c r="D1377" s="2" t="s">
         <v>6362</v>
       </c>
-      <c r="D1377" s="2" t="s">
+      <c r="E1377" s="2" t="s">
         <v>6363</v>
       </c>
-      <c r="E1377" s="2" t="s">
+      <c r="F1377" s="2" t="s">
         <v>6364</v>
-      </c>
-      <c r="F1377" s="2" t="s">
-        <v>6365</v>
       </c>
       <c r="G1377" s="3">
         <v>3</v>
       </c>
       <c r="H1377" s="2" t="s">
-        <v>6366</v>
+        <v>6365</v>
       </c>
       <c r="I1377" s="2" t="s">
         <v>15</v>
@@ -61940,7 +61941,7 @@
         <v>1377</v>
       </c>
       <c r="B1378" s="2" t="s">
-        <v>6367</v>
+        <v>6366</v>
       </c>
       <c r="C1378" s="2" t="s">
         <v>77</v>
@@ -61969,25 +61970,25 @@
         <v>1378</v>
       </c>
       <c r="B1379" s="2" t="s">
+        <v>6663</v>
+      </c>
+      <c r="C1379" s="2" t="s">
         <v>6664</v>
       </c>
-      <c r="C1379" s="2" t="s">
+      <c r="D1379" s="2" t="s">
         <v>6665</v>
       </c>
-      <c r="D1379" s="2" t="s">
+      <c r="E1379" s="2" t="s">
         <v>6666</v>
       </c>
-      <c r="E1379" s="2" t="s">
+      <c r="F1379" s="2" t="s">
         <v>6667</v>
-      </c>
-      <c r="F1379" s="2" t="s">
-        <v>6668</v>
       </c>
       <c r="G1379" s="3">
         <v>1</v>
       </c>
       <c r="H1379" s="2" t="s">
-        <v>6368</v>
+        <v>6367</v>
       </c>
       <c r="I1379" s="2" t="s">
         <v>805</v>
@@ -61998,7 +61999,7 @@
         <v>1379</v>
       </c>
       <c r="B1380" s="2" t="s">
-        <v>6369</v>
+        <v>6368</v>
       </c>
       <c r="C1380" s="2" t="s">
         <v>369</v>
@@ -62016,7 +62017,7 @@
         <v>1</v>
       </c>
       <c r="H1380" s="2" t="s">
-        <v>6370</v>
+        <v>6369</v>
       </c>
       <c r="I1380" s="2" t="s">
         <v>805</v>
@@ -62027,10 +62028,10 @@
         <v>1380</v>
       </c>
       <c r="B1381" s="2" t="s">
+        <v>6370</v>
+      </c>
+      <c r="C1381" s="2" t="s">
         <v>6371</v>
-      </c>
-      <c r="C1381" s="2" t="s">
-        <v>6372</v>
       </c>
       <c r="D1381" s="2" t="s">
         <v>12</v>
@@ -62039,13 +62040,13 @@
         <v>857</v>
       </c>
       <c r="F1381" s="2" t="s">
-        <v>6373</v>
+        <v>6372</v>
       </c>
       <c r="G1381" s="3">
         <v>1</v>
       </c>
       <c r="H1381" s="2" t="s">
-        <v>6374</v>
+        <v>6373</v>
       </c>
       <c r="I1381" s="2" t="s">
         <v>805</v>
@@ -62056,25 +62057,25 @@
         <v>1381</v>
       </c>
       <c r="B1382" s="2" t="s">
+        <v>6374</v>
+      </c>
+      <c r="C1382" s="2" t="s">
         <v>6375</v>
       </c>
-      <c r="C1382" s="2" t="s">
+      <c r="D1382" s="2" t="s">
         <v>6376</v>
       </c>
-      <c r="D1382" s="2" t="s">
+      <c r="E1382" s="2" t="s">
         <v>6377</v>
       </c>
-      <c r="E1382" s="2" t="s">
+      <c r="F1382" s="2" t="s">
         <v>6378</v>
-      </c>
-      <c r="F1382" s="2" t="s">
-        <v>6379</v>
       </c>
       <c r="G1382" s="3">
         <v>2</v>
       </c>
       <c r="H1382" s="2" t="s">
-        <v>6380</v>
+        <v>6379</v>
       </c>
       <c r="I1382" s="2" t="s">
         <v>15</v>
@@ -62085,25 +62086,25 @@
         <v>1382</v>
       </c>
       <c r="B1383" s="2" t="s">
-        <v>6381</v>
+        <v>6380</v>
       </c>
       <c r="C1383" s="2" t="s">
         <v>1416</v>
       </c>
       <c r="D1383" s="2" t="s">
+        <v>6381</v>
+      </c>
+      <c r="E1383" s="2" t="s">
         <v>6382</v>
       </c>
-      <c r="E1383" s="2" t="s">
+      <c r="F1383" s="2" t="s">
         <v>6383</v>
-      </c>
-      <c r="F1383" s="2" t="s">
-        <v>6384</v>
       </c>
       <c r="G1383" s="3">
         <v>4</v>
       </c>
       <c r="H1383" s="2" t="s">
-        <v>6385</v>
+        <v>6384</v>
       </c>
       <c r="I1383" s="2" t="s">
         <v>15</v>
@@ -62114,25 +62115,25 @@
         <v>1383</v>
       </c>
       <c r="B1384" s="2" t="s">
+        <v>6385</v>
+      </c>
+      <c r="C1384" s="2" t="s">
+        <v>6177</v>
+      </c>
+      <c r="D1384" s="2" t="s">
         <v>6386</v>
       </c>
-      <c r="C1384" s="2" t="s">
-        <v>6178</v>
-      </c>
-      <c r="D1384" s="2" t="s">
+      <c r="E1384" s="2" t="s">
         <v>6387</v>
       </c>
-      <c r="E1384" s="2" t="s">
+      <c r="F1384" s="2" t="s">
         <v>6388</v>
-      </c>
-      <c r="F1384" s="2" t="s">
-        <v>6389</v>
       </c>
       <c r="G1384" s="3">
         <v>4</v>
       </c>
       <c r="H1384" s="2" t="s">
-        <v>6390</v>
+        <v>6389</v>
       </c>
       <c r="I1384" s="2" t="s">
         <v>805</v>
@@ -62143,25 +62144,25 @@
         <v>1384</v>
       </c>
       <c r="B1385" s="2" t="s">
+        <v>6390</v>
+      </c>
+      <c r="C1385" s="2" t="s">
         <v>6391</v>
       </c>
-      <c r="C1385" s="2" t="s">
+      <c r="D1385" s="2" t="s">
         <v>6392</v>
       </c>
-      <c r="D1385" s="2" t="s">
+      <c r="E1385" s="2" t="s">
         <v>6393</v>
       </c>
-      <c r="E1385" s="2" t="s">
+      <c r="F1385" s="2" t="s">
         <v>6394</v>
-      </c>
-      <c r="F1385" s="2" t="s">
-        <v>6395</v>
       </c>
       <c r="G1385" s="3">
         <v>3</v>
       </c>
       <c r="H1385" s="2" t="s">
-        <v>6396</v>
+        <v>6395</v>
       </c>
       <c r="I1385" s="2" t="s">
         <v>805</v>
@@ -62172,25 +62173,25 @@
         <v>1385</v>
       </c>
       <c r="B1386" s="2" t="s">
+        <v>6396</v>
+      </c>
+      <c r="C1386" s="2" t="s">
         <v>6397</v>
       </c>
-      <c r="C1386" s="2" t="s">
+      <c r="D1386" s="2" t="s">
         <v>6398</v>
       </c>
-      <c r="D1386" s="2" t="s">
+      <c r="E1386" s="2" t="s">
         <v>6399</v>
       </c>
-      <c r="E1386" s="2" t="s">
+      <c r="F1386" s="2" t="s">
         <v>6400</v>
-      </c>
-      <c r="F1386" s="2" t="s">
-        <v>6401</v>
       </c>
       <c r="G1386" s="3">
         <v>3</v>
       </c>
       <c r="H1386" s="2" t="s">
-        <v>6402</v>
+        <v>6401</v>
       </c>
       <c r="I1386" s="2" t="s">
         <v>15</v>
@@ -62201,25 +62202,25 @@
         <v>1386</v>
       </c>
       <c r="B1387" s="2" t="s">
-        <v>6403</v>
+        <v>6402</v>
       </c>
       <c r="C1387" s="2" t="s">
+        <v>6586</v>
+      </c>
+      <c r="D1387" s="2" t="s">
         <v>6587</v>
       </c>
-      <c r="D1387" s="2" t="s">
+      <c r="E1387" s="2" t="s">
         <v>6588</v>
       </c>
-      <c r="E1387" s="2" t="s">
+      <c r="F1387" s="2" t="s">
         <v>6589</v>
-      </c>
-      <c r="F1387" s="2" t="s">
-        <v>6590</v>
       </c>
       <c r="G1387" s="3">
         <v>1</v>
       </c>
       <c r="H1387" s="2" t="s">
-        <v>6404</v>
+        <v>6403</v>
       </c>
       <c r="I1387" s="2" t="s">
         <v>15</v>
@@ -62230,25 +62231,25 @@
         <v>1387</v>
       </c>
       <c r="B1388" s="2" t="s">
+        <v>6404</v>
+      </c>
+      <c r="C1388" s="2" t="s">
         <v>6405</v>
-      </c>
-      <c r="C1388" s="2" t="s">
-        <v>6406</v>
       </c>
       <c r="D1388" s="2" t="s">
         <v>44</v>
       </c>
       <c r="E1388" s="2" t="s">
+        <v>6406</v>
+      </c>
+      <c r="F1388" s="2" t="s">
         <v>6407</v>
-      </c>
-      <c r="F1388" s="2" t="s">
-        <v>6408</v>
       </c>
       <c r="G1388" s="3">
         <v>1</v>
       </c>
       <c r="H1388" s="2" t="s">
-        <v>6409</v>
+        <v>6408</v>
       </c>
       <c r="I1388" s="2" t="s">
         <v>805</v>
@@ -62259,25 +62260,25 @@
         <v>1388</v>
       </c>
       <c r="B1389" s="2" t="s">
+        <v>6409</v>
+      </c>
+      <c r="C1389" s="2" t="s">
         <v>6410</v>
       </c>
-      <c r="C1389" s="2" t="s">
+      <c r="D1389" s="2" t="s">
         <v>6411</v>
       </c>
-      <c r="D1389" s="2" t="s">
+      <c r="E1389" s="2" t="s">
         <v>6412</v>
       </c>
-      <c r="E1389" s="2" t="s">
+      <c r="F1389" s="2" t="s">
         <v>6413</v>
-      </c>
-      <c r="F1389" s="2" t="s">
-        <v>6414</v>
       </c>
       <c r="G1389" s="3">
         <v>1</v>
       </c>
       <c r="H1389" s="2" t="s">
-        <v>6415</v>
+        <v>6414</v>
       </c>
       <c r="I1389" s="2" t="s">
         <v>15</v>
@@ -62288,25 +62289,25 @@
         <v>1389</v>
       </c>
       <c r="B1390" s="2" t="s">
+        <v>6415</v>
+      </c>
+      <c r="C1390" s="2" t="s">
         <v>6416</v>
       </c>
-      <c r="C1390" s="2" t="s">
+      <c r="D1390" s="2" t="s">
         <v>6417</v>
       </c>
-      <c r="D1390" s="2" t="s">
+      <c r="E1390" s="2" t="s">
         <v>6418</v>
       </c>
-      <c r="E1390" s="2" t="s">
+      <c r="F1390" s="2" t="s">
         <v>6419</v>
-      </c>
-      <c r="F1390" s="2" t="s">
-        <v>6420</v>
       </c>
       <c r="G1390" s="3">
         <v>4</v>
       </c>
       <c r="H1390" s="2" t="s">
-        <v>6421</v>
+        <v>6420</v>
       </c>
       <c r="I1390" s="2" t="s">
         <v>15</v>
@@ -62317,25 +62318,25 @@
         <v>1390</v>
       </c>
       <c r="B1391" s="2" t="s">
+        <v>6421</v>
+      </c>
+      <c r="C1391" s="2" t="s">
         <v>6422</v>
       </c>
-      <c r="C1391" s="2" t="s">
+      <c r="D1391" s="2" t="s">
         <v>6423</v>
       </c>
-      <c r="D1391" s="2" t="s">
+      <c r="E1391" s="2" t="s">
         <v>6424</v>
       </c>
-      <c r="E1391" s="2" t="s">
+      <c r="F1391" s="2" t="s">
         <v>6425</v>
-      </c>
-      <c r="F1391" s="2" t="s">
-        <v>6426</v>
       </c>
       <c r="G1391" s="3">
         <v>1</v>
       </c>
       <c r="H1391" s="2" t="s">
-        <v>6427</v>
+        <v>6426</v>
       </c>
       <c r="I1391" s="2" t="s">
         <v>15</v>
@@ -62346,25 +62347,25 @@
         <v>1391</v>
       </c>
       <c r="B1392" s="2" t="s">
+        <v>6427</v>
+      </c>
+      <c r="C1392" s="2" t="s">
         <v>6428</v>
       </c>
-      <c r="C1392" s="2" t="s">
+      <c r="D1392" s="2" t="s">
         <v>6429</v>
       </c>
-      <c r="D1392" s="2" t="s">
+      <c r="E1392" s="2" t="s">
         <v>6430</v>
       </c>
-      <c r="E1392" s="2" t="s">
+      <c r="F1392" s="2" t="s">
         <v>6431</v>
-      </c>
-      <c r="F1392" s="2" t="s">
-        <v>6432</v>
       </c>
       <c r="G1392" s="3">
         <v>2</v>
       </c>
       <c r="H1392" s="2" t="s">
-        <v>6433</v>
+        <v>6432</v>
       </c>
       <c r="I1392" s="2" t="s">
         <v>15</v>
@@ -62375,25 +62376,25 @@
         <v>1392</v>
       </c>
       <c r="B1393" s="2" t="s">
+        <v>6433</v>
+      </c>
+      <c r="C1393" s="2" t="s">
         <v>6434</v>
       </c>
-      <c r="C1393" s="2" t="s">
+      <c r="D1393" s="2" t="s">
         <v>6435</v>
       </c>
-      <c r="D1393" s="2" t="s">
+      <c r="E1393" s="2" t="s">
         <v>6436</v>
       </c>
-      <c r="E1393" s="2" t="s">
-        <v>6437</v>
-      </c>
       <c r="F1393" s="2" t="s">
-        <v>6937</v>
+        <v>6936</v>
       </c>
       <c r="G1393" s="3">
         <v>4</v>
       </c>
       <c r="H1393" s="2" t="s">
-        <v>6439</v>
+        <v>6438</v>
       </c>
       <c r="I1393" s="2" t="s">
         <v>805</v>
@@ -62404,25 +62405,25 @@
         <v>1393</v>
       </c>
       <c r="B1394" s="2" t="s">
+        <v>6439</v>
+      </c>
+      <c r="C1394" s="2" t="s">
+        <v>6434</v>
+      </c>
+      <c r="D1394" s="2" t="s">
         <v>6440</v>
       </c>
-      <c r="C1394" s="2" t="s">
-        <v>6435</v>
-      </c>
-      <c r="D1394" s="2" t="s">
+      <c r="E1394" s="2" t="s">
+        <v>6677</v>
+      </c>
+      <c r="F1394" s="2" t="s">
         <v>6441</v>
-      </c>
-      <c r="E1394" s="2" t="s">
-        <v>6678</v>
-      </c>
-      <c r="F1394" s="2" t="s">
-        <v>6442</v>
       </c>
       <c r="G1394" s="3">
         <v>3</v>
       </c>
       <c r="H1394" s="2" t="s">
-        <v>6443</v>
+        <v>6442</v>
       </c>
       <c r="I1394" s="2" t="s">
         <v>805</v>
@@ -62433,7 +62434,7 @@
         <v>1394</v>
       </c>
       <c r="B1395" s="2" t="s">
-        <v>6444</v>
+        <v>6443</v>
       </c>
       <c r="C1395" s="2" t="s">
         <v>496</v>
@@ -62451,7 +62452,7 @@
         <v>4</v>
       </c>
       <c r="H1395" s="2" t="s">
-        <v>6445</v>
+        <v>6444</v>
       </c>
       <c r="I1395" s="2" t="s">
         <v>805</v>
@@ -62462,10 +62463,10 @@
         <v>1395</v>
       </c>
       <c r="B1396" s="2" t="s">
+        <v>6445</v>
+      </c>
+      <c r="C1396" s="2" t="s">
         <v>6446</v>
-      </c>
-      <c r="C1396" s="2" t="s">
-        <v>6447</v>
       </c>
       <c r="D1396" s="2" t="s">
         <v>496</v>
@@ -62474,13 +62475,13 @@
         <v>495</v>
       </c>
       <c r="F1396" s="2" t="s">
-        <v>6448</v>
+        <v>6447</v>
       </c>
       <c r="G1396" s="3">
         <v>2</v>
       </c>
       <c r="H1396" s="2" t="s">
-        <v>6449</v>
+        <v>6448</v>
       </c>
       <c r="I1396" s="2" t="s">
         <v>805</v>
@@ -62491,25 +62492,25 @@
         <v>1396</v>
       </c>
       <c r="B1397" s="2" t="s">
-        <v>6450</v>
+        <v>6449</v>
       </c>
       <c r="C1397" s="2" t="s">
-        <v>6435</v>
+        <v>6434</v>
       </c>
       <c r="D1397" s="2" t="s">
-        <v>6441</v>
+        <v>6440</v>
       </c>
       <c r="E1397" s="2" t="s">
+        <v>6436</v>
+      </c>
+      <c r="F1397" s="2" t="s">
         <v>6437</v>
-      </c>
-      <c r="F1397" s="2" t="s">
-        <v>6438</v>
       </c>
       <c r="G1397" s="3">
         <v>1</v>
       </c>
       <c r="H1397" s="2" t="s">
-        <v>6451</v>
+        <v>6450</v>
       </c>
       <c r="I1397" s="2" t="s">
         <v>805</v>
@@ -62520,25 +62521,25 @@
         <v>1397</v>
       </c>
       <c r="B1398" s="2" t="s">
-        <v>6452</v>
+        <v>6451</v>
       </c>
       <c r="C1398" s="2" t="s">
-        <v>6435</v>
+        <v>6434</v>
       </c>
       <c r="D1398" s="2" t="s">
-        <v>6441</v>
+        <v>6440</v>
       </c>
       <c r="E1398" s="2" t="s">
+        <v>6436</v>
+      </c>
+      <c r="F1398" s="2" t="s">
         <v>6437</v>
-      </c>
-      <c r="F1398" s="2" t="s">
-        <v>6438</v>
       </c>
       <c r="G1398" s="3">
         <v>3</v>
       </c>
       <c r="H1398" s="2" t="s">
-        <v>6453</v>
+        <v>6452</v>
       </c>
       <c r="I1398" s="2" t="s">
         <v>805</v>
@@ -62549,7 +62550,7 @@
         <v>1398</v>
       </c>
       <c r="B1399" s="2" t="s">
-        <v>6454</v>
+        <v>6453</v>
       </c>
       <c r="C1399" s="2" t="s">
         <v>497</v>
@@ -62561,13 +62562,13 @@
         <v>495</v>
       </c>
       <c r="F1399" s="2" t="s">
-        <v>6455</v>
+        <v>6454</v>
       </c>
       <c r="G1399" s="3">
         <v>4</v>
       </c>
       <c r="H1399" s="2" t="s">
-        <v>6456</v>
+        <v>6455</v>
       </c>
       <c r="I1399" s="2" t="s">
         <v>805</v>
@@ -62578,25 +62579,25 @@
         <v>1399</v>
       </c>
       <c r="B1400" s="2" t="s">
+        <v>6456</v>
+      </c>
+      <c r="C1400" s="2" t="s">
         <v>6457</v>
       </c>
-      <c r="C1400" s="2" t="s">
+      <c r="D1400" s="2" t="s">
         <v>6458</v>
       </c>
-      <c r="D1400" s="2" t="s">
+      <c r="E1400" s="2" t="s">
         <v>6459</v>
       </c>
-      <c r="E1400" s="2" t="s">
+      <c r="F1400" s="2" t="s">
         <v>6460</v>
-      </c>
-      <c r="F1400" s="2" t="s">
-        <v>6461</v>
       </c>
       <c r="G1400" s="3">
         <v>2</v>
       </c>
       <c r="H1400" s="2" t="s">
-        <v>6462</v>
+        <v>6461</v>
       </c>
       <c r="I1400" s="2" t="s">
         <v>805</v>
@@ -62607,25 +62608,25 @@
         <v>1400</v>
       </c>
       <c r="B1401" s="2" t="s">
+        <v>6462</v>
+      </c>
+      <c r="C1401" s="2" t="s">
         <v>6463</v>
       </c>
-      <c r="C1401" s="2" t="s">
+      <c r="D1401" s="2" t="s">
         <v>6464</v>
       </c>
-      <c r="D1401" s="2" t="s">
+      <c r="E1401" s="2" t="s">
         <v>6465</v>
       </c>
-      <c r="E1401" s="2" t="s">
+      <c r="F1401" s="2" t="s">
         <v>6466</v>
-      </c>
-      <c r="F1401" s="2" t="s">
-        <v>6467</v>
       </c>
       <c r="G1401" s="3">
         <v>2</v>
       </c>
       <c r="H1401" s="2" t="s">
-        <v>6468</v>
+        <v>6467</v>
       </c>
       <c r="I1401" s="2" t="s">
         <v>805</v>
@@ -62636,25 +62637,25 @@
         <v>1401</v>
       </c>
       <c r="B1402" s="2" t="s">
+        <v>6468</v>
+      </c>
+      <c r="C1402" s="2" t="s">
         <v>6469</v>
       </c>
-      <c r="C1402" s="2" t="s">
+      <c r="D1402" s="2" t="s">
         <v>6470</v>
       </c>
-      <c r="D1402" s="2" t="s">
+      <c r="E1402" s="2" t="s">
         <v>6471</v>
       </c>
-      <c r="E1402" s="2" t="s">
+      <c r="F1402" s="2" t="s">
         <v>6472</v>
-      </c>
-      <c r="F1402" s="2" t="s">
-        <v>6473</v>
       </c>
       <c r="G1402" s="3">
         <v>2</v>
       </c>
       <c r="H1402" s="2" t="s">
-        <v>6474</v>
+        <v>6473</v>
       </c>
       <c r="I1402" s="2" t="s">
         <v>15</v>
@@ -62665,25 +62666,25 @@
         <v>1402</v>
       </c>
       <c r="B1403" s="2" t="s">
+        <v>6474</v>
+      </c>
+      <c r="C1403" s="2" t="s">
         <v>6475</v>
       </c>
-      <c r="C1403" s="2" t="s">
+      <c r="D1403" s="2" t="s">
         <v>6476</v>
       </c>
-      <c r="D1403" s="2" t="s">
+      <c r="E1403" s="2" t="s">
         <v>6477</v>
       </c>
-      <c r="E1403" s="2" t="s">
+      <c r="F1403" s="2" t="s">
         <v>6478</v>
-      </c>
-      <c r="F1403" s="2" t="s">
-        <v>6479</v>
       </c>
       <c r="G1403" s="3">
         <v>3</v>
       </c>
       <c r="H1403" s="2" t="s">
-        <v>6480</v>
+        <v>6479</v>
       </c>
       <c r="I1403" s="2" t="s">
         <v>15</v>
@@ -62694,25 +62695,25 @@
         <v>1403</v>
       </c>
       <c r="B1404" s="2" t="s">
+        <v>6480</v>
+      </c>
+      <c r="C1404" s="2" t="s">
         <v>6481</v>
       </c>
-      <c r="C1404" s="2" t="s">
+      <c r="D1404" s="2" t="s">
         <v>6482</v>
       </c>
-      <c r="D1404" s="2" t="s">
+      <c r="E1404" s="2" t="s">
         <v>6483</v>
       </c>
-      <c r="E1404" s="2" t="s">
+      <c r="F1404" s="2" t="s">
         <v>6484</v>
-      </c>
-      <c r="F1404" s="2" t="s">
-        <v>6485</v>
       </c>
       <c r="G1404" s="3">
         <v>2</v>
       </c>
       <c r="H1404" s="2" t="s">
-        <v>6486</v>
+        <v>6485</v>
       </c>
       <c r="I1404" s="2" t="s">
         <v>15</v>

--- a/salf/丙種職業安全衛生業務主管題庫.xlsx
+++ b/salf/丙種職業安全衛生業務主管題庫.xlsx
@@ -19,6 +19,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">乾淨題庫!$A$1:$I$1404</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -22197,6 +22198,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/salf/丙種職業安全衛生業務主管題庫.xlsx
+++ b/salf/丙種職業安全衛生業務主管題庫.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25f5a1833553ad9e/文件/GitHub/drher.github.io/salf/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{6257E10B-38E2-465E-BA40-CE0F6A045F2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E8A76E9B-7629-438C-97D0-335841D0A98D}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{6257E10B-38E2-465E-BA40-CE0F6A045F2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6585F5B1-82B3-4B01-B88E-3BCDB7DC96A5}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9463" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18524,16 +18524,10 @@
     <t>一、永久全失能 : 指任何還熏戴災者造成永久全失能, 或在一次事故中損失下列之一情形, 或失去其機能者 (一) 俯目。 (三) 一隻眼睛及一集半或手辟或腿或足。 (三) 不同肢體中之任何下多兩種: 手、足、足或腿。一、永久部分失能指除死寐及永久全失能以外的任何足以造成肢體之任何一部分完全失去, 或失去其機能者。不論該受和傷者之股體或損傷身體機能之事前有無任何失能。</t>
   </si>
   <si>
-    <t>. 勞工在一次事故中受傷使雙眼失明是屬下列何者 ?</t>
-  </si>
-  <si>
     <t>暫時全失能</t>
   </si>
   <si>
     <t>永久部分失能</t>
-  </si>
-  <si>
-    <t>永久全拓能。解析與補充 : 能者 (俯目 (三) 一隻眼貞及一俐閨, Rs 由四之任何下表: 手、怕、中歡王、永久部分失能克它及永久全失能以外的任何是剛或損傷身胜能 : 指任何思使國災者造成永久全失態, 或在一次事故中損失下列之一情形, 或失去其機</t>
   </si>
   <si>
     <t>正確答案為第4項：「永久全拓能。解析與補充 : 能者 (俯目 (三) 一隻眼貞及一俐閨, Rs 由四之任何下表: 手、怕、中歡王、永久部分失能克它及永久全失能以外的任何是剛或損傷身胜能 : 指任何思使國災者造成永久全失態, 或在一次事故中損失下列之一情形, 或失去其機」。本題重點在於理解題幹所涉及的職業安全衛生管理、危害預防或法規要求。</t>
@@ -22185,6 +22179,14 @@
   </si>
   <si>
     <t>高血壓</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>永久全失能</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>勞工在一次事故中受傷使雙眼失明是屬下列何者 ?</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -23063,7 +23065,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>6763</v>
+        <v>6761</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>87</v>
@@ -23072,10 +23074,10 @@
         <v>88</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>6765</v>
+        <v>6763</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>6764</v>
+        <v>6762</v>
       </c>
       <c r="G16" s="3">
         <v>1</v>
@@ -23264,7 +23266,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>6596</v>
+        <v>6594</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>122</v>
@@ -23276,7 +23278,7 @@
         <v>124</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>6597</v>
+        <v>6595</v>
       </c>
       <c r="G23" s="3">
         <v>4</v>
@@ -23322,10 +23324,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>6353</v>
+        <v>6351</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>6354</v>
+        <v>6352</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>132</v>
@@ -23380,10 +23382,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>6779</v>
+        <v>6777</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>6780</v>
+        <v>6778</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>142</v>
@@ -23392,7 +23394,7 @@
         <v>143</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>6781</v>
+        <v>6779</v>
       </c>
       <c r="G27" s="3">
         <v>3</v>
@@ -23824,7 +23826,7 @@
         <v>224</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>6975</v>
+        <v>6973</v>
       </c>
       <c r="F42" s="2"/>
       <c r="G42" s="3">
@@ -23842,19 +23844,19 @@
         <v>42</v>
       </c>
       <c r="B43" s="2" t="s">
+        <v>6458</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>6459</v>
+      </c>
+      <c r="D43" s="2" t="s">
         <v>6460</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>6461</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>6462</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>226</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>6463</v>
+        <v>6461</v>
       </c>
       <c r="G43" s="3">
         <v>3</v>
@@ -24306,7 +24308,7 @@
         <v>58</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>6883</v>
+        <v>6881</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>312</v>
@@ -24480,7 +24482,7 @@
         <v>64</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>6417</v>
+        <v>6415</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>340</v>
@@ -24515,7 +24517,7 @@
         <v>346</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>6418</v>
+        <v>6416</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>341</v>
@@ -24654,13 +24656,13 @@
         <v>70</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>6280</v>
+        <v>6278</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>371</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>6279</v>
+        <v>6277</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>372</v>
@@ -24683,7 +24685,7 @@
         <v>71</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>6369</v>
+        <v>6367</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>375</v>
@@ -24692,10 +24694,10 @@
         <v>376</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>6371</v>
+        <v>6369</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>6370</v>
+        <v>6368</v>
       </c>
       <c r="G72" s="3">
         <v>4</v>
@@ -24866,10 +24868,10 @@
         <v>405</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>6798</v>
+        <v>6796</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>6799</v>
+        <v>6797</v>
       </c>
       <c r="G78" s="3">
         <v>3</v>
@@ -24944,10 +24946,10 @@
         <v>80</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>6546</v>
+        <v>6544</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>6547</v>
+        <v>6545</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>418</v>
@@ -25263,7 +25265,7 @@
         <v>91</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>6329</v>
+        <v>6327</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>475</v>
@@ -25275,7 +25277,7 @@
         <v>477</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>6330</v>
+        <v>6328</v>
       </c>
       <c r="G92" s="3">
         <v>4</v>
@@ -25292,19 +25294,19 @@
         <v>92</v>
       </c>
       <c r="B93" s="2" t="s">
+        <v>6585</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>6586</v>
+      </c>
+      <c r="D93" s="2" t="s">
         <v>6587</v>
       </c>
-      <c r="C93" s="2" t="s">
+      <c r="E93" s="2" t="s">
         <v>6588</v>
       </c>
-      <c r="D93" s="2" t="s">
+      <c r="F93" s="2" t="s">
         <v>6589</v>
-      </c>
-      <c r="E93" s="2" t="s">
-        <v>6590</v>
-      </c>
-      <c r="F93" s="2" t="s">
-        <v>6591</v>
       </c>
       <c r="G93" s="3">
         <v>4</v>
@@ -25350,7 +25352,7 @@
         <v>94</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>6732</v>
+        <v>6730</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>485</v>
@@ -25408,10 +25410,10 @@
         <v>96</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>6847</v>
+        <v>6845</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>6846</v>
+        <v>6844</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>496</v>
@@ -25549,7 +25551,7 @@
         <v>101</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>6306</v>
+        <v>6304</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>521</v>
@@ -25558,10 +25560,10 @@
         <v>522</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>6307</v>
+        <v>6305</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>6308</v>
+        <v>6306</v>
       </c>
       <c r="G102" s="3">
         <v>1</v>
@@ -25607,7 +25609,7 @@
         <v>103</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>6669</v>
+        <v>6667</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>530</v>
@@ -26286,7 +26288,7 @@
         <v>638</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>6930</v>
+        <v>6928</v>
       </c>
       <c r="G127" s="3">
         <v>4</v>
@@ -26446,7 +26448,7 @@
         <v>132</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>6336</v>
+        <v>6334</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>341</v>
@@ -26455,10 +26457,10 @@
         <v>665</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>6337</v>
+        <v>6335</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>6338</v>
+        <v>6336</v>
       </c>
       <c r="G133" s="3">
         <v>3</v>
@@ -26922,7 +26924,7 @@
         <v>745</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>6790</v>
+        <v>6788</v>
       </c>
       <c r="G149" s="3">
         <v>4</v>
@@ -26939,7 +26941,7 @@
         <v>149</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>6714</v>
+        <v>6712</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>747</v>
@@ -27171,13 +27173,13 @@
         <v>157</v>
       </c>
       <c r="B158" s="2" t="s">
+        <v>6715</v>
+      </c>
+      <c r="C158" s="2" t="s">
+        <v>6716</v>
+      </c>
+      <c r="D158" s="2" t="s">
         <v>6717</v>
-      </c>
-      <c r="C158" s="2" t="s">
-        <v>6718</v>
-      </c>
-      <c r="D158" s="2" t="s">
-        <v>6719</v>
       </c>
       <c r="E158" s="2" t="s">
         <v>780</v>
@@ -27212,7 +27214,7 @@
         <v>786</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>6347</v>
+        <v>6345</v>
       </c>
       <c r="G159" s="3">
         <v>3</v>
@@ -27348,16 +27350,16 @@
         <v>808</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>6754</v>
+        <v>6752</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>6759</v>
+        <v>6757</v>
       </c>
       <c r="E164" s="2" t="s">
         <v>809</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>6756</v>
+        <v>6754</v>
       </c>
       <c r="G164" s="3">
         <v>3</v>
@@ -27374,19 +27376,19 @@
         <v>164</v>
       </c>
       <c r="B165" s="2" t="s">
+        <v>6751</v>
+      </c>
+      <c r="C165" s="2" t="s">
         <v>6753</v>
       </c>
-      <c r="C165" s="2" t="s">
-        <v>6755</v>
-      </c>
       <c r="D165" s="2" t="s">
-        <v>6754</v>
+        <v>6752</v>
       </c>
       <c r="E165" s="2" t="s">
         <v>811</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>6757</v>
+        <v>6755</v>
       </c>
       <c r="G165" s="3">
         <v>3</v>
@@ -27415,7 +27417,7 @@
         <v>814</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>6758</v>
+        <v>6756</v>
       </c>
       <c r="G166" s="3">
         <v>3</v>
@@ -27432,25 +27434,25 @@
         <v>166</v>
       </c>
       <c r="B167" s="2" t="s">
+        <v>6498</v>
+      </c>
+      <c r="C167" s="2" t="s">
+        <v>6499</v>
+      </c>
+      <c r="D167" s="2" t="s">
         <v>6500</v>
       </c>
-      <c r="C167" s="2" t="s">
+      <c r="E167" s="2" t="s">
         <v>6501</v>
       </c>
-      <c r="D167" s="2" t="s">
+      <c r="F167" s="2" t="s">
         <v>6502</v>
-      </c>
-      <c r="E167" s="2" t="s">
-        <v>6503</v>
-      </c>
-      <c r="F167" s="2" t="s">
-        <v>6504</v>
       </c>
       <c r="G167" s="3">
         <v>3</v>
       </c>
       <c r="H167" s="2" t="s">
-        <v>6505</v>
+        <v>6503</v>
       </c>
       <c r="I167" s="2" t="s">
         <v>15</v>
@@ -27522,7 +27524,7 @@
         <v>825</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>7000</v>
+        <v>6998</v>
       </c>
       <c r="D170" s="2" t="s">
         <v>826</v>
@@ -27531,7 +27533,7 @@
         <v>827</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>7001</v>
+        <v>6999</v>
       </c>
       <c r="G170" s="3">
         <v>1</v>
@@ -27664,7 +27666,7 @@
         <v>174</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>6516</v>
+        <v>6514</v>
       </c>
       <c r="C175" s="2" t="s">
         <v>435</v>
@@ -27780,7 +27782,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>6386</v>
+        <v>6384</v>
       </c>
       <c r="C179" s="2" t="s">
         <v>852</v>
@@ -27809,19 +27811,19 @@
         <v>179</v>
       </c>
       <c r="B180" s="2" t="s">
+        <v>6870</v>
+      </c>
+      <c r="C180" s="2" t="s">
         <v>6872</v>
       </c>
-      <c r="C180" s="2" t="s">
-        <v>6874</v>
-      </c>
       <c r="D180" s="2" t="s">
-        <v>6873</v>
+        <v>6871</v>
       </c>
       <c r="E180" s="2" t="s">
         <v>870</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>6875</v>
+        <v>6873</v>
       </c>
       <c r="G180" s="3">
         <v>3</v>
@@ -27925,19 +27927,19 @@
         <v>183</v>
       </c>
       <c r="B184" s="2" t="s">
+        <v>6771</v>
+      </c>
+      <c r="C184" s="2" t="s">
+        <v>6769</v>
+      </c>
+      <c r="D184" s="2" t="s">
+        <v>6770</v>
+      </c>
+      <c r="E184" s="2" t="s">
+        <v>6772</v>
+      </c>
+      <c r="F184" s="2" t="s">
         <v>6773</v>
-      </c>
-      <c r="C184" s="2" t="s">
-        <v>6771</v>
-      </c>
-      <c r="D184" s="2" t="s">
-        <v>6772</v>
-      </c>
-      <c r="E184" s="2" t="s">
-        <v>6774</v>
-      </c>
-      <c r="F184" s="2" t="s">
-        <v>6775</v>
       </c>
       <c r="G184" s="3">
         <v>2</v>
@@ -28070,7 +28072,7 @@
         <v>188</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>6459</v>
+        <v>6457</v>
       </c>
       <c r="C189" s="2" t="s">
         <v>906</v>
@@ -28221,13 +28223,13 @@
         <v>931</v>
       </c>
       <c r="D194" s="2" t="s">
+        <v>6515</v>
+      </c>
+      <c r="E194" s="2" t="s">
+        <v>6516</v>
+      </c>
+      <c r="F194" s="2" t="s">
         <v>6517</v>
-      </c>
-      <c r="E194" s="2" t="s">
-        <v>6518</v>
-      </c>
-      <c r="F194" s="2" t="s">
-        <v>6519</v>
       </c>
       <c r="G194" s="3">
         <v>4</v>
@@ -28247,22 +28249,22 @@
         <v>933</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>6831</v>
+        <v>6829</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>6830</v>
+        <v>6828</v>
       </c>
       <c r="E195" s="2" t="s">
         <v>934</v>
       </c>
       <c r="F195" s="2" t="s">
-        <v>6832</v>
+        <v>6830</v>
       </c>
       <c r="G195" s="3">
         <v>1</v>
       </c>
       <c r="H195" s="2" t="s">
-        <v>6833</v>
+        <v>6831</v>
       </c>
       <c r="I195" s="2" t="s">
         <v>15</v>
@@ -28392,16 +28394,16 @@
         <v>959</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>6739</v>
+        <v>6737</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>6737</v>
+        <v>6735</v>
       </c>
       <c r="E200" s="2" t="s">
         <v>960</v>
       </c>
       <c r="F200" s="2" t="s">
-        <v>6738</v>
+        <v>6736</v>
       </c>
       <c r="G200" s="3">
         <v>1</v>
@@ -28450,7 +28452,7 @@
         <v>968</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>7033</v>
+        <v>7031</v>
       </c>
       <c r="D202" s="2" t="s">
         <v>969</v>
@@ -28598,13 +28600,13 @@
         <v>997</v>
       </c>
       <c r="D207" s="2" t="s">
+        <v>6263</v>
+      </c>
+      <c r="E207" s="2" t="s">
+        <v>6264</v>
+      </c>
+      <c r="F207" s="2" t="s">
         <v>6265</v>
-      </c>
-      <c r="E207" s="2" t="s">
-        <v>6266</v>
-      </c>
-      <c r="F207" s="2" t="s">
-        <v>6267</v>
       </c>
       <c r="G207" s="3">
         <v>2</v>
@@ -29114,19 +29116,19 @@
         <v>224</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>6834</v>
+        <v>6832</v>
       </c>
       <c r="C225" s="2" t="s">
         <v>1097</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>6835</v>
+        <v>6833</v>
       </c>
       <c r="E225" s="2" t="s">
         <v>1098</v>
       </c>
       <c r="F225" s="2" t="s">
-        <v>6836</v>
+        <v>6834</v>
       </c>
       <c r="G225" s="3">
         <v>4</v>
@@ -29375,7 +29377,7 @@
         <v>233</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>6961</v>
+        <v>6959</v>
       </c>
       <c r="C234" s="2" t="s">
         <v>865</v>
@@ -29578,7 +29580,7 @@
         <v>240</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>6701</v>
+        <v>6699</v>
       </c>
       <c r="C241" s="2" t="s">
         <v>1163</v>
@@ -29590,7 +29592,7 @@
         <v>1181</v>
       </c>
       <c r="F241" s="2" t="s">
-        <v>6702</v>
+        <v>6700</v>
       </c>
       <c r="G241" s="3">
         <v>1</v>
@@ -29938,7 +29940,7 @@
         <v>1241</v>
       </c>
       <c r="F253" s="2" t="s">
-        <v>6818</v>
+        <v>6816</v>
       </c>
       <c r="G253" s="3">
         <v>4</v>
@@ -29961,13 +29963,13 @@
         <v>1244</v>
       </c>
       <c r="D254" s="2" t="s">
+        <v>6874</v>
+      </c>
+      <c r="E254" s="2" t="s">
+        <v>6875</v>
+      </c>
+      <c r="F254" s="2" t="s">
         <v>6876</v>
-      </c>
-      <c r="E254" s="2" t="s">
-        <v>6877</v>
-      </c>
-      <c r="F254" s="2" t="s">
-        <v>6878</v>
       </c>
       <c r="G254" s="3">
         <v>4</v>
@@ -30100,7 +30102,7 @@
         <v>258</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>6837</v>
+        <v>6835</v>
       </c>
       <c r="C259" s="2" t="s">
         <v>1266</v>
@@ -30112,7 +30114,7 @@
         <v>1268</v>
       </c>
       <c r="F259" s="2" t="s">
-        <v>6838</v>
+        <v>6836</v>
       </c>
       <c r="G259" s="3">
         <v>1</v>
@@ -30306,13 +30308,13 @@
         <v>1303</v>
       </c>
       <c r="C266" s="2" t="s">
+        <v>6722</v>
+      </c>
+      <c r="D266" s="2" t="s">
         <v>6724</v>
       </c>
-      <c r="D266" s="2" t="s">
-        <v>6726</v>
-      </c>
       <c r="E266" s="2" t="s">
-        <v>6725</v>
+        <v>6723</v>
       </c>
       <c r="F266" s="2" t="s">
         <v>1304</v>
@@ -30419,7 +30421,7 @@
         <v>269</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>6288</v>
+        <v>6286</v>
       </c>
       <c r="C270" s="2" t="s">
         <v>1320</v>
@@ -30564,7 +30566,7 @@
         <v>274</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>6944</v>
+        <v>6942</v>
       </c>
       <c r="C275" s="2" t="s">
         <v>1349</v>
@@ -30576,7 +30578,7 @@
         <v>1350</v>
       </c>
       <c r="F275" s="2" t="s">
-        <v>6945</v>
+        <v>6943</v>
       </c>
       <c r="G275" s="3">
         <v>1</v>
@@ -30605,7 +30607,7 @@
         <v>1355</v>
       </c>
       <c r="F276" s="2" t="s">
-        <v>6946</v>
+        <v>6944</v>
       </c>
       <c r="G276" s="3">
         <v>2</v>
@@ -30634,7 +30636,7 @@
         <v>1359</v>
       </c>
       <c r="F277" s="2" t="s">
-        <v>6947</v>
+        <v>6945</v>
       </c>
       <c r="G277" s="3">
         <v>3</v>
@@ -30680,19 +30682,19 @@
         <v>278</v>
       </c>
       <c r="B279" s="2" t="s">
+        <v>6518</v>
+      </c>
+      <c r="C279" s="2" t="s">
         <v>6520</v>
       </c>
-      <c r="C279" s="2" t="s">
+      <c r="D279" s="2" t="s">
+        <v>6521</v>
+      </c>
+      <c r="E279" s="2" t="s">
         <v>6522</v>
       </c>
-      <c r="D279" s="2" t="s">
-        <v>6523</v>
-      </c>
-      <c r="E279" s="2" t="s">
-        <v>6524</v>
-      </c>
       <c r="F279" s="2" t="s">
-        <v>6521</v>
+        <v>6519</v>
       </c>
       <c r="G279" s="3">
         <v>4</v>
@@ -30709,7 +30711,7 @@
         <v>279</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>6579</v>
+        <v>6577</v>
       </c>
       <c r="C280" s="2" t="s">
         <v>1366</v>
@@ -30718,10 +30720,10 @@
         <v>1367</v>
       </c>
       <c r="E280" s="2" t="s">
-        <v>6580</v>
+        <v>6578</v>
       </c>
       <c r="F280" s="2" t="s">
-        <v>6581</v>
+        <v>6579</v>
       </c>
       <c r="G280" s="3">
         <v>3</v>
@@ -30796,10 +30798,10 @@
         <v>282</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>6948</v>
+        <v>6946</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>6949</v>
+        <v>6947</v>
       </c>
       <c r="D283" s="2" t="s">
         <v>1381</v>
@@ -30808,7 +30810,7 @@
         <v>1076</v>
       </c>
       <c r="F283" s="2" t="s">
-        <v>6950</v>
+        <v>6948</v>
       </c>
       <c r="G283" s="3">
         <v>4</v>
@@ -30837,7 +30839,7 @@
         <v>1386</v>
       </c>
       <c r="F284" s="2" t="s">
-        <v>6852</v>
+        <v>6850</v>
       </c>
       <c r="G284" s="3">
         <v>1</v>
@@ -30912,19 +30914,19 @@
         <v>286</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>6848</v>
+        <v>6846</v>
       </c>
       <c r="C287" s="2" t="s">
         <v>1398</v>
       </c>
       <c r="D287" s="2" t="s">
+        <v>6847</v>
+      </c>
+      <c r="E287" s="2" t="s">
+        <v>6848</v>
+      </c>
+      <c r="F287" s="2" t="s">
         <v>6849</v>
-      </c>
-      <c r="E287" s="2" t="s">
-        <v>6850</v>
-      </c>
-      <c r="F287" s="2" t="s">
-        <v>6851</v>
       </c>
       <c r="G287" s="3">
         <v>3</v>
@@ -30999,19 +31001,19 @@
         <v>289</v>
       </c>
       <c r="B290" s="2" t="s">
+        <v>6573</v>
+      </c>
+      <c r="C290" s="2" t="s">
+        <v>6574</v>
+      </c>
+      <c r="D290" s="2" t="s">
         <v>6575</v>
-      </c>
-      <c r="C290" s="2" t="s">
-        <v>6576</v>
-      </c>
-      <c r="D290" s="2" t="s">
-        <v>6577</v>
       </c>
       <c r="E290" s="2" t="s">
         <v>1412</v>
       </c>
       <c r="F290" s="2" t="s">
-        <v>6578</v>
+        <v>6576</v>
       </c>
       <c r="G290" s="3">
         <v>1</v>
@@ -31057,19 +31059,19 @@
         <v>291</v>
       </c>
       <c r="B292" s="2" t="s">
+        <v>6506</v>
+      </c>
+      <c r="C292" s="2" t="s">
+        <v>6507</v>
+      </c>
+      <c r="D292" s="2" t="s">
         <v>6508</v>
       </c>
-      <c r="C292" s="2" t="s">
+      <c r="E292" s="2" t="s">
         <v>6509</v>
       </c>
-      <c r="D292" s="2" t="s">
+      <c r="F292" s="2" t="s">
         <v>6510</v>
-      </c>
-      <c r="E292" s="2" t="s">
-        <v>6511</v>
-      </c>
-      <c r="F292" s="2" t="s">
-        <v>6512</v>
       </c>
       <c r="G292" s="3">
         <v>1</v>
@@ -31579,7 +31581,7 @@
         <v>309</v>
       </c>
       <c r="B310" s="2" t="s">
-        <v>7045</v>
+        <v>7043</v>
       </c>
       <c r="C310" s="2" t="s">
         <v>1507</v>
@@ -31724,7 +31726,7 @@
         <v>314</v>
       </c>
       <c r="B315" s="2" t="s">
-        <v>6339</v>
+        <v>6337</v>
       </c>
       <c r="C315" s="2" t="s">
         <v>1536</v>
@@ -31753,10 +31755,10 @@
         <v>315</v>
       </c>
       <c r="B316" s="2" t="s">
-        <v>6582</v>
+        <v>6580</v>
       </c>
       <c r="C316" s="2" t="s">
-        <v>6583</v>
+        <v>6581</v>
       </c>
       <c r="D316" s="2" t="s">
         <v>1541</v>
@@ -31765,7 +31767,7 @@
         <v>1542</v>
       </c>
       <c r="F316" s="2" t="s">
-        <v>6584</v>
+        <v>6582</v>
       </c>
       <c r="G316" s="3">
         <v>1</v>
@@ -32107,13 +32109,13 @@
         <v>1606</v>
       </c>
       <c r="D328" s="2" t="s">
-        <v>6419</v>
+        <v>6417</v>
       </c>
       <c r="E328" s="2" t="s">
         <v>1608</v>
       </c>
       <c r="F328" s="2" t="s">
-        <v>6420</v>
+        <v>6418</v>
       </c>
       <c r="G328" s="3">
         <v>4</v>
@@ -32362,19 +32364,19 @@
         <v>336</v>
       </c>
       <c r="B337" s="2" t="s">
-        <v>6326</v>
+        <v>6324</v>
       </c>
       <c r="C337" s="2" t="s">
         <v>1655</v>
       </c>
       <c r="D337" s="2" t="s">
-        <v>6327</v>
+        <v>6325</v>
       </c>
       <c r="E337" s="2" t="s">
         <v>705</v>
       </c>
       <c r="F337" s="2" t="s">
-        <v>6328</v>
+        <v>6326</v>
       </c>
       <c r="G337" s="3">
         <v>4</v>
@@ -32507,7 +32509,7 @@
         <v>341</v>
       </c>
       <c r="B342" s="2" t="s">
-        <v>6697</v>
+        <v>6695</v>
       </c>
       <c r="C342" s="2" t="s">
         <v>1679</v>
@@ -32516,10 +32518,10 @@
         <v>1680</v>
       </c>
       <c r="E342" s="2" t="s">
-        <v>6695</v>
+        <v>6693</v>
       </c>
       <c r="F342" s="2" t="s">
-        <v>6696</v>
+        <v>6694</v>
       </c>
       <c r="G342" s="3">
         <v>2</v>
@@ -32568,7 +32570,7 @@
         <v>1688</v>
       </c>
       <c r="C344" s="2" t="s">
-        <v>6334</v>
+        <v>6332</v>
       </c>
       <c r="D344" s="2" t="s">
         <v>1683</v>
@@ -32577,7 +32579,7 @@
         <v>1684</v>
       </c>
       <c r="F344" s="2" t="s">
-        <v>6335</v>
+        <v>6333</v>
       </c>
       <c r="G344" s="3">
         <v>1</v>
@@ -32652,7 +32654,7 @@
         <v>346</v>
       </c>
       <c r="B347" s="2" t="s">
-        <v>7043</v>
+        <v>7041</v>
       </c>
       <c r="C347" s="2" t="s">
         <v>1702</v>
@@ -32855,19 +32857,19 @@
         <v>353</v>
       </c>
       <c r="B354" s="2" t="s">
+        <v>6791</v>
+      </c>
+      <c r="C354" s="2" t="s">
+        <v>6792</v>
+      </c>
+      <c r="D354" s="2" t="s">
         <v>6793</v>
-      </c>
-      <c r="C354" s="2" t="s">
-        <v>6794</v>
-      </c>
-      <c r="D354" s="2" t="s">
-        <v>6795</v>
       </c>
       <c r="E354" s="2" t="s">
         <v>1742</v>
       </c>
       <c r="F354" s="2" t="s">
-        <v>6796</v>
+        <v>6794</v>
       </c>
       <c r="G354" s="3">
         <v>1</v>
@@ -33493,19 +33495,19 @@
         <v>375</v>
       </c>
       <c r="B376" s="2" t="s">
-        <v>6881</v>
+        <v>6879</v>
       </c>
       <c r="C376" s="2" t="s">
         <v>1862</v>
       </c>
       <c r="D376" s="2" t="s">
-        <v>6879</v>
+        <v>6877</v>
       </c>
       <c r="E376" s="2" t="s">
         <v>1863</v>
       </c>
       <c r="F376" s="2" t="s">
-        <v>6880</v>
+        <v>6878</v>
       </c>
       <c r="G376" s="3">
         <v>1</v>
@@ -33551,7 +33553,7 @@
         <v>377</v>
       </c>
       <c r="B378" s="2" t="s">
-        <v>6882</v>
+        <v>6880</v>
       </c>
       <c r="C378" s="2" t="s">
         <v>1871</v>
@@ -33580,10 +33582,10 @@
         <v>378</v>
       </c>
       <c r="B379" s="2" t="s">
-        <v>6506</v>
+        <v>6504</v>
       </c>
       <c r="C379" s="2" t="s">
-        <v>6507</v>
+        <v>6505</v>
       </c>
       <c r="D379" s="2" t="s">
         <v>1876</v>
@@ -33786,7 +33788,7 @@
         <v>1912</v>
       </c>
       <c r="C386" s="2" t="s">
-        <v>6615</v>
+        <v>6613</v>
       </c>
       <c r="D386" s="2" t="s">
         <v>1909</v>
@@ -33795,7 +33797,7 @@
         <v>1913</v>
       </c>
       <c r="F386" s="2" t="s">
-        <v>6616</v>
+        <v>6614</v>
       </c>
       <c r="G386" s="3">
         <v>1</v>
@@ -33873,16 +33875,16 @@
         <v>1926</v>
       </c>
       <c r="C389" s="2" t="s">
-        <v>7047</v>
+        <v>7045</v>
       </c>
       <c r="D389" s="2" t="s">
-        <v>7048</v>
+        <v>7046</v>
       </c>
       <c r="E389" s="2" t="s">
         <v>1927</v>
       </c>
       <c r="F389" s="2" t="s">
-        <v>7049</v>
+        <v>7047</v>
       </c>
       <c r="G389" s="3">
         <v>1</v>
@@ -33992,7 +33994,7 @@
         <v>1948</v>
       </c>
       <c r="D393" s="2" t="s">
-        <v>6674</v>
+        <v>6672</v>
       </c>
       <c r="E393" s="2" t="s">
         <v>1949</v>
@@ -34015,13 +34017,13 @@
         <v>393</v>
       </c>
       <c r="B394" s="2" t="s">
-        <v>6673</v>
+        <v>6671</v>
       </c>
       <c r="C394" s="2" t="s">
         <v>1952</v>
       </c>
       <c r="D394" s="2" t="s">
-        <v>6675</v>
+        <v>6673</v>
       </c>
       <c r="E394" s="2" t="s">
         <v>1953</v>
@@ -34050,7 +34052,7 @@
         <v>1957</v>
       </c>
       <c r="D395" s="2" t="s">
-        <v>6884</v>
+        <v>6882</v>
       </c>
       <c r="E395" s="2" t="s">
         <v>1958</v>
@@ -34392,16 +34394,16 @@
         <v>406</v>
       </c>
       <c r="B407" s="2" t="s">
+        <v>6348</v>
+      </c>
+      <c r="C407" s="2" t="s">
         <v>6350</v>
-      </c>
-      <c r="C407" s="2" t="s">
-        <v>6352</v>
       </c>
       <c r="D407" s="2" t="s">
         <v>2024</v>
       </c>
       <c r="E407" s="2" t="s">
-        <v>6351</v>
+        <v>6349</v>
       </c>
       <c r="F407" s="2" t="s">
         <v>2025</v>
@@ -34709,7 +34711,7 @@
         <v>417</v>
       </c>
       <c r="B418" s="2" t="s">
-        <v>6595</v>
+        <v>6593</v>
       </c>
       <c r="C418" s="2" t="s">
         <v>77</v>
@@ -34834,10 +34836,10 @@
         <v>2096</v>
       </c>
       <c r="E422" s="2" t="s">
-        <v>6791</v>
+        <v>6789</v>
       </c>
       <c r="F422" s="2" t="s">
-        <v>6792</v>
+        <v>6790</v>
       </c>
       <c r="G422" s="3">
         <v>3</v>
@@ -34854,7 +34856,7 @@
         <v>422</v>
       </c>
       <c r="B423" s="2" t="s">
-        <v>6800</v>
+        <v>6798</v>
       </c>
       <c r="C423" s="2" t="s">
         <v>2098</v>
@@ -35096,7 +35098,7 @@
         <v>2142</v>
       </c>
       <c r="F431" s="2" t="s">
-        <v>6976</v>
+        <v>6974</v>
       </c>
       <c r="G431" s="3">
         <v>4</v>
@@ -35200,7 +35202,7 @@
         <v>434</v>
       </c>
       <c r="B435" s="2" t="s">
-        <v>6361</v>
+        <v>6359</v>
       </c>
       <c r="C435" s="2" t="s">
         <v>2158</v>
@@ -35212,7 +35214,7 @@
         <v>2160</v>
       </c>
       <c r="F435" s="2" t="s">
-        <v>6362</v>
+        <v>6360</v>
       </c>
       <c r="G435" s="3">
         <v>1</v>
@@ -35285,7 +35287,7 @@
         <v>437</v>
       </c>
       <c r="B438" s="2" t="s">
-        <v>6708</v>
+        <v>6706</v>
       </c>
       <c r="C438" s="2" t="s">
         <v>2170</v>
@@ -35294,10 +35296,10 @@
         <v>2171</v>
       </c>
       <c r="E438" s="2" t="s">
-        <v>6710</v>
+        <v>6708</v>
       </c>
       <c r="F438" s="2" t="s">
-        <v>6709</v>
+        <v>6707</v>
       </c>
       <c r="G438" s="3">
         <v>1</v>
@@ -35468,7 +35470,7 @@
         <v>1271</v>
       </c>
       <c r="E444" s="2" t="s">
-        <v>6713</v>
+        <v>6711</v>
       </c>
       <c r="F444" s="2" t="s">
         <v>2190</v>
@@ -35488,19 +35490,19 @@
         <v>444</v>
       </c>
       <c r="B445" s="2" t="s">
-        <v>6711</v>
+        <v>6709</v>
       </c>
       <c r="C445" s="2" t="s">
-        <v>6712</v>
+        <v>6710</v>
       </c>
       <c r="D445" s="2" t="s">
         <v>2170</v>
       </c>
       <c r="E445" s="2" t="s">
-        <v>6709</v>
+        <v>6707</v>
       </c>
       <c r="F445" s="2" t="s">
-        <v>6710</v>
+        <v>6708</v>
       </c>
       <c r="G445" s="3">
         <v>4</v>
@@ -35729,10 +35731,10 @@
         <v>2235</v>
       </c>
       <c r="E453" s="2" t="s">
-        <v>6376</v>
+        <v>6374</v>
       </c>
       <c r="F453" s="2" t="s">
-        <v>6375</v>
+        <v>6373</v>
       </c>
       <c r="G453" s="3">
         <v>1</v>
@@ -35749,7 +35751,7 @@
         <v>453</v>
       </c>
       <c r="B454" s="2" t="s">
-        <v>6372</v>
+        <v>6370</v>
       </c>
       <c r="C454" s="2" t="s">
         <v>1359</v>
@@ -35758,10 +35760,10 @@
         <v>1344</v>
       </c>
       <c r="E454" s="2" t="s">
-        <v>6374</v>
+        <v>6372</v>
       </c>
       <c r="F454" s="2" t="s">
-        <v>6373</v>
+        <v>6371</v>
       </c>
       <c r="G454" s="3">
         <v>4</v>
@@ -36188,13 +36190,13 @@
         <v>2304</v>
       </c>
       <c r="D469" s="2" t="s">
-        <v>6730</v>
+        <v>6728</v>
       </c>
       <c r="E469" s="2" t="s">
         <v>2305</v>
       </c>
       <c r="F469" s="2" t="s">
-        <v>6731</v>
+        <v>6729</v>
       </c>
       <c r="G469" s="3">
         <v>1</v>
@@ -36789,7 +36791,7 @@
         <v>489</v>
       </c>
       <c r="B490" s="2" t="s">
-        <v>6925</v>
+        <v>6923</v>
       </c>
       <c r="C490" s="2" t="s">
         <v>2410</v>
@@ -37050,7 +37052,7 @@
         <v>498</v>
       </c>
       <c r="B499" s="2" t="s">
-        <v>6853</v>
+        <v>6851</v>
       </c>
       <c r="C499" s="2" t="s">
         <v>2453</v>
@@ -37195,19 +37197,19 @@
         <v>503</v>
       </c>
       <c r="B504" s="2" t="s">
-        <v>6421</v>
+        <v>6419</v>
       </c>
       <c r="C504" s="2" t="s">
-        <v>6422</v>
+        <v>6420</v>
       </c>
       <c r="D504" s="2" t="s">
         <v>2480</v>
       </c>
       <c r="E504" s="2" t="s">
-        <v>6423</v>
+        <v>6421</v>
       </c>
       <c r="F504" s="2" t="s">
-        <v>6424</v>
+        <v>6422</v>
       </c>
       <c r="G504" s="3">
         <v>4</v>
@@ -37280,7 +37282,7 @@
         <v>506</v>
       </c>
       <c r="B507" s="2" t="s">
-        <v>6637</v>
+        <v>6635</v>
       </c>
       <c r="C507" s="2" t="s">
         <v>2492</v>
@@ -37292,13 +37294,13 @@
         <v>2494</v>
       </c>
       <c r="F507" s="2" t="s">
-        <v>6636</v>
+        <v>6634</v>
       </c>
       <c r="G507" s="3">
         <v>3</v>
       </c>
       <c r="H507" s="2" t="s">
-        <v>6638</v>
+        <v>6636</v>
       </c>
       <c r="I507" s="2" t="s">
         <v>284</v>
@@ -37510,10 +37512,10 @@
         <v>514</v>
       </c>
       <c r="B515" s="2" t="s">
-        <v>6744</v>
+        <v>6742</v>
       </c>
       <c r="C515" s="2" t="s">
-        <v>6742</v>
+        <v>6740</v>
       </c>
       <c r="D515" s="2" t="s">
         <v>2528</v>
@@ -37522,7 +37524,7 @@
         <v>2514</v>
       </c>
       <c r="F515" s="2" t="s">
-        <v>6743</v>
+        <v>6741</v>
       </c>
       <c r="G515" s="3">
         <v>3</v>
@@ -37771,7 +37773,7 @@
         <v>523</v>
       </c>
       <c r="B524" s="2" t="s">
-        <v>7021</v>
+        <v>7019</v>
       </c>
       <c r="C524" s="2" t="s">
         <v>2572</v>
@@ -37800,7 +37802,7 @@
         <v>524</v>
       </c>
       <c r="B525" s="2" t="s">
-        <v>7020</v>
+        <v>7018</v>
       </c>
       <c r="C525" s="2" t="s">
         <v>2576</v>
@@ -37858,19 +37860,19 @@
         <v>526</v>
       </c>
       <c r="B527" s="2" t="s">
-        <v>6785</v>
+        <v>6783</v>
       </c>
       <c r="C527" s="2" t="s">
         <v>436</v>
       </c>
       <c r="D527" s="2" t="s">
+        <v>6784</v>
+      </c>
+      <c r="E527" s="2" t="s">
+        <v>6785</v>
+      </c>
+      <c r="F527" s="2" t="s">
         <v>6786</v>
-      </c>
-      <c r="E527" s="2" t="s">
-        <v>6787</v>
-      </c>
-      <c r="F527" s="2" t="s">
-        <v>6788</v>
       </c>
       <c r="G527" s="3">
         <v>1</v>
@@ -37887,19 +37889,19 @@
         <v>527</v>
       </c>
       <c r="B528" s="2" t="s">
-        <v>6789</v>
+        <v>6787</v>
       </c>
       <c r="C528" s="2" t="s">
-        <v>6936</v>
+        <v>6934</v>
       </c>
       <c r="D528" s="2" t="s">
         <v>2586</v>
       </c>
       <c r="E528" s="2" t="s">
+        <v>6933</v>
+      </c>
+      <c r="F528" s="2" t="s">
         <v>6935</v>
-      </c>
-      <c r="F528" s="2" t="s">
-        <v>6937</v>
       </c>
       <c r="G528" s="3">
         <v>1</v>
@@ -37974,19 +37976,19 @@
         <v>530</v>
       </c>
       <c r="B531" s="2" t="s">
+        <v>6643</v>
+      </c>
+      <c r="C531" s="2" t="s">
         <v>6645</v>
       </c>
-      <c r="C531" s="2" t="s">
-        <v>6647</v>
-      </c>
       <c r="D531" s="2" t="s">
-        <v>6646</v>
+        <v>6644</v>
       </c>
       <c r="E531" s="2" t="s">
         <v>77</v>
       </c>
       <c r="F531" s="2" t="s">
-        <v>6648</v>
+        <v>6646</v>
       </c>
       <c r="G531" s="3">
         <v>4</v>
@@ -38003,7 +38005,7 @@
         <v>531</v>
       </c>
       <c r="B532" s="2" t="s">
-        <v>7040</v>
+        <v>7038</v>
       </c>
       <c r="C532" s="2" t="s">
         <v>2601</v>
@@ -38012,10 +38014,10 @@
         <v>2602</v>
       </c>
       <c r="E532" s="2" t="s">
-        <v>7042</v>
+        <v>7040</v>
       </c>
       <c r="F532" s="2" t="s">
-        <v>7041</v>
+        <v>7039</v>
       </c>
       <c r="G532" s="3">
         <v>4</v>
@@ -38258,7 +38260,7 @@
         <v>540</v>
       </c>
       <c r="B541" s="2" t="s">
-        <v>6989</v>
+        <v>6987</v>
       </c>
       <c r="C541" s="2" t="s">
         <v>2632</v>
@@ -38267,10 +38269,10 @@
         <v>2633</v>
       </c>
       <c r="E541" s="2" t="s">
-        <v>6990</v>
+        <v>6988</v>
       </c>
       <c r="F541" s="2" t="s">
-        <v>6991</v>
+        <v>6989</v>
       </c>
       <c r="G541" s="3">
         <v>3</v>
@@ -38293,13 +38295,13 @@
         <v>2641</v>
       </c>
       <c r="D542" s="2" t="s">
+        <v>6799</v>
+      </c>
+      <c r="E542" s="2" t="s">
+        <v>6800</v>
+      </c>
+      <c r="F542" s="2" t="s">
         <v>6801</v>
-      </c>
-      <c r="E542" s="2" t="s">
-        <v>6802</v>
-      </c>
-      <c r="F542" s="2" t="s">
-        <v>6803</v>
       </c>
       <c r="G542" s="3">
         <v>3</v>
@@ -38377,7 +38379,7 @@
         <v>2655</v>
       </c>
       <c r="C545" s="2" t="s">
-        <v>6649</v>
+        <v>6647</v>
       </c>
       <c r="D545" s="2" t="s">
         <v>2656</v>
@@ -38386,7 +38388,7 @@
         <v>2657</v>
       </c>
       <c r="F545" s="2" t="s">
-        <v>6650</v>
+        <v>6648</v>
       </c>
       <c r="G545" s="3">
         <v>4</v>
@@ -38461,19 +38463,19 @@
         <v>547</v>
       </c>
       <c r="B548" s="2" t="s">
-        <v>6857</v>
+        <v>6855</v>
       </c>
       <c r="C548" s="2" t="s">
-        <v>6858</v>
+        <v>6856</v>
       </c>
       <c r="D548" s="2" t="s">
         <v>2670</v>
       </c>
       <c r="E548" s="2" t="s">
-        <v>6860</v>
+        <v>6858</v>
       </c>
       <c r="F548" s="2" t="s">
-        <v>6859</v>
+        <v>6857</v>
       </c>
       <c r="G548" s="3">
         <v>4</v>
@@ -38664,19 +38666,19 @@
         <v>554</v>
       </c>
       <c r="B555" s="2" t="s">
-        <v>6734</v>
+        <v>6732</v>
       </c>
       <c r="C555" s="2" t="s">
         <v>2697</v>
       </c>
       <c r="D555" s="2" t="s">
-        <v>6735</v>
+        <v>6733</v>
       </c>
       <c r="E555" s="2" t="s">
         <v>2698</v>
       </c>
       <c r="F555" s="2" t="s">
-        <v>6736</v>
+        <v>6734</v>
       </c>
       <c r="G555" s="3">
         <v>4</v>
@@ -38699,7 +38701,7 @@
         <v>2700</v>
       </c>
       <c r="D556" s="2" t="s">
-        <v>6951</v>
+        <v>6949</v>
       </c>
       <c r="E556" s="2" t="s">
         <v>2701</v>
@@ -38722,13 +38724,13 @@
         <v>556</v>
       </c>
       <c r="B557" s="2" t="s">
+        <v>6269</v>
+      </c>
+      <c r="C557" s="2" t="s">
+        <v>6270</v>
+      </c>
+      <c r="D557" s="2" t="s">
         <v>6271</v>
-      </c>
-      <c r="C557" s="2" t="s">
-        <v>6272</v>
-      </c>
-      <c r="D557" s="2" t="s">
-        <v>6273</v>
       </c>
       <c r="E557" s="2" t="s">
         <v>2704</v>
@@ -38925,10 +38927,10 @@
         <v>563</v>
       </c>
       <c r="B564" s="2" t="s">
-        <v>7051</v>
+        <v>7049</v>
       </c>
       <c r="C564" s="2" t="s">
-        <v>7050</v>
+        <v>7048</v>
       </c>
       <c r="D564" s="2" t="s">
         <v>2737</v>
@@ -38937,7 +38939,7 @@
         <v>2738</v>
       </c>
       <c r="F564" s="2" t="s">
-        <v>7052</v>
+        <v>7050</v>
       </c>
       <c r="G564" s="3">
         <v>3</v>
@@ -38960,13 +38962,13 @@
         <v>2741</v>
       </c>
       <c r="D565" s="2" t="s">
-        <v>6565</v>
+        <v>6563</v>
       </c>
       <c r="E565" s="2" t="s">
-        <v>6563</v>
+        <v>6561</v>
       </c>
       <c r="F565" s="2" t="s">
-        <v>6564</v>
+        <v>6562</v>
       </c>
       <c r="G565" s="3">
         <v>4</v>
@@ -38983,7 +38985,7 @@
         <v>565</v>
       </c>
       <c r="B566" s="2" t="s">
-        <v>6654</v>
+        <v>6652</v>
       </c>
       <c r="C566" s="2" t="s">
         <v>2743</v>
@@ -38995,7 +38997,7 @@
         <v>2745</v>
       </c>
       <c r="F566" s="2" t="s">
-        <v>6655</v>
+        <v>6653</v>
       </c>
       <c r="G566" s="3">
         <v>3</v>
@@ -39157,19 +39159,19 @@
         <v>571</v>
       </c>
       <c r="B572" s="2" t="s">
-        <v>6451</v>
+        <v>6449</v>
       </c>
       <c r="C572" s="2" t="s">
+        <v>6393</v>
+      </c>
+      <c r="D572" s="2" t="s">
+        <v>6394</v>
+      </c>
+      <c r="E572" s="2" t="s">
+        <v>6396</v>
+      </c>
+      <c r="F572" s="2" t="s">
         <v>6395</v>
-      </c>
-      <c r="D572" s="2" t="s">
-        <v>6396</v>
-      </c>
-      <c r="E572" s="2" t="s">
-        <v>6398</v>
-      </c>
-      <c r="F572" s="2" t="s">
-        <v>6397</v>
       </c>
       <c r="G572" s="3">
         <v>4</v>
@@ -39186,19 +39188,19 @@
         <v>572</v>
       </c>
       <c r="B573" s="2" t="s">
-        <v>6452</v>
+        <v>6450</v>
       </c>
       <c r="C573" s="2" t="s">
-        <v>6398</v>
+        <v>6396</v>
       </c>
       <c r="D573" s="2" t="s">
-        <v>6397</v>
+        <v>6395</v>
       </c>
       <c r="E573" s="2" t="s">
-        <v>6395</v>
+        <v>6393</v>
       </c>
       <c r="F573" s="2" t="s">
-        <v>6396</v>
+        <v>6394</v>
       </c>
       <c r="G573" s="3">
         <v>4</v>
@@ -39215,19 +39217,19 @@
         <v>573</v>
       </c>
       <c r="B574" s="2" t="s">
+        <v>6397</v>
+      </c>
+      <c r="C574" s="2" t="s">
+        <v>6395</v>
+      </c>
+      <c r="D574" s="2" t="s">
+        <v>6398</v>
+      </c>
+      <c r="E574" s="2" t="s">
         <v>6399</v>
       </c>
-      <c r="C574" s="2" t="s">
-        <v>6397</v>
-      </c>
-      <c r="D574" s="2" t="s">
-        <v>6400</v>
-      </c>
-      <c r="E574" s="2" t="s">
-        <v>6401</v>
-      </c>
       <c r="F574" s="2" t="s">
-        <v>6398</v>
+        <v>6396</v>
       </c>
       <c r="G574" s="3">
         <v>2</v>
@@ -39250,7 +39252,7 @@
         <v>2779</v>
       </c>
       <c r="D575" s="2" t="s">
-        <v>6402</v>
+        <v>6400</v>
       </c>
       <c r="E575" s="2" t="s">
         <v>2780</v>
@@ -39302,19 +39304,19 @@
         <v>576</v>
       </c>
       <c r="B577" s="2" t="s">
+        <v>6406</v>
+      </c>
+      <c r="C577" s="2" t="s">
+        <v>6410</v>
+      </c>
+      <c r="D577" s="2" t="s">
+        <v>6407</v>
+      </c>
+      <c r="E577" s="2" t="s">
         <v>6408</v>
       </c>
-      <c r="C577" s="2" t="s">
-        <v>6412</v>
-      </c>
-      <c r="D577" s="2" t="s">
+      <c r="F577" s="2" t="s">
         <v>6409</v>
-      </c>
-      <c r="E577" s="2" t="s">
-        <v>6410</v>
-      </c>
-      <c r="F577" s="2" t="s">
-        <v>6411</v>
       </c>
       <c r="G577" s="3">
         <v>3</v>
@@ -39331,19 +39333,19 @@
         <v>577</v>
       </c>
       <c r="B578" s="5" t="s">
+        <v>6401</v>
+      </c>
+      <c r="C578" s="2" t="s">
+        <v>6402</v>
+      </c>
+      <c r="D578" s="2" t="s">
         <v>6403</v>
       </c>
-      <c r="C578" s="2" t="s">
+      <c r="E578" s="2" t="s">
+        <v>6405</v>
+      </c>
+      <c r="F578" s="2" t="s">
         <v>6404</v>
-      </c>
-      <c r="D578" s="2" t="s">
-        <v>6405</v>
-      </c>
-      <c r="E578" s="2" t="s">
-        <v>6407</v>
-      </c>
-      <c r="F578" s="2" t="s">
-        <v>6406</v>
       </c>
       <c r="G578" s="3">
         <v>1</v>
@@ -39360,16 +39362,16 @@
         <v>578</v>
       </c>
       <c r="B579" s="2" t="s">
+        <v>6411</v>
+      </c>
+      <c r="C579" s="2" t="s">
+        <v>6412</v>
+      </c>
+      <c r="D579" s="2" t="s">
         <v>6413</v>
       </c>
-      <c r="C579" s="2" t="s">
+      <c r="E579" s="2" t="s">
         <v>6414</v>
-      </c>
-      <c r="D579" s="2" t="s">
-        <v>6415</v>
-      </c>
-      <c r="E579" s="2" t="s">
-        <v>6416</v>
       </c>
       <c r="F579" s="2" t="s">
         <v>2789</v>
@@ -39398,7 +39400,7 @@
         <v>2793</v>
       </c>
       <c r="E580" s="2" t="s">
-        <v>6747</v>
+        <v>6745</v>
       </c>
       <c r="F580" s="2" t="s">
         <v>2794</v>
@@ -39430,7 +39432,7 @@
         <v>2799</v>
       </c>
       <c r="F581" s="2" t="s">
-        <v>6479</v>
+        <v>6477</v>
       </c>
       <c r="G581" s="3">
         <v>3</v>
@@ -39563,7 +39565,7 @@
         <v>585</v>
       </c>
       <c r="B586" s="2" t="s">
-        <v>7002</v>
+        <v>7000</v>
       </c>
       <c r="C586" s="2" t="s">
         <v>2823</v>
@@ -39572,10 +39574,10 @@
         <v>2824</v>
       </c>
       <c r="E586" s="2" t="s">
-        <v>7003</v>
+        <v>7001</v>
       </c>
       <c r="F586" s="2" t="s">
-        <v>7004</v>
+        <v>7002</v>
       </c>
       <c r="G586" s="3">
         <v>4</v>
@@ -39706,19 +39708,19 @@
         <v>590</v>
       </c>
       <c r="B591" s="2" t="s">
+        <v>6890</v>
+      </c>
+      <c r="C591" s="2" t="s">
+        <v>6891</v>
+      </c>
+      <c r="D591" s="2" t="s">
         <v>6892</v>
       </c>
-      <c r="C591" s="2" t="s">
+      <c r="E591" s="2" t="s">
+        <v>6894</v>
+      </c>
+      <c r="F591" s="2" t="s">
         <v>6893</v>
-      </c>
-      <c r="D591" s="2" t="s">
-        <v>6894</v>
-      </c>
-      <c r="E591" s="2" t="s">
-        <v>6896</v>
-      </c>
-      <c r="F591" s="2" t="s">
-        <v>6895</v>
       </c>
       <c r="G591" s="3">
         <v>4</v>
@@ -39735,19 +39737,19 @@
         <v>591</v>
       </c>
       <c r="B592" s="2" t="s">
+        <v>6546</v>
+      </c>
+      <c r="C592" s="2" t="s">
+        <v>6560</v>
+      </c>
+      <c r="D592" s="2" t="s">
+        <v>6547</v>
+      </c>
+      <c r="E592" s="2" t="s">
         <v>6548</v>
       </c>
-      <c r="C592" s="2" t="s">
-        <v>6562</v>
-      </c>
-      <c r="D592" s="2" t="s">
+      <c r="F592" s="2" t="s">
         <v>6549</v>
-      </c>
-      <c r="E592" s="2" t="s">
-        <v>6550</v>
-      </c>
-      <c r="F592" s="2" t="s">
-        <v>6551</v>
       </c>
       <c r="G592" s="3">
         <v>1</v>
@@ -39793,10 +39795,10 @@
         <v>593</v>
       </c>
       <c r="B594" s="2" t="s">
-        <v>6693</v>
+        <v>6691</v>
       </c>
       <c r="C594" s="2" t="s">
-        <v>6692</v>
+        <v>6690</v>
       </c>
       <c r="D594" s="2" t="s">
         <v>2856</v>
@@ -39805,7 +39807,7 @@
         <v>2857</v>
       </c>
       <c r="F594" s="2" t="s">
-        <v>6694</v>
+        <v>6692</v>
       </c>
       <c r="G594" s="3">
         <v>3</v>
@@ -40431,7 +40433,7 @@
         <v>615</v>
       </c>
       <c r="B616" s="2" t="s">
-        <v>6300</v>
+        <v>6298</v>
       </c>
       <c r="C616" s="2" t="s">
         <v>2956</v>
@@ -40547,7 +40549,7 @@
         <v>619</v>
       </c>
       <c r="B620" s="2" t="s">
-        <v>6363</v>
+        <v>6361</v>
       </c>
       <c r="C620" s="2" t="s">
         <v>2977</v>
@@ -40559,7 +40561,7 @@
         <v>2979</v>
       </c>
       <c r="F620" s="2" t="s">
-        <v>6364</v>
+        <v>6362</v>
       </c>
       <c r="G620" s="3">
         <v>4</v>
@@ -40576,7 +40578,7 @@
         <v>620</v>
       </c>
       <c r="B621" s="2" t="s">
-        <v>7012</v>
+        <v>7010</v>
       </c>
       <c r="C621" s="2" t="s">
         <v>2981</v>
@@ -40588,7 +40590,7 @@
         <v>2983</v>
       </c>
       <c r="F621" s="2" t="s">
-        <v>7013</v>
+        <v>7011</v>
       </c>
       <c r="G621" s="3">
         <v>4</v>
@@ -40634,7 +40636,7 @@
         <v>622</v>
       </c>
       <c r="B623" s="2" t="s">
-        <v>7027</v>
+        <v>7025</v>
       </c>
       <c r="C623" s="2" t="s">
         <v>954</v>
@@ -40646,7 +40648,7 @@
         <v>955</v>
       </c>
       <c r="F623" s="2" t="s">
-        <v>7028</v>
+        <v>7026</v>
       </c>
       <c r="G623" s="3">
         <v>3</v>
@@ -40663,19 +40665,19 @@
         <v>623</v>
       </c>
       <c r="B624" s="2" t="s">
+        <v>7027</v>
+      </c>
+      <c r="C624" s="2" t="s">
+        <v>7028</v>
+      </c>
+      <c r="D624" s="2" t="s">
         <v>7029</v>
       </c>
-      <c r="C624" s="2" t="s">
+      <c r="E624" s="2" t="s">
         <v>7030</v>
       </c>
-      <c r="D624" s="2" t="s">
-        <v>7031</v>
-      </c>
-      <c r="E624" s="2" t="s">
-        <v>7032</v>
-      </c>
       <c r="F624" s="2" t="s">
-        <v>7011</v>
+        <v>7009</v>
       </c>
       <c r="G624" s="3">
         <v>4</v>
@@ -40721,19 +40723,19 @@
         <v>625</v>
       </c>
       <c r="B626" s="2" t="s">
+        <v>6564</v>
+      </c>
+      <c r="C626" s="2" t="s">
+        <v>6565</v>
+      </c>
+      <c r="D626" s="2" t="s">
         <v>6566</v>
       </c>
-      <c r="C626" s="2" t="s">
+      <c r="E626" s="2" t="s">
         <v>6567</v>
       </c>
-      <c r="D626" s="2" t="s">
+      <c r="F626" s="2" t="s">
         <v>6568</v>
-      </c>
-      <c r="E626" s="2" t="s">
-        <v>6569</v>
-      </c>
-      <c r="F626" s="2" t="s">
-        <v>6570</v>
       </c>
       <c r="G626" s="3">
         <v>4</v>
@@ -40750,7 +40752,7 @@
         <v>626</v>
       </c>
       <c r="B627" s="2" t="s">
-        <v>6497</v>
+        <v>6495</v>
       </c>
       <c r="C627" s="2" t="s">
         <v>1022</v>
@@ -40846,10 +40848,10 @@
         <v>3016</v>
       </c>
       <c r="E630" s="2" t="s">
-        <v>6652</v>
+        <v>6650</v>
       </c>
       <c r="F630" s="2" t="s">
-        <v>6653</v>
+        <v>6651</v>
       </c>
       <c r="G630" s="3">
         <v>1</v>
@@ -40924,7 +40926,7 @@
         <v>632</v>
       </c>
       <c r="B633" s="2" t="s">
-        <v>6664</v>
+        <v>6662</v>
       </c>
       <c r="C633" s="2" t="s">
         <v>3030</v>
@@ -40953,19 +40955,19 @@
         <v>633</v>
       </c>
       <c r="B634" s="2" t="s">
-        <v>6667</v>
+        <v>6665</v>
       </c>
       <c r="C634" s="2" t="s">
+        <v>6661</v>
+      </c>
+      <c r="D634" s="2" t="s">
+        <v>6664</v>
+      </c>
+      <c r="E634" s="2" t="s">
+        <v>6666</v>
+      </c>
+      <c r="F634" s="2" t="s">
         <v>6663</v>
-      </c>
-      <c r="D634" s="2" t="s">
-        <v>6666</v>
-      </c>
-      <c r="E634" s="2" t="s">
-        <v>6668</v>
-      </c>
-      <c r="F634" s="2" t="s">
-        <v>6665</v>
       </c>
       <c r="G634" s="3">
         <v>4</v>
@@ -41011,19 +41013,19 @@
         <v>635</v>
       </c>
       <c r="B636" s="2" t="s">
-        <v>6842</v>
+        <v>6840</v>
       </c>
       <c r="C636" s="2" t="s">
+        <v>6837</v>
+      </c>
+      <c r="D636" s="2" t="s">
+        <v>6838</v>
+      </c>
+      <c r="E636" s="2" t="s">
         <v>6839</v>
       </c>
-      <c r="D636" s="2" t="s">
-        <v>6840</v>
-      </c>
-      <c r="E636" s="2" t="s">
+      <c r="F636" s="2" t="s">
         <v>6841</v>
-      </c>
-      <c r="F636" s="2" t="s">
-        <v>6843</v>
       </c>
       <c r="G636" s="3">
         <v>1</v>
@@ -41139,7 +41141,7 @@
         <v>3060</v>
       </c>
       <c r="F640" s="2" t="s">
-        <v>6278</v>
+        <v>6276</v>
       </c>
       <c r="G640" s="3">
         <v>2</v>
@@ -41359,7 +41361,7 @@
         <v>647</v>
       </c>
       <c r="B648" s="2" t="s">
-        <v>6617</v>
+        <v>6615</v>
       </c>
       <c r="C648" s="2" t="s">
         <v>3094</v>
@@ -41371,7 +41373,7 @@
         <v>3097</v>
       </c>
       <c r="F648" s="2" t="s">
-        <v>6618</v>
+        <v>6616</v>
       </c>
       <c r="G648" s="3">
         <v>1</v>
@@ -41417,7 +41419,7 @@
         <v>649</v>
       </c>
       <c r="B650" s="2" t="s">
-        <v>6861</v>
+        <v>6859</v>
       </c>
       <c r="C650" s="2" t="s">
         <v>3105</v>
@@ -41446,7 +41448,7 @@
         <v>650</v>
       </c>
       <c r="B651" s="2" t="s">
-        <v>6311</v>
+        <v>6309</v>
       </c>
       <c r="C651" s="2" t="s">
         <v>3110</v>
@@ -41455,10 +41457,10 @@
         <v>3111</v>
       </c>
       <c r="E651" s="2" t="s">
-        <v>6312</v>
+        <v>6310</v>
       </c>
       <c r="F651" s="2" t="s">
-        <v>6313</v>
+        <v>6311</v>
       </c>
       <c r="G651" s="3">
         <v>2</v>
@@ -41504,7 +41506,7 @@
         <v>652</v>
       </c>
       <c r="B653" s="2" t="s">
-        <v>6359</v>
+        <v>6357</v>
       </c>
       <c r="C653" s="2" t="s">
         <v>1436</v>
@@ -41516,7 +41518,7 @@
         <v>3120</v>
       </c>
       <c r="F653" s="2" t="s">
-        <v>6360</v>
+        <v>6358</v>
       </c>
       <c r="G653" s="3">
         <v>1</v>
@@ -41562,10 +41564,10 @@
         <v>654</v>
       </c>
       <c r="B655" s="2" t="s">
-        <v>6727</v>
+        <v>6725</v>
       </c>
       <c r="C655" s="2" t="s">
-        <v>6728</v>
+        <v>6726</v>
       </c>
       <c r="D655" s="2" t="s">
         <v>3129</v>
@@ -41574,7 +41576,7 @@
         <v>3130</v>
       </c>
       <c r="F655" s="2" t="s">
-        <v>6729</v>
+        <v>6727</v>
       </c>
       <c r="G655" s="3">
         <v>4</v>
@@ -41852,7 +41854,7 @@
         <v>664</v>
       </c>
       <c r="B665" s="2" t="s">
-        <v>7038</v>
+        <v>7036</v>
       </c>
       <c r="C665" s="2" t="s">
         <v>3181</v>
@@ -42805,7 +42807,7 @@
         <v>697</v>
       </c>
       <c r="B698" s="2" t="s">
-        <v>6700</v>
+        <v>6698</v>
       </c>
       <c r="C698" s="2" t="s">
         <v>3326</v>
@@ -42817,7 +42819,7 @@
         <v>3328</v>
       </c>
       <c r="F698" s="2" t="s">
-        <v>6699</v>
+        <v>6697</v>
       </c>
       <c r="G698" s="3">
         <v>4</v>
@@ -42834,7 +42836,7 @@
         <v>698</v>
       </c>
       <c r="B699" s="2" t="s">
-        <v>6698</v>
+        <v>6696</v>
       </c>
       <c r="C699" s="2" t="s">
         <v>3330</v>
@@ -42892,7 +42894,7 @@
         <v>700</v>
       </c>
       <c r="B701" s="2" t="s">
-        <v>6994</v>
+        <v>6992</v>
       </c>
       <c r="C701" s="2" t="s">
         <v>975</v>
@@ -43008,25 +43010,25 @@
         <v>704</v>
       </c>
       <c r="B705" s="2" t="s">
-        <v>6953</v>
+        <v>6951</v>
       </c>
       <c r="C705" s="2" t="s">
         <v>3361</v>
       </c>
       <c r="D705" s="2" t="s">
-        <v>6513</v>
+        <v>6511</v>
       </c>
       <c r="E705" s="2" t="s">
         <v>3362</v>
       </c>
       <c r="F705" s="2" t="s">
-        <v>6514</v>
+        <v>6512</v>
       </c>
       <c r="G705" s="3">
         <v>2</v>
       </c>
       <c r="H705" s="2" t="s">
-        <v>6515</v>
+        <v>6513</v>
       </c>
       <c r="I705" s="2" t="s">
         <v>15</v>
@@ -43037,7 +43039,7 @@
         <v>705</v>
       </c>
       <c r="B706" s="2" t="s">
-        <v>6952</v>
+        <v>6950</v>
       </c>
       <c r="C706" s="2" t="s">
         <v>107</v>
@@ -43046,10 +43048,10 @@
         <v>3363</v>
       </c>
       <c r="E706" s="2" t="s">
-        <v>6954</v>
+        <v>6952</v>
       </c>
       <c r="F706" s="2" t="s">
-        <v>6955</v>
+        <v>6953</v>
       </c>
       <c r="G706" s="3">
         <v>4</v>
@@ -43414,7 +43416,7 @@
         <v>718</v>
       </c>
       <c r="B719" s="2" t="s">
-        <v>6387</v>
+        <v>6385</v>
       </c>
       <c r="C719" s="2" t="s">
         <v>686</v>
@@ -43565,7 +43567,7 @@
         <v>3433</v>
       </c>
       <c r="D724" s="2" t="s">
-        <v>7046</v>
+        <v>7044</v>
       </c>
       <c r="E724" s="2" t="s">
         <v>3411</v>
@@ -43613,7 +43615,7 @@
         <v>725</v>
       </c>
       <c r="B726" s="2" t="s">
-        <v>6453</v>
+        <v>6451</v>
       </c>
       <c r="C726" s="2" t="s">
         <v>3439</v>
@@ -43622,10 +43624,10 @@
         <v>3440</v>
       </c>
       <c r="E726" s="2" t="s">
-        <v>6454</v>
+        <v>6452</v>
       </c>
       <c r="F726" s="2" t="s">
-        <v>6455</v>
+        <v>6453</v>
       </c>
       <c r="G726" s="3">
         <v>1</v>
@@ -43680,10 +43682,10 @@
         <v>3445</v>
       </c>
       <c r="E728" s="2" t="s">
-        <v>6722</v>
+        <v>6720</v>
       </c>
       <c r="F728" s="2" t="s">
-        <v>6723</v>
+        <v>6721</v>
       </c>
       <c r="G728" s="3">
         <v>3</v>
@@ -43758,16 +43760,16 @@
         <v>730</v>
       </c>
       <c r="B731" s="2" t="s">
+        <v>6473</v>
+      </c>
+      <c r="C731" s="2" t="s">
+        <v>6474</v>
+      </c>
+      <c r="D731" s="2" t="s">
         <v>6475</v>
       </c>
-      <c r="C731" s="2" t="s">
+      <c r="E731" s="2" t="s">
         <v>6476</v>
-      </c>
-      <c r="D731" s="2" t="s">
-        <v>6477</v>
-      </c>
-      <c r="E731" s="2" t="s">
-        <v>6478</v>
       </c>
       <c r="F731" s="2" t="s">
         <v>51</v>
@@ -43845,7 +43847,7 @@
         <v>733</v>
       </c>
       <c r="B734" s="2" t="s">
-        <v>6540</v>
+        <v>6538</v>
       </c>
       <c r="C734" s="6">
         <v>7.0000000000000007E-2</v>
@@ -43877,16 +43879,16 @@
         <v>3469</v>
       </c>
       <c r="C735" s="2" t="s">
+        <v>6535</v>
+      </c>
+      <c r="D735" s="2" t="s">
+        <v>6534</v>
+      </c>
+      <c r="E735" s="2" t="s">
         <v>6537</v>
       </c>
-      <c r="D735" s="2" t="s">
+      <c r="F735" s="2" t="s">
         <v>6536</v>
-      </c>
-      <c r="E735" s="2" t="s">
-        <v>6539</v>
-      </c>
-      <c r="F735" s="2" t="s">
-        <v>6538</v>
       </c>
       <c r="G735" s="3">
         <v>4</v>
@@ -43932,19 +43934,19 @@
         <v>736</v>
       </c>
       <c r="B737" s="2" t="s">
-        <v>6447</v>
+        <v>6445</v>
       </c>
       <c r="C737" s="2" t="s">
+        <v>6994</v>
+      </c>
+      <c r="D737" s="2" t="s">
+        <v>6995</v>
+      </c>
+      <c r="E737" s="2" t="s">
         <v>6996</v>
       </c>
-      <c r="D737" s="2" t="s">
+      <c r="F737" s="2" t="s">
         <v>6997</v>
-      </c>
-      <c r="E737" s="2" t="s">
-        <v>6998</v>
-      </c>
-      <c r="F737" s="2" t="s">
-        <v>6999</v>
       </c>
       <c r="G737" s="3">
         <v>2</v>
@@ -43961,13 +43963,13 @@
         <v>737</v>
       </c>
       <c r="B738" s="2" t="s">
+        <v>6446</v>
+      </c>
+      <c r="C738" s="2" t="s">
+        <v>6447</v>
+      </c>
+      <c r="D738" s="2" t="s">
         <v>6448</v>
-      </c>
-      <c r="C738" s="2" t="s">
-        <v>6449</v>
-      </c>
-      <c r="D738" s="2" t="s">
-        <v>6450</v>
       </c>
       <c r="E738" s="2" t="s">
         <v>3475</v>
@@ -44019,7 +44021,7 @@
         <v>739</v>
       </c>
       <c r="B740" s="2" t="s">
-        <v>6670</v>
+        <v>6668</v>
       </c>
       <c r="C740" s="6">
         <v>0.05</v>
@@ -44080,13 +44082,13 @@
         <v>3486</v>
       </c>
       <c r="C742" s="2" t="s">
-        <v>6268</v>
+        <v>6266</v>
       </c>
       <c r="D742" s="2" t="s">
         <v>3487</v>
       </c>
       <c r="E742" s="2" t="s">
-        <v>6269</v>
+        <v>6267</v>
       </c>
       <c r="F742" s="2" t="s">
         <v>51</v>
@@ -44365,19 +44367,19 @@
         <v>751</v>
       </c>
       <c r="B752" s="2" t="s">
+        <v>6806</v>
+      </c>
+      <c r="C752" s="2" t="s">
+        <v>6807</v>
+      </c>
+      <c r="D752" s="2" t="s">
         <v>6808</v>
-      </c>
-      <c r="C752" s="2" t="s">
-        <v>6809</v>
-      </c>
-      <c r="D752" s="2" t="s">
-        <v>6810</v>
       </c>
       <c r="E752" s="2" t="s">
         <v>3518</v>
       </c>
       <c r="F752" s="2" t="s">
-        <v>6811</v>
+        <v>6809</v>
       </c>
       <c r="G752" s="3">
         <v>2</v>
@@ -44464,7 +44466,7 @@
         <v>955</v>
       </c>
       <c r="F755" s="2" t="s">
-        <v>6934</v>
+        <v>6932</v>
       </c>
       <c r="G755" s="3">
         <v>2</v>
@@ -44481,25 +44483,25 @@
         <v>755</v>
       </c>
       <c r="B756" s="2" t="s">
+        <v>6287</v>
+      </c>
+      <c r="C756" s="2" t="s">
+        <v>6288</v>
+      </c>
+      <c r="D756" s="2" t="s">
         <v>6289</v>
       </c>
-      <c r="C756" s="2" t="s">
+      <c r="E756" s="2" t="s">
         <v>6290</v>
       </c>
-      <c r="D756" s="2" t="s">
+      <c r="F756" s="2" t="s">
         <v>6291</v>
-      </c>
-      <c r="E756" s="2" t="s">
-        <v>6292</v>
-      </c>
-      <c r="F756" s="2" t="s">
-        <v>6293</v>
       </c>
       <c r="G756" s="3">
         <v>2</v>
       </c>
       <c r="H756" s="2" t="s">
-        <v>6294</v>
+        <v>6292</v>
       </c>
       <c r="I756" s="2" t="s">
         <v>773</v>
@@ -44687,13 +44689,13 @@
         <v>3563</v>
       </c>
       <c r="C763" s="2" t="s">
-        <v>6898</v>
+        <v>6896</v>
       </c>
       <c r="D763" s="2" t="s">
         <v>3564</v>
       </c>
       <c r="E763" s="2" t="s">
-        <v>6899</v>
+        <v>6897</v>
       </c>
       <c r="F763" s="2" t="s">
         <v>3565</v>
@@ -44800,19 +44802,19 @@
         <v>766</v>
       </c>
       <c r="B767" s="2" t="s">
-        <v>6619</v>
+        <v>6617</v>
       </c>
       <c r="C767" s="2" t="s">
         <v>97</v>
       </c>
       <c r="D767" s="2" t="s">
-        <v>6620</v>
+        <v>6618</v>
       </c>
       <c r="E767" s="2" t="s">
         <v>3581</v>
       </c>
       <c r="F767" s="2" t="s">
-        <v>6621</v>
+        <v>6619</v>
       </c>
       <c r="G767" s="3">
         <v>3</v>
@@ -44885,7 +44887,7 @@
         <v>769</v>
       </c>
       <c r="B770" s="2" t="s">
-        <v>6867</v>
+        <v>6865</v>
       </c>
       <c r="C770" s="2" t="s">
         <v>3593</v>
@@ -44972,7 +44974,7 @@
         <v>772</v>
       </c>
       <c r="B773" s="2" t="s">
-        <v>6769</v>
+        <v>6767</v>
       </c>
       <c r="C773" s="2" t="s">
         <v>491</v>
@@ -44984,7 +44986,7 @@
         <v>493</v>
       </c>
       <c r="F773" s="4" t="s">
-        <v>6770</v>
+        <v>6768</v>
       </c>
       <c r="G773" s="3">
         <v>2</v>
@@ -45100,7 +45102,7 @@
         <v>494</v>
       </c>
       <c r="F777" s="4" t="s">
-        <v>6984</v>
+        <v>6982</v>
       </c>
       <c r="G777" s="3">
         <v>4</v>
@@ -45320,19 +45322,19 @@
         <v>784</v>
       </c>
       <c r="B785" s="2" t="s">
+        <v>6802</v>
+      </c>
+      <c r="C785" s="2" t="s">
+        <v>6803</v>
+      </c>
+      <c r="D785" s="2" t="s">
         <v>6804</v>
-      </c>
-      <c r="C785" s="2" t="s">
-        <v>6805</v>
-      </c>
-      <c r="D785" s="2" t="s">
-        <v>6806</v>
       </c>
       <c r="E785" s="2" t="s">
         <v>3651</v>
       </c>
       <c r="F785" s="2" t="s">
-        <v>6807</v>
+        <v>6805</v>
       </c>
       <c r="G785" s="3">
         <v>1</v>
@@ -45494,13 +45496,13 @@
         <v>790</v>
       </c>
       <c r="B791" s="2" t="s">
-        <v>6634</v>
+        <v>6632</v>
       </c>
       <c r="C791" s="2" t="s">
+        <v>6631</v>
+      </c>
+      <c r="D791" s="2" t="s">
         <v>6633</v>
-      </c>
-      <c r="D791" s="2" t="s">
-        <v>6635</v>
       </c>
       <c r="E791" s="2" t="s">
         <v>3411</v>
@@ -45842,19 +45844,19 @@
         <v>802</v>
       </c>
       <c r="B803" s="2" t="s">
-        <v>6592</v>
+        <v>6590</v>
       </c>
       <c r="C803" s="2" t="s">
         <v>3735</v>
       </c>
       <c r="D803" s="2" t="s">
-        <v>6593</v>
+        <v>6591</v>
       </c>
       <c r="E803" s="2" t="s">
         <v>3736</v>
       </c>
       <c r="F803" s="2" t="s">
-        <v>6594</v>
+        <v>6592</v>
       </c>
       <c r="G803" s="3">
         <v>3</v>
@@ -45900,7 +45902,7 @@
         <v>804</v>
       </c>
       <c r="B805" s="2" t="s">
-        <v>6426</v>
+        <v>6424</v>
       </c>
       <c r="C805" s="2" t="s">
         <v>3744</v>
@@ -46132,13 +46134,13 @@
         <v>812</v>
       </c>
       <c r="B813" s="2" t="s">
-        <v>6357</v>
+        <v>6355</v>
       </c>
       <c r="C813" s="2" t="s">
         <v>3786</v>
       </c>
       <c r="D813" s="2" t="s">
-        <v>6358</v>
+        <v>6356</v>
       </c>
       <c r="E813" s="2" t="s">
         <v>3787</v>
@@ -46161,7 +46163,7 @@
         <v>813</v>
       </c>
       <c r="B814" s="2" t="s">
-        <v>6684</v>
+        <v>6682</v>
       </c>
       <c r="C814" s="2" t="s">
         <v>3790</v>
@@ -46173,7 +46175,7 @@
         <v>3792</v>
       </c>
       <c r="F814" s="2" t="s">
-        <v>6685</v>
+        <v>6683</v>
       </c>
       <c r="G814" s="3">
         <v>1</v>
@@ -46190,7 +46192,7 @@
         <v>814</v>
       </c>
       <c r="B815" s="2" t="s">
-        <v>6355</v>
+        <v>6353</v>
       </c>
       <c r="C815" s="2" t="s">
         <v>3794</v>
@@ -46202,7 +46204,7 @@
         <v>3796</v>
       </c>
       <c r="F815" s="2" t="s">
-        <v>6356</v>
+        <v>6354</v>
       </c>
       <c r="G815" s="3">
         <v>1</v>
@@ -46341,13 +46343,13 @@
         <v>3816</v>
       </c>
       <c r="D820" s="2" t="s">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="E820" s="2" t="s">
         <v>3817</v>
       </c>
       <c r="F820" s="2" t="s">
-        <v>6465</v>
+        <v>6463</v>
       </c>
       <c r="G820" s="3">
         <v>4</v>
@@ -46422,7 +46424,7 @@
         <v>822</v>
       </c>
       <c r="B823" s="2" t="s">
-        <v>6689</v>
+        <v>6687</v>
       </c>
       <c r="C823" s="2" t="s">
         <v>3830</v>
@@ -46431,10 +46433,10 @@
         <v>3831</v>
       </c>
       <c r="E823" s="2" t="s">
-        <v>6690</v>
+        <v>6688</v>
       </c>
       <c r="F823" s="2" t="s">
-        <v>6691</v>
+        <v>6689</v>
       </c>
       <c r="G823" s="3">
         <v>4</v>
@@ -46480,7 +46482,7 @@
         <v>824</v>
       </c>
       <c r="B825" s="2" t="s">
-        <v>6783</v>
+        <v>6781</v>
       </c>
       <c r="C825" s="2" t="s">
         <v>102</v>
@@ -46492,7 +46494,7 @@
         <v>3839</v>
       </c>
       <c r="F825" s="2" t="s">
-        <v>6784</v>
+        <v>6782</v>
       </c>
       <c r="G825" s="3">
         <v>3</v>
@@ -46596,7 +46598,7 @@
         <v>828</v>
       </c>
       <c r="B829" s="2" t="s">
-        <v>6425</v>
+        <v>6423</v>
       </c>
       <c r="C829" s="2" t="s">
         <v>3857</v>
@@ -46628,16 +46630,16 @@
         <v>3862</v>
       </c>
       <c r="C830" s="2" t="s">
+        <v>6570</v>
+      </c>
+      <c r="D830" s="2" t="s">
+        <v>6569</v>
+      </c>
+      <c r="E830" s="2" t="s">
+        <v>6571</v>
+      </c>
+      <c r="F830" s="2" t="s">
         <v>6572</v>
-      </c>
-      <c r="D830" s="2" t="s">
-        <v>6571</v>
-      </c>
-      <c r="E830" s="2" t="s">
-        <v>6573</v>
-      </c>
-      <c r="F830" s="2" t="s">
-        <v>6574</v>
       </c>
       <c r="G830" s="3">
         <v>4</v>
@@ -46686,16 +46688,16 @@
         <v>3870</v>
       </c>
       <c r="C832" s="2" t="s">
+        <v>6389</v>
+      </c>
+      <c r="D832" s="2" t="s">
+        <v>6390</v>
+      </c>
+      <c r="E832" s="2" t="s">
         <v>6391</v>
       </c>
-      <c r="D832" s="2" t="s">
+      <c r="F832" s="2" t="s">
         <v>6392</v>
-      </c>
-      <c r="E832" s="2" t="s">
-        <v>6393</v>
-      </c>
-      <c r="F832" s="2" t="s">
-        <v>6394</v>
       </c>
       <c r="G832" s="3">
         <v>4</v>
@@ -46857,7 +46859,7 @@
         <v>837</v>
       </c>
       <c r="B838" s="2" t="s">
-        <v>6826</v>
+        <v>6824</v>
       </c>
       <c r="C838" s="2" t="s">
         <v>3896</v>
@@ -46869,7 +46871,7 @@
         <v>3898</v>
       </c>
       <c r="F838" s="2" t="s">
-        <v>6827</v>
+        <v>6825</v>
       </c>
       <c r="G838" s="3">
         <v>4</v>
@@ -46944,13 +46946,13 @@
         <v>840</v>
       </c>
       <c r="B841" s="2" t="s">
+        <v>7032</v>
+      </c>
+      <c r="C841" s="2" t="s">
+        <v>7033</v>
+      </c>
+      <c r="D841" s="2" t="s">
         <v>7034</v>
-      </c>
-      <c r="C841" s="2" t="s">
-        <v>7035</v>
-      </c>
-      <c r="D841" s="2" t="s">
-        <v>7036</v>
       </c>
       <c r="E841" s="2" t="s">
         <v>3912</v>
@@ -47002,7 +47004,7 @@
         <v>842</v>
       </c>
       <c r="B843" s="7" t="s">
-        <v>7022</v>
+        <v>7020</v>
       </c>
       <c r="C843" s="2" t="s">
         <v>3916</v>
@@ -47011,16 +47013,16 @@
         <v>3921</v>
       </c>
       <c r="E843" s="2" t="s">
+        <v>7021</v>
+      </c>
+      <c r="F843" s="2" t="s">
         <v>7023</v>
-      </c>
-      <c r="F843" s="2" t="s">
-        <v>7025</v>
       </c>
       <c r="G843" s="3">
         <v>3</v>
       </c>
       <c r="H843" s="2" t="s">
-        <v>7024</v>
+        <v>7022</v>
       </c>
       <c r="I843" s="2" t="s">
         <v>15</v>
@@ -47290,7 +47292,7 @@
         <v>852</v>
       </c>
       <c r="B853" s="2" t="s">
-        <v>6828</v>
+        <v>6826</v>
       </c>
       <c r="C853" s="2" t="s">
         <v>743</v>
@@ -47299,7 +47301,7 @@
         <v>744</v>
       </c>
       <c r="E853" s="2" t="s">
-        <v>6829</v>
+        <v>6827</v>
       </c>
       <c r="F853" s="2" t="s">
         <v>3962</v>
@@ -47496,7 +47498,7 @@
         <v>3996</v>
       </c>
       <c r="C860" s="2" t="s">
-        <v>6745</v>
+        <v>6743</v>
       </c>
       <c r="D860" s="2" t="s">
         <v>3997</v>
@@ -47638,7 +47640,7 @@
         <v>864</v>
       </c>
       <c r="B865" s="2" t="s">
-        <v>6316</v>
+        <v>6314</v>
       </c>
       <c r="C865" s="2" t="s">
         <v>4023</v>
@@ -47647,10 +47649,10 @@
         <v>2878</v>
       </c>
       <c r="E865" s="2" t="s">
-        <v>6314</v>
+        <v>6312</v>
       </c>
       <c r="F865" s="2" t="s">
-        <v>6315</v>
+        <v>6313</v>
       </c>
       <c r="G865" s="3">
         <v>4</v>
@@ -47667,19 +47669,19 @@
         <v>865</v>
       </c>
       <c r="B866" s="2" t="s">
+        <v>6319</v>
+      </c>
+      <c r="C866" s="2" t="s">
+        <v>6320</v>
+      </c>
+      <c r="D866" s="4" t="s">
         <v>6321</v>
       </c>
-      <c r="C866" s="2" t="s">
+      <c r="E866" s="2" t="s">
         <v>6322</v>
       </c>
-      <c r="D866" s="4" t="s">
+      <c r="F866" s="2" t="s">
         <v>6323</v>
-      </c>
-      <c r="E866" s="2" t="s">
-        <v>6324</v>
-      </c>
-      <c r="F866" s="2" t="s">
-        <v>6325</v>
       </c>
       <c r="G866" s="3">
         <v>3</v>
@@ -47783,7 +47785,7 @@
         <v>869</v>
       </c>
       <c r="B870" s="2" t="s">
-        <v>6527</v>
+        <v>6525</v>
       </c>
       <c r="C870" s="2" t="s">
         <v>4041</v>
@@ -47792,10 +47794,10 @@
         <v>4042</v>
       </c>
       <c r="E870" s="2" t="s">
-        <v>6529</v>
+        <v>6527</v>
       </c>
       <c r="F870" s="2" t="s">
-        <v>6528</v>
+        <v>6526</v>
       </c>
       <c r="G870" s="3">
         <v>4</v>
@@ -47870,7 +47872,7 @@
         <v>872</v>
       </c>
       <c r="B873" s="2" t="s">
-        <v>6817</v>
+        <v>6815</v>
       </c>
       <c r="C873" s="2" t="s">
         <v>3766</v>
@@ -47899,7 +47901,7 @@
         <v>873</v>
       </c>
       <c r="B874" s="2" t="s">
-        <v>6687</v>
+        <v>6685</v>
       </c>
       <c r="C874" s="2" t="s">
         <v>927</v>
@@ -47911,7 +47913,7 @@
         <v>4062</v>
       </c>
       <c r="F874" s="2" t="s">
-        <v>6688</v>
+        <v>6686</v>
       </c>
       <c r="G874" s="3">
         <v>1</v>
@@ -48103,7 +48105,7 @@
         <v>4097</v>
       </c>
       <c r="C881" s="2" t="s">
-        <v>6276</v>
+        <v>6274</v>
       </c>
       <c r="D881" s="2" t="s">
         <v>2878</v>
@@ -48112,7 +48114,7 @@
         <v>4098</v>
       </c>
       <c r="F881" s="2" t="s">
-        <v>6277</v>
+        <v>6275</v>
       </c>
       <c r="G881" s="3">
         <v>1</v>
@@ -48129,7 +48131,7 @@
         <v>881</v>
       </c>
       <c r="B882" s="2" t="s">
-        <v>6656</v>
+        <v>6654</v>
       </c>
       <c r="C882" s="2" t="s">
         <v>3897</v>
@@ -48141,7 +48143,7 @@
         <v>4100</v>
       </c>
       <c r="F882" s="2" t="s">
-        <v>6657</v>
+        <v>6655</v>
       </c>
       <c r="G882" s="3">
         <v>3</v>
@@ -48245,7 +48247,7 @@
         <v>885</v>
       </c>
       <c r="B886" s="2" t="s">
-        <v>6632</v>
+        <v>6630</v>
       </c>
       <c r="C886" s="2" t="s">
         <v>4120</v>
@@ -48344,7 +48346,7 @@
         <v>4136</v>
       </c>
       <c r="F889" s="2" t="s">
-        <v>6897</v>
+        <v>6895</v>
       </c>
       <c r="G889" s="3">
         <v>3</v>
@@ -48448,19 +48450,19 @@
         <v>892</v>
       </c>
       <c r="B893" s="2" t="s">
+        <v>6530</v>
+      </c>
+      <c r="C893" s="2" t="s">
+        <v>6531</v>
+      </c>
+      <c r="D893" s="2" t="s">
         <v>6532</v>
-      </c>
-      <c r="C893" s="2" t="s">
-        <v>6533</v>
-      </c>
-      <c r="D893" s="2" t="s">
-        <v>6534</v>
       </c>
       <c r="E893" s="2" t="s">
         <v>4151</v>
       </c>
       <c r="F893" s="2" t="s">
-        <v>6535</v>
+        <v>6533</v>
       </c>
       <c r="G893" s="3">
         <v>2</v>
@@ -48541,7 +48543,7 @@
         <v>4166</v>
       </c>
       <c r="D896" s="2" t="s">
-        <v>6745</v>
+        <v>6743</v>
       </c>
       <c r="E896" s="2" t="s">
         <v>3997</v>
@@ -48564,16 +48566,16 @@
         <v>896</v>
       </c>
       <c r="B897" s="2" t="s">
-        <v>6282</v>
+        <v>6280</v>
       </c>
       <c r="C897" s="2" t="s">
         <v>3897</v>
       </c>
       <c r="D897" s="2" t="s">
-        <v>6283</v>
+        <v>6281</v>
       </c>
       <c r="E897" s="2" t="s">
-        <v>6284</v>
+        <v>6282</v>
       </c>
       <c r="F897" s="2" t="s">
         <v>3977</v>
@@ -48596,7 +48598,7 @@
         <v>4170</v>
       </c>
       <c r="C898" s="2" t="s">
-        <v>6622</v>
+        <v>6620</v>
       </c>
       <c r="D898" s="2" t="s">
         <v>4171</v>
@@ -48605,7 +48607,7 @@
         <v>4172</v>
       </c>
       <c r="F898" s="2" t="s">
-        <v>6623</v>
+        <v>6621</v>
       </c>
       <c r="G898" s="3">
         <v>1</v>
@@ -48765,7 +48767,7 @@
         <v>903</v>
       </c>
       <c r="B904" s="2" t="s">
-        <v>6938</v>
+        <v>6936</v>
       </c>
       <c r="C904" s="2" t="s">
         <v>4199</v>
@@ -48777,7 +48779,7 @@
         <v>4201</v>
       </c>
       <c r="F904" s="2" t="s">
-        <v>6939</v>
+        <v>6937</v>
       </c>
       <c r="G904" s="3">
         <v>4</v>
@@ -48881,19 +48883,19 @@
         <v>907</v>
       </c>
       <c r="B908" s="2" t="s">
-        <v>6639</v>
+        <v>6637</v>
       </c>
       <c r="C908" s="2" t="s">
         <v>4221</v>
       </c>
       <c r="D908" s="2" t="s">
-        <v>6640</v>
+        <v>6638</v>
       </c>
       <c r="E908" s="2" t="s">
         <v>3754</v>
       </c>
       <c r="F908" s="2" t="s">
-        <v>6641</v>
+        <v>6639</v>
       </c>
       <c r="G908" s="3">
         <v>3</v>
@@ -49055,19 +49057,19 @@
         <v>913</v>
       </c>
       <c r="B914" s="2" t="s">
-        <v>6427</v>
+        <v>6425</v>
       </c>
       <c r="C914" s="2" t="s">
-        <v>6428</v>
+        <v>6426</v>
       </c>
       <c r="D914" s="2" t="s">
         <v>4253</v>
       </c>
       <c r="E914" s="2" t="s">
-        <v>6429</v>
+        <v>6427</v>
       </c>
       <c r="F914" s="2" t="s">
-        <v>6430</v>
+        <v>6428</v>
       </c>
       <c r="G914" s="3">
         <v>3</v>
@@ -49339,7 +49341,7 @@
         <v>923</v>
       </c>
       <c r="B924" s="2" t="s">
-        <v>6281</v>
+        <v>6279</v>
       </c>
       <c r="C924" s="2" t="s">
         <v>2922</v>
@@ -49772,7 +49774,7 @@
         <v>938</v>
       </c>
       <c r="B939" s="2" t="s">
-        <v>6482</v>
+        <v>6480</v>
       </c>
       <c r="C939" s="2" t="s">
         <v>4374</v>
@@ -50036,16 +50038,16 @@
         <v>4426</v>
       </c>
       <c r="C948" s="2" t="s">
-        <v>6776</v>
+        <v>6774</v>
       </c>
       <c r="D948" s="2" t="s">
         <v>4427</v>
       </c>
       <c r="E948" s="2" t="s">
-        <v>6777</v>
+        <v>6775</v>
       </c>
       <c r="F948" s="2" t="s">
-        <v>6778</v>
+        <v>6776</v>
       </c>
       <c r="G948" s="3">
         <v>3</v>
@@ -50188,7 +50190,7 @@
         <v>4444</v>
       </c>
       <c r="F953" s="2" t="s">
-        <v>6270</v>
+        <v>6268</v>
       </c>
       <c r="G953" s="3">
         <v>3</v>
@@ -50205,19 +50207,19 @@
         <v>953</v>
       </c>
       <c r="B954" s="2" t="s">
-        <v>6904</v>
+        <v>6902</v>
       </c>
       <c r="C954" s="2" t="s">
         <v>4442</v>
       </c>
       <c r="D954" s="2" t="s">
-        <v>6903</v>
+        <v>6901</v>
       </c>
       <c r="E954" s="2" t="s">
         <v>4444</v>
       </c>
       <c r="F954" s="2" t="s">
-        <v>6905</v>
+        <v>6903</v>
       </c>
       <c r="G954" s="3">
         <v>4</v>
@@ -50237,16 +50239,16 @@
         <v>4450</v>
       </c>
       <c r="C955" s="2" t="s">
+        <v>6904</v>
+      </c>
+      <c r="D955" s="2" t="s">
+        <v>6905</v>
+      </c>
+      <c r="E955" s="2" t="s">
         <v>6906</v>
       </c>
-      <c r="D955" s="2" t="s">
+      <c r="F955" s="2" t="s">
         <v>6907</v>
-      </c>
-      <c r="E955" s="2" t="s">
-        <v>6908</v>
-      </c>
-      <c r="F955" s="2" t="s">
-        <v>6909</v>
       </c>
       <c r="G955" s="3">
         <v>3</v>
@@ -50263,19 +50265,19 @@
         <v>955</v>
       </c>
       <c r="B956" s="2" t="s">
+        <v>6908</v>
+      </c>
+      <c r="C956" s="2" t="s">
+        <v>6909</v>
+      </c>
+      <c r="D956" s="2" t="s">
         <v>6910</v>
       </c>
-      <c r="C956" s="2" t="s">
+      <c r="E956" s="2" t="s">
         <v>6911</v>
       </c>
-      <c r="D956" s="2" t="s">
+      <c r="F956" s="2" t="s">
         <v>6912</v>
-      </c>
-      <c r="E956" s="2" t="s">
-        <v>6913</v>
-      </c>
-      <c r="F956" s="2" t="s">
-        <v>6914</v>
       </c>
       <c r="G956" s="3">
         <v>1</v>
@@ -50379,7 +50381,7 @@
         <v>959</v>
       </c>
       <c r="B960" s="2" t="s">
-        <v>6921</v>
+        <v>6919</v>
       </c>
       <c r="C960" s="2" t="s">
         <v>4467</v>
@@ -50411,13 +50413,13 @@
         <v>4472</v>
       </c>
       <c r="C961" s="2" t="s">
+        <v>6557</v>
+      </c>
+      <c r="D961" s="2" t="s">
+        <v>6558</v>
+      </c>
+      <c r="E961" s="2" t="s">
         <v>6559</v>
-      </c>
-      <c r="D961" s="2" t="s">
-        <v>6560</v>
-      </c>
-      <c r="E961" s="2" t="s">
-        <v>6561</v>
       </c>
       <c r="F961" s="2" t="s">
         <v>4473</v>
@@ -50988,19 +50990,19 @@
         <v>980</v>
       </c>
       <c r="B981" s="2" t="s">
+        <v>6338</v>
+      </c>
+      <c r="C981" s="2" t="s">
         <v>6340</v>
       </c>
-      <c r="C981" s="2" t="s">
-        <v>6342</v>
-      </c>
       <c r="D981" s="2" t="s">
-        <v>6343</v>
+        <v>6341</v>
       </c>
       <c r="E981" s="2" t="s">
         <v>4576</v>
       </c>
       <c r="F981" s="2" t="s">
-        <v>6341</v>
+        <v>6339</v>
       </c>
       <c r="G981" s="3">
         <v>2</v>
@@ -51029,7 +51031,7 @@
         <v>3126</v>
       </c>
       <c r="F982" s="2" t="s">
-        <v>6974</v>
+        <v>6972</v>
       </c>
       <c r="G982" s="3">
         <v>2</v>
@@ -51220,19 +51222,19 @@
         <v>988</v>
       </c>
       <c r="B989" s="2" t="s">
+        <v>6299</v>
+      </c>
+      <c r="C989" s="2" t="s">
+        <v>6300</v>
+      </c>
+      <c r="D989" s="2" t="s">
         <v>6301</v>
       </c>
-      <c r="C989" s="2" t="s">
+      <c r="E989" s="2" t="s">
         <v>6302</v>
       </c>
-      <c r="D989" s="2" t="s">
+      <c r="F989" s="2" t="s">
         <v>6303</v>
-      </c>
-      <c r="E989" s="2" t="s">
-        <v>6304</v>
-      </c>
-      <c r="F989" s="2" t="s">
-        <v>6305</v>
       </c>
       <c r="G989" s="3">
         <v>3</v>
@@ -51281,16 +51283,16 @@
         <v>4615</v>
       </c>
       <c r="C991" s="2" t="s">
-        <v>6762</v>
+        <v>6760</v>
       </c>
       <c r="D991" s="2" t="s">
         <v>4616</v>
       </c>
       <c r="E991" s="2" t="s">
-        <v>6760</v>
+        <v>6758</v>
       </c>
       <c r="F991" s="2" t="s">
-        <v>6761</v>
+        <v>6759</v>
       </c>
       <c r="G991" s="3">
         <v>2</v>
@@ -51307,10 +51309,10 @@
         <v>991</v>
       </c>
       <c r="B992" s="2" t="s">
-        <v>6630</v>
+        <v>6628</v>
       </c>
       <c r="C992" s="2" t="s">
-        <v>6629</v>
+        <v>6627</v>
       </c>
       <c r="D992" s="2" t="s">
         <v>4618</v>
@@ -51452,19 +51454,19 @@
         <v>996</v>
       </c>
       <c r="B997" s="2" t="s">
-        <v>6472</v>
+        <v>6470</v>
       </c>
       <c r="C997" s="2" t="s">
         <v>3745</v>
       </c>
       <c r="D997" s="2" t="s">
-        <v>6473</v>
+        <v>6471</v>
       </c>
       <c r="E997" s="2" t="s">
         <v>4634</v>
       </c>
       <c r="F997" s="2" t="s">
-        <v>6474</v>
+        <v>6472</v>
       </c>
       <c r="G997" s="3">
         <v>3</v>
@@ -51655,19 +51657,19 @@
         <v>1003</v>
       </c>
       <c r="B1004" s="2" t="s">
-        <v>6812</v>
+        <v>6810</v>
       </c>
       <c r="C1004" s="2" t="s">
-        <v>6813</v>
+        <v>6811</v>
       </c>
       <c r="D1004" s="2" t="s">
         <v>4656</v>
       </c>
       <c r="E1004" s="2" t="s">
+        <v>6812</v>
+      </c>
+      <c r="F1004" s="2" t="s">
         <v>6814</v>
-      </c>
-      <c r="F1004" s="2" t="s">
-        <v>6816</v>
       </c>
       <c r="G1004" s="3">
         <v>1</v>
@@ -51684,7 +51686,7 @@
         <v>1004</v>
       </c>
       <c r="B1005" s="2" t="s">
-        <v>6815</v>
+        <v>6813</v>
       </c>
       <c r="C1005" s="2" t="s">
         <v>4658</v>
@@ -51856,7 +51858,7 @@
         <v>1010</v>
       </c>
       <c r="B1011" s="2" t="s">
-        <v>6766</v>
+        <v>6764</v>
       </c>
       <c r="C1011" s="2" t="s">
         <v>4677</v>
@@ -51917,16 +51919,16 @@
         <v>4688</v>
       </c>
       <c r="C1013" s="2" t="s">
-        <v>6680</v>
+        <v>6678</v>
       </c>
       <c r="D1013" s="2" t="s">
+        <v>6677</v>
+      </c>
+      <c r="E1013" s="2" t="s">
         <v>6679</v>
       </c>
-      <c r="E1013" s="2" t="s">
+      <c r="F1013" s="2" t="s">
         <v>6681</v>
-      </c>
-      <c r="F1013" s="2" t="s">
-        <v>6683</v>
       </c>
       <c r="G1013" s="3">
         <v>2</v>
@@ -51943,7 +51945,7 @@
         <v>1013</v>
       </c>
       <c r="B1014" s="2" t="s">
-        <v>6682</v>
+        <v>6680</v>
       </c>
       <c r="C1014" s="2" t="s">
         <v>4689</v>
@@ -52004,16 +52006,16 @@
         <v>4701</v>
       </c>
       <c r="C1016" s="2" t="s">
-        <v>6431</v>
+        <v>6429</v>
       </c>
       <c r="D1016" s="2" t="s">
-        <v>6432</v>
+        <v>6430</v>
       </c>
       <c r="E1016" s="2" t="s">
         <v>4702</v>
       </c>
       <c r="F1016" s="2" t="s">
-        <v>6433</v>
+        <v>6431</v>
       </c>
       <c r="G1016" s="3">
         <v>1</v>
@@ -52030,7 +52032,7 @@
         <v>1016</v>
       </c>
       <c r="B1017" s="2" t="s">
-        <v>6434</v>
+        <v>6432</v>
       </c>
       <c r="C1017" s="2" t="s">
         <v>4704</v>
@@ -52059,10 +52061,10 @@
         <v>1017</v>
       </c>
       <c r="B1018" s="2" t="s">
-        <v>6676</v>
+        <v>6674</v>
       </c>
       <c r="C1018" s="2" t="s">
-        <v>6677</v>
+        <v>6675</v>
       </c>
       <c r="D1018" s="2" t="s">
         <v>4709</v>
@@ -52071,7 +52073,7 @@
         <v>4710</v>
       </c>
       <c r="F1018" s="2" t="s">
-        <v>6678</v>
+        <v>6676</v>
       </c>
       <c r="G1018" s="3">
         <v>4</v>
@@ -52088,7 +52090,7 @@
         <v>1018</v>
       </c>
       <c r="B1019" s="2" t="s">
-        <v>6995</v>
+        <v>6993</v>
       </c>
       <c r="C1019" s="2" t="s">
         <v>1041</v>
@@ -52291,7 +52293,7 @@
         <v>1025</v>
       </c>
       <c r="B1026" s="2" t="s">
-        <v>6344</v>
+        <v>6342</v>
       </c>
       <c r="C1026" s="2" t="s">
         <v>4742</v>
@@ -52300,10 +52302,10 @@
         <v>937</v>
       </c>
       <c r="E1026" s="2" t="s">
-        <v>6345</v>
+        <v>6343</v>
       </c>
       <c r="F1026" s="2" t="s">
-        <v>6346</v>
+        <v>6344</v>
       </c>
       <c r="G1026" s="3">
         <v>1</v>
@@ -52355,7 +52357,7 @@
         <v>4751</v>
       </c>
       <c r="D1028" s="2" t="s">
-        <v>6746</v>
+        <v>6744</v>
       </c>
       <c r="E1028" s="2" t="s">
         <v>4752</v>
@@ -52639,7 +52641,7 @@
         <v>1037</v>
       </c>
       <c r="B1038" s="2" t="s">
-        <v>6624</v>
+        <v>6622</v>
       </c>
       <c r="C1038" s="2" t="s">
         <v>866</v>
@@ -52668,7 +52670,7 @@
         <v>1038</v>
       </c>
       <c r="B1039" s="2" t="s">
-        <v>6437</v>
+        <v>6435</v>
       </c>
       <c r="C1039" s="2" t="s">
         <v>4806</v>
@@ -52677,10 +52679,10 @@
         <v>4807</v>
       </c>
       <c r="E1039" s="2" t="s">
-        <v>6435</v>
+        <v>6433</v>
       </c>
       <c r="F1039" s="2" t="s">
-        <v>6436</v>
+        <v>6434</v>
       </c>
       <c r="G1039" s="3">
         <v>2</v>
@@ -52697,19 +52699,19 @@
         <v>1039</v>
       </c>
       <c r="B1040" s="2" t="s">
+        <v>6293</v>
+      </c>
+      <c r="C1040" s="2" t="s">
+        <v>6294</v>
+      </c>
+      <c r="D1040" s="2" t="s">
         <v>6295</v>
       </c>
-      <c r="C1040" s="2" t="s">
+      <c r="E1040" s="2" t="s">
         <v>6296</v>
       </c>
-      <c r="D1040" s="2" t="s">
+      <c r="F1040" s="2" t="s">
         <v>6297</v>
-      </c>
-      <c r="E1040" s="2" t="s">
-        <v>6298</v>
-      </c>
-      <c r="F1040" s="2" t="s">
-        <v>6299</v>
       </c>
       <c r="G1040" s="3">
         <v>4</v>
@@ -52938,7 +52940,7 @@
         <v>4853</v>
       </c>
       <c r="E1048" s="2" t="s">
-        <v>6782</v>
+        <v>6780</v>
       </c>
       <c r="F1048" s="2" t="s">
         <v>4854</v>
@@ -52987,7 +52989,7 @@
         <v>1049</v>
       </c>
       <c r="B1050" s="2" t="s">
-        <v>6530</v>
+        <v>6528</v>
       </c>
       <c r="C1050" s="2" t="s">
         <v>1466</v>
@@ -52999,7 +53001,7 @@
         <v>4862</v>
       </c>
       <c r="F1050" s="2" t="s">
-        <v>6531</v>
+        <v>6529</v>
       </c>
       <c r="G1050" s="3">
         <v>3</v>
@@ -53016,7 +53018,7 @@
         <v>1050</v>
       </c>
       <c r="B1051" s="2" t="s">
-        <v>6662</v>
+        <v>6660</v>
       </c>
       <c r="C1051" s="2" t="s">
         <v>4864</v>
@@ -53028,7 +53030,7 @@
         <v>4866</v>
       </c>
       <c r="F1051" s="2" t="s">
-        <v>6661</v>
+        <v>6659</v>
       </c>
       <c r="G1051" s="3">
         <v>1</v>
@@ -53103,19 +53105,19 @@
         <v>1053</v>
       </c>
       <c r="B1054" s="2" t="s">
-        <v>6986</v>
+        <v>6984</v>
       </c>
       <c r="C1054" s="2" t="s">
         <v>1709</v>
       </c>
       <c r="D1054" s="2" t="s">
-        <v>6985</v>
+        <v>6983</v>
       </c>
       <c r="E1054" s="2" t="s">
         <v>4877</v>
       </c>
       <c r="F1054" s="2" t="s">
-        <v>6987</v>
+        <v>6985</v>
       </c>
       <c r="G1054" s="3">
         <v>4</v>
@@ -53132,7 +53134,7 @@
         <v>1054</v>
       </c>
       <c r="B1055" s="2" t="s">
-        <v>6988</v>
+        <v>6986</v>
       </c>
       <c r="C1055" s="2" t="s">
         <v>4879</v>
@@ -53161,19 +53163,19 @@
         <v>1055</v>
       </c>
       <c r="B1056" s="2" t="s">
-        <v>7005</v>
+        <v>7003</v>
       </c>
       <c r="C1056" s="2" t="s">
         <v>4884</v>
       </c>
       <c r="D1056" s="2" t="s">
+        <v>7004</v>
+      </c>
+      <c r="E1056" s="2" t="s">
+        <v>7005</v>
+      </c>
+      <c r="F1056" s="2" t="s">
         <v>7006</v>
-      </c>
-      <c r="E1056" s="2" t="s">
-        <v>7007</v>
-      </c>
-      <c r="F1056" s="2" t="s">
-        <v>7008</v>
       </c>
       <c r="G1056" s="3">
         <v>2</v>
@@ -53190,7 +53192,7 @@
         <v>1056</v>
       </c>
       <c r="B1057" s="2" t="s">
-        <v>6992</v>
+        <v>6990</v>
       </c>
       <c r="C1057" s="2" t="s">
         <v>4886</v>
@@ -53202,7 +53204,7 @@
         <v>4888</v>
       </c>
       <c r="F1057" s="2" t="s">
-        <v>6993</v>
+        <v>6991</v>
       </c>
       <c r="G1057" s="3">
         <v>2</v>
@@ -53219,19 +53221,19 @@
         <v>1057</v>
       </c>
       <c r="B1058" s="2" t="s">
-        <v>6868</v>
+        <v>6866</v>
       </c>
       <c r="C1058" s="2" t="s">
-        <v>6869</v>
+        <v>6867</v>
       </c>
       <c r="D1058" s="2" t="s">
         <v>4890</v>
       </c>
       <c r="E1058" s="2" t="s">
-        <v>6870</v>
+        <v>6868</v>
       </c>
       <c r="F1058" s="2" t="s">
-        <v>6871</v>
+        <v>6869</v>
       </c>
       <c r="G1058" s="3">
         <v>3</v>
@@ -53277,19 +53279,19 @@
         <v>1059</v>
       </c>
       <c r="B1060" s="2" t="s">
+        <v>6481</v>
+      </c>
+      <c r="C1060" s="2" t="s">
+        <v>6484</v>
+      </c>
+      <c r="D1060" s="2" t="s">
+        <v>6482</v>
+      </c>
+      <c r="E1060" s="2" t="s">
         <v>6483</v>
       </c>
-      <c r="C1060" s="2" t="s">
-        <v>6486</v>
-      </c>
-      <c r="D1060" s="2" t="s">
-        <v>6484</v>
-      </c>
-      <c r="E1060" s="2" t="s">
+      <c r="F1060" s="2" t="s">
         <v>6485</v>
-      </c>
-      <c r="F1060" s="2" t="s">
-        <v>6487</v>
       </c>
       <c r="G1060" s="3">
         <v>4</v>
@@ -53335,19 +53337,19 @@
         <v>1061</v>
       </c>
       <c r="B1062" s="2" t="s">
-        <v>6552</v>
+        <v>6550</v>
       </c>
       <c r="C1062" s="2" t="s">
         <v>4906</v>
       </c>
       <c r="D1062" s="2" t="s">
+        <v>6551</v>
+      </c>
+      <c r="E1062" s="2" t="s">
+        <v>6552</v>
+      </c>
+      <c r="F1062" s="2" t="s">
         <v>6553</v>
-      </c>
-      <c r="E1062" s="2" t="s">
-        <v>6554</v>
-      </c>
-      <c r="F1062" s="2" t="s">
-        <v>6555</v>
       </c>
       <c r="G1062" s="3">
         <v>1</v>
@@ -53376,7 +53378,7 @@
         <v>927</v>
       </c>
       <c r="F1063" s="2" t="s">
-        <v>7026</v>
+        <v>7024</v>
       </c>
       <c r="G1063" s="3">
         <v>3</v>
@@ -53393,7 +53395,7 @@
         <v>1063</v>
       </c>
       <c r="B1064" s="2" t="s">
-        <v>6900</v>
+        <v>6898</v>
       </c>
       <c r="C1064" s="2" t="s">
         <v>4912</v>
@@ -53402,10 +53404,10 @@
         <v>4913</v>
       </c>
       <c r="E1064" s="2" t="s">
-        <v>6901</v>
+        <v>6899</v>
       </c>
       <c r="F1064" s="2" t="s">
-        <v>6902</v>
+        <v>6900</v>
       </c>
       <c r="G1064" s="3">
         <v>1</v>
@@ -53428,13 +53430,13 @@
         <v>4916</v>
       </c>
       <c r="D1065" s="2" t="s">
-        <v>6585</v>
+        <v>6583</v>
       </c>
       <c r="E1065" s="2" t="s">
         <v>4917</v>
       </c>
       <c r="F1065" s="2" t="s">
-        <v>6586</v>
+        <v>6584</v>
       </c>
       <c r="G1065" s="3">
         <v>2</v>
@@ -53537,16 +53539,16 @@
         <v>4929</v>
       </c>
       <c r="C1069" s="2" t="s">
-        <v>6556</v>
+        <v>6554</v>
       </c>
       <c r="D1069" s="2" t="s">
         <v>4930</v>
       </c>
       <c r="E1069" s="2" t="s">
-        <v>6557</v>
+        <v>6555</v>
       </c>
       <c r="F1069" s="2" t="s">
-        <v>6558</v>
+        <v>6556</v>
       </c>
       <c r="G1069" s="3">
         <v>4</v>
@@ -53563,7 +53565,7 @@
         <v>1069</v>
       </c>
       <c r="B1070" s="2" t="s">
-        <v>6720</v>
+        <v>6718</v>
       </c>
       <c r="C1070" s="2" t="s">
         <v>743</v>
@@ -53575,7 +53577,7 @@
         <v>917</v>
       </c>
       <c r="F1070" s="2" t="s">
-        <v>6721</v>
+        <v>6719</v>
       </c>
       <c r="G1070" s="3">
         <v>4</v>
@@ -53679,7 +53681,7 @@
         <v>1073</v>
       </c>
       <c r="B1074" s="2" t="s">
-        <v>6923</v>
+        <v>6921</v>
       </c>
       <c r="C1074" s="2" t="s">
         <v>492</v>
@@ -53824,7 +53826,7 @@
         <v>1078</v>
       </c>
       <c r="B1079" s="2" t="s">
-        <v>6929</v>
+        <v>6927</v>
       </c>
       <c r="C1079" s="2" t="s">
         <v>865</v>
@@ -53911,19 +53913,19 @@
         <v>1081</v>
       </c>
       <c r="B1082" s="2" t="s">
-        <v>6962</v>
+        <v>6960</v>
       </c>
       <c r="C1082" s="2" t="s">
         <v>4980</v>
       </c>
       <c r="D1082" s="2" t="s">
+        <v>6961</v>
+      </c>
+      <c r="E1082" s="2" t="s">
+        <v>6962</v>
+      </c>
+      <c r="F1082" s="2" t="s">
         <v>6963</v>
-      </c>
-      <c r="E1082" s="2" t="s">
-        <v>6964</v>
-      </c>
-      <c r="F1082" s="2" t="s">
-        <v>6965</v>
       </c>
       <c r="G1082" s="3">
         <v>3</v>
@@ -53940,7 +53942,7 @@
         <v>1082</v>
       </c>
       <c r="B1083" s="2" t="s">
-        <v>6438</v>
+        <v>6436</v>
       </c>
       <c r="C1083" s="2" t="s">
         <v>4982</v>
@@ -54027,19 +54029,19 @@
         <v>1085</v>
       </c>
       <c r="B1086" s="2" t="s">
-        <v>6931</v>
+        <v>6929</v>
       </c>
       <c r="C1086" s="2" t="s">
         <v>4994</v>
       </c>
       <c r="D1086" s="2" t="s">
-        <v>6932</v>
+        <v>6930</v>
       </c>
       <c r="E1086" s="2" t="s">
         <v>4995</v>
       </c>
       <c r="F1086" s="2" t="s">
-        <v>6933</v>
+        <v>6931</v>
       </c>
       <c r="G1086" s="3">
         <v>1</v>
@@ -54085,10 +54087,10 @@
         <v>1087</v>
       </c>
       <c r="B1088" s="2" t="s">
-        <v>6889</v>
+        <v>6887</v>
       </c>
       <c r="C1088" s="2" t="s">
-        <v>6890</v>
+        <v>6888</v>
       </c>
       <c r="D1088" s="2" t="s">
         <v>5003</v>
@@ -54097,7 +54099,7 @@
         <v>3896</v>
       </c>
       <c r="F1088" s="2" t="s">
-        <v>6891</v>
+        <v>6889</v>
       </c>
       <c r="G1088" s="3">
         <v>2</v>
@@ -54172,19 +54174,19 @@
         <v>1090</v>
       </c>
       <c r="B1091" s="2" t="s">
-        <v>7014</v>
+        <v>7012</v>
       </c>
       <c r="C1091" s="2" t="s">
-        <v>7015</v>
+        <v>7013</v>
       </c>
       <c r="D1091" s="2" t="s">
         <v>4930</v>
       </c>
       <c r="E1091" s="2" t="s">
-        <v>7016</v>
+        <v>7014</v>
       </c>
       <c r="F1091" s="2" t="s">
-        <v>7017</v>
+        <v>7015</v>
       </c>
       <c r="G1091" s="3">
         <v>2</v>
@@ -54213,7 +54215,7 @@
         <v>5018</v>
       </c>
       <c r="F1092" s="2" t="s">
-        <v>7044</v>
+        <v>7042</v>
       </c>
       <c r="G1092" s="3">
         <v>1</v>
@@ -54317,7 +54319,7 @@
         <v>1095</v>
       </c>
       <c r="B1096" s="2" t="s">
-        <v>6751</v>
+        <v>6749</v>
       </c>
       <c r="C1096" s="2" t="s">
         <v>5038</v>
@@ -54329,7 +54331,7 @@
         <v>5039</v>
       </c>
       <c r="F1096" s="2" t="s">
-        <v>6752</v>
+        <v>6750</v>
       </c>
       <c r="G1096" s="3">
         <v>4</v>
@@ -54781,19 +54783,19 @@
         <v>1111</v>
       </c>
       <c r="B1112" s="2" t="s">
+        <v>6539</v>
+      </c>
+      <c r="C1112" s="2" t="s">
+        <v>6540</v>
+      </c>
+      <c r="D1112" s="2" t="s">
         <v>6541</v>
       </c>
-      <c r="C1112" s="2" t="s">
+      <c r="E1112" s="2" t="s">
         <v>6542</v>
       </c>
-      <c r="D1112" s="2" t="s">
+      <c r="F1112" s="2" t="s">
         <v>6543</v>
-      </c>
-      <c r="E1112" s="2" t="s">
-        <v>6544</v>
-      </c>
-      <c r="F1112" s="2" t="s">
-        <v>6545</v>
       </c>
       <c r="G1112" s="3">
         <v>4</v>
@@ -54906,10 +54908,10 @@
         <v>5122</v>
       </c>
       <c r="E1116" s="2" t="s">
-        <v>6498</v>
+        <v>6496</v>
       </c>
       <c r="F1116" s="2" t="s">
-        <v>6499</v>
+        <v>6497</v>
       </c>
       <c r="G1116" s="3">
         <v>1</v>
@@ -54964,10 +54966,10 @@
         <v>5132</v>
       </c>
       <c r="E1118" s="2" t="s">
-        <v>6275</v>
+        <v>6273</v>
       </c>
       <c r="F1118" s="2" t="s">
-        <v>6274</v>
+        <v>6272</v>
       </c>
       <c r="G1118" s="3">
         <v>4</v>
@@ -55129,19 +55131,19 @@
         <v>1123</v>
       </c>
       <c r="B1124" s="2" t="s">
+        <v>6623</v>
+      </c>
+      <c r="C1124" s="2" t="s">
+        <v>6624</v>
+      </c>
+      <c r="D1124" s="2" t="s">
         <v>6625</v>
       </c>
-      <c r="C1124" s="2" t="s">
+      <c r="E1124" s="2" t="s">
         <v>6626</v>
       </c>
-      <c r="D1124" s="2" t="s">
-        <v>6627</v>
-      </c>
-      <c r="E1124" s="2" t="s">
-        <v>6628</v>
-      </c>
       <c r="F1124" s="2" t="s">
-        <v>6651</v>
+        <v>6649</v>
       </c>
       <c r="G1124" s="3">
         <v>4</v>
@@ -55332,7 +55334,7 @@
         <v>1130</v>
       </c>
       <c r="B1131" s="2" t="s">
-        <v>6599</v>
+        <v>6597</v>
       </c>
       <c r="C1131" s="2" t="s">
         <v>5188</v>
@@ -55341,10 +55343,10 @@
         <v>5189</v>
       </c>
       <c r="E1131" s="2" t="s">
-        <v>6600</v>
+        <v>6598</v>
       </c>
       <c r="F1131" s="2" t="s">
-        <v>6601</v>
+        <v>6599</v>
       </c>
       <c r="G1131" s="3">
         <v>1</v>
@@ -55361,19 +55363,19 @@
         <v>1131</v>
       </c>
       <c r="B1132" s="2" t="s">
+        <v>6601</v>
+      </c>
+      <c r="C1132" s="5" t="s">
+        <v>6602</v>
+      </c>
+      <c r="D1132" s="2" t="s">
         <v>6603</v>
       </c>
-      <c r="C1132" s="5" t="s">
+      <c r="E1132" s="2" t="s">
         <v>6604</v>
       </c>
-      <c r="D1132" s="2" t="s">
+      <c r="F1132" s="2" t="s">
         <v>6605</v>
-      </c>
-      <c r="E1132" s="2" t="s">
-        <v>6606</v>
-      </c>
-      <c r="F1132" s="2" t="s">
-        <v>6607</v>
       </c>
       <c r="G1132" s="3">
         <v>3</v>
@@ -55390,19 +55392,19 @@
         <v>1132</v>
       </c>
       <c r="B1133" s="2" t="s">
+        <v>6608</v>
+      </c>
+      <c r="C1133" s="2" t="s">
+        <v>6609</v>
+      </c>
+      <c r="D1133" s="2" t="s">
         <v>6610</v>
       </c>
-      <c r="C1133" s="2" t="s">
+      <c r="E1133" s="2" t="s">
         <v>6611</v>
       </c>
-      <c r="D1133" s="2" t="s">
+      <c r="F1133" s="2" t="s">
         <v>6612</v>
-      </c>
-      <c r="E1133" s="2" t="s">
-        <v>6613</v>
-      </c>
-      <c r="F1133" s="2" t="s">
-        <v>6614</v>
       </c>
       <c r="G1133" s="3">
         <v>2</v>
@@ -55419,7 +55421,7 @@
         <v>1133</v>
       </c>
       <c r="B1134" s="2" t="s">
-        <v>6602</v>
+        <v>6600</v>
       </c>
       <c r="C1134" s="2" t="s">
         <v>5191</v>
@@ -55428,10 +55430,10 @@
         <v>5192</v>
       </c>
       <c r="E1134" s="2" t="s">
-        <v>6608</v>
+        <v>6606</v>
       </c>
       <c r="F1134" s="2" t="s">
-        <v>6609</v>
+        <v>6607</v>
       </c>
       <c r="G1134" s="3">
         <v>1</v>
@@ -55525,7 +55527,7 @@
         <v>1137</v>
       </c>
       <c r="B1138" s="2" t="s">
-        <v>7039</v>
+        <v>7037</v>
       </c>
       <c r="C1138" s="2" t="s">
         <v>5206</v>
@@ -55612,19 +55614,19 @@
         <v>1140</v>
       </c>
       <c r="B1141" s="2" t="s">
+        <v>6968</v>
+      </c>
+      <c r="C1141" s="2" t="s">
+        <v>6969</v>
+      </c>
+      <c r="D1141" s="2" t="s">
         <v>6970</v>
-      </c>
-      <c r="C1141" s="2" t="s">
-        <v>6971</v>
-      </c>
-      <c r="D1141" s="2" t="s">
-        <v>6972</v>
       </c>
       <c r="E1141" s="2" t="s">
         <v>5222</v>
       </c>
       <c r="F1141" s="2" t="s">
-        <v>6973</v>
+        <v>6971</v>
       </c>
       <c r="G1141" s="3">
         <v>3</v>
@@ -55641,19 +55643,19 @@
         <v>1141</v>
       </c>
       <c r="B1142" s="2" t="s">
-        <v>6969</v>
+        <v>6967</v>
       </c>
       <c r="C1142" s="2" t="s">
-        <v>7017</v>
+        <v>7015</v>
       </c>
       <c r="D1142" s="2" t="s">
         <v>4930</v>
       </c>
       <c r="E1142" s="2" t="s">
-        <v>7018</v>
+        <v>7016</v>
       </c>
       <c r="F1142" s="2" t="s">
-        <v>7019</v>
+        <v>7017</v>
       </c>
       <c r="G1142" s="3">
         <v>4</v>
@@ -55728,7 +55730,7 @@
         <v>1144</v>
       </c>
       <c r="B1145" s="2" t="s">
-        <v>6915</v>
+        <v>6913</v>
       </c>
       <c r="C1145" s="2" t="s">
         <v>5238</v>
@@ -55757,7 +55759,7 @@
         <v>1145</v>
       </c>
       <c r="B1146" s="2" t="s">
-        <v>6916</v>
+        <v>6914</v>
       </c>
       <c r="C1146" s="2" t="s">
         <v>4041</v>
@@ -55786,7 +55788,7 @@
         <v>1146</v>
       </c>
       <c r="B1147" s="2" t="s">
-        <v>6917</v>
+        <v>6915</v>
       </c>
       <c r="C1147" s="2" t="s">
         <v>5246</v>
@@ -55815,7 +55817,7 @@
         <v>1147</v>
       </c>
       <c r="B1148" s="2" t="s">
-        <v>6918</v>
+        <v>6916</v>
       </c>
       <c r="C1148" s="2" t="s">
         <v>5251</v>
@@ -55844,10 +55846,10 @@
         <v>1148</v>
       </c>
       <c r="B1149" s="2" t="s">
-        <v>6919</v>
+        <v>6917</v>
       </c>
       <c r="C1149" s="2" t="s">
-        <v>6920</v>
+        <v>6918</v>
       </c>
       <c r="D1149" s="2" t="s">
         <v>5256</v>
@@ -55989,19 +55991,19 @@
         <v>1153</v>
       </c>
       <c r="B1154" s="2" t="s">
+        <v>6860</v>
+      </c>
+      <c r="C1154" s="2" t="s">
+        <v>6861</v>
+      </c>
+      <c r="D1154" s="2" t="s">
         <v>6862</v>
       </c>
-      <c r="C1154" s="2" t="s">
+      <c r="E1154" s="2" t="s">
+        <v>6864</v>
+      </c>
+      <c r="F1154" s="2" t="s">
         <v>6863</v>
-      </c>
-      <c r="D1154" s="2" t="s">
-        <v>6864</v>
-      </c>
-      <c r="E1154" s="2" t="s">
-        <v>6866</v>
-      </c>
-      <c r="F1154" s="2" t="s">
-        <v>6865</v>
       </c>
       <c r="G1154" s="3">
         <v>3</v>
@@ -56076,10 +56078,10 @@
         <v>1156</v>
       </c>
       <c r="B1157" s="2" t="s">
-        <v>7009</v>
+        <v>7007</v>
       </c>
       <c r="C1157" s="2" t="s">
-        <v>7010</v>
+        <v>7008</v>
       </c>
       <c r="D1157" s="2" t="s">
         <v>5286</v>
@@ -56088,7 +56090,7 @@
         <v>5287</v>
       </c>
       <c r="F1157" s="2" t="s">
-        <v>7011</v>
+        <v>7009</v>
       </c>
       <c r="G1157" s="3">
         <v>2</v>
@@ -56395,19 +56397,19 @@
         <v>1167</v>
       </c>
       <c r="B1168" s="2" t="s">
-        <v>6819</v>
+        <v>6817</v>
       </c>
       <c r="C1168" s="2" t="s">
-        <v>6820</v>
+        <v>6818</v>
       </c>
       <c r="D1168" s="2" t="s">
         <v>5336</v>
       </c>
       <c r="E1168" s="2" t="s">
-        <v>6821</v>
+        <v>6819</v>
       </c>
       <c r="F1168" s="2" t="s">
-        <v>6822</v>
+        <v>6820</v>
       </c>
       <c r="G1168" s="3">
         <v>3</v>
@@ -56656,7 +56658,7 @@
         <v>1176</v>
       </c>
       <c r="B1177" s="2" t="s">
-        <v>7037</v>
+        <v>7035</v>
       </c>
       <c r="C1177" s="2" t="s">
         <v>1710</v>
@@ -56801,10 +56803,10 @@
         <v>1181</v>
       </c>
       <c r="B1182" s="2" t="s">
-        <v>6388</v>
+        <v>6386</v>
       </c>
       <c r="C1182" s="2" t="s">
-        <v>6389</v>
+        <v>6387</v>
       </c>
       <c r="D1182" s="2" t="s">
         <v>5394</v>
@@ -56813,7 +56815,7 @@
         <v>1710</v>
       </c>
       <c r="F1182" s="2" t="s">
-        <v>6390</v>
+        <v>6388</v>
       </c>
       <c r="G1182" s="3">
         <v>4</v>
@@ -56859,7 +56861,7 @@
         <v>1183</v>
       </c>
       <c r="B1184" s="2" t="s">
-        <v>6716</v>
+        <v>6714</v>
       </c>
       <c r="C1184" s="2" t="s">
         <v>4052</v>
@@ -56888,7 +56890,7 @@
         <v>1184</v>
       </c>
       <c r="B1185" s="2" t="s">
-        <v>6488</v>
+        <v>6486</v>
       </c>
       <c r="C1185" s="2" t="s">
         <v>5402</v>
@@ -56900,7 +56902,7 @@
         <v>4054</v>
       </c>
       <c r="F1185" s="4" t="s">
-        <v>6489</v>
+        <v>6487</v>
       </c>
       <c r="G1185" s="3">
         <v>1</v>
@@ -56917,7 +56919,7 @@
         <v>1185</v>
       </c>
       <c r="B1186" s="2" t="s">
-        <v>6466</v>
+        <v>6464</v>
       </c>
       <c r="C1186" s="2" t="s">
         <v>4053</v>
@@ -56929,7 +56931,7 @@
         <v>5405</v>
       </c>
       <c r="F1186" s="4" t="s">
-        <v>6490</v>
+        <v>6488</v>
       </c>
       <c r="G1186" s="3">
         <v>2</v>
@@ -57294,7 +57296,7 @@
         <v>1198</v>
       </c>
       <c r="B1199" s="2" t="s">
-        <v>6671</v>
+        <v>6669</v>
       </c>
       <c r="C1199" s="2" t="s">
         <v>5444</v>
@@ -57323,7 +57325,7 @@
         <v>1199</v>
       </c>
       <c r="B1200" s="2" t="s">
-        <v>6672</v>
+        <v>6670</v>
       </c>
       <c r="C1200" s="2" t="s">
         <v>4092</v>
@@ -57335,7 +57337,7 @@
         <v>4094</v>
       </c>
       <c r="F1200" s="2" t="s">
-        <v>6686</v>
+        <v>6684</v>
       </c>
       <c r="G1200" s="3">
         <v>1</v>
@@ -57381,7 +57383,7 @@
         <v>1201</v>
       </c>
       <c r="B1202" s="2" t="s">
-        <v>6922</v>
+        <v>6920</v>
       </c>
       <c r="C1202" s="2" t="s">
         <v>4053</v>
@@ -57439,19 +57441,19 @@
         <v>1203</v>
       </c>
       <c r="B1204" s="2" t="s">
-        <v>6960</v>
+        <v>6958</v>
       </c>
       <c r="C1204" s="2" t="s">
+        <v>6954</v>
+      </c>
+      <c r="D1204" s="2" t="s">
+        <v>6955</v>
+      </c>
+      <c r="E1204" s="2" t="s">
         <v>6956</v>
       </c>
-      <c r="D1204" s="2" t="s">
+      <c r="F1204" s="2" t="s">
         <v>6957</v>
-      </c>
-      <c r="E1204" s="2" t="s">
-        <v>6958</v>
-      </c>
-      <c r="F1204" s="2" t="s">
-        <v>6959</v>
       </c>
       <c r="G1204" s="3">
         <v>3</v>
@@ -57555,7 +57557,7 @@
         <v>1207</v>
       </c>
       <c r="B1208" s="2" t="s">
-        <v>6480</v>
+        <v>6478</v>
       </c>
       <c r="C1208" s="2" t="s">
         <v>4053</v>
@@ -57584,7 +57586,7 @@
         <v>1208</v>
       </c>
       <c r="B1209" s="2" t="s">
-        <v>6481</v>
+        <v>6479</v>
       </c>
       <c r="C1209" s="2" t="s">
         <v>4053</v>
@@ -57700,7 +57702,7 @@
         <v>1212</v>
       </c>
       <c r="B1213" s="2" t="s">
-        <v>6441</v>
+        <v>6439</v>
       </c>
       <c r="C1213" s="2" t="s">
         <v>5472</v>
@@ -57741,7 +57743,7 @@
         <v>2880</v>
       </c>
       <c r="F1214" s="2" t="s">
-        <v>6797</v>
+        <v>6795</v>
       </c>
       <c r="G1214" s="3">
         <v>1</v>
@@ -57764,13 +57766,13 @@
         <v>5481</v>
       </c>
       <c r="D1215" s="2" t="s">
-        <v>6439</v>
+        <v>6437</v>
       </c>
       <c r="E1215" s="2" t="s">
         <v>5482</v>
       </c>
       <c r="F1215" s="2" t="s">
-        <v>6440</v>
+        <v>6438</v>
       </c>
       <c r="G1215" s="3">
         <v>4</v>
@@ -57961,19 +57963,19 @@
         <v>1221</v>
       </c>
       <c r="B1222" s="2" t="s">
+        <v>6884</v>
+      </c>
+      <c r="C1222" s="2" t="s">
+        <v>6883</v>
+      </c>
+      <c r="D1222" s="2" t="s">
         <v>6886</v>
-      </c>
-      <c r="C1222" s="2" t="s">
-        <v>6885</v>
-      </c>
-      <c r="D1222" s="2" t="s">
-        <v>6888</v>
       </c>
       <c r="E1222" s="2" t="s">
         <v>5512</v>
       </c>
       <c r="F1222" s="2" t="s">
-        <v>6887</v>
+        <v>6885</v>
       </c>
       <c r="G1222" s="3">
         <v>1</v>
@@ -58022,16 +58024,16 @@
         <v>5520</v>
       </c>
       <c r="C1224" s="2" t="s">
-        <v>6966</v>
+        <v>6964</v>
       </c>
       <c r="D1224" s="2" t="s">
-        <v>6967</v>
+        <v>6965</v>
       </c>
       <c r="E1224" s="2" t="s">
         <v>4345</v>
       </c>
       <c r="F1224" s="2" t="s">
-        <v>6968</v>
+        <v>6966</v>
       </c>
       <c r="G1224" s="3">
         <v>1</v>
@@ -58048,16 +58050,16 @@
         <v>1224</v>
       </c>
       <c r="B1225" s="2" t="s">
-        <v>6854</v>
+        <v>6852</v>
       </c>
       <c r="C1225" s="2" t="s">
-        <v>6855</v>
+        <v>6853</v>
       </c>
       <c r="D1225" s="2" t="s">
         <v>4870</v>
       </c>
       <c r="E1225" s="2" t="s">
-        <v>6856</v>
+        <v>6854</v>
       </c>
       <c r="F1225" s="2" t="s">
         <v>5522</v>
@@ -58135,7 +58137,7 @@
         <v>1227</v>
       </c>
       <c r="B1228" s="2" t="s">
-        <v>6285</v>
+        <v>6283</v>
       </c>
       <c r="C1228" s="2" t="s">
         <v>5533</v>
@@ -58144,10 +58146,10 @@
         <v>5534</v>
       </c>
       <c r="E1228" s="2" t="s">
-        <v>6286</v>
+        <v>6284</v>
       </c>
       <c r="F1228" s="2" t="s">
-        <v>6287</v>
+        <v>6285</v>
       </c>
       <c r="G1228" s="3">
         <v>4</v>
@@ -58278,13 +58280,13 @@
         <v>1232</v>
       </c>
       <c r="B1233" s="2" t="s">
-        <v>6457</v>
+        <v>6455</v>
       </c>
       <c r="C1233" s="2" t="s">
         <v>5551</v>
       </c>
       <c r="D1233" s="2" t="s">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="E1233" s="2" t="s">
         <v>3675</v>
@@ -58394,16 +58396,16 @@
         <v>1236</v>
       </c>
       <c r="B1237" s="2" t="s">
-        <v>6748</v>
+        <v>6746</v>
       </c>
       <c r="C1237" s="2" t="s">
-        <v>6749</v>
+        <v>6747</v>
       </c>
       <c r="D1237" s="2" t="s">
         <v>5568</v>
       </c>
       <c r="E1237" s="2" t="s">
-        <v>6750</v>
+        <v>6748</v>
       </c>
       <c r="F1237" s="2" t="s">
         <v>5569</v>
@@ -58511,10 +58513,10 @@
         <v>5582</v>
       </c>
       <c r="C1241" s="2" t="s">
-        <v>6348</v>
+        <v>6346</v>
       </c>
       <c r="D1241" s="2" t="s">
-        <v>6349</v>
+        <v>6347</v>
       </c>
       <c r="E1241" s="2" t="s">
         <v>5517</v>
@@ -58653,7 +58655,7 @@
         <v>1245</v>
       </c>
       <c r="B1246" s="2" t="s">
-        <v>6733</v>
+        <v>6731</v>
       </c>
       <c r="C1246" s="2" t="s">
         <v>5604</v>
@@ -58827,7 +58829,7 @@
         <v>1251</v>
       </c>
       <c r="B1252" s="2" t="s">
-        <v>6942</v>
+        <v>6940</v>
       </c>
       <c r="C1252" s="2" t="s">
         <v>5633</v>
@@ -58836,7 +58838,7 @@
         <v>5634</v>
       </c>
       <c r="E1252" s="2" t="s">
-        <v>6943</v>
+        <v>6941</v>
       </c>
       <c r="F1252" s="2" t="s">
         <v>5635</v>
@@ -59356,7 +59358,7 @@
         <v>2551</v>
       </c>
       <c r="E1270" s="2" t="s">
-        <v>6644</v>
+        <v>6642</v>
       </c>
       <c r="F1270" s="2" t="s">
         <v>5723</v>
@@ -59579,7 +59581,7 @@
         <v>1277</v>
       </c>
       <c r="B1278" s="2" t="s">
-        <v>6525</v>
+        <v>6523</v>
       </c>
       <c r="C1278" s="2" t="s">
         <v>5760</v>
@@ -59591,7 +59593,7 @@
         <v>117</v>
       </c>
       <c r="F1278" s="2" t="s">
-        <v>6526</v>
+        <v>6524</v>
       </c>
       <c r="G1278" s="3">
         <v>4</v>
@@ -59608,7 +59610,7 @@
         <v>1278</v>
       </c>
       <c r="B1279" s="2" t="s">
-        <v>6658</v>
+        <v>6656</v>
       </c>
       <c r="C1279" s="2" t="s">
         <v>5763</v>
@@ -59617,10 +59619,10 @@
         <v>5764</v>
       </c>
       <c r="E1279" s="2" t="s">
-        <v>6659</v>
+        <v>6657</v>
       </c>
       <c r="F1279" s="2" t="s">
-        <v>6660</v>
+        <v>6658</v>
       </c>
       <c r="G1279" s="3">
         <v>1</v>
@@ -59637,19 +59639,19 @@
         <v>1279</v>
       </c>
       <c r="B1280" s="2" t="s">
+        <v>6465</v>
+      </c>
+      <c r="C1280" s="2" t="s">
+        <v>6466</v>
+      </c>
+      <c r="D1280" s="2" t="s">
+        <v>6469</v>
+      </c>
+      <c r="E1280" s="2" t="s">
         <v>6467</v>
       </c>
-      <c r="C1280" s="2" t="s">
+      <c r="F1280" s="2" t="s">
         <v>6468</v>
-      </c>
-      <c r="D1280" s="2" t="s">
-        <v>6471</v>
-      </c>
-      <c r="E1280" s="2" t="s">
-        <v>6469</v>
-      </c>
-      <c r="F1280" s="2" t="s">
-        <v>6470</v>
       </c>
       <c r="G1280" s="3">
         <v>4</v>
@@ -59782,10 +59784,10 @@
         <v>1284</v>
       </c>
       <c r="B1285" s="2" t="s">
-        <v>6331</v>
+        <v>6329</v>
       </c>
       <c r="C1285" s="2" t="s">
-        <v>6332</v>
+        <v>6330</v>
       </c>
       <c r="D1285" s="2" t="s">
         <v>3095</v>
@@ -59794,7 +59796,7 @@
         <v>5785</v>
       </c>
       <c r="F1285" s="2" t="s">
-        <v>6333</v>
+        <v>6331</v>
       </c>
       <c r="G1285" s="3">
         <v>2</v>
@@ -59927,19 +59929,19 @@
         <v>1289</v>
       </c>
       <c r="B1290" s="2" t="s">
+        <v>6315</v>
+      </c>
+      <c r="C1290" s="2" t="s">
+        <v>6316</v>
+      </c>
+      <c r="D1290" s="2" t="s">
         <v>6317</v>
-      </c>
-      <c r="C1290" s="2" t="s">
-        <v>6318</v>
-      </c>
-      <c r="D1290" s="2" t="s">
-        <v>6319</v>
       </c>
       <c r="E1290" s="2" t="s">
         <v>5807</v>
       </c>
       <c r="F1290" s="2" t="s">
-        <v>6320</v>
+        <v>6318</v>
       </c>
       <c r="G1290" s="3">
         <v>3</v>
@@ -59959,7 +59961,7 @@
         <v>5809</v>
       </c>
       <c r="C1291" s="2" t="s">
-        <v>6926</v>
+        <v>6924</v>
       </c>
       <c r="D1291" s="2" t="s">
         <v>4172</v>
@@ -59985,7 +59987,7 @@
         <v>1291</v>
       </c>
       <c r="B1292" s="2" t="s">
-        <v>6642</v>
+        <v>6640</v>
       </c>
       <c r="C1292" s="2" t="s">
         <v>492</v>
@@ -59997,7 +59999,7 @@
         <v>494</v>
       </c>
       <c r="F1292" s="2" t="s">
-        <v>6643</v>
+        <v>6641</v>
       </c>
       <c r="G1292" s="3">
         <v>2</v>
@@ -60304,7 +60306,7 @@
         <v>1302</v>
       </c>
       <c r="B1303" s="2" t="s">
-        <v>6491</v>
+        <v>6489</v>
       </c>
       <c r="C1303" s="2" t="s">
         <v>5860</v>
@@ -60316,7 +60318,7 @@
         <v>5862</v>
       </c>
       <c r="F1303" s="2" t="s">
-        <v>6492</v>
+        <v>6490</v>
       </c>
       <c r="G1303" s="3">
         <v>2</v>
@@ -60629,13 +60631,13 @@
         <v>5717</v>
       </c>
       <c r="D1314" s="2" t="s">
-        <v>6382</v>
+        <v>6380</v>
       </c>
       <c r="E1314" s="2" t="s">
+        <v>6379</v>
+      </c>
+      <c r="F1314" s="2" t="s">
         <v>6381</v>
-      </c>
-      <c r="F1314" s="2" t="s">
-        <v>6383</v>
       </c>
       <c r="G1314" s="3">
         <v>3</v>
@@ -60652,19 +60654,19 @@
         <v>1314</v>
       </c>
       <c r="B1315" s="2" t="s">
-        <v>6377</v>
+        <v>6375</v>
       </c>
       <c r="C1315" s="2" t="s">
         <v>5903</v>
       </c>
       <c r="D1315" s="2" t="s">
+        <v>6376</v>
+      </c>
+      <c r="E1315" s="2" t="s">
+        <v>6377</v>
+      </c>
+      <c r="F1315" s="2" t="s">
         <v>6378</v>
-      </c>
-      <c r="E1315" s="2" t="s">
-        <v>6379</v>
-      </c>
-      <c r="F1315" s="2" t="s">
-        <v>6380</v>
       </c>
       <c r="G1315" s="3">
         <v>4</v>
@@ -60710,7 +60712,7 @@
         <v>1316</v>
       </c>
       <c r="B1317" s="2" t="s">
-        <v>6384</v>
+        <v>6382</v>
       </c>
       <c r="C1317" s="2" t="s">
         <v>5909</v>
@@ -60722,7 +60724,7 @@
         <v>5911</v>
       </c>
       <c r="F1317" s="2" t="s">
-        <v>6385</v>
+        <v>6383</v>
       </c>
       <c r="G1317" s="3">
         <v>2</v>
@@ -60826,19 +60828,19 @@
         <v>1320</v>
       </c>
       <c r="B1321" s="2" t="s">
-        <v>6824</v>
+        <v>6822</v>
       </c>
       <c r="C1321" s="2" t="s">
         <v>1326</v>
       </c>
       <c r="D1321" s="2" t="s">
-        <v>6823</v>
+        <v>6821</v>
       </c>
       <c r="E1321" s="2" t="s">
         <v>1328</v>
       </c>
       <c r="F1321" s="2" t="s">
-        <v>6825</v>
+        <v>6823</v>
       </c>
       <c r="G1321" s="3">
         <v>4</v>
@@ -60858,7 +60860,7 @@
         <v>5927</v>
       </c>
       <c r="C1322" s="2" t="s">
-        <v>6309</v>
+        <v>6307</v>
       </c>
       <c r="D1322" s="2" t="s">
         <v>5928</v>
@@ -60867,7 +60869,7 @@
         <v>5929</v>
       </c>
       <c r="F1322" s="2" t="s">
-        <v>6310</v>
+        <v>6308</v>
       </c>
       <c r="G1322" s="3">
         <v>4</v>
@@ -60913,7 +60915,7 @@
         <v>1323</v>
       </c>
       <c r="B1324" s="2" t="s">
-        <v>6598</v>
+        <v>6596</v>
       </c>
       <c r="C1324" s="2" t="s">
         <v>5935</v>
@@ -60998,7 +61000,7 @@
         <v>1326</v>
       </c>
       <c r="B1327" s="2" t="s">
-        <v>6706</v>
+        <v>6704</v>
       </c>
       <c r="C1327" s="2" t="s">
         <v>5942</v>
@@ -61010,7 +61012,7 @@
         <v>1326</v>
       </c>
       <c r="F1327" s="2" t="s">
-        <v>6707</v>
+        <v>6705</v>
       </c>
       <c r="G1327" s="3">
         <v>3</v>
@@ -61056,7 +61058,7 @@
         <v>1328</v>
       </c>
       <c r="B1329" s="2" t="s">
-        <v>6768</v>
+        <v>6766</v>
       </c>
       <c r="C1329" s="2" t="s">
         <v>1326</v>
@@ -61114,7 +61116,7 @@
         <v>1330</v>
       </c>
       <c r="B1331" s="2" t="s">
-        <v>6767</v>
+        <v>6765</v>
       </c>
       <c r="C1331" s="2" t="s">
         <v>1326</v>
@@ -61143,13 +61145,13 @@
         <v>1331</v>
       </c>
       <c r="B1332" s="2" t="s">
-        <v>6741</v>
+        <v>6739</v>
       </c>
       <c r="C1332" s="2" t="s">
         <v>5949</v>
       </c>
       <c r="D1332" s="2" t="s">
-        <v>6740</v>
+        <v>6738</v>
       </c>
       <c r="E1332" s="2" t="s">
         <v>5950</v>
@@ -61329,7 +61331,7 @@
         <v>4643</v>
       </c>
       <c r="F1338" s="4" t="s">
-        <v>6983</v>
+        <v>6981</v>
       </c>
       <c r="G1338" s="3">
         <v>4</v>
@@ -61358,7 +61360,7 @@
         <v>5976</v>
       </c>
       <c r="F1339" s="2" t="s">
-        <v>6982</v>
+        <v>6980</v>
       </c>
       <c r="G1339" s="3">
         <v>2</v>
@@ -61387,7 +61389,7 @@
         <v>318</v>
       </c>
       <c r="F1340" s="2" t="s">
-        <v>6979</v>
+        <v>6977</v>
       </c>
       <c r="G1340" s="3">
         <v>2</v>
@@ -61407,16 +61409,16 @@
         <v>5980</v>
       </c>
       <c r="C1341" s="2" t="s">
-        <v>6977</v>
+        <v>6975</v>
       </c>
       <c r="D1341" s="2" t="s">
-        <v>6978</v>
+        <v>6976</v>
       </c>
       <c r="E1341" s="2" t="s">
         <v>5968</v>
       </c>
       <c r="F1341" s="2" t="s">
-        <v>6981</v>
+        <v>6979</v>
       </c>
       <c r="G1341" s="3">
         <v>4</v>
@@ -61445,7 +61447,7 @@
         <v>5985</v>
       </c>
       <c r="F1342" s="2" t="s">
-        <v>6980</v>
+        <v>6978</v>
       </c>
       <c r="G1342" s="3">
         <v>4</v>
@@ -61520,7 +61522,7 @@
         <v>1344</v>
       </c>
       <c r="B1345" s="2" t="s">
-        <v>6927</v>
+        <v>6925</v>
       </c>
       <c r="C1345" s="2" t="s">
         <v>492</v>
@@ -61532,7 +61534,7 @@
         <v>5998</v>
       </c>
       <c r="F1345" s="4" t="s">
-        <v>6928</v>
+        <v>6926</v>
       </c>
       <c r="G1345" s="3">
         <v>4</v>
@@ -61811,16 +61813,16 @@
         <v>6040</v>
       </c>
       <c r="C1355" s="2" t="s">
+        <v>6492</v>
+      </c>
+      <c r="D1355" s="2" t="s">
+        <v>6491</v>
+      </c>
+      <c r="E1355" s="2" t="s">
         <v>6494</v>
       </c>
-      <c r="D1355" s="2" t="s">
+      <c r="F1355" s="2" t="s">
         <v>6493</v>
-      </c>
-      <c r="E1355" s="2" t="s">
-        <v>6496</v>
-      </c>
-      <c r="F1355" s="2" t="s">
-        <v>6495</v>
       </c>
       <c r="G1355" s="3">
         <v>4</v>
@@ -61956,16 +61958,16 @@
         <v>6066</v>
       </c>
       <c r="C1360" s="2" t="s">
-        <v>6703</v>
+        <v>6701</v>
       </c>
       <c r="D1360" s="2" t="s">
-        <v>6704</v>
+        <v>6702</v>
       </c>
       <c r="E1360" s="2" t="s">
         <v>6067</v>
       </c>
       <c r="F1360" s="2" t="s">
-        <v>6705</v>
+        <v>6703</v>
       </c>
       <c r="G1360" s="3">
         <v>1</v>
@@ -62417,7 +62419,7 @@
         <v>1375</v>
       </c>
       <c r="B1376" s="2" t="s">
-        <v>6631</v>
+        <v>6629</v>
       </c>
       <c r="C1376" s="2" t="s">
         <v>6139</v>
@@ -62446,10 +62448,10 @@
         <v>1376</v>
       </c>
       <c r="B1377" s="2" t="s">
-        <v>6845</v>
+        <v>6843</v>
       </c>
       <c r="C1377" s="2" t="s">
-        <v>6844</v>
+        <v>6842</v>
       </c>
       <c r="D1377" s="2" t="s">
         <v>6144</v>
@@ -62504,19 +62506,19 @@
         <v>1378</v>
       </c>
       <c r="B1379" s="2" t="s">
+        <v>6440</v>
+      </c>
+      <c r="C1379" s="2" t="s">
+        <v>6441</v>
+      </c>
+      <c r="D1379" s="2" t="s">
         <v>6442</v>
       </c>
-      <c r="C1379" s="2" t="s">
+      <c r="E1379" s="2" t="s">
         <v>6443</v>
       </c>
-      <c r="D1379" s="2" t="s">
+      <c r="F1379" s="2" t="s">
         <v>6444</v>
-      </c>
-      <c r="E1379" s="2" t="s">
-        <v>6445</v>
-      </c>
-      <c r="F1379" s="2" t="s">
-        <v>6446</v>
       </c>
       <c r="G1379" s="3">
         <v>1</v>
@@ -62615,30 +62617,30 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1383" spans="1:9" ht="108">
+    <row r="1383" spans="1:9" ht="92.6">
       <c r="A1383" s="2">
         <v>1382</v>
       </c>
       <c r="B1383" s="2" t="s">
-        <v>6162</v>
+        <v>7052</v>
       </c>
       <c r="C1383" s="2" t="s">
         <v>1385</v>
       </c>
       <c r="D1383" s="2" t="s">
+        <v>6162</v>
+      </c>
+      <c r="E1383" s="2" t="s">
         <v>6163</v>
       </c>
-      <c r="E1383" s="2" t="s">
-        <v>6164</v>
-      </c>
       <c r="F1383" s="2" t="s">
-        <v>6165</v>
+        <v>7051</v>
       </c>
       <c r="G1383" s="3">
         <v>4</v>
       </c>
       <c r="H1383" s="2" t="s">
-        <v>6166</v>
+        <v>6164</v>
       </c>
       <c r="I1383" s="2" t="s">
         <v>15</v>
@@ -62649,25 +62651,25 @@
         <v>1383</v>
       </c>
       <c r="B1384" s="2" t="s">
-        <v>6167</v>
+        <v>6165</v>
       </c>
       <c r="C1384" s="2" t="s">
         <v>5968</v>
       </c>
       <c r="D1384" s="2" t="s">
-        <v>6168</v>
+        <v>6166</v>
       </c>
       <c r="E1384" s="2" t="s">
-        <v>6940</v>
+        <v>6938</v>
       </c>
       <c r="F1384" s="2" t="s">
-        <v>6941</v>
+        <v>6939</v>
       </c>
       <c r="G1384" s="3">
         <v>4</v>
       </c>
       <c r="H1384" s="2" t="s">
-        <v>6169</v>
+        <v>6167</v>
       </c>
       <c r="I1384" s="2" t="s">
         <v>798</v>
@@ -62678,25 +62680,25 @@
         <v>1384</v>
       </c>
       <c r="B1385" s="2" t="s">
+        <v>6168</v>
+      </c>
+      <c r="C1385" s="2" t="s">
+        <v>6169</v>
+      </c>
+      <c r="D1385" s="2" t="s">
         <v>6170</v>
       </c>
-      <c r="C1385" s="2" t="s">
+      <c r="E1385" s="2" t="s">
         <v>6171</v>
       </c>
-      <c r="D1385" s="2" t="s">
+      <c r="F1385" s="2" t="s">
         <v>6172</v>
-      </c>
-      <c r="E1385" s="2" t="s">
-        <v>6173</v>
-      </c>
-      <c r="F1385" s="2" t="s">
-        <v>6174</v>
       </c>
       <c r="G1385" s="3">
         <v>3</v>
       </c>
       <c r="H1385" s="2" t="s">
-        <v>6175</v>
+        <v>6173</v>
       </c>
       <c r="I1385" s="2" t="s">
         <v>798</v>
@@ -62707,25 +62709,25 @@
         <v>1385</v>
       </c>
       <c r="B1386" s="2" t="s">
+        <v>6174</v>
+      </c>
+      <c r="C1386" s="2" t="s">
+        <v>6175</v>
+      </c>
+      <c r="D1386" s="2" t="s">
         <v>6176</v>
       </c>
-      <c r="C1386" s="2" t="s">
+      <c r="E1386" s="2" t="s">
         <v>6177</v>
       </c>
-      <c r="D1386" s="2" t="s">
+      <c r="F1386" s="2" t="s">
         <v>6178</v>
-      </c>
-      <c r="E1386" s="2" t="s">
-        <v>6179</v>
-      </c>
-      <c r="F1386" s="2" t="s">
-        <v>6180</v>
       </c>
       <c r="G1386" s="3">
         <v>3</v>
       </c>
       <c r="H1386" s="2" t="s">
-        <v>6181</v>
+        <v>6179</v>
       </c>
       <c r="I1386" s="2" t="s">
         <v>15</v>
@@ -62736,25 +62738,25 @@
         <v>1386</v>
       </c>
       <c r="B1387" s="2" t="s">
-        <v>6182</v>
+        <v>6180</v>
       </c>
       <c r="C1387" s="2" t="s">
+        <v>6363</v>
+      </c>
+      <c r="D1387" s="2" t="s">
+        <v>6364</v>
+      </c>
+      <c r="E1387" s="2" t="s">
         <v>6365</v>
       </c>
-      <c r="D1387" s="2" t="s">
+      <c r="F1387" s="2" t="s">
         <v>6366</v>
-      </c>
-      <c r="E1387" s="2" t="s">
-        <v>6367</v>
-      </c>
-      <c r="F1387" s="2" t="s">
-        <v>6368</v>
       </c>
       <c r="G1387" s="3">
         <v>1</v>
       </c>
       <c r="H1387" s="2" t="s">
-        <v>6183</v>
+        <v>6181</v>
       </c>
       <c r="I1387" s="2" t="s">
         <v>15</v>
@@ -62765,25 +62767,25 @@
         <v>1387</v>
       </c>
       <c r="B1388" s="2" t="s">
-        <v>6184</v>
+        <v>6182</v>
       </c>
       <c r="C1388" s="2" t="s">
-        <v>6185</v>
+        <v>6183</v>
       </c>
       <c r="D1388" s="2" t="s">
         <v>44</v>
       </c>
       <c r="E1388" s="2" t="s">
-        <v>6186</v>
+        <v>6184</v>
       </c>
       <c r="F1388" s="2" t="s">
-        <v>6187</v>
+        <v>6185</v>
       </c>
       <c r="G1388" s="3">
         <v>1</v>
       </c>
       <c r="H1388" s="2" t="s">
-        <v>6188</v>
+        <v>6186</v>
       </c>
       <c r="I1388" s="2" t="s">
         <v>798</v>
@@ -62794,25 +62796,25 @@
         <v>1388</v>
       </c>
       <c r="B1389" s="2" t="s">
+        <v>6187</v>
+      </c>
+      <c r="C1389" s="2" t="s">
+        <v>6188</v>
+      </c>
+      <c r="D1389" s="2" t="s">
         <v>6189</v>
       </c>
-      <c r="C1389" s="2" t="s">
+      <c r="E1389" s="2" t="s">
         <v>6190</v>
       </c>
-      <c r="D1389" s="2" t="s">
+      <c r="F1389" s="2" t="s">
         <v>6191</v>
-      </c>
-      <c r="E1389" s="2" t="s">
-        <v>6192</v>
-      </c>
-      <c r="F1389" s="2" t="s">
-        <v>6193</v>
       </c>
       <c r="G1389" s="3">
         <v>1</v>
       </c>
       <c r="H1389" s="2" t="s">
-        <v>6194</v>
+        <v>6192</v>
       </c>
       <c r="I1389" s="2" t="s">
         <v>15</v>
@@ -62823,25 +62825,25 @@
         <v>1389</v>
       </c>
       <c r="B1390" s="2" t="s">
+        <v>6193</v>
+      </c>
+      <c r="C1390" s="2" t="s">
+        <v>6194</v>
+      </c>
+      <c r="D1390" s="2" t="s">
         <v>6195</v>
       </c>
-      <c r="C1390" s="2" t="s">
+      <c r="E1390" s="2" t="s">
         <v>6196</v>
       </c>
-      <c r="D1390" s="2" t="s">
+      <c r="F1390" s="2" t="s">
         <v>6197</v>
-      </c>
-      <c r="E1390" s="2" t="s">
-        <v>6198</v>
-      </c>
-      <c r="F1390" s="2" t="s">
-        <v>6199</v>
       </c>
       <c r="G1390" s="3">
         <v>4</v>
       </c>
       <c r="H1390" s="2" t="s">
-        <v>6200</v>
+        <v>6198</v>
       </c>
       <c r="I1390" s="2" t="s">
         <v>15</v>
@@ -62852,25 +62854,25 @@
         <v>1390</v>
       </c>
       <c r="B1391" s="2" t="s">
+        <v>6199</v>
+      </c>
+      <c r="C1391" s="2" t="s">
+        <v>6200</v>
+      </c>
+      <c r="D1391" s="2" t="s">
         <v>6201</v>
       </c>
-      <c r="C1391" s="2" t="s">
+      <c r="E1391" s="2" t="s">
         <v>6202</v>
       </c>
-      <c r="D1391" s="2" t="s">
+      <c r="F1391" s="2" t="s">
         <v>6203</v>
-      </c>
-      <c r="E1391" s="2" t="s">
-        <v>6204</v>
-      </c>
-      <c r="F1391" s="2" t="s">
-        <v>6205</v>
       </c>
       <c r="G1391" s="3">
         <v>1</v>
       </c>
       <c r="H1391" s="2" t="s">
-        <v>6206</v>
+        <v>6204</v>
       </c>
       <c r="I1391" s="2" t="s">
         <v>15</v>
@@ -62881,25 +62883,25 @@
         <v>1391</v>
       </c>
       <c r="B1392" s="2" t="s">
+        <v>6205</v>
+      </c>
+      <c r="C1392" s="2" t="s">
+        <v>6206</v>
+      </c>
+      <c r="D1392" s="2" t="s">
         <v>6207</v>
       </c>
-      <c r="C1392" s="2" t="s">
+      <c r="E1392" s="2" t="s">
         <v>6208</v>
       </c>
-      <c r="D1392" s="2" t="s">
+      <c r="F1392" s="2" t="s">
         <v>6209</v>
-      </c>
-      <c r="E1392" s="2" t="s">
-        <v>6210</v>
-      </c>
-      <c r="F1392" s="2" t="s">
-        <v>6211</v>
       </c>
       <c r="G1392" s="3">
         <v>2</v>
       </c>
       <c r="H1392" s="2" t="s">
-        <v>6212</v>
+        <v>6210</v>
       </c>
       <c r="I1392" s="2" t="s">
         <v>15</v>
@@ -62910,25 +62912,25 @@
         <v>1392</v>
       </c>
       <c r="B1393" s="2" t="s">
+        <v>6211</v>
+      </c>
+      <c r="C1393" s="2" t="s">
+        <v>6212</v>
+      </c>
+      <c r="D1393" s="2" t="s">
         <v>6213</v>
       </c>
-      <c r="C1393" s="2" t="s">
+      <c r="E1393" s="2" t="s">
         <v>6214</v>
       </c>
-      <c r="D1393" s="2" t="s">
-        <v>6215</v>
-      </c>
-      <c r="E1393" s="2" t="s">
-        <v>6216</v>
-      </c>
       <c r="F1393" s="2" t="s">
-        <v>6715</v>
+        <v>6713</v>
       </c>
       <c r="G1393" s="3">
         <v>4</v>
       </c>
       <c r="H1393" s="2" t="s">
-        <v>6218</v>
+        <v>6216</v>
       </c>
       <c r="I1393" s="2" t="s">
         <v>798</v>
@@ -62939,25 +62941,25 @@
         <v>1393</v>
       </c>
       <c r="B1394" s="2" t="s">
+        <v>6217</v>
+      </c>
+      <c r="C1394" s="2" t="s">
+        <v>6212</v>
+      </c>
+      <c r="D1394" s="2" t="s">
+        <v>6218</v>
+      </c>
+      <c r="E1394" s="2" t="s">
+        <v>6454</v>
+      </c>
+      <c r="F1394" s="2" t="s">
         <v>6219</v>
-      </c>
-      <c r="C1394" s="2" t="s">
-        <v>6214</v>
-      </c>
-      <c r="D1394" s="2" t="s">
-        <v>6220</v>
-      </c>
-      <c r="E1394" s="2" t="s">
-        <v>6456</v>
-      </c>
-      <c r="F1394" s="2" t="s">
-        <v>6221</v>
       </c>
       <c r="G1394" s="3">
         <v>3</v>
       </c>
       <c r="H1394" s="2" t="s">
-        <v>6222</v>
+        <v>6220</v>
       </c>
       <c r="I1394" s="2" t="s">
         <v>798</v>
@@ -62968,7 +62970,7 @@
         <v>1394</v>
       </c>
       <c r="B1395" s="2" t="s">
-        <v>6223</v>
+        <v>6221</v>
       </c>
       <c r="C1395" s="2" t="s">
         <v>492</v>
@@ -62986,7 +62988,7 @@
         <v>4</v>
       </c>
       <c r="H1395" s="2" t="s">
-        <v>6224</v>
+        <v>6222</v>
       </c>
       <c r="I1395" s="2" t="s">
         <v>798</v>
@@ -62997,10 +62999,10 @@
         <v>1395</v>
       </c>
       <c r="B1396" s="2" t="s">
-        <v>6225</v>
+        <v>6223</v>
       </c>
       <c r="C1396" s="2" t="s">
-        <v>6226</v>
+        <v>6224</v>
       </c>
       <c r="D1396" s="2" t="s">
         <v>492</v>
@@ -63009,13 +63011,13 @@
         <v>491</v>
       </c>
       <c r="F1396" s="2" t="s">
-        <v>6227</v>
+        <v>6225</v>
       </c>
       <c r="G1396" s="3">
         <v>2</v>
       </c>
       <c r="H1396" s="2" t="s">
-        <v>6228</v>
+        <v>6226</v>
       </c>
       <c r="I1396" s="2" t="s">
         <v>798</v>
@@ -63026,25 +63028,25 @@
         <v>1396</v>
       </c>
       <c r="B1397" s="2" t="s">
-        <v>6229</v>
+        <v>6227</v>
       </c>
       <c r="C1397" s="2" t="s">
+        <v>6212</v>
+      </c>
+      <c r="D1397" s="2" t="s">
+        <v>6218</v>
+      </c>
+      <c r="E1397" s="2" t="s">
         <v>6214</v>
       </c>
-      <c r="D1397" s="2" t="s">
-        <v>6220</v>
-      </c>
-      <c r="E1397" s="2" t="s">
-        <v>6216</v>
-      </c>
       <c r="F1397" s="2" t="s">
-        <v>6217</v>
+        <v>6215</v>
       </c>
       <c r="G1397" s="3">
         <v>1</v>
       </c>
       <c r="H1397" s="2" t="s">
-        <v>6230</v>
+        <v>6228</v>
       </c>
       <c r="I1397" s="2" t="s">
         <v>798</v>
@@ -63055,25 +63057,25 @@
         <v>1397</v>
       </c>
       <c r="B1398" s="2" t="s">
-        <v>6231</v>
+        <v>6229</v>
       </c>
       <c r="C1398" s="2" t="s">
+        <v>6212</v>
+      </c>
+      <c r="D1398" s="2" t="s">
+        <v>6218</v>
+      </c>
+      <c r="E1398" s="2" t="s">
         <v>6214</v>
       </c>
-      <c r="D1398" s="2" t="s">
-        <v>6220</v>
-      </c>
-      <c r="E1398" s="2" t="s">
-        <v>6216</v>
-      </c>
       <c r="F1398" s="2" t="s">
-        <v>6217</v>
+        <v>6215</v>
       </c>
       <c r="G1398" s="3">
         <v>3</v>
       </c>
       <c r="H1398" s="2" t="s">
-        <v>6232</v>
+        <v>6230</v>
       </c>
       <c r="I1398" s="2" t="s">
         <v>798</v>
@@ -63084,7 +63086,7 @@
         <v>1398</v>
       </c>
       <c r="B1399" s="2" t="s">
-        <v>6233</v>
+        <v>6231</v>
       </c>
       <c r="C1399" s="2" t="s">
         <v>493</v>
@@ -63096,13 +63098,13 @@
         <v>491</v>
       </c>
       <c r="F1399" s="2" t="s">
-        <v>6234</v>
+        <v>6232</v>
       </c>
       <c r="G1399" s="3">
         <v>4</v>
       </c>
       <c r="H1399" s="2" t="s">
-        <v>6235</v>
+        <v>6233</v>
       </c>
       <c r="I1399" s="2" t="s">
         <v>798</v>
@@ -63113,25 +63115,25 @@
         <v>1399</v>
       </c>
       <c r="B1400" s="2" t="s">
+        <v>6234</v>
+      </c>
+      <c r="C1400" s="2" t="s">
+        <v>6235</v>
+      </c>
+      <c r="D1400" s="2" t="s">
         <v>6236</v>
       </c>
-      <c r="C1400" s="2" t="s">
+      <c r="E1400" s="2" t="s">
         <v>6237</v>
       </c>
-      <c r="D1400" s="2" t="s">
+      <c r="F1400" s="2" t="s">
         <v>6238</v>
-      </c>
-      <c r="E1400" s="2" t="s">
-        <v>6239</v>
-      </c>
-      <c r="F1400" s="2" t="s">
-        <v>6240</v>
       </c>
       <c r="G1400" s="3">
         <v>2</v>
       </c>
       <c r="H1400" s="2" t="s">
-        <v>6241</v>
+        <v>6239</v>
       </c>
       <c r="I1400" s="2" t="s">
         <v>798</v>
@@ -63142,25 +63144,25 @@
         <v>1400</v>
       </c>
       <c r="B1401" s="2" t="s">
+        <v>6240</v>
+      </c>
+      <c r="C1401" s="2" t="s">
+        <v>6241</v>
+      </c>
+      <c r="D1401" s="2" t="s">
         <v>6242</v>
       </c>
-      <c r="C1401" s="2" t="s">
+      <c r="E1401" s="2" t="s">
         <v>6243</v>
       </c>
-      <c r="D1401" s="2" t="s">
+      <c r="F1401" s="2" t="s">
         <v>6244</v>
-      </c>
-      <c r="E1401" s="2" t="s">
-        <v>6245</v>
-      </c>
-      <c r="F1401" s="2" t="s">
-        <v>6246</v>
       </c>
       <c r="G1401" s="3">
         <v>2</v>
       </c>
       <c r="H1401" s="2" t="s">
-        <v>6247</v>
+        <v>6245</v>
       </c>
       <c r="I1401" s="2" t="s">
         <v>798</v>
@@ -63171,25 +63173,25 @@
         <v>1401</v>
       </c>
       <c r="B1402" s="2" t="s">
-        <v>6924</v>
+        <v>6922</v>
       </c>
       <c r="C1402" s="2" t="s">
+        <v>6246</v>
+      </c>
+      <c r="D1402" s="2" t="s">
+        <v>6247</v>
+      </c>
+      <c r="E1402" s="2" t="s">
         <v>6248</v>
       </c>
-      <c r="D1402" s="2" t="s">
+      <c r="F1402" s="2" t="s">
         <v>6249</v>
-      </c>
-      <c r="E1402" s="2" t="s">
-        <v>6250</v>
-      </c>
-      <c r="F1402" s="2" t="s">
-        <v>6251</v>
       </c>
       <c r="G1402" s="3">
         <v>2</v>
       </c>
       <c r="H1402" s="2" t="s">
-        <v>6252</v>
+        <v>6250</v>
       </c>
       <c r="I1402" s="2" t="s">
         <v>15</v>
@@ -63200,25 +63202,25 @@
         <v>1402</v>
       </c>
       <c r="B1403" s="2" t="s">
+        <v>6251</v>
+      </c>
+      <c r="C1403" s="2" t="s">
+        <v>6252</v>
+      </c>
+      <c r="D1403" s="2" t="s">
         <v>6253</v>
       </c>
-      <c r="C1403" s="2" t="s">
+      <c r="E1403" s="2" t="s">
         <v>6254</v>
       </c>
-      <c r="D1403" s="2" t="s">
+      <c r="F1403" s="2" t="s">
         <v>6255</v>
-      </c>
-      <c r="E1403" s="2" t="s">
-        <v>6256</v>
-      </c>
-      <c r="F1403" s="2" t="s">
-        <v>6257</v>
       </c>
       <c r="G1403" s="3">
         <v>3</v>
       </c>
       <c r="H1403" s="2" t="s">
-        <v>6258</v>
+        <v>6256</v>
       </c>
       <c r="I1403" s="2" t="s">
         <v>15</v>
@@ -63229,25 +63231,25 @@
         <v>1403</v>
       </c>
       <c r="B1404" s="2" t="s">
+        <v>6257</v>
+      </c>
+      <c r="C1404" s="2" t="s">
+        <v>6258</v>
+      </c>
+      <c r="D1404" s="2" t="s">
         <v>6259</v>
       </c>
-      <c r="C1404" s="2" t="s">
+      <c r="E1404" s="2" t="s">
         <v>6260</v>
       </c>
-      <c r="D1404" s="2" t="s">
+      <c r="F1404" s="2" t="s">
         <v>6261</v>
-      </c>
-      <c r="E1404" s="2" t="s">
-        <v>6262</v>
-      </c>
-      <c r="F1404" s="2" t="s">
-        <v>6263</v>
       </c>
       <c r="G1404" s="3">
         <v>2</v>
       </c>
       <c r="H1404" s="2" t="s">
-        <v>6264</v>
+        <v>6262</v>
       </c>
       <c r="I1404" s="2" t="s">
         <v>15</v>

--- a/salf/丙種職業安全衛生業務主管題庫.xlsx
+++ b/salf/丙種職業安全衛生業務主管題庫.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\drher\OneDrive\文件\GitHub\drher.github.io\salf\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25f5a1833553ad9e/文件/GitHub/drher.github.io/salf/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77FCB85B-4632-4A77-A667-90D98E3EB9B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="15397" windowHeight="8751" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9463" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="乾淨題庫" sheetId="1" r:id="rId1"/>
@@ -27881,7 +27881,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="176" spans="1:9" ht="46.3">
+    <row r="176" spans="1:9" ht="61.75">
       <c r="A176" s="2">
         <v>175</v>
       </c>
@@ -32434,7 +32434,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="333" spans="1:9" ht="30.9">
+    <row r="333" spans="1:9" ht="46.3">
       <c r="A333" s="2">
         <v>332</v>
       </c>
@@ -36948,7 +36948,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="489" spans="1:9" ht="30.9">
+    <row r="489" spans="1:9" ht="46.3">
       <c r="A489" s="2">
         <v>488</v>
       </c>
@@ -38363,7 +38363,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="538" spans="1:9" ht="30.9">
+    <row r="538" spans="1:9" ht="46.3">
       <c r="A538" s="2">
         <v>537</v>
       </c>
@@ -38881,7 +38881,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="556" spans="1:9" ht="30.9">
+    <row r="556" spans="1:9" ht="46.3">
       <c r="A556" s="2">
         <v>555</v>
       </c>
@@ -45255,7 +45255,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="776" spans="1:9" ht="30.9">
+    <row r="776" spans="1:9" ht="46.3">
       <c r="A776" s="2">
         <v>775</v>
       </c>
@@ -57842,7 +57842,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="1211" spans="1:9" ht="30.9">
+    <row r="1211" spans="1:9" ht="46.3">
       <c r="A1211" s="2">
         <v>1210</v>
       </c>
@@ -61894,7 +61894,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="1351" spans="1:9" ht="30.9">
+    <row r="1351" spans="1:9" ht="46.3">
       <c r="A1351" s="2">
         <v>1350</v>
       </c>
@@ -61952,7 +61952,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="1353" spans="1:9" ht="30.9">
+    <row r="1353" spans="1:9" ht="46.3">
       <c r="A1353" s="2">
         <v>1352</v>
       </c>
@@ -62907,7 +62907,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="1386" spans="1:9" ht="77.150000000000006">
+    <row r="1386" spans="1:9" ht="92.6">
       <c r="A1386" s="2">
         <v>1385</v>
       </c>

--- a/salf/丙種職業安全衛生業務主管題庫.xlsx
+++ b/salf/丙種職業安全衛生業務主管題庫.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25f5a1833553ad9e/文件/GitHub/drher.github.io/salf/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{77FCB85B-4632-4A77-A667-90D98E3EB9B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DEB218F2-DDC3-4883-A83D-28C8999D5732}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{77FCB85B-4632-4A77-A667-90D98E3EB9B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{32561DF7-1602-4338-9A2A-58B9B957E57E}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9463" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18272,16 +18272,10 @@
     <t>死亡與永久全失人能的損失天數均為 6000 日。</t>
   </si>
   <si>
-    <t>傷害損失日數之計算每次應按損失登記 ?</t>
-  </si>
-  <si>
     <t>1000 日</t>
   </si>
   <si>
     <t>1 日</t>
-  </si>
-  <si>
-    <t>6000 昌</t>
   </si>
   <si>
     <t>10000 日</t>
@@ -22384,6 +22378,14 @@
   </si>
   <si>
     <t>雇主雇用勞工人數未滿 30 人者, 應設置何種職業安全衛生業務主管 ?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>傷害損失日數之計算每次應按損失登記 ?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>6000 日</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -23258,7 +23260,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>6629</v>
+        <v>6627</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>87</v>
@@ -23267,10 +23269,10 @@
         <v>88</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>6631</v>
+        <v>6629</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>6630</v>
+        <v>6628</v>
       </c>
       <c r="G16" s="3">
         <v>1</v>
@@ -23459,7 +23461,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>6462</v>
+        <v>6460</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>122</v>
@@ -23471,7 +23473,7 @@
         <v>124</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>6463</v>
+        <v>6461</v>
       </c>
       <c r="G23" s="3">
         <v>4</v>
@@ -23517,10 +23519,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>6219</v>
+        <v>6217</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>6220</v>
+        <v>6218</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>132</v>
@@ -23575,10 +23577,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>6645</v>
+        <v>6643</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>6646</v>
+        <v>6644</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>142</v>
@@ -23587,7 +23589,7 @@
         <v>143</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>6647</v>
+        <v>6645</v>
       </c>
       <c r="G27" s="3">
         <v>3</v>
@@ -24019,7 +24021,7 @@
         <v>224</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>6841</v>
+        <v>6839</v>
       </c>
       <c r="F42" s="2"/>
       <c r="G42" s="3">
@@ -24037,19 +24039,19 @@
         <v>42</v>
       </c>
       <c r="B43" s="2" t="s">
+        <v>6324</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>6325</v>
+      </c>
+      <c r="D43" s="2" t="s">
         <v>6326</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>6327</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>6328</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>226</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>6329</v>
+        <v>6327</v>
       </c>
       <c r="G43" s="3">
         <v>3</v>
@@ -24298,19 +24300,19 @@
         <v>51</v>
       </c>
       <c r="B52" s="2" t="s">
+        <v>6983</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>6984</v>
+      </c>
+      <c r="D52" s="2" t="s">
         <v>6985</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="E52" s="2" t="s">
         <v>6986</v>
       </c>
-      <c r="D52" s="2" t="s">
+      <c r="F52" s="2" t="s">
         <v>6987</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>6988</v>
-      </c>
-      <c r="F52" s="2" t="s">
-        <v>6989</v>
       </c>
       <c r="G52" s="3">
         <v>1</v>
@@ -24327,7 +24329,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>7015</v>
+        <v>7013</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>273</v>
@@ -24336,10 +24338,10 @@
         <v>274</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>7016</v>
+        <v>7014</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>7017</v>
+        <v>7015</v>
       </c>
       <c r="G53" s="3">
         <v>3</v>
@@ -24484,7 +24486,7 @@
         <v>303</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>6940</v>
+        <v>6938</v>
       </c>
       <c r="G58" s="3">
         <v>1</v>
@@ -24501,7 +24503,7 @@
         <v>58</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>6749</v>
+        <v>6747</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>305</v>
@@ -24513,7 +24515,7 @@
         <v>306</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>6936</v>
+        <v>6934</v>
       </c>
       <c r="G59" s="3">
         <v>1</v>
@@ -24542,7 +24544,7 @@
         <v>117</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>6937</v>
+        <v>6935</v>
       </c>
       <c r="G60" s="3">
         <v>3</v>
@@ -24571,7 +24573,7 @@
         <v>315</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>6938</v>
+        <v>6936</v>
       </c>
       <c r="G61" s="3">
         <v>4</v>
@@ -24600,7 +24602,7 @@
         <v>319</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>6939</v>
+        <v>6937</v>
       </c>
       <c r="G62" s="3">
         <v>4</v>
@@ -24629,7 +24631,7 @@
         <v>315</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>6938</v>
+        <v>6936</v>
       </c>
       <c r="G63" s="3">
         <v>3</v>
@@ -24675,7 +24677,7 @@
         <v>64</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>6283</v>
+        <v>6281</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>329</v>
@@ -24710,7 +24712,7 @@
         <v>335</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>6284</v>
+        <v>6282</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>330</v>
@@ -24849,13 +24851,13 @@
         <v>70</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>6146</v>
+        <v>6144</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>360</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>6145</v>
+        <v>6143</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>361</v>
@@ -24878,7 +24880,7 @@
         <v>71</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>6235</v>
+        <v>6233</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>364</v>
@@ -24887,10 +24889,10 @@
         <v>365</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>6237</v>
+        <v>6235</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>6236</v>
+        <v>6234</v>
       </c>
       <c r="G72" s="3">
         <v>4</v>
@@ -24939,7 +24941,7 @@
         <v>373</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>7054</v>
+        <v>7052</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>374</v>
@@ -25061,10 +25063,10 @@
         <v>393</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>6664</v>
+        <v>6662</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>6665</v>
+        <v>6663</v>
       </c>
       <c r="G78" s="3">
         <v>3</v>
@@ -25139,10 +25141,10 @@
         <v>80</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>6412</v>
+        <v>6410</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>6413</v>
+        <v>6411</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>406</v>
@@ -25258,7 +25260,7 @@
         <v>427</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>6946</v>
+        <v>6944</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>428</v>
@@ -25458,7 +25460,7 @@
         <v>91</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>6195</v>
+        <v>6193</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>462</v>
@@ -25470,7 +25472,7 @@
         <v>464</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>6196</v>
+        <v>6194</v>
       </c>
       <c r="G92" s="3">
         <v>4</v>
@@ -25487,19 +25489,19 @@
         <v>92</v>
       </c>
       <c r="B93" s="2" t="s">
+        <v>6451</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>6452</v>
+      </c>
+      <c r="D93" s="2" t="s">
         <v>6453</v>
       </c>
-      <c r="C93" s="2" t="s">
+      <c r="E93" s="2" t="s">
         <v>6454</v>
       </c>
-      <c r="D93" s="2" t="s">
+      <c r="F93" s="2" t="s">
         <v>6455</v>
-      </c>
-      <c r="E93" s="2" t="s">
-        <v>6456</v>
-      </c>
-      <c r="F93" s="2" t="s">
-        <v>6457</v>
       </c>
       <c r="G93" s="3">
         <v>4</v>
@@ -25545,7 +25547,7 @@
         <v>94</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>6598</v>
+        <v>6596</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>472</v>
@@ -25603,10 +25605,10 @@
         <v>96</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>6713</v>
+        <v>6711</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>6712</v>
+        <v>6710</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>483</v>
@@ -25744,7 +25746,7 @@
         <v>101</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>6172</v>
+        <v>6170</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>508</v>
@@ -25753,10 +25755,10 @@
         <v>509</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>6173</v>
+        <v>6171</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>6174</v>
+        <v>6172</v>
       </c>
       <c r="G102" s="3">
         <v>1</v>
@@ -25802,7 +25804,7 @@
         <v>103</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>6535</v>
+        <v>6533</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>517</v>
@@ -26034,7 +26036,7 @@
         <v>111</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>7066</v>
+        <v>7064</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>554</v>
@@ -26063,7 +26065,7 @@
         <v>112</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>7067</v>
+        <v>7065</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>554</v>
@@ -26304,10 +26306,10 @@
         <v>588</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>7004</v>
+        <v>7002</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>7005</v>
+        <v>7003</v>
       </c>
       <c r="G121" s="3">
         <v>4</v>
@@ -26481,7 +26483,7 @@
         <v>621</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>6796</v>
+        <v>6794</v>
       </c>
       <c r="G127" s="3">
         <v>4</v>
@@ -26641,7 +26643,7 @@
         <v>132</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>6202</v>
+        <v>6200</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>330</v>
@@ -26650,10 +26652,10 @@
         <v>648</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>6203</v>
+        <v>6201</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>6204</v>
+        <v>6202</v>
       </c>
       <c r="G133" s="3">
         <v>3</v>
@@ -27117,7 +27119,7 @@
         <v>728</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>6656</v>
+        <v>6654</v>
       </c>
       <c r="G149" s="3">
         <v>4</v>
@@ -27134,7 +27136,7 @@
         <v>149</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>6580</v>
+        <v>6578</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>730</v>
@@ -27366,13 +27368,13 @@
         <v>157</v>
       </c>
       <c r="B158" s="2" t="s">
+        <v>6581</v>
+      </c>
+      <c r="C158" s="2" t="s">
+        <v>6582</v>
+      </c>
+      <c r="D158" s="2" t="s">
         <v>6583</v>
-      </c>
-      <c r="C158" s="2" t="s">
-        <v>6584</v>
-      </c>
-      <c r="D158" s="2" t="s">
-        <v>6585</v>
       </c>
       <c r="E158" s="2" t="s">
         <v>763</v>
@@ -27407,7 +27409,7 @@
         <v>769</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>6213</v>
+        <v>6211</v>
       </c>
       <c r="G159" s="3">
         <v>3</v>
@@ -27543,16 +27545,16 @@
         <v>791</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>6620</v>
+        <v>6618</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>6625</v>
+        <v>6623</v>
       </c>
       <c r="E164" s="2" t="s">
         <v>792</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>6622</v>
+        <v>6620</v>
       </c>
       <c r="G164" s="3">
         <v>3</v>
@@ -27569,19 +27571,19 @@
         <v>164</v>
       </c>
       <c r="B165" s="2" t="s">
+        <v>6617</v>
+      </c>
+      <c r="C165" s="2" t="s">
         <v>6619</v>
       </c>
-      <c r="C165" s="2" t="s">
-        <v>6621</v>
-      </c>
       <c r="D165" s="2" t="s">
-        <v>6620</v>
+        <v>6618</v>
       </c>
       <c r="E165" s="2" t="s">
         <v>794</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>6623</v>
+        <v>6621</v>
       </c>
       <c r="G165" s="3">
         <v>3</v>
@@ -27610,7 +27612,7 @@
         <v>797</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>6624</v>
+        <v>6622</v>
       </c>
       <c r="G166" s="3">
         <v>3</v>
@@ -27627,25 +27629,25 @@
         <v>166</v>
       </c>
       <c r="B167" s="2" t="s">
+        <v>6364</v>
+      </c>
+      <c r="C167" s="2" t="s">
+        <v>6365</v>
+      </c>
+      <c r="D167" s="2" t="s">
         <v>6366</v>
       </c>
-      <c r="C167" s="2" t="s">
+      <c r="E167" s="2" t="s">
         <v>6367</v>
       </c>
-      <c r="D167" s="2" t="s">
+      <c r="F167" s="2" t="s">
         <v>6368</v>
-      </c>
-      <c r="E167" s="2" t="s">
-        <v>6369</v>
-      </c>
-      <c r="F167" s="2" t="s">
-        <v>6370</v>
       </c>
       <c r="G167" s="3">
         <v>3</v>
       </c>
       <c r="H167" s="2" t="s">
-        <v>6371</v>
+        <v>6369</v>
       </c>
       <c r="I167" s="2" t="s">
         <v>15</v>
@@ -27717,7 +27719,7 @@
         <v>808</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>6866</v>
+        <v>6864</v>
       </c>
       <c r="D170" s="2" t="s">
         <v>809</v>
@@ -27726,7 +27728,7 @@
         <v>810</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>6867</v>
+        <v>6865</v>
       </c>
       <c r="G170" s="3">
         <v>1</v>
@@ -27859,7 +27861,7 @@
         <v>174</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>6382</v>
+        <v>6380</v>
       </c>
       <c r="C175" s="2" t="s">
         <v>423</v>
@@ -27975,7 +27977,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>6252</v>
+        <v>6250</v>
       </c>
       <c r="C179" s="2" t="s">
         <v>835</v>
@@ -28004,19 +28006,19 @@
         <v>179</v>
       </c>
       <c r="B180" s="2" t="s">
+        <v>6736</v>
+      </c>
+      <c r="C180" s="2" t="s">
         <v>6738</v>
       </c>
-      <c r="C180" s="2" t="s">
-        <v>6740</v>
-      </c>
       <c r="D180" s="2" t="s">
-        <v>6739</v>
+        <v>6737</v>
       </c>
       <c r="E180" s="2" t="s">
         <v>853</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>6741</v>
+        <v>6739</v>
       </c>
       <c r="G180" s="3">
         <v>3</v>
@@ -28120,19 +28122,19 @@
         <v>183</v>
       </c>
       <c r="B184" s="2" t="s">
+        <v>6637</v>
+      </c>
+      <c r="C184" s="2" t="s">
+        <v>6635</v>
+      </c>
+      <c r="D184" s="2" t="s">
+        <v>6636</v>
+      </c>
+      <c r="E184" s="2" t="s">
+        <v>6638</v>
+      </c>
+      <c r="F184" s="2" t="s">
         <v>6639</v>
-      </c>
-      <c r="C184" s="2" t="s">
-        <v>6637</v>
-      </c>
-      <c r="D184" s="2" t="s">
-        <v>6638</v>
-      </c>
-      <c r="E184" s="2" t="s">
-        <v>6640</v>
-      </c>
-      <c r="F184" s="2" t="s">
-        <v>6641</v>
       </c>
       <c r="G184" s="3">
         <v>2</v>
@@ -28265,7 +28267,7 @@
         <v>188</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>6325</v>
+        <v>6323</v>
       </c>
       <c r="C189" s="2" t="s">
         <v>889</v>
@@ -28416,13 +28418,13 @@
         <v>914</v>
       </c>
       <c r="D194" s="2" t="s">
+        <v>6381</v>
+      </c>
+      <c r="E194" s="2" t="s">
+        <v>6382</v>
+      </c>
+      <c r="F194" s="2" t="s">
         <v>6383</v>
-      </c>
-      <c r="E194" s="2" t="s">
-        <v>6384</v>
-      </c>
-      <c r="F194" s="2" t="s">
-        <v>6385</v>
       </c>
       <c r="G194" s="3">
         <v>4</v>
@@ -28442,22 +28444,22 @@
         <v>916</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>6697</v>
+        <v>6695</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>6696</v>
+        <v>6694</v>
       </c>
       <c r="E195" s="2" t="s">
         <v>917</v>
       </c>
       <c r="F195" s="2" t="s">
-        <v>6698</v>
+        <v>6696</v>
       </c>
       <c r="G195" s="3">
         <v>1</v>
       </c>
       <c r="H195" s="2" t="s">
-        <v>6699</v>
+        <v>6697</v>
       </c>
       <c r="I195" s="2" t="s">
         <v>15</v>
@@ -28587,16 +28589,16 @@
         <v>942</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>6605</v>
+        <v>6603</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>6603</v>
+        <v>6601</v>
       </c>
       <c r="E200" s="2" t="s">
         <v>943</v>
       </c>
       <c r="F200" s="2" t="s">
-        <v>6604</v>
+        <v>6602</v>
       </c>
       <c r="G200" s="3">
         <v>1</v>
@@ -28645,7 +28647,7 @@
         <v>951</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>6899</v>
+        <v>6897</v>
       </c>
       <c r="D202" s="2" t="s">
         <v>952</v>
@@ -28793,13 +28795,13 @@
         <v>980</v>
       </c>
       <c r="D207" s="2" t="s">
+        <v>6129</v>
+      </c>
+      <c r="E207" s="2" t="s">
+        <v>6130</v>
+      </c>
+      <c r="F207" s="2" t="s">
         <v>6131</v>
-      </c>
-      <c r="E207" s="2" t="s">
-        <v>6132</v>
-      </c>
-      <c r="F207" s="2" t="s">
-        <v>6133</v>
       </c>
       <c r="G207" s="3">
         <v>2</v>
@@ -29309,19 +29311,19 @@
         <v>224</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>6700</v>
+        <v>6698</v>
       </c>
       <c r="C225" s="2" t="s">
         <v>1080</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>6701</v>
+        <v>6699</v>
       </c>
       <c r="E225" s="2" t="s">
         <v>1081</v>
       </c>
       <c r="F225" s="2" t="s">
-        <v>6702</v>
+        <v>6700</v>
       </c>
       <c r="G225" s="3">
         <v>4</v>
@@ -29570,7 +29572,7 @@
         <v>233</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>6827</v>
+        <v>6825</v>
       </c>
       <c r="C234" s="2" t="s">
         <v>848</v>
@@ -29773,7 +29775,7 @@
         <v>240</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>6567</v>
+        <v>6565</v>
       </c>
       <c r="C241" s="2" t="s">
         <v>1146</v>
@@ -29785,7 +29787,7 @@
         <v>1164</v>
       </c>
       <c r="F241" s="2" t="s">
-        <v>6568</v>
+        <v>6566</v>
       </c>
       <c r="G241" s="3">
         <v>1</v>
@@ -30133,7 +30135,7 @@
         <v>1224</v>
       </c>
       <c r="F253" s="2" t="s">
-        <v>6684</v>
+        <v>6682</v>
       </c>
       <c r="G253" s="3">
         <v>4</v>
@@ -30156,13 +30158,13 @@
         <v>1227</v>
       </c>
       <c r="D254" s="2" t="s">
+        <v>6740</v>
+      </c>
+      <c r="E254" s="2" t="s">
+        <v>6741</v>
+      </c>
+      <c r="F254" s="2" t="s">
         <v>6742</v>
-      </c>
-      <c r="E254" s="2" t="s">
-        <v>6743</v>
-      </c>
-      <c r="F254" s="2" t="s">
-        <v>6744</v>
       </c>
       <c r="G254" s="3">
         <v>4</v>
@@ -30295,7 +30297,7 @@
         <v>258</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>6703</v>
+        <v>6701</v>
       </c>
       <c r="C259" s="2" t="s">
         <v>1249</v>
@@ -30307,7 +30309,7 @@
         <v>1251</v>
       </c>
       <c r="F259" s="2" t="s">
-        <v>6704</v>
+        <v>6702</v>
       </c>
       <c r="G259" s="3">
         <v>1</v>
@@ -30501,13 +30503,13 @@
         <v>1286</v>
       </c>
       <c r="C266" s="2" t="s">
+        <v>6588</v>
+      </c>
+      <c r="D266" s="2" t="s">
         <v>6590</v>
       </c>
-      <c r="D266" s="2" t="s">
-        <v>6592</v>
-      </c>
       <c r="E266" s="2" t="s">
-        <v>6591</v>
+        <v>6589</v>
       </c>
       <c r="F266" s="2" t="s">
         <v>1287</v>
@@ -30614,7 +30616,7 @@
         <v>269</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>6154</v>
+        <v>6152</v>
       </c>
       <c r="C270" s="2" t="s">
         <v>1303</v>
@@ -30759,7 +30761,7 @@
         <v>274</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>6810</v>
+        <v>6808</v>
       </c>
       <c r="C275" s="2" t="s">
         <v>1332</v>
@@ -30771,7 +30773,7 @@
         <v>1333</v>
       </c>
       <c r="F275" s="2" t="s">
-        <v>6811</v>
+        <v>6809</v>
       </c>
       <c r="G275" s="3">
         <v>1</v>
@@ -30800,7 +30802,7 @@
         <v>1338</v>
       </c>
       <c r="F276" s="2" t="s">
-        <v>6812</v>
+        <v>6810</v>
       </c>
       <c r="G276" s="3">
         <v>2</v>
@@ -30829,7 +30831,7 @@
         <v>1342</v>
       </c>
       <c r="F277" s="2" t="s">
-        <v>6813</v>
+        <v>6811</v>
       </c>
       <c r="G277" s="3">
         <v>3</v>
@@ -30875,19 +30877,19 @@
         <v>278</v>
       </c>
       <c r="B279" s="2" t="s">
+        <v>6384</v>
+      </c>
+      <c r="C279" s="2" t="s">
         <v>6386</v>
       </c>
-      <c r="C279" s="2" t="s">
+      <c r="D279" s="2" t="s">
+        <v>6387</v>
+      </c>
+      <c r="E279" s="2" t="s">
         <v>6388</v>
       </c>
-      <c r="D279" s="2" t="s">
-        <v>6389</v>
-      </c>
-      <c r="E279" s="2" t="s">
-        <v>6390</v>
-      </c>
       <c r="F279" s="2" t="s">
-        <v>6387</v>
+        <v>6385</v>
       </c>
       <c r="G279" s="3">
         <v>4</v>
@@ -30904,7 +30906,7 @@
         <v>279</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>6445</v>
+        <v>6443</v>
       </c>
       <c r="C280" s="2" t="s">
         <v>1349</v>
@@ -30913,10 +30915,10 @@
         <v>1350</v>
       </c>
       <c r="E280" s="2" t="s">
-        <v>6446</v>
+        <v>6444</v>
       </c>
       <c r="F280" s="2" t="s">
-        <v>6447</v>
+        <v>6445</v>
       </c>
       <c r="G280" s="3">
         <v>3</v>
@@ -30965,16 +30967,16 @@
         <v>1358</v>
       </c>
       <c r="C282" s="2" t="s">
+        <v>7036</v>
+      </c>
+      <c r="D282" s="2" t="s">
+        <v>7037</v>
+      </c>
+      <c r="E282" s="2" t="s">
         <v>7038</v>
       </c>
-      <c r="D282" s="2" t="s">
+      <c r="F282" s="2" t="s">
         <v>7039</v>
-      </c>
-      <c r="E282" s="2" t="s">
-        <v>7040</v>
-      </c>
-      <c r="F282" s="2" t="s">
-        <v>7041</v>
       </c>
       <c r="G282" s="3">
         <v>4</v>
@@ -30991,10 +30993,10 @@
         <v>282</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>6814</v>
+        <v>6812</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>6815</v>
+        <v>6813</v>
       </c>
       <c r="D283" s="2" t="s">
         <v>1361</v>
@@ -31003,7 +31005,7 @@
         <v>1059</v>
       </c>
       <c r="F283" s="2" t="s">
-        <v>6816</v>
+        <v>6814</v>
       </c>
       <c r="G283" s="3">
         <v>4</v>
@@ -31032,7 +31034,7 @@
         <v>1366</v>
       </c>
       <c r="F284" s="2" t="s">
-        <v>6718</v>
+        <v>6716</v>
       </c>
       <c r="G284" s="3">
         <v>1</v>
@@ -31107,19 +31109,19 @@
         <v>286</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>6714</v>
+        <v>6712</v>
       </c>
       <c r="C287" s="2" t="s">
         <v>1378</v>
       </c>
       <c r="D287" s="2" t="s">
+        <v>6713</v>
+      </c>
+      <c r="E287" s="2" t="s">
+        <v>6714</v>
+      </c>
+      <c r="F287" s="2" t="s">
         <v>6715</v>
-      </c>
-      <c r="E287" s="2" t="s">
-        <v>6716</v>
-      </c>
-      <c r="F287" s="2" t="s">
-        <v>6717</v>
       </c>
       <c r="G287" s="3">
         <v>3</v>
@@ -31194,19 +31196,19 @@
         <v>289</v>
       </c>
       <c r="B290" s="2" t="s">
+        <v>6439</v>
+      </c>
+      <c r="C290" s="2" t="s">
+        <v>6440</v>
+      </c>
+      <c r="D290" s="2" t="s">
         <v>6441</v>
-      </c>
-      <c r="C290" s="2" t="s">
-        <v>6442</v>
-      </c>
-      <c r="D290" s="2" t="s">
-        <v>6443</v>
       </c>
       <c r="E290" s="2" t="s">
         <v>1392</v>
       </c>
       <c r="F290" s="2" t="s">
-        <v>6444</v>
+        <v>6442</v>
       </c>
       <c r="G290" s="3">
         <v>1</v>
@@ -31252,19 +31254,19 @@
         <v>291</v>
       </c>
       <c r="B292" s="2" t="s">
+        <v>6372</v>
+      </c>
+      <c r="C292" s="2" t="s">
+        <v>6373</v>
+      </c>
+      <c r="D292" s="2" t="s">
         <v>6374</v>
       </c>
-      <c r="C292" s="2" t="s">
+      <c r="E292" s="2" t="s">
         <v>6375</v>
       </c>
-      <c r="D292" s="2" t="s">
+      <c r="F292" s="2" t="s">
         <v>6376</v>
-      </c>
-      <c r="E292" s="2" t="s">
-        <v>6377</v>
-      </c>
-      <c r="F292" s="2" t="s">
-        <v>6378</v>
       </c>
       <c r="G292" s="3">
         <v>1</v>
@@ -31774,7 +31776,7 @@
         <v>309</v>
       </c>
       <c r="B310" s="2" t="s">
-        <v>6911</v>
+        <v>6909</v>
       </c>
       <c r="C310" s="2" t="s">
         <v>1487</v>
@@ -31919,7 +31921,7 @@
         <v>314</v>
       </c>
       <c r="B315" s="2" t="s">
-        <v>6205</v>
+        <v>6203</v>
       </c>
       <c r="C315" s="2" t="s">
         <v>1516</v>
@@ -31948,10 +31950,10 @@
         <v>315</v>
       </c>
       <c r="B316" s="2" t="s">
-        <v>6448</v>
+        <v>6446</v>
       </c>
       <c r="C316" s="2" t="s">
-        <v>6449</v>
+        <v>6447</v>
       </c>
       <c r="D316" s="2" t="s">
         <v>1521</v>
@@ -31960,7 +31962,7 @@
         <v>1522</v>
       </c>
       <c r="F316" s="2" t="s">
-        <v>6450</v>
+        <v>6448</v>
       </c>
       <c r="G316" s="3">
         <v>1</v>
@@ -32302,13 +32304,13 @@
         <v>1586</v>
       </c>
       <c r="D328" s="2" t="s">
-        <v>6285</v>
+        <v>6283</v>
       </c>
       <c r="E328" s="2" t="s">
         <v>1588</v>
       </c>
       <c r="F328" s="2" t="s">
-        <v>6286</v>
+        <v>6284</v>
       </c>
       <c r="G328" s="3">
         <v>4</v>
@@ -32557,19 +32559,19 @@
         <v>336</v>
       </c>
       <c r="B337" s="2" t="s">
-        <v>6192</v>
+        <v>6190</v>
       </c>
       <c r="C337" s="2" t="s">
         <v>1635</v>
       </c>
       <c r="D337" s="2" t="s">
-        <v>6193</v>
+        <v>6191</v>
       </c>
       <c r="E337" s="2" t="s">
         <v>688</v>
       </c>
       <c r="F337" s="2" t="s">
-        <v>6194</v>
+        <v>6192</v>
       </c>
       <c r="G337" s="3">
         <v>4</v>
@@ -32702,7 +32704,7 @@
         <v>341</v>
       </c>
       <c r="B342" s="2" t="s">
-        <v>6563</v>
+        <v>6561</v>
       </c>
       <c r="C342" s="2" t="s">
         <v>1659</v>
@@ -32711,10 +32713,10 @@
         <v>1660</v>
       </c>
       <c r="E342" s="2" t="s">
-        <v>6561</v>
+        <v>6559</v>
       </c>
       <c r="F342" s="2" t="s">
-        <v>6562</v>
+        <v>6560</v>
       </c>
       <c r="G342" s="3">
         <v>2</v>
@@ -32763,7 +32765,7 @@
         <v>1668</v>
       </c>
       <c r="C344" s="2" t="s">
-        <v>6200</v>
+        <v>6198</v>
       </c>
       <c r="D344" s="2" t="s">
         <v>1663</v>
@@ -32772,7 +32774,7 @@
         <v>1664</v>
       </c>
       <c r="F344" s="2" t="s">
-        <v>6201</v>
+        <v>6199</v>
       </c>
       <c r="G344" s="3">
         <v>1</v>
@@ -32847,7 +32849,7 @@
         <v>346</v>
       </c>
       <c r="B347" s="2" t="s">
-        <v>6909</v>
+        <v>6907</v>
       </c>
       <c r="C347" s="2" t="s">
         <v>1682</v>
@@ -32914,7 +32916,7 @@
         <v>1695</v>
       </c>
       <c r="E349" s="2" t="s">
-        <v>7035</v>
+        <v>7033</v>
       </c>
       <c r="F349" s="2" t="s">
         <v>1696</v>
@@ -32937,16 +32939,16 @@
         <v>1698</v>
       </c>
       <c r="C350" s="2" t="s">
-        <v>7033</v>
+        <v>7031</v>
       </c>
       <c r="D350" s="2" t="s">
+        <v>7032</v>
+      </c>
+      <c r="E350" s="2" t="s">
         <v>7034</v>
       </c>
-      <c r="E350" s="2" t="s">
-        <v>7036</v>
-      </c>
       <c r="F350" s="2" t="s">
-        <v>7037</v>
+        <v>7035</v>
       </c>
       <c r="G350" s="3">
         <v>4</v>
@@ -33050,19 +33052,19 @@
         <v>353</v>
       </c>
       <c r="B354" s="2" t="s">
+        <v>6657</v>
+      </c>
+      <c r="C354" s="2" t="s">
+        <v>6658</v>
+      </c>
+      <c r="D354" s="2" t="s">
         <v>6659</v>
-      </c>
-      <c r="C354" s="2" t="s">
-        <v>6660</v>
-      </c>
-      <c r="D354" s="2" t="s">
-        <v>6661</v>
       </c>
       <c r="E354" s="2" t="s">
         <v>1717</v>
       </c>
       <c r="F354" s="2" t="s">
-        <v>6662</v>
+        <v>6660</v>
       </c>
       <c r="G354" s="3">
         <v>1</v>
@@ -33688,19 +33690,19 @@
         <v>375</v>
       </c>
       <c r="B376" s="2" t="s">
-        <v>6747</v>
+        <v>6745</v>
       </c>
       <c r="C376" s="2" t="s">
         <v>1837</v>
       </c>
       <c r="D376" s="2" t="s">
-        <v>6745</v>
+        <v>6743</v>
       </c>
       <c r="E376" s="2" t="s">
         <v>1838</v>
       </c>
       <c r="F376" s="2" t="s">
-        <v>6746</v>
+        <v>6744</v>
       </c>
       <c r="G376" s="3">
         <v>1</v>
@@ -33746,7 +33748,7 @@
         <v>377</v>
       </c>
       <c r="B378" s="2" t="s">
-        <v>6748</v>
+        <v>6746</v>
       </c>
       <c r="C378" s="2" t="s">
         <v>1846</v>
@@ -33775,10 +33777,10 @@
         <v>378</v>
       </c>
       <c r="B379" s="2" t="s">
-        <v>6372</v>
+        <v>6370</v>
       </c>
       <c r="C379" s="2" t="s">
-        <v>6373</v>
+        <v>6371</v>
       </c>
       <c r="D379" s="2" t="s">
         <v>1851</v>
@@ -33891,10 +33893,10 @@
         <v>382</v>
       </c>
       <c r="B383" s="2" t="s">
-        <v>7058</v>
+        <v>7056</v>
       </c>
       <c r="C383" s="2" t="s">
-        <v>7059</v>
+        <v>7057</v>
       </c>
       <c r="D383" s="2" t="s">
         <v>1871</v>
@@ -33903,7 +33905,7 @@
         <v>1872</v>
       </c>
       <c r="F383" s="2" t="s">
-        <v>7057</v>
+        <v>7055</v>
       </c>
       <c r="G383" s="3">
         <v>2</v>
@@ -33981,7 +33983,7 @@
         <v>1884</v>
       </c>
       <c r="C386" s="2" t="s">
-        <v>6481</v>
+        <v>6479</v>
       </c>
       <c r="D386" s="2" t="s">
         <v>1881</v>
@@ -33990,7 +33992,7 @@
         <v>1885</v>
       </c>
       <c r="F386" s="2" t="s">
-        <v>6482</v>
+        <v>6480</v>
       </c>
       <c r="G386" s="3">
         <v>1</v>
@@ -34068,16 +34070,16 @@
         <v>1898</v>
       </c>
       <c r="C389" s="2" t="s">
-        <v>6913</v>
+        <v>6911</v>
       </c>
       <c r="D389" s="2" t="s">
-        <v>6914</v>
+        <v>6912</v>
       </c>
       <c r="E389" s="2" t="s">
         <v>1899</v>
       </c>
       <c r="F389" s="2" t="s">
-        <v>6915</v>
+        <v>6913</v>
       </c>
       <c r="G389" s="3">
         <v>1</v>
@@ -34187,7 +34189,7 @@
         <v>1920</v>
       </c>
       <c r="D393" s="2" t="s">
-        <v>6540</v>
+        <v>6538</v>
       </c>
       <c r="E393" s="2" t="s">
         <v>1921</v>
@@ -34210,13 +34212,13 @@
         <v>393</v>
       </c>
       <c r="B394" s="2" t="s">
-        <v>6539</v>
+        <v>6537</v>
       </c>
       <c r="C394" s="2" t="s">
         <v>1924</v>
       </c>
       <c r="D394" s="2" t="s">
-        <v>6541</v>
+        <v>6539</v>
       </c>
       <c r="E394" s="2" t="s">
         <v>1925</v>
@@ -34245,7 +34247,7 @@
         <v>1929</v>
       </c>
       <c r="D395" s="2" t="s">
-        <v>6750</v>
+        <v>6748</v>
       </c>
       <c r="E395" s="2" t="s">
         <v>1930</v>
@@ -34587,16 +34589,16 @@
         <v>406</v>
       </c>
       <c r="B407" s="2" t="s">
+        <v>6214</v>
+      </c>
+      <c r="C407" s="2" t="s">
         <v>6216</v>
-      </c>
-      <c r="C407" s="2" t="s">
-        <v>6218</v>
       </c>
       <c r="D407" s="2" t="s">
         <v>1996</v>
       </c>
       <c r="E407" s="2" t="s">
-        <v>6217</v>
+        <v>6215</v>
       </c>
       <c r="F407" s="2" t="s">
         <v>1997</v>
@@ -34616,7 +34618,7 @@
         <v>407</v>
       </c>
       <c r="B408" s="2" t="s">
-        <v>6964</v>
+        <v>6962</v>
       </c>
       <c r="C408" s="2" t="s">
         <v>1999</v>
@@ -34904,7 +34906,7 @@
         <v>417</v>
       </c>
       <c r="B418" s="2" t="s">
-        <v>6461</v>
+        <v>6459</v>
       </c>
       <c r="C418" s="2" t="s">
         <v>77</v>
@@ -35029,10 +35031,10 @@
         <v>2067</v>
       </c>
       <c r="E422" s="2" t="s">
-        <v>6657</v>
+        <v>6655</v>
       </c>
       <c r="F422" s="2" t="s">
-        <v>6658</v>
+        <v>6656</v>
       </c>
       <c r="G422" s="3">
         <v>3</v>
@@ -35049,7 +35051,7 @@
         <v>422</v>
       </c>
       <c r="B423" s="2" t="s">
-        <v>6666</v>
+        <v>6664</v>
       </c>
       <c r="C423" s="2" t="s">
         <v>2069</v>
@@ -35291,7 +35293,7 @@
         <v>2113</v>
       </c>
       <c r="F431" s="2" t="s">
-        <v>6842</v>
+        <v>6840</v>
       </c>
       <c r="G431" s="3">
         <v>4</v>
@@ -35395,7 +35397,7 @@
         <v>434</v>
       </c>
       <c r="B435" s="2" t="s">
-        <v>6227</v>
+        <v>6225</v>
       </c>
       <c r="C435" s="2" t="s">
         <v>2129</v>
@@ -35407,7 +35409,7 @@
         <v>2131</v>
       </c>
       <c r="F435" s="2" t="s">
-        <v>6228</v>
+        <v>6226</v>
       </c>
       <c r="G435" s="3">
         <v>1</v>
@@ -35480,7 +35482,7 @@
         <v>437</v>
       </c>
       <c r="B438" s="2" t="s">
-        <v>6574</v>
+        <v>6572</v>
       </c>
       <c r="C438" s="2" t="s">
         <v>2141</v>
@@ -35489,10 +35491,10 @@
         <v>2142</v>
       </c>
       <c r="E438" s="2" t="s">
-        <v>6576</v>
+        <v>6574</v>
       </c>
       <c r="F438" s="2" t="s">
-        <v>6575</v>
+        <v>6573</v>
       </c>
       <c r="G438" s="3">
         <v>1</v>
@@ -35663,7 +35665,7 @@
         <v>1254</v>
       </c>
       <c r="E444" s="2" t="s">
-        <v>6579</v>
+        <v>6577</v>
       </c>
       <c r="F444" s="2" t="s">
         <v>2161</v>
@@ -35683,19 +35685,19 @@
         <v>444</v>
       </c>
       <c r="B445" s="2" t="s">
-        <v>6577</v>
+        <v>6575</v>
       </c>
       <c r="C445" s="2" t="s">
-        <v>6578</v>
+        <v>6576</v>
       </c>
       <c r="D445" s="2" t="s">
         <v>2141</v>
       </c>
       <c r="E445" s="2" t="s">
-        <v>6575</v>
+        <v>6573</v>
       </c>
       <c r="F445" s="2" t="s">
-        <v>6576</v>
+        <v>6574</v>
       </c>
       <c r="G445" s="3">
         <v>4</v>
@@ -35924,10 +35926,10 @@
         <v>2206</v>
       </c>
       <c r="E453" s="2" t="s">
-        <v>6242</v>
+        <v>6240</v>
       </c>
       <c r="F453" s="2" t="s">
-        <v>6241</v>
+        <v>6239</v>
       </c>
       <c r="G453" s="3">
         <v>1</v>
@@ -35944,7 +35946,7 @@
         <v>453</v>
       </c>
       <c r="B454" s="2" t="s">
-        <v>6238</v>
+        <v>6236</v>
       </c>
       <c r="C454" s="2" t="s">
         <v>1342</v>
@@ -35953,10 +35955,10 @@
         <v>1327</v>
       </c>
       <c r="E454" s="2" t="s">
-        <v>6240</v>
+        <v>6238</v>
       </c>
       <c r="F454" s="2" t="s">
-        <v>6239</v>
+        <v>6237</v>
       </c>
       <c r="G454" s="3">
         <v>4</v>
@@ -36383,13 +36385,13 @@
         <v>2275</v>
       </c>
       <c r="D469" s="2" t="s">
-        <v>6596</v>
+        <v>6594</v>
       </c>
       <c r="E469" s="2" t="s">
         <v>2276</v>
       </c>
       <c r="F469" s="2" t="s">
-        <v>6597</v>
+        <v>6595</v>
       </c>
       <c r="G469" s="3">
         <v>1</v>
@@ -36984,7 +36986,7 @@
         <v>489</v>
       </c>
       <c r="B490" s="2" t="s">
-        <v>6791</v>
+        <v>6789</v>
       </c>
       <c r="C490" s="2" t="s">
         <v>2381</v>
@@ -37245,7 +37247,7 @@
         <v>498</v>
       </c>
       <c r="B499" s="2" t="s">
-        <v>6719</v>
+        <v>6717</v>
       </c>
       <c r="C499" s="2" t="s">
         <v>2424</v>
@@ -37390,19 +37392,19 @@
         <v>503</v>
       </c>
       <c r="B504" s="2" t="s">
-        <v>6287</v>
+        <v>6285</v>
       </c>
       <c r="C504" s="2" t="s">
-        <v>6288</v>
+        <v>6286</v>
       </c>
       <c r="D504" s="2" t="s">
         <v>2451</v>
       </c>
       <c r="E504" s="2" t="s">
-        <v>6289</v>
+        <v>6287</v>
       </c>
       <c r="F504" s="2" t="s">
-        <v>6290</v>
+        <v>6288</v>
       </c>
       <c r="G504" s="3">
         <v>4</v>
@@ -37475,7 +37477,7 @@
         <v>506</v>
       </c>
       <c r="B507" s="2" t="s">
-        <v>6503</v>
+        <v>6501</v>
       </c>
       <c r="C507" s="2" t="s">
         <v>2463</v>
@@ -37487,13 +37489,13 @@
         <v>2465</v>
       </c>
       <c r="F507" s="2" t="s">
-        <v>6502</v>
+        <v>6500</v>
       </c>
       <c r="G507" s="3">
         <v>3</v>
       </c>
       <c r="H507" s="2" t="s">
-        <v>6504</v>
+        <v>6502</v>
       </c>
       <c r="I507" s="2" t="s">
         <v>277</v>
@@ -37560,7 +37562,7 @@
         <v>509</v>
       </c>
       <c r="B510" s="2" t="s">
-        <v>7001</v>
+        <v>6999</v>
       </c>
       <c r="C510" s="2" t="s">
         <v>2473</v>
@@ -37705,10 +37707,10 @@
         <v>514</v>
       </c>
       <c r="B515" s="2" t="s">
-        <v>6610</v>
+        <v>6608</v>
       </c>
       <c r="C515" s="2" t="s">
-        <v>6608</v>
+        <v>6606</v>
       </c>
       <c r="D515" s="2" t="s">
         <v>2498</v>
@@ -37717,7 +37719,7 @@
         <v>2484</v>
       </c>
       <c r="F515" s="2" t="s">
-        <v>6609</v>
+        <v>6607</v>
       </c>
       <c r="G515" s="3">
         <v>3</v>
@@ -37966,7 +37968,7 @@
         <v>523</v>
       </c>
       <c r="B524" s="2" t="s">
-        <v>6887</v>
+        <v>6885</v>
       </c>
       <c r="C524" s="2" t="s">
         <v>2542</v>
@@ -37995,7 +37997,7 @@
         <v>524</v>
       </c>
       <c r="B525" s="2" t="s">
-        <v>6886</v>
+        <v>6884</v>
       </c>
       <c r="C525" s="2" t="s">
         <v>2546</v>
@@ -38053,19 +38055,19 @@
         <v>526</v>
       </c>
       <c r="B527" s="2" t="s">
-        <v>6651</v>
+        <v>6649</v>
       </c>
       <c r="C527" s="2" t="s">
         <v>424</v>
       </c>
       <c r="D527" s="2" t="s">
+        <v>6650</v>
+      </c>
+      <c r="E527" s="2" t="s">
+        <v>6651</v>
+      </c>
+      <c r="F527" s="2" t="s">
         <v>6652</v>
-      </c>
-      <c r="E527" s="2" t="s">
-        <v>6653</v>
-      </c>
-      <c r="F527" s="2" t="s">
-        <v>6654</v>
       </c>
       <c r="G527" s="3">
         <v>1</v>
@@ -38082,19 +38084,19 @@
         <v>527</v>
       </c>
       <c r="B528" s="2" t="s">
-        <v>6655</v>
+        <v>6653</v>
       </c>
       <c r="C528" s="2" t="s">
-        <v>6802</v>
+        <v>6800</v>
       </c>
       <c r="D528" s="2" t="s">
         <v>2556</v>
       </c>
       <c r="E528" s="2" t="s">
+        <v>6799</v>
+      </c>
+      <c r="F528" s="2" t="s">
         <v>6801</v>
-      </c>
-      <c r="F528" s="2" t="s">
-        <v>6803</v>
       </c>
       <c r="G528" s="3">
         <v>1</v>
@@ -38169,19 +38171,19 @@
         <v>530</v>
       </c>
       <c r="B531" s="2" t="s">
+        <v>6509</v>
+      </c>
+      <c r="C531" s="2" t="s">
         <v>6511</v>
       </c>
-      <c r="C531" s="2" t="s">
-        <v>6513</v>
-      </c>
       <c r="D531" s="2" t="s">
-        <v>6512</v>
+        <v>6510</v>
       </c>
       <c r="E531" s="2" t="s">
         <v>77</v>
       </c>
       <c r="F531" s="2" t="s">
-        <v>6514</v>
+        <v>6512</v>
       </c>
       <c r="G531" s="3">
         <v>4</v>
@@ -38198,7 +38200,7 @@
         <v>531</v>
       </c>
       <c r="B532" s="2" t="s">
-        <v>6906</v>
+        <v>6904</v>
       </c>
       <c r="C532" s="2" t="s">
         <v>2571</v>
@@ -38207,10 +38209,10 @@
         <v>2572</v>
       </c>
       <c r="E532" s="2" t="s">
-        <v>6908</v>
+        <v>6906</v>
       </c>
       <c r="F532" s="2" t="s">
-        <v>6907</v>
+        <v>6905</v>
       </c>
       <c r="G532" s="3">
         <v>4</v>
@@ -38407,7 +38409,7 @@
         <v>2604</v>
       </c>
       <c r="F539" s="2" t="s">
-        <v>6973</v>
+        <v>6971</v>
       </c>
       <c r="G539" s="3">
         <v>1</v>
@@ -38424,7 +38426,7 @@
         <v>539</v>
       </c>
       <c r="B540" s="2" t="s">
-        <v>6972</v>
+        <v>6970</v>
       </c>
       <c r="C540" s="2" t="s">
         <v>2602</v>
@@ -38436,7 +38438,7 @@
         <v>2604</v>
       </c>
       <c r="F540" s="2" t="s">
-        <v>6973</v>
+        <v>6971</v>
       </c>
       <c r="G540" s="3">
         <v>2</v>
@@ -38453,7 +38455,7 @@
         <v>540</v>
       </c>
       <c r="B541" s="2" t="s">
-        <v>6855</v>
+        <v>6853</v>
       </c>
       <c r="C541" s="2" t="s">
         <v>2602</v>
@@ -38462,10 +38464,10 @@
         <v>2603</v>
       </c>
       <c r="E541" s="2" t="s">
-        <v>6856</v>
+        <v>6854</v>
       </c>
       <c r="F541" s="2" t="s">
-        <v>6857</v>
+        <v>6855</v>
       </c>
       <c r="G541" s="3">
         <v>3</v>
@@ -38488,13 +38490,13 @@
         <v>2609</v>
       </c>
       <c r="D542" s="2" t="s">
+        <v>6665</v>
+      </c>
+      <c r="E542" s="2" t="s">
+        <v>6666</v>
+      </c>
+      <c r="F542" s="2" t="s">
         <v>6667</v>
-      </c>
-      <c r="E542" s="2" t="s">
-        <v>6668</v>
-      </c>
-      <c r="F542" s="2" t="s">
-        <v>6669</v>
       </c>
       <c r="G542" s="3">
         <v>3</v>
@@ -38511,7 +38513,7 @@
         <v>542</v>
       </c>
       <c r="B543" s="2" t="s">
-        <v>7029</v>
+        <v>7027</v>
       </c>
       <c r="C543" s="2" t="s">
         <v>2611</v>
@@ -38543,10 +38545,10 @@
         <v>2616</v>
       </c>
       <c r="C544" s="2" t="s">
-        <v>7060</v>
+        <v>7058</v>
       </c>
       <c r="D544" s="2" t="s">
-        <v>7061</v>
+        <v>7059</v>
       </c>
       <c r="E544" s="2" t="s">
         <v>2617</v>
@@ -38572,7 +38574,7 @@
         <v>2620</v>
       </c>
       <c r="C545" s="2" t="s">
-        <v>6515</v>
+        <v>6513</v>
       </c>
       <c r="D545" s="2" t="s">
         <v>2621</v>
@@ -38581,7 +38583,7 @@
         <v>2622</v>
       </c>
       <c r="F545" s="2" t="s">
-        <v>6516</v>
+        <v>6514</v>
       </c>
       <c r="G545" s="3">
         <v>4</v>
@@ -38656,19 +38658,19 @@
         <v>547</v>
       </c>
       <c r="B548" s="2" t="s">
-        <v>6723</v>
+        <v>6721</v>
       </c>
       <c r="C548" s="2" t="s">
-        <v>6724</v>
+        <v>6722</v>
       </c>
       <c r="D548" s="2" t="s">
         <v>2635</v>
       </c>
       <c r="E548" s="2" t="s">
-        <v>6726</v>
+        <v>6724</v>
       </c>
       <c r="F548" s="2" t="s">
-        <v>6725</v>
+        <v>6723</v>
       </c>
       <c r="G548" s="3">
         <v>4</v>
@@ -38859,19 +38861,19 @@
         <v>554</v>
       </c>
       <c r="B555" s="2" t="s">
-        <v>6600</v>
+        <v>6598</v>
       </c>
       <c r="C555" s="2" t="s">
         <v>2662</v>
       </c>
       <c r="D555" s="2" t="s">
-        <v>6601</v>
+        <v>6599</v>
       </c>
       <c r="E555" s="2" t="s">
         <v>2663</v>
       </c>
       <c r="F555" s="2" t="s">
-        <v>6602</v>
+        <v>6600</v>
       </c>
       <c r="G555" s="3">
         <v>4</v>
@@ -38894,7 +38896,7 @@
         <v>2665</v>
       </c>
       <c r="D556" s="2" t="s">
-        <v>6817</v>
+        <v>6815</v>
       </c>
       <c r="E556" s="2" t="s">
         <v>2666</v>
@@ -38917,13 +38919,13 @@
         <v>556</v>
       </c>
       <c r="B557" s="2" t="s">
+        <v>6135</v>
+      </c>
+      <c r="C557" s="2" t="s">
+        <v>6136</v>
+      </c>
+      <c r="D557" s="2" t="s">
         <v>6137</v>
-      </c>
-      <c r="C557" s="2" t="s">
-        <v>6138</v>
-      </c>
-      <c r="D557" s="2" t="s">
-        <v>6139</v>
       </c>
       <c r="E557" s="2" t="s">
         <v>2669</v>
@@ -39033,7 +39035,7 @@
         <v>560</v>
       </c>
       <c r="B561" s="2" t="s">
-        <v>6981</v>
+        <v>6979</v>
       </c>
       <c r="C561" s="2" t="s">
         <v>2688</v>
@@ -39045,7 +39047,7 @@
         <v>2690</v>
       </c>
       <c r="F561" s="2" t="s">
-        <v>6982</v>
+        <v>6980</v>
       </c>
       <c r="G561" s="3">
         <v>1</v>
@@ -39120,10 +39122,10 @@
         <v>563</v>
       </c>
       <c r="B564" s="2" t="s">
-        <v>6917</v>
+        <v>6915</v>
       </c>
       <c r="C564" s="2" t="s">
-        <v>6916</v>
+        <v>6914</v>
       </c>
       <c r="D564" s="2" t="s">
         <v>2700</v>
@@ -39132,7 +39134,7 @@
         <v>2701</v>
       </c>
       <c r="F564" s="2" t="s">
-        <v>6918</v>
+        <v>6916</v>
       </c>
       <c r="G564" s="3">
         <v>3</v>
@@ -39155,13 +39157,13 @@
         <v>2704</v>
       </c>
       <c r="D565" s="2" t="s">
-        <v>6431</v>
+        <v>6429</v>
       </c>
       <c r="E565" s="2" t="s">
-        <v>6429</v>
+        <v>6427</v>
       </c>
       <c r="F565" s="2" t="s">
-        <v>6430</v>
+        <v>6428</v>
       </c>
       <c r="G565" s="3">
         <v>4</v>
@@ -39178,7 +39180,7 @@
         <v>565</v>
       </c>
       <c r="B566" s="2" t="s">
-        <v>6520</v>
+        <v>6518</v>
       </c>
       <c r="C566" s="2" t="s">
         <v>2706</v>
@@ -39190,7 +39192,7 @@
         <v>2708</v>
       </c>
       <c r="F566" s="2" t="s">
-        <v>6521</v>
+        <v>6519</v>
       </c>
       <c r="G566" s="3">
         <v>3</v>
@@ -39352,19 +39354,19 @@
         <v>571</v>
       </c>
       <c r="B572" s="2" t="s">
-        <v>6317</v>
+        <v>6315</v>
       </c>
       <c r="C572" s="2" t="s">
+        <v>6259</v>
+      </c>
+      <c r="D572" s="2" t="s">
+        <v>6260</v>
+      </c>
+      <c r="E572" s="2" t="s">
+        <v>6262</v>
+      </c>
+      <c r="F572" s="2" t="s">
         <v>6261</v>
-      </c>
-      <c r="D572" s="2" t="s">
-        <v>6262</v>
-      </c>
-      <c r="E572" s="2" t="s">
-        <v>6264</v>
-      </c>
-      <c r="F572" s="2" t="s">
-        <v>6263</v>
       </c>
       <c r="G572" s="3">
         <v>4</v>
@@ -39381,19 +39383,19 @@
         <v>572</v>
       </c>
       <c r="B573" s="2" t="s">
-        <v>6318</v>
+        <v>6316</v>
       </c>
       <c r="C573" s="2" t="s">
-        <v>6264</v>
+        <v>6262</v>
       </c>
       <c r="D573" s="2" t="s">
-        <v>6263</v>
+        <v>6261</v>
       </c>
       <c r="E573" s="2" t="s">
-        <v>6261</v>
+        <v>6259</v>
       </c>
       <c r="F573" s="2" t="s">
-        <v>6262</v>
+        <v>6260</v>
       </c>
       <c r="G573" s="3">
         <v>4</v>
@@ -39410,19 +39412,19 @@
         <v>573</v>
       </c>
       <c r="B574" s="2" t="s">
+        <v>6263</v>
+      </c>
+      <c r="C574" s="2" t="s">
+        <v>6261</v>
+      </c>
+      <c r="D574" s="2" t="s">
+        <v>6264</v>
+      </c>
+      <c r="E574" s="2" t="s">
         <v>6265</v>
       </c>
-      <c r="C574" s="2" t="s">
-        <v>6263</v>
-      </c>
-      <c r="D574" s="2" t="s">
-        <v>6266</v>
-      </c>
-      <c r="E574" s="2" t="s">
-        <v>6267</v>
-      </c>
       <c r="F574" s="2" t="s">
-        <v>6264</v>
+        <v>6262</v>
       </c>
       <c r="G574" s="3">
         <v>2</v>
@@ -39445,7 +39447,7 @@
         <v>2742</v>
       </c>
       <c r="D575" s="2" t="s">
-        <v>6268</v>
+        <v>6266</v>
       </c>
       <c r="E575" s="2" t="s">
         <v>2743</v>
@@ -39497,19 +39499,19 @@
         <v>576</v>
       </c>
       <c r="B577" s="2" t="s">
+        <v>6272</v>
+      </c>
+      <c r="C577" s="2" t="s">
+        <v>6276</v>
+      </c>
+      <c r="D577" s="2" t="s">
+        <v>6273</v>
+      </c>
+      <c r="E577" s="2" t="s">
         <v>6274</v>
       </c>
-      <c r="C577" s="2" t="s">
-        <v>6278</v>
-      </c>
-      <c r="D577" s="2" t="s">
+      <c r="F577" s="2" t="s">
         <v>6275</v>
-      </c>
-      <c r="E577" s="2" t="s">
-        <v>6276</v>
-      </c>
-      <c r="F577" s="2" t="s">
-        <v>6277</v>
       </c>
       <c r="G577" s="3">
         <v>3</v>
@@ -39526,19 +39528,19 @@
         <v>577</v>
       </c>
       <c r="B578" s="5" t="s">
+        <v>6267</v>
+      </c>
+      <c r="C578" s="2" t="s">
+        <v>6268</v>
+      </c>
+      <c r="D578" s="2" t="s">
         <v>6269</v>
       </c>
-      <c r="C578" s="2" t="s">
+      <c r="E578" s="2" t="s">
+        <v>6271</v>
+      </c>
+      <c r="F578" s="2" t="s">
         <v>6270</v>
-      </c>
-      <c r="D578" s="2" t="s">
-        <v>6271</v>
-      </c>
-      <c r="E578" s="2" t="s">
-        <v>6273</v>
-      </c>
-      <c r="F578" s="2" t="s">
-        <v>6272</v>
       </c>
       <c r="G578" s="3">
         <v>1</v>
@@ -39555,16 +39557,16 @@
         <v>578</v>
       </c>
       <c r="B579" s="2" t="s">
+        <v>6277</v>
+      </c>
+      <c r="C579" s="2" t="s">
+        <v>6278</v>
+      </c>
+      <c r="D579" s="2" t="s">
         <v>6279</v>
       </c>
-      <c r="C579" s="2" t="s">
+      <c r="E579" s="2" t="s">
         <v>6280</v>
-      </c>
-      <c r="D579" s="2" t="s">
-        <v>6281</v>
-      </c>
-      <c r="E579" s="2" t="s">
-        <v>6282</v>
       </c>
       <c r="F579" s="2" t="s">
         <v>2752</v>
@@ -39593,7 +39595,7 @@
         <v>2756</v>
       </c>
       <c r="E580" s="2" t="s">
-        <v>6613</v>
+        <v>6611</v>
       </c>
       <c r="F580" s="2" t="s">
         <v>2757</v>
@@ -39625,7 +39627,7 @@
         <v>2762</v>
       </c>
       <c r="F581" s="2" t="s">
-        <v>6345</v>
+        <v>6343</v>
       </c>
       <c r="G581" s="3">
         <v>3</v>
@@ -39758,7 +39760,7 @@
         <v>585</v>
       </c>
       <c r="B586" s="2" t="s">
-        <v>6868</v>
+        <v>6866</v>
       </c>
       <c r="C586" s="2" t="s">
         <v>2786</v>
@@ -39767,10 +39769,10 @@
         <v>2787</v>
       </c>
       <c r="E586" s="2" t="s">
-        <v>6869</v>
+        <v>6867</v>
       </c>
       <c r="F586" s="2" t="s">
-        <v>6870</v>
+        <v>6868</v>
       </c>
       <c r="G586" s="3">
         <v>4</v>
@@ -39901,19 +39903,19 @@
         <v>590</v>
       </c>
       <c r="B591" s="2" t="s">
+        <v>6756</v>
+      </c>
+      <c r="C591" s="2" t="s">
+        <v>6757</v>
+      </c>
+      <c r="D591" s="2" t="s">
         <v>6758</v>
       </c>
-      <c r="C591" s="2" t="s">
+      <c r="E591" s="2" t="s">
+        <v>6760</v>
+      </c>
+      <c r="F591" s="2" t="s">
         <v>6759</v>
-      </c>
-      <c r="D591" s="2" t="s">
-        <v>6760</v>
-      </c>
-      <c r="E591" s="2" t="s">
-        <v>6762</v>
-      </c>
-      <c r="F591" s="2" t="s">
-        <v>6761</v>
       </c>
       <c r="G591" s="3">
         <v>4</v>
@@ -39930,19 +39932,19 @@
         <v>591</v>
       </c>
       <c r="B592" s="2" t="s">
+        <v>6412</v>
+      </c>
+      <c r="C592" s="2" t="s">
+        <v>6426</v>
+      </c>
+      <c r="D592" s="2" t="s">
+        <v>6413</v>
+      </c>
+      <c r="E592" s="2" t="s">
         <v>6414</v>
       </c>
-      <c r="C592" s="2" t="s">
-        <v>6428</v>
-      </c>
-      <c r="D592" s="2" t="s">
+      <c r="F592" s="2" t="s">
         <v>6415</v>
-      </c>
-      <c r="E592" s="2" t="s">
-        <v>6416</v>
-      </c>
-      <c r="F592" s="2" t="s">
-        <v>6417</v>
       </c>
       <c r="G592" s="3">
         <v>1</v>
@@ -39988,10 +39990,10 @@
         <v>593</v>
       </c>
       <c r="B594" s="2" t="s">
-        <v>6559</v>
+        <v>6557</v>
       </c>
       <c r="C594" s="2" t="s">
-        <v>6558</v>
+        <v>6556</v>
       </c>
       <c r="D594" s="2" t="s">
         <v>2819</v>
@@ -40000,7 +40002,7 @@
         <v>2820</v>
       </c>
       <c r="F594" s="2" t="s">
-        <v>6560</v>
+        <v>6558</v>
       </c>
       <c r="G594" s="3">
         <v>3</v>
@@ -40365,7 +40367,7 @@
         <v>606</v>
       </c>
       <c r="B607" s="2" t="s">
-        <v>7065</v>
+        <v>7063</v>
       </c>
       <c r="C607" s="2" t="s">
         <v>957</v>
@@ -40626,7 +40628,7 @@
         <v>615</v>
       </c>
       <c r="B616" s="2" t="s">
-        <v>6166</v>
+        <v>6164</v>
       </c>
       <c r="C616" s="2" t="s">
         <v>2918</v>
@@ -40742,7 +40744,7 @@
         <v>619</v>
       </c>
       <c r="B620" s="2" t="s">
-        <v>6229</v>
+        <v>6227</v>
       </c>
       <c r="C620" s="2" t="s">
         <v>2939</v>
@@ -40754,7 +40756,7 @@
         <v>2941</v>
       </c>
       <c r="F620" s="2" t="s">
-        <v>6230</v>
+        <v>6228</v>
       </c>
       <c r="G620" s="3">
         <v>4</v>
@@ -40771,7 +40773,7 @@
         <v>620</v>
       </c>
       <c r="B621" s="2" t="s">
-        <v>6878</v>
+        <v>6876</v>
       </c>
       <c r="C621" s="2" t="s">
         <v>2943</v>
@@ -40783,7 +40785,7 @@
         <v>2945</v>
       </c>
       <c r="F621" s="2" t="s">
-        <v>6879</v>
+        <v>6877</v>
       </c>
       <c r="G621" s="3">
         <v>4</v>
@@ -40829,7 +40831,7 @@
         <v>622</v>
       </c>
       <c r="B623" s="2" t="s">
-        <v>6893</v>
+        <v>6891</v>
       </c>
       <c r="C623" s="2" t="s">
         <v>937</v>
@@ -40841,7 +40843,7 @@
         <v>938</v>
       </c>
       <c r="F623" s="2" t="s">
-        <v>6894</v>
+        <v>6892</v>
       </c>
       <c r="G623" s="3">
         <v>3</v>
@@ -40858,19 +40860,19 @@
         <v>623</v>
       </c>
       <c r="B624" s="2" t="s">
+        <v>6893</v>
+      </c>
+      <c r="C624" s="2" t="s">
+        <v>6894</v>
+      </c>
+      <c r="D624" s="2" t="s">
         <v>6895</v>
       </c>
-      <c r="C624" s="2" t="s">
+      <c r="E624" s="2" t="s">
         <v>6896</v>
       </c>
-      <c r="D624" s="2" t="s">
-        <v>6897</v>
-      </c>
-      <c r="E624" s="2" t="s">
-        <v>6898</v>
-      </c>
       <c r="F624" s="2" t="s">
-        <v>6877</v>
+        <v>6875</v>
       </c>
       <c r="G624" s="3">
         <v>4</v>
@@ -40916,19 +40918,19 @@
         <v>625</v>
       </c>
       <c r="B626" s="2" t="s">
+        <v>6430</v>
+      </c>
+      <c r="C626" s="2" t="s">
+        <v>6431</v>
+      </c>
+      <c r="D626" s="2" t="s">
         <v>6432</v>
       </c>
-      <c r="C626" s="2" t="s">
+      <c r="E626" s="2" t="s">
         <v>6433</v>
       </c>
-      <c r="D626" s="2" t="s">
+      <c r="F626" s="2" t="s">
         <v>6434</v>
-      </c>
-      <c r="E626" s="2" t="s">
-        <v>6435</v>
-      </c>
-      <c r="F626" s="2" t="s">
-        <v>6436</v>
       </c>
       <c r="G626" s="3">
         <v>4</v>
@@ -40945,7 +40947,7 @@
         <v>626</v>
       </c>
       <c r="B627" s="2" t="s">
-        <v>6363</v>
+        <v>6361</v>
       </c>
       <c r="C627" s="2" t="s">
         <v>1005</v>
@@ -41041,10 +41043,10 @@
         <v>2978</v>
       </c>
       <c r="E630" s="2" t="s">
-        <v>6518</v>
+        <v>6516</v>
       </c>
       <c r="F630" s="2" t="s">
-        <v>6519</v>
+        <v>6517</v>
       </c>
       <c r="G630" s="3">
         <v>1</v>
@@ -41119,7 +41121,7 @@
         <v>632</v>
       </c>
       <c r="B633" s="2" t="s">
-        <v>6530</v>
+        <v>6528</v>
       </c>
       <c r="C633" s="2" t="s">
         <v>2992</v>
@@ -41148,19 +41150,19 @@
         <v>633</v>
       </c>
       <c r="B634" s="2" t="s">
-        <v>6533</v>
+        <v>6531</v>
       </c>
       <c r="C634" s="2" t="s">
+        <v>6527</v>
+      </c>
+      <c r="D634" s="2" t="s">
+        <v>6530</v>
+      </c>
+      <c r="E634" s="2" t="s">
+        <v>6532</v>
+      </c>
+      <c r="F634" s="2" t="s">
         <v>6529</v>
-      </c>
-      <c r="D634" s="2" t="s">
-        <v>6532</v>
-      </c>
-      <c r="E634" s="2" t="s">
-        <v>6534</v>
-      </c>
-      <c r="F634" s="2" t="s">
-        <v>6531</v>
       </c>
       <c r="G634" s="3">
         <v>4</v>
@@ -41206,19 +41208,19 @@
         <v>635</v>
       </c>
       <c r="B636" s="2" t="s">
-        <v>6708</v>
+        <v>6706</v>
       </c>
       <c r="C636" s="2" t="s">
+        <v>6703</v>
+      </c>
+      <c r="D636" s="2" t="s">
+        <v>6704</v>
+      </c>
+      <c r="E636" s="2" t="s">
         <v>6705</v>
       </c>
-      <c r="D636" s="2" t="s">
-        <v>6706</v>
-      </c>
-      <c r="E636" s="2" t="s">
+      <c r="F636" s="2" t="s">
         <v>6707</v>
-      </c>
-      <c r="F636" s="2" t="s">
-        <v>6709</v>
       </c>
       <c r="G636" s="3">
         <v>1</v>
@@ -41293,7 +41295,7 @@
         <v>638</v>
       </c>
       <c r="B639" s="2" t="s">
-        <v>6932</v>
+        <v>6930</v>
       </c>
       <c r="C639" s="2" t="s">
         <v>3015</v>
@@ -41302,7 +41304,7 @@
         <v>3016</v>
       </c>
       <c r="E639" s="2" t="s">
-        <v>6933</v>
+        <v>6931</v>
       </c>
       <c r="F639" s="2" t="s">
         <v>3017</v>
@@ -41334,7 +41336,7 @@
         <v>3020</v>
       </c>
       <c r="F640" s="2" t="s">
-        <v>6144</v>
+        <v>6142</v>
       </c>
       <c r="G640" s="3">
         <v>2</v>
@@ -41499,7 +41501,7 @@
         <v>3047</v>
       </c>
       <c r="C646" s="2" t="s">
-        <v>7042</v>
+        <v>7040</v>
       </c>
       <c r="D646" s="2" t="s">
         <v>3048</v>
@@ -41554,7 +41556,7 @@
         <v>647</v>
       </c>
       <c r="B648" s="2" t="s">
-        <v>6483</v>
+        <v>6481</v>
       </c>
       <c r="C648" s="2" t="s">
         <v>3053</v>
@@ -41566,7 +41568,7 @@
         <v>3056</v>
       </c>
       <c r="F648" s="2" t="s">
-        <v>6484</v>
+        <v>6482</v>
       </c>
       <c r="G648" s="3">
         <v>1</v>
@@ -41612,7 +41614,7 @@
         <v>649</v>
       </c>
       <c r="B650" s="2" t="s">
-        <v>6727</v>
+        <v>6725</v>
       </c>
       <c r="C650" s="2" t="s">
         <v>3064</v>
@@ -41641,7 +41643,7 @@
         <v>650</v>
       </c>
       <c r="B651" s="2" t="s">
-        <v>6177</v>
+        <v>6175</v>
       </c>
       <c r="C651" s="2" t="s">
         <v>3069</v>
@@ -41650,10 +41652,10 @@
         <v>3070</v>
       </c>
       <c r="E651" s="2" t="s">
-        <v>6178</v>
+        <v>6176</v>
       </c>
       <c r="F651" s="2" t="s">
-        <v>6179</v>
+        <v>6177</v>
       </c>
       <c r="G651" s="3">
         <v>2</v>
@@ -41699,7 +41701,7 @@
         <v>652</v>
       </c>
       <c r="B653" s="2" t="s">
-        <v>6225</v>
+        <v>6223</v>
       </c>
       <c r="C653" s="2" t="s">
         <v>1416</v>
@@ -41711,7 +41713,7 @@
         <v>3079</v>
       </c>
       <c r="F653" s="2" t="s">
-        <v>6226</v>
+        <v>6224</v>
       </c>
       <c r="G653" s="3">
         <v>1</v>
@@ -41757,10 +41759,10 @@
         <v>654</v>
       </c>
       <c r="B655" s="2" t="s">
-        <v>6593</v>
+        <v>6591</v>
       </c>
       <c r="C655" s="2" t="s">
-        <v>6594</v>
+        <v>6592</v>
       </c>
       <c r="D655" s="2" t="s">
         <v>3088</v>
@@ -41769,7 +41771,7 @@
         <v>3089</v>
       </c>
       <c r="F655" s="2" t="s">
-        <v>6595</v>
+        <v>6593</v>
       </c>
       <c r="G655" s="3">
         <v>4</v>
@@ -42047,7 +42049,7 @@
         <v>664</v>
       </c>
       <c r="B665" s="2" t="s">
-        <v>6904</v>
+        <v>6902</v>
       </c>
       <c r="C665" s="2" t="s">
         <v>3140</v>
@@ -42517,13 +42519,13 @@
         <v>3210</v>
       </c>
       <c r="D681" s="2" t="s">
-        <v>6976</v>
+        <v>6974</v>
       </c>
       <c r="E681" s="2" t="s">
         <v>3211</v>
       </c>
       <c r="F681" s="2" t="s">
-        <v>6977</v>
+        <v>6975</v>
       </c>
       <c r="G681" s="3">
         <v>4</v>
@@ -42656,7 +42658,7 @@
         <v>685</v>
       </c>
       <c r="B686" s="2" t="s">
-        <v>7026</v>
+        <v>7024</v>
       </c>
       <c r="C686" s="2" t="s">
         <v>3229</v>
@@ -42668,7 +42670,7 @@
         <v>3231</v>
       </c>
       <c r="F686" s="2" t="s">
-        <v>7025</v>
+        <v>7023</v>
       </c>
       <c r="G686" s="3">
         <v>1</v>
@@ -42859,19 +42861,19 @@
         <v>692</v>
       </c>
       <c r="B693" s="2" t="s">
+        <v>6939</v>
+      </c>
+      <c r="C693" s="2" t="s">
+        <v>6940</v>
+      </c>
+      <c r="D693" s="2" t="s">
         <v>6941</v>
       </c>
-      <c r="C693" s="2" t="s">
+      <c r="E693" s="2" t="s">
+        <v>6943</v>
+      </c>
+      <c r="F693" s="2" t="s">
         <v>6942</v>
-      </c>
-      <c r="D693" s="2" t="s">
-        <v>6943</v>
-      </c>
-      <c r="E693" s="2" t="s">
-        <v>6945</v>
-      </c>
-      <c r="F693" s="2" t="s">
-        <v>6944</v>
       </c>
       <c r="G693" s="3">
         <v>4</v>
@@ -42900,7 +42902,7 @@
         <v>964</v>
       </c>
       <c r="F694" s="2" t="s">
-        <v>6934</v>
+        <v>6932</v>
       </c>
       <c r="G694" s="3">
         <v>3</v>
@@ -42917,7 +42919,7 @@
         <v>694</v>
       </c>
       <c r="B695" s="2" t="s">
-        <v>6935</v>
+        <v>6933</v>
       </c>
       <c r="C695" s="2" t="s">
         <v>3263</v>
@@ -43004,7 +43006,7 @@
         <v>697</v>
       </c>
       <c r="B698" s="2" t="s">
-        <v>6566</v>
+        <v>6564</v>
       </c>
       <c r="C698" s="2" t="s">
         <v>3277</v>
@@ -43016,7 +43018,7 @@
         <v>3279</v>
       </c>
       <c r="F698" s="2" t="s">
-        <v>6565</v>
+        <v>6563</v>
       </c>
       <c r="G698" s="3">
         <v>4</v>
@@ -43033,7 +43035,7 @@
         <v>698</v>
       </c>
       <c r="B699" s="2" t="s">
-        <v>6564</v>
+        <v>6562</v>
       </c>
       <c r="C699" s="2" t="s">
         <v>3281</v>
@@ -43091,7 +43093,7 @@
         <v>700</v>
       </c>
       <c r="B701" s="2" t="s">
-        <v>6860</v>
+        <v>6858</v>
       </c>
       <c r="C701" s="2" t="s">
         <v>958</v>
@@ -43155,13 +43157,13 @@
         <v>3303</v>
       </c>
       <c r="D703" s="2" t="s">
-        <v>7027</v>
+        <v>7025</v>
       </c>
       <c r="E703" s="2" t="s">
         <v>3304</v>
       </c>
       <c r="F703" s="2" t="s">
-        <v>7028</v>
+        <v>7026</v>
       </c>
       <c r="G703" s="3">
         <v>2</v>
@@ -43207,25 +43209,25 @@
         <v>704</v>
       </c>
       <c r="B705" s="2" t="s">
-        <v>6819</v>
+        <v>6817</v>
       </c>
       <c r="C705" s="2" t="s">
         <v>3310</v>
       </c>
       <c r="D705" s="2" t="s">
-        <v>6379</v>
+        <v>6377</v>
       </c>
       <c r="E705" s="2" t="s">
         <v>3311</v>
       </c>
       <c r="F705" s="2" t="s">
-        <v>6380</v>
+        <v>6378</v>
       </c>
       <c r="G705" s="3">
         <v>2</v>
       </c>
       <c r="H705" s="2" t="s">
-        <v>6381</v>
+        <v>6379</v>
       </c>
       <c r="I705" s="2" t="s">
         <v>15</v>
@@ -43236,7 +43238,7 @@
         <v>705</v>
       </c>
       <c r="B706" s="2" t="s">
-        <v>6818</v>
+        <v>6816</v>
       </c>
       <c r="C706" s="2" t="s">
         <v>107</v>
@@ -43245,10 +43247,10 @@
         <v>3312</v>
       </c>
       <c r="E706" s="2" t="s">
-        <v>6820</v>
+        <v>6818</v>
       </c>
       <c r="F706" s="2" t="s">
-        <v>6821</v>
+        <v>6819</v>
       </c>
       <c r="G706" s="3">
         <v>4</v>
@@ -43352,7 +43354,7 @@
         <v>709</v>
       </c>
       <c r="B710" s="2" t="s">
-        <v>7009</v>
+        <v>7007</v>
       </c>
       <c r="C710" s="2" t="s">
         <v>2955</v>
@@ -43613,7 +43615,7 @@
         <v>718</v>
       </c>
       <c r="B719" s="2" t="s">
-        <v>6253</v>
+        <v>6251</v>
       </c>
       <c r="C719" s="2" t="s">
         <v>669</v>
@@ -43764,7 +43766,7 @@
         <v>3381</v>
       </c>
       <c r="D724" s="2" t="s">
-        <v>6912</v>
+        <v>6910</v>
       </c>
       <c r="E724" s="2" t="s">
         <v>3359</v>
@@ -43790,16 +43792,16 @@
         <v>3384</v>
       </c>
       <c r="C725" s="2" t="s">
+        <v>7048</v>
+      </c>
+      <c r="D725" s="2" t="s">
+        <v>7049</v>
+      </c>
+      <c r="E725" s="2" t="s">
+        <v>7051</v>
+      </c>
+      <c r="F725" s="2" t="s">
         <v>7050</v>
-      </c>
-      <c r="D725" s="2" t="s">
-        <v>7051</v>
-      </c>
-      <c r="E725" s="2" t="s">
-        <v>7053</v>
-      </c>
-      <c r="F725" s="2" t="s">
-        <v>7052</v>
       </c>
       <c r="G725" s="3">
         <v>4</v>
@@ -43816,7 +43818,7 @@
         <v>725</v>
       </c>
       <c r="B726" s="2" t="s">
-        <v>6319</v>
+        <v>6317</v>
       </c>
       <c r="C726" s="2" t="s">
         <v>3385</v>
@@ -43825,10 +43827,10 @@
         <v>3386</v>
       </c>
       <c r="E726" s="2" t="s">
-        <v>6320</v>
+        <v>6318</v>
       </c>
       <c r="F726" s="2" t="s">
-        <v>6321</v>
+        <v>6319</v>
       </c>
       <c r="G726" s="3">
         <v>1</v>
@@ -43883,10 +43885,10 @@
         <v>3391</v>
       </c>
       <c r="E728" s="2" t="s">
-        <v>6588</v>
+        <v>6586</v>
       </c>
       <c r="F728" s="2" t="s">
-        <v>6589</v>
+        <v>6587</v>
       </c>
       <c r="G728" s="3">
         <v>3</v>
@@ -43903,7 +43905,7 @@
         <v>728</v>
       </c>
       <c r="B729" s="2" t="s">
-        <v>7010</v>
+        <v>7008</v>
       </c>
       <c r="C729" s="2" t="s">
         <v>3393</v>
@@ -43915,7 +43917,7 @@
         <v>3395</v>
       </c>
       <c r="F729" s="2" t="s">
-        <v>7011</v>
+        <v>7009</v>
       </c>
       <c r="G729" s="3">
         <v>1</v>
@@ -43932,7 +43934,7 @@
         <v>729</v>
       </c>
       <c r="B730" s="2" t="s">
-        <v>6993</v>
+        <v>6991</v>
       </c>
       <c r="C730" s="2" t="s">
         <v>3397</v>
@@ -43961,16 +43963,16 @@
         <v>730</v>
       </c>
       <c r="B731" s="2" t="s">
+        <v>6339</v>
+      </c>
+      <c r="C731" s="2" t="s">
+        <v>6340</v>
+      </c>
+      <c r="D731" s="2" t="s">
         <v>6341</v>
       </c>
-      <c r="C731" s="2" t="s">
+      <c r="E731" s="2" t="s">
         <v>6342</v>
-      </c>
-      <c r="D731" s="2" t="s">
-        <v>6343</v>
-      </c>
-      <c r="E731" s="2" t="s">
-        <v>6344</v>
       </c>
       <c r="F731" s="2" t="s">
         <v>51</v>
@@ -44048,7 +44050,7 @@
         <v>733</v>
       </c>
       <c r="B734" s="2" t="s">
-        <v>6406</v>
+        <v>6404</v>
       </c>
       <c r="C734" s="6">
         <v>7.0000000000000007E-2</v>
@@ -44080,16 +44082,16 @@
         <v>3413</v>
       </c>
       <c r="C735" s="2" t="s">
+        <v>6401</v>
+      </c>
+      <c r="D735" s="2" t="s">
+        <v>6400</v>
+      </c>
+      <c r="E735" s="2" t="s">
         <v>6403</v>
       </c>
-      <c r="D735" s="2" t="s">
+      <c r="F735" s="2" t="s">
         <v>6402</v>
-      </c>
-      <c r="E735" s="2" t="s">
-        <v>6405</v>
-      </c>
-      <c r="F735" s="2" t="s">
-        <v>6404</v>
       </c>
       <c r="G735" s="3">
         <v>4</v>
@@ -44135,19 +44137,19 @@
         <v>736</v>
       </c>
       <c r="B737" s="2" t="s">
-        <v>6313</v>
+        <v>6311</v>
       </c>
       <c r="C737" s="2" t="s">
+        <v>6860</v>
+      </c>
+      <c r="D737" s="2" t="s">
+        <v>6861</v>
+      </c>
+      <c r="E737" s="2" t="s">
         <v>6862</v>
       </c>
-      <c r="D737" s="2" t="s">
+      <c r="F737" s="2" t="s">
         <v>6863</v>
-      </c>
-      <c r="E737" s="2" t="s">
-        <v>6864</v>
-      </c>
-      <c r="F737" s="2" t="s">
-        <v>6865</v>
       </c>
       <c r="G737" s="3">
         <v>2</v>
@@ -44164,13 +44166,13 @@
         <v>737</v>
       </c>
       <c r="B738" s="2" t="s">
+        <v>6312</v>
+      </c>
+      <c r="C738" s="2" t="s">
+        <v>6313</v>
+      </c>
+      <c r="D738" s="2" t="s">
         <v>6314</v>
-      </c>
-      <c r="C738" s="2" t="s">
-        <v>6315</v>
-      </c>
-      <c r="D738" s="2" t="s">
-        <v>6316</v>
       </c>
       <c r="E738" s="2" t="s">
         <v>3419</v>
@@ -44222,7 +44224,7 @@
         <v>739</v>
       </c>
       <c r="B740" s="2" t="s">
-        <v>6536</v>
+        <v>6534</v>
       </c>
       <c r="C740" s="6">
         <v>0.05</v>
@@ -44283,13 +44285,13 @@
         <v>3430</v>
       </c>
       <c r="C742" s="2" t="s">
-        <v>6134</v>
+        <v>6132</v>
       </c>
       <c r="D742" s="2" t="s">
         <v>3431</v>
       </c>
       <c r="E742" s="2" t="s">
-        <v>6135</v>
+        <v>6133</v>
       </c>
       <c r="F742" s="2" t="s">
         <v>51</v>
@@ -44568,19 +44570,19 @@
         <v>751</v>
       </c>
       <c r="B752" s="2" t="s">
+        <v>6672</v>
+      </c>
+      <c r="C752" s="2" t="s">
+        <v>6673</v>
+      </c>
+      <c r="D752" s="2" t="s">
         <v>6674</v>
-      </c>
-      <c r="C752" s="2" t="s">
-        <v>6675</v>
-      </c>
-      <c r="D752" s="2" t="s">
-        <v>6676</v>
       </c>
       <c r="E752" s="2" t="s">
         <v>3462</v>
       </c>
       <c r="F752" s="2" t="s">
-        <v>6677</v>
+        <v>6675</v>
       </c>
       <c r="G752" s="3">
         <v>2</v>
@@ -44667,7 +44669,7 @@
         <v>938</v>
       </c>
       <c r="F755" s="2" t="s">
-        <v>6800</v>
+        <v>6798</v>
       </c>
       <c r="G755" s="3">
         <v>2</v>
@@ -44684,25 +44686,25 @@
         <v>755</v>
       </c>
       <c r="B756" s="2" t="s">
+        <v>6153</v>
+      </c>
+      <c r="C756" s="2" t="s">
+        <v>6154</v>
+      </c>
+      <c r="D756" s="2" t="s">
         <v>6155</v>
       </c>
-      <c r="C756" s="2" t="s">
+      <c r="E756" s="2" t="s">
         <v>6156</v>
       </c>
-      <c r="D756" s="2" t="s">
+      <c r="F756" s="2" t="s">
         <v>6157</v>
-      </c>
-      <c r="E756" s="2" t="s">
-        <v>6158</v>
-      </c>
-      <c r="F756" s="2" t="s">
-        <v>6159</v>
       </c>
       <c r="G756" s="3">
         <v>2</v>
       </c>
       <c r="H756" s="2" t="s">
-        <v>6160</v>
+        <v>6158</v>
       </c>
       <c r="I756" s="2" t="s">
         <v>756</v>
@@ -44890,13 +44892,13 @@
         <v>3507</v>
       </c>
       <c r="C763" s="2" t="s">
-        <v>6764</v>
+        <v>6762</v>
       </c>
       <c r="D763" s="2" t="s">
         <v>3508</v>
       </c>
       <c r="E763" s="2" t="s">
-        <v>6765</v>
+        <v>6763</v>
       </c>
       <c r="F763" s="2" t="s">
         <v>3509</v>
@@ -45003,19 +45005,19 @@
         <v>766</v>
       </c>
       <c r="B767" s="2" t="s">
-        <v>6485</v>
+        <v>6483</v>
       </c>
       <c r="C767" s="2" t="s">
         <v>97</v>
       </c>
       <c r="D767" s="2" t="s">
-        <v>6486</v>
+        <v>6484</v>
       </c>
       <c r="E767" s="2" t="s">
         <v>3525</v>
       </c>
       <c r="F767" s="2" t="s">
-        <v>6487</v>
+        <v>6485</v>
       </c>
       <c r="G767" s="3">
         <v>3</v>
@@ -45088,7 +45090,7 @@
         <v>769</v>
       </c>
       <c r="B770" s="2" t="s">
-        <v>6733</v>
+        <v>6731</v>
       </c>
       <c r="C770" s="2" t="s">
         <v>3537</v>
@@ -45175,7 +45177,7 @@
         <v>772</v>
       </c>
       <c r="B773" s="2" t="s">
-        <v>6635</v>
+        <v>6633</v>
       </c>
       <c r="C773" s="2" t="s">
         <v>478</v>
@@ -45187,7 +45189,7 @@
         <v>480</v>
       </c>
       <c r="F773" s="4" t="s">
-        <v>6636</v>
+        <v>6634</v>
       </c>
       <c r="G773" s="3">
         <v>2</v>
@@ -45303,7 +45305,7 @@
         <v>481</v>
       </c>
       <c r="F777" s="4" t="s">
-        <v>6850</v>
+        <v>6848</v>
       </c>
       <c r="G777" s="3">
         <v>4</v>
@@ -45320,7 +45322,7 @@
         <v>777</v>
       </c>
       <c r="B778" s="2" t="s">
-        <v>7063</v>
+        <v>7061</v>
       </c>
       <c r="C778" s="2" t="s">
         <v>3565</v>
@@ -45349,10 +45351,10 @@
         <v>778</v>
       </c>
       <c r="B779" s="2" t="s">
-        <v>7064</v>
+        <v>7062</v>
       </c>
       <c r="C779" s="2" t="s">
-        <v>7062</v>
+        <v>7060</v>
       </c>
       <c r="D779" s="2" t="s">
         <v>1060</v>
@@ -45361,7 +45363,7 @@
         <v>1061</v>
       </c>
       <c r="F779" s="2" t="s">
-        <v>7040</v>
+        <v>7038</v>
       </c>
       <c r="G779" s="3">
         <v>3</v>
@@ -45523,19 +45525,19 @@
         <v>784</v>
       </c>
       <c r="B785" s="2" t="s">
+        <v>6668</v>
+      </c>
+      <c r="C785" s="2" t="s">
+        <v>6669</v>
+      </c>
+      <c r="D785" s="2" t="s">
         <v>6670</v>
-      </c>
-      <c r="C785" s="2" t="s">
-        <v>6671</v>
-      </c>
-      <c r="D785" s="2" t="s">
-        <v>6672</v>
       </c>
       <c r="E785" s="2" t="s">
         <v>3592</v>
       </c>
       <c r="F785" s="2" t="s">
-        <v>6673</v>
+        <v>6671</v>
       </c>
       <c r="G785" s="3">
         <v>1</v>
@@ -45697,13 +45699,13 @@
         <v>790</v>
       </c>
       <c r="B791" s="2" t="s">
-        <v>6500</v>
+        <v>6498</v>
       </c>
       <c r="C791" s="2" t="s">
+        <v>6497</v>
+      </c>
+      <c r="D791" s="2" t="s">
         <v>6499</v>
-      </c>
-      <c r="D791" s="2" t="s">
-        <v>6501</v>
       </c>
       <c r="E791" s="2" t="s">
         <v>3359</v>
@@ -45851,7 +45853,7 @@
         <v>3643</v>
       </c>
       <c r="E796" s="2" t="s">
-        <v>6947</v>
+        <v>6945</v>
       </c>
       <c r="F796" s="2" t="s">
         <v>51</v>
@@ -46045,19 +46047,19 @@
         <v>802</v>
       </c>
       <c r="B803" s="2" t="s">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="C803" s="2" t="s">
         <v>3675</v>
       </c>
       <c r="D803" s="2" t="s">
-        <v>6459</v>
+        <v>6457</v>
       </c>
       <c r="E803" s="2" t="s">
         <v>3676</v>
       </c>
       <c r="F803" s="2" t="s">
-        <v>6460</v>
+        <v>6458</v>
       </c>
       <c r="G803" s="3">
         <v>3</v>
@@ -46103,7 +46105,7 @@
         <v>804</v>
       </c>
       <c r="B805" s="2" t="s">
-        <v>6292</v>
+        <v>6290</v>
       </c>
       <c r="C805" s="2" t="s">
         <v>3684</v>
@@ -46335,13 +46337,13 @@
         <v>812</v>
       </c>
       <c r="B813" s="2" t="s">
-        <v>6223</v>
+        <v>6221</v>
       </c>
       <c r="C813" s="2" t="s">
         <v>3726</v>
       </c>
       <c r="D813" s="2" t="s">
-        <v>6224</v>
+        <v>6222</v>
       </c>
       <c r="E813" s="2" t="s">
         <v>3727</v>
@@ -46364,7 +46366,7 @@
         <v>813</v>
       </c>
       <c r="B814" s="2" t="s">
-        <v>6550</v>
+        <v>6548</v>
       </c>
       <c r="C814" s="2" t="s">
         <v>3730</v>
@@ -46376,7 +46378,7 @@
         <v>3732</v>
       </c>
       <c r="F814" s="2" t="s">
-        <v>6551</v>
+        <v>6549</v>
       </c>
       <c r="G814" s="3">
         <v>1</v>
@@ -46393,7 +46395,7 @@
         <v>814</v>
       </c>
       <c r="B815" s="2" t="s">
-        <v>6221</v>
+        <v>6219</v>
       </c>
       <c r="C815" s="2" t="s">
         <v>3734</v>
@@ -46405,7 +46407,7 @@
         <v>3736</v>
       </c>
       <c r="F815" s="2" t="s">
-        <v>6222</v>
+        <v>6220</v>
       </c>
       <c r="G815" s="3">
         <v>1</v>
@@ -46483,16 +46485,16 @@
         <v>3748</v>
       </c>
       <c r="C818" s="2" t="s">
-        <v>6965</v>
+        <v>6963</v>
       </c>
       <c r="D818" s="2" t="s">
         <v>3525</v>
       </c>
       <c r="E818" s="2" t="s">
-        <v>6966</v>
+        <v>6964</v>
       </c>
       <c r="F818" s="2" t="s">
-        <v>6967</v>
+        <v>6965</v>
       </c>
       <c r="G818" s="3">
         <v>3</v>
@@ -46544,13 +46546,13 @@
         <v>3754</v>
       </c>
       <c r="D820" s="2" t="s">
-        <v>6330</v>
+        <v>6328</v>
       </c>
       <c r="E820" s="2" t="s">
         <v>3755</v>
       </c>
       <c r="F820" s="2" t="s">
-        <v>6331</v>
+        <v>6329</v>
       </c>
       <c r="G820" s="3">
         <v>4</v>
@@ -46625,7 +46627,7 @@
         <v>822</v>
       </c>
       <c r="B823" s="2" t="s">
-        <v>6555</v>
+        <v>6553</v>
       </c>
       <c r="C823" s="2" t="s">
         <v>3768</v>
@@ -46634,10 +46636,10 @@
         <v>3769</v>
       </c>
       <c r="E823" s="2" t="s">
-        <v>6556</v>
+        <v>6554</v>
       </c>
       <c r="F823" s="2" t="s">
-        <v>6557</v>
+        <v>6555</v>
       </c>
       <c r="G823" s="3">
         <v>4</v>
@@ -46683,7 +46685,7 @@
         <v>824</v>
       </c>
       <c r="B825" s="2" t="s">
-        <v>6649</v>
+        <v>6647</v>
       </c>
       <c r="C825" s="2" t="s">
         <v>102</v>
@@ -46695,7 +46697,7 @@
         <v>3777</v>
       </c>
       <c r="F825" s="2" t="s">
-        <v>6650</v>
+        <v>6648</v>
       </c>
       <c r="G825" s="3">
         <v>3</v>
@@ -46744,16 +46746,16 @@
         <v>3784</v>
       </c>
       <c r="C827" s="2" t="s">
-        <v>6990</v>
+        <v>6988</v>
       </c>
       <c r="D827" s="2" t="s">
-        <v>6991</v>
+        <v>6989</v>
       </c>
       <c r="E827" s="2" t="s">
         <v>3582</v>
       </c>
       <c r="F827" s="2" t="s">
-        <v>6992</v>
+        <v>6990</v>
       </c>
       <c r="G827" s="3">
         <v>2</v>
@@ -46799,7 +46801,7 @@
         <v>828</v>
       </c>
       <c r="B829" s="2" t="s">
-        <v>6291</v>
+        <v>6289</v>
       </c>
       <c r="C829" s="2" t="s">
         <v>3792</v>
@@ -46831,16 +46833,16 @@
         <v>3797</v>
       </c>
       <c r="C830" s="2" t="s">
+        <v>6436</v>
+      </c>
+      <c r="D830" s="2" t="s">
+        <v>6435</v>
+      </c>
+      <c r="E830" s="2" t="s">
+        <v>6437</v>
+      </c>
+      <c r="F830" s="2" t="s">
         <v>6438</v>
-      </c>
-      <c r="D830" s="2" t="s">
-        <v>6437</v>
-      </c>
-      <c r="E830" s="2" t="s">
-        <v>6439</v>
-      </c>
-      <c r="F830" s="2" t="s">
-        <v>6440</v>
       </c>
       <c r="G830" s="3">
         <v>4</v>
@@ -46857,16 +46859,16 @@
         <v>830</v>
       </c>
       <c r="B831" s="2" t="s">
+        <v>6958</v>
+      </c>
+      <c r="C831" s="2" t="s">
+        <v>6959</v>
+      </c>
+      <c r="D831" s="2" t="s">
         <v>6960</v>
       </c>
-      <c r="C831" s="2" t="s">
+      <c r="E831" s="2" t="s">
         <v>6961</v>
-      </c>
-      <c r="D831" s="2" t="s">
-        <v>6962</v>
-      </c>
-      <c r="E831" s="2" t="s">
-        <v>6963</v>
       </c>
       <c r="F831" s="2" t="s">
         <v>3799</v>
@@ -46889,16 +46891,16 @@
         <v>3801</v>
       </c>
       <c r="C832" s="2" t="s">
+        <v>6255</v>
+      </c>
+      <c r="D832" s="2" t="s">
+        <v>6256</v>
+      </c>
+      <c r="E832" s="2" t="s">
         <v>6257</v>
       </c>
-      <c r="D832" s="2" t="s">
+      <c r="F832" s="2" t="s">
         <v>6258</v>
-      </c>
-      <c r="E832" s="2" t="s">
-        <v>6259</v>
-      </c>
-      <c r="F832" s="2" t="s">
-        <v>6260</v>
       </c>
       <c r="G832" s="3">
         <v>4</v>
@@ -46927,7 +46929,7 @@
         <v>3806</v>
       </c>
       <c r="F833" s="2" t="s">
-        <v>6975</v>
+        <v>6973</v>
       </c>
       <c r="G833" s="3">
         <v>2</v>
@@ -47060,7 +47062,7 @@
         <v>837</v>
       </c>
       <c r="B838" s="2" t="s">
-        <v>6692</v>
+        <v>6690</v>
       </c>
       <c r="C838" s="2" t="s">
         <v>3826</v>
@@ -47072,7 +47074,7 @@
         <v>3828</v>
       </c>
       <c r="F838" s="2" t="s">
-        <v>6693</v>
+        <v>6691</v>
       </c>
       <c r="G838" s="3">
         <v>4</v>
@@ -47147,13 +47149,13 @@
         <v>840</v>
       </c>
       <c r="B841" s="2" t="s">
+        <v>6898</v>
+      </c>
+      <c r="C841" s="2" t="s">
+        <v>6899</v>
+      </c>
+      <c r="D841" s="2" t="s">
         <v>6900</v>
-      </c>
-      <c r="C841" s="2" t="s">
-        <v>6901</v>
-      </c>
-      <c r="D841" s="2" t="s">
-        <v>6902</v>
       </c>
       <c r="E841" s="2" t="s">
         <v>3842</v>
@@ -47176,19 +47178,19 @@
         <v>841</v>
       </c>
       <c r="B842" s="2" t="s">
-        <v>6953</v>
+        <v>6951</v>
       </c>
       <c r="C842" s="2" t="s">
         <v>3845</v>
       </c>
       <c r="D842" s="2" t="s">
+        <v>6952</v>
+      </c>
+      <c r="E842" s="2" t="s">
+        <v>6953</v>
+      </c>
+      <c r="F842" s="2" t="s">
         <v>6954</v>
-      </c>
-      <c r="E842" s="2" t="s">
-        <v>6955</v>
-      </c>
-      <c r="F842" s="2" t="s">
-        <v>6956</v>
       </c>
       <c r="G842" s="3">
         <v>2</v>
@@ -47205,7 +47207,7 @@
         <v>842</v>
       </c>
       <c r="B843" s="7" t="s">
-        <v>6888</v>
+        <v>6886</v>
       </c>
       <c r="C843" s="2" t="s">
         <v>3845</v>
@@ -47214,16 +47216,16 @@
         <v>3847</v>
       </c>
       <c r="E843" s="2" t="s">
+        <v>6887</v>
+      </c>
+      <c r="F843" s="2" t="s">
         <v>6889</v>
-      </c>
-      <c r="F843" s="2" t="s">
-        <v>6891</v>
       </c>
       <c r="G843" s="3">
         <v>3</v>
       </c>
       <c r="H843" s="2" t="s">
-        <v>6890</v>
+        <v>6888</v>
       </c>
       <c r="I843" s="2" t="s">
         <v>15</v>
@@ -47493,7 +47495,7 @@
         <v>852</v>
       </c>
       <c r="B853" s="2" t="s">
-        <v>6694</v>
+        <v>6692</v>
       </c>
       <c r="C853" s="2" t="s">
         <v>726</v>
@@ -47502,7 +47504,7 @@
         <v>727</v>
       </c>
       <c r="E853" s="2" t="s">
-        <v>6695</v>
+        <v>6693</v>
       </c>
       <c r="F853" s="2" t="s">
         <v>3888</v>
@@ -47612,7 +47614,7 @@
         <v>3906</v>
       </c>
       <c r="C857" s="2" t="s">
-        <v>7008</v>
+        <v>7006</v>
       </c>
       <c r="D857" s="2" t="s">
         <v>3907</v>
@@ -47621,7 +47623,7 @@
         <v>3908</v>
       </c>
       <c r="F857" s="2" t="s">
-        <v>7007</v>
+        <v>7005</v>
       </c>
       <c r="G857" s="3">
         <v>4</v>
@@ -47699,7 +47701,7 @@
         <v>3920</v>
       </c>
       <c r="C860" s="2" t="s">
-        <v>6611</v>
+        <v>6609</v>
       </c>
       <c r="D860" s="2" t="s">
         <v>3921</v>
@@ -47841,7 +47843,7 @@
         <v>864</v>
       </c>
       <c r="B865" s="2" t="s">
-        <v>6182</v>
+        <v>6180</v>
       </c>
       <c r="C865" s="2" t="s">
         <v>3947</v>
@@ -47850,10 +47852,10 @@
         <v>2841</v>
       </c>
       <c r="E865" s="2" t="s">
-        <v>6180</v>
+        <v>6178</v>
       </c>
       <c r="F865" s="2" t="s">
-        <v>6181</v>
+        <v>6179</v>
       </c>
       <c r="G865" s="3">
         <v>4</v>
@@ -47870,19 +47872,19 @@
         <v>865</v>
       </c>
       <c r="B866" s="2" t="s">
+        <v>6185</v>
+      </c>
+      <c r="C866" s="2" t="s">
+        <v>6186</v>
+      </c>
+      <c r="D866" s="4" t="s">
         <v>6187</v>
       </c>
-      <c r="C866" s="2" t="s">
+      <c r="E866" s="2" t="s">
         <v>6188</v>
       </c>
-      <c r="D866" s="4" t="s">
+      <c r="F866" s="2" t="s">
         <v>6189</v>
-      </c>
-      <c r="E866" s="2" t="s">
-        <v>6190</v>
-      </c>
-      <c r="F866" s="2" t="s">
-        <v>6191</v>
       </c>
       <c r="G866" s="3">
         <v>3</v>
@@ -47986,7 +47988,7 @@
         <v>869</v>
       </c>
       <c r="B870" s="2" t="s">
-        <v>6393</v>
+        <v>6391</v>
       </c>
       <c r="C870" s="2" t="s">
         <v>3965</v>
@@ -47995,10 +47997,10 @@
         <v>3966</v>
       </c>
       <c r="E870" s="2" t="s">
-        <v>6395</v>
+        <v>6393</v>
       </c>
       <c r="F870" s="2" t="s">
-        <v>6394</v>
+        <v>6392</v>
       </c>
       <c r="G870" s="3">
         <v>4</v>
@@ -48024,10 +48026,10 @@
         <v>3971</v>
       </c>
       <c r="E871" s="2" t="s">
-        <v>7013</v>
+        <v>7011</v>
       </c>
       <c r="F871" s="2" t="s">
-        <v>7014</v>
+        <v>7012</v>
       </c>
       <c r="G871" s="3">
         <v>1</v>
@@ -48073,7 +48075,7 @@
         <v>872</v>
       </c>
       <c r="B873" s="2" t="s">
-        <v>6683</v>
+        <v>6681</v>
       </c>
       <c r="C873" s="2" t="s">
         <v>3706</v>
@@ -48102,7 +48104,7 @@
         <v>873</v>
       </c>
       <c r="B874" s="2" t="s">
-        <v>6553</v>
+        <v>6551</v>
       </c>
       <c r="C874" s="2" t="s">
         <v>910</v>
@@ -48114,7 +48116,7 @@
         <v>3984</v>
       </c>
       <c r="F874" s="2" t="s">
-        <v>6554</v>
+        <v>6552</v>
       </c>
       <c r="G874" s="3">
         <v>1</v>
@@ -48163,16 +48165,16 @@
         <v>3986</v>
       </c>
       <c r="C876" s="2" t="s">
-        <v>7022</v>
+        <v>7020</v>
       </c>
       <c r="D876" s="2" t="s">
-        <v>7023</v>
+        <v>7021</v>
       </c>
       <c r="E876" s="2" t="s">
         <v>3992</v>
       </c>
       <c r="F876" s="2" t="s">
-        <v>7024</v>
+        <v>7022</v>
       </c>
       <c r="G876" s="3">
         <v>4</v>
@@ -48306,7 +48308,7 @@
         <v>4016</v>
       </c>
       <c r="C881" s="2" t="s">
-        <v>6142</v>
+        <v>6140</v>
       </c>
       <c r="D881" s="2" t="s">
         <v>2841</v>
@@ -48315,7 +48317,7 @@
         <v>4017</v>
       </c>
       <c r="F881" s="2" t="s">
-        <v>6143</v>
+        <v>6141</v>
       </c>
       <c r="G881" s="3">
         <v>1</v>
@@ -48332,7 +48334,7 @@
         <v>881</v>
       </c>
       <c r="B882" s="2" t="s">
-        <v>6522</v>
+        <v>6520</v>
       </c>
       <c r="C882" s="2" t="s">
         <v>3827</v>
@@ -48344,7 +48346,7 @@
         <v>4019</v>
       </c>
       <c r="F882" s="2" t="s">
-        <v>6523</v>
+        <v>6521</v>
       </c>
       <c r="G882" s="3">
         <v>3</v>
@@ -48390,7 +48392,7 @@
         <v>883</v>
       </c>
       <c r="B884" s="2" t="s">
-        <v>6983</v>
+        <v>6981</v>
       </c>
       <c r="C884" s="2" t="s">
         <v>4027</v>
@@ -48448,7 +48450,7 @@
         <v>885</v>
       </c>
       <c r="B886" s="2" t="s">
-        <v>6498</v>
+        <v>6496</v>
       </c>
       <c r="C886" s="2" t="s">
         <v>4038</v>
@@ -48547,7 +48549,7 @@
         <v>4054</v>
       </c>
       <c r="F889" s="2" t="s">
-        <v>6763</v>
+        <v>6761</v>
       </c>
       <c r="G889" s="3">
         <v>3</v>
@@ -48651,19 +48653,19 @@
         <v>892</v>
       </c>
       <c r="B893" s="2" t="s">
+        <v>6396</v>
+      </c>
+      <c r="C893" s="2" t="s">
+        <v>6397</v>
+      </c>
+      <c r="D893" s="2" t="s">
         <v>6398</v>
-      </c>
-      <c r="C893" s="2" t="s">
-        <v>6399</v>
-      </c>
-      <c r="D893" s="2" t="s">
-        <v>6400</v>
       </c>
       <c r="E893" s="2" t="s">
         <v>4069</v>
       </c>
       <c r="F893" s="2" t="s">
-        <v>6401</v>
+        <v>6399</v>
       </c>
       <c r="G893" s="3">
         <v>2</v>
@@ -48744,7 +48746,7 @@
         <v>4084</v>
       </c>
       <c r="D896" s="2" t="s">
-        <v>6611</v>
+        <v>6609</v>
       </c>
       <c r="E896" s="2" t="s">
         <v>3921</v>
@@ -48767,16 +48769,16 @@
         <v>896</v>
       </c>
       <c r="B897" s="2" t="s">
-        <v>6148</v>
+        <v>6146</v>
       </c>
       <c r="C897" s="2" t="s">
         <v>3827</v>
       </c>
       <c r="D897" s="2" t="s">
-        <v>6149</v>
+        <v>6147</v>
       </c>
       <c r="E897" s="2" t="s">
-        <v>6150</v>
+        <v>6148</v>
       </c>
       <c r="F897" s="2" t="s">
         <v>3903</v>
@@ -48799,7 +48801,7 @@
         <v>4088</v>
       </c>
       <c r="C898" s="2" t="s">
-        <v>6488</v>
+        <v>6486</v>
       </c>
       <c r="D898" s="2" t="s">
         <v>4089</v>
@@ -48808,7 +48810,7 @@
         <v>4090</v>
       </c>
       <c r="F898" s="2" t="s">
-        <v>6489</v>
+        <v>6487</v>
       </c>
       <c r="G898" s="3">
         <v>1</v>
@@ -48968,7 +48970,7 @@
         <v>903</v>
       </c>
       <c r="B904" s="2" t="s">
-        <v>6804</v>
+        <v>6802</v>
       </c>
       <c r="C904" s="2" t="s">
         <v>4117</v>
@@ -48980,7 +48982,7 @@
         <v>4119</v>
       </c>
       <c r="F904" s="2" t="s">
-        <v>6805</v>
+        <v>6803</v>
       </c>
       <c r="G904" s="3">
         <v>4</v>
@@ -49084,19 +49086,19 @@
         <v>907</v>
       </c>
       <c r="B908" s="2" t="s">
-        <v>6505</v>
+        <v>6503</v>
       </c>
       <c r="C908" s="2" t="s">
         <v>4139</v>
       </c>
       <c r="D908" s="2" t="s">
-        <v>6506</v>
+        <v>6504</v>
       </c>
       <c r="E908" s="2" t="s">
         <v>3694</v>
       </c>
       <c r="F908" s="2" t="s">
-        <v>6507</v>
+        <v>6505</v>
       </c>
       <c r="G908" s="3">
         <v>3</v>
@@ -49258,19 +49260,19 @@
         <v>913</v>
       </c>
       <c r="B914" s="2" t="s">
-        <v>6293</v>
+        <v>6291</v>
       </c>
       <c r="C914" s="2" t="s">
-        <v>6294</v>
+        <v>6292</v>
       </c>
       <c r="D914" s="2" t="s">
         <v>4171</v>
       </c>
       <c r="E914" s="2" t="s">
-        <v>6295</v>
+        <v>6293</v>
       </c>
       <c r="F914" s="2" t="s">
-        <v>6296</v>
+        <v>6294</v>
       </c>
       <c r="G914" s="3">
         <v>3</v>
@@ -49542,7 +49544,7 @@
         <v>923</v>
       </c>
       <c r="B924" s="2" t="s">
-        <v>6147</v>
+        <v>6145</v>
       </c>
       <c r="C924" s="2" t="s">
         <v>2884</v>
@@ -49975,7 +49977,7 @@
         <v>938</v>
       </c>
       <c r="B939" s="2" t="s">
-        <v>6348</v>
+        <v>6346</v>
       </c>
       <c r="C939" s="2" t="s">
         <v>4292</v>
@@ -50033,7 +50035,7 @@
         <v>940</v>
       </c>
       <c r="B941" s="2" t="s">
-        <v>6984</v>
+        <v>6982</v>
       </c>
       <c r="C941" s="2" t="s">
         <v>4304</v>
@@ -50178,19 +50180,19 @@
         <v>945</v>
       </c>
       <c r="B946" s="2" t="s">
-        <v>6998</v>
+        <v>6996</v>
       </c>
       <c r="C946" s="2" t="s">
         <v>4332</v>
       </c>
       <c r="D946" s="2" t="s">
-        <v>7000</v>
+        <v>6998</v>
       </c>
       <c r="E946" s="2" t="s">
         <v>4333</v>
       </c>
       <c r="F946" s="2" t="s">
-        <v>6999</v>
+        <v>6997</v>
       </c>
       <c r="G946" s="3">
         <v>3</v>
@@ -50239,16 +50241,16 @@
         <v>4340</v>
       </c>
       <c r="C948" s="2" t="s">
-        <v>6642</v>
+        <v>6640</v>
       </c>
       <c r="D948" s="2" t="s">
         <v>4341</v>
       </c>
       <c r="E948" s="2" t="s">
-        <v>6643</v>
+        <v>6641</v>
       </c>
       <c r="F948" s="2" t="s">
-        <v>6644</v>
+        <v>6642</v>
       </c>
       <c r="G948" s="3">
         <v>3</v>
@@ -50391,7 +50393,7 @@
         <v>4358</v>
       </c>
       <c r="F953" s="2" t="s">
-        <v>6136</v>
+        <v>6134</v>
       </c>
       <c r="G953" s="3">
         <v>3</v>
@@ -50408,19 +50410,19 @@
         <v>953</v>
       </c>
       <c r="B954" s="2" t="s">
-        <v>6770</v>
+        <v>6768</v>
       </c>
       <c r="C954" s="2" t="s">
         <v>4356</v>
       </c>
       <c r="D954" s="2" t="s">
-        <v>6769</v>
+        <v>6767</v>
       </c>
       <c r="E954" s="2" t="s">
         <v>4358</v>
       </c>
       <c r="F954" s="2" t="s">
-        <v>6771</v>
+        <v>6769</v>
       </c>
       <c r="G954" s="3">
         <v>4</v>
@@ -50440,16 +50442,16 @@
         <v>4364</v>
       </c>
       <c r="C955" s="2" t="s">
+        <v>6770</v>
+      </c>
+      <c r="D955" s="2" t="s">
+        <v>6771</v>
+      </c>
+      <c r="E955" s="2" t="s">
         <v>6772</v>
       </c>
-      <c r="D955" s="2" t="s">
+      <c r="F955" s="2" t="s">
         <v>6773</v>
-      </c>
-      <c r="E955" s="2" t="s">
-        <v>6774</v>
-      </c>
-      <c r="F955" s="2" t="s">
-        <v>6775</v>
       </c>
       <c r="G955" s="3">
         <v>3</v>
@@ -50466,19 +50468,19 @@
         <v>955</v>
       </c>
       <c r="B956" s="2" t="s">
+        <v>6774</v>
+      </c>
+      <c r="C956" s="2" t="s">
+        <v>6775</v>
+      </c>
+      <c r="D956" s="2" t="s">
         <v>6776</v>
       </c>
-      <c r="C956" s="2" t="s">
+      <c r="E956" s="2" t="s">
         <v>6777</v>
       </c>
-      <c r="D956" s="2" t="s">
+      <c r="F956" s="2" t="s">
         <v>6778</v>
-      </c>
-      <c r="E956" s="2" t="s">
-        <v>6779</v>
-      </c>
-      <c r="F956" s="2" t="s">
-        <v>6780</v>
       </c>
       <c r="G956" s="3">
         <v>1</v>
@@ -50582,7 +50584,7 @@
         <v>959</v>
       </c>
       <c r="B960" s="2" t="s">
-        <v>6787</v>
+        <v>6785</v>
       </c>
       <c r="C960" s="2" t="s">
         <v>4381</v>
@@ -50614,13 +50616,13 @@
         <v>4386</v>
       </c>
       <c r="C961" s="2" t="s">
+        <v>6423</v>
+      </c>
+      <c r="D961" s="2" t="s">
+        <v>6424</v>
+      </c>
+      <c r="E961" s="2" t="s">
         <v>6425</v>
-      </c>
-      <c r="D961" s="2" t="s">
-        <v>6426</v>
-      </c>
-      <c r="E961" s="2" t="s">
-        <v>6427</v>
       </c>
       <c r="F961" s="2" t="s">
         <v>4387</v>
@@ -51191,19 +51193,19 @@
         <v>980</v>
       </c>
       <c r="B981" s="2" t="s">
+        <v>6204</v>
+      </c>
+      <c r="C981" s="2" t="s">
         <v>6206</v>
       </c>
-      <c r="C981" s="2" t="s">
-        <v>6208</v>
-      </c>
       <c r="D981" s="2" t="s">
-        <v>6209</v>
+        <v>6207</v>
       </c>
       <c r="E981" s="2" t="s">
         <v>4490</v>
       </c>
       <c r="F981" s="2" t="s">
-        <v>6207</v>
+        <v>6205</v>
       </c>
       <c r="G981" s="3">
         <v>2</v>
@@ -51232,7 +51234,7 @@
         <v>3085</v>
       </c>
       <c r="F982" s="2" t="s">
-        <v>6840</v>
+        <v>6838</v>
       </c>
       <c r="G982" s="3">
         <v>2</v>
@@ -51423,19 +51425,19 @@
         <v>988</v>
       </c>
       <c r="B989" s="2" t="s">
+        <v>6165</v>
+      </c>
+      <c r="C989" s="2" t="s">
+        <v>6166</v>
+      </c>
+      <c r="D989" s="2" t="s">
         <v>6167</v>
       </c>
-      <c r="C989" s="2" t="s">
+      <c r="E989" s="2" t="s">
         <v>6168</v>
       </c>
-      <c r="D989" s="2" t="s">
+      <c r="F989" s="2" t="s">
         <v>6169</v>
-      </c>
-      <c r="E989" s="2" t="s">
-        <v>6170</v>
-      </c>
-      <c r="F989" s="2" t="s">
-        <v>6171</v>
       </c>
       <c r="G989" s="3">
         <v>3</v>
@@ -51452,19 +51454,19 @@
         <v>989</v>
       </c>
       <c r="B990" s="2" t="s">
-        <v>6978</v>
+        <v>6976</v>
       </c>
       <c r="C990" s="2" t="s">
         <v>4524</v>
       </c>
       <c r="D990" s="2" t="s">
-        <v>6979</v>
+        <v>6977</v>
       </c>
       <c r="E990" s="2" t="s">
         <v>1361</v>
       </c>
       <c r="F990" s="2" t="s">
-        <v>6980</v>
+        <v>6978</v>
       </c>
       <c r="G990" s="3">
         <v>4</v>
@@ -51484,16 +51486,16 @@
         <v>4526</v>
       </c>
       <c r="C991" s="2" t="s">
-        <v>6628</v>
+        <v>6626</v>
       </c>
       <c r="D991" s="2" t="s">
         <v>4527</v>
       </c>
       <c r="E991" s="2" t="s">
-        <v>6626</v>
+        <v>6624</v>
       </c>
       <c r="F991" s="2" t="s">
-        <v>6627</v>
+        <v>6625</v>
       </c>
       <c r="G991" s="3">
         <v>2</v>
@@ -51510,10 +51512,10 @@
         <v>991</v>
       </c>
       <c r="B992" s="2" t="s">
-        <v>6496</v>
+        <v>6494</v>
       </c>
       <c r="C992" s="2" t="s">
-        <v>6495</v>
+        <v>6493</v>
       </c>
       <c r="D992" s="2" t="s">
         <v>4529</v>
@@ -51655,19 +51657,19 @@
         <v>996</v>
       </c>
       <c r="B997" s="2" t="s">
-        <v>6338</v>
+        <v>6336</v>
       </c>
       <c r="C997" s="2" t="s">
         <v>3685</v>
       </c>
       <c r="D997" s="2" t="s">
-        <v>6339</v>
+        <v>6337</v>
       </c>
       <c r="E997" s="2" t="s">
         <v>4545</v>
       </c>
       <c r="F997" s="2" t="s">
-        <v>6340</v>
+        <v>6338</v>
       </c>
       <c r="G997" s="3">
         <v>3</v>
@@ -51858,19 +51860,19 @@
         <v>1003</v>
       </c>
       <c r="B1004" s="2" t="s">
-        <v>6678</v>
+        <v>6676</v>
       </c>
       <c r="C1004" s="2" t="s">
-        <v>6679</v>
+        <v>6677</v>
       </c>
       <c r="D1004" s="2" t="s">
         <v>4567</v>
       </c>
       <c r="E1004" s="2" t="s">
+        <v>6678</v>
+      </c>
+      <c r="F1004" s="2" t="s">
         <v>6680</v>
-      </c>
-      <c r="F1004" s="2" t="s">
-        <v>6682</v>
       </c>
       <c r="G1004" s="3">
         <v>1</v>
@@ -51887,7 +51889,7 @@
         <v>1004</v>
       </c>
       <c r="B1005" s="2" t="s">
-        <v>6681</v>
+        <v>6679</v>
       </c>
       <c r="C1005" s="2" t="s">
         <v>4569</v>
@@ -52059,7 +52061,7 @@
         <v>1010</v>
       </c>
       <c r="B1011" s="2" t="s">
-        <v>6632</v>
+        <v>6630</v>
       </c>
       <c r="C1011" s="2" t="s">
         <v>4588</v>
@@ -52120,16 +52122,16 @@
         <v>4599</v>
       </c>
       <c r="C1013" s="2" t="s">
-        <v>6546</v>
+        <v>6544</v>
       </c>
       <c r="D1013" s="2" t="s">
+        <v>6543</v>
+      </c>
+      <c r="E1013" s="2" t="s">
         <v>6545</v>
       </c>
-      <c r="E1013" s="2" t="s">
+      <c r="F1013" s="2" t="s">
         <v>6547</v>
-      </c>
-      <c r="F1013" s="2" t="s">
-        <v>6549</v>
       </c>
       <c r="G1013" s="3">
         <v>2</v>
@@ -52146,7 +52148,7 @@
         <v>1013</v>
       </c>
       <c r="B1014" s="2" t="s">
-        <v>6548</v>
+        <v>6546</v>
       </c>
       <c r="C1014" s="2" t="s">
         <v>4600</v>
@@ -52175,10 +52177,10 @@
         <v>1014</v>
       </c>
       <c r="B1015" s="2" t="s">
-        <v>7030</v>
+        <v>7028</v>
       </c>
       <c r="C1015" s="2" t="s">
-        <v>7031</v>
+        <v>7029</v>
       </c>
       <c r="D1015" s="2" t="s">
         <v>4606</v>
@@ -52187,7 +52189,7 @@
         <v>4607</v>
       </c>
       <c r="F1015" s="2" t="s">
-        <v>7032</v>
+        <v>7030</v>
       </c>
       <c r="G1015" s="3">
         <v>1</v>
@@ -52207,16 +52209,16 @@
         <v>4609</v>
       </c>
       <c r="C1016" s="2" t="s">
-        <v>6297</v>
+        <v>6295</v>
       </c>
       <c r="D1016" s="2" t="s">
-        <v>6298</v>
+        <v>6296</v>
       </c>
       <c r="E1016" s="2" t="s">
         <v>4610</v>
       </c>
       <c r="F1016" s="2" t="s">
-        <v>6299</v>
+        <v>6297</v>
       </c>
       <c r="G1016" s="3">
         <v>1</v>
@@ -52233,7 +52235,7 @@
         <v>1016</v>
       </c>
       <c r="B1017" s="2" t="s">
-        <v>6300</v>
+        <v>6298</v>
       </c>
       <c r="C1017" s="2" t="s">
         <v>4612</v>
@@ -52262,10 +52264,10 @@
         <v>1017</v>
       </c>
       <c r="B1018" s="2" t="s">
-        <v>6542</v>
+        <v>6540</v>
       </c>
       <c r="C1018" s="2" t="s">
-        <v>6543</v>
+        <v>6541</v>
       </c>
       <c r="D1018" s="2" t="s">
         <v>4617</v>
@@ -52274,7 +52276,7 @@
         <v>4618</v>
       </c>
       <c r="F1018" s="2" t="s">
-        <v>6544</v>
+        <v>6542</v>
       </c>
       <c r="G1018" s="3">
         <v>4</v>
@@ -52291,7 +52293,7 @@
         <v>1018</v>
       </c>
       <c r="B1019" s="2" t="s">
-        <v>6861</v>
+        <v>6859</v>
       </c>
       <c r="C1019" s="2" t="s">
         <v>1024</v>
@@ -52349,7 +52351,7 @@
         <v>1020</v>
       </c>
       <c r="B1021" s="2" t="s">
-        <v>6997</v>
+        <v>6995</v>
       </c>
       <c r="C1021" s="2" t="s">
         <v>4628</v>
@@ -52468,16 +52470,16 @@
         <v>4642</v>
       </c>
       <c r="C1025" s="2" t="s">
-        <v>7047</v>
+        <v>7045</v>
       </c>
       <c r="D1025" s="2" t="s">
-        <v>7048</v>
+        <v>7046</v>
       </c>
       <c r="E1025" s="2" t="s">
         <v>4643</v>
       </c>
       <c r="F1025" s="2" t="s">
-        <v>7049</v>
+        <v>7047</v>
       </c>
       <c r="G1025" s="3">
         <v>2</v>
@@ -52494,7 +52496,7 @@
         <v>1025</v>
       </c>
       <c r="B1026" s="2" t="s">
-        <v>6210</v>
+        <v>6208</v>
       </c>
       <c r="C1026" s="2" t="s">
         <v>4645</v>
@@ -52503,10 +52505,10 @@
         <v>920</v>
       </c>
       <c r="E1026" s="2" t="s">
-        <v>6211</v>
+        <v>6209</v>
       </c>
       <c r="F1026" s="2" t="s">
-        <v>6212</v>
+        <v>6210</v>
       </c>
       <c r="G1026" s="3">
         <v>1</v>
@@ -52558,7 +52560,7 @@
         <v>4654</v>
       </c>
       <c r="D1028" s="2" t="s">
-        <v>6612</v>
+        <v>6610</v>
       </c>
       <c r="E1028" s="2" t="s">
         <v>4655</v>
@@ -52842,7 +52844,7 @@
         <v>1037</v>
       </c>
       <c r="B1038" s="2" t="s">
-        <v>6490</v>
+        <v>6488</v>
       </c>
       <c r="C1038" s="2" t="s">
         <v>849</v>
@@ -52871,7 +52873,7 @@
         <v>1038</v>
       </c>
       <c r="B1039" s="2" t="s">
-        <v>6303</v>
+        <v>6301</v>
       </c>
       <c r="C1039" s="2" t="s">
         <v>4709</v>
@@ -52880,10 +52882,10 @@
         <v>4710</v>
       </c>
       <c r="E1039" s="2" t="s">
-        <v>6301</v>
+        <v>6299</v>
       </c>
       <c r="F1039" s="2" t="s">
-        <v>6302</v>
+        <v>6300</v>
       </c>
       <c r="G1039" s="3">
         <v>2</v>
@@ -52900,19 +52902,19 @@
         <v>1039</v>
       </c>
       <c r="B1040" s="2" t="s">
+        <v>6159</v>
+      </c>
+      <c r="C1040" s="2" t="s">
+        <v>6160</v>
+      </c>
+      <c r="D1040" s="2" t="s">
         <v>6161</v>
       </c>
-      <c r="C1040" s="2" t="s">
+      <c r="E1040" s="2" t="s">
         <v>6162</v>
       </c>
-      <c r="D1040" s="2" t="s">
+      <c r="F1040" s="2" t="s">
         <v>6163</v>
-      </c>
-      <c r="E1040" s="2" t="s">
-        <v>6164</v>
-      </c>
-      <c r="F1040" s="2" t="s">
-        <v>6165</v>
       </c>
       <c r="G1040" s="3">
         <v>4</v>
@@ -53141,7 +53143,7 @@
         <v>4756</v>
       </c>
       <c r="E1048" s="2" t="s">
-        <v>6648</v>
+        <v>6646</v>
       </c>
       <c r="F1048" s="2" t="s">
         <v>4757</v>
@@ -53190,7 +53192,7 @@
         <v>1049</v>
       </c>
       <c r="B1050" s="2" t="s">
-        <v>6396</v>
+        <v>6394</v>
       </c>
       <c r="C1050" s="2" t="s">
         <v>1446</v>
@@ -53202,7 +53204,7 @@
         <v>4765</v>
       </c>
       <c r="F1050" s="2" t="s">
-        <v>6397</v>
+        <v>6395</v>
       </c>
       <c r="G1050" s="3">
         <v>3</v>
@@ -53219,7 +53221,7 @@
         <v>1050</v>
       </c>
       <c r="B1051" s="2" t="s">
-        <v>6528</v>
+        <v>6526</v>
       </c>
       <c r="C1051" s="2" t="s">
         <v>4767</v>
@@ -53231,7 +53233,7 @@
         <v>4769</v>
       </c>
       <c r="F1051" s="2" t="s">
-        <v>6527</v>
+        <v>6525</v>
       </c>
       <c r="G1051" s="3">
         <v>1</v>
@@ -53306,19 +53308,19 @@
         <v>1053</v>
       </c>
       <c r="B1054" s="2" t="s">
-        <v>6852</v>
+        <v>6850</v>
       </c>
       <c r="C1054" s="2" t="s">
         <v>1689</v>
       </c>
       <c r="D1054" s="2" t="s">
-        <v>6851</v>
+        <v>6849</v>
       </c>
       <c r="E1054" s="2" t="s">
         <v>4780</v>
       </c>
       <c r="F1054" s="2" t="s">
-        <v>6853</v>
+        <v>6851</v>
       </c>
       <c r="G1054" s="3">
         <v>4</v>
@@ -53335,19 +53337,19 @@
         <v>1054</v>
       </c>
       <c r="B1055" s="2" t="s">
-        <v>6854</v>
+        <v>6852</v>
       </c>
       <c r="C1055" s="2" t="s">
+        <v>7041</v>
+      </c>
+      <c r="D1055" s="2" t="s">
+        <v>7042</v>
+      </c>
+      <c r="E1055" s="2" t="s">
         <v>7043</v>
       </c>
-      <c r="D1055" s="2" t="s">
+      <c r="F1055" s="2" t="s">
         <v>7044</v>
-      </c>
-      <c r="E1055" s="2" t="s">
-        <v>7045</v>
-      </c>
-      <c r="F1055" s="2" t="s">
-        <v>7046</v>
       </c>
       <c r="G1055" s="3">
         <v>2</v>
@@ -53364,19 +53366,19 @@
         <v>1055</v>
       </c>
       <c r="B1056" s="2" t="s">
-        <v>6871</v>
+        <v>6869</v>
       </c>
       <c r="C1056" s="2" t="s">
         <v>4784</v>
       </c>
       <c r="D1056" s="2" t="s">
+        <v>6870</v>
+      </c>
+      <c r="E1056" s="2" t="s">
+        <v>6871</v>
+      </c>
+      <c r="F1056" s="2" t="s">
         <v>6872</v>
-      </c>
-      <c r="E1056" s="2" t="s">
-        <v>6873</v>
-      </c>
-      <c r="F1056" s="2" t="s">
-        <v>6874</v>
       </c>
       <c r="G1056" s="3">
         <v>2</v>
@@ -53393,7 +53395,7 @@
         <v>1056</v>
       </c>
       <c r="B1057" s="2" t="s">
-        <v>6858</v>
+        <v>6856</v>
       </c>
       <c r="C1057" s="2" t="s">
         <v>4786</v>
@@ -53405,7 +53407,7 @@
         <v>4788</v>
       </c>
       <c r="F1057" s="2" t="s">
-        <v>6859</v>
+        <v>6857</v>
       </c>
       <c r="G1057" s="3">
         <v>2</v>
@@ -53422,19 +53424,19 @@
         <v>1057</v>
       </c>
       <c r="B1058" s="2" t="s">
-        <v>6734</v>
+        <v>6732</v>
       </c>
       <c r="C1058" s="2" t="s">
-        <v>6735</v>
+        <v>6733</v>
       </c>
       <c r="D1058" s="2" t="s">
         <v>4790</v>
       </c>
       <c r="E1058" s="2" t="s">
-        <v>6736</v>
+        <v>6734</v>
       </c>
       <c r="F1058" s="2" t="s">
-        <v>6737</v>
+        <v>6735</v>
       </c>
       <c r="G1058" s="3">
         <v>3</v>
@@ -53480,19 +53482,19 @@
         <v>1059</v>
       </c>
       <c r="B1060" s="2" t="s">
+        <v>6347</v>
+      </c>
+      <c r="C1060" s="2" t="s">
+        <v>6350</v>
+      </c>
+      <c r="D1060" s="2" t="s">
+        <v>6348</v>
+      </c>
+      <c r="E1060" s="2" t="s">
         <v>6349</v>
       </c>
-      <c r="C1060" s="2" t="s">
-        <v>6352</v>
-      </c>
-      <c r="D1060" s="2" t="s">
-        <v>6350</v>
-      </c>
-      <c r="E1060" s="2" t="s">
+      <c r="F1060" s="2" t="s">
         <v>6351</v>
-      </c>
-      <c r="F1060" s="2" t="s">
-        <v>6353</v>
       </c>
       <c r="G1060" s="3">
         <v>4</v>
@@ -53538,19 +53540,19 @@
         <v>1061</v>
       </c>
       <c r="B1062" s="2" t="s">
-        <v>6418</v>
+        <v>6416</v>
       </c>
       <c r="C1062" s="2" t="s">
         <v>4806</v>
       </c>
       <c r="D1062" s="2" t="s">
+        <v>6417</v>
+      </c>
+      <c r="E1062" s="2" t="s">
+        <v>6418</v>
+      </c>
+      <c r="F1062" s="2" t="s">
         <v>6419</v>
-      </c>
-      <c r="E1062" s="2" t="s">
-        <v>6420</v>
-      </c>
-      <c r="F1062" s="2" t="s">
-        <v>6421</v>
       </c>
       <c r="G1062" s="3">
         <v>1</v>
@@ -53579,7 +53581,7 @@
         <v>910</v>
       </c>
       <c r="F1063" s="2" t="s">
-        <v>6892</v>
+        <v>6890</v>
       </c>
       <c r="G1063" s="3">
         <v>3</v>
@@ -53596,7 +53598,7 @@
         <v>1063</v>
       </c>
       <c r="B1064" s="2" t="s">
-        <v>6766</v>
+        <v>6764</v>
       </c>
       <c r="C1064" s="2" t="s">
         <v>4812</v>
@@ -53605,10 +53607,10 @@
         <v>4813</v>
       </c>
       <c r="E1064" s="2" t="s">
-        <v>6767</v>
+        <v>6765</v>
       </c>
       <c r="F1064" s="2" t="s">
-        <v>6768</v>
+        <v>6766</v>
       </c>
       <c r="G1064" s="3">
         <v>1</v>
@@ -53631,13 +53633,13 @@
         <v>4816</v>
       </c>
       <c r="D1065" s="2" t="s">
-        <v>6451</v>
+        <v>6449</v>
       </c>
       <c r="E1065" s="2" t="s">
         <v>4817</v>
       </c>
       <c r="F1065" s="2" t="s">
-        <v>6452</v>
+        <v>6450</v>
       </c>
       <c r="G1065" s="3">
         <v>2</v>
@@ -53718,13 +53720,13 @@
         <v>848</v>
       </c>
       <c r="D1068" s="4" t="s">
+        <v>7016</v>
+      </c>
+      <c r="E1068" s="4" t="s">
+        <v>7017</v>
+      </c>
+      <c r="F1068" s="4" t="s">
         <v>7018</v>
-      </c>
-      <c r="E1068" s="4" t="s">
-        <v>7019</v>
-      </c>
-      <c r="F1068" s="4" t="s">
-        <v>7020</v>
       </c>
       <c r="G1068" s="3">
         <v>1</v>
@@ -53744,16 +53746,16 @@
         <v>4828</v>
       </c>
       <c r="C1069" s="2" t="s">
-        <v>6422</v>
+        <v>6420</v>
       </c>
       <c r="D1069" s="2" t="s">
         <v>4829</v>
       </c>
       <c r="E1069" s="2" t="s">
-        <v>6423</v>
+        <v>6421</v>
       </c>
       <c r="F1069" s="2" t="s">
-        <v>6424</v>
+        <v>6422</v>
       </c>
       <c r="G1069" s="3">
         <v>4</v>
@@ -53770,7 +53772,7 @@
         <v>1069</v>
       </c>
       <c r="B1070" s="2" t="s">
-        <v>6586</v>
+        <v>6584</v>
       </c>
       <c r="C1070" s="2" t="s">
         <v>726</v>
@@ -53782,7 +53784,7 @@
         <v>900</v>
       </c>
       <c r="F1070" s="2" t="s">
-        <v>6587</v>
+        <v>6585</v>
       </c>
       <c r="G1070" s="3">
         <v>4</v>
@@ -53886,7 +53888,7 @@
         <v>1073</v>
       </c>
       <c r="B1074" s="2" t="s">
-        <v>6789</v>
+        <v>6787</v>
       </c>
       <c r="C1074" s="2" t="s">
         <v>479</v>
@@ -53924,10 +53926,10 @@
         <v>4829</v>
       </c>
       <c r="E1075" s="2" t="s">
-        <v>6948</v>
+        <v>6946</v>
       </c>
       <c r="F1075" s="2" t="s">
-        <v>6949</v>
+        <v>6947</v>
       </c>
       <c r="G1075" s="3">
         <v>4</v>
@@ -54031,7 +54033,7 @@
         <v>1078</v>
       </c>
       <c r="B1079" s="2" t="s">
-        <v>6795</v>
+        <v>6793</v>
       </c>
       <c r="C1079" s="2" t="s">
         <v>848</v>
@@ -54118,19 +54120,19 @@
         <v>1081</v>
       </c>
       <c r="B1082" s="2" t="s">
-        <v>6828</v>
+        <v>6826</v>
       </c>
       <c r="C1082" s="2" t="s">
         <v>4878</v>
       </c>
       <c r="D1082" s="2" t="s">
+        <v>6827</v>
+      </c>
+      <c r="E1082" s="2" t="s">
+        <v>6828</v>
+      </c>
+      <c r="F1082" s="2" t="s">
         <v>6829</v>
-      </c>
-      <c r="E1082" s="2" t="s">
-        <v>6830</v>
-      </c>
-      <c r="F1082" s="2" t="s">
-        <v>6831</v>
       </c>
       <c r="G1082" s="3">
         <v>3</v>
@@ -54147,7 +54149,7 @@
         <v>1082</v>
       </c>
       <c r="B1083" s="2" t="s">
-        <v>6304</v>
+        <v>6302</v>
       </c>
       <c r="C1083" s="2" t="s">
         <v>4880</v>
@@ -54234,19 +54236,19 @@
         <v>1085</v>
       </c>
       <c r="B1086" s="2" t="s">
-        <v>6797</v>
+        <v>6795</v>
       </c>
       <c r="C1086" s="2" t="s">
         <v>4892</v>
       </c>
       <c r="D1086" s="2" t="s">
-        <v>6798</v>
+        <v>6796</v>
       </c>
       <c r="E1086" s="2" t="s">
         <v>4893</v>
       </c>
       <c r="F1086" s="2" t="s">
-        <v>6799</v>
+        <v>6797</v>
       </c>
       <c r="G1086" s="3">
         <v>1</v>
@@ -54292,10 +54294,10 @@
         <v>1087</v>
       </c>
       <c r="B1088" s="2" t="s">
-        <v>6755</v>
+        <v>6753</v>
       </c>
       <c r="C1088" s="2" t="s">
-        <v>6756</v>
+        <v>6754</v>
       </c>
       <c r="D1088" s="2" t="s">
         <v>4901</v>
@@ -54304,7 +54306,7 @@
         <v>3826</v>
       </c>
       <c r="F1088" s="2" t="s">
-        <v>6757</v>
+        <v>6755</v>
       </c>
       <c r="G1088" s="3">
         <v>2</v>
@@ -54379,19 +54381,19 @@
         <v>1090</v>
       </c>
       <c r="B1091" s="2" t="s">
-        <v>6880</v>
+        <v>6878</v>
       </c>
       <c r="C1091" s="2" t="s">
-        <v>6881</v>
+        <v>6879</v>
       </c>
       <c r="D1091" s="2" t="s">
         <v>4829</v>
       </c>
       <c r="E1091" s="2" t="s">
-        <v>6882</v>
+        <v>6880</v>
       </c>
       <c r="F1091" s="2" t="s">
-        <v>6883</v>
+        <v>6881</v>
       </c>
       <c r="G1091" s="3">
         <v>2</v>
@@ -54420,7 +54422,7 @@
         <v>4916</v>
       </c>
       <c r="F1092" s="2" t="s">
-        <v>6910</v>
+        <v>6908</v>
       </c>
       <c r="G1092" s="3">
         <v>1</v>
@@ -54524,7 +54526,7 @@
         <v>1095</v>
       </c>
       <c r="B1096" s="2" t="s">
-        <v>6617</v>
+        <v>6615</v>
       </c>
       <c r="C1096" s="2" t="s">
         <v>4936</v>
@@ -54536,7 +54538,7 @@
         <v>4937</v>
       </c>
       <c r="F1096" s="2" t="s">
-        <v>6618</v>
+        <v>6616</v>
       </c>
       <c r="G1096" s="3">
         <v>4</v>
@@ -54756,19 +54758,19 @@
         <v>1103</v>
       </c>
       <c r="B1104" s="2" t="s">
-        <v>6968</v>
+        <v>6966</v>
       </c>
       <c r="C1104" s="2" t="s">
-        <v>6969</v>
+        <v>6967</v>
       </c>
       <c r="D1104" s="2" t="s">
         <v>727</v>
       </c>
       <c r="E1104" s="2" t="s">
-        <v>6970</v>
+        <v>6968</v>
       </c>
       <c r="F1104" s="2" t="s">
-        <v>6971</v>
+        <v>6969</v>
       </c>
       <c r="G1104" s="3">
         <v>4</v>
@@ -54849,7 +54851,7 @@
         <v>914</v>
       </c>
       <c r="D1107" s="2" t="s">
-        <v>6959</v>
+        <v>6957</v>
       </c>
       <c r="E1107" s="2" t="s">
         <v>4000</v>
@@ -54988,19 +54990,19 @@
         <v>1111</v>
       </c>
       <c r="B1112" s="2" t="s">
+        <v>6405</v>
+      </c>
+      <c r="C1112" s="2" t="s">
+        <v>6406</v>
+      </c>
+      <c r="D1112" s="2" t="s">
         <v>6407</v>
       </c>
-      <c r="C1112" s="2" t="s">
+      <c r="E1112" s="2" t="s">
         <v>6408</v>
       </c>
-      <c r="D1112" s="2" t="s">
+      <c r="F1112" s="2" t="s">
         <v>6409</v>
-      </c>
-      <c r="E1112" s="2" t="s">
-        <v>6410</v>
-      </c>
-      <c r="F1112" s="2" t="s">
-        <v>6411</v>
       </c>
       <c r="G1112" s="3">
         <v>4</v>
@@ -55113,10 +55115,10 @@
         <v>5016</v>
       </c>
       <c r="E1116" s="2" t="s">
-        <v>6364</v>
+        <v>6362</v>
       </c>
       <c r="F1116" s="2" t="s">
-        <v>6365</v>
+        <v>6363</v>
       </c>
       <c r="G1116" s="3">
         <v>1</v>
@@ -55171,10 +55173,10 @@
         <v>5026</v>
       </c>
       <c r="E1118" s="2" t="s">
-        <v>6141</v>
+        <v>6139</v>
       </c>
       <c r="F1118" s="2" t="s">
-        <v>6140</v>
+        <v>6138</v>
       </c>
       <c r="G1118" s="3">
         <v>4</v>
@@ -55336,19 +55338,19 @@
         <v>1123</v>
       </c>
       <c r="B1124" s="2" t="s">
+        <v>6489</v>
+      </c>
+      <c r="C1124" s="2" t="s">
+        <v>6490</v>
+      </c>
+      <c r="D1124" s="2" t="s">
         <v>6491</v>
       </c>
-      <c r="C1124" s="2" t="s">
+      <c r="E1124" s="2" t="s">
         <v>6492</v>
       </c>
-      <c r="D1124" s="2" t="s">
-        <v>6493</v>
-      </c>
-      <c r="E1124" s="2" t="s">
-        <v>6494</v>
-      </c>
       <c r="F1124" s="2" t="s">
-        <v>6517</v>
+        <v>6515</v>
       </c>
       <c r="G1124" s="3">
         <v>4</v>
@@ -55539,7 +55541,7 @@
         <v>1130</v>
       </c>
       <c r="B1131" s="2" t="s">
-        <v>6465</v>
+        <v>6463</v>
       </c>
       <c r="C1131" s="2" t="s">
         <v>5082</v>
@@ -55548,10 +55550,10 @@
         <v>5083</v>
       </c>
       <c r="E1131" s="2" t="s">
-        <v>6466</v>
+        <v>6464</v>
       </c>
       <c r="F1131" s="2" t="s">
-        <v>6467</v>
+        <v>6465</v>
       </c>
       <c r="G1131" s="3">
         <v>1</v>
@@ -55568,19 +55570,19 @@
         <v>1131</v>
       </c>
       <c r="B1132" s="2" t="s">
+        <v>6467</v>
+      </c>
+      <c r="C1132" s="5" t="s">
+        <v>6468</v>
+      </c>
+      <c r="D1132" s="2" t="s">
         <v>6469</v>
       </c>
-      <c r="C1132" s="5" t="s">
+      <c r="E1132" s="2" t="s">
         <v>6470</v>
       </c>
-      <c r="D1132" s="2" t="s">
+      <c r="F1132" s="2" t="s">
         <v>6471</v>
-      </c>
-      <c r="E1132" s="2" t="s">
-        <v>6472</v>
-      </c>
-      <c r="F1132" s="2" t="s">
-        <v>6473</v>
       </c>
       <c r="G1132" s="3">
         <v>3</v>
@@ -55597,19 +55599,19 @@
         <v>1132</v>
       </c>
       <c r="B1133" s="2" t="s">
+        <v>6474</v>
+      </c>
+      <c r="C1133" s="2" t="s">
+        <v>6475</v>
+      </c>
+      <c r="D1133" s="2" t="s">
         <v>6476</v>
       </c>
-      <c r="C1133" s="2" t="s">
+      <c r="E1133" s="2" t="s">
         <v>6477</v>
       </c>
-      <c r="D1133" s="2" t="s">
+      <c r="F1133" s="2" t="s">
         <v>6478</v>
-      </c>
-      <c r="E1133" s="2" t="s">
-        <v>6479</v>
-      </c>
-      <c r="F1133" s="2" t="s">
-        <v>6480</v>
       </c>
       <c r="G1133" s="3">
         <v>2</v>
@@ -55626,7 +55628,7 @@
         <v>1133</v>
       </c>
       <c r="B1134" s="2" t="s">
-        <v>6468</v>
+        <v>6466</v>
       </c>
       <c r="C1134" s="2" t="s">
         <v>5085</v>
@@ -55635,10 +55637,10 @@
         <v>5086</v>
       </c>
       <c r="E1134" s="2" t="s">
-        <v>6474</v>
+        <v>6472</v>
       </c>
       <c r="F1134" s="2" t="s">
-        <v>6475</v>
+        <v>6473</v>
       </c>
       <c r="G1134" s="3">
         <v>1</v>
@@ -55732,7 +55734,7 @@
         <v>1137</v>
       </c>
       <c r="B1138" s="2" t="s">
-        <v>6905</v>
+        <v>6903</v>
       </c>
       <c r="C1138" s="2" t="s">
         <v>5100</v>
@@ -55819,19 +55821,19 @@
         <v>1140</v>
       </c>
       <c r="B1141" s="2" t="s">
+        <v>6834</v>
+      </c>
+      <c r="C1141" s="2" t="s">
+        <v>6835</v>
+      </c>
+      <c r="D1141" s="2" t="s">
         <v>6836</v>
-      </c>
-      <c r="C1141" s="2" t="s">
-        <v>6837</v>
-      </c>
-      <c r="D1141" s="2" t="s">
-        <v>6838</v>
       </c>
       <c r="E1141" s="2" t="s">
         <v>5116</v>
       </c>
       <c r="F1141" s="2" t="s">
-        <v>6839</v>
+        <v>6837</v>
       </c>
       <c r="G1141" s="3">
         <v>3</v>
@@ -55848,19 +55850,19 @@
         <v>1141</v>
       </c>
       <c r="B1142" s="2" t="s">
-        <v>6835</v>
+        <v>6833</v>
       </c>
       <c r="C1142" s="2" t="s">
-        <v>6883</v>
+        <v>6881</v>
       </c>
       <c r="D1142" s="2" t="s">
         <v>4829</v>
       </c>
       <c r="E1142" s="2" t="s">
-        <v>6884</v>
+        <v>6882</v>
       </c>
       <c r="F1142" s="2" t="s">
-        <v>6885</v>
+        <v>6883</v>
       </c>
       <c r="G1142" s="3">
         <v>4</v>
@@ -55935,7 +55937,7 @@
         <v>1144</v>
       </c>
       <c r="B1145" s="2" t="s">
-        <v>6781</v>
+        <v>6779</v>
       </c>
       <c r="C1145" s="2" t="s">
         <v>5132</v>
@@ -55964,7 +55966,7 @@
         <v>1145</v>
       </c>
       <c r="B1146" s="2" t="s">
-        <v>6782</v>
+        <v>6780</v>
       </c>
       <c r="C1146" s="2" t="s">
         <v>3965</v>
@@ -55973,10 +55975,10 @@
         <v>3966</v>
       </c>
       <c r="E1146" s="2" t="s">
-        <v>7002</v>
+        <v>7000</v>
       </c>
       <c r="F1146" s="2" t="s">
-        <v>7003</v>
+        <v>7001</v>
       </c>
       <c r="G1146" s="3">
         <v>1</v>
@@ -55993,7 +55995,7 @@
         <v>1146</v>
       </c>
       <c r="B1147" s="2" t="s">
-        <v>6783</v>
+        <v>6781</v>
       </c>
       <c r="C1147" s="2" t="s">
         <v>5138</v>
@@ -56022,7 +56024,7 @@
         <v>1147</v>
       </c>
       <c r="B1148" s="2" t="s">
-        <v>6784</v>
+        <v>6782</v>
       </c>
       <c r="C1148" s="2" t="s">
         <v>5143</v>
@@ -56051,10 +56053,10 @@
         <v>1148</v>
       </c>
       <c r="B1149" s="2" t="s">
-        <v>6785</v>
+        <v>6783</v>
       </c>
       <c r="C1149" s="2" t="s">
-        <v>6786</v>
+        <v>6784</v>
       </c>
       <c r="D1149" s="2" t="s">
         <v>5148</v>
@@ -56109,16 +56111,16 @@
         <v>1150</v>
       </c>
       <c r="B1151" s="2" t="s">
-        <v>6950</v>
+        <v>6948</v>
       </c>
       <c r="C1151" s="2" t="s">
-        <v>6951</v>
+        <v>6949</v>
       </c>
       <c r="D1151" s="2" t="s">
         <v>5156</v>
       </c>
       <c r="E1151" s="2" t="s">
-        <v>6952</v>
+        <v>6950</v>
       </c>
       <c r="F1151" s="2" t="s">
         <v>5157</v>
@@ -56196,19 +56198,19 @@
         <v>1153</v>
       </c>
       <c r="B1154" s="2" t="s">
+        <v>6726</v>
+      </c>
+      <c r="C1154" s="2" t="s">
+        <v>6727</v>
+      </c>
+      <c r="D1154" s="2" t="s">
         <v>6728</v>
       </c>
-      <c r="C1154" s="2" t="s">
+      <c r="E1154" s="2" t="s">
+        <v>6730</v>
+      </c>
+      <c r="F1154" s="2" t="s">
         <v>6729</v>
-      </c>
-      <c r="D1154" s="2" t="s">
-        <v>6730</v>
-      </c>
-      <c r="E1154" s="2" t="s">
-        <v>6732</v>
-      </c>
-      <c r="F1154" s="2" t="s">
-        <v>6731</v>
       </c>
       <c r="G1154" s="3">
         <v>3</v>
@@ -56283,10 +56285,10 @@
         <v>1156</v>
       </c>
       <c r="B1157" s="2" t="s">
-        <v>6875</v>
+        <v>6873</v>
       </c>
       <c r="C1157" s="2" t="s">
-        <v>6876</v>
+        <v>6874</v>
       </c>
       <c r="D1157" s="2" t="s">
         <v>5175</v>
@@ -56295,7 +56297,7 @@
         <v>5176</v>
       </c>
       <c r="F1157" s="2" t="s">
-        <v>6877</v>
+        <v>6875</v>
       </c>
       <c r="G1157" s="3">
         <v>2</v>
@@ -56602,19 +56604,19 @@
         <v>1167</v>
       </c>
       <c r="B1168" s="2" t="s">
-        <v>6685</v>
+        <v>6683</v>
       </c>
       <c r="C1168" s="2" t="s">
-        <v>6686</v>
+        <v>6684</v>
       </c>
       <c r="D1168" s="2" t="s">
         <v>5225</v>
       </c>
       <c r="E1168" s="2" t="s">
-        <v>6687</v>
+        <v>6685</v>
       </c>
       <c r="F1168" s="2" t="s">
-        <v>6688</v>
+        <v>6686</v>
       </c>
       <c r="G1168" s="3">
         <v>3</v>
@@ -56750,16 +56752,16 @@
         <v>5246</v>
       </c>
       <c r="C1173" s="2" t="s">
-        <v>6926</v>
+        <v>6924</v>
       </c>
       <c r="D1173" s="2" t="s">
         <v>5247</v>
       </c>
       <c r="E1173" s="2" t="s">
-        <v>6924</v>
+        <v>6922</v>
       </c>
       <c r="F1173" s="2" t="s">
-        <v>6925</v>
+        <v>6923</v>
       </c>
       <c r="G1173" s="3">
         <v>3</v>
@@ -56863,7 +56865,7 @@
         <v>1176</v>
       </c>
       <c r="B1177" s="2" t="s">
-        <v>6903</v>
+        <v>6901</v>
       </c>
       <c r="C1177" s="2" t="s">
         <v>1690</v>
@@ -57008,10 +57010,10 @@
         <v>1181</v>
       </c>
       <c r="B1182" s="2" t="s">
-        <v>6254</v>
+        <v>6252</v>
       </c>
       <c r="C1182" s="2" t="s">
-        <v>6255</v>
+        <v>6253</v>
       </c>
       <c r="D1182" s="2" t="s">
         <v>5280</v>
@@ -57020,7 +57022,7 @@
         <v>1690</v>
       </c>
       <c r="F1182" s="2" t="s">
-        <v>6256</v>
+        <v>6254</v>
       </c>
       <c r="G1182" s="3">
         <v>4</v>
@@ -57066,7 +57068,7 @@
         <v>1183</v>
       </c>
       <c r="B1184" s="2" t="s">
-        <v>6582</v>
+        <v>6580</v>
       </c>
       <c r="C1184" s="2" t="s">
         <v>3974</v>
@@ -57095,7 +57097,7 @@
         <v>1184</v>
       </c>
       <c r="B1185" s="2" t="s">
-        <v>6354</v>
+        <v>6352</v>
       </c>
       <c r="C1185" s="2" t="s">
         <v>5288</v>
@@ -57107,7 +57109,7 @@
         <v>3976</v>
       </c>
       <c r="F1185" s="4" t="s">
-        <v>6355</v>
+        <v>6353</v>
       </c>
       <c r="G1185" s="3">
         <v>1</v>
@@ -57124,7 +57126,7 @@
         <v>1185</v>
       </c>
       <c r="B1186" s="2" t="s">
-        <v>6332</v>
+        <v>6330</v>
       </c>
       <c r="C1186" s="2" t="s">
         <v>3975</v>
@@ -57136,7 +57138,7 @@
         <v>5291</v>
       </c>
       <c r="F1186" s="4" t="s">
-        <v>6356</v>
+        <v>6354</v>
       </c>
       <c r="G1186" s="3">
         <v>2</v>
@@ -57153,7 +57155,7 @@
         <v>1186</v>
       </c>
       <c r="B1187" s="2" t="s">
-        <v>6957</v>
+        <v>6955</v>
       </c>
       <c r="C1187" s="2" t="s">
         <v>3976</v>
@@ -57182,7 +57184,7 @@
         <v>1187</v>
       </c>
       <c r="B1188" s="2" t="s">
-        <v>6958</v>
+        <v>6956</v>
       </c>
       <c r="C1188" s="2" t="s">
         <v>4628</v>
@@ -57298,7 +57300,7 @@
         <v>1191</v>
       </c>
       <c r="B1192" s="2" t="s">
-        <v>7021</v>
+        <v>7019</v>
       </c>
       <c r="C1192" s="2" t="s">
         <v>5294</v>
@@ -57501,7 +57503,7 @@
         <v>1198</v>
       </c>
       <c r="B1199" s="2" t="s">
-        <v>6537</v>
+        <v>6535</v>
       </c>
       <c r="C1199" s="2" t="s">
         <v>5327</v>
@@ -57530,7 +57532,7 @@
         <v>1199</v>
       </c>
       <c r="B1200" s="2" t="s">
-        <v>6538</v>
+        <v>6536</v>
       </c>
       <c r="C1200" s="2" t="s">
         <v>4011</v>
@@ -57542,7 +57544,7 @@
         <v>4013</v>
       </c>
       <c r="F1200" s="2" t="s">
-        <v>6552</v>
+        <v>6550</v>
       </c>
       <c r="G1200" s="3">
         <v>1</v>
@@ -57588,7 +57590,7 @@
         <v>1201</v>
       </c>
       <c r="B1202" s="2" t="s">
-        <v>6788</v>
+        <v>6786</v>
       </c>
       <c r="C1202" s="2" t="s">
         <v>3975</v>
@@ -57646,19 +57648,19 @@
         <v>1203</v>
       </c>
       <c r="B1204" s="2" t="s">
-        <v>6826</v>
+        <v>6824</v>
       </c>
       <c r="C1204" s="2" t="s">
+        <v>6820</v>
+      </c>
+      <c r="D1204" s="2" t="s">
+        <v>6821</v>
+      </c>
+      <c r="E1204" s="2" t="s">
         <v>6822</v>
       </c>
-      <c r="D1204" s="2" t="s">
+      <c r="F1204" s="2" t="s">
         <v>6823</v>
-      </c>
-      <c r="E1204" s="2" t="s">
-        <v>6824</v>
-      </c>
-      <c r="F1204" s="2" t="s">
-        <v>6825</v>
       </c>
       <c r="G1204" s="3">
         <v>3</v>
@@ -57762,7 +57764,7 @@
         <v>1207</v>
       </c>
       <c r="B1208" s="2" t="s">
-        <v>6346</v>
+        <v>6344</v>
       </c>
       <c r="C1208" s="2" t="s">
         <v>3975</v>
@@ -57791,7 +57793,7 @@
         <v>1208</v>
       </c>
       <c r="B1209" s="2" t="s">
-        <v>6347</v>
+        <v>6345</v>
       </c>
       <c r="C1209" s="2" t="s">
         <v>3975</v>
@@ -57907,7 +57909,7 @@
         <v>1212</v>
       </c>
       <c r="B1213" s="2" t="s">
-        <v>6307</v>
+        <v>6305</v>
       </c>
       <c r="C1213" s="2" t="s">
         <v>5355</v>
@@ -57948,7 +57950,7 @@
         <v>2843</v>
       </c>
       <c r="F1214" s="2" t="s">
-        <v>6663</v>
+        <v>6661</v>
       </c>
       <c r="G1214" s="3">
         <v>1</v>
@@ -57971,13 +57973,13 @@
         <v>5364</v>
       </c>
       <c r="D1215" s="2" t="s">
-        <v>6305</v>
+        <v>6303</v>
       </c>
       <c r="E1215" s="2" t="s">
         <v>5365</v>
       </c>
       <c r="F1215" s="2" t="s">
-        <v>6306</v>
+        <v>6304</v>
       </c>
       <c r="G1215" s="3">
         <v>4</v>
@@ -58139,7 +58141,7 @@
         <v>1220</v>
       </c>
       <c r="B1221" s="2" t="s">
-        <v>6921</v>
+        <v>6919</v>
       </c>
       <c r="C1221" s="2" t="s">
         <v>5389</v>
@@ -58168,19 +58170,19 @@
         <v>1221</v>
       </c>
       <c r="B1222" s="2" t="s">
+        <v>6750</v>
+      </c>
+      <c r="C1222" s="2" t="s">
+        <v>6749</v>
+      </c>
+      <c r="D1222" s="2" t="s">
         <v>6752</v>
-      </c>
-      <c r="C1222" s="2" t="s">
-        <v>6751</v>
-      </c>
-      <c r="D1222" s="2" t="s">
-        <v>6754</v>
       </c>
       <c r="E1222" s="2" t="s">
         <v>5394</v>
       </c>
       <c r="F1222" s="2" t="s">
-        <v>6753</v>
+        <v>6751</v>
       </c>
       <c r="G1222" s="3">
         <v>1</v>
@@ -58197,13 +58199,13 @@
         <v>1222</v>
       </c>
       <c r="B1223" s="2" t="s">
-        <v>6923</v>
+        <v>6921</v>
       </c>
       <c r="C1223" s="2" t="s">
         <v>5396</v>
       </c>
       <c r="D1223" s="2" t="s">
-        <v>6922</v>
+        <v>6920</v>
       </c>
       <c r="E1223" s="2" t="s">
         <v>5397</v>
@@ -58229,16 +58231,16 @@
         <v>5400</v>
       </c>
       <c r="C1224" s="2" t="s">
-        <v>6832</v>
+        <v>6830</v>
       </c>
       <c r="D1224" s="2" t="s">
-        <v>6833</v>
+        <v>6831</v>
       </c>
       <c r="E1224" s="2" t="s">
         <v>4263</v>
       </c>
       <c r="F1224" s="2" t="s">
-        <v>6834</v>
+        <v>6832</v>
       </c>
       <c r="G1224" s="3">
         <v>1</v>
@@ -58255,16 +58257,16 @@
         <v>1224</v>
       </c>
       <c r="B1225" s="2" t="s">
-        <v>6720</v>
+        <v>6718</v>
       </c>
       <c r="C1225" s="2" t="s">
-        <v>6721</v>
+        <v>6719</v>
       </c>
       <c r="D1225" s="2" t="s">
         <v>4773</v>
       </c>
       <c r="E1225" s="2" t="s">
-        <v>6722</v>
+        <v>6720</v>
       </c>
       <c r="F1225" s="2" t="s">
         <v>5402</v>
@@ -58342,7 +58344,7 @@
         <v>1227</v>
       </c>
       <c r="B1228" s="2" t="s">
-        <v>6151</v>
+        <v>6149</v>
       </c>
       <c r="C1228" s="2" t="s">
         <v>5413</v>
@@ -58351,10 +58353,10 @@
         <v>5414</v>
       </c>
       <c r="E1228" s="2" t="s">
-        <v>6152</v>
+        <v>6150</v>
       </c>
       <c r="F1228" s="2" t="s">
-        <v>6153</v>
+        <v>6151</v>
       </c>
       <c r="G1228" s="3">
         <v>4</v>
@@ -58485,13 +58487,13 @@
         <v>1232</v>
       </c>
       <c r="B1233" s="2" t="s">
-        <v>6323</v>
+        <v>6321</v>
       </c>
       <c r="C1233" s="2" t="s">
         <v>5431</v>
       </c>
       <c r="D1233" s="2" t="s">
-        <v>6324</v>
+        <v>6322</v>
       </c>
       <c r="E1233" s="2" t="s">
         <v>3616</v>
@@ -58514,7 +58516,7 @@
         <v>1233</v>
       </c>
       <c r="B1234" s="2" t="s">
-        <v>7055</v>
+        <v>7053</v>
       </c>
       <c r="C1234" s="2" t="s">
         <v>4765</v>
@@ -58526,7 +58528,7 @@
         <v>1444</v>
       </c>
       <c r="F1234" s="2" t="s">
-        <v>7056</v>
+        <v>7054</v>
       </c>
       <c r="G1234" s="3">
         <v>4</v>
@@ -58601,16 +58603,16 @@
         <v>1236</v>
       </c>
       <c r="B1237" s="2" t="s">
-        <v>6614</v>
+        <v>6612</v>
       </c>
       <c r="C1237" s="2" t="s">
-        <v>6615</v>
+        <v>6613</v>
       </c>
       <c r="D1237" s="2" t="s">
         <v>5446</v>
       </c>
       <c r="E1237" s="2" t="s">
-        <v>6616</v>
+        <v>6614</v>
       </c>
       <c r="F1237" s="2" t="s">
         <v>5447</v>
@@ -58718,10 +58720,10 @@
         <v>5460</v>
       </c>
       <c r="C1241" s="2" t="s">
-        <v>6214</v>
+        <v>6212</v>
       </c>
       <c r="D1241" s="2" t="s">
-        <v>6215</v>
+        <v>6213</v>
       </c>
       <c r="E1241" s="2" t="s">
         <v>5397</v>
@@ -58860,7 +58862,7 @@
         <v>1245</v>
       </c>
       <c r="B1246" s="2" t="s">
-        <v>6599</v>
+        <v>6597</v>
       </c>
       <c r="C1246" s="2" t="s">
         <v>5482</v>
@@ -59034,7 +59036,7 @@
         <v>1251</v>
       </c>
       <c r="B1252" s="2" t="s">
-        <v>6808</v>
+        <v>6806</v>
       </c>
       <c r="C1252" s="2" t="s">
         <v>5511</v>
@@ -59043,7 +59045,7 @@
         <v>5512</v>
       </c>
       <c r="E1252" s="2" t="s">
-        <v>6809</v>
+        <v>6807</v>
       </c>
       <c r="F1252" s="2" t="s">
         <v>5513</v>
@@ -59563,7 +59565,7 @@
         <v>2521</v>
       </c>
       <c r="E1270" s="2" t="s">
-        <v>6510</v>
+        <v>6508</v>
       </c>
       <c r="F1270" s="2" t="s">
         <v>5601</v>
@@ -59786,7 +59788,7 @@
         <v>1277</v>
       </c>
       <c r="B1278" s="2" t="s">
-        <v>6391</v>
+        <v>6389</v>
       </c>
       <c r="C1278" s="2" t="s">
         <v>5638</v>
@@ -59798,7 +59800,7 @@
         <v>117</v>
       </c>
       <c r="F1278" s="2" t="s">
-        <v>6392</v>
+        <v>6390</v>
       </c>
       <c r="G1278" s="3">
         <v>4</v>
@@ -59815,7 +59817,7 @@
         <v>1278</v>
       </c>
       <c r="B1279" s="2" t="s">
-        <v>6524</v>
+        <v>6522</v>
       </c>
       <c r="C1279" s="2" t="s">
         <v>5641</v>
@@ -59824,10 +59826,10 @@
         <v>5642</v>
       </c>
       <c r="E1279" s="2" t="s">
-        <v>6525</v>
+        <v>6523</v>
       </c>
       <c r="F1279" s="2" t="s">
-        <v>6526</v>
+        <v>6524</v>
       </c>
       <c r="G1279" s="3">
         <v>1</v>
@@ -59844,19 +59846,19 @@
         <v>1279</v>
       </c>
       <c r="B1280" s="2" t="s">
+        <v>6331</v>
+      </c>
+      <c r="C1280" s="2" t="s">
+        <v>6332</v>
+      </c>
+      <c r="D1280" s="2" t="s">
+        <v>6335</v>
+      </c>
+      <c r="E1280" s="2" t="s">
         <v>6333</v>
       </c>
-      <c r="C1280" s="2" t="s">
+      <c r="F1280" s="2" t="s">
         <v>6334</v>
-      </c>
-      <c r="D1280" s="2" t="s">
-        <v>6337</v>
-      </c>
-      <c r="E1280" s="2" t="s">
-        <v>6335</v>
-      </c>
-      <c r="F1280" s="2" t="s">
-        <v>6336</v>
       </c>
       <c r="G1280" s="3">
         <v>4</v>
@@ -59989,10 +59991,10 @@
         <v>1284</v>
       </c>
       <c r="B1285" s="2" t="s">
-        <v>6197</v>
+        <v>6195</v>
       </c>
       <c r="C1285" s="2" t="s">
-        <v>6198</v>
+        <v>6196</v>
       </c>
       <c r="D1285" s="2" t="s">
         <v>3054</v>
@@ -60001,7 +60003,7 @@
         <v>5663</v>
       </c>
       <c r="F1285" s="2" t="s">
-        <v>6199</v>
+        <v>6197</v>
       </c>
       <c r="G1285" s="3">
         <v>2</v>
@@ -60134,19 +60136,19 @@
         <v>1289</v>
       </c>
       <c r="B1290" s="2" t="s">
+        <v>6181</v>
+      </c>
+      <c r="C1290" s="2" t="s">
+        <v>6182</v>
+      </c>
+      <c r="D1290" s="2" t="s">
         <v>6183</v>
-      </c>
-      <c r="C1290" s="2" t="s">
-        <v>6184</v>
-      </c>
-      <c r="D1290" s="2" t="s">
-        <v>6185</v>
       </c>
       <c r="E1290" s="2" t="s">
         <v>5685</v>
       </c>
       <c r="F1290" s="2" t="s">
-        <v>6186</v>
+        <v>6184</v>
       </c>
       <c r="G1290" s="3">
         <v>3</v>
@@ -60166,7 +60168,7 @@
         <v>5687</v>
       </c>
       <c r="C1291" s="2" t="s">
-        <v>6792</v>
+        <v>6790</v>
       </c>
       <c r="D1291" s="2" t="s">
         <v>4090</v>
@@ -60192,7 +60194,7 @@
         <v>1291</v>
       </c>
       <c r="B1292" s="2" t="s">
-        <v>6508</v>
+        <v>6506</v>
       </c>
       <c r="C1292" s="2" t="s">
         <v>479</v>
@@ -60204,7 +60206,7 @@
         <v>481</v>
       </c>
       <c r="F1292" s="2" t="s">
-        <v>6509</v>
+        <v>6507</v>
       </c>
       <c r="G1292" s="3">
         <v>2</v>
@@ -60224,7 +60226,7 @@
         <v>5691</v>
       </c>
       <c r="C1293" s="2" t="s">
-        <v>7012</v>
+        <v>7010</v>
       </c>
       <c r="D1293" s="2" t="s">
         <v>5692</v>
@@ -60366,7 +60368,7 @@
         <v>1297</v>
       </c>
       <c r="B1298" s="2" t="s">
-        <v>6974</v>
+        <v>6972</v>
       </c>
       <c r="C1298" s="2" t="s">
         <v>544</v>
@@ -60511,7 +60513,7 @@
         <v>1302</v>
       </c>
       <c r="B1303" s="2" t="s">
-        <v>6357</v>
+        <v>6355</v>
       </c>
       <c r="C1303" s="2" t="s">
         <v>5736</v>
@@ -60523,7 +60525,7 @@
         <v>5738</v>
       </c>
       <c r="F1303" s="2" t="s">
-        <v>6358</v>
+        <v>6356</v>
       </c>
       <c r="G1303" s="3">
         <v>2</v>
@@ -60836,13 +60838,13 @@
         <v>5595</v>
       </c>
       <c r="D1314" s="2" t="s">
-        <v>6248</v>
+        <v>6246</v>
       </c>
       <c r="E1314" s="2" t="s">
+        <v>6245</v>
+      </c>
+      <c r="F1314" s="2" t="s">
         <v>6247</v>
-      </c>
-      <c r="F1314" s="2" t="s">
-        <v>6249</v>
       </c>
       <c r="G1314" s="3">
         <v>3</v>
@@ -60859,19 +60861,19 @@
         <v>1314</v>
       </c>
       <c r="B1315" s="2" t="s">
-        <v>6243</v>
+        <v>6241</v>
       </c>
       <c r="C1315" s="2" t="s">
         <v>5779</v>
       </c>
       <c r="D1315" s="2" t="s">
+        <v>6242</v>
+      </c>
+      <c r="E1315" s="2" t="s">
+        <v>6243</v>
+      </c>
+      <c r="F1315" s="2" t="s">
         <v>6244</v>
-      </c>
-      <c r="E1315" s="2" t="s">
-        <v>6245</v>
-      </c>
-      <c r="F1315" s="2" t="s">
-        <v>6246</v>
       </c>
       <c r="G1315" s="3">
         <v>4</v>
@@ -60917,7 +60919,7 @@
         <v>1316</v>
       </c>
       <c r="B1317" s="2" t="s">
-        <v>6250</v>
+        <v>6248</v>
       </c>
       <c r="C1317" s="2" t="s">
         <v>5785</v>
@@ -60929,7 +60931,7 @@
         <v>5787</v>
       </c>
       <c r="F1317" s="2" t="s">
-        <v>6251</v>
+        <v>6249</v>
       </c>
       <c r="G1317" s="3">
         <v>2</v>
@@ -61033,19 +61035,19 @@
         <v>1320</v>
       </c>
       <c r="B1321" s="2" t="s">
-        <v>6690</v>
+        <v>6688</v>
       </c>
       <c r="C1321" s="2" t="s">
         <v>1309</v>
       </c>
       <c r="D1321" s="2" t="s">
-        <v>6689</v>
+        <v>6687</v>
       </c>
       <c r="E1321" s="2" t="s">
         <v>1311</v>
       </c>
       <c r="F1321" s="2" t="s">
-        <v>6691</v>
+        <v>6689</v>
       </c>
       <c r="G1321" s="3">
         <v>4</v>
@@ -61065,7 +61067,7 @@
         <v>5803</v>
       </c>
       <c r="C1322" s="2" t="s">
-        <v>6175</v>
+        <v>6173</v>
       </c>
       <c r="D1322" s="2" t="s">
         <v>5804</v>
@@ -61074,7 +61076,7 @@
         <v>5805</v>
       </c>
       <c r="F1322" s="2" t="s">
-        <v>6176</v>
+        <v>6174</v>
       </c>
       <c r="G1322" s="3">
         <v>4</v>
@@ -61120,7 +61122,7 @@
         <v>1323</v>
       </c>
       <c r="B1324" s="2" t="s">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="C1324" s="2" t="s">
         <v>5811</v>
@@ -61205,7 +61207,7 @@
         <v>1326</v>
       </c>
       <c r="B1327" s="2" t="s">
-        <v>6572</v>
+        <v>6570</v>
       </c>
       <c r="C1327" s="2" t="s">
         <v>5818</v>
@@ -61217,7 +61219,7 @@
         <v>1309</v>
       </c>
       <c r="F1327" s="2" t="s">
-        <v>6573</v>
+        <v>6571</v>
       </c>
       <c r="G1327" s="3">
         <v>3</v>
@@ -61263,7 +61265,7 @@
         <v>1328</v>
       </c>
       <c r="B1329" s="2" t="s">
-        <v>6634</v>
+        <v>6632</v>
       </c>
       <c r="C1329" s="2" t="s">
         <v>1309</v>
@@ -61321,7 +61323,7 @@
         <v>1330</v>
       </c>
       <c r="B1331" s="2" t="s">
-        <v>6633</v>
+        <v>6631</v>
       </c>
       <c r="C1331" s="2" t="s">
         <v>1309</v>
@@ -61350,13 +61352,13 @@
         <v>1331</v>
       </c>
       <c r="B1332" s="2" t="s">
-        <v>6607</v>
+        <v>6605</v>
       </c>
       <c r="C1332" s="2" t="s">
         <v>5825</v>
       </c>
       <c r="D1332" s="2" t="s">
-        <v>6606</v>
+        <v>6604</v>
       </c>
       <c r="E1332" s="2" t="s">
         <v>5826</v>
@@ -61498,16 +61500,16 @@
         <v>5843</v>
       </c>
       <c r="C1337" s="2" t="s">
-        <v>6994</v>
+        <v>6992</v>
       </c>
       <c r="D1337" s="2" t="s">
         <v>5845</v>
       </c>
       <c r="E1337" s="2" t="s">
-        <v>6995</v>
+        <v>6993</v>
       </c>
       <c r="F1337" s="2" t="s">
-        <v>6996</v>
+        <v>6994</v>
       </c>
       <c r="G1337" s="3">
         <v>3</v>
@@ -61536,7 +61538,7 @@
         <v>4554</v>
       </c>
       <c r="F1338" s="4" t="s">
-        <v>6849</v>
+        <v>6847</v>
       </c>
       <c r="G1338" s="3">
         <v>4</v>
@@ -61565,7 +61567,7 @@
         <v>5850</v>
       </c>
       <c r="F1339" s="2" t="s">
-        <v>6848</v>
+        <v>6846</v>
       </c>
       <c r="G1339" s="3">
         <v>2</v>
@@ -61594,7 +61596,7 @@
         <v>310</v>
       </c>
       <c r="F1340" s="2" t="s">
-        <v>6845</v>
+        <v>6843</v>
       </c>
       <c r="G1340" s="3">
         <v>2</v>
@@ -61614,16 +61616,16 @@
         <v>5854</v>
       </c>
       <c r="C1341" s="2" t="s">
-        <v>6843</v>
+        <v>6841</v>
       </c>
       <c r="D1341" s="2" t="s">
-        <v>6844</v>
+        <v>6842</v>
       </c>
       <c r="E1341" s="2" t="s">
         <v>5844</v>
       </c>
       <c r="F1341" s="2" t="s">
-        <v>6847</v>
+        <v>6845</v>
       </c>
       <c r="G1341" s="3">
         <v>4</v>
@@ -61652,7 +61654,7 @@
         <v>5859</v>
       </c>
       <c r="F1342" s="2" t="s">
-        <v>6846</v>
+        <v>6844</v>
       </c>
       <c r="G1342" s="3">
         <v>4</v>
@@ -61727,7 +61729,7 @@
         <v>1344</v>
       </c>
       <c r="B1345" s="2" t="s">
-        <v>6793</v>
+        <v>6791</v>
       </c>
       <c r="C1345" s="2" t="s">
         <v>479</v>
@@ -61739,7 +61741,7 @@
         <v>5872</v>
       </c>
       <c r="F1345" s="4" t="s">
-        <v>6794</v>
+        <v>6792</v>
       </c>
       <c r="G1345" s="3">
         <v>4</v>
@@ -62018,16 +62020,16 @@
         <v>5914</v>
       </c>
       <c r="C1355" s="2" t="s">
+        <v>6358</v>
+      </c>
+      <c r="D1355" s="2" t="s">
+        <v>6357</v>
+      </c>
+      <c r="E1355" s="2" t="s">
         <v>6360</v>
       </c>
-      <c r="D1355" s="2" t="s">
+      <c r="F1355" s="2" t="s">
         <v>6359</v>
-      </c>
-      <c r="E1355" s="2" t="s">
-        <v>6362</v>
-      </c>
-      <c r="F1355" s="2" t="s">
-        <v>6361</v>
       </c>
       <c r="G1355" s="3">
         <v>4</v>
@@ -62163,16 +62165,16 @@
         <v>5940</v>
       </c>
       <c r="C1360" s="2" t="s">
-        <v>6569</v>
+        <v>6567</v>
       </c>
       <c r="D1360" s="2" t="s">
-        <v>6570</v>
+        <v>6568</v>
       </c>
       <c r="E1360" s="2" t="s">
         <v>5941</v>
       </c>
       <c r="F1360" s="2" t="s">
-        <v>6571</v>
+        <v>6569</v>
       </c>
       <c r="G1360" s="3">
         <v>1</v>
@@ -62230,7 +62232,7 @@
         <v>5950</v>
       </c>
       <c r="F1362" s="2" t="s">
-        <v>7006</v>
+        <v>7004</v>
       </c>
       <c r="G1362" s="3">
         <v>1</v>
@@ -62624,7 +62626,7 @@
         <v>1375</v>
       </c>
       <c r="B1376" s="2" t="s">
-        <v>6497</v>
+        <v>6495</v>
       </c>
       <c r="C1376" s="2" t="s">
         <v>6012</v>
@@ -62653,10 +62655,10 @@
         <v>1376</v>
       </c>
       <c r="B1377" s="2" t="s">
-        <v>6711</v>
+        <v>6709</v>
       </c>
       <c r="C1377" s="2" t="s">
-        <v>6710</v>
+        <v>6708</v>
       </c>
       <c r="D1377" s="2" t="s">
         <v>6017</v>
@@ -62711,19 +62713,19 @@
         <v>1378</v>
       </c>
       <c r="B1379" s="2" t="s">
+        <v>6306</v>
+      </c>
+      <c r="C1379" s="2" t="s">
+        <v>6307</v>
+      </c>
+      <c r="D1379" s="2" t="s">
         <v>6308</v>
       </c>
-      <c r="C1379" s="2" t="s">
+      <c r="E1379" s="2" t="s">
         <v>6309</v>
       </c>
-      <c r="D1379" s="2" t="s">
+      <c r="F1379" s="2" t="s">
         <v>6310</v>
-      </c>
-      <c r="E1379" s="2" t="s">
-        <v>6311</v>
-      </c>
-      <c r="F1379" s="2" t="s">
-        <v>6312</v>
       </c>
       <c r="G1379" s="3">
         <v>1</v>
@@ -62827,7 +62829,7 @@
         <v>1382</v>
       </c>
       <c r="B1383" s="2" t="s">
-        <v>6920</v>
+        <v>6918</v>
       </c>
       <c r="C1383" s="2" t="s">
         <v>1365</v>
@@ -62839,7 +62841,7 @@
         <v>6036</v>
       </c>
       <c r="F1383" s="2" t="s">
-        <v>6919</v>
+        <v>6917</v>
       </c>
       <c r="G1383" s="3">
         <v>4</v>
@@ -62865,10 +62867,10 @@
         <v>6039</v>
       </c>
       <c r="E1384" s="2" t="s">
-        <v>6806</v>
+        <v>6804</v>
       </c>
       <c r="F1384" s="2" t="s">
-        <v>6807</v>
+        <v>6805</v>
       </c>
       <c r="G1384" s="3">
         <v>4</v>
@@ -62946,16 +62948,16 @@
         <v>6053</v>
       </c>
       <c r="C1387" s="2" t="s">
+        <v>6229</v>
+      </c>
+      <c r="D1387" s="2" t="s">
+        <v>6230</v>
+      </c>
+      <c r="E1387" s="2" t="s">
         <v>6231</v>
       </c>
-      <c r="D1387" s="2" t="s">
+      <c r="F1387" s="2" t="s">
         <v>6232</v>
-      </c>
-      <c r="E1387" s="2" t="s">
-        <v>6233</v>
-      </c>
-      <c r="F1387" s="2" t="s">
-        <v>6234</v>
       </c>
       <c r="G1387" s="3">
         <v>1</v>
@@ -63088,25 +63090,25 @@
         <v>1391</v>
       </c>
       <c r="B1392" s="2" t="s">
+        <v>7066</v>
+      </c>
+      <c r="C1392" s="2" t="s">
         <v>6078</v>
       </c>
-      <c r="C1392" s="2" t="s">
+      <c r="D1392" s="2" t="s">
         <v>6079</v>
       </c>
-      <c r="D1392" s="2" t="s">
+      <c r="E1392" s="2" t="s">
+        <v>7067</v>
+      </c>
+      <c r="F1392" s="2" t="s">
         <v>6080</v>
-      </c>
-      <c r="E1392" s="2" t="s">
-        <v>6081</v>
-      </c>
-      <c r="F1392" s="2" t="s">
-        <v>6082</v>
       </c>
       <c r="G1392" s="3">
         <v>2</v>
       </c>
       <c r="H1392" s="2" t="s">
-        <v>6083</v>
+        <v>6081</v>
       </c>
       <c r="I1392" s="2" t="s">
         <v>15</v>
@@ -63117,25 +63119,25 @@
         <v>1392</v>
       </c>
       <c r="B1393" s="2" t="s">
+        <v>6082</v>
+      </c>
+      <c r="C1393" s="2" t="s">
+        <v>6083</v>
+      </c>
+      <c r="D1393" s="2" t="s">
         <v>6084</v>
       </c>
-      <c r="C1393" s="2" t="s">
+      <c r="E1393" s="2" t="s">
         <v>6085</v>
       </c>
-      <c r="D1393" s="2" t="s">
-        <v>6086</v>
-      </c>
-      <c r="E1393" s="2" t="s">
-        <v>6087</v>
-      </c>
       <c r="F1393" s="2" t="s">
-        <v>6581</v>
+        <v>6579</v>
       </c>
       <c r="G1393" s="3">
         <v>4</v>
       </c>
       <c r="H1393" s="2" t="s">
-        <v>6089</v>
+        <v>6087</v>
       </c>
       <c r="I1393" s="2" t="s">
         <v>781</v>
@@ -63146,25 +63148,25 @@
         <v>1393</v>
       </c>
       <c r="B1394" s="2" t="s">
+        <v>6088</v>
+      </c>
+      <c r="C1394" s="2" t="s">
+        <v>6083</v>
+      </c>
+      <c r="D1394" s="2" t="s">
+        <v>6089</v>
+      </c>
+      <c r="E1394" s="2" t="s">
+        <v>6320</v>
+      </c>
+      <c r="F1394" s="2" t="s">
         <v>6090</v>
-      </c>
-      <c r="C1394" s="2" t="s">
-        <v>6085</v>
-      </c>
-      <c r="D1394" s="2" t="s">
-        <v>6091</v>
-      </c>
-      <c r="E1394" s="2" t="s">
-        <v>6322</v>
-      </c>
-      <c r="F1394" s="2" t="s">
-        <v>6092</v>
       </c>
       <c r="G1394" s="3">
         <v>3</v>
       </c>
       <c r="H1394" s="2" t="s">
-        <v>6093</v>
+        <v>6091</v>
       </c>
       <c r="I1394" s="2" t="s">
         <v>781</v>
@@ -63175,7 +63177,7 @@
         <v>1394</v>
       </c>
       <c r="B1395" s="2" t="s">
-        <v>6094</v>
+        <v>6092</v>
       </c>
       <c r="C1395" s="2" t="s">
         <v>479</v>
@@ -63193,7 +63195,7 @@
         <v>4</v>
       </c>
       <c r="H1395" s="2" t="s">
-        <v>6095</v>
+        <v>6093</v>
       </c>
       <c r="I1395" s="2" t="s">
         <v>781</v>
@@ -63204,10 +63206,10 @@
         <v>1395</v>
       </c>
       <c r="B1396" s="2" t="s">
-        <v>6096</v>
+        <v>6094</v>
       </c>
       <c r="C1396" s="2" t="s">
-        <v>6097</v>
+        <v>6095</v>
       </c>
       <c r="D1396" s="2" t="s">
         <v>479</v>
@@ -63216,13 +63218,13 @@
         <v>478</v>
       </c>
       <c r="F1396" s="2" t="s">
-        <v>6098</v>
+        <v>6096</v>
       </c>
       <c r="G1396" s="3">
         <v>2</v>
       </c>
       <c r="H1396" s="2" t="s">
-        <v>6099</v>
+        <v>6097</v>
       </c>
       <c r="I1396" s="2" t="s">
         <v>781</v>
@@ -63233,25 +63235,25 @@
         <v>1396</v>
       </c>
       <c r="B1397" s="2" t="s">
-        <v>6100</v>
+        <v>6098</v>
       </c>
       <c r="C1397" s="2" t="s">
+        <v>6083</v>
+      </c>
+      <c r="D1397" s="2" t="s">
+        <v>6089</v>
+      </c>
+      <c r="E1397" s="2" t="s">
         <v>6085</v>
       </c>
-      <c r="D1397" s="2" t="s">
-        <v>6091</v>
-      </c>
-      <c r="E1397" s="2" t="s">
-        <v>6087</v>
-      </c>
       <c r="F1397" s="2" t="s">
-        <v>6088</v>
+        <v>6086</v>
       </c>
       <c r="G1397" s="3">
         <v>1</v>
       </c>
       <c r="H1397" s="2" t="s">
-        <v>6101</v>
+        <v>6099</v>
       </c>
       <c r="I1397" s="2" t="s">
         <v>781</v>
@@ -63262,25 +63264,25 @@
         <v>1397</v>
       </c>
       <c r="B1398" s="2" t="s">
-        <v>6102</v>
+        <v>6100</v>
       </c>
       <c r="C1398" s="2" t="s">
+        <v>6083</v>
+      </c>
+      <c r="D1398" s="2" t="s">
+        <v>6089</v>
+      </c>
+      <c r="E1398" s="2" t="s">
         <v>6085</v>
       </c>
-      <c r="D1398" s="2" t="s">
-        <v>6091</v>
-      </c>
-      <c r="E1398" s="2" t="s">
-        <v>6087</v>
-      </c>
       <c r="F1398" s="2" t="s">
-        <v>6088</v>
+        <v>6086</v>
       </c>
       <c r="G1398" s="3">
         <v>3</v>
       </c>
       <c r="H1398" s="2" t="s">
-        <v>6103</v>
+        <v>6101</v>
       </c>
       <c r="I1398" s="2" t="s">
         <v>781</v>
@@ -63291,7 +63293,7 @@
         <v>1398</v>
       </c>
       <c r="B1399" s="2" t="s">
-        <v>6104</v>
+        <v>6102</v>
       </c>
       <c r="C1399" s="2" t="s">
         <v>480</v>
@@ -63303,13 +63305,13 @@
         <v>478</v>
       </c>
       <c r="F1399" s="2" t="s">
-        <v>6105</v>
+        <v>6103</v>
       </c>
       <c r="G1399" s="3">
         <v>4</v>
       </c>
       <c r="H1399" s="2" t="s">
-        <v>6106</v>
+        <v>6104</v>
       </c>
       <c r="I1399" s="2" t="s">
         <v>781</v>
@@ -63320,25 +63322,25 @@
         <v>1399</v>
       </c>
       <c r="B1400" s="2" t="s">
+        <v>6105</v>
+      </c>
+      <c r="C1400" s="2" t="s">
+        <v>6106</v>
+      </c>
+      <c r="D1400" s="2" t="s">
         <v>6107</v>
       </c>
-      <c r="C1400" s="2" t="s">
+      <c r="E1400" s="2" t="s">
+        <v>6927</v>
+      </c>
+      <c r="F1400" s="2" t="s">
         <v>6108</v>
-      </c>
-      <c r="D1400" s="2" t="s">
-        <v>6109</v>
-      </c>
-      <c r="E1400" s="2" t="s">
-        <v>6929</v>
-      </c>
-      <c r="F1400" s="2" t="s">
-        <v>6110</v>
       </c>
       <c r="G1400" s="3">
         <v>2</v>
       </c>
       <c r="H1400" s="2" t="s">
-        <v>6111</v>
+        <v>6109</v>
       </c>
       <c r="I1400" s="2" t="s">
         <v>781</v>
@@ -63349,25 +63351,25 @@
         <v>1400</v>
       </c>
       <c r="B1401" s="2" t="s">
-        <v>6112</v>
+        <v>6110</v>
       </c>
       <c r="C1401" s="2" t="s">
-        <v>6927</v>
+        <v>6925</v>
       </c>
       <c r="D1401" s="2" t="s">
+        <v>6926</v>
+      </c>
+      <c r="E1401" s="2" t="s">
+        <v>6929</v>
+      </c>
+      <c r="F1401" s="2" t="s">
         <v>6928</v>
-      </c>
-      <c r="E1401" s="2" t="s">
-        <v>6931</v>
-      </c>
-      <c r="F1401" s="2" t="s">
-        <v>6930</v>
       </c>
       <c r="G1401" s="3">
         <v>2</v>
       </c>
       <c r="H1401" s="2" t="s">
-        <v>6113</v>
+        <v>6111</v>
       </c>
       <c r="I1401" s="2" t="s">
         <v>781</v>
@@ -63378,25 +63380,25 @@
         <v>1401</v>
       </c>
       <c r="B1402" s="2" t="s">
-        <v>6790</v>
+        <v>6788</v>
       </c>
       <c r="C1402" s="2" t="s">
+        <v>6112</v>
+      </c>
+      <c r="D1402" s="2" t="s">
+        <v>6113</v>
+      </c>
+      <c r="E1402" s="2" t="s">
         <v>6114</v>
       </c>
-      <c r="D1402" s="2" t="s">
+      <c r="F1402" s="2" t="s">
         <v>6115</v>
-      </c>
-      <c r="E1402" s="2" t="s">
-        <v>6116</v>
-      </c>
-      <c r="F1402" s="2" t="s">
-        <v>6117</v>
       </c>
       <c r="G1402" s="3">
         <v>2</v>
       </c>
       <c r="H1402" s="2" t="s">
-        <v>6118</v>
+        <v>6116</v>
       </c>
       <c r="I1402" s="2" t="s">
         <v>15</v>
@@ -63407,25 +63409,25 @@
         <v>1402</v>
       </c>
       <c r="B1403" s="2" t="s">
+        <v>6117</v>
+      </c>
+      <c r="C1403" s="2" t="s">
+        <v>6118</v>
+      </c>
+      <c r="D1403" s="2" t="s">
         <v>6119</v>
       </c>
-      <c r="C1403" s="2" t="s">
+      <c r="E1403" s="2" t="s">
         <v>6120</v>
       </c>
-      <c r="D1403" s="2" t="s">
+      <c r="F1403" s="2" t="s">
         <v>6121</v>
-      </c>
-      <c r="E1403" s="2" t="s">
-        <v>6122</v>
-      </c>
-      <c r="F1403" s="2" t="s">
-        <v>6123</v>
       </c>
       <c r="G1403" s="3">
         <v>3</v>
       </c>
       <c r="H1403" s="2" t="s">
-        <v>6124</v>
+        <v>6122</v>
       </c>
       <c r="I1403" s="2" t="s">
         <v>15</v>
@@ -63436,25 +63438,25 @@
         <v>1403</v>
       </c>
       <c r="B1404" s="2" t="s">
+        <v>6123</v>
+      </c>
+      <c r="C1404" s="2" t="s">
+        <v>6124</v>
+      </c>
+      <c r="D1404" s="2" t="s">
         <v>6125</v>
       </c>
-      <c r="C1404" s="2" t="s">
+      <c r="E1404" s="2" t="s">
         <v>6126</v>
       </c>
-      <c r="D1404" s="2" t="s">
+      <c r="F1404" s="2" t="s">
         <v>6127</v>
-      </c>
-      <c r="E1404" s="2" t="s">
-        <v>6128</v>
-      </c>
-      <c r="F1404" s="2" t="s">
-        <v>6129</v>
       </c>
       <c r="G1404" s="3">
         <v>2</v>
       </c>
       <c r="H1404" s="2" t="s">
-        <v>6130</v>
+        <v>6128</v>
       </c>
       <c r="I1404" s="2" t="s">
         <v>15</v>

--- a/salf/丙種職業安全衛生業務主管題庫.xlsx
+++ b/salf/丙種職業安全衛生業務主管題庫.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25f5a1833553ad9e/文件/GitHub/drher.github.io/salf/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{6F768573-F417-4A9D-97DF-CDB2866B7AA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D3952EE9-47F5-4631-AB5E-6A08D5AAE7F7}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{6F768573-F417-4A9D-97DF-CDB2866B7AA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5FF75CD7-3124-4A1D-AC44-A6FC061BCD6A}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9463" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9788" uniqueCount="7087">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9788" uniqueCount="7088">
   <si>
     <t>題號</t>
   </si>
@@ -22686,6 +22686,10 @@
   </si>
   <si>
     <t>沸點</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>閃火點</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -47728,7 +47732,7 @@
         <v>3759</v>
       </c>
       <c r="F850" s="2" t="s">
-        <v>3770</v>
+        <v>7087</v>
       </c>
       <c r="G850" s="3">
         <v>2</v>

--- a/salf/丙種職業安全衛生業務主管題庫.xlsx
+++ b/salf/丙種職業安全衛生業務主管題庫.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\drher\OneDrive\文件\GitHub\drher.github.io\salf\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25f5a1833553ad9e/文件/GitHub/drher.github.io/salf/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D28A871C-448F-401F-B0AB-19E2AE007041}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="15397" windowHeight="8751" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9463" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="乾淨題庫" sheetId="1" r:id="rId1"/>
@@ -28523,7 +28523,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="176" spans="1:9" ht="46.3">
+    <row r="176" spans="1:9" ht="61.75">
       <c r="A176" s="2">
         <v>175</v>
       </c>
@@ -33076,7 +33076,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="333" spans="1:9" ht="30.9">
+    <row r="333" spans="1:9" ht="46.3">
       <c r="A333" s="2">
         <v>332</v>
       </c>
@@ -37598,7 +37598,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="489" spans="1:9" ht="30.9">
+    <row r="489" spans="1:9" ht="46.3">
       <c r="A489" s="2">
         <v>488</v>
       </c>
@@ -39539,7 +39539,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="556" spans="1:9" ht="30.9">
+    <row r="556" spans="1:9" ht="46.3">
       <c r="A556" s="2">
         <v>555</v>
       </c>
@@ -45917,7 +45917,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="776" spans="1:9" ht="30.9">
+    <row r="776" spans="1:9" ht="46.3">
       <c r="A776" s="2">
         <v>775</v>
       </c>
@@ -58522,7 +58522,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="1211" spans="1:9" ht="30.9">
+    <row r="1211" spans="1:9" ht="46.3">
       <c r="A1211" s="2">
         <v>1210</v>
       </c>
@@ -62578,7 +62578,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="1351" spans="1:9" ht="30.9">
+    <row r="1351" spans="1:9" ht="46.3">
       <c r="A1351" s="2">
         <v>1350</v>
       </c>
@@ -62636,7 +62636,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="1353" spans="1:9" ht="30.9">
+    <row r="1353" spans="1:9" ht="46.3">
       <c r="A1353" s="2">
         <v>1352</v>
       </c>
@@ -63593,7 +63593,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="1386" spans="1:9" ht="77.150000000000006">
+    <row r="1386" spans="1:9" ht="92.6">
       <c r="A1386" s="2">
         <v>1385</v>
       </c>

--- a/salf/丙種職業安全衛生業務主管題庫.xlsx
+++ b/salf/丙種職業安全衛生業務主管題庫.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25f5a1833553ad9e/文件/GitHub/drher.github.io/salf/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="42" documentId="13_ncr:1_{D28A871C-448F-401F-B0AB-19E2AE007041}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7DF9FEF3-ED1A-4DBD-B93B-BCA03A49C8DE}"/>
+  <xr:revisionPtr revIDLastSave="43" documentId="13_ncr:1_{D28A871C-448F-401F-B0AB-19E2AE007041}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F5AD8543-B84F-4C85-8713-0DE76D4FC51B}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9463" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21411,10 +21411,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>依職業安全衛生設施規則規定, 於時量平均音壓級為 90dBA 之戰音環境下, 勞工一天容許暴露時間至多幾小時 ?</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>大眾傳播業</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -23043,6 +23039,10 @@
   </si>
   <si>
     <t>廢棄物處理作業</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>依職業安全衛生設施規則規定, 於時量平均音壓級為 90dBA 之噪音環境下, 勞工一天容許暴露時間至多幾小時 ?</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -23952,19 +23952,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>7046</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>7047</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>7048</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>91</v>
       </c>
       <c r="E17" s="2" t="s">
+        <v>7048</v>
+      </c>
+      <c r="F17" s="2" t="s">
         <v>7049</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>7050</v>
       </c>
       <c r="G17" s="3">
         <v>4</v>
@@ -24684,10 +24684,10 @@
         <v>219</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>7019</v>
+        <v>7018</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>7018</v>
+        <v>7017</v>
       </c>
       <c r="G42" s="3">
         <v>1</v>
@@ -24832,7 +24832,7 @@
         <v>244</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>6829</v>
+        <v>6828</v>
       </c>
       <c r="G47" s="3">
         <v>1</v>
@@ -24849,7 +24849,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>6827</v>
+        <v>6826</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>246</v>
@@ -24861,7 +24861,7 @@
         <v>247</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>6828</v>
+        <v>6827</v>
       </c>
       <c r="G48" s="3">
         <v>3</v>
@@ -24890,7 +24890,7 @@
         <v>252</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>6830</v>
+        <v>6829</v>
       </c>
       <c r="G49" s="3">
         <v>3</v>
@@ -25052,19 +25052,19 @@
         <v>54</v>
       </c>
       <c r="B55" s="2" t="s">
+        <v>6900</v>
+      </c>
+      <c r="C55" s="2" t="s">
         <v>6901</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="D55" s="2" t="s">
         <v>6902</v>
       </c>
-      <c r="D55" s="2" t="s">
+      <c r="E55" s="2" t="s">
         <v>6903</v>
       </c>
-      <c r="E55" s="2" t="s">
+      <c r="F55" s="2" t="s">
         <v>6904</v>
-      </c>
-      <c r="F55" s="2" t="s">
-        <v>6905</v>
       </c>
       <c r="G55" s="3">
         <v>2</v>
@@ -25432,16 +25432,16 @@
         <v>329</v>
       </c>
       <c r="C68" s="2" t="s">
+        <v>6771</v>
+      </c>
+      <c r="D68" s="2" t="s">
         <v>6772</v>
       </c>
-      <c r="D68" s="2" t="s">
+      <c r="E68" s="2" t="s">
         <v>6773</v>
       </c>
-      <c r="E68" s="2" t="s">
+      <c r="F68" s="2" t="s">
         <v>6774</v>
-      </c>
-      <c r="F68" s="2" t="s">
-        <v>6775</v>
       </c>
       <c r="G68" s="3">
         <v>3</v>
@@ -25470,7 +25470,7 @@
         <v>334</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>6749</v>
+        <v>6748</v>
       </c>
       <c r="G69" s="3">
         <v>4</v>
@@ -25487,7 +25487,7 @@
         <v>69</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>6748</v>
+        <v>6747</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>336</v>
@@ -25499,7 +25499,7 @@
         <v>337</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>6750</v>
+        <v>6749</v>
       </c>
       <c r="G70" s="3">
         <v>4</v>
@@ -25632,7 +25632,7 @@
         <v>74</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>6988</v>
+        <v>6987</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>353</v>
@@ -25777,19 +25777,19 @@
         <v>79</v>
       </c>
       <c r="B80" s="2" t="s">
+        <v>7103</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>7100</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>7101</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>7102</v>
+      </c>
+      <c r="F80" s="2" t="s">
         <v>7104</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>7101</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>7102</v>
-      </c>
-      <c r="E80" s="2" t="s">
-        <v>7103</v>
-      </c>
-      <c r="F80" s="2" t="s">
-        <v>7105</v>
       </c>
       <c r="G80" s="3">
         <v>4</v>
@@ -25980,7 +25980,7 @@
         <v>86</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>7070</v>
+        <v>7069</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>406</v>
@@ -26183,7 +26183,7 @@
         <v>93</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>6860</v>
+        <v>6859</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>435</v>
@@ -26279,7 +26279,7 @@
         <v>450</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>7055</v>
+        <v>7054</v>
       </c>
       <c r="F97" s="2" t="s">
         <v>451</v>
@@ -26299,19 +26299,19 @@
         <v>97</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>7053</v>
+        <v>7052</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>453</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>7054</v>
+        <v>7053</v>
       </c>
       <c r="E98" s="2" t="s">
+        <v>7055</v>
+      </c>
+      <c r="F98" s="2" t="s">
         <v>7056</v>
-      </c>
-      <c r="F98" s="2" t="s">
-        <v>7057</v>
       </c>
       <c r="G98" s="3">
         <v>2</v>
@@ -27033,10 +27033,10 @@
         <v>562</v>
       </c>
       <c r="E123" s="2" t="s">
+        <v>6731</v>
+      </c>
+      <c r="F123" s="2" t="s">
         <v>6732</v>
-      </c>
-      <c r="F123" s="2" t="s">
-        <v>6733</v>
       </c>
       <c r="G123" s="3">
         <v>3</v>
@@ -27259,16 +27259,16 @@
         <v>599</v>
       </c>
       <c r="C131" s="2" t="s">
+        <v>6972</v>
+      </c>
+      <c r="D131" s="2" t="s">
         <v>6973</v>
-      </c>
-      <c r="D131" s="2" t="s">
-        <v>6974</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>600</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>6975</v>
+        <v>6974</v>
       </c>
       <c r="G131" s="3">
         <v>3</v>
@@ -27384,7 +27384,7 @@
         <v>618</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>6764</v>
+        <v>6763</v>
       </c>
       <c r="G135" s="3">
         <v>3</v>
@@ -27633,7 +27633,7 @@
         <v>143</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>6867</v>
+        <v>6866</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>445</v>
@@ -27923,7 +27923,7 @@
         <v>153</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>7021</v>
+        <v>7020</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>700</v>
@@ -27935,7 +27935,7 @@
         <v>702</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>7022</v>
+        <v>7021</v>
       </c>
       <c r="G154" s="3">
         <v>4</v>
@@ -28445,7 +28445,7 @@
         <v>171</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>6855</v>
+        <v>6854</v>
       </c>
       <c r="C172" s="2" t="s">
         <v>770</v>
@@ -28454,10 +28454,10 @@
         <v>771</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>6856</v>
+        <v>6855</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>6851</v>
+        <v>6850</v>
       </c>
       <c r="G172" s="3">
         <v>4</v>
@@ -28921,7 +28921,7 @@
         <v>835</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>6984</v>
+        <v>6983</v>
       </c>
       <c r="G188" s="3">
         <v>3</v>
@@ -28973,7 +28973,7 @@
         <v>841</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>7071</v>
+        <v>7070</v>
       </c>
       <c r="E190" s="2" t="s">
         <v>842</v>
@@ -29344,7 +29344,7 @@
         <v>202</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>7076</v>
+        <v>7075</v>
       </c>
       <c r="C203" s="2" t="s">
         <v>907</v>
@@ -29373,7 +29373,7 @@
         <v>203</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>7075</v>
+        <v>7074</v>
       </c>
       <c r="C204" s="2" t="s">
         <v>911</v>
@@ -29402,19 +29402,19 @@
         <v>204</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>6761</v>
+        <v>6760</v>
       </c>
       <c r="C205" s="2" t="s">
         <v>916</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>6762</v>
+        <v>6761</v>
       </c>
       <c r="E205" s="2" t="s">
         <v>917</v>
       </c>
       <c r="F205" s="2" t="s">
-        <v>6763</v>
+        <v>6762</v>
       </c>
       <c r="G205" s="3">
         <v>2</v>
@@ -29956,16 +29956,16 @@
         <v>1020</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>7072</v>
+        <v>7071</v>
       </c>
       <c r="D224" s="2" t="s">
         <v>1021</v>
       </c>
       <c r="E224" s="2" t="s">
+        <v>7072</v>
+      </c>
+      <c r="F224" s="2" t="s">
         <v>7073</v>
-      </c>
-      <c r="F224" s="2" t="s">
-        <v>7074</v>
       </c>
       <c r="G224" s="3">
         <v>3</v>
@@ -30072,16 +30072,16 @@
         <v>1038</v>
       </c>
       <c r="C228" s="2" t="s">
+        <v>6793</v>
+      </c>
+      <c r="D228" s="2" t="s">
         <v>6794</v>
       </c>
-      <c r="D228" s="2" t="s">
+      <c r="E228" s="2" t="s">
         <v>6795</v>
       </c>
-      <c r="E228" s="2" t="s">
+      <c r="F228" s="2" t="s">
         <v>6796</v>
-      </c>
-      <c r="F228" s="2" t="s">
-        <v>6797</v>
       </c>
       <c r="G228" s="3">
         <v>3</v>
@@ -30272,7 +30272,7 @@
         <v>234</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>6844</v>
+        <v>6843</v>
       </c>
       <c r="C235" s="2" t="s">
         <v>1069</v>
@@ -30284,7 +30284,7 @@
         <v>996</v>
       </c>
       <c r="F235" s="2" t="s">
-        <v>6845</v>
+        <v>6844</v>
       </c>
       <c r="G235" s="3">
         <v>1</v>
@@ -30591,7 +30591,7 @@
         <v>245</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>7092</v>
+        <v>7091</v>
       </c>
       <c r="C246" s="2" t="s">
         <v>1116</v>
@@ -30719,7 +30719,7 @@
         <v>1138</v>
       </c>
       <c r="F250" s="2" t="s">
-        <v>6766</v>
+        <v>6765</v>
       </c>
       <c r="G250" s="3">
         <v>1</v>
@@ -30768,13 +30768,13 @@
         <v>1146</v>
       </c>
       <c r="C252" s="2" t="s">
+        <v>6797</v>
+      </c>
+      <c r="D252" s="2" t="s">
         <v>6798</v>
       </c>
-      <c r="D252" s="2" t="s">
+      <c r="E252" s="2" t="s">
         <v>6799</v>
-      </c>
-      <c r="E252" s="2" t="s">
-        <v>6800</v>
       </c>
       <c r="F252" s="2" t="s">
         <v>1147</v>
@@ -30910,10 +30910,10 @@
         <v>256</v>
       </c>
       <c r="B257" s="2" t="s">
+        <v>6931</v>
+      </c>
+      <c r="C257" s="2" t="s">
         <v>6932</v>
-      </c>
-      <c r="C257" s="2" t="s">
-        <v>6933</v>
       </c>
       <c r="D257" s="2" t="s">
         <v>1166</v>
@@ -30922,7 +30922,7 @@
         <v>1161</v>
       </c>
       <c r="F257" s="2" t="s">
-        <v>6934</v>
+        <v>6933</v>
       </c>
       <c r="G257" s="3">
         <v>1</v>
@@ -31519,7 +31519,7 @@
         <v>277</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>6989</v>
+        <v>6988</v>
       </c>
       <c r="C278" s="2" t="s">
         <v>1269</v>
@@ -31609,16 +31609,16 @@
         <v>1276</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>7033</v>
+        <v>7032</v>
       </c>
       <c r="D281" s="2" t="s">
         <v>1277</v>
       </c>
       <c r="E281" s="2" t="s">
+        <v>7033</v>
+      </c>
+      <c r="F281" s="2" t="s">
         <v>7034</v>
-      </c>
-      <c r="F281" s="2" t="s">
-        <v>7035</v>
       </c>
       <c r="G281" s="3">
         <v>2</v>
@@ -31722,16 +31722,16 @@
         <v>284</v>
       </c>
       <c r="B285" s="2" t="s">
+        <v>6744</v>
+      </c>
+      <c r="C285" s="2" t="s">
         <v>6745</v>
-      </c>
-      <c r="C285" s="2" t="s">
-        <v>6746</v>
       </c>
       <c r="D285" s="2" t="s">
         <v>1289</v>
       </c>
       <c r="E285" s="2" t="s">
-        <v>6747</v>
+        <v>6746</v>
       </c>
       <c r="F285" s="2" t="s">
         <v>1290</v>
@@ -31754,16 +31754,16 @@
         <v>1291</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>6791</v>
+        <v>6790</v>
       </c>
       <c r="D286" s="2" t="s">
         <v>1254</v>
       </c>
       <c r="E286" s="2" t="s">
+        <v>6791</v>
+      </c>
+      <c r="F286" s="2" t="s">
         <v>6792</v>
-      </c>
-      <c r="F286" s="2" t="s">
-        <v>6793</v>
       </c>
       <c r="G286" s="3">
         <v>2</v>
@@ -31896,19 +31896,19 @@
         <v>290</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>7084</v>
+        <v>7083</v>
       </c>
       <c r="C291" s="2" t="s">
         <v>1309</v>
       </c>
       <c r="D291" s="2" t="s">
-        <v>7085</v>
+        <v>7084</v>
       </c>
       <c r="E291" s="2" t="s">
         <v>1310</v>
       </c>
       <c r="F291" s="2" t="s">
-        <v>7086</v>
+        <v>7085</v>
       </c>
       <c r="G291" s="3">
         <v>2</v>
@@ -31934,10 +31934,10 @@
         <v>6002</v>
       </c>
       <c r="E292" s="2" t="s">
-        <v>7088</v>
+        <v>7087</v>
       </c>
       <c r="F292" s="2" t="s">
-        <v>7087</v>
+        <v>7086</v>
       </c>
       <c r="G292" s="3">
         <v>1</v>
@@ -32012,19 +32012,19 @@
         <v>294</v>
       </c>
       <c r="B295" s="2" t="s">
+        <v>7092</v>
+      </c>
+      <c r="C295" s="2" t="s">
         <v>7093</v>
       </c>
-      <c r="C295" s="2" t="s">
+      <c r="D295" s="2" t="s">
+        <v>7095</v>
+      </c>
+      <c r="E295" s="2" t="s">
+        <v>7096</v>
+      </c>
+      <c r="F295" s="2" t="s">
         <v>7094</v>
-      </c>
-      <c r="D295" s="2" t="s">
-        <v>7096</v>
-      </c>
-      <c r="E295" s="2" t="s">
-        <v>7097</v>
-      </c>
-      <c r="F295" s="2" t="s">
-        <v>7095</v>
       </c>
       <c r="G295" s="3">
         <v>3</v>
@@ -32537,7 +32537,7 @@
         <v>1411</v>
       </c>
       <c r="C313" s="2" t="s">
-        <v>7066</v>
+        <v>7065</v>
       </c>
       <c r="D313" s="2" t="s">
         <v>1412</v>
@@ -33987,16 +33987,16 @@
         <v>1667</v>
       </c>
       <c r="C363" s="2" t="s">
-        <v>6817</v>
+        <v>6816</v>
       </c>
       <c r="D363" s="2" t="s">
         <v>1668</v>
       </c>
       <c r="E363" s="2" t="s">
+        <v>6817</v>
+      </c>
+      <c r="F363" s="2" t="s">
         <v>6818</v>
-      </c>
-      <c r="F363" s="2" t="s">
-        <v>6819</v>
       </c>
       <c r="G363" s="3">
         <v>1</v>
@@ -34054,7 +34054,7 @@
         <v>1679</v>
       </c>
       <c r="F365" s="2" t="s">
-        <v>6849</v>
+        <v>6848</v>
       </c>
       <c r="G365" s="3">
         <v>1</v>
@@ -34100,7 +34100,7 @@
         <v>366</v>
       </c>
       <c r="B367" s="2" t="s">
-        <v>6736</v>
+        <v>6735</v>
       </c>
       <c r="C367" s="2" t="s">
         <v>1687</v>
@@ -34248,10 +34248,10 @@
         <v>1716</v>
       </c>
       <c r="C372" s="2" t="s">
-        <v>6822</v>
+        <v>6821</v>
       </c>
       <c r="D372" s="2" t="s">
-        <v>6821</v>
+        <v>6820</v>
       </c>
       <c r="E372" s="2" t="s">
         <v>1717</v>
@@ -34596,16 +34596,16 @@
         <v>1773</v>
       </c>
       <c r="C384" s="2" t="s">
+        <v>7077</v>
+      </c>
+      <c r="D384" s="2" t="s">
         <v>7078</v>
-      </c>
-      <c r="D384" s="2" t="s">
-        <v>7079</v>
       </c>
       <c r="E384" s="2" t="s">
         <v>1774</v>
       </c>
       <c r="F384" s="2" t="s">
-        <v>7080</v>
+        <v>7079</v>
       </c>
       <c r="G384" s="3">
         <v>3</v>
@@ -34634,7 +34634,7 @@
         <v>1777</v>
       </c>
       <c r="F385" s="2" t="s">
-        <v>7081</v>
+        <v>7080</v>
       </c>
       <c r="G385" s="3">
         <v>3</v>
@@ -34709,7 +34709,7 @@
         <v>387</v>
       </c>
       <c r="B388" s="2" t="s">
-        <v>6951</v>
+        <v>6950</v>
       </c>
       <c r="C388" s="2" t="s">
         <v>1788</v>
@@ -34721,7 +34721,7 @@
         <v>1789</v>
       </c>
       <c r="F388" s="2" t="s">
-        <v>6952</v>
+        <v>6951</v>
       </c>
       <c r="G388" s="3">
         <v>4</v>
@@ -35086,7 +35086,7 @@
         <v>400</v>
       </c>
       <c r="B401" s="2" t="s">
-        <v>6743</v>
+        <v>6742</v>
       </c>
       <c r="C401" s="2" t="s">
         <v>1853</v>
@@ -35098,7 +35098,7 @@
         <v>1855</v>
       </c>
       <c r="F401" s="2" t="s">
-        <v>6744</v>
+        <v>6743</v>
       </c>
       <c r="G401" s="3">
         <v>3</v>
@@ -35867,10 +35867,10 @@
         <v>427</v>
       </c>
       <c r="B428" s="2" t="s">
+        <v>6952</v>
+      </c>
+      <c r="C428" s="2" t="s">
         <v>6953</v>
-      </c>
-      <c r="C428" s="2" t="s">
-        <v>6954</v>
       </c>
       <c r="D428" s="2" t="s">
         <v>1985</v>
@@ -35896,7 +35896,7 @@
         <v>428</v>
       </c>
       <c r="B429" s="2" t="s">
-        <v>6820</v>
+        <v>6819</v>
       </c>
       <c r="C429" s="2" t="s">
         <v>1989</v>
@@ -35908,7 +35908,7 @@
         <v>1991</v>
       </c>
       <c r="F429" s="2" t="s">
-        <v>7051</v>
+        <v>7050</v>
       </c>
       <c r="G429" s="3">
         <v>3</v>
@@ -35983,19 +35983,19 @@
         <v>431</v>
       </c>
       <c r="B432" s="2" t="s">
-        <v>6810</v>
+        <v>6809</v>
       </c>
       <c r="C432" s="2" t="s">
         <v>2003</v>
       </c>
       <c r="D432" s="2" t="s">
-        <v>6812</v>
+        <v>6811</v>
       </c>
       <c r="E432" s="2" t="s">
         <v>2004</v>
       </c>
       <c r="F432" s="2" t="s">
-        <v>6804</v>
+        <v>6803</v>
       </c>
       <c r="G432" s="3">
         <v>4</v>
@@ -36015,7 +36015,7 @@
         <v>2005</v>
       </c>
       <c r="C433" s="2" t="s">
-        <v>6811</v>
+        <v>6810</v>
       </c>
       <c r="D433" s="2" t="s">
         <v>2006</v>
@@ -36041,19 +36041,19 @@
         <v>433</v>
       </c>
       <c r="B434" s="2" t="s">
-        <v>6938</v>
+        <v>6937</v>
       </c>
       <c r="C434" s="2" t="s">
+        <v>6934</v>
+      </c>
+      <c r="D434" s="2" t="s">
         <v>6935</v>
-      </c>
-      <c r="D434" s="2" t="s">
-        <v>6936</v>
       </c>
       <c r="E434" s="2" t="s">
         <v>2008</v>
       </c>
       <c r="F434" s="2" t="s">
-        <v>6937</v>
+        <v>6936</v>
       </c>
       <c r="G434" s="3">
         <v>1</v>
@@ -36128,7 +36128,7 @@
         <v>436</v>
       </c>
       <c r="B437" s="2" t="s">
-        <v>6976</v>
+        <v>6975</v>
       </c>
       <c r="C437" s="2" t="s">
         <v>1990</v>
@@ -36137,10 +36137,10 @@
         <v>2019</v>
       </c>
       <c r="E437" s="2" t="s">
+        <v>6976</v>
+      </c>
+      <c r="F437" s="2" t="s">
         <v>6977</v>
-      </c>
-      <c r="F437" s="2" t="s">
-        <v>6978</v>
       </c>
       <c r="G437" s="3">
         <v>1</v>
@@ -36192,7 +36192,7 @@
         <v>2025</v>
       </c>
       <c r="D439" s="2" t="s">
-        <v>6831</v>
+        <v>6830</v>
       </c>
       <c r="E439" s="2" t="s">
         <v>2026</v>
@@ -36418,7 +36418,7 @@
         <v>446</v>
       </c>
       <c r="B447" s="2" t="s">
-        <v>6955</v>
+        <v>6954</v>
       </c>
       <c r="C447" s="2" t="s">
         <v>2050</v>
@@ -36430,7 +36430,7 @@
         <v>2052</v>
       </c>
       <c r="F447" s="2" t="s">
-        <v>6956</v>
+        <v>6955</v>
       </c>
       <c r="G447" s="3">
         <v>4</v>
@@ -36717,10 +36717,10 @@
         <v>2093</v>
       </c>
       <c r="E457" s="2" t="s">
+        <v>6736</v>
+      </c>
+      <c r="F457" s="2" t="s">
         <v>6737</v>
-      </c>
-      <c r="F457" s="2" t="s">
-        <v>6738</v>
       </c>
       <c r="G457" s="3">
         <v>4</v>
@@ -36940,7 +36940,7 @@
         <v>464</v>
       </c>
       <c r="B465" s="2" t="s">
-        <v>6786</v>
+        <v>6785</v>
       </c>
       <c r="C465" s="2" t="s">
         <v>2021</v>
@@ -36952,7 +36952,7 @@
         <v>2130</v>
       </c>
       <c r="F465" s="2" t="s">
-        <v>6787</v>
+        <v>6786</v>
       </c>
       <c r="G465" s="3">
         <v>4</v>
@@ -36998,10 +36998,10 @@
         <v>466</v>
       </c>
       <c r="B467" s="2" t="s">
+        <v>6870</v>
+      </c>
+      <c r="C467" s="2" t="s">
         <v>6871</v>
-      </c>
-      <c r="C467" s="2" t="s">
-        <v>6872</v>
       </c>
       <c r="D467" s="2" t="s">
         <v>2137</v>
@@ -37143,7 +37143,7 @@
         <v>471</v>
       </c>
       <c r="B472" s="2" t="s">
-        <v>6825</v>
+        <v>6824</v>
       </c>
       <c r="C472" s="2" t="s">
         <v>2163</v>
@@ -37155,7 +37155,7 @@
         <v>2165</v>
       </c>
       <c r="F472" s="2" t="s">
-        <v>6826</v>
+        <v>6825</v>
       </c>
       <c r="G472" s="3">
         <v>3</v>
@@ -37404,16 +37404,16 @@
         <v>480</v>
       </c>
       <c r="B481" s="2" t="s">
+        <v>6941</v>
+      </c>
+      <c r="C481" s="2" t="s">
         <v>6942</v>
-      </c>
-      <c r="C481" s="2" t="s">
-        <v>6943</v>
       </c>
       <c r="D481" s="2" t="s">
         <v>2201</v>
       </c>
       <c r="E481" s="2" t="s">
-        <v>6944</v>
+        <v>6943</v>
       </c>
       <c r="F481" s="2" t="s">
         <v>2203</v>
@@ -37480,7 +37480,7 @@
         <v>2</v>
       </c>
       <c r="H483" s="2" t="s">
-        <v>6926</v>
+        <v>6925</v>
       </c>
       <c r="I483" s="2" t="s">
         <v>1366</v>
@@ -37549,19 +37549,19 @@
         <v>485</v>
       </c>
       <c r="B486" s="2" t="s">
+        <v>6926</v>
+      </c>
+      <c r="C486" s="2" t="s">
         <v>6927</v>
       </c>
-      <c r="C486" s="2" t="s">
+      <c r="D486" s="2" t="s">
         <v>6928</v>
       </c>
-      <c r="D486" s="2" t="s">
+      <c r="E486" s="2" t="s">
         <v>6929</v>
       </c>
-      <c r="E486" s="2" t="s">
+      <c r="F486" s="2" t="s">
         <v>6930</v>
-      </c>
-      <c r="F486" s="2" t="s">
-        <v>6931</v>
       </c>
       <c r="G486" s="3">
         <v>3</v>
@@ -38185,19 +38185,19 @@
         <v>507</v>
       </c>
       <c r="B508" s="2" t="s">
+        <v>6836</v>
+      </c>
+      <c r="C508" s="2" t="s">
         <v>6837</v>
-      </c>
-      <c r="C508" s="2" t="s">
-        <v>6838</v>
       </c>
       <c r="D508" s="2" t="s">
         <v>2328</v>
       </c>
       <c r="E508" s="2" t="s">
+        <v>6838</v>
+      </c>
+      <c r="F508" s="2" t="s">
         <v>6839</v>
-      </c>
-      <c r="F508" s="2" t="s">
-        <v>6840</v>
       </c>
       <c r="G508" s="3">
         <v>2</v>
@@ -38446,7 +38446,7 @@
         <v>516</v>
       </c>
       <c r="B517" s="2" t="s">
-        <v>6972</v>
+        <v>6971</v>
       </c>
       <c r="C517" s="2" t="s">
         <v>2365</v>
@@ -38458,7 +38458,7 @@
         <v>2366</v>
       </c>
       <c r="F517" s="2" t="s">
-        <v>6971</v>
+        <v>6970</v>
       </c>
       <c r="G517" s="3">
         <v>2</v>
@@ -38475,10 +38475,10 @@
         <v>517</v>
       </c>
       <c r="B518" s="2" t="s">
-        <v>7099</v>
+        <v>7098</v>
       </c>
       <c r="C518" s="2" t="s">
-        <v>6816</v>
+        <v>6815</v>
       </c>
       <c r="D518" s="2" t="s">
         <v>2368</v>
@@ -38504,7 +38504,7 @@
         <v>518</v>
       </c>
       <c r="B519" s="2" t="s">
-        <v>7098</v>
+        <v>7097</v>
       </c>
       <c r="C519" s="2" t="s">
         <v>2372</v>
@@ -38707,19 +38707,19 @@
         <v>525</v>
       </c>
       <c r="B526" s="2" t="s">
-        <v>7006</v>
+        <v>7005</v>
       </c>
       <c r="C526" s="2" t="s">
         <v>2405</v>
       </c>
       <c r="D526" s="2" t="s">
-        <v>7007</v>
+        <v>7006</v>
       </c>
       <c r="E526" s="2" t="s">
         <v>2406</v>
       </c>
       <c r="F526" s="2" t="s">
-        <v>7008</v>
+        <v>7007</v>
       </c>
       <c r="G526" s="3">
         <v>4</v>
@@ -39026,7 +39026,7 @@
         <v>536</v>
       </c>
       <c r="B537" s="2" t="s">
-        <v>6909</v>
+        <v>6908</v>
       </c>
       <c r="C537" s="2" t="s">
         <v>2447</v>
@@ -39035,10 +39035,10 @@
         <v>1717</v>
       </c>
       <c r="E537" s="2" t="s">
+        <v>6909</v>
+      </c>
+      <c r="F537" s="2" t="s">
         <v>6910</v>
-      </c>
-      <c r="F537" s="2" t="s">
-        <v>6911</v>
       </c>
       <c r="G537" s="3">
         <v>2</v>
@@ -39203,16 +39203,16 @@
         <v>6649</v>
       </c>
       <c r="C543" s="2" t="s">
+        <v>6880</v>
+      </c>
+      <c r="D543" s="2" t="s">
         <v>6881</v>
-      </c>
-      <c r="D543" s="2" t="s">
-        <v>6882</v>
       </c>
       <c r="E543" s="2" t="s">
         <v>2458</v>
       </c>
       <c r="F543" s="2" t="s">
-        <v>6883</v>
+        <v>6882</v>
       </c>
       <c r="G543" s="3">
         <v>1</v>
@@ -39293,13 +39293,13 @@
         <v>2468</v>
       </c>
       <c r="D546" s="2" t="s">
+        <v>7088</v>
+      </c>
+      <c r="E546" s="2" t="s">
         <v>7089</v>
       </c>
-      <c r="E546" s="2" t="s">
+      <c r="F546" s="2" t="s">
         <v>7090</v>
-      </c>
-      <c r="F546" s="2" t="s">
-        <v>7091</v>
       </c>
       <c r="G546" s="3">
         <v>2</v>
@@ -39693,7 +39693,7 @@
         <v>559</v>
       </c>
       <c r="B560" s="2" t="s">
-        <v>6815</v>
+        <v>6814</v>
       </c>
       <c r="C560" s="2" t="s">
         <v>2523</v>
@@ -40012,7 +40012,7 @@
         <v>570</v>
       </c>
       <c r="B571" s="2" t="s">
-        <v>6751</v>
+        <v>6750</v>
       </c>
       <c r="C571" s="2" t="s">
         <v>2574</v>
@@ -40024,7 +40024,7 @@
         <v>2563</v>
       </c>
       <c r="F571" s="2" t="s">
-        <v>6752</v>
+        <v>6751</v>
       </c>
       <c r="G571" s="3">
         <v>4</v>
@@ -40508,16 +40508,16 @@
         <v>2632</v>
       </c>
       <c r="C588" s="2" t="s">
+        <v>6965</v>
+      </c>
+      <c r="D588" s="2" t="s">
         <v>6966</v>
       </c>
-      <c r="D588" s="2" t="s">
+      <c r="E588" s="2" t="s">
         <v>6967</v>
       </c>
-      <c r="E588" s="2" t="s">
+      <c r="F588" s="2" t="s">
         <v>6968</v>
-      </c>
-      <c r="F588" s="2" t="s">
-        <v>6969</v>
       </c>
       <c r="G588" s="3">
         <v>4</v>
@@ -40563,19 +40563,19 @@
         <v>589</v>
       </c>
       <c r="B590" s="2" t="s">
-        <v>6945</v>
+        <v>6944</v>
       </c>
       <c r="C590" s="2" t="s">
         <v>2640</v>
       </c>
       <c r="D590" s="2" t="s">
+        <v>6945</v>
+      </c>
+      <c r="E590" s="2" t="s">
         <v>6946</v>
       </c>
-      <c r="E590" s="2" t="s">
+      <c r="F590" s="2" t="s">
         <v>6947</v>
-      </c>
-      <c r="F590" s="2" t="s">
-        <v>6948</v>
       </c>
       <c r="G590" s="3">
         <v>2</v>
@@ -40711,7 +40711,7 @@
         <v>2653</v>
       </c>
       <c r="C595" s="2" t="s">
-        <v>6900</v>
+        <v>6899</v>
       </c>
       <c r="D595" s="2" t="s">
         <v>2654</v>
@@ -40740,7 +40740,7 @@
         <v>2658</v>
       </c>
       <c r="C596" s="2" t="s">
-        <v>6735</v>
+        <v>6734</v>
       </c>
       <c r="D596" s="2" t="s">
         <v>2659</v>
@@ -40766,7 +40766,7 @@
         <v>596</v>
       </c>
       <c r="B597" s="2" t="s">
-        <v>6734</v>
+        <v>6733</v>
       </c>
       <c r="C597" s="2" t="s">
         <v>2663</v>
@@ -41184,7 +41184,7 @@
         <v>2722</v>
       </c>
       <c r="F611" s="2" t="s">
-        <v>6851</v>
+        <v>6850</v>
       </c>
       <c r="G611" s="3">
         <v>4</v>
@@ -41201,7 +41201,7 @@
         <v>611</v>
       </c>
       <c r="B612" s="2" t="s">
-        <v>6850</v>
+        <v>6849</v>
       </c>
       <c r="C612" s="2" t="s">
         <v>2377</v>
@@ -41259,7 +41259,7 @@
         <v>613</v>
       </c>
       <c r="B614" s="2" t="s">
-        <v>6832</v>
+        <v>6831</v>
       </c>
       <c r="C614" s="2" t="s">
         <v>2732</v>
@@ -41268,10 +41268,10 @@
         <v>2733</v>
       </c>
       <c r="E614" s="2" t="s">
+        <v>6832</v>
+      </c>
+      <c r="F614" s="2" t="s">
         <v>6833</v>
-      </c>
-      <c r="F614" s="2" t="s">
-        <v>6834</v>
       </c>
       <c r="G614" s="3">
         <v>3</v>
@@ -41349,16 +41349,16 @@
         <v>2746</v>
       </c>
       <c r="C617" s="2" t="s">
+        <v>6801</v>
+      </c>
+      <c r="D617" s="2" t="s">
         <v>6802</v>
-      </c>
-      <c r="D617" s="2" t="s">
-        <v>6803</v>
       </c>
       <c r="E617" s="2" t="s">
         <v>2747</v>
       </c>
       <c r="F617" s="2" t="s">
-        <v>6804</v>
+        <v>6803</v>
       </c>
       <c r="G617" s="3">
         <v>4</v>
@@ -41375,19 +41375,19 @@
         <v>617</v>
       </c>
       <c r="B618" s="2" t="s">
+        <v>6883</v>
+      </c>
+      <c r="C618" s="2" t="s">
         <v>6884</v>
       </c>
-      <c r="C618" s="2" t="s">
+      <c r="D618" s="2" t="s">
         <v>6885</v>
       </c>
-      <c r="D618" s="2" t="s">
+      <c r="E618" s="2" t="s">
         <v>6886</v>
       </c>
-      <c r="E618" s="2" t="s">
+      <c r="F618" s="2" t="s">
         <v>6887</v>
-      </c>
-      <c r="F618" s="2" t="s">
-        <v>6888</v>
       </c>
       <c r="G618" s="3">
         <v>3</v>
@@ -41793,7 +41793,7 @@
         <v>2805</v>
       </c>
       <c r="F632" s="2" t="s">
-        <v>6809</v>
+        <v>6808</v>
       </c>
       <c r="G632" s="3">
         <v>3</v>
@@ -41810,19 +41810,19 @@
         <v>632</v>
       </c>
       <c r="B633" s="2" t="s">
+        <v>6806</v>
+      </c>
+      <c r="C633" s="2" t="s">
+        <v>6804</v>
+      </c>
+      <c r="D633" s="2" t="s">
+        <v>6805</v>
+      </c>
+      <c r="E633" s="2" t="s">
         <v>6807</v>
       </c>
-      <c r="C633" s="2" t="s">
-        <v>6805</v>
-      </c>
-      <c r="D633" s="2" t="s">
-        <v>6806</v>
-      </c>
-      <c r="E633" s="2" t="s">
-        <v>6808</v>
-      </c>
       <c r="F633" s="2" t="s">
-        <v>6804</v>
+        <v>6803</v>
       </c>
       <c r="G633" s="3">
         <v>4</v>
@@ -42071,16 +42071,16 @@
         <v>641</v>
       </c>
       <c r="B642" s="2" t="s">
-        <v>6906</v>
+        <v>6905</v>
       </c>
       <c r="C642" s="2" t="s">
-        <v>6908</v>
+        <v>6907</v>
       </c>
       <c r="D642" s="2" t="s">
         <v>2837</v>
       </c>
       <c r="E642" s="2" t="s">
-        <v>6907</v>
+        <v>6906</v>
       </c>
       <c r="F642" s="2" t="s">
         <v>187</v>
@@ -42509,16 +42509,16 @@
         <v>2906</v>
       </c>
       <c r="C657" s="2" t="s">
+        <v>7026</v>
+      </c>
+      <c r="D657" s="2" t="s">
         <v>7027</v>
       </c>
-      <c r="D657" s="2" t="s">
+      <c r="E657" s="2" t="s">
         <v>7028</v>
       </c>
-      <c r="E657" s="2" t="s">
+      <c r="F657" s="2" t="s">
         <v>7029</v>
-      </c>
-      <c r="F657" s="2" t="s">
-        <v>7030</v>
       </c>
       <c r="G657" s="3">
         <v>1</v>
@@ -42547,7 +42547,7 @@
         <v>2910</v>
       </c>
       <c r="F658" s="2" t="s">
-        <v>7031</v>
+        <v>7030</v>
       </c>
       <c r="G658" s="3">
         <v>2</v>
@@ -42564,13 +42564,13 @@
         <v>658</v>
       </c>
       <c r="B659" s="2" t="s">
+        <v>6939</v>
+      </c>
+      <c r="C659" s="2" t="s">
         <v>6940</v>
       </c>
-      <c r="C659" s="2" t="s">
-        <v>6941</v>
-      </c>
       <c r="D659" s="2" t="s">
-        <v>6939</v>
+        <v>6938</v>
       </c>
       <c r="E659" s="2" t="s">
         <v>2912</v>
@@ -42596,16 +42596,16 @@
         <v>2915</v>
       </c>
       <c r="C660" s="2" t="s">
+        <v>7002</v>
+      </c>
+      <c r="D660" s="2" t="s">
         <v>7003</v>
       </c>
-      <c r="D660" s="2" t="s">
+      <c r="E660" s="2" t="s">
         <v>7004</v>
       </c>
-      <c r="E660" s="2" t="s">
-        <v>7005</v>
-      </c>
       <c r="F660" s="2" t="s">
-        <v>7001</v>
+        <v>7000</v>
       </c>
       <c r="G660" s="3">
         <v>4</v>
@@ -42634,7 +42634,7 @@
         <v>2919</v>
       </c>
       <c r="F661" s="2" t="s">
-        <v>7001</v>
+        <v>7000</v>
       </c>
       <c r="G661" s="3">
         <v>4</v>
@@ -42779,7 +42779,7 @@
         <v>2945</v>
       </c>
       <c r="F666" s="2" t="s">
-        <v>7060</v>
+        <v>7059</v>
       </c>
       <c r="G666" s="3">
         <v>2</v>
@@ -42796,7 +42796,7 @@
         <v>666</v>
       </c>
       <c r="B667" s="2" t="s">
-        <v>7059</v>
+        <v>7058</v>
       </c>
       <c r="C667" s="2" t="s">
         <v>2943</v>
@@ -43672,7 +43672,7 @@
         <v>3070</v>
       </c>
       <c r="D697" s="2" t="s">
-        <v>6899</v>
+        <v>6898</v>
       </c>
       <c r="E697" s="2" t="s">
         <v>3071</v>
@@ -43956,19 +43956,19 @@
         <v>706</v>
       </c>
       <c r="B707" s="2" t="s">
+        <v>6875</v>
+      </c>
+      <c r="C707" s="2" t="s">
+        <v>6879</v>
+      </c>
+      <c r="D707" s="2" t="s">
         <v>6876</v>
       </c>
-      <c r="C707" s="2" t="s">
-        <v>6880</v>
-      </c>
-      <c r="D707" s="2" t="s">
+      <c r="E707" s="2" t="s">
         <v>6877</v>
       </c>
-      <c r="E707" s="2" t="s">
+      <c r="F707" s="2" t="s">
         <v>6878</v>
-      </c>
-      <c r="F707" s="2" t="s">
-        <v>6879</v>
       </c>
       <c r="G707" s="3">
         <v>1</v>
@@ -43985,7 +43985,7 @@
         <v>707</v>
       </c>
       <c r="B708" s="2" t="s">
-        <v>6862</v>
+        <v>6861</v>
       </c>
       <c r="C708" s="2" t="s">
         <v>3110</v>
@@ -43997,7 +43997,7 @@
         <v>3112</v>
       </c>
       <c r="F708" s="2" t="s">
-        <v>6851</v>
+        <v>6850</v>
       </c>
       <c r="G708" s="3">
         <v>4</v>
@@ -44014,7 +44014,7 @@
         <v>708</v>
       </c>
       <c r="B709" s="2" t="s">
-        <v>7023</v>
+        <v>7022</v>
       </c>
       <c r="C709" s="2" t="s">
         <v>3113</v>
@@ -44916,16 +44916,16 @@
         <v>6159</v>
       </c>
       <c r="C740" s="8" t="s">
+        <v>6862</v>
+      </c>
+      <c r="D740" s="8" t="s">
         <v>6863</v>
       </c>
-      <c r="D740" s="8" t="s">
+      <c r="E740" s="8" t="s">
         <v>6864</v>
       </c>
-      <c r="E740" s="8" t="s">
+      <c r="F740" s="8" t="s">
         <v>6865</v>
-      </c>
-      <c r="F740" s="8" t="s">
-        <v>6866</v>
       </c>
       <c r="G740" s="3">
         <v>4</v>
@@ -44945,16 +44945,16 @@
         <v>3216</v>
       </c>
       <c r="C741" s="8" t="s">
+        <v>6862</v>
+      </c>
+      <c r="D741" s="8" t="s">
         <v>6863</v>
       </c>
-      <c r="D741" s="8" t="s">
+      <c r="E741" s="8" t="s">
         <v>6864</v>
       </c>
-      <c r="E741" s="8" t="s">
+      <c r="F741" s="8" t="s">
         <v>6865</v>
-      </c>
-      <c r="F741" s="8" t="s">
-        <v>6866</v>
       </c>
       <c r="G741" s="3">
         <v>1</v>
@@ -45058,7 +45058,7 @@
         <v>744</v>
       </c>
       <c r="B745" s="2" t="s">
-        <v>7032</v>
+        <v>7031</v>
       </c>
       <c r="C745" s="2" t="s">
         <v>446</v>
@@ -45087,7 +45087,7 @@
         <v>745</v>
       </c>
       <c r="B746" s="2" t="s">
-        <v>6771</v>
+        <v>6770</v>
       </c>
       <c r="C746" s="2" t="s">
         <v>2663</v>
@@ -45174,7 +45174,7 @@
         <v>748</v>
       </c>
       <c r="B749" s="2" t="s">
-        <v>7000</v>
+        <v>6999</v>
       </c>
       <c r="C749" s="2" t="s">
         <v>3234</v>
@@ -45183,10 +45183,10 @@
         <v>3235</v>
       </c>
       <c r="E749" s="2" t="s">
-        <v>7002</v>
+        <v>7001</v>
       </c>
       <c r="F749" s="2" t="s">
-        <v>7001</v>
+        <v>7000</v>
       </c>
       <c r="G749" s="3">
         <v>4</v>
@@ -45493,10 +45493,10 @@
         <v>759</v>
       </c>
       <c r="B760" s="2" t="s">
-        <v>6841</v>
+        <v>6840</v>
       </c>
       <c r="C760" s="2" t="s">
-        <v>6843</v>
+        <v>6842</v>
       </c>
       <c r="D760" s="2" t="s">
         <v>3277</v>
@@ -45505,7 +45505,7 @@
         <v>3278</v>
       </c>
       <c r="F760" s="2" t="s">
-        <v>6842</v>
+        <v>6841</v>
       </c>
       <c r="G760" s="3">
         <v>4</v>
@@ -45810,7 +45810,7 @@
         <v>770</v>
       </c>
       <c r="B771" s="2" t="s">
-        <v>6753</v>
+        <v>6752</v>
       </c>
       <c r="C771" s="2" t="s">
         <v>447</v>
@@ -46187,19 +46187,19 @@
         <v>783</v>
       </c>
       <c r="B784" s="2" t="s">
+        <v>6766</v>
+      </c>
+      <c r="C784" s="2" t="s">
         <v>6767</v>
       </c>
-      <c r="C784" s="2" t="s">
+      <c r="D784" s="2" t="s">
         <v>6768</v>
-      </c>
-      <c r="D784" s="2" t="s">
-        <v>6769</v>
       </c>
       <c r="E784" s="2" t="s">
         <v>3366</v>
       </c>
       <c r="F784" s="2" t="s">
-        <v>6770</v>
+        <v>6769</v>
       </c>
       <c r="G784" s="3">
         <v>3</v>
@@ -46283,7 +46283,7 @@
         <v>3378</v>
       </c>
       <c r="E787" s="2" t="s">
-        <v>7024</v>
+        <v>7023</v>
       </c>
       <c r="F787" s="2" t="s">
         <v>3379</v>
@@ -46454,13 +46454,13 @@
         <v>3397</v>
       </c>
       <c r="D793" s="2" t="s">
-        <v>7061</v>
+        <v>7060</v>
       </c>
       <c r="E793" s="2" t="s">
         <v>3398</v>
       </c>
       <c r="F793" s="2" t="s">
-        <v>7062</v>
+        <v>7061</v>
       </c>
       <c r="G793" s="3">
         <v>2</v>
@@ -46593,7 +46593,7 @@
         <v>797</v>
       </c>
       <c r="B798" s="2" t="s">
-        <v>7063</v>
+        <v>7062</v>
       </c>
       <c r="C798" s="2" t="s">
         <v>3421</v>
@@ -46709,19 +46709,19 @@
         <v>801</v>
       </c>
       <c r="B802" s="2" t="s">
-        <v>6985</v>
+        <v>6984</v>
       </c>
       <c r="C802" s="2" t="s">
         <v>3439</v>
       </c>
       <c r="D802" s="2" t="s">
-        <v>6986</v>
+        <v>6985</v>
       </c>
       <c r="E802" s="2" t="s">
         <v>3440</v>
       </c>
       <c r="F802" s="2" t="s">
-        <v>6987</v>
+        <v>6986</v>
       </c>
       <c r="G802" s="3">
         <v>2</v>
@@ -47289,7 +47289,7 @@
         <v>821</v>
       </c>
       <c r="B822" s="2" t="s">
-        <v>6963</v>
+        <v>6962</v>
       </c>
       <c r="C822" s="2" t="s">
         <v>3525</v>
@@ -47356,7 +47356,7 @@
         <v>3535</v>
       </c>
       <c r="E824" s="2" t="s">
-        <v>6835</v>
+        <v>6834</v>
       </c>
       <c r="F824" s="2" t="s">
         <v>3536</v>
@@ -47637,7 +47637,7 @@
         <v>833</v>
       </c>
       <c r="B834" s="2" t="s">
-        <v>7016</v>
+        <v>7015</v>
       </c>
       <c r="C834" s="2" t="s">
         <v>3569</v>
@@ -47649,7 +47649,7 @@
         <v>3571</v>
       </c>
       <c r="F834" s="2" t="s">
-        <v>7017</v>
+        <v>7016</v>
       </c>
       <c r="G834" s="3">
         <v>2</v>
@@ -47724,7 +47724,7 @@
         <v>836</v>
       </c>
       <c r="B837" s="2" t="s">
-        <v>6961</v>
+        <v>6960</v>
       </c>
       <c r="C837" s="2" t="s">
         <v>3569</v>
@@ -47811,19 +47811,19 @@
         <v>839</v>
       </c>
       <c r="B840" s="2" t="s">
-        <v>6982</v>
+        <v>6981</v>
       </c>
       <c r="C840" s="2" t="s">
-        <v>6980</v>
+        <v>6979</v>
       </c>
       <c r="D840" s="2" t="s">
         <v>3594</v>
       </c>
       <c r="E840" s="2" t="s">
-        <v>6981</v>
+        <v>6980</v>
       </c>
       <c r="F840" s="2" t="s">
-        <v>6979</v>
+        <v>6978</v>
       </c>
       <c r="G840" s="3">
         <v>4</v>
@@ -47954,7 +47954,7 @@
         <v>844</v>
       </c>
       <c r="B845" s="2" t="s">
-        <v>7045</v>
+        <v>7044</v>
       </c>
       <c r="C845" s="2" t="s">
         <v>3607</v>
@@ -47966,7 +47966,7 @@
         <v>3609</v>
       </c>
       <c r="F845" s="2" t="s">
-        <v>7046</v>
+        <v>7045</v>
       </c>
       <c r="G845" s="3">
         <v>2</v>
@@ -48070,7 +48070,7 @@
         <v>848</v>
       </c>
       <c r="B849" s="2" t="s">
-        <v>6846</v>
+        <v>6845</v>
       </c>
       <c r="C849" s="2" t="s">
         <v>3607</v>
@@ -48082,7 +48082,7 @@
         <v>3609</v>
       </c>
       <c r="F849" s="2" t="s">
-        <v>6847</v>
+        <v>6846</v>
       </c>
       <c r="G849" s="3">
         <v>3</v>
@@ -48111,7 +48111,7 @@
         <v>3608</v>
       </c>
       <c r="F850" s="2" t="s">
-        <v>6848</v>
+        <v>6847</v>
       </c>
       <c r="G850" s="3">
         <v>2</v>
@@ -48244,7 +48244,7 @@
         <v>854</v>
       </c>
       <c r="B855" s="2" t="s">
-        <v>7037</v>
+        <v>7036</v>
       </c>
       <c r="C855" s="2" t="s">
         <v>3647</v>
@@ -48253,7 +48253,7 @@
         <v>3648</v>
       </c>
       <c r="E855" s="2" t="s">
-        <v>7069</v>
+        <v>7068</v>
       </c>
       <c r="F855" s="2" t="s">
         <v>3649</v>
@@ -48943,10 +48943,10 @@
         <v>3749</v>
       </c>
       <c r="C879" s="2" t="s">
+        <v>6963</v>
+      </c>
+      <c r="D879" s="2" t="s">
         <v>6964</v>
-      </c>
-      <c r="D879" s="2" t="s">
-        <v>6965</v>
       </c>
       <c r="E879" s="2" t="s">
         <v>3750</v>
@@ -49094,7 +49094,7 @@
         <v>3770</v>
       </c>
       <c r="E884" s="2" t="s">
-        <v>6962</v>
+        <v>6961</v>
       </c>
       <c r="F884" s="2" t="s">
         <v>3771</v>
@@ -49558,7 +49558,7 @@
         <v>3841</v>
       </c>
       <c r="E900" s="2" t="s">
-        <v>6993</v>
+        <v>6992</v>
       </c>
       <c r="F900" s="2" t="s">
         <v>3842</v>
@@ -49616,10 +49616,10 @@
         <v>3852</v>
       </c>
       <c r="E902" s="2" t="s">
-        <v>6814</v>
+        <v>6813</v>
       </c>
       <c r="F902" s="2" t="s">
-        <v>6813</v>
+        <v>6812</v>
       </c>
       <c r="G902" s="3">
         <v>1</v>
@@ -50123,7 +50123,7 @@
         <v>919</v>
       </c>
       <c r="B920" s="2" t="s">
-        <v>7052</v>
+        <v>7051</v>
       </c>
       <c r="C920" s="2" t="s">
         <v>3935</v>
@@ -50271,16 +50271,16 @@
         <v>3958</v>
       </c>
       <c r="C925" s="2" t="s">
-        <v>6742</v>
+        <v>6741</v>
       </c>
       <c r="D925" s="2" t="s">
-        <v>6741</v>
+        <v>6740</v>
       </c>
       <c r="E925" s="2" t="s">
-        <v>6740</v>
+        <v>6739</v>
       </c>
       <c r="F925" s="2" t="s">
-        <v>6739</v>
+        <v>6738</v>
       </c>
       <c r="G925" s="3">
         <v>4</v>
@@ -50297,7 +50297,7 @@
         <v>925</v>
       </c>
       <c r="B926" s="2" t="s">
-        <v>7058</v>
+        <v>7057</v>
       </c>
       <c r="C926" s="2" t="s">
         <v>3960</v>
@@ -50759,7 +50759,7 @@
         <v>941</v>
       </c>
       <c r="B942" s="2" t="s">
-        <v>6970</v>
+        <v>6969</v>
       </c>
       <c r="C942" s="2" t="s">
         <v>4038</v>
@@ -51020,19 +51020,19 @@
         <v>950</v>
       </c>
       <c r="B951" s="2" t="s">
+        <v>6893</v>
+      </c>
+      <c r="C951" s="2" t="s">
         <v>6894</v>
       </c>
-      <c r="C951" s="2" t="s">
+      <c r="D951" s="2" t="s">
         <v>6895</v>
       </c>
-      <c r="D951" s="2" t="s">
+      <c r="E951" s="2" t="s">
         <v>6896</v>
       </c>
-      <c r="E951" s="2" t="s">
+      <c r="F951" s="2" t="s">
         <v>6897</v>
-      </c>
-      <c r="F951" s="2" t="s">
-        <v>6898</v>
       </c>
       <c r="G951" s="3">
         <v>1</v>
@@ -51194,7 +51194,7 @@
         <v>956</v>
       </c>
       <c r="B957" s="2" t="s">
-        <v>6873</v>
+        <v>6872</v>
       </c>
       <c r="C957" s="2" t="s">
         <v>1005</v>
@@ -51203,10 +51203,10 @@
         <v>1280</v>
       </c>
       <c r="E957" s="2" t="s">
+        <v>6873</v>
+      </c>
+      <c r="F957" s="2" t="s">
         <v>6874</v>
-      </c>
-      <c r="F957" s="2" t="s">
-        <v>6875</v>
       </c>
       <c r="G957" s="3">
         <v>1</v>
@@ -51513,7 +51513,7 @@
         <v>967</v>
       </c>
       <c r="B968" s="2" t="s">
-        <v>6949</v>
+        <v>6948</v>
       </c>
       <c r="C968" s="2" t="s">
         <v>3851</v>
@@ -51525,7 +51525,7 @@
         <v>4143</v>
       </c>
       <c r="F968" s="2" t="s">
-        <v>6950</v>
+        <v>6949</v>
       </c>
       <c r="G968" s="3">
         <v>1</v>
@@ -51600,7 +51600,7 @@
         <v>970</v>
       </c>
       <c r="B971" s="2" t="s">
-        <v>7025</v>
+        <v>7024</v>
       </c>
       <c r="C971" s="2" t="s">
         <v>4153</v>
@@ -51803,19 +51803,19 @@
         <v>977</v>
       </c>
       <c r="B978" s="2" t="s">
+        <v>7011</v>
+      </c>
+      <c r="C978" s="2" t="s">
+        <v>7014</v>
+      </c>
+      <c r="D978" s="2" t="s">
         <v>7012</v>
-      </c>
-      <c r="C978" s="2" t="s">
-        <v>7015</v>
-      </c>
-      <c r="D978" s="2" t="s">
-        <v>7013</v>
       </c>
       <c r="E978" s="2" t="s">
         <v>4190</v>
       </c>
       <c r="F978" s="2" t="s">
-        <v>7014</v>
+        <v>7013</v>
       </c>
       <c r="G978" s="3">
         <v>4</v>
@@ -52154,7 +52154,7 @@
         <v>6598</v>
       </c>
       <c r="C990" s="2" t="s">
-        <v>6861</v>
+        <v>6860</v>
       </c>
       <c r="D990" s="2" t="s">
         <v>6599</v>
@@ -52238,19 +52238,19 @@
         <v>992</v>
       </c>
       <c r="B993" s="2" t="s">
-        <v>7038</v>
+        <v>7037</v>
       </c>
       <c r="C993" s="2" t="s">
         <v>4245</v>
       </c>
       <c r="D993" s="2" t="s">
+        <v>7038</v>
+      </c>
+      <c r="E993" s="2" t="s">
         <v>7039</v>
       </c>
-      <c r="E993" s="2" t="s">
+      <c r="F993" s="2" t="s">
         <v>7040</v>
-      </c>
-      <c r="F993" s="2" t="s">
-        <v>7041</v>
       </c>
       <c r="G993" s="3">
         <v>1</v>
@@ -52383,16 +52383,16 @@
         <v>997</v>
       </c>
       <c r="B998" s="2" t="s">
+        <v>6956</v>
+      </c>
+      <c r="C998" s="2" t="s">
         <v>6957</v>
       </c>
-      <c r="C998" s="2" t="s">
+      <c r="D998" s="2" t="s">
         <v>6958</v>
       </c>
-      <c r="D998" s="2" t="s">
+      <c r="E998" s="2" t="s">
         <v>6959</v>
-      </c>
-      <c r="E998" s="2" t="s">
-        <v>6960</v>
       </c>
       <c r="F998" s="2" t="s">
         <v>4254</v>
@@ -52412,7 +52412,7 @@
         <v>998</v>
       </c>
       <c r="B999" s="2" t="s">
-        <v>6760</v>
+        <v>6759</v>
       </c>
       <c r="C999" s="2" t="s">
         <v>802</v>
@@ -52511,7 +52511,7 @@
         <v>889</v>
       </c>
       <c r="F1002" s="2" t="s">
-        <v>7065</v>
+        <v>7064</v>
       </c>
       <c r="G1002" s="3">
         <v>3</v>
@@ -52528,7 +52528,7 @@
         <v>1002</v>
       </c>
       <c r="B1003" s="2" t="s">
-        <v>7064</v>
+        <v>7063</v>
       </c>
       <c r="C1003" s="2" t="s">
         <v>888</v>
@@ -52644,10 +52644,10 @@
         <v>1006</v>
       </c>
       <c r="B1007" s="2" t="s">
+        <v>6917</v>
+      </c>
+      <c r="C1007" s="2" t="s">
         <v>6918</v>
-      </c>
-      <c r="C1007" s="2" t="s">
-        <v>6919</v>
       </c>
       <c r="D1007" s="2" t="s">
         <v>3362</v>
@@ -52656,7 +52656,7 @@
         <v>4276</v>
       </c>
       <c r="F1007" s="2" t="s">
-        <v>6920</v>
+        <v>6919</v>
       </c>
       <c r="G1007" s="3">
         <v>4</v>
@@ -52789,7 +52789,7 @@
         <v>1011</v>
       </c>
       <c r="B1012" s="2" t="s">
-        <v>6998</v>
+        <v>6997</v>
       </c>
       <c r="C1012" s="2" t="s">
         <v>4291</v>
@@ -52856,7 +52856,7 @@
         <v>4299</v>
       </c>
       <c r="E1014" s="2" t="s">
-        <v>6983</v>
+        <v>6982</v>
       </c>
       <c r="F1014" s="2" t="s">
         <v>4300</v>
@@ -53311,7 +53311,7 @@
         <v>1029</v>
       </c>
       <c r="B1030" s="2" t="s">
-        <v>7036</v>
+        <v>7035</v>
       </c>
       <c r="C1030" s="2" t="s">
         <v>4358</v>
@@ -53981,13 +53981,13 @@
         <v>4466</v>
       </c>
       <c r="C1053" s="2" t="s">
+        <v>6756</v>
+      </c>
+      <c r="D1053" s="2" t="s">
         <v>6757</v>
       </c>
-      <c r="D1053" s="2" t="s">
+      <c r="E1053" s="2" t="s">
         <v>6758</v>
-      </c>
-      <c r="E1053" s="2" t="s">
-        <v>6759</v>
       </c>
       <c r="F1053" s="2" t="s">
         <v>4472</v>
@@ -54152,19 +54152,19 @@
         <v>1058</v>
       </c>
       <c r="B1059" s="2" t="s">
+        <v>6888</v>
+      </c>
+      <c r="C1059" s="2" t="s">
         <v>6889</v>
       </c>
-      <c r="C1059" s="2" t="s">
+      <c r="D1059" s="2" t="s">
         <v>6890</v>
       </c>
-      <c r="D1059" s="2" t="s">
+      <c r="E1059" s="2" t="s">
+        <v>6892</v>
+      </c>
+      <c r="F1059" s="2" t="s">
         <v>6891</v>
-      </c>
-      <c r="E1059" s="2" t="s">
-        <v>6893</v>
-      </c>
-      <c r="F1059" s="2" t="s">
-        <v>6892</v>
       </c>
       <c r="G1059" s="3">
         <v>4</v>
@@ -54790,7 +54790,7 @@
         <v>1080</v>
       </c>
       <c r="B1081" s="2" t="s">
-        <v>7020</v>
+        <v>7019</v>
       </c>
       <c r="C1081" s="2" t="s">
         <v>4561</v>
@@ -54964,19 +54964,19 @@
         <v>1086</v>
       </c>
       <c r="B1087" s="2" t="s">
+        <v>6920</v>
+      </c>
+      <c r="C1087" s="2" t="s">
         <v>6921</v>
       </c>
-      <c r="C1087" s="2" t="s">
+      <c r="D1087" s="2" t="s">
         <v>6922</v>
       </c>
-      <c r="D1087" s="2" t="s">
+      <c r="E1087" s="2" t="s">
         <v>6923</v>
       </c>
-      <c r="E1087" s="2" t="s">
+      <c r="F1087" s="2" t="s">
         <v>6924</v>
-      </c>
-      <c r="F1087" s="2" t="s">
-        <v>6925</v>
       </c>
       <c r="G1087" s="3">
         <v>2</v>
@@ -55167,10 +55167,10 @@
         <v>1093</v>
       </c>
       <c r="B1094" s="2" t="s">
-        <v>6994</v>
+        <v>6993</v>
       </c>
       <c r="C1094" s="2" t="s">
-        <v>6996</v>
+        <v>6995</v>
       </c>
       <c r="D1094" s="2" t="s">
         <v>4607</v>
@@ -55179,7 +55179,7 @@
         <v>4608</v>
       </c>
       <c r="F1094" s="2" t="s">
-        <v>6997</v>
+        <v>6996</v>
       </c>
       <c r="G1094" s="3">
         <v>3</v>
@@ -55199,7 +55199,7 @@
         <v>4610</v>
       </c>
       <c r="C1095" s="2" t="s">
-        <v>6995</v>
+        <v>6994</v>
       </c>
       <c r="D1095" s="2" t="s">
         <v>4611</v>
@@ -55399,7 +55399,7 @@
         <v>1101</v>
       </c>
       <c r="B1102" s="2" t="s">
-        <v>6801</v>
+        <v>6800</v>
       </c>
       <c r="C1102" s="2" t="s">
         <v>4639</v>
@@ -55637,13 +55637,13 @@
         <v>4670</v>
       </c>
       <c r="D1110" s="2" t="s">
-        <v>7082</v>
+        <v>7081</v>
       </c>
       <c r="E1110" s="2" t="s">
         <v>4671</v>
       </c>
       <c r="F1110" s="2" t="s">
-        <v>7083</v>
+        <v>7082</v>
       </c>
       <c r="G1110" s="3">
         <v>3</v>
@@ -55747,7 +55747,7 @@
         <v>1113</v>
       </c>
       <c r="B1114" s="2" t="s">
-        <v>6858</v>
+        <v>6857</v>
       </c>
       <c r="C1114" s="2" t="s">
         <v>4683</v>
@@ -55759,7 +55759,7 @@
         <v>4685</v>
       </c>
       <c r="F1114" s="2" t="s">
-        <v>6859</v>
+        <v>6858</v>
       </c>
       <c r="G1114" s="3">
         <v>4</v>
@@ -55950,7 +55950,7 @@
         <v>1120</v>
       </c>
       <c r="B1121" s="2" t="s">
-        <v>6836</v>
+        <v>6835</v>
       </c>
       <c r="C1121" s="2" t="s">
         <v>4712</v>
@@ -56385,19 +56385,19 @@
         <v>1135</v>
       </c>
       <c r="B1136" s="2" t="s">
+        <v>6775</v>
+      </c>
+      <c r="C1136" s="2" t="s">
         <v>6776</v>
       </c>
-      <c r="C1136" s="2" t="s">
+      <c r="D1136" s="2" t="s">
         <v>6777</v>
       </c>
-      <c r="D1136" s="2" t="s">
+      <c r="E1136" s="2" t="s">
         <v>6778</v>
       </c>
-      <c r="E1136" s="2" t="s">
+      <c r="F1136" s="2" t="s">
         <v>6779</v>
-      </c>
-      <c r="F1136" s="2" t="s">
-        <v>6780</v>
       </c>
       <c r="G1136" s="3">
         <v>3</v>
@@ -56414,19 +56414,19 @@
         <v>1136</v>
       </c>
       <c r="B1137" s="2" t="s">
+        <v>6780</v>
+      </c>
+      <c r="C1137" s="2" t="s">
         <v>6781</v>
       </c>
-      <c r="C1137" s="2" t="s">
+      <c r="D1137" s="2" t="s">
         <v>6782</v>
       </c>
-      <c r="D1137" s="2" t="s">
+      <c r="E1137" s="2" t="s">
         <v>6783</v>
       </c>
-      <c r="E1137" s="2" t="s">
+      <c r="F1137" s="2" t="s">
         <v>6784</v>
-      </c>
-      <c r="F1137" s="2" t="s">
-        <v>6785</v>
       </c>
       <c r="G1137" s="3">
         <v>4</v>
@@ -56675,7 +56675,7 @@
         <v>1145</v>
       </c>
       <c r="B1146" s="2" t="s">
-        <v>7100</v>
+        <v>7099</v>
       </c>
       <c r="C1146" s="2" t="s">
         <v>3714</v>
@@ -56704,7 +56704,7 @@
         <v>1146</v>
       </c>
       <c r="B1147" s="2" t="s">
-        <v>7067</v>
+        <v>7066</v>
       </c>
       <c r="C1147" s="2" t="s">
         <v>4805</v>
@@ -56716,7 +56716,7 @@
         <v>4807</v>
       </c>
       <c r="F1147" s="2" t="s">
-        <v>7068</v>
+        <v>7067</v>
       </c>
       <c r="G1147" s="3">
         <v>2</v>
@@ -57400,10 +57400,10 @@
         <v>1170</v>
       </c>
       <c r="B1171" s="2" t="s">
-        <v>6852</v>
+        <v>6851</v>
       </c>
       <c r="C1171" s="2" t="s">
-        <v>6854</v>
+        <v>6853</v>
       </c>
       <c r="D1171" s="2" t="s">
         <v>4903</v>
@@ -57412,7 +57412,7 @@
         <v>4724</v>
       </c>
       <c r="F1171" s="2" t="s">
-        <v>6853</v>
+        <v>6852</v>
       </c>
       <c r="G1171" s="3">
         <v>2</v>
@@ -57748,7 +57748,7 @@
         <v>1182</v>
       </c>
       <c r="B1183" s="2" t="s">
-        <v>6869</v>
+        <v>6868</v>
       </c>
       <c r="C1183" s="2" t="s">
         <v>4945</v>
@@ -57760,7 +57760,7 @@
         <v>4946</v>
       </c>
       <c r="F1183" s="2" t="s">
-        <v>6870</v>
+        <v>6869</v>
       </c>
       <c r="G1183" s="3">
         <v>2</v>
@@ -58183,7 +58183,7 @@
         <v>1197</v>
       </c>
       <c r="B1198" s="2" t="s">
-        <v>6857</v>
+        <v>6856</v>
       </c>
       <c r="C1198" s="2" t="s">
         <v>3753</v>
@@ -58560,7 +58560,7 @@
         <v>1210</v>
       </c>
       <c r="B1211" s="2" t="s">
-        <v>6731</v>
+        <v>7105</v>
       </c>
       <c r="C1211" s="2" t="s">
         <v>446</v>
@@ -58734,7 +58734,7 @@
         <v>1216</v>
       </c>
       <c r="B1217" s="2" t="s">
-        <v>7077</v>
+        <v>7076</v>
       </c>
       <c r="C1217" s="2" t="s">
         <v>2887</v>
@@ -59123,7 +59123,7 @@
         <v>4482</v>
       </c>
       <c r="F1230" s="2" t="s">
-        <v>6765</v>
+        <v>6764</v>
       </c>
       <c r="G1230" s="3">
         <v>4</v>
@@ -59347,13 +59347,13 @@
         <v>5107</v>
       </c>
       <c r="D1238" s="2" t="s">
-        <v>7011</v>
+        <v>7010</v>
       </c>
       <c r="E1238" s="2" t="s">
         <v>5072</v>
       </c>
       <c r="F1238" s="2" t="s">
-        <v>7010</v>
+        <v>7009</v>
       </c>
       <c r="G1238" s="3">
         <v>3</v>
@@ -59370,7 +59370,7 @@
         <v>1238</v>
       </c>
       <c r="B1239" s="2" t="s">
-        <v>7009</v>
+        <v>7008</v>
       </c>
       <c r="C1239" s="2" t="s">
         <v>5070</v>
@@ -59382,7 +59382,7 @@
         <v>5072</v>
       </c>
       <c r="F1239" s="2" t="s">
-        <v>7010</v>
+        <v>7009</v>
       </c>
       <c r="G1239" s="3">
         <v>4</v>
@@ -59515,10 +59515,10 @@
         <v>1243</v>
       </c>
       <c r="B1244" s="2" t="s">
+        <v>7041</v>
+      </c>
+      <c r="C1244" s="2" t="s">
         <v>7042</v>
-      </c>
-      <c r="C1244" s="2" t="s">
-        <v>7043</v>
       </c>
       <c r="D1244" s="2" t="s">
         <v>5126</v>
@@ -59527,7 +59527,7 @@
         <v>3699</v>
       </c>
       <c r="F1244" s="2" t="s">
-        <v>7044</v>
+        <v>7043</v>
       </c>
       <c r="G1244" s="3">
         <v>4</v>
@@ -59547,13 +59547,13 @@
         <v>5128</v>
       </c>
       <c r="C1245" s="2" t="s">
+        <v>6990</v>
+      </c>
+      <c r="D1245" s="2" t="s">
+        <v>6989</v>
+      </c>
+      <c r="E1245" s="2" t="s">
         <v>6991</v>
-      </c>
-      <c r="D1245" s="2" t="s">
-        <v>6990</v>
-      </c>
-      <c r="E1245" s="2" t="s">
-        <v>6992</v>
       </c>
       <c r="F1245" s="2" t="s">
         <v>5129</v>
@@ -60046,7 +60046,7 @@
         <v>5204</v>
       </c>
       <c r="E1262" s="2" t="s">
-        <v>6912</v>
+        <v>6911</v>
       </c>
       <c r="F1262" s="2" t="s">
         <v>5205</v>
@@ -60101,7 +60101,7 @@
         <v>5214</v>
       </c>
       <c r="D1264" s="2" t="s">
-        <v>7026</v>
+        <v>7025</v>
       </c>
       <c r="E1264" s="2" t="s">
         <v>5215</v>
@@ -62506,13 +62506,13 @@
         <v>1280</v>
       </c>
       <c r="D1347" s="2" t="s">
-        <v>6823</v>
+        <v>6822</v>
       </c>
       <c r="E1347" s="2" t="s">
         <v>1005</v>
       </c>
       <c r="F1347" s="2" t="s">
-        <v>6824</v>
+        <v>6823</v>
       </c>
       <c r="G1347" s="3">
         <v>2</v>
@@ -62703,19 +62703,19 @@
         <v>1353</v>
       </c>
       <c r="B1354" s="2" t="s">
+        <v>6912</v>
+      </c>
+      <c r="C1354" s="2" t="s">
         <v>6913</v>
       </c>
-      <c r="C1354" s="2" t="s">
+      <c r="D1354" s="2" t="s">
         <v>6914</v>
       </c>
-      <c r="D1354" s="2" t="s">
+      <c r="E1354" s="2" t="s">
         <v>6915</v>
       </c>
-      <c r="E1354" s="2" t="s">
+      <c r="F1354" s="2" t="s">
         <v>6916</v>
-      </c>
-      <c r="F1354" s="2" t="s">
-        <v>6917</v>
       </c>
       <c r="G1354" s="3">
         <v>1</v>
@@ -62761,7 +62761,7 @@
         <v>1355</v>
       </c>
       <c r="B1356" s="2" t="s">
-        <v>6788</v>
+        <v>6787</v>
       </c>
       <c r="C1356" s="2" t="s">
         <v>5554</v>
@@ -62770,10 +62770,10 @@
         <v>5555</v>
       </c>
       <c r="E1356" s="2" t="s">
+        <v>6788</v>
+      </c>
+      <c r="F1356" s="2" t="s">
         <v>6789</v>
-      </c>
-      <c r="F1356" s="2" t="s">
-        <v>6790</v>
       </c>
       <c r="G1356" s="3">
         <v>2</v>
@@ -62796,7 +62796,7 @@
         <v>5558</v>
       </c>
       <c r="D1357" s="2" t="s">
-        <v>6868</v>
+        <v>6867</v>
       </c>
       <c r="E1357" s="2" t="s">
         <v>5559</v>
@@ -63312,7 +63312,7 @@
         <v>1374</v>
       </c>
       <c r="B1375" s="2" t="s">
-        <v>6754</v>
+        <v>6753</v>
       </c>
       <c r="C1375" s="2" t="s">
         <v>5640</v>
@@ -63321,10 +63321,10 @@
         <v>5641</v>
       </c>
       <c r="E1375" s="2" t="s">
+        <v>6754</v>
+      </c>
+      <c r="F1375" s="2" t="s">
         <v>6755</v>
-      </c>
-      <c r="F1375" s="2" t="s">
-        <v>6756</v>
       </c>
       <c r="G1375" s="3">
         <v>1</v>
@@ -63962,7 +63962,7 @@
         <v>5716</v>
       </c>
       <c r="F1397" s="2" t="s">
-        <v>6999</v>
+        <v>6998</v>
       </c>
       <c r="G1397" s="3">
         <v>1</v>
@@ -63991,7 +63991,7 @@
         <v>5716</v>
       </c>
       <c r="F1398" s="2" t="s">
-        <v>6999</v>
+        <v>6998</v>
       </c>
       <c r="G1398" s="3">
         <v>3</v>
